--- a/Inventory_KNIME.xlsx
+++ b/Inventory_KNIME.xlsx
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>316.211</v>
+        <v>229.14100000000002</v>
       </c>
       <c r="F37" t="n">
         <v>2208.447</v>
@@ -1431,10 +1431,10 @@
         <v>3.0469999999999997</v>
       </c>
       <c r="H37" t="n">
-        <v>229.622</v>
+        <v>229.14100000000002</v>
       </c>
       <c r="I37" t="n">
-        <v>86.589</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="38">
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1969.384</v>
+        <v>1292.076</v>
       </c>
       <c r="F38" t="n">
         <v>281.326</v>
@@ -1468,10 +1468,10 @@
         <v>186.057</v>
       </c>
       <c r="H38" t="n">
-        <v>1293.952</v>
+        <v>1292.076</v>
       </c>
       <c r="I38" t="n">
-        <v>675.432</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="39">
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2279.739</v>
+        <v>0.156</v>
       </c>
       <c r="F42" t="n">
         <v>2322.892</v>
@@ -1619,7 +1619,7 @@
         <v>0.156</v>
       </c>
       <c r="I42" t="n">
-        <v>2279.583</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="43">
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1041.707</v>
+        <v>1041.133</v>
       </c>
       <c r="F43" t="n">
         <v>17.094</v>
@@ -1653,7 +1653,7 @@
         <v>0.0</v>
       </c>
       <c r="H43" t="n">
-        <v>1041.707</v>
+        <v>1041.133</v>
       </c>
       <c r="I43" t="n">
         <v>0.0</v>
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>774.49</v>
+        <v>168.367</v>
       </c>
       <c r="F45" t="n">
         <v>767.595</v>
@@ -1730,7 +1730,7 @@
         <v>168.367</v>
       </c>
       <c r="I45" t="n">
-        <v>606.123</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="46">
@@ -2532,7 +2532,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>21.744</v>
+        <v>0.0</v>
       </c>
       <c r="F67" t="n">
         <v>0.0</v>
@@ -2541,7 +2541,7 @@
         <v>0.0</v>
       </c>
       <c r="H67" t="n">
-        <v>21.744</v>
+        <v>0.0</v>
       </c>
       <c r="I67" t="n">
         <v>0.0</v>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5.184</v>
+        <v>0.0</v>
       </c>
       <c r="F68" t="n">
         <v>0.0</v>
@@ -2578,7 +2578,7 @@
         <v>0.0</v>
       </c>
       <c r="H68" t="n">
-        <v>5.184</v>
+        <v>0.0</v>
       </c>
       <c r="I68" t="n">
         <v>0.0</v>
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>141.351</v>
+        <v>140.81799999999998</v>
       </c>
       <c r="F74" t="n">
         <v>3.467</v>
@@ -2800,7 +2800,7 @@
         <v>0.0</v>
       </c>
       <c r="H74" t="n">
-        <v>141.351</v>
+        <v>140.81799999999998</v>
       </c>
       <c r="I74" t="n">
         <v>0.0</v>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2857.8</v>
+        <v>2854.6000000000004</v>
       </c>
       <c r="F77" t="n">
         <v>1.2</v>
@@ -2911,7 +2911,7 @@
         <v>0.0</v>
       </c>
       <c r="H77" t="n">
-        <v>2857.8</v>
+        <v>2854.6000000000004</v>
       </c>
       <c r="I77" t="n">
         <v>0.0</v>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1922.372</v>
+        <v>1921.305</v>
       </c>
       <c r="F78" t="n">
         <v>5.067</v>
@@ -2948,7 +2948,7 @@
         <v>17.069000000000003</v>
       </c>
       <c r="H78" t="n">
-        <v>1922.372</v>
+        <v>1921.305</v>
       </c>
       <c r="I78" t="n">
         <v>0.0</v>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>380.58</v>
+        <v>380.313</v>
       </c>
       <c r="F79" t="n">
         <v>0.0</v>
@@ -2985,7 +2985,7 @@
         <v>4.267</v>
       </c>
       <c r="H79" t="n">
-        <v>380.58</v>
+        <v>380.313</v>
       </c>
       <c r="I79" t="n">
         <v>0.0</v>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1418.08</v>
+        <v>1950.694</v>
       </c>
       <c r="F80" t="n">
         <v>6.666</v>
@@ -3022,10 +3022,10 @@
         <v>0.0</v>
       </c>
       <c r="H80" t="n">
-        <v>1418.08</v>
+        <v>1426.302</v>
       </c>
       <c r="I80" t="n">
-        <v>0.0</v>
+        <v>524.392</v>
       </c>
     </row>
     <row r="81">
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>7677.493</v>
+        <v>7675.093</v>
       </c>
       <c r="F82" t="n">
         <v>10.401</v>
@@ -3096,7 +3096,7 @@
         <v>17.069000000000003</v>
       </c>
       <c r="H82" t="n">
-        <v>7677.493</v>
+        <v>7675.093</v>
       </c>
       <c r="I82" t="n">
         <v>0.0</v>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1247.355</v>
+        <v>1247.088</v>
       </c>
       <c r="F84" t="n">
         <v>50.94</v>
@@ -3170,7 +3170,7 @@
         <v>0.0</v>
       </c>
       <c r="H84" t="n">
-        <v>1247.355</v>
+        <v>1247.088</v>
       </c>
       <c r="I84" t="n">
         <v>0.0</v>
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>924.0</v>
+        <v>0.0</v>
       </c>
       <c r="F103" t="n">
         <v>21.0</v>
@@ -3873,7 +3873,7 @@
         <v>0.0</v>
       </c>
       <c r="H103" t="n">
-        <v>924.0</v>
+        <v>0.0</v>
       </c>
       <c r="I103" t="n">
         <v>0.0</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1043.503</v>
+        <v>1043.501</v>
       </c>
       <c r="F114" t="n">
         <v>0.0</v>
@@ -4280,7 +4280,7 @@
         <v>0.834</v>
       </c>
       <c r="H114" t="n">
-        <v>1043.503</v>
+        <v>1043.501</v>
       </c>
       <c r="I114" t="n">
         <v>0.0</v>
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>839.505</v>
+        <v>839.504</v>
       </c>
       <c r="F115" t="n">
         <v>0.0</v>
@@ -4317,7 +4317,7 @@
         <v>0.27799999999999997</v>
       </c>
       <c r="H115" t="n">
-        <v>839.505</v>
+        <v>839.504</v>
       </c>
       <c r="I115" t="n">
         <v>0.0</v>
@@ -4974,7 +4974,7 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5.96</v>
+        <v>293.6</v>
       </c>
       <c r="F133" t="n">
         <v>0.24000000000000002</v>
@@ -4983,10 +4983,10 @@
         <v>0.48000000000000004</v>
       </c>
       <c r="H133" t="n">
-        <v>5.96</v>
+        <v>5.6000000000000005</v>
       </c>
       <c r="I133" t="n">
-        <v>0.0</v>
+        <v>288.0</v>
       </c>
     </row>
     <row r="134">
@@ -5011,7 +5011,7 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2.364</v>
+        <v>487.689</v>
       </c>
       <c r="F134" t="n">
         <v>0.0</v>
@@ -5020,10 +5020,10 @@
         <v>0.675</v>
       </c>
       <c r="H134" t="n">
-        <v>2.364</v>
+        <v>1.689</v>
       </c>
       <c r="I134" t="n">
-        <v>0.0</v>
+        <v>486.0</v>
       </c>
     </row>
     <row r="135">
@@ -5048,7 +5048,7 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5914.959</v>
+        <v>5914.773999999999</v>
       </c>
       <c r="F135" t="n">
         <v>0.0</v>
@@ -5057,7 +5057,7 @@
         <v>0.0</v>
       </c>
       <c r="H135" t="n">
-        <v>5914.959</v>
+        <v>5914.773999999999</v>
       </c>
       <c r="I135" t="n">
         <v>0.0</v>
@@ -5159,7 +5159,7 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1284.5949999999998</v>
+        <v>988.04</v>
       </c>
       <c r="F138" t="n">
         <v>0.0</v>
@@ -5168,10 +5168,10 @@
         <v>0.0</v>
       </c>
       <c r="H138" t="n">
-        <v>988.2249999999999</v>
+        <v>988.04</v>
       </c>
       <c r="I138" t="n">
-        <v>296.37</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="139">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>219.72</v>
+        <v>218.88</v>
       </c>
       <c r="F139" t="n">
         <v>0.48000000000000004</v>
@@ -5205,7 +5205,7 @@
         <v>0.04</v>
       </c>
       <c r="H139" t="n">
-        <v>219.72</v>
+        <v>218.88</v>
       </c>
       <c r="I139" t="n">
         <v>0.0</v>
@@ -5862,7 +5862,7 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>727.0</v>
+        <v>1228.0</v>
       </c>
       <c r="F157" t="n">
         <v>0.0</v>
@@ -5874,7 +5874,7 @@
         <v>727.0</v>
       </c>
       <c r="I157" t="n">
-        <v>0.0</v>
+        <v>501.0</v>
       </c>
     </row>
     <row r="158">
@@ -6423,7 +6423,7 @@
         <v>37.947</v>
       </c>
       <c r="G172" t="n">
-        <v>5030.021</v>
+        <v>3313.649</v>
       </c>
       <c r="H172" t="n">
         <v>11634.161</v>
@@ -6571,7 +6571,7 @@
         <v>67.2</v>
       </c>
       <c r="G176" t="n">
-        <v>8.0</v>
+        <v>14.4</v>
       </c>
       <c r="H176" t="n">
         <v>10740.0</v>
@@ -7601,7 +7601,7 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1731.464</v>
+        <v>1726.5629999999999</v>
       </c>
       <c r="F204" t="n">
         <v>0.46799999999999997</v>
@@ -7610,7 +7610,7 @@
         <v>4.201</v>
       </c>
       <c r="H204" t="n">
-        <v>1731.464</v>
+        <v>1726.5629999999999</v>
       </c>
       <c r="I204" t="n">
         <v>0.0</v>
@@ -7638,7 +7638,7 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>3300.972</v>
+        <v>3308.206</v>
       </c>
       <c r="F205" t="n">
         <v>1.168</v>
@@ -7647,7 +7647,7 @@
         <v>18.32</v>
       </c>
       <c r="H205" t="n">
-        <v>3300.972</v>
+        <v>3308.206</v>
       </c>
       <c r="I205" t="n">
         <v>0.0</v>
@@ -7897,7 +7897,7 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>287.625</v>
+        <v>289.125</v>
       </c>
       <c r="F212" t="n">
         <v>0.0</v>
@@ -7906,7 +7906,7 @@
         <v>0.0</v>
       </c>
       <c r="H212" t="n">
-        <v>287.625</v>
+        <v>289.125</v>
       </c>
       <c r="I212" t="n">
         <v>0.0</v>
@@ -7971,7 +7971,7 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>643.284</v>
+        <v>643.2819999999999</v>
       </c>
       <c r="F214" t="n">
         <v>0.0</v>
@@ -7980,7 +7980,7 @@
         <v>0.0</v>
       </c>
       <c r="H214" t="n">
-        <v>643.284</v>
+        <v>643.2819999999999</v>
       </c>
       <c r="I214" t="n">
         <v>0.0</v>
@@ -8082,7 +8082,7 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>318.031</v>
+        <v>317.858</v>
       </c>
       <c r="F217" t="n">
         <v>0.0</v>
@@ -8091,7 +8091,7 @@
         <v>0.859</v>
       </c>
       <c r="H217" t="n">
-        <v>318.031</v>
+        <v>317.858</v>
       </c>
       <c r="I217" t="n">
         <v>0.0</v>
@@ -8156,7 +8156,7 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>733.585</v>
+        <v>740.114</v>
       </c>
       <c r="F219" t="n">
         <v>1.374</v>
@@ -8165,7 +8165,7 @@
         <v>0.34400000000000003</v>
       </c>
       <c r="H219" t="n">
-        <v>733.585</v>
+        <v>740.114</v>
       </c>
       <c r="I219" t="n">
         <v>0.0</v>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>897.3100000000001</v>
+        <v>896.1650000000001</v>
       </c>
       <c r="F224" t="n">
         <v>0.0</v>
@@ -8350,7 +8350,7 @@
         <v>0.0</v>
       </c>
       <c r="H224" t="n">
-        <v>897.3100000000001</v>
+        <v>896.1650000000001</v>
       </c>
       <c r="I224" t="n">
         <v>0.0</v>
@@ -8378,7 +8378,7 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>203.92600000000002</v>
+        <v>203.296</v>
       </c>
       <c r="F225" t="n">
         <v>0.0</v>
@@ -8387,7 +8387,7 @@
         <v>0.0</v>
       </c>
       <c r="H225" t="n">
-        <v>203.92600000000002</v>
+        <v>203.296</v>
       </c>
       <c r="I225" t="n">
         <v>0.0</v>
@@ -8452,7 +8452,7 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>2007.539</v>
+        <v>2001.526</v>
       </c>
       <c r="F227" t="n">
         <v>0.859</v>
@@ -8461,7 +8461,7 @@
         <v>0.34400000000000003</v>
       </c>
       <c r="H227" t="n">
-        <v>2007.539</v>
+        <v>2001.526</v>
       </c>
       <c r="I227" t="n">
         <v>0.0</v>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>817.825</v>
+        <v>818.4540000000001</v>
       </c>
       <c r="F229" t="n">
         <v>0.057</v>
@@ -8535,7 +8535,7 @@
         <v>0.0</v>
       </c>
       <c r="H229" t="n">
-        <v>817.825</v>
+        <v>818.4540000000001</v>
       </c>
       <c r="I229" t="n">
         <v>0.0</v>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>1272.808</v>
+        <v>1280.252</v>
       </c>
       <c r="F235" t="n">
         <v>0.34400000000000003</v>
@@ -8757,7 +8757,7 @@
         <v>0.0</v>
       </c>
       <c r="H235" t="n">
-        <v>1272.808</v>
+        <v>1280.252</v>
       </c>
       <c r="I235" t="n">
         <v>0.0</v>
@@ -8859,7 +8859,7 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>1644.0</v>
+        <v>5652.0</v>
       </c>
       <c r="F238" t="n">
         <v>6.0</v>
@@ -8871,7 +8871,7 @@
         <v>1644.0</v>
       </c>
       <c r="I238" t="n">
-        <v>0.0</v>
+        <v>4008.0</v>
       </c>
     </row>
     <row r="239">
@@ -9599,7 +9599,7 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>23.2</v>
+        <v>426.4</v>
       </c>
       <c r="F258" t="n">
         <v>267.0</v>
@@ -9611,7 +9611,7 @@
         <v>23.2</v>
       </c>
       <c r="I258" t="n">
-        <v>0.0</v>
+        <v>403.2</v>
       </c>
     </row>
     <row r="259">
@@ -9747,16 +9747,16 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>5198.851</v>
+        <v>5195.183999999999</v>
       </c>
       <c r="F262" t="n">
         <v>49.864</v>
       </c>
       <c r="G262" t="n">
-        <v>65.508</v>
+        <v>3239.964</v>
       </c>
       <c r="H262" t="n">
-        <v>5198.851</v>
+        <v>5195.183999999999</v>
       </c>
       <c r="I262" t="n">
         <v>0.0</v>
@@ -9784,16 +9784,16 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6282.9980000000005</v>
+        <v>6281.264</v>
       </c>
       <c r="F263" t="n">
         <v>1.7329999999999999</v>
       </c>
       <c r="G263" t="n">
-        <v>1154.1570000000002</v>
+        <v>222.454</v>
       </c>
       <c r="H263" t="n">
-        <v>6282.9980000000005</v>
+        <v>6281.264</v>
       </c>
       <c r="I263" t="n">
         <v>0.0</v>
@@ -10080,7 +10080,7 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>1544.8</v>
+        <v>1540.2</v>
       </c>
       <c r="F271" t="n">
         <v>5.4</v>
@@ -10089,7 +10089,7 @@
         <v>0.8</v>
       </c>
       <c r="H271" t="n">
-        <v>1544.8</v>
+        <v>1540.2</v>
       </c>
       <c r="I271" t="n">
         <v>0.0</v>
@@ -10154,7 +10154,7 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>319.656</v>
+        <v>319.24</v>
       </c>
       <c r="F273" t="n">
         <v>0.13899999999999998</v>
@@ -10163,7 +10163,7 @@
         <v>604.1959999999999</v>
       </c>
       <c r="H273" t="n">
-        <v>319.656</v>
+        <v>319.24</v>
       </c>
       <c r="I273" t="n">
         <v>0.0</v>
@@ -10228,7 +10228,7 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>263.59999999999997</v>
+        <v>263.4</v>
       </c>
       <c r="F275" t="n">
         <v>0.8</v>
@@ -10237,7 +10237,7 @@
         <v>0.0</v>
       </c>
       <c r="H275" t="n">
-        <v>263.59999999999997</v>
+        <v>263.4</v>
       </c>
       <c r="I275" t="n">
         <v>0.0</v>
@@ -10265,7 +10265,7 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>5042.944</v>
+        <v>5040.512000000001</v>
       </c>
       <c r="F276" t="n">
         <v>1.31</v>
@@ -10274,7 +10274,7 @@
         <v>0.047</v>
       </c>
       <c r="H276" t="n">
-        <v>5042.944</v>
+        <v>5040.512000000001</v>
       </c>
       <c r="I276" t="n">
         <v>0.0</v>
@@ -10302,7 +10302,7 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>2582.548</v>
+        <v>2578.9939999999997</v>
       </c>
       <c r="F277" t="n">
         <v>4.166</v>
@@ -10311,7 +10311,7 @@
         <v>0.0</v>
       </c>
       <c r="H277" t="n">
-        <v>2582.548</v>
+        <v>2578.9939999999997</v>
       </c>
       <c r="I277" t="n">
         <v>0.0</v>
@@ -10339,7 +10339,7 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>3493.328</v>
+        <v>3490.569</v>
       </c>
       <c r="F278" t="n">
         <v>3.367</v>
@@ -10348,7 +10348,7 @@
         <v>0.281</v>
       </c>
       <c r="H278" t="n">
-        <v>3493.328</v>
+        <v>3490.569</v>
       </c>
       <c r="I278" t="n">
         <v>0.0</v>
@@ -10561,7 +10561,7 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>17890.780600000002</v>
+        <v>9749.824</v>
       </c>
       <c r="F284" t="n">
         <v>0.0</v>
@@ -10573,7 +10573,7 @@
         <v>9749.824</v>
       </c>
       <c r="I284" t="n">
-        <v>8140.9566</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="285">
@@ -10783,7 +10783,7 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>543.321</v>
+        <v>543.2810000000001</v>
       </c>
       <c r="F290" t="n">
         <v>0.24000000000000002</v>
@@ -10792,7 +10792,7 @@
         <v>0.0</v>
       </c>
       <c r="H290" t="n">
-        <v>543.321</v>
+        <v>543.2810000000001</v>
       </c>
       <c r="I290" t="n">
         <v>0.0</v>
@@ -10857,7 +10857,7 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>371.52000000000004</v>
+        <v>371.44</v>
       </c>
       <c r="F292" t="n">
         <v>0.0</v>
@@ -10866,7 +10866,7 @@
         <v>0.44</v>
       </c>
       <c r="H292" t="n">
-        <v>371.52000000000004</v>
+        <v>371.44</v>
       </c>
       <c r="I292" t="n">
         <v>0.0</v>
@@ -11042,7 +11042,7 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>4113.0</v>
+        <v>5523.0</v>
       </c>
       <c r="F297" t="n">
         <v>0.2</v>
@@ -11054,7 +11054,7 @@
         <v>4113.0</v>
       </c>
       <c r="I297" t="n">
-        <v>0.0</v>
+        <v>1410.0</v>
       </c>
     </row>
     <row r="298">
@@ -11079,7 +11079,7 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>3813.842</v>
+        <v>3829.841</v>
       </c>
       <c r="F298" t="n">
         <v>3.111</v>
@@ -11088,7 +11088,7 @@
         <v>18.665000000000003</v>
       </c>
       <c r="H298" t="n">
-        <v>3813.842</v>
+        <v>3829.841</v>
       </c>
       <c r="I298" t="n">
         <v>0.0</v>
@@ -11116,7 +11116,7 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>6632.002</v>
+        <v>6631.113</v>
       </c>
       <c r="F299" t="n">
         <v>0.222</v>
@@ -11125,7 +11125,7 @@
         <v>31.996999999999996</v>
       </c>
       <c r="H299" t="n">
-        <v>6632.002</v>
+        <v>6631.113</v>
       </c>
       <c r="I299" t="n">
         <v>0.0</v>
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>1353.1970000000001</v>
+        <v>1349.642</v>
       </c>
       <c r="F300" t="n">
         <v>0.0</v>
@@ -11162,7 +11162,7 @@
         <v>0.0</v>
       </c>
       <c r="H300" t="n">
-        <v>1353.1970000000001</v>
+        <v>1349.642</v>
       </c>
       <c r="I300" t="n">
         <v>0.0</v>
@@ -11190,7 +11190,7 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>1714.495</v>
+        <v>4295.5702</v>
       </c>
       <c r="F301" t="n">
         <v>0.222</v>
@@ -11202,7 +11202,7 @@
         <v>1714.495</v>
       </c>
       <c r="I301" t="n">
-        <v>0.0</v>
+        <v>2581.0752</v>
       </c>
     </row>
     <row r="302">
@@ -11227,7 +11227,7 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>3551.708</v>
+        <v>5399.036</v>
       </c>
       <c r="F302" t="n">
         <v>0.0</v>
@@ -11239,7 +11239,7 @@
         <v>3551.708</v>
       </c>
       <c r="I302" t="n">
-        <v>0.0</v>
+        <v>1847.328</v>
       </c>
     </row>
     <row r="303">
@@ -11560,7 +11560,7 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>2142.0</v>
+        <v>2141.0</v>
       </c>
       <c r="F311" t="n">
         <v>0.8</v>
@@ -11569,7 +11569,7 @@
         <v>6.4</v>
       </c>
       <c r="H311" t="n">
-        <v>2142.0</v>
+        <v>2141.0</v>
       </c>
       <c r="I311" t="n">
         <v>0.0</v>
@@ -11597,16 +11597,16 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>1996.0</v>
+        <v>1995.6000000000001</v>
       </c>
       <c r="F312" t="n">
         <v>8.4</v>
       </c>
       <c r="G312" t="n">
-        <v>10.4</v>
+        <v>6.6</v>
       </c>
       <c r="H312" t="n">
-        <v>1996.0</v>
+        <v>1995.6000000000001</v>
       </c>
       <c r="I312" t="n">
         <v>0.0</v>
@@ -11634,7 +11634,7 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>192.4</v>
+        <v>190.0</v>
       </c>
       <c r="F313" t="n">
         <v>2.0</v>
@@ -11643,7 +11643,7 @@
         <v>7.2</v>
       </c>
       <c r="H313" t="n">
-        <v>192.4</v>
+        <v>190.0</v>
       </c>
       <c r="I313" t="n">
         <v>0.0</v>
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>391.0</v>
+        <v>388.8</v>
       </c>
       <c r="F314" t="n">
         <v>0.2</v>
@@ -11680,7 +11680,7 @@
         <v>0.0</v>
       </c>
       <c r="H314" t="n">
-        <v>391.0</v>
+        <v>388.8</v>
       </c>
       <c r="I314" t="n">
         <v>0.0</v>
@@ -11708,7 +11708,7 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>241.58499999999998</v>
+        <v>241.05200000000002</v>
       </c>
       <c r="F315" t="n">
         <v>0.533</v>
@@ -11717,7 +11717,7 @@
         <v>0.0</v>
       </c>
       <c r="H315" t="n">
-        <v>241.58499999999998</v>
+        <v>241.05200000000002</v>
       </c>
       <c r="I315" t="n">
         <v>0.0</v>
@@ -11819,7 +11819,7 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>5673.779</v>
+        <v>5670.046</v>
       </c>
       <c r="F318" t="n">
         <v>0.533</v>
@@ -11828,7 +11828,7 @@
         <v>0.0</v>
       </c>
       <c r="H318" t="n">
-        <v>5673.779</v>
+        <v>5670.046</v>
       </c>
       <c r="I318" t="n">
         <v>0.0</v>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>1986.0</v>
+        <v>1990.4</v>
       </c>
       <c r="F326" t="n">
         <v>14.0</v>
@@ -12124,7 +12124,7 @@
         <v>121.6</v>
       </c>
       <c r="H326" t="n">
-        <v>1986.0</v>
+        <v>1990.4</v>
       </c>
       <c r="I326" t="n">
         <v>0.0</v>
@@ -12300,7 +12300,7 @@
         </is>
       </c>
       <c r="E331" t="n">
-        <v>2911.285</v>
+        <v>2910.218</v>
       </c>
       <c r="F331" t="n">
         <v>0.0</v>
@@ -12309,7 +12309,7 @@
         <v>0.0</v>
       </c>
       <c r="H331" t="n">
-        <v>2911.285</v>
+        <v>2910.218</v>
       </c>
       <c r="I331" t="n">
         <v>0.0</v>
@@ -12337,7 +12337,7 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>12956.552</v>
+        <v>12956.286</v>
       </c>
       <c r="F332" t="n">
         <v>0.533</v>
@@ -12346,7 +12346,7 @@
         <v>0.0</v>
       </c>
       <c r="H332" t="n">
-        <v>12956.552</v>
+        <v>12956.286</v>
       </c>
       <c r="I332" t="n">
         <v>0.0</v>
@@ -12522,7 +12522,7 @@
         </is>
       </c>
       <c r="E337" t="n">
-        <v>2676.4</v>
+        <v>2675.7999999999997</v>
       </c>
       <c r="F337" t="n">
         <v>1.6</v>
@@ -12531,7 +12531,7 @@
         <v>0.0</v>
       </c>
       <c r="H337" t="n">
-        <v>2676.4</v>
+        <v>2675.7999999999997</v>
       </c>
       <c r="I337" t="n">
         <v>0.0</v>
@@ -12744,7 +12744,7 @@
         </is>
       </c>
       <c r="E343" t="n">
-        <v>293.2</v>
+        <v>266.0</v>
       </c>
       <c r="F343" t="n">
         <v>4.0</v>
@@ -12753,7 +12753,7 @@
         <v>0.0</v>
       </c>
       <c r="H343" t="n">
-        <v>293.2</v>
+        <v>266.0</v>
       </c>
       <c r="I343" t="n">
         <v>0.0</v>
@@ -12855,7 +12855,7 @@
         </is>
       </c>
       <c r="E346" t="n">
-        <v>2615.3999999999996</v>
+        <v>2516.16</v>
       </c>
       <c r="F346" t="n">
         <v>1.56</v>
@@ -12864,10 +12864,10 @@
         <v>5.760000000000001</v>
       </c>
       <c r="H346" t="n">
-        <v>2520.8399999999997</v>
+        <v>2516.16</v>
       </c>
       <c r="I346" t="n">
-        <v>94.56</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="347">
@@ -12892,7 +12892,7 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>3702.263</v>
+        <v>3703.163</v>
       </c>
       <c r="F347" t="n">
         <v>0.45</v>
@@ -12901,7 +12901,7 @@
         <v>1.575</v>
       </c>
       <c r="H347" t="n">
-        <v>3702.263</v>
+        <v>3703.163</v>
       </c>
       <c r="I347" t="n">
         <v>0.0</v>
@@ -12929,7 +12929,7 @@
         </is>
       </c>
       <c r="E348" t="n">
-        <v>5733.289</v>
+        <v>6234.5470000000005</v>
       </c>
       <c r="F348" t="n">
         <v>0.0</v>
@@ -12938,10 +12938,10 @@
         <v>0.555</v>
       </c>
       <c r="H348" t="n">
-        <v>5733.289</v>
+        <v>5735.0470000000005</v>
       </c>
       <c r="I348" t="n">
-        <v>0.0</v>
+        <v>499.5</v>
       </c>
     </row>
     <row r="349">
@@ -13484,7 +13484,7 @@
         </is>
       </c>
       <c r="E363" t="n">
-        <v>1736.0</v>
+        <v>2226.0</v>
       </c>
       <c r="F363" t="n">
         <v>0.0</v>
@@ -13496,7 +13496,7 @@
         <v>1736.0</v>
       </c>
       <c r="I363" t="n">
-        <v>0.0</v>
+        <v>490.0</v>
       </c>
     </row>
     <row r="364">
@@ -13854,7 +13854,7 @@
         </is>
       </c>
       <c r="E373" t="n">
-        <v>578.472</v>
+        <v>566.47</v>
       </c>
       <c r="F373" t="n">
         <v>20.003</v>
@@ -13863,7 +13863,7 @@
         <v>0.0</v>
       </c>
       <c r="H373" t="n">
-        <v>578.472</v>
+        <v>566.47</v>
       </c>
       <c r="I373" t="n">
         <v>0.0</v>
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="E375" t="n">
-        <v>194.15699999999998</v>
+        <v>147.218</v>
       </c>
       <c r="F375" t="n">
         <v>28.804</v>
@@ -13937,7 +13937,7 @@
         <v>9.601</v>
       </c>
       <c r="H375" t="n">
-        <v>194.15699999999998</v>
+        <v>147.218</v>
       </c>
       <c r="I375" t="n">
         <v>0.0</v>
@@ -13965,7 +13965,7 @@
         </is>
       </c>
       <c r="E376" t="n">
-        <v>1019.482</v>
+        <v>1579.9299999999998</v>
       </c>
       <c r="F376" t="n">
         <v>0.0</v>
@@ -13977,7 +13977,7 @@
         <v>1019.482</v>
       </c>
       <c r="I376" t="n">
-        <v>0.0</v>
+        <v>560.448</v>
       </c>
     </row>
     <row r="377">
@@ -14076,7 +14076,7 @@
         </is>
       </c>
       <c r="E379" t="n">
-        <v>7960.473</v>
+        <v>10736.026</v>
       </c>
       <c r="F379" t="n">
         <v>2.669</v>
@@ -14085,10 +14085,10 @@
         <v>2.891</v>
       </c>
       <c r="H379" t="n">
-        <v>7960.473</v>
+        <v>6532.666</v>
       </c>
       <c r="I379" t="n">
-        <v>0.0</v>
+        <v>4203.36</v>
       </c>
     </row>
     <row r="380">
@@ -14594,7 +14594,7 @@
         </is>
       </c>
       <c r="E393" t="n">
-        <v>2179.152</v>
+        <v>2161.3920000000003</v>
       </c>
       <c r="F393" t="n">
         <v>0.0</v>
@@ -14603,7 +14603,7 @@
         <v>0.0</v>
       </c>
       <c r="H393" t="n">
-        <v>2179.152</v>
+        <v>2161.3920000000003</v>
       </c>
       <c r="I393" t="n">
         <v>0.0</v>
@@ -14705,16 +14705,16 @@
         </is>
       </c>
       <c r="E396" t="n">
-        <v>1294.287</v>
+        <v>1118.278</v>
       </c>
       <c r="F396" t="n">
         <v>37.335</v>
       </c>
       <c r="G396" t="n">
-        <v>153.341</v>
+        <v>987.383</v>
       </c>
       <c r="H396" t="n">
-        <v>1294.287</v>
+        <v>1118.278</v>
       </c>
       <c r="I396" t="n">
         <v>0.0</v>
@@ -14742,16 +14742,16 @@
         </is>
       </c>
       <c r="E397" t="n">
-        <v>3823.145</v>
+        <v>3749.475</v>
       </c>
       <c r="F397" t="n">
         <v>12.656</v>
       </c>
       <c r="G397" t="n">
-        <v>976.9910000000001</v>
+        <v>1152.101</v>
       </c>
       <c r="H397" t="n">
-        <v>3823.145</v>
+        <v>3749.475</v>
       </c>
       <c r="I397" t="n">
         <v>0.0</v>
@@ -14853,7 +14853,7 @@
         </is>
       </c>
       <c r="E400" t="n">
-        <v>70.0</v>
+        <v>69.0</v>
       </c>
       <c r="F400" t="n">
         <v>0.0</v>
@@ -14862,7 +14862,7 @@
         <v>0.0</v>
       </c>
       <c r="H400" t="n">
-        <v>70.0</v>
+        <v>69.0</v>
       </c>
       <c r="I400" t="n">
         <v>0.0</v>
@@ -15445,7 +15445,7 @@
         </is>
       </c>
       <c r="E416" t="n">
-        <v>3994.75</v>
+        <v>2741.9500000000003</v>
       </c>
       <c r="F416" t="n">
         <v>0.05</v>
@@ -15454,10 +15454,10 @@
         <v>1.8</v>
       </c>
       <c r="H416" t="n">
-        <v>2736.25</v>
+        <v>2741.9500000000003</v>
       </c>
       <c r="I416" t="n">
-        <v>1258.5</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="417">
@@ -15482,7 +15482,7 @@
         </is>
       </c>
       <c r="E417" t="n">
-        <v>1805.2</v>
+        <v>1806.8500000000001</v>
       </c>
       <c r="F417" t="n">
         <v>0.0</v>
@@ -15491,7 +15491,7 @@
         <v>0.1</v>
       </c>
       <c r="H417" t="n">
-        <v>1805.2</v>
+        <v>1806.8500000000001</v>
       </c>
       <c r="I417" t="n">
         <v>0.0</v>
@@ -15519,7 +15519,7 @@
         </is>
       </c>
       <c r="E418" t="n">
-        <v>1804.3</v>
+        <v>1803.3500000000001</v>
       </c>
       <c r="F418" t="n">
         <v>0.0</v>
@@ -15528,7 +15528,7 @@
         <v>0.0</v>
       </c>
       <c r="H418" t="n">
-        <v>1804.3</v>
+        <v>1803.3500000000001</v>
       </c>
       <c r="I418" t="n">
         <v>0.0</v>
@@ -15556,7 +15556,7 @@
         </is>
       </c>
       <c r="E419" t="n">
-        <v>2207.75</v>
+        <v>1941.4</v>
       </c>
       <c r="F419" t="n">
         <v>0.05</v>
@@ -15565,10 +15565,10 @@
         <v>0.0</v>
       </c>
       <c r="H419" t="n">
-        <v>1938.95</v>
+        <v>1941.4</v>
       </c>
       <c r="I419" t="n">
-        <v>268.8</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="420">
@@ -15593,7 +15593,7 @@
         </is>
       </c>
       <c r="E420" t="n">
-        <v>2300.85</v>
+        <v>2306.15</v>
       </c>
       <c r="F420" t="n">
         <v>0.1</v>
@@ -15602,7 +15602,7 @@
         <v>0.3</v>
       </c>
       <c r="H420" t="n">
-        <v>2300.85</v>
+        <v>2306.15</v>
       </c>
       <c r="I420" t="n">
         <v>0.0</v>
@@ -15630,7 +15630,7 @@
         </is>
       </c>
       <c r="E421" t="n">
-        <v>2863.45</v>
+        <v>2866.6</v>
       </c>
       <c r="F421" t="n">
         <v>0.15</v>
@@ -15639,7 +15639,7 @@
         <v>0.0</v>
       </c>
       <c r="H421" t="n">
-        <v>2863.45</v>
+        <v>2866.6</v>
       </c>
       <c r="I421" t="n">
         <v>0.0</v>
@@ -15667,7 +15667,7 @@
         </is>
       </c>
       <c r="E422" t="n">
-        <v>3598.8</v>
+        <v>1619.1</v>
       </c>
       <c r="F422" t="n">
         <v>0.5</v>
@@ -15676,10 +15676,10 @@
         <v>0.0</v>
       </c>
       <c r="H422" t="n">
-        <v>1623.3</v>
+        <v>1619.1</v>
       </c>
       <c r="I422" t="n">
-        <v>1975.5</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="423">
@@ -16074,7 +16074,7 @@
         </is>
       </c>
       <c r="E433" t="n">
-        <v>871.1999999999999</v>
+        <v>1231.1999999999998</v>
       </c>
       <c r="F433" t="n">
         <v>0.0</v>
@@ -16086,7 +16086,7 @@
         <v>871.1999999999999</v>
       </c>
       <c r="I433" t="n">
-        <v>0.0</v>
+        <v>360.0</v>
       </c>
     </row>
     <row r="434">
@@ -16370,7 +16370,7 @@
         </is>
       </c>
       <c r="E441" t="n">
-        <v>1526.1529</v>
+        <v>416.641</v>
       </c>
       <c r="F441" t="n">
         <v>62.225</v>
@@ -16379,10 +16379,10 @@
         <v>4.107</v>
       </c>
       <c r="H441" t="n">
-        <v>423.31600000000003</v>
+        <v>416.641</v>
       </c>
       <c r="I441" t="n">
-        <v>1102.8369</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="442">
@@ -16407,7 +16407,7 @@
         </is>
       </c>
       <c r="E442" t="n">
-        <v>2654.0632</v>
+        <v>484.075</v>
       </c>
       <c r="F442" t="n">
         <v>194.34199999999998</v>
@@ -16416,10 +16416,10 @@
         <v>0.0</v>
       </c>
       <c r="H442" t="n">
-        <v>464.81899999999996</v>
+        <v>484.075</v>
       </c>
       <c r="I442" t="n">
-        <v>2189.2442</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="443">
@@ -16444,7 +16444,7 @@
         </is>
       </c>
       <c r="E443" t="n">
-        <v>6297.861000000001</v>
+        <v>4221.7570000000005</v>
       </c>
       <c r="F443" t="n">
         <v>0.0</v>
@@ -16456,7 +16456,7 @@
         <v>4221.7570000000005</v>
       </c>
       <c r="I443" t="n">
-        <v>2076.104</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="444">
@@ -16481,7 +16481,7 @@
         </is>
       </c>
       <c r="E444" t="n">
-        <v>1105.4879999999998</v>
+        <v>1108.9109999999998</v>
       </c>
       <c r="F444" t="n">
         <v>2.054</v>
@@ -16490,7 +16490,7 @@
         <v>2.054</v>
       </c>
       <c r="H444" t="n">
-        <v>1105.4879999999998</v>
+        <v>1108.9109999999998</v>
       </c>
       <c r="I444" t="n">
         <v>0.0</v>
@@ -16518,7 +16518,7 @@
         </is>
       </c>
       <c r="E445" t="n">
-        <v>624.041</v>
+        <v>618.907</v>
       </c>
       <c r="F445" t="n">
         <v>0.0</v>
@@ -16527,7 +16527,7 @@
         <v>0.9349999999999999</v>
       </c>
       <c r="H445" t="n">
-        <v>624.041</v>
+        <v>618.907</v>
       </c>
       <c r="I445" t="n">
         <v>0.0</v>
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="E446" t="n">
-        <v>6979.616</v>
+        <v>6995.661</v>
       </c>
       <c r="F446" t="n">
         <v>445.752</v>
@@ -16564,7 +16564,7 @@
         <v>1.75</v>
       </c>
       <c r="H446" t="n">
-        <v>6979.616</v>
+        <v>6995.661</v>
       </c>
       <c r="I446" t="n">
         <v>0.0</v>
@@ -16629,7 +16629,7 @@
         </is>
       </c>
       <c r="E448" t="n">
-        <v>3075.4139999999998</v>
+        <v>3070.7459999999996</v>
       </c>
       <c r="F448" t="n">
         <v>0.0</v>
@@ -16638,7 +16638,7 @@
         <v>15.405999999999999</v>
       </c>
       <c r="H448" t="n">
-        <v>3075.4139999999998</v>
+        <v>3070.7459999999996</v>
       </c>
       <c r="I448" t="n">
         <v>0.0</v>
@@ -16666,7 +16666,7 @@
         </is>
       </c>
       <c r="E449" t="n">
-        <v>7532.876499999999</v>
+        <v>7104.8679999999995</v>
       </c>
       <c r="F449" t="n">
         <v>0.0</v>
@@ -16675,10 +16675,10 @@
         <v>31.273000000000003</v>
       </c>
       <c r="H449" t="n">
-        <v>7087.597</v>
+        <v>7104.8679999999995</v>
       </c>
       <c r="I449" t="n">
-        <v>445.2795</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="450">
@@ -16703,7 +16703,7 @@
         </is>
       </c>
       <c r="E450" t="n">
-        <v>8371.156</v>
+        <v>8384.691</v>
       </c>
       <c r="F450" t="n">
         <v>5.601</v>
@@ -16712,7 +16712,7 @@
         <v>50.879</v>
       </c>
       <c r="H450" t="n">
-        <v>8371.156</v>
+        <v>8384.691</v>
       </c>
       <c r="I450" t="n">
         <v>0.0</v>
@@ -16740,7 +16740,7 @@
         </is>
       </c>
       <c r="E451" t="n">
-        <v>1845.405</v>
+        <v>1851.531</v>
       </c>
       <c r="F451" t="n">
         <v>212.371</v>
@@ -16749,7 +16749,7 @@
         <v>7.001</v>
       </c>
       <c r="H451" t="n">
-        <v>1845.405</v>
+        <v>1851.531</v>
       </c>
       <c r="I451" t="n">
         <v>0.0</v>
@@ -16777,7 +16777,7 @@
         </is>
       </c>
       <c r="E452" t="n">
-        <v>1469.0829999999999</v>
+        <v>1173.865</v>
       </c>
       <c r="F452" t="n">
         <v>294.922</v>
@@ -16786,10 +16786,10 @@
         <v>3.5010000000000003</v>
       </c>
       <c r="H452" t="n">
-        <v>1171.532</v>
+        <v>1173.865</v>
       </c>
       <c r="I452" t="n">
-        <v>297.551</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="453">
@@ -16820,7 +16820,7 @@
         <v>3.3609999999999998</v>
       </c>
       <c r="G453" t="n">
-        <v>2.1</v>
+        <v>1.6800000000000002</v>
       </c>
       <c r="H453" t="n">
         <v>910.825</v>
@@ -16888,7 +16888,7 @@
         </is>
       </c>
       <c r="E455" t="n">
-        <v>853.849</v>
+        <v>677.0680000000001</v>
       </c>
       <c r="F455" t="n">
         <v>0.0</v>
@@ -16897,10 +16897,10 @@
         <v>0.292</v>
       </c>
       <c r="H455" t="n">
-        <v>678.8190000000001</v>
+        <v>677.0680000000001</v>
       </c>
       <c r="I455" t="n">
-        <v>175.03</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="456">
@@ -16925,7 +16925,7 @@
         </is>
       </c>
       <c r="E456" t="n">
-        <v>3893.248</v>
+        <v>3897.916</v>
       </c>
       <c r="F456" t="n">
         <v>380.69399999999996</v>
@@ -16934,7 +16934,7 @@
         <v>0.292</v>
       </c>
       <c r="H456" t="n">
-        <v>3893.248</v>
+        <v>3897.916</v>
       </c>
       <c r="I456" t="n">
         <v>0.0</v>
@@ -16962,7 +16962,7 @@
         </is>
       </c>
       <c r="E457" t="n">
-        <v>2524.208</v>
+        <v>2525.083</v>
       </c>
       <c r="F457" t="n">
         <v>0.0</v>
@@ -16971,7 +16971,7 @@
         <v>1.75</v>
       </c>
       <c r="H457" t="n">
-        <v>2524.208</v>
+        <v>2525.083</v>
       </c>
       <c r="I457" t="n">
         <v>0.0</v>
@@ -17036,7 +17036,7 @@
         </is>
       </c>
       <c r="E459" t="n">
-        <v>9.043</v>
+        <v>1.75</v>
       </c>
       <c r="F459" t="n">
         <v>0.0</v>
@@ -17045,7 +17045,7 @@
         <v>0.0</v>
       </c>
       <c r="H459" t="n">
-        <v>9.043</v>
+        <v>1.75</v>
       </c>
       <c r="I459" t="n">
         <v>0.0</v>
@@ -17443,7 +17443,7 @@
         </is>
       </c>
       <c r="E470" t="n">
-        <v>262.966</v>
+        <v>262.433</v>
       </c>
       <c r="F470" t="n">
         <v>0.0</v>
@@ -17452,7 +17452,7 @@
         <v>0.0</v>
       </c>
       <c r="H470" t="n">
-        <v>262.966</v>
+        <v>262.433</v>
       </c>
       <c r="I470" t="n">
         <v>0.0</v>
@@ -17480,7 +17480,7 @@
         </is>
       </c>
       <c r="E471" t="n">
-        <v>758.813</v>
+        <v>757.546</v>
       </c>
       <c r="F471" t="n">
         <v>0.0</v>
@@ -17489,7 +17489,7 @@
         <v>0.0</v>
       </c>
       <c r="H471" t="n">
-        <v>758.813</v>
+        <v>757.546</v>
       </c>
       <c r="I471" t="n">
         <v>0.0</v>
@@ -17813,7 +17813,7 @@
         </is>
       </c>
       <c r="E480" t="n">
-        <v>1014.102</v>
+        <v>1014.1009999999999</v>
       </c>
       <c r="F480" t="n">
         <v>0.0</v>
@@ -17822,7 +17822,7 @@
         <v>0.0</v>
       </c>
       <c r="H480" t="n">
-        <v>1014.102</v>
+        <v>1014.1009999999999</v>
       </c>
       <c r="I480" t="n">
         <v>0.0</v>
@@ -17924,7 +17924,7 @@
         </is>
       </c>
       <c r="E483" t="n">
-        <v>367.87699999999995</v>
+        <v>366.75199999999995</v>
       </c>
       <c r="F483" t="n">
         <v>0.675</v>
@@ -17933,7 +17933,7 @@
         <v>0.0</v>
       </c>
       <c r="H483" t="n">
-        <v>367.87699999999995</v>
+        <v>366.75199999999995</v>
       </c>
       <c r="I483" t="n">
         <v>0.0</v>
@@ -17961,7 +17961,7 @@
         </is>
       </c>
       <c r="E484" t="n">
-        <v>969.75</v>
+        <v>969.525</v>
       </c>
       <c r="F484" t="n">
         <v>0.0</v>
@@ -17970,7 +17970,7 @@
         <v>0.0</v>
       </c>
       <c r="H484" t="n">
-        <v>969.75</v>
+        <v>969.525</v>
       </c>
       <c r="I484" t="n">
         <v>0.0</v>
@@ -18035,7 +18035,7 @@
         </is>
       </c>
       <c r="E486" t="n">
-        <v>741.406</v>
+        <v>725.7660000000001</v>
       </c>
       <c r="F486" t="n">
         <v>0.0</v>
@@ -18044,10 +18044,10 @@
         <v>0.115</v>
       </c>
       <c r="H486" t="n">
-        <v>724.846</v>
+        <v>725.7660000000001</v>
       </c>
       <c r="I486" t="n">
-        <v>16.56</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="487">
@@ -18072,7 +18072,7 @@
         </is>
       </c>
       <c r="E487" t="n">
-        <v>225.60799999999998</v>
+        <v>225.42299999999997</v>
       </c>
       <c r="F487" t="n">
         <v>0.13899999999999998</v>
@@ -18081,7 +18081,7 @@
         <v>662.67</v>
       </c>
       <c r="H487" t="n">
-        <v>225.60799999999998</v>
+        <v>225.42299999999997</v>
       </c>
       <c r="I487" t="n">
         <v>0.0</v>
@@ -18109,7 +18109,7 @@
         </is>
       </c>
       <c r="E488" t="n">
-        <v>1290.8</v>
+        <v>1236.92</v>
       </c>
       <c r="F488" t="n">
         <v>0.0</v>
@@ -18118,10 +18118,10 @@
         <v>1.9200000000000002</v>
       </c>
       <c r="H488" t="n">
-        <v>1238.96</v>
+        <v>1236.92</v>
       </c>
       <c r="I488" t="n">
-        <v>51.84</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="489">
@@ -18146,7 +18146,7 @@
         </is>
       </c>
       <c r="E489" t="n">
-        <v>201.48000000000002</v>
+        <v>202.32</v>
       </c>
       <c r="F489" t="n">
         <v>0.0</v>
@@ -18155,7 +18155,7 @@
         <v>606.24</v>
       </c>
       <c r="H489" t="n">
-        <v>201.48000000000002</v>
+        <v>202.32</v>
       </c>
       <c r="I489" t="n">
         <v>0.0</v>
@@ -18183,7 +18183,7 @@
         </is>
       </c>
       <c r="E490" t="n">
-        <v>2376.972</v>
+        <v>2353.339</v>
       </c>
       <c r="F490" t="n">
         <v>0.231</v>
@@ -18192,10 +18192,10 @@
         <v>0.0</v>
       </c>
       <c r="H490" t="n">
-        <v>2355.882</v>
+        <v>2353.339</v>
       </c>
       <c r="I490" t="n">
-        <v>21.09</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="491">
@@ -18220,7 +18220,7 @@
         </is>
       </c>
       <c r="E491" t="n">
-        <v>249.6</v>
+        <v>250.07999999999998</v>
       </c>
       <c r="F491" t="n">
         <v>0.9600000000000001</v>
@@ -18229,7 +18229,7 @@
         <v>0.0</v>
       </c>
       <c r="H491" t="n">
-        <v>249.6</v>
+        <v>250.07999999999998</v>
       </c>
       <c r="I491" t="n">
         <v>0.0</v>
@@ -18257,7 +18257,7 @@
         </is>
       </c>
       <c r="E492" t="n">
-        <v>3140.19</v>
+        <v>3138.201</v>
       </c>
       <c r="F492" t="n">
         <v>0.462</v>
@@ -18266,7 +18266,7 @@
         <v>1.11</v>
       </c>
       <c r="H492" t="n">
-        <v>3140.19</v>
+        <v>3138.201</v>
       </c>
       <c r="I492" t="n">
         <v>0.0</v>
@@ -18294,7 +18294,7 @@
         </is>
       </c>
       <c r="E493" t="n">
-        <v>64.39999999999999</v>
+        <v>63.31999999999999</v>
       </c>
       <c r="F493" t="n">
         <v>0.48000000000000004</v>
@@ -18303,7 +18303,7 @@
         <v>0.0</v>
       </c>
       <c r="H493" t="n">
-        <v>64.39999999999999</v>
+        <v>63.31999999999999</v>
       </c>
       <c r="I493" t="n">
         <v>0.0</v>
@@ -18331,7 +18331,7 @@
         </is>
       </c>
       <c r="E494" t="n">
-        <v>2389.876</v>
+        <v>2383.725</v>
       </c>
       <c r="F494" t="n">
         <v>0.925</v>
@@ -18340,7 +18340,7 @@
         <v>0.0</v>
       </c>
       <c r="H494" t="n">
-        <v>2389.876</v>
+        <v>2383.725</v>
       </c>
       <c r="I494" t="n">
         <v>0.0</v>
@@ -18368,7 +18368,7 @@
         </is>
       </c>
       <c r="E495" t="n">
-        <v>597.256</v>
+        <v>597.117</v>
       </c>
       <c r="F495" t="n">
         <v>0.0</v>
@@ -18377,7 +18377,7 @@
         <v>0.0</v>
       </c>
       <c r="H495" t="n">
-        <v>597.256</v>
+        <v>597.117</v>
       </c>
       <c r="I495" t="n">
         <v>0.0</v>
@@ -18442,7 +18442,7 @@
         </is>
       </c>
       <c r="E497" t="n">
-        <v>427.782</v>
+        <v>428.19800000000004</v>
       </c>
       <c r="F497" t="n">
         <v>0.0</v>
@@ -18451,7 +18451,7 @@
         <v>533.27</v>
       </c>
       <c r="H497" t="n">
-        <v>427.782</v>
+        <v>428.19800000000004</v>
       </c>
       <c r="I497" t="n">
         <v>0.0</v>
@@ -18516,19 +18516,19 @@
         </is>
       </c>
       <c r="E499" t="n">
-        <v>6824.338599999999</v>
+        <v>3043.65</v>
       </c>
       <c r="F499" t="n">
         <v>52.003</v>
       </c>
       <c r="G499" t="n">
-        <v>729.703</v>
+        <v>1820.424</v>
       </c>
       <c r="H499" t="n">
-        <v>3078.8179999999998</v>
+        <v>3043.65</v>
       </c>
       <c r="I499" t="n">
-        <v>3745.5206</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="500">
@@ -18553,16 +18553,16 @@
         </is>
       </c>
       <c r="E500" t="n">
-        <v>6986.217</v>
+        <v>6967.552</v>
       </c>
       <c r="F500" t="n">
         <v>18.665999999999997</v>
       </c>
       <c r="G500" t="n">
-        <v>3841.463</v>
+        <v>3843.329</v>
       </c>
       <c r="H500" t="n">
-        <v>6986.217</v>
+        <v>6967.552</v>
       </c>
       <c r="I500" t="n">
         <v>0.0</v>
@@ -18590,19 +18590,19 @@
         </is>
       </c>
       <c r="E501" t="n">
-        <v>6287.5545999999995</v>
+        <v>2546.302</v>
       </c>
       <c r="F501" t="n">
         <v>22.488</v>
       </c>
       <c r="G501" t="n">
-        <v>235.10600000000002</v>
+        <v>603.0980000000001</v>
       </c>
       <c r="H501" t="n">
-        <v>2563.68</v>
+        <v>2546.302</v>
       </c>
       <c r="I501" t="n">
-        <v>3723.8745999999996</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="502">
@@ -18627,19 +18627,19 @@
         </is>
       </c>
       <c r="E502" t="n">
-        <v>8198.800000000001</v>
+        <v>5083.4</v>
       </c>
       <c r="F502" t="n">
         <v>76.0</v>
       </c>
       <c r="G502" t="n">
-        <v>748.8000000000001</v>
+        <v>2255.2</v>
       </c>
       <c r="H502" t="n">
-        <v>3888.4</v>
+        <v>3856.2</v>
       </c>
       <c r="I502" t="n">
-        <v>4310.400000000001</v>
+        <v>1227.2</v>
       </c>
     </row>
     <row r="503">
@@ -19626,7 +19626,7 @@
         </is>
       </c>
       <c r="E529" t="n">
-        <v>2.5</v>
+        <v>254.5</v>
       </c>
       <c r="F529" t="n">
         <v>281.5</v>
@@ -19638,7 +19638,7 @@
         <v>2.5</v>
       </c>
       <c r="I529" t="n">
-        <v>0.0</v>
+        <v>252.0</v>
       </c>
     </row>
     <row r="530">
@@ -20181,7 +20181,7 @@
         </is>
       </c>
       <c r="E544" t="n">
-        <v>1477.767</v>
+        <v>1480.633</v>
       </c>
       <c r="F544" t="n">
         <v>43.101</v>
@@ -20190,7 +20190,7 @@
         <v>0.313</v>
       </c>
       <c r="H544" t="n">
-        <v>1477.767</v>
+        <v>1480.633</v>
       </c>
       <c r="I544" t="n">
         <v>0.0</v>
@@ -20255,7 +20255,7 @@
         </is>
       </c>
       <c r="E546" t="n">
-        <v>2740.585</v>
+        <v>2739.7659999999996</v>
       </c>
       <c r="F546" t="n">
         <v>2609.918</v>
@@ -20264,7 +20264,7 @@
         <v>2.999</v>
       </c>
       <c r="H546" t="n">
-        <v>2740.585</v>
+        <v>2739.7659999999996</v>
       </c>
       <c r="I546" t="n">
         <v>0.0</v>
@@ -20625,16 +20625,16 @@
         </is>
       </c>
       <c r="E556" t="n">
-        <v>9388.135</v>
+        <v>9345.633</v>
       </c>
       <c r="F556" t="n">
         <v>15.001000000000001</v>
       </c>
       <c r="G556" t="n">
-        <v>51.003</v>
+        <v>52.336</v>
       </c>
       <c r="H556" t="n">
-        <v>9388.135</v>
+        <v>9345.633</v>
       </c>
       <c r="I556" t="n">
         <v>0.0</v>
@@ -20662,19 +20662,19 @@
         </is>
       </c>
       <c r="E557" t="n">
-        <v>6617.253199999999</v>
+        <v>4273.408</v>
       </c>
       <c r="F557" t="n">
         <v>22.39</v>
       </c>
       <c r="G557" t="n">
-        <v>4150.482</v>
+        <v>4048.789</v>
       </c>
       <c r="H557" t="n">
-        <v>3205.922</v>
+        <v>3129.364</v>
       </c>
       <c r="I557" t="n">
-        <v>3411.3311999999996</v>
+        <v>1144.044</v>
       </c>
     </row>
     <row r="558">
@@ -20699,7 +20699,7 @@
         </is>
       </c>
       <c r="E558" t="n">
-        <v>1845.2420000000002</v>
+        <v>1791.085</v>
       </c>
       <c r="F558" t="n">
         <v>9.413</v>
@@ -20708,7 +20708,7 @@
         <v>684.356</v>
       </c>
       <c r="H558" t="n">
-        <v>1845.2420000000002</v>
+        <v>1791.085</v>
       </c>
       <c r="I558" t="n">
         <v>0.0</v>
@@ -21698,7 +21698,7 @@
         </is>
       </c>
       <c r="E585" t="n">
-        <v>437.551</v>
+        <v>437.54900000000004</v>
       </c>
       <c r="F585" t="n">
         <v>0.0</v>
@@ -21707,7 +21707,7 @@
         <v>0.0</v>
       </c>
       <c r="H585" t="n">
-        <v>437.551</v>
+        <v>437.54900000000004</v>
       </c>
       <c r="I585" t="n">
         <v>0.0</v>
@@ -21735,7 +21735,7 @@
         </is>
       </c>
       <c r="E586" t="n">
-        <v>5993.688</v>
+        <v>5980.764</v>
       </c>
       <c r="F586" t="n">
         <v>4.615</v>
@@ -21744,7 +21744,7 @@
         <v>5.539</v>
       </c>
       <c r="H586" t="n">
-        <v>5993.688</v>
+        <v>5980.764</v>
       </c>
       <c r="I586" t="n">
         <v>0.0</v>
@@ -21883,7 +21883,7 @@
         </is>
       </c>
       <c r="E590" t="n">
-        <v>21.184</v>
+        <v>10.383999999999999</v>
       </c>
       <c r="F590" t="n">
         <v>3.738</v>
@@ -21892,7 +21892,7 @@
         <v>0.0</v>
       </c>
       <c r="H590" t="n">
-        <v>21.184</v>
+        <v>10.383999999999999</v>
       </c>
       <c r="I590" t="n">
         <v>0.0</v>
@@ -21920,7 +21920,7 @@
         </is>
       </c>
       <c r="E591" t="n">
-        <v>774.02</v>
+        <v>767.097</v>
       </c>
       <c r="F591" t="n">
         <v>6.0</v>
@@ -21929,7 +21929,7 @@
         <v>9.231</v>
       </c>
       <c r="H591" t="n">
-        <v>774.02</v>
+        <v>767.097</v>
       </c>
       <c r="I591" t="n">
         <v>0.0</v>
@@ -21994,7 +21994,7 @@
         </is>
       </c>
       <c r="E593" t="n">
-        <v>1761.275</v>
+        <v>1761.2749999999999</v>
       </c>
       <c r="F593" t="n">
         <v>0.0</v>
@@ -22003,7 +22003,7 @@
         <v>0.0</v>
       </c>
       <c r="H593" t="n">
-        <v>1761.275</v>
+        <v>1761.2749999999999</v>
       </c>
       <c r="I593" t="n">
         <v>0.0</v>
@@ -22327,7 +22327,7 @@
         </is>
       </c>
       <c r="E602" t="n">
-        <v>6573.789</v>
+        <v>6572.3099999999995</v>
       </c>
       <c r="F602" t="n">
         <v>0.0</v>
@@ -22336,7 +22336,7 @@
         <v>14.201</v>
       </c>
       <c r="H602" t="n">
-        <v>6573.789</v>
+        <v>6572.3099999999995</v>
       </c>
       <c r="I602" t="n">
         <v>0.0</v>
@@ -22364,7 +22364,7 @@
         </is>
       </c>
       <c r="E603" t="n">
-        <v>4187.312</v>
+        <v>4486.4156</v>
       </c>
       <c r="F603" t="n">
         <v>1.331</v>
@@ -22373,10 +22373,10 @@
         <v>15.383000000000001</v>
       </c>
       <c r="H603" t="n">
-        <v>2820.485</v>
+        <v>2807.1710000000003</v>
       </c>
       <c r="I603" t="n">
-        <v>1366.827</v>
+        <v>1679.2446</v>
       </c>
     </row>
     <row r="604">
@@ -22475,7 +22475,7 @@
         </is>
       </c>
       <c r="E606" t="n">
-        <v>12425.255000000001</v>
+        <v>12444.336000000001</v>
       </c>
       <c r="F606" t="n">
         <v>2.81</v>
@@ -22484,7 +22484,7 @@
         <v>76.329</v>
       </c>
       <c r="H606" t="n">
-        <v>12425.255000000001</v>
+        <v>12444.336000000001</v>
       </c>
       <c r="I606" t="n">
         <v>0.0</v>
@@ -22512,7 +22512,7 @@
         </is>
       </c>
       <c r="E607" t="n">
-        <v>8441.603</v>
+        <v>8963.494999999999</v>
       </c>
       <c r="F607" t="n">
         <v>0.0</v>
@@ -22524,7 +22524,7 @@
         <v>8441.603</v>
       </c>
       <c r="I607" t="n">
-        <v>0.0</v>
+        <v>521.892</v>
       </c>
     </row>
     <row r="608">
@@ -22549,7 +22549,7 @@
         </is>
       </c>
       <c r="E608" t="n">
-        <v>397.6216</v>
+        <v>310.198</v>
       </c>
       <c r="F608" t="n">
         <v>2.663</v>
@@ -22558,10 +22558,10 @@
         <v>0.888</v>
       </c>
       <c r="H608" t="n">
-        <v>315.967</v>
+        <v>310.198</v>
       </c>
       <c r="I608" t="n">
-        <v>81.6546</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="609">
@@ -24103,7 +24103,7 @@
         </is>
       </c>
       <c r="E650" t="n">
-        <v>439.5882</v>
+        <v>367.073</v>
       </c>
       <c r="F650" t="n">
         <v>2.81</v>
@@ -24115,7 +24115,7 @@
         <v>367.073</v>
       </c>
       <c r="I650" t="n">
-        <v>72.5152</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="651">
@@ -24251,7 +24251,7 @@
         </is>
       </c>
       <c r="E654" t="n">
-        <v>1552.312</v>
+        <v>1552.3100000000002</v>
       </c>
       <c r="F654" t="n">
         <v>0.0</v>
@@ -24260,7 +24260,7 @@
         <v>1.5</v>
       </c>
       <c r="H654" t="n">
-        <v>1552.312</v>
+        <v>1552.3100000000002</v>
       </c>
       <c r="I654" t="n">
         <v>0.0</v>
@@ -24288,7 +24288,7 @@
         </is>
       </c>
       <c r="E655" t="n">
-        <v>6295.6994</v>
+        <v>5100.077</v>
       </c>
       <c r="F655" t="n">
         <v>0.0</v>
@@ -24300,7 +24300,7 @@
         <v>5100.077</v>
       </c>
       <c r="I655" t="n">
-        <v>1195.6224</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="656">
@@ -24325,7 +24325,7 @@
         </is>
       </c>
       <c r="E656" t="n">
-        <v>1671.496</v>
+        <v>1668.163</v>
       </c>
       <c r="F656" t="n">
         <v>0.4</v>
@@ -24334,7 +24334,7 @@
         <v>0.0</v>
       </c>
       <c r="H656" t="n">
-        <v>1671.496</v>
+        <v>1668.163</v>
       </c>
       <c r="I656" t="n">
         <v>0.0</v>
@@ -24405,7 +24405,7 @@
         <v>3.5</v>
       </c>
       <c r="G658" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="H658" t="n">
         <v>3761.5</v>
@@ -24479,7 +24479,7 @@
         <v>1.0</v>
       </c>
       <c r="G660" t="n">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="H660" t="n">
         <v>3515.5</v>
@@ -24658,7 +24658,7 @@
         </is>
       </c>
       <c r="E665" t="n">
-        <v>1599.271</v>
+        <v>1595.579</v>
       </c>
       <c r="F665" t="n">
         <v>1.385</v>
@@ -24667,7 +24667,7 @@
         <v>11.077</v>
       </c>
       <c r="H665" t="n">
-        <v>1599.271</v>
+        <v>1595.579</v>
       </c>
       <c r="I665" t="n">
         <v>0.0</v>
@@ -24769,7 +24769,7 @@
         </is>
       </c>
       <c r="E668" t="n">
-        <v>2344.019</v>
+        <v>2372.2729999999997</v>
       </c>
       <c r="F668" t="n">
         <v>6.944</v>
@@ -24778,7 +24778,7 @@
         <v>5.325</v>
       </c>
       <c r="H668" t="n">
-        <v>2344.019</v>
+        <v>2372.2729999999997</v>
       </c>
       <c r="I668" t="n">
         <v>0.0</v>
@@ -24806,7 +24806,7 @@
         </is>
       </c>
       <c r="E669" t="n">
-        <v>2920.632</v>
+        <v>2920.6310000000003</v>
       </c>
       <c r="F669" t="n">
         <v>0.0</v>
@@ -24815,7 +24815,7 @@
         <v>1.183</v>
       </c>
       <c r="H669" t="n">
-        <v>2920.632</v>
+        <v>2920.6310000000003</v>
       </c>
       <c r="I669" t="n">
         <v>0.0</v>
@@ -24843,7 +24843,7 @@
         </is>
       </c>
       <c r="E670" t="n">
-        <v>2223.6094000000003</v>
+        <v>642.587</v>
       </c>
       <c r="F670" t="n">
         <v>0.0</v>
@@ -24855,7 +24855,7 @@
         <v>642.587</v>
       </c>
       <c r="I670" t="n">
-        <v>1581.0224</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="671">
@@ -24880,7 +24880,7 @@
         </is>
       </c>
       <c r="E671" t="n">
-        <v>154.73</v>
+        <v>122.778</v>
       </c>
       <c r="F671" t="n">
         <v>11.235999999999999</v>
@@ -24889,7 +24889,7 @@
         <v>0.0</v>
       </c>
       <c r="H671" t="n">
-        <v>154.73</v>
+        <v>122.778</v>
       </c>
       <c r="I671" t="n">
         <v>0.0</v>
@@ -24917,7 +24917,7 @@
         </is>
       </c>
       <c r="E672" t="n">
-        <v>30.468</v>
+        <v>12.864</v>
       </c>
       <c r="F672" t="n">
         <v>7.093</v>
@@ -24926,7 +24926,7 @@
         <v>0.0</v>
       </c>
       <c r="H672" t="n">
-        <v>30.468</v>
+        <v>12.864</v>
       </c>
       <c r="I672" t="n">
         <v>0.0</v>
@@ -24991,7 +24991,7 @@
         </is>
       </c>
       <c r="E674" t="n">
-        <v>296.734</v>
+        <v>272.77</v>
       </c>
       <c r="F674" t="n">
         <v>5.762</v>
@@ -25000,7 +25000,7 @@
         <v>0.0</v>
       </c>
       <c r="H674" t="n">
-        <v>296.734</v>
+        <v>272.77</v>
       </c>
       <c r="I674" t="n">
         <v>0.0</v>
@@ -25028,7 +25028,7 @@
         </is>
       </c>
       <c r="E675" t="n">
-        <v>0.0</v>
+        <v>1368.0104000000001</v>
       </c>
       <c r="F675" t="n">
         <v>0.0</v>
@@ -25040,7 +25040,7 @@
         <v>0.0</v>
       </c>
       <c r="I675" t="n">
-        <v>0.0</v>
+        <v>1368.0104000000001</v>
       </c>
     </row>
     <row r="676">
@@ -25398,7 +25398,7 @@
         </is>
       </c>
       <c r="E685" t="n">
-        <v>5350.594</v>
+        <v>5430.177000000001</v>
       </c>
       <c r="F685" t="n">
         <v>51.473</v>
@@ -25407,7 +25407,7 @@
         <v>14.347999999999999</v>
       </c>
       <c r="H685" t="n">
-        <v>5350.594</v>
+        <v>5430.177000000001</v>
       </c>
       <c r="I685" t="n">
         <v>0.0</v>
@@ -25583,7 +25583,7 @@
         </is>
       </c>
       <c r="E690" t="n">
-        <v>3008.0469999999996</v>
+        <v>3014.8929999999996</v>
       </c>
       <c r="F690" t="n">
         <v>0.0</v>
@@ -25592,7 +25592,7 @@
         <v>0.0</v>
       </c>
       <c r="H690" t="n">
-        <v>3008.0469999999996</v>
+        <v>3014.8929999999996</v>
       </c>
       <c r="I690" t="n">
         <v>0.0</v>
@@ -25620,7 +25620,7 @@
         </is>
       </c>
       <c r="E691" t="n">
-        <v>7527.1179999999995</v>
+        <v>7530.23</v>
       </c>
       <c r="F691" t="n">
         <v>0.312</v>
@@ -25629,7 +25629,7 @@
         <v>0.0</v>
       </c>
       <c r="H691" t="n">
-        <v>7527.1179999999995</v>
+        <v>7530.23</v>
       </c>
       <c r="I691" t="n">
         <v>0.0</v>
@@ -26027,7 +26027,7 @@
         </is>
       </c>
       <c r="E702" t="n">
-        <v>2137.1071</v>
+        <v>28.434</v>
       </c>
       <c r="F702" t="n">
         <v>0.0</v>
@@ -26039,7 +26039,7 @@
         <v>28.434</v>
       </c>
       <c r="I702" t="n">
-        <v>2108.6731</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="703">
@@ -26101,7 +26101,7 @@
         </is>
       </c>
       <c r="E704" t="n">
-        <v>2994.724</v>
+        <v>2994.726</v>
       </c>
       <c r="F704" t="n">
         <v>0.0</v>
@@ -26110,7 +26110,7 @@
         <v>1.984</v>
       </c>
       <c r="H704" t="n">
-        <v>2994.724</v>
+        <v>2994.726</v>
       </c>
       <c r="I704" t="n">
         <v>0.0</v>
@@ -26212,16 +26212,16 @@
         </is>
       </c>
       <c r="E707" t="n">
-        <v>4700.481000000001</v>
+        <v>4761.780000000001</v>
       </c>
       <c r="F707" t="n">
         <v>2.491</v>
       </c>
       <c r="G707" t="n">
-        <v>6.846</v>
+        <v>5.601</v>
       </c>
       <c r="H707" t="n">
-        <v>4700.481000000001</v>
+        <v>4761.780000000001</v>
       </c>
       <c r="I707" t="n">
         <v>0.0</v>
@@ -26249,7 +26249,7 @@
         </is>
       </c>
       <c r="E708" t="n">
-        <v>9411.855</v>
+        <v>9513.295</v>
       </c>
       <c r="F708" t="n">
         <v>5.913</v>
@@ -26258,7 +26258,7 @@
         <v>9.334999999999999</v>
       </c>
       <c r="H708" t="n">
-        <v>9411.855</v>
+        <v>9513.295</v>
       </c>
       <c r="I708" t="n">
         <v>0.0</v>
@@ -26286,7 +26286,7 @@
         </is>
       </c>
       <c r="E709" t="n">
-        <v>3935.313</v>
+        <v>3935.3129999999996</v>
       </c>
       <c r="F709" t="n">
         <v>0.0</v>
@@ -26295,7 +26295,7 @@
         <v>3.851</v>
       </c>
       <c r="H709" t="n">
-        <v>3935.313</v>
+        <v>3935.3129999999996</v>
       </c>
       <c r="I709" t="n">
         <v>0.0</v>
@@ -26619,7 +26619,7 @@
         </is>
       </c>
       <c r="E718" t="n">
-        <v>1762.295</v>
+        <v>1762.2949999999998</v>
       </c>
       <c r="F718" t="n">
         <v>0.16699999999999998</v>
@@ -26628,7 +26628,7 @@
         <v>10.996</v>
       </c>
       <c r="H718" t="n">
-        <v>1762.295</v>
+        <v>1762.2949999999998</v>
       </c>
       <c r="I718" t="n">
         <v>0.0</v>
@@ -26730,7 +26730,7 @@
         </is>
       </c>
       <c r="E721" t="n">
-        <v>408.7597</v>
+        <v>119.332</v>
       </c>
       <c r="F721" t="n">
         <v>0.0</v>
@@ -26742,7 +26742,7 @@
         <v>119.332</v>
       </c>
       <c r="I721" t="n">
-        <v>289.4277</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="722">
@@ -26884,7 +26884,7 @@
         <v>38.672</v>
       </c>
       <c r="G725" t="n">
-        <v>9.601</v>
+        <v>0.0</v>
       </c>
       <c r="H725" t="n">
         <v>1806.0929999999998</v>
@@ -26952,7 +26952,7 @@
         </is>
       </c>
       <c r="E727" t="n">
-        <v>621.678</v>
+        <v>637.413</v>
       </c>
       <c r="F727" t="n">
         <v>0.533</v>
@@ -26961,7 +26961,7 @@
         <v>0.0</v>
       </c>
       <c r="H727" t="n">
-        <v>621.678</v>
+        <v>637.413</v>
       </c>
       <c r="I727" t="n">
         <v>0.0</v>
@@ -26989,7 +26989,7 @@
         </is>
       </c>
       <c r="E728" t="n">
-        <v>3557.111</v>
+        <v>3555.511</v>
       </c>
       <c r="F728" t="n">
         <v>0.0</v>
@@ -26998,7 +26998,7 @@
         <v>0.0</v>
       </c>
       <c r="H728" t="n">
-        <v>3557.111</v>
+        <v>3555.511</v>
       </c>
       <c r="I728" t="n">
         <v>0.0</v>
@@ -27026,7 +27026,7 @@
         </is>
       </c>
       <c r="E729" t="n">
-        <v>32394.447999999997</v>
+        <v>32382.98</v>
       </c>
       <c r="F729" t="n">
         <v>24.802999999999997</v>
@@ -27035,7 +27035,7 @@
         <v>19.202</v>
       </c>
       <c r="H729" t="n">
-        <v>32394.447999999997</v>
+        <v>32382.98</v>
       </c>
       <c r="I729" t="n">
         <v>0.0</v>
@@ -27063,7 +27063,7 @@
         </is>
       </c>
       <c r="E730" t="n">
-        <v>2737.676</v>
+        <v>2737.409</v>
       </c>
       <c r="F730" t="n">
         <v>2.4</v>
@@ -27072,7 +27072,7 @@
         <v>1.6</v>
       </c>
       <c r="H730" t="n">
-        <v>2737.676</v>
+        <v>2737.409</v>
       </c>
       <c r="I730" t="n">
         <v>0.0</v>
@@ -27100,7 +27100,7 @@
         </is>
       </c>
       <c r="E731" t="n">
-        <v>1353.275</v>
+        <v>1458.355</v>
       </c>
       <c r="F731" t="n">
         <v>0.185</v>
@@ -27109,10 +27109,10 @@
         <v>0.555</v>
       </c>
       <c r="H731" t="n">
-        <v>1353.275</v>
+        <v>1358.455</v>
       </c>
       <c r="I731" t="n">
-        <v>0.0</v>
+        <v>99.9</v>
       </c>
     </row>
     <row r="732">
@@ -27137,7 +27137,7 @@
         </is>
       </c>
       <c r="E732" t="n">
-        <v>2216.68</v>
+        <v>2215.0</v>
       </c>
       <c r="F732" t="n">
         <v>0.0</v>
@@ -27146,7 +27146,7 @@
         <v>2.8800000000000003</v>
       </c>
       <c r="H732" t="n">
-        <v>2216.68</v>
+        <v>2215.0</v>
       </c>
       <c r="I732" t="n">
         <v>0.0</v>
@@ -27174,7 +27174,7 @@
         </is>
       </c>
       <c r="E733" t="n">
-        <v>3383.511</v>
+        <v>3382.494</v>
       </c>
       <c r="F733" t="n">
         <v>0.093</v>
@@ -27183,7 +27183,7 @@
         <v>0.555</v>
       </c>
       <c r="H733" t="n">
-        <v>3383.511</v>
+        <v>3382.494</v>
       </c>
       <c r="I733" t="n">
         <v>0.0</v>
@@ -27211,7 +27211,7 @@
         </is>
       </c>
       <c r="E734" t="n">
-        <v>1796.561</v>
+        <v>1797.761</v>
       </c>
       <c r="F734" t="n">
         <v>0.0</v>
@@ -27220,7 +27220,7 @@
         <v>0.0</v>
       </c>
       <c r="H734" t="n">
-        <v>1796.561</v>
+        <v>1797.761</v>
       </c>
       <c r="I734" t="n">
         <v>0.0</v>
@@ -27322,7 +27322,7 @@
         </is>
       </c>
       <c r="E737" t="n">
-        <v>284.04</v>
+        <v>298.08000000000004</v>
       </c>
       <c r="F737" t="n">
         <v>0.54</v>
@@ -27331,7 +27331,7 @@
         <v>0.40499999999999997</v>
       </c>
       <c r="H737" t="n">
-        <v>284.04</v>
+        <v>298.08000000000004</v>
       </c>
       <c r="I737" t="n">
         <v>0.0</v>
@@ -27507,7 +27507,7 @@
         </is>
       </c>
       <c r="E742" t="n">
-        <v>1988.853</v>
+        <v>1981.387</v>
       </c>
       <c r="F742" t="n">
         <v>133.858</v>
@@ -27516,7 +27516,7 @@
         <v>60.796</v>
       </c>
       <c r="H742" t="n">
-        <v>1988.853</v>
+        <v>1981.387</v>
       </c>
       <c r="I742" t="n">
         <v>0.0</v>
@@ -27840,7 +27840,7 @@
         </is>
       </c>
       <c r="E751" t="n">
-        <v>4312.882</v>
+        <v>4471.313999999999</v>
       </c>
       <c r="F751" t="n">
         <v>12.574</v>
@@ -27849,7 +27849,7 @@
         <v>2.5149999999999997</v>
       </c>
       <c r="H751" t="n">
-        <v>4312.882</v>
+        <v>4471.313999999999</v>
       </c>
       <c r="I751" t="n">
         <v>0.0</v>
@@ -27877,7 +27877,7 @@
         </is>
       </c>
       <c r="E752" t="n">
-        <v>324.409</v>
+        <v>301.775</v>
       </c>
       <c r="F752" t="n">
         <v>36.464999999999996</v>
@@ -27886,7 +27886,7 @@
         <v>0.0</v>
       </c>
       <c r="H752" t="n">
-        <v>324.409</v>
+        <v>301.775</v>
       </c>
       <c r="I752" t="n">
         <v>0.0</v>
@@ -28025,7 +28025,7 @@
         </is>
       </c>
       <c r="E756" t="n">
-        <v>30.064</v>
+        <v>23.673</v>
       </c>
       <c r="F756" t="n">
         <v>2.84</v>
@@ -28034,7 +28034,7 @@
         <v>0.0</v>
       </c>
       <c r="H756" t="n">
-        <v>30.064</v>
+        <v>23.673</v>
       </c>
       <c r="I756" t="n">
         <v>0.0</v>
@@ -28099,7 +28099,7 @@
         </is>
       </c>
       <c r="E758" t="n">
-        <v>5007.708</v>
+        <v>6161.557999999999</v>
       </c>
       <c r="F758" t="n">
         <v>0.0</v>
@@ -28111,7 +28111,7 @@
         <v>5007.708</v>
       </c>
       <c r="I758" t="n">
-        <v>0.0</v>
+        <v>1153.85</v>
       </c>
     </row>
     <row r="759">
@@ -28210,7 +28210,7 @@
         </is>
       </c>
       <c r="E761" t="n">
-        <v>6295.4053</v>
+        <v>6159.251</v>
       </c>
       <c r="F761" t="n">
         <v>0.0</v>
@@ -28222,7 +28222,7 @@
         <v>6159.251</v>
       </c>
       <c r="I761" t="n">
-        <v>136.1543</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="762">
@@ -28617,7 +28617,7 @@
         </is>
       </c>
       <c r="E772" t="n">
-        <v>1113.5900000000001</v>
+        <v>1133.22</v>
       </c>
       <c r="F772" t="n">
         <v>16.954</v>
@@ -28626,7 +28626,7 @@
         <v>0.0</v>
       </c>
       <c r="H772" t="n">
-        <v>1113.5900000000001</v>
+        <v>1133.22</v>
       </c>
       <c r="I772" t="n">
         <v>0.0</v>
@@ -28765,7 +28765,7 @@
         </is>
       </c>
       <c r="E776" t="n">
-        <v>13650.343</v>
+        <v>13789.27</v>
       </c>
       <c r="F776" t="n">
         <v>54.001</v>
@@ -28774,7 +28774,7 @@
         <v>5.539</v>
       </c>
       <c r="H776" t="n">
-        <v>13650.343</v>
+        <v>13789.27</v>
       </c>
       <c r="I776" t="n">
         <v>0.0</v>
@@ -28913,7 +28913,7 @@
         </is>
       </c>
       <c r="E780" t="n">
-        <v>2497.2070000000003</v>
+        <v>2515.8230000000003</v>
       </c>
       <c r="F780" t="n">
         <v>2.709</v>
@@ -28922,7 +28922,7 @@
         <v>2.0309999999999997</v>
       </c>
       <c r="H780" t="n">
-        <v>2497.2070000000003</v>
+        <v>2515.8230000000003</v>
       </c>
       <c r="I780" t="n">
         <v>0.0</v>
@@ -28950,7 +28950,7 @@
         </is>
       </c>
       <c r="E781" t="n">
-        <v>892.197</v>
+        <v>903.7049999999999</v>
       </c>
       <c r="F781" t="n">
         <v>0.0</v>
@@ -28959,7 +28959,7 @@
         <v>4.061999999999999</v>
       </c>
       <c r="H781" t="n">
-        <v>892.197</v>
+        <v>903.7049999999999</v>
       </c>
       <c r="I781" t="n">
         <v>0.0</v>
@@ -29024,7 +29024,7 @@
         </is>
       </c>
       <c r="E783" t="n">
-        <v>5891.018</v>
+        <v>5905.573</v>
       </c>
       <c r="F783" t="n">
         <v>5.412</v>
@@ -29033,7 +29033,7 @@
         <v>12.185</v>
       </c>
       <c r="H783" t="n">
-        <v>5891.018</v>
+        <v>5905.573</v>
       </c>
       <c r="I783" t="n">
         <v>0.0</v>
@@ -29172,7 +29172,7 @@
         </is>
       </c>
       <c r="E787" t="n">
-        <v>1438.4820000000002</v>
+        <v>1433.7440000000001</v>
       </c>
       <c r="F787" t="n">
         <v>0.0</v>
@@ -29181,7 +29181,7 @@
         <v>0.0</v>
       </c>
       <c r="H787" t="n">
-        <v>1438.4820000000002</v>
+        <v>1433.7440000000001</v>
       </c>
       <c r="I787" t="n">
         <v>0.0</v>
@@ -29246,7 +29246,7 @@
         </is>
       </c>
       <c r="E789" t="n">
-        <v>6473.192</v>
+        <v>6471.16</v>
       </c>
       <c r="F789" t="n">
         <v>0.0</v>
@@ -29255,7 +29255,7 @@
         <v>0.0</v>
       </c>
       <c r="H789" t="n">
-        <v>6473.192</v>
+        <v>6471.16</v>
       </c>
       <c r="I789" t="n">
         <v>0.0</v>
@@ -29320,7 +29320,7 @@
         </is>
       </c>
       <c r="E791" t="n">
-        <v>108.40100000000001</v>
+        <v>109.52099999999999</v>
       </c>
       <c r="F791" t="n">
         <v>0.0</v>
@@ -29329,7 +29329,7 @@
         <v>0.0</v>
       </c>
       <c r="H791" t="n">
-        <v>108.40100000000001</v>
+        <v>109.52099999999999</v>
       </c>
       <c r="I791" t="n">
         <v>0.0</v>
@@ -29394,7 +29394,7 @@
         </is>
       </c>
       <c r="E793" t="n">
-        <v>1273.355</v>
+        <v>1233.441</v>
       </c>
       <c r="F793" t="n">
         <v>0.925</v>
@@ -29403,10 +29403,10 @@
         <v>1.156</v>
       </c>
       <c r="H793" t="n">
-        <v>1250.045</v>
+        <v>1233.441</v>
       </c>
       <c r="I793" t="n">
-        <v>23.31</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="794">
@@ -29431,7 +29431,7 @@
         </is>
       </c>
       <c r="E794" t="n">
-        <v>675.713</v>
+        <v>676.961</v>
       </c>
       <c r="F794" t="n">
         <v>5.18</v>
@@ -29440,7 +29440,7 @@
         <v>0.0</v>
       </c>
       <c r="H794" t="n">
-        <v>675.713</v>
+        <v>676.961</v>
       </c>
       <c r="I794" t="n">
         <v>0.0</v>
@@ -29505,7 +29505,7 @@
         </is>
       </c>
       <c r="E796" t="n">
-        <v>14.84</v>
+        <v>373.04</v>
       </c>
       <c r="F796" t="n">
         <v>0.0</v>
@@ -29514,10 +29514,10 @@
         <v>0.5199999999999999</v>
       </c>
       <c r="H796" t="n">
-        <v>14.84</v>
+        <v>13.04</v>
       </c>
       <c r="I796" t="n">
-        <v>0.0</v>
+        <v>360.0</v>
       </c>
     </row>
     <row r="797">
@@ -29653,7 +29653,7 @@
         </is>
       </c>
       <c r="E800" t="n">
-        <v>2448.441</v>
+        <v>1353.7079999999999</v>
       </c>
       <c r="F800" t="n">
         <v>14.556</v>
@@ -29662,10 +29662,10 @@
         <v>9.704</v>
       </c>
       <c r="H800" t="n">
-        <v>1395.5569999999998</v>
+        <v>1353.7079999999999</v>
       </c>
       <c r="I800" t="n">
-        <v>1052.884</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="801">
@@ -29690,7 +29690,7 @@
         </is>
       </c>
       <c r="E801" t="n">
-        <v>2490.2889999999998</v>
+        <v>2477.553</v>
       </c>
       <c r="F801" t="n">
         <v>1.213</v>
@@ -29699,7 +29699,7 @@
         <v>0.0</v>
       </c>
       <c r="H801" t="n">
-        <v>2490.2889999999998</v>
+        <v>2477.553</v>
       </c>
       <c r="I801" t="n">
         <v>0.0</v>
@@ -29875,7 +29875,7 @@
         </is>
       </c>
       <c r="E806" t="n">
-        <v>1323.366</v>
+        <v>1330.3049999999998</v>
       </c>
       <c r="F806" t="n">
         <v>6.308</v>
@@ -29884,7 +29884,7 @@
         <v>0.631</v>
       </c>
       <c r="H806" t="n">
-        <v>1323.366</v>
+        <v>1330.3049999999998</v>
       </c>
       <c r="I806" t="n">
         <v>0.0</v>
@@ -29949,7 +29949,7 @@
         </is>
       </c>
       <c r="E808" t="n">
-        <v>0.0</v>
+        <v>98.7</v>
       </c>
       <c r="F808" t="n">
         <v>0.0</v>
@@ -29958,7 +29958,7 @@
         <v>0.0</v>
       </c>
       <c r="H808" t="n">
-        <v>0.0</v>
+        <v>98.7</v>
       </c>
       <c r="I808" t="n">
         <v>0.0</v>
@@ -29986,7 +29986,7 @@
         </is>
       </c>
       <c r="E809" t="n">
-        <v>0.0</v>
+        <v>380.09999999999997</v>
       </c>
       <c r="F809" t="n">
         <v>0.0</v>
@@ -29995,7 +29995,7 @@
         <v>0.0</v>
       </c>
       <c r="H809" t="n">
-        <v>0.0</v>
+        <v>380.09999999999997</v>
       </c>
       <c r="I809" t="n">
         <v>0.0</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="E819" t="n">
-        <v>1275.6</v>
+        <v>1278.4</v>
       </c>
       <c r="F819" t="n">
         <v>0.4</v>
@@ -30365,7 +30365,7 @@
         <v>0.0</v>
       </c>
       <c r="H819" t="n">
-        <v>1275.6</v>
+        <v>1278.4</v>
       </c>
       <c r="I819" t="n">
         <v>0.0</v>
@@ -30541,7 +30541,7 @@
         </is>
       </c>
       <c r="E824" t="n">
-        <v>10129.0</v>
+        <v>10128.999</v>
       </c>
       <c r="F824" t="n">
         <v>2.4</v>
@@ -30550,7 +30550,7 @@
         <v>3.734</v>
       </c>
       <c r="H824" t="n">
-        <v>10129.0</v>
+        <v>10128.999</v>
       </c>
       <c r="I824" t="n">
         <v>0.0</v>
@@ -30615,7 +30615,7 @@
         </is>
       </c>
       <c r="E826" t="n">
-        <v>1263.684</v>
+        <v>2047.4879999999998</v>
       </c>
       <c r="F826" t="n">
         <v>0.0</v>
@@ -30627,7 +30627,7 @@
         <v>1263.684</v>
       </c>
       <c r="I826" t="n">
-        <v>0.0</v>
+        <v>783.804</v>
       </c>
     </row>
     <row r="827">
@@ -30652,7 +30652,7 @@
         </is>
       </c>
       <c r="E827" t="n">
-        <v>2044.671</v>
+        <v>2275.0566</v>
       </c>
       <c r="F827" t="n">
         <v>3.2</v>
@@ -30664,7 +30664,7 @@
         <v>2044.671</v>
       </c>
       <c r="I827" t="n">
-        <v>0.0</v>
+        <v>230.3856</v>
       </c>
     </row>
     <row r="828">
@@ -31688,7 +31688,7 @@
         </is>
       </c>
       <c r="E855" t="n">
-        <v>2622.1310000000003</v>
+        <v>2620.797</v>
       </c>
       <c r="F855" t="n">
         <v>2.6670000000000003</v>
@@ -31697,7 +31697,7 @@
         <v>0.0</v>
       </c>
       <c r="H855" t="n">
-        <v>2622.1310000000003</v>
+        <v>2620.797</v>
       </c>
       <c r="I855" t="n">
         <v>0.0</v>
@@ -31725,7 +31725,7 @@
         </is>
       </c>
       <c r="E856" t="n">
-        <v>21850.026</v>
+        <v>21786.006</v>
       </c>
       <c r="F856" t="n">
         <v>4.268</v>
@@ -31734,7 +31734,7 @@
         <v>0.0</v>
       </c>
       <c r="H856" t="n">
-        <v>21850.026</v>
+        <v>21786.006</v>
       </c>
       <c r="I856" t="n">
         <v>0.0</v>
@@ -31799,7 +31799,7 @@
         </is>
       </c>
       <c r="E858" t="n">
-        <v>7440.619</v>
+        <v>7439.753</v>
       </c>
       <c r="F858" t="n">
         <v>0.0</v>
@@ -31808,7 +31808,7 @@
         <v>0.0</v>
       </c>
       <c r="H858" t="n">
-        <v>7440.619</v>
+        <v>7439.753</v>
       </c>
       <c r="I858" t="n">
         <v>0.0</v>
@@ -31910,7 +31910,7 @@
         </is>
       </c>
       <c r="E861" t="n">
-        <v>10344.065</v>
+        <v>10336.265</v>
       </c>
       <c r="F861" t="n">
         <v>36.401</v>
@@ -31919,7 +31919,7 @@
         <v>0.0</v>
       </c>
       <c r="H861" t="n">
-        <v>10344.065</v>
+        <v>10336.265</v>
       </c>
       <c r="I861" t="n">
         <v>0.0</v>
@@ -31947,7 +31947,7 @@
         </is>
       </c>
       <c r="E862" t="n">
-        <v>1226.82</v>
+        <v>1172.413</v>
       </c>
       <c r="F862" t="n">
         <v>21.336000000000002</v>
@@ -31956,7 +31956,7 @@
         <v>0.0</v>
       </c>
       <c r="H862" t="n">
-        <v>1226.82</v>
+        <v>1172.413</v>
       </c>
       <c r="I862" t="n">
         <v>0.0</v>
@@ -31984,7 +31984,7 @@
         </is>
       </c>
       <c r="E863" t="n">
-        <v>1697.5859999999998</v>
+        <v>1799.0249999999999</v>
       </c>
       <c r="F863" t="n">
         <v>1.734</v>
@@ -31993,10 +31993,10 @@
         <v>0.0</v>
       </c>
       <c r="H863" t="n">
-        <v>1697.5859999999998</v>
+        <v>1694.985</v>
       </c>
       <c r="I863" t="n">
-        <v>0.0</v>
+        <v>104.04</v>
       </c>
     </row>
     <row r="864">
@@ -32206,7 +32206,7 @@
         </is>
       </c>
       <c r="E869" t="n">
-        <v>1139.71</v>
+        <v>1137.977</v>
       </c>
       <c r="F869" t="n">
         <v>0.867</v>
@@ -32215,7 +32215,7 @@
         <v>0.0</v>
       </c>
       <c r="H869" t="n">
-        <v>1139.71</v>
+        <v>1137.977</v>
       </c>
       <c r="I869" t="n">
         <v>0.0</v>
@@ -32243,7 +32243,7 @@
         </is>
       </c>
       <c r="E870" t="n">
-        <v>4970.219999999999</v>
+        <v>7617.7518</v>
       </c>
       <c r="F870" t="n">
         <v>58.407000000000004</v>
@@ -32252,10 +32252,10 @@
         <v>0.0</v>
       </c>
       <c r="H870" t="n">
-        <v>4970.219999999999</v>
+        <v>4891.0109999999995</v>
       </c>
       <c r="I870" t="n">
-        <v>0.0</v>
+        <v>2726.7408</v>
       </c>
     </row>
     <row r="871">
@@ -32317,7 +32317,7 @@
         </is>
       </c>
       <c r="E872" t="n">
-        <v>1226.82</v>
+        <v>2272.2832</v>
       </c>
       <c r="F872" t="n">
         <v>1.067</v>
@@ -32326,10 +32326,10 @@
         <v>0.0</v>
       </c>
       <c r="H872" t="n">
-        <v>1226.82</v>
+        <v>1222.552</v>
       </c>
       <c r="I872" t="n">
-        <v>0.0</v>
+        <v>1049.7312</v>
       </c>
     </row>
     <row r="873">
@@ -32354,7 +32354,7 @@
         </is>
       </c>
       <c r="E873" t="n">
-        <v>1246.0220000000002</v>
+        <v>1243.8890000000001</v>
       </c>
       <c r="F873" t="n">
         <v>1.067</v>
@@ -32363,7 +32363,7 @@
         <v>25.603</v>
       </c>
       <c r="H873" t="n">
-        <v>1246.0220000000002</v>
+        <v>1243.8890000000001</v>
       </c>
       <c r="I873" t="n">
         <v>0.0</v>
@@ -32391,7 +32391,7 @@
         </is>
       </c>
       <c r="E874" t="n">
-        <v>4244.287</v>
+        <v>4147.854</v>
       </c>
       <c r="F874" t="n">
         <v>31.537999999999997</v>
@@ -32400,7 +32400,7 @@
         <v>19.408</v>
       </c>
       <c r="H874" t="n">
-        <v>4244.287</v>
+        <v>4147.854</v>
       </c>
       <c r="I874" t="n">
         <v>0.0</v>
@@ -32428,7 +32428,7 @@
         </is>
       </c>
       <c r="E875" t="n">
-        <v>999.974</v>
+        <v>999.973</v>
       </c>
       <c r="F875" t="n">
         <v>0.0</v>
@@ -32437,7 +32437,7 @@
         <v>0.0</v>
       </c>
       <c r="H875" t="n">
-        <v>999.974</v>
+        <v>999.973</v>
       </c>
       <c r="I875" t="n">
         <v>0.0</v>
@@ -32502,7 +32502,7 @@
         </is>
       </c>
       <c r="E877" t="n">
-        <v>2552.0033000000003</v>
+        <v>2565.907</v>
       </c>
       <c r="F877" t="n">
         <v>11.984</v>
@@ -32511,10 +32511,10 @@
         <v>19.526000000000003</v>
       </c>
       <c r="H877" t="n">
-        <v>2511.1760000000004</v>
+        <v>2565.907</v>
       </c>
       <c r="I877" t="n">
-        <v>40.8273</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="878">
@@ -32539,7 +32539,7 @@
         </is>
       </c>
       <c r="E878" t="n">
-        <v>2770.339</v>
+        <v>13133.3728</v>
       </c>
       <c r="F878" t="n">
         <v>5.327</v>
@@ -32551,7 +32551,7 @@
         <v>2770.339</v>
       </c>
       <c r="I878" t="n">
-        <v>0.0</v>
+        <v>10363.0338</v>
       </c>
     </row>
     <row r="879">
@@ -32798,7 +32798,7 @@
         </is>
       </c>
       <c r="E885" t="n">
-        <v>4001.961</v>
+        <v>3835.102</v>
       </c>
       <c r="F885" t="n">
         <v>43.052</v>
@@ -32807,7 +32807,7 @@
         <v>40.827000000000005</v>
       </c>
       <c r="H885" t="n">
-        <v>4001.961</v>
+        <v>3835.102</v>
       </c>
       <c r="I885" t="n">
         <v>0.0</v>
@@ -32872,7 +32872,7 @@
         </is>
       </c>
       <c r="E887" t="n">
-        <v>1873.3226</v>
+        <v>992.873</v>
       </c>
       <c r="F887" t="n">
         <v>0.0</v>
@@ -32884,7 +32884,7 @@
         <v>992.873</v>
       </c>
       <c r="I887" t="n">
-        <v>880.4496</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="888">
@@ -32909,7 +32909,7 @@
         </is>
       </c>
       <c r="E888" t="n">
-        <v>3159.054</v>
+        <v>3140.482</v>
       </c>
       <c r="F888" t="n">
         <v>4.993</v>
@@ -32918,7 +32918,7 @@
         <v>0.0</v>
       </c>
       <c r="H888" t="n">
-        <v>3159.054</v>
+        <v>3140.482</v>
       </c>
       <c r="I888" t="n">
         <v>0.0</v>
@@ -32983,7 +32983,7 @@
         </is>
       </c>
       <c r="E890" t="n">
-        <v>2085.154</v>
+        <v>2065.0370000000003</v>
       </c>
       <c r="F890" t="n">
         <v>9.020999999999999</v>
@@ -32992,7 +32992,7 @@
         <v>0.0</v>
       </c>
       <c r="H890" t="n">
-        <v>2085.154</v>
+        <v>2065.0370000000003</v>
       </c>
       <c r="I890" t="n">
         <v>0.0</v>
@@ -33020,7 +33020,7 @@
         </is>
       </c>
       <c r="E891" t="n">
-        <v>3712.8887</v>
+        <v>3315.878</v>
       </c>
       <c r="F891" t="n">
         <v>0.0</v>
@@ -33032,7 +33032,7 @@
         <v>3315.878</v>
       </c>
       <c r="I891" t="n">
-        <v>397.0107</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="892">
@@ -33057,7 +33057,7 @@
         </is>
       </c>
       <c r="E892" t="n">
-        <v>2541.9456</v>
+        <v>3150.2132</v>
       </c>
       <c r="F892" t="n">
         <v>1.183</v>
@@ -33069,7 +33069,7 @@
         <v>2265.03</v>
       </c>
       <c r="I892" t="n">
-        <v>276.9156</v>
+        <v>885.1832</v>
       </c>
     </row>
     <row r="893">
@@ -33094,7 +33094,7 @@
         </is>
       </c>
       <c r="E893" t="n">
-        <v>0.0</v>
+        <v>600.0</v>
       </c>
       <c r="F893" t="n">
         <v>0.0</v>
@@ -33106,7 +33106,7 @@
         <v>0.0</v>
       </c>
       <c r="I893" t="n">
-        <v>0.0</v>
+        <v>600.0</v>
       </c>
     </row>
     <row r="894">
@@ -33131,7 +33131,7 @@
         </is>
       </c>
       <c r="E894" t="n">
-        <v>0.0</v>
+        <v>1200.0</v>
       </c>
       <c r="F894" t="n">
         <v>0.0</v>
@@ -33143,7 +33143,7 @@
         <v>0.0</v>
       </c>
       <c r="I894" t="n">
-        <v>0.0</v>
+        <v>1200.0</v>
       </c>
     </row>
     <row r="895">
@@ -33242,7 +33242,7 @@
         </is>
       </c>
       <c r="E897" t="n">
-        <v>3016.412</v>
+        <v>3016.411</v>
       </c>
       <c r="F897" t="n">
         <v>0.0</v>
@@ -33251,7 +33251,7 @@
         <v>4.002999999999999</v>
       </c>
       <c r="H897" t="n">
-        <v>3016.412</v>
+        <v>3016.411</v>
       </c>
       <c r="I897" t="n">
         <v>0.0</v>
@@ -33316,7 +33316,7 @@
         </is>
       </c>
       <c r="E899" t="n">
-        <v>11419.7948</v>
+        <v>10130.765</v>
       </c>
       <c r="F899" t="n">
         <v>0.0</v>
@@ -33325,10 +33325,10 @@
         <v>1.001</v>
       </c>
       <c r="H899" t="n">
-        <v>11003.462</v>
+        <v>10130.765</v>
       </c>
       <c r="I899" t="n">
-        <v>416.3328</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="900">
@@ -33575,7 +33575,7 @@
         </is>
       </c>
       <c r="E906" t="n">
-        <v>1962.028</v>
+        <v>1934.129</v>
       </c>
       <c r="F906" t="n">
         <v>240.781</v>
@@ -33584,7 +33584,7 @@
         <v>0.0</v>
       </c>
       <c r="H906" t="n">
-        <v>1962.028</v>
+        <v>1934.129</v>
       </c>
       <c r="I906" t="n">
         <v>0.0</v>
@@ -33612,7 +33612,7 @@
         </is>
       </c>
       <c r="E907" t="n">
-        <v>1675.1529999999998</v>
+        <v>1664.2359999999999</v>
       </c>
       <c r="F907" t="n">
         <v>2.426</v>
@@ -33621,7 +33621,7 @@
         <v>0.0</v>
       </c>
       <c r="H907" t="n">
-        <v>1675.1529999999998</v>
+        <v>1664.2359999999999</v>
       </c>
       <c r="I907" t="n">
         <v>0.0</v>
@@ -33686,7 +33686,7 @@
         </is>
       </c>
       <c r="E909" t="n">
-        <v>1840.653</v>
+        <v>1770.0739999999998</v>
       </c>
       <c r="F909" t="n">
         <v>67.218</v>
@@ -33695,7 +33695,7 @@
         <v>0.0</v>
       </c>
       <c r="H909" t="n">
-        <v>1840.653</v>
+        <v>1770.0739999999998</v>
       </c>
       <c r="I909" t="n">
         <v>0.0</v>
@@ -33871,7 +33871,7 @@
         </is>
       </c>
       <c r="E914" t="n">
-        <v>3435.3030000000003</v>
+        <v>3440.904</v>
       </c>
       <c r="F914" t="n">
         <v>1.245</v>
@@ -33880,7 +33880,7 @@
         <v>1.245</v>
       </c>
       <c r="H914" t="n">
-        <v>3435.3030000000003</v>
+        <v>3440.904</v>
       </c>
       <c r="I914" t="n">
         <v>0.0</v>
@@ -33908,7 +33908,7 @@
         </is>
       </c>
       <c r="E915" t="n">
-        <v>838.288</v>
+        <v>844.5120000000001</v>
       </c>
       <c r="F915" t="n">
         <v>1.245</v>
@@ -33917,7 +33917,7 @@
         <v>0.0</v>
       </c>
       <c r="H915" t="n">
-        <v>838.288</v>
+        <v>844.5120000000001</v>
       </c>
       <c r="I915" t="n">
         <v>0.0</v>
@@ -34167,7 +34167,7 @@
         </is>
       </c>
       <c r="E922" t="n">
-        <v>118.56200000000001</v>
+        <v>126.452</v>
       </c>
       <c r="F922" t="n">
         <v>0.9470000000000001</v>
@@ -34176,7 +34176,7 @@
         <v>0.0</v>
       </c>
       <c r="H922" t="n">
-        <v>118.56200000000001</v>
+        <v>126.452</v>
       </c>
       <c r="I922" t="n">
         <v>0.0</v>
@@ -34204,7 +34204,7 @@
         </is>
       </c>
       <c r="E923" t="n">
-        <v>2581.609</v>
+        <v>2550.996</v>
       </c>
       <c r="F923" t="n">
         <v>4.838</v>
@@ -34213,7 +34213,7 @@
         <v>1.262</v>
       </c>
       <c r="H923" t="n">
-        <v>2581.609</v>
+        <v>2550.996</v>
       </c>
       <c r="I923" t="n">
         <v>0.0</v>
@@ -34241,7 +34241,7 @@
         </is>
       </c>
       <c r="E924" t="n">
-        <v>2497.975</v>
+        <v>2486.1910000000003</v>
       </c>
       <c r="F924" t="n">
         <v>1.8940000000000001</v>
@@ -34250,7 +34250,7 @@
         <v>0.0</v>
       </c>
       <c r="H924" t="n">
-        <v>2497.975</v>
+        <v>2486.1910000000003</v>
       </c>
       <c r="I924" t="n">
         <v>0.0</v>
@@ -34315,7 +34315,7 @@
         </is>
       </c>
       <c r="E926" t="n">
-        <v>2506.1622</v>
+        <v>2400.0080000000003</v>
       </c>
       <c r="F926" t="n">
         <v>0.0</v>
@@ -34327,7 +34327,7 @@
         <v>2400.0080000000003</v>
       </c>
       <c r="I926" t="n">
-        <v>106.1542</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="927">
@@ -34574,7 +34574,7 @@
         </is>
       </c>
       <c r="E933" t="n">
-        <v>8319.003999999999</v>
+        <v>10242.029</v>
       </c>
       <c r="F933" t="n">
         <v>14.794</v>
@@ -34583,10 +34583,10 @@
         <v>3.8449999999999998</v>
       </c>
       <c r="H933" t="n">
-        <v>8319.003999999999</v>
+        <v>8289.419</v>
       </c>
       <c r="I933" t="n">
-        <v>0.0</v>
+        <v>1952.61</v>
       </c>
     </row>
     <row r="934">
@@ -34685,7 +34685,7 @@
         </is>
       </c>
       <c r="E936" t="n">
-        <v>2495.762</v>
+        <v>2719.4300000000003</v>
       </c>
       <c r="F936" t="n">
         <v>1.8639999999999999</v>
@@ -34697,7 +34697,7 @@
         <v>2495.762</v>
       </c>
       <c r="I936" t="n">
-        <v>0.0</v>
+        <v>223.668</v>
       </c>
     </row>
     <row r="937">
@@ -34796,7 +34796,7 @@
         </is>
       </c>
       <c r="E939" t="n">
-        <v>854.5060000000001</v>
+        <v>896.111</v>
       </c>
       <c r="F939" t="n">
         <v>6.401</v>
@@ -34805,7 +34805,7 @@
         <v>0.0</v>
       </c>
       <c r="H939" t="n">
-        <v>854.5060000000001</v>
+        <v>896.111</v>
       </c>
       <c r="I939" t="n">
         <v>0.0</v>
@@ -34870,7 +34870,7 @@
         </is>
       </c>
       <c r="E941" t="n">
-        <v>48.576</v>
+        <v>48.183</v>
       </c>
       <c r="F941" t="n">
         <v>0.525</v>
@@ -34879,7 +34879,7 @@
         <v>0.0</v>
       </c>
       <c r="H941" t="n">
-        <v>48.576</v>
+        <v>48.183</v>
       </c>
       <c r="I941" t="n">
         <v>0.0</v>
@@ -35018,7 +35018,7 @@
         </is>
       </c>
       <c r="E945" t="n">
-        <v>2759.4919999999997</v>
+        <v>2793.312</v>
       </c>
       <c r="F945" t="n">
         <v>57.216</v>
@@ -35027,7 +35027,7 @@
         <v>0.0</v>
       </c>
       <c r="H945" t="n">
-        <v>2759.4919999999997</v>
+        <v>2793.312</v>
       </c>
       <c r="I945" t="n">
         <v>0.0</v>
@@ -35055,7 +35055,7 @@
         </is>
       </c>
       <c r="E946" t="n">
-        <v>1363.204</v>
+        <v>1345.29</v>
       </c>
       <c r="F946" t="n">
         <v>1.643</v>
@@ -35064,7 +35064,7 @@
         <v>0.0</v>
       </c>
       <c r="H946" t="n">
-        <v>1363.204</v>
+        <v>1345.29</v>
       </c>
       <c r="I946" t="n">
         <v>0.0</v>
@@ -35166,7 +35166,7 @@
         </is>
       </c>
       <c r="E949" t="n">
-        <v>6048.0</v>
+        <v>6044.0</v>
       </c>
       <c r="F949" t="n">
         <v>0.0</v>
@@ -35175,7 +35175,7 @@
         <v>180.0</v>
       </c>
       <c r="H949" t="n">
-        <v>6048.0</v>
+        <v>6044.0</v>
       </c>
       <c r="I949" t="n">
         <v>0.0</v>
@@ -35980,7 +35980,7 @@
         </is>
       </c>
       <c r="E971" t="n">
-        <v>2289.233</v>
+        <v>2254.233</v>
       </c>
       <c r="F971" t="n">
         <v>12.6</v>
@@ -35989,7 +35989,7 @@
         <v>9.799999999999999</v>
       </c>
       <c r="H971" t="n">
-        <v>2289.233</v>
+        <v>2254.233</v>
       </c>
       <c r="I971" t="n">
         <v>0.0</v>
@@ -36017,7 +36017,7 @@
         </is>
       </c>
       <c r="E972" t="n">
-        <v>1299.183</v>
+        <v>1427.454</v>
       </c>
       <c r="F972" t="n">
         <v>19.934</v>
@@ -36026,7 +36026,7 @@
         <v>0.867</v>
       </c>
       <c r="H972" t="n">
-        <v>1299.183</v>
+        <v>1427.454</v>
       </c>
       <c r="I972" t="n">
         <v>0.0</v>
@@ -36054,7 +36054,7 @@
         </is>
       </c>
       <c r="E973" t="n">
-        <v>4937.903</v>
+        <v>4929.203</v>
       </c>
       <c r="F973" t="n">
         <v>14.501</v>
@@ -36063,7 +36063,7 @@
         <v>8.7</v>
       </c>
       <c r="H973" t="n">
-        <v>4937.903</v>
+        <v>4929.203</v>
       </c>
       <c r="I973" t="n">
         <v>0.0</v>
@@ -36134,7 +36134,7 @@
         <v>0.0</v>
       </c>
       <c r="G975" t="n">
-        <v>2.5829999999999997</v>
+        <v>0.0</v>
       </c>
       <c r="H975" t="n">
         <v>1639.713</v>
@@ -36979,7 +36979,7 @@
         </is>
       </c>
       <c r="E998" t="n">
-        <v>33.727</v>
+        <v>2781.5818</v>
       </c>
       <c r="F998" t="n">
         <v>0.0</v>
@@ -36991,7 +36991,7 @@
         <v>33.727</v>
       </c>
       <c r="I998" t="n">
-        <v>0.0</v>
+        <v>2747.8548</v>
       </c>
     </row>
     <row r="999">
@@ -37053,7 +37053,7 @@
         </is>
       </c>
       <c r="E1000" t="n">
-        <v>22999.971</v>
+        <v>22999.970999999998</v>
       </c>
       <c r="F1000" t="n">
         <v>0.0</v>
@@ -37062,7 +37062,7 @@
         <v>0.0</v>
       </c>
       <c r="H1000" t="n">
-        <v>22999.971</v>
+        <v>22999.970999999998</v>
       </c>
       <c r="I1000" t="n">
         <v>0.0</v>
@@ -37127,7 +37127,7 @@
         </is>
       </c>
       <c r="E1002" t="n">
-        <v>447.0</v>
+        <v>408.6</v>
       </c>
       <c r="F1002" t="n">
         <v>31.2</v>
@@ -37136,7 +37136,7 @@
         <v>5.4</v>
       </c>
       <c r="H1002" t="n">
-        <v>447.0</v>
+        <v>408.6</v>
       </c>
       <c r="I1002" t="n">
         <v>0.0</v>
@@ -37275,7 +37275,7 @@
         </is>
       </c>
       <c r="E1006" t="n">
-        <v>5425.9220000000005</v>
+        <v>3157.89</v>
       </c>
       <c r="F1006" t="n">
         <v>68.15</v>
@@ -37287,7 +37287,7 @@
         <v>3157.89</v>
       </c>
       <c r="I1006" t="n">
-        <v>2268.032</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1007">
@@ -37571,7 +37571,7 @@
         </is>
       </c>
       <c r="E1014" t="n">
-        <v>7726.9839999999995</v>
+        <v>7758.981999999999</v>
       </c>
       <c r="F1014" t="n">
         <v>0.0</v>
@@ -37583,7 +37583,7 @@
         <v>7726.9839999999995</v>
       </c>
       <c r="I1014" t="n">
-        <v>0.0</v>
+        <v>31.998</v>
       </c>
     </row>
     <row r="1015">
@@ -37608,7 +37608,7 @@
         </is>
       </c>
       <c r="E1015" t="n">
-        <v>3608.451</v>
+        <v>6456.807000000001</v>
       </c>
       <c r="F1015" t="n">
         <v>0.533</v>
@@ -37620,7 +37620,7 @@
         <v>3608.451</v>
       </c>
       <c r="I1015" t="n">
-        <v>0.0</v>
+        <v>2848.356</v>
       </c>
     </row>
     <row r="1016">
@@ -37793,7 +37793,7 @@
         </is>
       </c>
       <c r="E1020" t="n">
-        <v>596.875</v>
+        <v>2045.357</v>
       </c>
       <c r="F1020" t="n">
         <v>22.78</v>
@@ -37802,10 +37802,10 @@
         <v>10.651000000000002</v>
       </c>
       <c r="H1020" t="n">
-        <v>596.875</v>
+        <v>447.767</v>
       </c>
       <c r="I1020" t="n">
-        <v>0.0</v>
+        <v>1597.59</v>
       </c>
     </row>
     <row r="1021">
@@ -38163,7 +38163,7 @@
         </is>
       </c>
       <c r="E1030" t="n">
-        <v>2545.1769999999997</v>
+        <v>2547.9719999999998</v>
       </c>
       <c r="F1030" t="n">
         <v>0.599</v>
@@ -38172,7 +38172,7 @@
         <v>0.0</v>
       </c>
       <c r="H1030" t="n">
-        <v>2545.1769999999997</v>
+        <v>2547.9719999999998</v>
       </c>
       <c r="I1030" t="n">
         <v>0.0</v>
@@ -38237,7 +38237,7 @@
         </is>
       </c>
       <c r="E1032" t="n">
-        <v>422.124</v>
+        <v>229.863</v>
       </c>
       <c r="F1032" t="n">
         <v>52.159</v>
@@ -38246,7 +38246,7 @@
         <v>2.426</v>
       </c>
       <c r="H1032" t="n">
-        <v>422.124</v>
+        <v>229.863</v>
       </c>
       <c r="I1032" t="n">
         <v>0.0</v>
@@ -38274,7 +38274,7 @@
         </is>
       </c>
       <c r="E1033" t="n">
-        <v>6029.554</v>
+        <v>12212.7268</v>
       </c>
       <c r="F1033" t="n">
         <v>0.0</v>
@@ -38286,7 +38286,7 @@
         <v>6029.554</v>
       </c>
       <c r="I1033" t="n">
-        <v>0.0</v>
+        <v>6183.1728</v>
       </c>
     </row>
     <row r="1034">
@@ -38311,7 +38311,7 @@
         </is>
       </c>
       <c r="E1034" t="n">
-        <v>10100.462</v>
+        <v>13172.846</v>
       </c>
       <c r="F1034" t="n">
         <v>0.0</v>
@@ -38323,7 +38323,7 @@
         <v>10100.462</v>
       </c>
       <c r="I1034" t="n">
-        <v>0.0</v>
+        <v>3072.384</v>
       </c>
     </row>
     <row r="1035">
@@ -38570,7 +38570,7 @@
         </is>
       </c>
       <c r="E1041" t="n">
-        <v>6479.846</v>
+        <v>3237.254</v>
       </c>
       <c r="F1041" t="n">
         <v>0.0</v>
@@ -38582,7 +38582,7 @@
         <v>3237.254</v>
       </c>
       <c r="I1041" t="n">
-        <v>3242.592</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1042">
@@ -38718,7 +38718,7 @@
         </is>
       </c>
       <c r="E1045" t="n">
-        <v>6018.3</v>
+        <v>5997.072</v>
       </c>
       <c r="F1045" t="n">
         <v>2.426</v>
@@ -38727,7 +38727,7 @@
         <v>0.0</v>
       </c>
       <c r="H1045" t="n">
-        <v>6018.3</v>
+        <v>5997.072</v>
       </c>
       <c r="I1045" t="n">
         <v>0.0</v>
@@ -38755,7 +38755,7 @@
         </is>
       </c>
       <c r="E1046" t="n">
-        <v>229.864</v>
+        <v>163.755</v>
       </c>
       <c r="F1046" t="n">
         <v>10.311</v>
@@ -38764,7 +38764,7 @@
         <v>33.964</v>
       </c>
       <c r="H1046" t="n">
-        <v>229.864</v>
+        <v>163.755</v>
       </c>
       <c r="I1046" t="n">
         <v>0.0</v>
@@ -38792,7 +38792,7 @@
         </is>
       </c>
       <c r="E1047" t="n">
-        <v>3171.5099999999998</v>
+        <v>3193.6589999999997</v>
       </c>
       <c r="F1047" t="n">
         <v>0.0</v>
@@ -38801,7 +38801,7 @@
         <v>47.608</v>
       </c>
       <c r="H1047" t="n">
-        <v>3171.5099999999998</v>
+        <v>3193.6589999999997</v>
       </c>
       <c r="I1047" t="n">
         <v>0.0</v>
@@ -38829,7 +38829,7 @@
         </is>
       </c>
       <c r="E1048" t="n">
-        <v>6392.309</v>
+        <v>3089.86</v>
       </c>
       <c r="F1048" t="n">
         <v>0.988</v>
@@ -38838,10 +38838,10 @@
         <v>15.869000000000002</v>
       </c>
       <c r="H1048" t="n">
-        <v>3059.777</v>
+        <v>3089.86</v>
       </c>
       <c r="I1048" t="n">
-        <v>3332.532</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1049">
@@ -38866,7 +38866,7 @@
         </is>
       </c>
       <c r="E1049" t="n">
-        <v>4074.412</v>
+        <v>4084.997</v>
       </c>
       <c r="F1049" t="n">
         <v>0.0</v>
@@ -38875,7 +38875,7 @@
         <v>0.0</v>
       </c>
       <c r="H1049" t="n">
-        <v>4074.412</v>
+        <v>4084.997</v>
       </c>
       <c r="I1049" t="n">
         <v>0.0</v>
@@ -38903,7 +38903,7 @@
         </is>
       </c>
       <c r="E1050" t="n">
-        <v>15888.703</v>
+        <v>15965.736</v>
       </c>
       <c r="F1050" t="n">
         <v>3.305</v>
@@ -38912,7 +38912,7 @@
         <v>0.0</v>
       </c>
       <c r="H1050" t="n">
-        <v>15888.703</v>
+        <v>15965.736</v>
       </c>
       <c r="I1050" t="n">
         <v>0.0</v>
@@ -38977,7 +38977,7 @@
         </is>
       </c>
       <c r="E1052" t="n">
-        <v>12374.007</v>
+        <v>12399.132</v>
       </c>
       <c r="F1052" t="n">
         <v>2.313</v>
@@ -38986,7 +38986,7 @@
         <v>0.0</v>
       </c>
       <c r="H1052" t="n">
-        <v>12374.007</v>
+        <v>12399.132</v>
       </c>
       <c r="I1052" t="n">
         <v>0.0</v>
@@ -39051,7 +39051,7 @@
         </is>
       </c>
       <c r="E1054" t="n">
-        <v>4899.612</v>
+        <v>4920.769</v>
       </c>
       <c r="F1054" t="n">
         <v>0.988</v>
@@ -39060,7 +39060,7 @@
         <v>0.0</v>
       </c>
       <c r="H1054" t="n">
-        <v>4899.612</v>
+        <v>4920.769</v>
       </c>
       <c r="I1054" t="n">
         <v>0.0</v>
@@ -39125,7 +39125,7 @@
         </is>
       </c>
       <c r="E1056" t="n">
-        <v>17563.4272</v>
+        <v>7738.5502</v>
       </c>
       <c r="F1056" t="n">
         <v>0.0</v>
@@ -39137,7 +39137,7 @@
         <v>23.338</v>
       </c>
       <c r="I1056" t="n">
-        <v>17540.0892</v>
+        <v>7715.2122</v>
       </c>
     </row>
     <row r="1057">
@@ -39162,7 +39162,7 @@
         </is>
       </c>
       <c r="E1057" t="n">
-        <v>21020.7432</v>
+        <v>20710.965</v>
       </c>
       <c r="F1057" t="n">
         <v>7.6049999999999995</v>
@@ -39171,10 +39171,10 @@
         <v>3.967</v>
       </c>
       <c r="H1057" t="n">
-        <v>20885.855</v>
+        <v>20710.965</v>
       </c>
       <c r="I1057" t="n">
-        <v>134.8882</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1058">
@@ -39199,7 +39199,7 @@
         </is>
       </c>
       <c r="E1058" t="n">
-        <v>23003.065</v>
+        <v>23129.689000000002</v>
       </c>
       <c r="F1058" t="n">
         <v>18.515</v>
@@ -39208,7 +39208,7 @@
         <v>0.0</v>
       </c>
       <c r="H1058" t="n">
-        <v>23003.065</v>
+        <v>23129.689000000002</v>
       </c>
       <c r="I1058" t="n">
         <v>0.0</v>
@@ -39754,7 +39754,7 @@
         </is>
       </c>
       <c r="E1073" t="n">
-        <v>669.268</v>
+        <v>669.2660000000001</v>
       </c>
       <c r="F1073" t="n">
         <v>0.0</v>
@@ -39763,7 +39763,7 @@
         <v>0.0</v>
       </c>
       <c r="H1073" t="n">
-        <v>669.268</v>
+        <v>669.2660000000001</v>
       </c>
       <c r="I1073" t="n">
         <v>0.0</v>
@@ -39902,19 +39902,19 @@
         </is>
       </c>
       <c r="E1077" t="n">
-        <v>7088.7433</v>
+        <v>3672.848</v>
       </c>
       <c r="F1077" t="n">
         <v>12.602</v>
       </c>
       <c r="G1077" t="n">
-        <v>1008.875</v>
+        <v>0.699</v>
       </c>
       <c r="H1077" t="n">
-        <v>3667.2459999999996</v>
+        <v>3672.848</v>
       </c>
       <c r="I1077" t="n">
-        <v>3421.4973</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1078">
@@ -39939,19 +39939,19 @@
         </is>
       </c>
       <c r="E1078" t="n">
-        <v>4498.9914</v>
+        <v>4442.281000000001</v>
       </c>
       <c r="F1078" t="n">
         <v>0.0</v>
       </c>
       <c r="G1078" t="n">
-        <v>4448.577</v>
+        <v>6.301</v>
       </c>
       <c r="H1078" t="n">
-        <v>0.006</v>
+        <v>4442.281000000001</v>
       </c>
       <c r="I1078" t="n">
-        <v>4498.9854</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1079">
@@ -40050,7 +40050,7 @@
         </is>
       </c>
       <c r="E1081" t="n">
-        <v>180.587</v>
+        <v>828.723</v>
       </c>
       <c r="F1081" t="n">
         <v>0.0</v>
@@ -40059,7 +40059,7 @@
         <v>0.0</v>
       </c>
       <c r="H1081" t="n">
-        <v>180.587</v>
+        <v>828.723</v>
       </c>
       <c r="I1081" t="n">
         <v>0.0</v>
@@ -40087,7 +40087,7 @@
         </is>
       </c>
       <c r="E1082" t="n">
-        <v>105.018</v>
+        <v>0.0</v>
       </c>
       <c r="F1082" t="n">
         <v>0.585</v>
@@ -40096,7 +40096,7 @@
         <v>0.0</v>
       </c>
       <c r="H1082" t="n">
-        <v>105.018</v>
+        <v>0.0</v>
       </c>
       <c r="I1082" t="n">
         <v>0.0</v>
@@ -40457,7 +40457,7 @@
         </is>
       </c>
       <c r="E1092" t="n">
-        <v>4675.5</v>
+        <v>5647.5</v>
       </c>
       <c r="F1092" t="n">
         <v>0.0</v>
@@ -40469,7 +40469,7 @@
         <v>4675.5</v>
       </c>
       <c r="I1092" t="n">
-        <v>0.0</v>
+        <v>972.0</v>
       </c>
     </row>
     <row r="1093">
@@ -40790,7 +40790,7 @@
         </is>
       </c>
       <c r="E1101" t="n">
-        <v>2231.6969999999997</v>
+        <v>2211.71</v>
       </c>
       <c r="F1101" t="n">
         <v>0.0</v>
@@ -40799,7 +40799,7 @@
         <v>0.0</v>
       </c>
       <c r="H1101" t="n">
-        <v>2231.6969999999997</v>
+        <v>2211.71</v>
       </c>
       <c r="I1101" t="n">
         <v>0.0</v>
@@ -40870,7 +40870,7 @@
         <v>0.316</v>
       </c>
       <c r="G1103" t="n">
-        <v>0.0</v>
+        <v>1.262</v>
       </c>
       <c r="H1103" t="n">
         <v>1179.081</v>
@@ -40901,7 +40901,7 @@
         </is>
       </c>
       <c r="E1104" t="n">
-        <v>823.852</v>
+        <v>815.524</v>
       </c>
       <c r="F1104" t="n">
         <v>0.0</v>
@@ -40910,7 +40910,7 @@
         <v>0.0</v>
       </c>
       <c r="H1104" t="n">
-        <v>823.852</v>
+        <v>815.524</v>
       </c>
       <c r="I1104" t="n">
         <v>0.0</v>
@@ -40938,7 +40938,7 @@
         </is>
       </c>
       <c r="E1105" t="n">
-        <v>0.0</v>
+        <v>67250.078</v>
       </c>
       <c r="F1105" t="n">
         <v>0.0</v>
@@ -40950,7 +40950,7 @@
         <v>0.0</v>
       </c>
       <c r="I1105" t="n">
-        <v>0.0</v>
+        <v>67250.078</v>
       </c>
     </row>
     <row r="1106">
@@ -40975,7 +40975,7 @@
         </is>
       </c>
       <c r="E1106" t="n">
-        <v>8334.357</v>
+        <v>8932.8114</v>
       </c>
       <c r="F1106" t="n">
         <v>0.0</v>
@@ -40987,7 +40987,7 @@
         <v>8334.357</v>
       </c>
       <c r="I1106" t="n">
-        <v>0.0</v>
+        <v>598.4544</v>
       </c>
     </row>
     <row r="1107">
@@ -41086,7 +41086,7 @@
         </is>
       </c>
       <c r="E1109" t="n">
-        <v>7489.481</v>
+        <v>7542.2858</v>
       </c>
       <c r="F1109" t="n">
         <v>0.0</v>
@@ -41098,7 +41098,7 @@
         <v>7489.481</v>
       </c>
       <c r="I1109" t="n">
-        <v>0.0</v>
+        <v>52.8048</v>
       </c>
     </row>
     <row r="1110">
@@ -41123,7 +41123,7 @@
         </is>
       </c>
       <c r="E1110" t="n">
-        <v>235.2</v>
+        <v>8188.799999999999</v>
       </c>
       <c r="F1110" t="n">
         <v>3.2</v>
@@ -41132,10 +41132,10 @@
         <v>0.0</v>
       </c>
       <c r="H1110" t="n">
-        <v>235.2</v>
+        <v>182.4</v>
       </c>
       <c r="I1110" t="n">
-        <v>0.0</v>
+        <v>8006.4</v>
       </c>
     </row>
     <row r="1111">
@@ -41197,7 +41197,7 @@
         </is>
       </c>
       <c r="E1112" t="n">
-        <v>432.3456</v>
+        <v>0.0</v>
       </c>
       <c r="F1112" t="n">
         <v>0.0</v>
@@ -41209,7 +41209,7 @@
         <v>0.0</v>
       </c>
       <c r="I1112" t="n">
-        <v>432.3456</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1113">
@@ -41234,7 +41234,7 @@
         </is>
       </c>
       <c r="E1113" t="n">
-        <v>1108.8868</v>
+        <v>72.05799999999999</v>
       </c>
       <c r="F1113" t="n">
         <v>0.0</v>
@@ -41246,7 +41246,7 @@
         <v>72.05799999999999</v>
       </c>
       <c r="I1113" t="n">
-        <v>1036.8288</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1114">
@@ -41271,7 +41271,7 @@
         </is>
       </c>
       <c r="E1114" t="n">
-        <v>810.648</v>
+        <v>0.0</v>
       </c>
       <c r="F1114" t="n">
         <v>0.0</v>
@@ -41283,7 +41283,7 @@
         <v>0.0</v>
       </c>
       <c r="I1114" t="n">
-        <v>810.648</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1115">
@@ -41678,7 +41678,7 @@
         </is>
       </c>
       <c r="E1125" t="n">
-        <v>1813.2240000000002</v>
+        <v>1811.941</v>
       </c>
       <c r="F1125" t="n">
         <v>0.0</v>
@@ -41687,7 +41687,7 @@
         <v>0.0</v>
       </c>
       <c r="H1125" t="n">
-        <v>1813.2240000000002</v>
+        <v>1811.941</v>
       </c>
       <c r="I1125" t="n">
         <v>0.0</v>
@@ -41715,7 +41715,7 @@
         </is>
       </c>
       <c r="E1126" t="n">
-        <v>903.6185</v>
+        <v>572.89</v>
       </c>
       <c r="F1126" t="n">
         <v>0.0</v>
@@ -41724,10 +41724,10 @@
         <v>0.0</v>
       </c>
       <c r="H1126" t="n">
-        <v>574.174</v>
+        <v>572.89</v>
       </c>
       <c r="I1126" t="n">
-        <v>329.4445</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1127">
@@ -41826,7 +41826,7 @@
         </is>
       </c>
       <c r="E1129" t="n">
-        <v>1769.92</v>
+        <v>1841.799</v>
       </c>
       <c r="F1129" t="n">
         <v>1.553</v>
@@ -41835,7 +41835,7 @@
         <v>0.0</v>
       </c>
       <c r="H1129" t="n">
-        <v>1769.92</v>
+        <v>1841.799</v>
       </c>
       <c r="I1129" t="n">
         <v>0.0</v>
@@ -41937,19 +41937,19 @@
         </is>
       </c>
       <c r="E1132" t="n">
-        <v>14996.964899999999</v>
+        <v>10213.802</v>
       </c>
       <c r="F1132" t="n">
         <v>22.166</v>
       </c>
       <c r="G1132" t="n">
-        <v>2443.613</v>
+        <v>2328.817</v>
       </c>
       <c r="H1132" t="n">
-        <v>10318.332</v>
+        <v>10213.802</v>
       </c>
       <c r="I1132" t="n">
-        <v>4678.6329</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1133">
@@ -42011,7 +42011,7 @@
         </is>
       </c>
       <c r="E1134" t="n">
-        <v>10971.27</v>
+        <v>10952.87</v>
       </c>
       <c r="F1134" t="n">
         <v>11.244</v>
@@ -42020,7 +42020,7 @@
         <v>72.57600000000001</v>
       </c>
       <c r="H1134" t="n">
-        <v>10971.27</v>
+        <v>10952.87</v>
       </c>
       <c r="I1134" t="n">
         <v>0.0</v>
@@ -42048,19 +42048,19 @@
         </is>
       </c>
       <c r="E1135" t="n">
-        <v>12392.4576</v>
+        <v>12136.445</v>
       </c>
       <c r="F1135" t="n">
         <v>11.334</v>
       </c>
       <c r="G1135" t="n">
-        <v>493.358</v>
+        <v>546.027</v>
       </c>
       <c r="H1135" t="n">
-        <v>12200.448</v>
+        <v>12136.445</v>
       </c>
       <c r="I1135" t="n">
-        <v>192.0096</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1136">
@@ -42085,16 +42085,16 @@
         </is>
       </c>
       <c r="E1136" t="n">
-        <v>10870.0</v>
+        <v>11422.0</v>
       </c>
       <c r="F1136" t="n">
         <v>27.2</v>
       </c>
       <c r="G1136" t="n">
-        <v>4010.3999999999996</v>
+        <v>381.6</v>
       </c>
       <c r="H1136" t="n">
-        <v>10870.0</v>
+        <v>11422.0</v>
       </c>
       <c r="I1136" t="n">
         <v>0.0</v>
@@ -42159,7 +42159,7 @@
         </is>
       </c>
       <c r="E1138" t="n">
-        <v>1827.085</v>
+        <v>2241.4588</v>
       </c>
       <c r="F1138" t="n">
         <v>4.266</v>
@@ -42168,10 +42168,10 @@
         <v>0.0</v>
       </c>
       <c r="H1138" t="n">
-        <v>1827.085</v>
+        <v>1742.29</v>
       </c>
       <c r="I1138" t="n">
-        <v>0.0</v>
+        <v>499.1688</v>
       </c>
     </row>
     <row r="1139">
@@ -42270,7 +42270,7 @@
         </is>
       </c>
       <c r="E1141" t="n">
-        <v>2245.762</v>
+        <v>3791.4724</v>
       </c>
       <c r="F1141" t="n">
         <v>0.0</v>
@@ -42282,7 +42282,7 @@
         <v>2245.762</v>
       </c>
       <c r="I1141" t="n">
-        <v>0.0</v>
+        <v>1545.7104</v>
       </c>
     </row>
     <row r="1142">
@@ -42307,7 +42307,7 @@
         </is>
       </c>
       <c r="E1142" t="n">
-        <v>276.818</v>
+        <v>274.251</v>
       </c>
       <c r="F1142" t="n">
         <v>0.0</v>
@@ -42316,7 +42316,7 @@
         <v>0.0</v>
       </c>
       <c r="H1142" t="n">
-        <v>276.818</v>
+        <v>274.251</v>
       </c>
       <c r="I1142" t="n">
         <v>0.0</v>
@@ -42455,7 +42455,7 @@
         </is>
       </c>
       <c r="E1146" t="n">
-        <v>0.0</v>
+        <v>1164.8</v>
       </c>
       <c r="F1146" t="n">
         <v>0.0</v>
@@ -42467,7 +42467,7 @@
         <v>0.0</v>
       </c>
       <c r="I1146" t="n">
-        <v>0.0</v>
+        <v>1164.8</v>
       </c>
     </row>
     <row r="1147">
@@ -42492,7 +42492,7 @@
         </is>
       </c>
       <c r="E1147" t="n">
-        <v>0.0</v>
+        <v>1927.9134</v>
       </c>
       <c r="F1147" t="n">
         <v>0.0</v>
@@ -42504,7 +42504,7 @@
         <v>0.0</v>
       </c>
       <c r="I1147" t="n">
-        <v>0.0</v>
+        <v>1927.9134</v>
       </c>
     </row>
     <row r="1148">
@@ -42529,7 +42529,7 @@
         </is>
       </c>
       <c r="E1148" t="n">
-        <v>0.0</v>
+        <v>2242.7788</v>
       </c>
       <c r="F1148" t="n">
         <v>0.0</v>
@@ -42541,7 +42541,7 @@
         <v>0.0</v>
       </c>
       <c r="I1148" t="n">
-        <v>0.0</v>
+        <v>2242.7788</v>
       </c>
     </row>
     <row r="1149">
@@ -42714,7 +42714,7 @@
         </is>
       </c>
       <c r="E1153" t="n">
-        <v>5779.2</v>
+        <v>6310.4</v>
       </c>
       <c r="F1153" t="n">
         <v>0.2</v>
@@ -42726,7 +42726,7 @@
         <v>5779.2</v>
       </c>
       <c r="I1153" t="n">
-        <v>0.0</v>
+        <v>531.2</v>
       </c>
     </row>
     <row r="1154">
@@ -43158,7 +43158,7 @@
         </is>
       </c>
       <c r="E1165" t="n">
-        <v>4190.0</v>
+        <v>4151.2</v>
       </c>
       <c r="F1165" t="n">
         <v>4.8</v>
@@ -43167,7 +43167,7 @@
         <v>0.0</v>
       </c>
       <c r="H1165" t="n">
-        <v>4190.0</v>
+        <v>4151.2</v>
       </c>
       <c r="I1165" t="n">
         <v>0.0</v>
@@ -43306,7 +43306,7 @@
         </is>
       </c>
       <c r="E1169" t="n">
-        <v>1681.498</v>
+        <v>1681.499</v>
       </c>
       <c r="F1169" t="n">
         <v>0.6669999999999999</v>
@@ -43315,7 +43315,7 @@
         <v>0.0</v>
       </c>
       <c r="H1169" t="n">
-        <v>1681.498</v>
+        <v>1681.499</v>
       </c>
       <c r="I1169" t="n">
         <v>0.0</v>
@@ -43343,7 +43343,7 @@
         </is>
       </c>
       <c r="E1170" t="n">
-        <v>2216.0</v>
+        <v>2202.0</v>
       </c>
       <c r="F1170" t="n">
         <v>2.0</v>
@@ -43352,7 +43352,7 @@
         <v>0.8</v>
       </c>
       <c r="H1170" t="n">
-        <v>2216.0</v>
+        <v>2202.0</v>
       </c>
       <c r="I1170" t="n">
         <v>0.0</v>
@@ -43861,7 +43861,7 @@
         </is>
       </c>
       <c r="E1184" t="n">
-        <v>2743.6940000000004</v>
+        <v>2739.6710000000003</v>
       </c>
       <c r="F1184" t="n">
         <v>0.0</v>
@@ -43870,7 +43870,7 @@
         <v>19.172</v>
       </c>
       <c r="H1184" t="n">
-        <v>2743.6940000000004</v>
+        <v>2739.6710000000003</v>
       </c>
       <c r="I1184" t="n">
         <v>0.0</v>
@@ -43898,7 +43898,7 @@
         </is>
       </c>
       <c r="E1185" t="n">
-        <v>2517.6620000000003</v>
+        <v>2516.9530000000004</v>
       </c>
       <c r="F1185" t="n">
         <v>0.0</v>
@@ -43907,7 +43907,7 @@
         <v>4.26</v>
       </c>
       <c r="H1185" t="n">
-        <v>2517.6620000000003</v>
+        <v>2516.9530000000004</v>
       </c>
       <c r="I1185" t="n">
         <v>0.0</v>
@@ -43972,7 +43972,7 @@
         </is>
       </c>
       <c r="E1187" t="n">
-        <v>0.0</v>
+        <v>969.228</v>
       </c>
       <c r="F1187" t="n">
         <v>0.0</v>
@@ -43984,7 +43984,7 @@
         <v>0.0</v>
       </c>
       <c r="I1187" t="n">
-        <v>0.0</v>
+        <v>969.228</v>
       </c>
     </row>
     <row r="1188">
@@ -44009,7 +44009,7 @@
         </is>
       </c>
       <c r="E1188" t="n">
-        <v>0.0</v>
+        <v>298.224</v>
       </c>
       <c r="F1188" t="n">
         <v>0.0</v>
@@ -44021,7 +44021,7 @@
         <v>0.0</v>
       </c>
       <c r="I1188" t="n">
-        <v>0.0</v>
+        <v>298.224</v>
       </c>
     </row>
     <row r="1189">
@@ -44120,7 +44120,7 @@
         </is>
       </c>
       <c r="E1191" t="n">
-        <v>1130.147</v>
+        <v>0.0</v>
       </c>
       <c r="F1191" t="n">
         <v>0.0</v>
@@ -44132,7 +44132,7 @@
         <v>0.0</v>
       </c>
       <c r="I1191" t="n">
-        <v>1130.147</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1192">
@@ -44157,7 +44157,7 @@
         </is>
       </c>
       <c r="E1192" t="n">
-        <v>976.305</v>
+        <v>0.0</v>
       </c>
       <c r="F1192" t="n">
         <v>0.0</v>
@@ -44169,7 +44169,7 @@
         <v>0.0</v>
       </c>
       <c r="I1192" t="n">
-        <v>976.305</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1193">
@@ -44194,7 +44194,7 @@
         </is>
       </c>
       <c r="E1193" t="n">
-        <v>0.0</v>
+        <v>2076.93</v>
       </c>
       <c r="F1193" t="n">
         <v>0.0</v>
@@ -44206,7 +44206,7 @@
         <v>0.0</v>
       </c>
       <c r="I1193" t="n">
-        <v>0.0</v>
+        <v>2076.93</v>
       </c>
     </row>
     <row r="1194">
@@ -44268,7 +44268,7 @@
         </is>
       </c>
       <c r="E1195" t="n">
-        <v>0.0</v>
+        <v>1078.38</v>
       </c>
       <c r="F1195" t="n">
         <v>0.0</v>
@@ -44280,7 +44280,7 @@
         <v>0.0</v>
       </c>
       <c r="I1195" t="n">
-        <v>0.0</v>
+        <v>1078.38</v>
       </c>
     </row>
     <row r="1196">
@@ -44305,7 +44305,7 @@
         </is>
       </c>
       <c r="E1196" t="n">
-        <v>0.0</v>
+        <v>172.1847</v>
       </c>
       <c r="F1196" t="n">
         <v>0.0</v>
@@ -44317,7 +44317,7 @@
         <v>0.0</v>
       </c>
       <c r="I1196" t="n">
-        <v>0.0</v>
+        <v>172.1847</v>
       </c>
     </row>
     <row r="1197">
@@ -44342,7 +44342,7 @@
         </is>
       </c>
       <c r="E1197" t="n">
-        <v>0.0</v>
+        <v>643.7696</v>
       </c>
       <c r="F1197" t="n">
         <v>0.0</v>
@@ -44354,7 +44354,7 @@
         <v>0.0</v>
       </c>
       <c r="I1197" t="n">
-        <v>0.0</v>
+        <v>643.7696</v>
       </c>
     </row>
     <row r="1198">
@@ -44379,7 +44379,7 @@
         </is>
       </c>
       <c r="E1198" t="n">
-        <v>0.0</v>
+        <v>115.385</v>
       </c>
       <c r="F1198" t="n">
         <v>0.0</v>
@@ -44391,7 +44391,7 @@
         <v>0.0</v>
       </c>
       <c r="I1198" t="n">
-        <v>0.0</v>
+        <v>115.385</v>
       </c>
     </row>
     <row r="1199">
@@ -44453,7 +44453,7 @@
         </is>
       </c>
       <c r="E1200" t="n">
-        <v>0.0</v>
+        <v>698.688</v>
       </c>
       <c r="F1200" t="n">
         <v>0.0</v>
@@ -44465,7 +44465,7 @@
         <v>0.0</v>
       </c>
       <c r="I1200" t="n">
-        <v>0.0</v>
+        <v>698.688</v>
       </c>
     </row>
     <row r="1201">
@@ -44527,7 +44527,7 @@
         </is>
       </c>
       <c r="E1202" t="n">
-        <v>0.0</v>
+        <v>724.2408</v>
       </c>
       <c r="F1202" t="n">
         <v>0.0</v>
@@ -44539,7 +44539,7 @@
         <v>0.0</v>
       </c>
       <c r="I1202" t="n">
-        <v>0.0</v>
+        <v>724.2408</v>
       </c>
     </row>
     <row r="1203">
@@ -44675,7 +44675,7 @@
         </is>
       </c>
       <c r="E1206" t="n">
-        <v>4239.2449</v>
+        <v>3807.705</v>
       </c>
       <c r="F1206" t="n">
         <v>0.0</v>
@@ -44687,7 +44687,7 @@
         <v>3807.705</v>
       </c>
       <c r="I1206" t="n">
-        <v>431.5399</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1207">
@@ -44749,7 +44749,7 @@
         </is>
       </c>
       <c r="E1208" t="n">
-        <v>0.0</v>
+        <v>596.448</v>
       </c>
       <c r="F1208" t="n">
         <v>0.0</v>
@@ -44761,7 +44761,7 @@
         <v>0.0</v>
       </c>
       <c r="I1208" t="n">
-        <v>0.0</v>
+        <v>596.448</v>
       </c>
     </row>
     <row r="1209">
@@ -44897,7 +44897,7 @@
         </is>
       </c>
       <c r="E1212" t="n">
-        <v>1570.3242</v>
+        <v>847.821</v>
       </c>
       <c r="F1212" t="n">
         <v>0.11699999999999999</v>
@@ -44909,7 +44909,7 @@
         <v>847.821</v>
       </c>
       <c r="I1212" t="n">
-        <v>722.5032</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1213">
@@ -45119,7 +45119,7 @@
         </is>
       </c>
       <c r="E1218" t="n">
-        <v>347.82000000000005</v>
+        <v>1081.74</v>
       </c>
       <c r="F1218" t="n">
         <v>0.0</v>
@@ -45131,7 +45131,7 @@
         <v>347.82000000000005</v>
       </c>
       <c r="I1218" t="n">
-        <v>0.0</v>
+        <v>733.92</v>
       </c>
     </row>
     <row r="1219">
@@ -45156,7 +45156,7 @@
         </is>
       </c>
       <c r="E1219" t="n">
-        <v>0.0</v>
+        <v>244.485</v>
       </c>
       <c r="F1219" t="n">
         <v>0.0</v>
@@ -45168,7 +45168,7 @@
         <v>0.0</v>
       </c>
       <c r="I1219" t="n">
-        <v>0.0</v>
+        <v>244.485</v>
       </c>
     </row>
     <row r="1220">
@@ -45674,7 +45674,7 @@
         </is>
       </c>
       <c r="E1233" t="n">
-        <v>0.0</v>
+        <v>864.0</v>
       </c>
       <c r="F1233" t="n">
         <v>0.0</v>
@@ -45686,7 +45686,7 @@
         <v>0.0</v>
       </c>
       <c r="I1233" t="n">
-        <v>0.0</v>
+        <v>864.0</v>
       </c>
     </row>
     <row r="1234">
@@ -45933,19 +45933,19 @@
         </is>
       </c>
       <c r="E1240" t="n">
-        <v>0.0</v>
+        <v>932.0466</v>
       </c>
       <c r="F1240" t="n">
         <v>0.0</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.0</v>
+        <v>10.667</v>
       </c>
       <c r="H1240" t="n">
         <v>0.0</v>
       </c>
       <c r="I1240" t="n">
-        <v>0.0</v>
+        <v>932.0466</v>
       </c>
     </row>
     <row r="1241">
@@ -46747,7 +46747,7 @@
         </is>
       </c>
       <c r="E1262" t="n">
-        <v>1.5</v>
+        <v>37.5</v>
       </c>
       <c r="F1262" t="n">
         <v>0.9</v>
@@ -46759,7 +46759,7 @@
         <v>1.5</v>
       </c>
       <c r="I1262" t="n">
-        <v>0.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="1263">
@@ -46784,7 +46784,7 @@
         </is>
       </c>
       <c r="E1263" t="n">
-        <v>588.0</v>
+        <v>1188.0</v>
       </c>
       <c r="F1263" t="n">
         <v>3.0</v>
@@ -46796,7 +46796,7 @@
         <v>588.0</v>
       </c>
       <c r="I1263" t="n">
-        <v>0.0</v>
+        <v>600.0</v>
       </c>
     </row>
     <row r="1264">
@@ -46858,7 +46858,7 @@
         </is>
       </c>
       <c r="E1265" t="n">
-        <v>5498.0</v>
+        <v>8360.0</v>
       </c>
       <c r="F1265" t="n">
         <v>4.0</v>
@@ -46870,7 +46870,7 @@
         <v>5498.0</v>
       </c>
       <c r="I1265" t="n">
-        <v>0.0</v>
+        <v>2862.0</v>
       </c>
     </row>
     <row r="1266">
@@ -46969,7 +46969,7 @@
         </is>
       </c>
       <c r="E1268" t="n">
-        <v>4926.0</v>
+        <v>5526.0</v>
       </c>
       <c r="F1268" t="n">
         <v>1.0</v>
@@ -46981,7 +46981,7 @@
         <v>4926.0</v>
       </c>
       <c r="I1268" t="n">
-        <v>0.0</v>
+        <v>600.0</v>
       </c>
     </row>
     <row r="1269">
@@ -48116,7 +48116,7 @@
         </is>
       </c>
       <c r="E1299" t="n">
-        <v>3715.9148</v>
+        <v>2045.246</v>
       </c>
       <c r="F1299" t="n">
         <v>0.0</v>
@@ -48128,7 +48128,7 @@
         <v>2045.246</v>
       </c>
       <c r="I1299" t="n">
-        <v>1670.6688</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1300">
@@ -48523,7 +48523,7 @@
         </is>
       </c>
       <c r="E1310" t="n">
-        <v>9.68</v>
+        <v>0.0</v>
       </c>
       <c r="F1310" t="n">
         <v>0.0</v>
@@ -48532,7 +48532,7 @@
         <v>0.0</v>
       </c>
       <c r="H1310" t="n">
-        <v>9.68</v>
+        <v>0.0</v>
       </c>
       <c r="I1310" t="n">
         <v>0.0</v>
@@ -48745,7 +48745,7 @@
         </is>
       </c>
       <c r="E1316" t="n">
-        <v>0.0</v>
+        <v>362.88</v>
       </c>
       <c r="F1316" t="n">
         <v>0.0</v>
@@ -48754,7 +48754,7 @@
         <v>0.0</v>
       </c>
       <c r="H1316" t="n">
-        <v>0.0</v>
+        <v>362.88</v>
       </c>
       <c r="I1316" t="n">
         <v>0.0</v>
@@ -48782,7 +48782,7 @@
         </is>
       </c>
       <c r="E1317" t="n">
-        <v>3947.4599999999996</v>
+        <v>3613.8599999999997</v>
       </c>
       <c r="F1317" t="n">
         <v>2.669</v>
@@ -48794,7 +48794,7 @@
         <v>3613.8599999999997</v>
       </c>
       <c r="I1317" t="n">
-        <v>333.6</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1318">
@@ -48930,7 +48930,7 @@
         </is>
       </c>
       <c r="E1321" t="n">
-        <v>1681.5</v>
+        <v>1987.5</v>
       </c>
       <c r="F1321" t="n">
         <v>0.0</v>
@@ -48942,7 +48942,7 @@
         <v>1681.5</v>
       </c>
       <c r="I1321" t="n">
-        <v>0.0</v>
+        <v>306.0</v>
       </c>
     </row>
     <row r="1322">
@@ -49010,7 +49010,7 @@
         <v>0.222</v>
       </c>
       <c r="G1323" t="n">
-        <v>5.92</v>
+        <v>3.552</v>
       </c>
       <c r="H1323" t="n">
         <v>4135.49</v>
@@ -49707,7 +49707,7 @@
         </is>
       </c>
       <c r="E1342" t="n">
-        <v>38.72</v>
+        <v>0.0</v>
       </c>
       <c r="F1342" t="n">
         <v>0.0</v>
@@ -49716,7 +49716,7 @@
         <v>0.0</v>
       </c>
       <c r="H1342" t="n">
-        <v>38.72</v>
+        <v>0.0</v>
       </c>
       <c r="I1342" t="n">
         <v>0.0</v>
@@ -49818,7 +49818,7 @@
         </is>
       </c>
       <c r="E1345" t="n">
-        <v>10781.952</v>
+        <v>11709.359999999999</v>
       </c>
       <c r="F1345" t="n">
         <v>0.0</v>
@@ -49830,7 +49830,7 @@
         <v>10781.952</v>
       </c>
       <c r="I1345" t="n">
-        <v>0.0</v>
+        <v>927.408</v>
       </c>
     </row>
     <row r="1346">
@@ -49929,7 +49929,7 @@
         </is>
       </c>
       <c r="E1348" t="n">
-        <v>69.0</v>
+        <v>67.4</v>
       </c>
       <c r="F1348" t="n">
         <v>0.0</v>
@@ -49938,7 +49938,7 @@
         <v>0.0</v>
       </c>
       <c r="H1348" t="n">
-        <v>69.0</v>
+        <v>67.4</v>
       </c>
       <c r="I1348" t="n">
         <v>0.0</v>
@@ -50336,7 +50336,7 @@
         </is>
       </c>
       <c r="E1359" t="n">
-        <v>14.475999999999999</v>
+        <v>0.0</v>
       </c>
       <c r="F1359" t="n">
         <v>0.0</v>
@@ -50345,7 +50345,7 @@
         <v>0.0</v>
       </c>
       <c r="H1359" t="n">
-        <v>14.475999999999999</v>
+        <v>0.0</v>
       </c>
       <c r="I1359" t="n">
         <v>0.0</v>
@@ -50780,7 +50780,7 @@
         </is>
       </c>
       <c r="E1371" t="n">
-        <v>3259.1049999999996</v>
+        <v>2458.4649999999997</v>
       </c>
       <c r="F1371" t="n">
         <v>0.0</v>
@@ -50792,7 +50792,7 @@
         <v>2458.4649999999997</v>
       </c>
       <c r="I1371" t="n">
-        <v>800.64</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1372">
@@ -50854,7 +50854,7 @@
         </is>
       </c>
       <c r="E1373" t="n">
-        <v>1370.874</v>
+        <v>676.986</v>
       </c>
       <c r="F1373" t="n">
         <v>0.0</v>
@@ -50866,7 +50866,7 @@
         <v>676.986</v>
       </c>
       <c r="I1373" t="n">
-        <v>693.888</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1374">
@@ -51113,7 +51113,7 @@
         </is>
       </c>
       <c r="E1380" t="n">
-        <v>0.0</v>
+        <v>282.74399999999997</v>
       </c>
       <c r="F1380" t="n">
         <v>0.0</v>
@@ -51122,7 +51122,7 @@
         <v>0.0</v>
       </c>
       <c r="H1380" t="n">
-        <v>0.0</v>
+        <v>282.74399999999997</v>
       </c>
       <c r="I1380" t="n">
         <v>0.0</v>
@@ -51150,7 +51150,7 @@
         </is>
       </c>
       <c r="E1381" t="n">
-        <v>0.0</v>
+        <v>29.358999999999998</v>
       </c>
       <c r="F1381" t="n">
         <v>0.0</v>
@@ -51159,7 +51159,7 @@
         <v>0.0</v>
       </c>
       <c r="H1381" t="n">
-        <v>0.0</v>
+        <v>29.358999999999998</v>
       </c>
       <c r="I1381" t="n">
         <v>0.0</v>
@@ -51372,7 +51372,7 @@
         </is>
       </c>
       <c r="E1387" t="n">
-        <v>124.373</v>
+        <v>124.248</v>
       </c>
       <c r="F1387" t="n">
         <v>0.25</v>
@@ -51381,7 +51381,7 @@
         <v>0.0</v>
       </c>
       <c r="H1387" t="n">
-        <v>124.373</v>
+        <v>124.248</v>
       </c>
       <c r="I1387" t="n">
         <v>0.0</v>
@@ -51483,7 +51483,7 @@
         </is>
       </c>
       <c r="E1390" t="n">
-        <v>41.25</v>
+        <v>466.5</v>
       </c>
       <c r="F1390" t="n">
         <v>0.0</v>
@@ -51495,7 +51495,7 @@
         <v>41.25</v>
       </c>
       <c r="I1390" t="n">
-        <v>0.0</v>
+        <v>425.25</v>
       </c>
     </row>
     <row r="1391">
@@ -51631,7 +51631,7 @@
         </is>
       </c>
       <c r="E1394" t="n">
-        <v>854.375</v>
+        <v>851.375</v>
       </c>
       <c r="F1394" t="n">
         <v>0.0</v>
@@ -51640,7 +51640,7 @@
         <v>0.0</v>
       </c>
       <c r="H1394" t="n">
-        <v>854.375</v>
+        <v>851.375</v>
       </c>
       <c r="I1394" t="n">
         <v>0.0</v>
@@ -51853,7 +51853,7 @@
         </is>
       </c>
       <c r="E1400" t="n">
-        <v>3752.25</v>
+        <v>4049.25</v>
       </c>
       <c r="F1400" t="n">
         <v>0.0</v>
@@ -51865,7 +51865,7 @@
         <v>3752.25</v>
       </c>
       <c r="I1400" t="n">
-        <v>0.0</v>
+        <v>297.0</v>
       </c>
     </row>
     <row r="1401">
@@ -51927,7 +51927,7 @@
         </is>
       </c>
       <c r="E1402" t="n">
-        <v>123.437</v>
+        <v>264.437</v>
       </c>
       <c r="F1402" t="n">
         <v>0.0</v>
@@ -51936,10 +51936,10 @@
         <v>0.0</v>
       </c>
       <c r="H1402" t="n">
-        <v>123.437</v>
+        <v>123.062</v>
       </c>
       <c r="I1402" t="n">
-        <v>0.0</v>
+        <v>141.375</v>
       </c>
     </row>
     <row r="1403">
@@ -52075,7 +52075,7 @@
         </is>
       </c>
       <c r="E1406" t="n">
-        <v>38.163999999999994</v>
+        <v>0.0</v>
       </c>
       <c r="F1406" t="n">
         <v>0.0</v>
@@ -52084,7 +52084,7 @@
         <v>0.0</v>
       </c>
       <c r="H1406" t="n">
-        <v>38.163999999999994</v>
+        <v>0.0</v>
       </c>
       <c r="I1406" t="n">
         <v>0.0</v>
@@ -52451,7 +52451,7 @@
         <v>1.835</v>
       </c>
       <c r="G1416" t="n">
-        <v>2.085</v>
+        <v>7.812</v>
       </c>
       <c r="H1416" t="n">
         <v>128.546</v>
@@ -52741,16 +52741,16 @@
         </is>
       </c>
       <c r="E1424" t="n">
-        <v>5140.769</v>
+        <v>5151.309</v>
       </c>
       <c r="F1424" t="n">
         <v>0.393</v>
       </c>
       <c r="G1424" t="n">
-        <v>617.0889999999999</v>
+        <v>619.053</v>
       </c>
       <c r="H1424" t="n">
-        <v>5140.769</v>
+        <v>5151.309</v>
       </c>
       <c r="I1424" t="n">
         <v>0.0</v>
@@ -52926,7 +52926,7 @@
         </is>
       </c>
       <c r="E1429" t="n">
-        <v>0.0</v>
+        <v>148.01</v>
       </c>
       <c r="F1429" t="n">
         <v>0.809</v>
@@ -52935,7 +52935,7 @@
         <v>0.0</v>
       </c>
       <c r="H1429" t="n">
-        <v>0.0</v>
+        <v>148.01</v>
       </c>
       <c r="I1429" t="n">
         <v>0.0</v>
@@ -53037,7 +53037,7 @@
         </is>
       </c>
       <c r="E1432" t="n">
-        <v>7651.200000000001</v>
+        <v>7675.2</v>
       </c>
       <c r="F1432" t="n">
         <v>0.0</v>
@@ -53046,10 +53046,10 @@
         <v>0.0</v>
       </c>
       <c r="H1432" t="n">
-        <v>7651.200000000001</v>
+        <v>7646.4</v>
       </c>
       <c r="I1432" t="n">
-        <v>0.0</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="1433">
@@ -53111,7 +53111,7 @@
         </is>
       </c>
       <c r="E1434" t="n">
-        <v>616.4929999999999</v>
+        <v>616.493</v>
       </c>
       <c r="F1434" t="n">
         <v>0.0</v>
@@ -53120,7 +53120,7 @@
         <v>0.0</v>
       </c>
       <c r="H1434" t="n">
-        <v>616.4929999999999</v>
+        <v>616.493</v>
       </c>
       <c r="I1434" t="n">
         <v>0.0</v>
@@ -53604,13 +53604,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A70F7DDE-E794-467B-B34C-E74F5C2BCE8D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80DE0575-8374-4479-A5F7-B2340AD9F240}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4290E4C-93D6-4A5E-AF67-41A96B62F414}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{977A29F3-EAF4-4F5C-888F-FCC934DB5C23}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{955F03CF-9225-4F1A-B864-A39D20C89CC7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B88E944-D298-4E60-BAB5-097F0DA5049E}"/>
 </file>
--- a/Inventory_KNIME.xlsx
+++ b/Inventory_KNIME.xlsx
@@ -423,7 +423,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>722.3</v>
+        <v>718.7</v>
       </c>
       <c r="F10" t="n">
         <v>0.0</v>
@@ -432,7 +432,7 @@
         <v>0.2</v>
       </c>
       <c r="H10" t="n">
-        <v>722.3</v>
+        <v>718.7</v>
       </c>
       <c r="I10" t="n">
         <v>0.0</v>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1217.5</v>
+        <v>1127.5</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
@@ -691,7 +691,7 @@
         <v>0.5</v>
       </c>
       <c r="H17" t="n">
-        <v>1217.5</v>
+        <v>1127.5</v>
       </c>
       <c r="I17" t="n">
         <v>0.0</v>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>11390.5</v>
+        <v>11357.5</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -839,7 +839,7 @@
         <v>0.0</v>
       </c>
       <c r="H21" t="n">
-        <v>11390.5</v>
+        <v>11357.5</v>
       </c>
       <c r="I21" t="n">
         <v>0.0</v>
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2179.5</v>
+        <v>2443.5</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -876,7 +876,7 @@
         <v>2007.0000000000002</v>
       </c>
       <c r="H22" t="n">
-        <v>2179.5</v>
+        <v>2443.5</v>
       </c>
       <c r="I22" t="n">
         <v>0.0</v>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>178.5</v>
+        <v>170.7</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -950,7 +950,7 @@
         <v>0.4</v>
       </c>
       <c r="H24" t="n">
-        <v>178.5</v>
+        <v>170.7</v>
       </c>
       <c r="I24" t="n">
         <v>0.0</v>
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3596.3289999999997</v>
+        <v>3583.5009999999997</v>
       </c>
       <c r="F34" t="n">
         <v>37.094</v>
@@ -1320,7 +1320,7 @@
         <v>4.971</v>
       </c>
       <c r="H34" t="n">
-        <v>3596.3289999999997</v>
+        <v>3583.5009999999997</v>
       </c>
       <c r="I34" t="n">
         <v>0.0</v>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2376.153</v>
+        <v>2368.909</v>
       </c>
       <c r="F35" t="n">
         <v>282.264</v>
@@ -1357,7 +1357,7 @@
         <v>192.623</v>
       </c>
       <c r="H35" t="n">
-        <v>2376.153</v>
+        <v>2368.909</v>
       </c>
       <c r="I35" t="n">
         <v>0.0</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1870.103</v>
+        <v>1819.444</v>
       </c>
       <c r="F39" t="n">
         <v>2200.261</v>
@@ -1505,7 +1505,7 @@
         <v>3.179</v>
       </c>
       <c r="H39" t="n">
-        <v>1870.103</v>
+        <v>1819.444</v>
       </c>
       <c r="I39" t="n">
         <v>0.0</v>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>989.538</v>
+        <v>968.743</v>
       </c>
       <c r="F40" t="n">
         <v>17.094</v>
@@ -1542,7 +1542,7 @@
         <v>25.329</v>
       </c>
       <c r="H40" t="n">
-        <v>989.538</v>
+        <v>968.743</v>
       </c>
       <c r="I40" t="n">
         <v>0.0</v>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1133.995</v>
+        <v>1095.511</v>
       </c>
       <c r="F42" t="n">
         <v>767.328</v>
@@ -1616,7 +1616,7 @@
         <v>332.94</v>
       </c>
       <c r="H42" t="n">
-        <v>1133.995</v>
+        <v>1095.511</v>
       </c>
       <c r="I42" t="n">
         <v>0.0</v>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>127.749</v>
+        <v>126.68299999999999</v>
       </c>
       <c r="F68" t="n">
         <v>3.467</v>
@@ -2578,7 +2578,7 @@
         <v>0.0</v>
       </c>
       <c r="H68" t="n">
-        <v>127.749</v>
+        <v>126.68299999999999</v>
       </c>
       <c r="I68" t="n">
         <v>0.0</v>
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1529.791</v>
+        <v>1482.8519999999999</v>
       </c>
       <c r="F72" t="n">
         <v>4.534</v>
@@ -2726,7 +2726,7 @@
         <v>17.069000000000003</v>
       </c>
       <c r="H72" t="n">
-        <v>1529.791</v>
+        <v>1482.8519999999999</v>
       </c>
       <c r="I72" t="n">
         <v>0.0</v>
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2031.13</v>
+        <v>1986.024</v>
       </c>
       <c r="F74" t="n">
         <v>5.777</v>
@@ -2800,7 +2800,7 @@
         <v>0.0</v>
       </c>
       <c r="H74" t="n">
-        <v>2031.13</v>
+        <v>1986.024</v>
       </c>
       <c r="I74" t="n">
         <v>0.0</v>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>7055.015</v>
+        <v>7053.6810000000005</v>
       </c>
       <c r="F76" t="n">
         <v>9.601</v>
@@ -2874,7 +2874,7 @@
         <v>17.069000000000003</v>
       </c>
       <c r="H76" t="n">
-        <v>7055.015</v>
+        <v>7053.6810000000005</v>
       </c>
       <c r="I76" t="n">
         <v>0.0</v>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>425.11999999999995</v>
+        <v>424.853</v>
       </c>
       <c r="F77" t="n">
         <v>1.333</v>
@@ -2911,7 +2911,7 @@
         <v>0.0</v>
       </c>
       <c r="H77" t="n">
-        <v>425.11999999999995</v>
+        <v>424.853</v>
       </c>
       <c r="I77" t="n">
         <v>0.0</v>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1152.1429999999998</v>
+        <v>1145.743</v>
       </c>
       <c r="F78" t="n">
         <v>50.94</v>
@@ -2948,7 +2948,7 @@
         <v>0.0</v>
       </c>
       <c r="H78" t="n">
-        <v>1152.1429999999998</v>
+        <v>1145.743</v>
       </c>
       <c r="I78" t="n">
         <v>0.0</v>
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3353.704</v>
+        <v>3319.932</v>
       </c>
       <c r="F86" t="n">
         <v>0.0</v>
@@ -3244,7 +3244,7 @@
         <v>0.0</v>
       </c>
       <c r="H86" t="n">
-        <v>3353.704</v>
+        <v>3319.932</v>
       </c>
       <c r="I86" t="n">
         <v>0.0</v>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>533.704</v>
+        <v>505.682</v>
       </c>
       <c r="F106" t="n">
         <v>0.0</v>
@@ -3984,7 +3984,7 @@
         <v>4.002999999999999</v>
       </c>
       <c r="H106" t="n">
-        <v>533.704</v>
+        <v>505.682</v>
       </c>
       <c r="I106" t="n">
         <v>0.0</v>
@@ -4012,7 +4012,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1011.4749999999999</v>
+        <v>998.133</v>
       </c>
       <c r="F107" t="n">
         <v>0.0</v>
@@ -4021,7 +4021,7 @@
         <v>24.853</v>
       </c>
       <c r="H107" t="n">
-        <v>1011.4749999999999</v>
+        <v>998.133</v>
       </c>
       <c r="I107" t="n">
         <v>0.0</v>
@@ -4049,7 +4049,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>804.8100000000001</v>
+        <v>751.435</v>
       </c>
       <c r="F108" t="n">
         <v>0.0</v>
@@ -4058,7 +4058,7 @@
         <v>18.96</v>
       </c>
       <c r="H108" t="n">
-        <v>804.8100000000001</v>
+        <v>751.435</v>
       </c>
       <c r="I108" t="n">
         <v>0.0</v>
@@ -4123,7 +4123,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1037.857</v>
+        <v>933.773</v>
       </c>
       <c r="F110" t="n">
         <v>0.0</v>
@@ -4132,7 +4132,7 @@
         <v>69.38900000000001</v>
       </c>
       <c r="H110" t="n">
-        <v>1037.857</v>
+        <v>933.773</v>
       </c>
       <c r="I110" t="n">
         <v>0.0</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>482.38599999999997</v>
+        <v>471.71</v>
       </c>
       <c r="F114" t="n">
         <v>0.0</v>
@@ -4280,7 +4280,7 @@
         <v>8.283999999999999</v>
       </c>
       <c r="H114" t="n">
-        <v>482.38599999999997</v>
+        <v>471.71</v>
       </c>
       <c r="I114" t="n">
         <v>0.0</v>
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>969.439</v>
+        <v>953.427</v>
       </c>
       <c r="F115" t="n">
         <v>0.0</v>
@@ -4317,7 +4317,7 @@
         <v>0.0</v>
       </c>
       <c r="H115" t="n">
-        <v>969.439</v>
+        <v>953.427</v>
       </c>
       <c r="I115" t="n">
         <v>0.0</v>
@@ -4604,7 +4604,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>896.28</v>
+        <v>1656.12</v>
       </c>
       <c r="F123" t="n">
         <v>0.0</v>
@@ -4613,10 +4613,10 @@
         <v>25.44</v>
       </c>
       <c r="H123" t="n">
-        <v>896.28</v>
+        <v>948.12</v>
       </c>
       <c r="I123" t="n">
-        <v>0.0</v>
+        <v>708.0</v>
       </c>
     </row>
     <row r="124">
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1675.3500000000001</v>
+        <v>1543.7250000000001</v>
       </c>
       <c r="F124" t="n">
         <v>0.0</v>
@@ -4650,7 +4650,7 @@
         <v>116.775</v>
       </c>
       <c r="H124" t="n">
-        <v>1675.3500000000001</v>
+        <v>1543.7250000000001</v>
       </c>
       <c r="I124" t="n">
         <v>0.0</v>
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4752.649</v>
+        <v>4738.959</v>
       </c>
       <c r="F125" t="n">
         <v>0.0</v>
@@ -4687,7 +4687,7 @@
         <v>118.215</v>
       </c>
       <c r="H125" t="n">
-        <v>4752.649</v>
+        <v>4738.959</v>
       </c>
       <c r="I125" t="n">
         <v>0.0</v>
@@ -4789,7 +4789,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>714.516</v>
+        <v>693.241</v>
       </c>
       <c r="F128" t="n">
         <v>0.0</v>
@@ -4798,7 +4798,7 @@
         <v>106.005</v>
       </c>
       <c r="H128" t="n">
-        <v>714.516</v>
+        <v>693.241</v>
       </c>
       <c r="I128" t="n">
         <v>0.0</v>
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>483.88000000000005</v>
+        <v>461.92</v>
       </c>
       <c r="F129" t="n">
         <v>0.0</v>
@@ -4835,7 +4835,7 @@
         <v>75.39999999999999</v>
       </c>
       <c r="H129" t="n">
-        <v>483.88000000000005</v>
+        <v>461.92</v>
       </c>
       <c r="I129" t="n">
         <v>0.0</v>
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1400.564</v>
+        <v>1407.2359999999999</v>
       </c>
       <c r="F131" t="n">
         <v>0.0</v>
@@ -4909,7 +4909,7 @@
         <v>787.296</v>
       </c>
       <c r="H131" t="n">
-        <v>1400.564</v>
+        <v>1407.2359999999999</v>
       </c>
       <c r="I131" t="n">
         <v>0.0</v>
@@ -4937,7 +4937,7 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>467.039</v>
+        <v>464.371</v>
       </c>
       <c r="F132" t="n">
         <v>0.0</v>
@@ -4946,7 +4946,7 @@
         <v>0.0</v>
       </c>
       <c r="H132" t="n">
-        <v>467.039</v>
+        <v>464.371</v>
       </c>
       <c r="I132" t="n">
         <v>0.0</v>
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4348.0</v>
+        <v>4346.8</v>
       </c>
       <c r="F141" t="n">
         <v>0.0</v>
@@ -5279,7 +5279,7 @@
         <v>1.0</v>
       </c>
       <c r="H141" t="n">
-        <v>4348.0</v>
+        <v>4346.8</v>
       </c>
       <c r="I141" t="n">
         <v>0.0</v>
@@ -5381,7 +5381,7 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>856.5</v>
+        <v>1003.5000000000001</v>
       </c>
       <c r="F144" t="n">
         <v>0.0</v>
@@ -5390,7 +5390,7 @@
         <v>501.0</v>
       </c>
       <c r="H144" t="n">
-        <v>856.5</v>
+        <v>1003.5000000000001</v>
       </c>
       <c r="I144" t="n">
         <v>0.0</v>
@@ -5418,7 +5418,7 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>883.5</v>
+        <v>877.5</v>
       </c>
       <c r="F145" t="n">
         <v>0.0</v>
@@ -5427,7 +5427,7 @@
         <v>2.5</v>
       </c>
       <c r="H145" t="n">
-        <v>883.5</v>
+        <v>877.5</v>
       </c>
       <c r="I145" t="n">
         <v>0.0</v>
@@ -6010,7 +6010,7 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>9079.454</v>
+        <v>8070.646</v>
       </c>
       <c r="F161" t="n">
         <v>0.0</v>
@@ -6019,7 +6019,7 @@
         <v>2248.603</v>
       </c>
       <c r="H161" t="n">
-        <v>9079.454</v>
+        <v>8070.646</v>
       </c>
       <c r="I161" t="n">
         <v>0.0</v>
@@ -6972,7 +6972,7 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>2757.0</v>
+        <v>2742.0</v>
       </c>
       <c r="F187" t="n">
         <v>0.0</v>
@@ -6981,7 +6981,7 @@
         <v>0.0</v>
       </c>
       <c r="H187" t="n">
-        <v>2757.0</v>
+        <v>2742.0</v>
       </c>
       <c r="I187" t="n">
         <v>0.0</v>
@@ -7194,7 +7194,7 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>1098.224</v>
+        <v>1098.2240000000002</v>
       </c>
       <c r="F193" t="n">
         <v>0.0</v>
@@ -7203,7 +7203,7 @@
         <v>4.201</v>
       </c>
       <c r="H193" t="n">
-        <v>1098.224</v>
+        <v>1098.2240000000002</v>
       </c>
       <c r="I193" t="n">
         <v>0.0</v>
@@ -7490,7 +7490,7 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>167.75</v>
+        <v>150.125</v>
       </c>
       <c r="F201" t="n">
         <v>0.0</v>
@@ -7499,7 +7499,7 @@
         <v>79.125</v>
       </c>
       <c r="H201" t="n">
-        <v>167.75</v>
+        <v>150.125</v>
       </c>
       <c r="I201" t="n">
         <v>0.0</v>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>423.75</v>
+        <v>423.0</v>
       </c>
       <c r="F202" t="n">
         <v>0.0</v>
@@ -7536,7 +7536,7 @@
         <v>9.0</v>
       </c>
       <c r="H202" t="n">
-        <v>423.75</v>
+        <v>423.0</v>
       </c>
       <c r="I202" t="n">
         <v>0.0</v>
@@ -7675,7 +7675,7 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>862.347</v>
+        <v>862.1759999999999</v>
       </c>
       <c r="F206" t="n">
         <v>0.0</v>
@@ -7684,7 +7684,7 @@
         <v>0.859</v>
       </c>
       <c r="H206" t="n">
-        <v>862.347</v>
+        <v>862.1759999999999</v>
       </c>
       <c r="I206" t="n">
         <v>0.0</v>
@@ -7749,7 +7749,7 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>691.8960000000001</v>
+        <v>688.116</v>
       </c>
       <c r="F208" t="n">
         <v>0.34400000000000003</v>
@@ -7758,7 +7758,7 @@
         <v>0.34400000000000003</v>
       </c>
       <c r="H208" t="n">
-        <v>691.8960000000001</v>
+        <v>688.116</v>
       </c>
       <c r="I208" t="n">
         <v>0.0</v>
@@ -7786,7 +7786,7 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>848.13</v>
+        <v>841.943</v>
       </c>
       <c r="F209" t="n">
         <v>0.0</v>
@@ -7795,7 +7795,7 @@
         <v>0.0</v>
       </c>
       <c r="H209" t="n">
-        <v>848.13</v>
+        <v>841.943</v>
       </c>
       <c r="I209" t="n">
         <v>0.0</v>
@@ -7823,7 +7823,7 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>600.013</v>
+        <v>590.391</v>
       </c>
       <c r="F210" t="n">
         <v>0.0</v>
@@ -7832,7 +7832,7 @@
         <v>22.681</v>
       </c>
       <c r="H210" t="n">
-        <v>600.013</v>
+        <v>590.391</v>
       </c>
       <c r="I210" t="n">
         <v>0.0</v>
@@ -7860,7 +7860,7 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>497.834</v>
+        <v>488.899</v>
       </c>
       <c r="F211" t="n">
         <v>0.0</v>
@@ -7869,7 +7869,7 @@
         <v>48.111000000000004</v>
       </c>
       <c r="H211" t="n">
-        <v>497.834</v>
+        <v>488.899</v>
       </c>
       <c r="I211" t="n">
         <v>0.0</v>
@@ -7934,7 +7934,7 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>869.423</v>
+        <v>868.334</v>
       </c>
       <c r="F213" t="n">
         <v>0.0</v>
@@ -7943,7 +7943,7 @@
         <v>1.374</v>
       </c>
       <c r="H213" t="n">
-        <v>869.423</v>
+        <v>868.334</v>
       </c>
       <c r="I213" t="n">
         <v>0.0</v>
@@ -7971,7 +7971,7 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>160.576</v>
+        <v>158.801</v>
       </c>
       <c r="F214" t="n">
         <v>0.0</v>
@@ -7980,7 +7980,7 @@
         <v>43.981</v>
       </c>
       <c r="H214" t="n">
-        <v>160.576</v>
+        <v>158.801</v>
       </c>
       <c r="I214" t="n">
         <v>0.0</v>
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>120.965</v>
+        <v>111.343</v>
       </c>
       <c r="F215" t="n">
         <v>0.0</v>
@@ -8017,7 +8017,7 @@
         <v>11.684</v>
       </c>
       <c r="H215" t="n">
-        <v>120.965</v>
+        <v>111.343</v>
       </c>
       <c r="I215" t="n">
         <v>0.0</v>
@@ -8045,7 +8045,7 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>1844.157</v>
+        <v>1831.386</v>
       </c>
       <c r="F216" t="n">
         <v>0.34400000000000003</v>
@@ -8054,7 +8054,7 @@
         <v>0.34400000000000003</v>
       </c>
       <c r="H216" t="n">
-        <v>1844.157</v>
+        <v>1831.386</v>
       </c>
       <c r="I216" t="n">
         <v>0.0</v>
@@ -8082,7 +8082,7 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>191.07</v>
+        <v>186.946</v>
       </c>
       <c r="F217" t="n">
         <v>0.0</v>
@@ -8091,7 +8091,7 @@
         <v>1019.9530000000001</v>
       </c>
       <c r="H217" t="n">
-        <v>191.07</v>
+        <v>186.946</v>
       </c>
       <c r="I217" t="n">
         <v>0.0</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>782.663</v>
+        <v>782.2049999999999</v>
       </c>
       <c r="F218" t="n">
         <v>0.0</v>
@@ -8128,7 +8128,7 @@
         <v>7.216</v>
       </c>
       <c r="H218" t="n">
-        <v>782.663</v>
+        <v>782.2049999999999</v>
       </c>
       <c r="I218" t="n">
         <v>0.0</v>
@@ -8193,7 +8193,7 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>301.023</v>
+        <v>293.806</v>
       </c>
       <c r="F220" t="n">
         <v>0.0</v>
@@ -8202,7 +8202,7 @@
         <v>0.0</v>
       </c>
       <c r="H220" t="n">
-        <v>301.023</v>
+        <v>293.806</v>
       </c>
       <c r="I220" t="n">
         <v>0.0</v>
@@ -8230,7 +8230,7 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>113.398</v>
+        <v>112.368</v>
       </c>
       <c r="F221" t="n">
         <v>0.0</v>
@@ -8239,7 +8239,7 @@
         <v>0.859</v>
       </c>
       <c r="H221" t="n">
-        <v>113.398</v>
+        <v>112.368</v>
       </c>
       <c r="I221" t="n">
         <v>0.0</v>
@@ -8267,7 +8267,7 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>313.393</v>
+        <v>305.146</v>
       </c>
       <c r="F222" t="n">
         <v>0.0</v>
@@ -8276,7 +8276,7 @@
         <v>0.0</v>
       </c>
       <c r="H222" t="n">
-        <v>313.393</v>
+        <v>305.146</v>
       </c>
       <c r="I222" t="n">
         <v>0.0</v>
@@ -8304,7 +8304,7 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>111.343</v>
+        <v>105.157</v>
       </c>
       <c r="F223" t="n">
         <v>0.0</v>
@@ -8313,7 +8313,7 @@
         <v>685.238</v>
       </c>
       <c r="H223" t="n">
-        <v>111.343</v>
+        <v>105.157</v>
       </c>
       <c r="I223" t="n">
         <v>0.0</v>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>1179.864</v>
+        <v>1172.248</v>
       </c>
       <c r="F224" t="n">
         <v>0.0</v>
@@ -8350,7 +8350,7 @@
         <v>3.436</v>
       </c>
       <c r="H224" t="n">
-        <v>1179.864</v>
+        <v>1172.248</v>
       </c>
       <c r="I224" t="n">
         <v>0.0</v>
@@ -8896,7 +8896,7 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>88.738</v>
+        <v>86.07</v>
       </c>
       <c r="F239" t="n">
         <v>0.0</v>
@@ -8905,7 +8905,7 @@
         <v>1.056</v>
       </c>
       <c r="H239" t="n">
-        <v>88.738</v>
+        <v>86.07</v>
       </c>
       <c r="I239" t="n">
         <v>0.0</v>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>101.414</v>
+        <v>100.747</v>
       </c>
       <c r="F240" t="n">
         <v>0.0</v>
@@ -8942,7 +8942,7 @@
         <v>0.0</v>
       </c>
       <c r="H240" t="n">
-        <v>101.414</v>
+        <v>100.747</v>
       </c>
       <c r="I240" t="n">
         <v>0.0</v>
@@ -8970,7 +8970,7 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>83.4</v>
+        <v>82.733</v>
       </c>
       <c r="F241" t="n">
         <v>0.0</v>
@@ -8979,7 +8979,7 @@
         <v>0.0</v>
       </c>
       <c r="H241" t="n">
-        <v>83.4</v>
+        <v>82.733</v>
       </c>
       <c r="I241" t="n">
         <v>0.0</v>
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>115.425</v>
+        <v>114.758</v>
       </c>
       <c r="F242" t="n">
         <v>0.0</v>
@@ -9016,7 +9016,7 @@
         <v>5.338</v>
       </c>
       <c r="H242" t="n">
-        <v>115.425</v>
+        <v>114.758</v>
       </c>
       <c r="I242" t="n">
         <v>0.0</v>
@@ -9377,7 +9377,7 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>8289.712000000001</v>
+        <v>9465.9244</v>
       </c>
       <c r="F252" t="n">
         <v>0.0</v>
@@ -9386,10 +9386,10 @@
         <v>1246.121</v>
       </c>
       <c r="H252" t="n">
-        <v>8289.712000000001</v>
+        <v>8286.778</v>
       </c>
       <c r="I252" t="n">
-        <v>0.0</v>
+        <v>1179.1464</v>
       </c>
     </row>
     <row r="253">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>9605.925</v>
+        <v>9083.304999999998</v>
       </c>
       <c r="F253" t="n">
         <v>1.7329999999999999</v>
@@ -9423,7 +9423,7 @@
         <v>291.79</v>
       </c>
       <c r="H253" t="n">
-        <v>9605.925</v>
+        <v>9083.304999999998</v>
       </c>
       <c r="I253" t="n">
         <v>0.0</v>
@@ -9451,7 +9451,7 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>4343.0</v>
+        <v>4341.0</v>
       </c>
       <c r="F254" t="n">
         <v>0.0</v>
@@ -9460,7 +9460,7 @@
         <v>100.334</v>
       </c>
       <c r="H254" t="n">
-        <v>4343.0</v>
+        <v>4341.0</v>
       </c>
       <c r="I254" t="n">
         <v>0.0</v>
@@ -9710,7 +9710,7 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>1050.2</v>
+        <v>1005.4</v>
       </c>
       <c r="F261" t="n">
         <v>5.4</v>
@@ -9719,7 +9719,7 @@
         <v>8.0</v>
       </c>
       <c r="H261" t="n">
-        <v>1050.2</v>
+        <v>1005.4</v>
       </c>
       <c r="I261" t="n">
         <v>0.0</v>
@@ -9784,7 +9784,7 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>315.353</v>
+        <v>315.214</v>
       </c>
       <c r="F263" t="n">
         <v>0.0</v>
@@ -9793,7 +9793,7 @@
         <v>604.1959999999999</v>
       </c>
       <c r="H263" t="n">
-        <v>315.353</v>
+        <v>315.214</v>
       </c>
       <c r="I263" t="n">
         <v>0.0</v>
@@ -9821,7 +9821,7 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>227.20000000000002</v>
+        <v>227.0</v>
       </c>
       <c r="F264" t="n">
         <v>0.6</v>
@@ -9830,7 +9830,7 @@
         <v>8.0</v>
       </c>
       <c r="H264" t="n">
-        <v>227.20000000000002</v>
+        <v>227.0</v>
       </c>
       <c r="I264" t="n">
         <v>0.0</v>
@@ -9858,7 +9858,7 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>6651.95</v>
+        <v>3319.4519999999998</v>
       </c>
       <c r="F265" t="n">
         <v>1.31</v>
@@ -9867,10 +9867,10 @@
         <v>62.620999999999995</v>
       </c>
       <c r="H265" t="n">
-        <v>3339.4669999999996</v>
+        <v>3319.4519999999998</v>
       </c>
       <c r="I265" t="n">
-        <v>3312.483</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="266">
@@ -9895,7 +9895,7 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>3628.6270000000004</v>
+        <v>1939.132</v>
       </c>
       <c r="F266" t="n">
         <v>3.791</v>
@@ -9904,10 +9904,10 @@
         <v>124.306</v>
       </c>
       <c r="H266" t="n">
-        <v>1964.669</v>
+        <v>1939.132</v>
       </c>
       <c r="I266" t="n">
-        <v>1663.958</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="267">
@@ -9932,7 +9932,7 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>3421.121</v>
+        <v>3401.5730000000003</v>
       </c>
       <c r="F267" t="n">
         <v>3.367</v>
@@ -9941,7 +9941,7 @@
         <v>145.07</v>
       </c>
       <c r="H267" t="n">
-        <v>3421.121</v>
+        <v>3401.5730000000003</v>
       </c>
       <c r="I267" t="n">
         <v>0.0</v>
@@ -10339,7 +10339,7 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>356.96200000000005</v>
+        <v>349.68199999999996</v>
       </c>
       <c r="F278" t="n">
         <v>0.04</v>
@@ -10348,7 +10348,7 @@
         <v>3.8400000000000003</v>
       </c>
       <c r="H278" t="n">
-        <v>356.96200000000005</v>
+        <v>349.68199999999996</v>
       </c>
       <c r="I278" t="n">
         <v>0.0</v>
@@ -10376,7 +10376,7 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>436.401</v>
+        <v>428.601</v>
       </c>
       <c r="F279" t="n">
         <v>0.0</v>
@@ -10385,7 +10385,7 @@
         <v>0.0</v>
       </c>
       <c r="H279" t="n">
-        <v>436.401</v>
+        <v>428.601</v>
       </c>
       <c r="I279" t="n">
         <v>0.0</v>
@@ -10413,7 +10413,7 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>603.439</v>
+        <v>596.519</v>
       </c>
       <c r="F280" t="n">
         <v>0.08</v>
@@ -10422,7 +10422,7 @@
         <v>0.0</v>
       </c>
       <c r="H280" t="n">
-        <v>603.439</v>
+        <v>596.519</v>
       </c>
       <c r="I280" t="n">
         <v>0.0</v>
@@ -10450,7 +10450,7 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>347.4</v>
+        <v>341.96</v>
       </c>
       <c r="F281" t="n">
         <v>0.0</v>
@@ -10459,7 +10459,7 @@
         <v>0.44</v>
       </c>
       <c r="H281" t="n">
-        <v>347.4</v>
+        <v>341.96</v>
       </c>
       <c r="I281" t="n">
         <v>0.0</v>
@@ -10561,7 +10561,7 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>3871.976</v>
+        <v>3851.975</v>
       </c>
       <c r="F284" t="n">
         <v>0.0</v>
@@ -10570,7 +10570,7 @@
         <v>18.752000000000002</v>
       </c>
       <c r="H284" t="n">
-        <v>3871.976</v>
+        <v>3851.975</v>
       </c>
       <c r="I284" t="n">
         <v>0.0</v>
@@ -10598,7 +10598,7 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>2776.8</v>
+        <v>2702.4</v>
       </c>
       <c r="F285" t="n">
         <v>0.0</v>
@@ -10607,7 +10607,7 @@
         <v>194.39999999999998</v>
       </c>
       <c r="H285" t="n">
-        <v>2776.8</v>
+        <v>2702.4</v>
       </c>
       <c r="I285" t="n">
         <v>0.0</v>
@@ -10635,7 +10635,7 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>4735.599999999999</v>
+        <v>4587.4</v>
       </c>
       <c r="F286" t="n">
         <v>0.2</v>
@@ -10644,7 +10644,7 @@
         <v>84.0</v>
       </c>
       <c r="H286" t="n">
-        <v>4735.599999999999</v>
+        <v>4587.4</v>
       </c>
       <c r="I286" t="n">
         <v>0.0</v>
@@ -10672,7 +10672,7 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>2412.204</v>
+        <v>2329.103</v>
       </c>
       <c r="F287" t="n">
         <v>2.222</v>
@@ -10681,7 +10681,7 @@
         <v>18.665000000000003</v>
       </c>
       <c r="H287" t="n">
-        <v>2412.204</v>
+        <v>2329.103</v>
       </c>
       <c r="I287" t="n">
         <v>0.0</v>
@@ -10709,7 +10709,7 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>5300.359</v>
+        <v>5229.477</v>
       </c>
       <c r="F288" t="n">
         <v>0.444</v>
@@ -10718,7 +10718,7 @@
         <v>383.96200000000005</v>
       </c>
       <c r="H288" t="n">
-        <v>5300.359</v>
+        <v>5229.477</v>
       </c>
       <c r="I288" t="n">
         <v>0.0</v>
@@ -10746,7 +10746,7 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>1325.2</v>
+        <v>1310.5349999999999</v>
       </c>
       <c r="F289" t="n">
         <v>0.444</v>
@@ -10755,7 +10755,7 @@
         <v>0.0</v>
       </c>
       <c r="H289" t="n">
-        <v>1325.2</v>
+        <v>1310.5349999999999</v>
       </c>
       <c r="I289" t="n">
         <v>0.0</v>
@@ -10783,7 +10783,7 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>3800.954</v>
+        <v>3671.634</v>
       </c>
       <c r="F290" t="n">
         <v>0.0</v>
@@ -10792,7 +10792,7 @@
         <v>351.965</v>
       </c>
       <c r="H290" t="n">
-        <v>3800.954</v>
+        <v>3671.634</v>
       </c>
       <c r="I290" t="n">
         <v>0.0</v>
@@ -11079,7 +11079,7 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>1134.0</v>
+        <v>1131.0</v>
       </c>
       <c r="F298" t="n">
         <v>0.0</v>
@@ -11088,7 +11088,7 @@
         <v>0.0</v>
       </c>
       <c r="H298" t="n">
-        <v>1134.0</v>
+        <v>1131.0</v>
       </c>
       <c r="I298" t="n">
         <v>0.0</v>
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>1949.2</v>
+        <v>1863.8000000000002</v>
       </c>
       <c r="F300" t="n">
         <v>0.8</v>
@@ -11162,7 +11162,7 @@
         <v>134.4</v>
       </c>
       <c r="H300" t="n">
-        <v>1949.2</v>
+        <v>1863.8000000000002</v>
       </c>
       <c r="I300" t="n">
         <v>0.0</v>
@@ -11190,7 +11190,7 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>5255.8</v>
+        <v>1044.4</v>
       </c>
       <c r="F301" t="n">
         <v>2.4</v>
@@ -11199,10 +11199,10 @@
         <v>333.0</v>
       </c>
       <c r="H301" t="n">
-        <v>1134.1999999999998</v>
+        <v>1044.4</v>
       </c>
       <c r="I301" t="n">
-        <v>4121.6</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="302">
@@ -11227,7 +11227,7 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>606.0</v>
+        <v>491.4</v>
       </c>
       <c r="F302" t="n">
         <v>1.0</v>
@@ -11236,7 +11236,7 @@
         <v>136.8</v>
       </c>
       <c r="H302" t="n">
-        <v>606.0</v>
+        <v>491.4</v>
       </c>
       <c r="I302" t="n">
         <v>0.0</v>
@@ -11264,7 +11264,7 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>824.2</v>
+        <v>814.6</v>
       </c>
       <c r="F303" t="n">
         <v>0.2</v>
@@ -11273,7 +11273,7 @@
         <v>0.0</v>
       </c>
       <c r="H303" t="n">
-        <v>824.2</v>
+        <v>814.6</v>
       </c>
       <c r="I303" t="n">
         <v>0.0</v>
@@ -11412,7 +11412,7 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>5653.513</v>
+        <v>5652.98</v>
       </c>
       <c r="F307" t="n">
         <v>1.067</v>
@@ -11421,7 +11421,7 @@
         <v>0.0</v>
       </c>
       <c r="H307" t="n">
-        <v>5653.513</v>
+        <v>5652.98</v>
       </c>
       <c r="I307" t="n">
         <v>0.0</v>
@@ -11708,7 +11708,7 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>173.6</v>
+        <v>18.4</v>
       </c>
       <c r="F315" t="n">
         <v>14.200000000000001</v>
@@ -11717,7 +11717,7 @@
         <v>121.6</v>
       </c>
       <c r="H315" t="n">
-        <v>173.6</v>
+        <v>18.4</v>
       </c>
       <c r="I315" t="n">
         <v>0.0</v>
@@ -11745,7 +11745,7 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>5263.8</v>
+        <v>5134.200000000001</v>
       </c>
       <c r="F316" t="n">
         <v>0.0</v>
@@ -11754,7 +11754,7 @@
         <v>166.4</v>
       </c>
       <c r="H316" t="n">
-        <v>5263.8</v>
+        <v>5134.200000000001</v>
       </c>
       <c r="I316" t="n">
         <v>0.0</v>
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>2803.0249999999996</v>
+        <v>2797.692</v>
       </c>
       <c r="F320" t="n">
         <v>0.0</v>
@@ -11902,7 +11902,7 @@
         <v>0.0</v>
       </c>
       <c r="H320" t="n">
-        <v>2803.0249999999996</v>
+        <v>2797.692</v>
       </c>
       <c r="I320" t="n">
         <v>0.0</v>
@@ -11930,7 +11930,7 @@
         </is>
       </c>
       <c r="E321" t="n">
-        <v>12587.44</v>
+        <v>12547.168</v>
       </c>
       <c r="F321" t="n">
         <v>0.533</v>
@@ -11939,7 +11939,7 @@
         <v>0.0</v>
       </c>
       <c r="H321" t="n">
-        <v>12587.44</v>
+        <v>12547.168</v>
       </c>
       <c r="I321" t="n">
         <v>0.0</v>
@@ -12004,7 +12004,7 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>2759.0</v>
+        <v>1043.8</v>
       </c>
       <c r="F323" t="n">
         <v>0.6</v>
@@ -12013,10 +12013,10 @@
         <v>6.4</v>
       </c>
       <c r="H323" t="n">
-        <v>1325.3999999999999</v>
+        <v>1043.8</v>
       </c>
       <c r="I323" t="n">
-        <v>1433.6</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="324">
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>2959.6</v>
+        <v>2809.4</v>
       </c>
       <c r="F326" t="n">
         <v>1.4</v>
@@ -12124,7 +12124,7 @@
         <v>43.2</v>
       </c>
       <c r="H326" t="n">
-        <v>2959.6</v>
+        <v>2809.4</v>
       </c>
       <c r="I326" t="n">
         <v>0.0</v>
@@ -12337,7 +12337,7 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>152.8</v>
+        <v>145.60000000000002</v>
       </c>
       <c r="F332" t="n">
         <v>4.8</v>
@@ -12346,7 +12346,7 @@
         <v>0.0</v>
       </c>
       <c r="H332" t="n">
-        <v>152.8</v>
+        <v>145.60000000000002</v>
       </c>
       <c r="I332" t="n">
         <v>0.0</v>
@@ -12448,7 +12448,7 @@
         </is>
       </c>
       <c r="E335" t="n">
-        <v>2316.159</v>
+        <v>1688.7990000000002</v>
       </c>
       <c r="F335" t="n">
         <v>0.0</v>
@@ -12457,10 +12457,10 @@
         <v>77.75999999999999</v>
       </c>
       <c r="H335" t="n">
-        <v>1484.799</v>
+        <v>1610.0790000000002</v>
       </c>
       <c r="I335" t="n">
-        <v>831.36</v>
+        <v>78.72</v>
       </c>
     </row>
     <row r="336">
@@ -12485,7 +12485,7 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>4249.914000000001</v>
+        <v>4230.339</v>
       </c>
       <c r="F336" t="n">
         <v>0.0</v>
@@ -12494,7 +12494,7 @@
         <v>39.375</v>
       </c>
       <c r="H336" t="n">
-        <v>4249.914000000001</v>
+        <v>4230.339</v>
       </c>
       <c r="I336" t="n">
         <v>0.0</v>
@@ -12522,7 +12522,7 @@
         </is>
       </c>
       <c r="E337" t="n">
-        <v>3719.611</v>
+        <v>3629.931</v>
       </c>
       <c r="F337" t="n">
         <v>0.0</v>
@@ -12531,7 +12531,7 @@
         <v>88.245</v>
       </c>
       <c r="H337" t="n">
-        <v>3719.611</v>
+        <v>3629.931</v>
       </c>
       <c r="I337" t="n">
         <v>0.0</v>
@@ -12855,7 +12855,7 @@
         </is>
       </c>
       <c r="E346" t="n">
-        <v>48.7</v>
+        <v>102.7</v>
       </c>
       <c r="F346" t="n">
         <v>0.0</v>
@@ -12864,7 +12864,7 @@
         <v>564.0</v>
       </c>
       <c r="H346" t="n">
-        <v>48.7</v>
+        <v>102.7</v>
       </c>
       <c r="I346" t="n">
         <v>0.0</v>
@@ -12929,7 +12929,7 @@
         </is>
       </c>
       <c r="E348" t="n">
-        <v>943.0</v>
+        <v>935.8</v>
       </c>
       <c r="F348" t="n">
         <v>0.0</v>
@@ -12938,7 +12938,7 @@
         <v>3.0</v>
       </c>
       <c r="H348" t="n">
-        <v>943.0</v>
+        <v>935.8</v>
       </c>
       <c r="I348" t="n">
         <v>0.0</v>
@@ -12966,7 +12966,7 @@
         </is>
       </c>
       <c r="E349" t="n">
-        <v>371.4</v>
+        <v>369.6</v>
       </c>
       <c r="F349" t="n">
         <v>0.0</v>
@@ -12975,7 +12975,7 @@
         <v>0.1</v>
       </c>
       <c r="H349" t="n">
-        <v>371.4</v>
+        <v>369.6</v>
       </c>
       <c r="I349" t="n">
         <v>0.0</v>
@@ -13447,7 +13447,7 @@
         </is>
       </c>
       <c r="E362" t="n">
-        <v>500.062</v>
+        <v>488.061</v>
       </c>
       <c r="F362" t="n">
         <v>18.402</v>
@@ -13456,7 +13456,7 @@
         <v>0.0</v>
       </c>
       <c r="H362" t="n">
-        <v>500.062</v>
+        <v>488.061</v>
       </c>
       <c r="I362" t="n">
         <v>0.0</v>
@@ -13632,7 +13632,7 @@
         </is>
       </c>
       <c r="E367" t="n">
-        <v>3587.641</v>
+        <v>3584.975</v>
       </c>
       <c r="F367" t="n">
         <v>0.0</v>
@@ -13641,7 +13641,7 @@
         <v>3.0</v>
       </c>
       <c r="H367" t="n">
-        <v>3587.641</v>
+        <v>3584.975</v>
       </c>
       <c r="I367" t="n">
         <v>0.0</v>
@@ -13706,7 +13706,7 @@
         </is>
       </c>
       <c r="E369" t="n">
-        <v>493.73</v>
+        <v>491.06</v>
       </c>
       <c r="F369" t="n">
         <v>0.0</v>
@@ -13715,7 +13715,7 @@
         <v>296.682</v>
       </c>
       <c r="H369" t="n">
-        <v>493.73</v>
+        <v>491.06</v>
       </c>
       <c r="I369" t="n">
         <v>0.0</v>
@@ -14076,7 +14076,7 @@
         </is>
       </c>
       <c r="E379" t="n">
-        <v>9619.603</v>
+        <v>5284.481</v>
       </c>
       <c r="F379" t="n">
         <v>0.0</v>
@@ -14085,7 +14085,7 @@
         <v>0.0</v>
       </c>
       <c r="H379" t="n">
-        <v>9619.603</v>
+        <v>5284.481</v>
       </c>
       <c r="I379" t="n">
         <v>0.0</v>
@@ -14335,7 +14335,7 @@
         </is>
       </c>
       <c r="E386" t="n">
-        <v>821.2789999999999</v>
+        <v>821.0020000000001</v>
       </c>
       <c r="F386" t="n">
         <v>0.0</v>
@@ -14344,7 +14344,7 @@
         <v>30.12</v>
       </c>
       <c r="H386" t="n">
-        <v>821.2789999999999</v>
+        <v>821.0020000000001</v>
       </c>
       <c r="I386" t="n">
         <v>0.0</v>
@@ -14372,7 +14372,7 @@
         </is>
       </c>
       <c r="E387" t="n">
-        <v>0.222</v>
+        <v>35.557100000000005</v>
       </c>
       <c r="F387" t="n">
         <v>44.669</v>
@@ -14384,7 +14384,7 @@
         <v>0.222</v>
       </c>
       <c r="I387" t="n">
-        <v>0.0</v>
+        <v>35.335100000000004</v>
       </c>
     </row>
     <row r="388">
@@ -14409,7 +14409,7 @@
         </is>
       </c>
       <c r="E388" t="n">
-        <v>2459.666</v>
+        <v>2508.4025</v>
       </c>
       <c r="F388" t="n">
         <v>16.056</v>
@@ -14418,10 +14418,10 @@
         <v>976.9910000000001</v>
       </c>
       <c r="H388" t="n">
-        <v>2459.666</v>
+        <v>2471.567</v>
       </c>
       <c r="I388" t="n">
-        <v>0.0</v>
+        <v>36.8355</v>
       </c>
     </row>
     <row r="389">
@@ -14446,7 +14446,7 @@
         </is>
       </c>
       <c r="E389" t="n">
-        <v>1233.866</v>
+        <v>1189.066</v>
       </c>
       <c r="F389" t="n">
         <v>36.0</v>
@@ -14455,7 +14455,7 @@
         <v>30.4</v>
       </c>
       <c r="H389" t="n">
-        <v>1233.866</v>
+        <v>1189.066</v>
       </c>
       <c r="I389" t="n">
         <v>0.0</v>
@@ -14594,7 +14594,7 @@
         </is>
       </c>
       <c r="E393" t="n">
-        <v>57.0</v>
+        <v>55.0</v>
       </c>
       <c r="F393" t="n">
         <v>0.0</v>
@@ -14603,7 +14603,7 @@
         <v>0.0</v>
       </c>
       <c r="H393" t="n">
-        <v>57.0</v>
+        <v>55.0</v>
       </c>
       <c r="I393" t="n">
         <v>0.0</v>
@@ -15112,7 +15112,7 @@
         </is>
       </c>
       <c r="E407" t="n">
-        <v>44.622</v>
+        <v>44.4</v>
       </c>
       <c r="F407" t="n">
         <v>0.0</v>
@@ -15121,7 +15121,7 @@
         <v>0.0</v>
       </c>
       <c r="H407" t="n">
-        <v>44.622</v>
+        <v>44.4</v>
       </c>
       <c r="I407" t="n">
         <v>0.0</v>
@@ -15260,7 +15260,7 @@
         </is>
       </c>
       <c r="E411" t="n">
-        <v>3330.5989999999997</v>
+        <v>3314.049</v>
       </c>
       <c r="F411" t="n">
         <v>0.2</v>
@@ -15269,7 +15269,7 @@
         <v>74.39999999999999</v>
       </c>
       <c r="H411" t="n">
-        <v>3330.5989999999997</v>
+        <v>3314.049</v>
       </c>
       <c r="I411" t="n">
         <v>0.0</v>
@@ -15297,7 +15297,7 @@
         </is>
       </c>
       <c r="E412" t="n">
-        <v>987.0500000000001</v>
+        <v>963.5500000000001</v>
       </c>
       <c r="F412" t="n">
         <v>0.0</v>
@@ -15306,7 +15306,7 @@
         <v>180.10000000000002</v>
       </c>
       <c r="H412" t="n">
-        <v>987.0500000000001</v>
+        <v>963.5500000000001</v>
       </c>
       <c r="I412" t="n">
         <v>0.0</v>
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="E413" t="n">
-        <v>1274.551</v>
+        <v>1255.2</v>
       </c>
       <c r="F413" t="n">
         <v>0.15</v>
@@ -15343,7 +15343,7 @@
         <v>101.1</v>
       </c>
       <c r="H413" t="n">
-        <v>1274.551</v>
+        <v>1255.2</v>
       </c>
       <c r="I413" t="n">
         <v>0.0</v>
@@ -15371,7 +15371,7 @@
         </is>
       </c>
       <c r="E414" t="n">
-        <v>1872.8999999999999</v>
+        <v>1863.1499999999999</v>
       </c>
       <c r="F414" t="n">
         <v>0.0</v>
@@ -15380,7 +15380,7 @@
         <v>163.5</v>
       </c>
       <c r="H414" t="n">
-        <v>1872.8999999999999</v>
+        <v>1863.1499999999999</v>
       </c>
       <c r="I414" t="n">
         <v>0.0</v>
@@ -15408,7 +15408,7 @@
         </is>
       </c>
       <c r="E415" t="n">
-        <v>1381.45</v>
+        <v>1396.75</v>
       </c>
       <c r="F415" t="n">
         <v>0.15</v>
@@ -15417,7 +15417,7 @@
         <v>31.2</v>
       </c>
       <c r="H415" t="n">
-        <v>1381.45</v>
+        <v>1396.75</v>
       </c>
       <c r="I415" t="n">
         <v>0.0</v>
@@ -15445,7 +15445,7 @@
         </is>
       </c>
       <c r="E416" t="n">
-        <v>1868.45</v>
+        <v>1951.25</v>
       </c>
       <c r="F416" t="n">
         <v>0.1</v>
@@ -15454,7 +15454,7 @@
         <v>0.0</v>
       </c>
       <c r="H416" t="n">
-        <v>1868.45</v>
+        <v>1951.25</v>
       </c>
       <c r="I416" t="n">
         <v>0.0</v>
@@ -15482,7 +15482,7 @@
         </is>
       </c>
       <c r="E417" t="n">
-        <v>4855.1</v>
+        <v>3635.6</v>
       </c>
       <c r="F417" t="n">
         <v>0.0</v>
@@ -15491,10 +15491,10 @@
         <v>0.0</v>
       </c>
       <c r="H417" t="n">
-        <v>3548.3</v>
+        <v>3635.6</v>
       </c>
       <c r="I417" t="n">
-        <v>1306.8</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="418">
@@ -15704,7 +15704,7 @@
         </is>
       </c>
       <c r="E423" t="n">
-        <v>700.0</v>
+        <v>580.0</v>
       </c>
       <c r="F423" t="n">
         <v>0.0</v>
@@ -15713,7 +15713,7 @@
         <v>0.0</v>
       </c>
       <c r="H423" t="n">
-        <v>700.0</v>
+        <v>580.0</v>
       </c>
       <c r="I423" t="n">
         <v>0.0</v>
@@ -15778,7 +15778,7 @@
         </is>
       </c>
       <c r="E425" t="n">
-        <v>374.9</v>
+        <v>373.1</v>
       </c>
       <c r="F425" t="n">
         <v>0.0</v>
@@ -15787,7 +15787,7 @@
         <v>0.0</v>
       </c>
       <c r="H425" t="n">
-        <v>374.9</v>
+        <v>373.1</v>
       </c>
       <c r="I425" t="n">
         <v>0.0</v>
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="E436" t="n">
-        <v>1257.6354000000001</v>
+        <v>1269.9584</v>
       </c>
       <c r="F436" t="n">
         <v>61.196</v>
@@ -16194,7 +16194,7 @@
         <v>4.107</v>
       </c>
       <c r="H436" t="n">
-        <v>411.51099999999997</v>
+        <v>423.834</v>
       </c>
       <c r="I436" t="n">
         <v>846.1244</v>
@@ -16222,7 +16222,7 @@
         </is>
       </c>
       <c r="E437" t="n">
-        <v>3167.5759999999996</v>
+        <v>2879.966</v>
       </c>
       <c r="F437" t="n">
         <v>191.516</v>
@@ -16231,7 +16231,7 @@
         <v>2.054</v>
       </c>
       <c r="H437" t="n">
-        <v>3167.5759999999996</v>
+        <v>2879.966</v>
       </c>
       <c r="I437" t="n">
         <v>0.0</v>
@@ -16296,7 +16296,7 @@
         </is>
       </c>
       <c r="E439" t="n">
-        <v>1559.357</v>
+        <v>1517.6000000000001</v>
       </c>
       <c r="F439" t="n">
         <v>0.0</v>
@@ -16305,7 +16305,7 @@
         <v>2.054</v>
       </c>
       <c r="H439" t="n">
-        <v>1559.357</v>
+        <v>1517.6000000000001</v>
       </c>
       <c r="I439" t="n">
         <v>0.0</v>
@@ -16333,7 +16333,7 @@
         </is>
       </c>
       <c r="E440" t="n">
-        <v>1101.5259999999998</v>
+        <v>211.899</v>
       </c>
       <c r="F440" t="n">
         <v>0.0</v>
@@ -16342,10 +16342,10 @@
         <v>395.806</v>
       </c>
       <c r="H440" t="n">
-        <v>266.977</v>
+        <v>211.899</v>
       </c>
       <c r="I440" t="n">
-        <v>834.549</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="441">
@@ -16370,7 +16370,7 @@
         </is>
       </c>
       <c r="E441" t="n">
-        <v>6455.4015</v>
+        <v>4231.938999999999</v>
       </c>
       <c r="F441" t="n">
         <v>444.002</v>
@@ -16379,10 +16379,10 @@
         <v>2.043</v>
       </c>
       <c r="H441" t="n">
-        <v>4293.781</v>
+        <v>4231.938999999999</v>
       </c>
       <c r="I441" t="n">
-        <v>2161.6205</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="442">
@@ -16444,7 +16444,7 @@
         </is>
       </c>
       <c r="E443" t="n">
-        <v>2752.418</v>
+        <v>2722.08</v>
       </c>
       <c r="F443" t="n">
         <v>0.0</v>
@@ -16453,7 +16453,7 @@
         <v>191.83700000000002</v>
       </c>
       <c r="H443" t="n">
-        <v>2752.418</v>
+        <v>2722.08</v>
       </c>
       <c r="I443" t="n">
         <v>0.0</v>
@@ -16481,7 +16481,7 @@
         </is>
       </c>
       <c r="E444" t="n">
-        <v>6171.8369999999995</v>
+        <v>6136.36</v>
       </c>
       <c r="F444" t="n">
         <v>6.069</v>
@@ -16490,7 +16490,7 @@
         <v>146.094</v>
       </c>
       <c r="H444" t="n">
-        <v>6171.8369999999995</v>
+        <v>6136.36</v>
       </c>
       <c r="I444" t="n">
         <v>0.0</v>
@@ -16518,7 +16518,7 @@
         </is>
       </c>
       <c r="E445" t="n">
-        <v>16164.949499999999</v>
+        <v>10507.940999999999</v>
       </c>
       <c r="F445" t="n">
         <v>3.733</v>
@@ -16527,10 +16527,10 @@
         <v>50.879</v>
       </c>
       <c r="H445" t="n">
-        <v>9681.792</v>
+        <v>10507.940999999999</v>
       </c>
       <c r="I445" t="n">
-        <v>6483.157499999999</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="446">
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="E446" t="n">
-        <v>979.586</v>
+        <v>932.036</v>
       </c>
       <c r="F446" t="n">
         <v>211.49599999999998</v>
@@ -16564,7 +16564,7 @@
         <v>71.762</v>
       </c>
       <c r="H446" t="n">
-        <v>979.586</v>
+        <v>932.036</v>
       </c>
       <c r="I446" t="n">
         <v>0.0</v>
@@ -16592,7 +16592,7 @@
         </is>
       </c>
       <c r="E447" t="n">
-        <v>1623.4029999999998</v>
+        <v>1579.644</v>
       </c>
       <c r="F447" t="n">
         <v>294.63</v>
@@ -16601,7 +16601,7 @@
         <v>79.056</v>
       </c>
       <c r="H447" t="n">
-        <v>1623.4029999999998</v>
+        <v>1579.644</v>
       </c>
       <c r="I447" t="n">
         <v>0.0</v>
@@ -16703,7 +16703,7 @@
         </is>
       </c>
       <c r="E450" t="n">
-        <v>1060.972</v>
+        <v>1043.469</v>
       </c>
       <c r="F450" t="n">
         <v>0.0</v>
@@ -16712,7 +16712,7 @@
         <v>73.80499999999999</v>
       </c>
       <c r="H450" t="n">
-        <v>1060.972</v>
+        <v>1043.469</v>
       </c>
       <c r="I450" t="n">
         <v>0.0</v>
@@ -16740,7 +16740,7 @@
         </is>
       </c>
       <c r="E451" t="n">
-        <v>5559.5341</v>
+        <v>2872.823</v>
       </c>
       <c r="F451" t="n">
         <v>380.69399999999996</v>
@@ -16749,10 +16749,10 @@
         <v>0.292</v>
       </c>
       <c r="H451" t="n">
-        <v>2834.317</v>
+        <v>2872.823</v>
       </c>
       <c r="I451" t="n">
-        <v>2725.2171</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="452">
@@ -16777,7 +16777,7 @@
         </is>
       </c>
       <c r="E452" t="n">
-        <v>1926.1879999999999</v>
+        <v>1887.388</v>
       </c>
       <c r="F452" t="n">
         <v>0.0</v>
@@ -16786,7 +16786,7 @@
         <v>19.253</v>
       </c>
       <c r="H452" t="n">
-        <v>1926.1879999999999</v>
+        <v>1887.388</v>
       </c>
       <c r="I452" t="n">
         <v>0.0</v>
@@ -17110,7 +17110,7 @@
         </is>
       </c>
       <c r="E461" t="n">
-        <v>704.488</v>
+        <v>630.891</v>
       </c>
       <c r="F461" t="n">
         <v>0.0</v>
@@ -17119,7 +17119,7 @@
         <v>3.2</v>
       </c>
       <c r="H461" t="n">
-        <v>704.488</v>
+        <v>630.891</v>
       </c>
       <c r="I461" t="n">
         <v>0.0</v>
@@ -17258,7 +17258,7 @@
         </is>
       </c>
       <c r="E465" t="n">
-        <v>221.894</v>
+        <v>221.36100000000002</v>
       </c>
       <c r="F465" t="n">
         <v>0.0</v>
@@ -17267,7 +17267,7 @@
         <v>0.0</v>
       </c>
       <c r="H465" t="n">
-        <v>221.894</v>
+        <v>221.36100000000002</v>
       </c>
       <c r="I465" t="n">
         <v>0.0</v>
@@ -17295,7 +17295,7 @@
         </is>
       </c>
       <c r="E466" t="n">
-        <v>734.743</v>
+        <v>733.476</v>
       </c>
       <c r="F466" t="n">
         <v>1.267</v>
@@ -17304,7 +17304,7 @@
         <v>0.0</v>
       </c>
       <c r="H466" t="n">
-        <v>734.743</v>
+        <v>733.476</v>
       </c>
       <c r="I466" t="n">
         <v>0.0</v>
@@ -17517,7 +17517,7 @@
         </is>
       </c>
       <c r="E472" t="n">
-        <v>2074.64</v>
+        <v>2022.644</v>
       </c>
       <c r="F472" t="n">
         <v>135.19</v>
@@ -17526,7 +17526,7 @@
         <v>561.557</v>
       </c>
       <c r="H472" t="n">
-        <v>2074.64</v>
+        <v>2022.644</v>
       </c>
       <c r="I472" t="n">
         <v>0.0</v>
@@ -17702,7 +17702,7 @@
         </is>
       </c>
       <c r="E477" t="n">
-        <v>86.74</v>
+        <v>70.089</v>
       </c>
       <c r="F477" t="n">
         <v>0.562</v>
@@ -17711,7 +17711,7 @@
         <v>85.725</v>
       </c>
       <c r="H477" t="n">
-        <v>86.74</v>
+        <v>70.089</v>
       </c>
       <c r="I477" t="n">
         <v>0.0</v>
@@ -17739,7 +17739,7 @@
         </is>
       </c>
       <c r="E478" t="n">
-        <v>2076.525</v>
+        <v>2058.975</v>
       </c>
       <c r="F478" t="n">
         <v>0.0</v>
@@ -17748,7 +17748,7 @@
         <v>105.30000000000001</v>
       </c>
       <c r="H478" t="n">
-        <v>2076.525</v>
+        <v>2058.975</v>
       </c>
       <c r="I478" t="n">
         <v>0.0</v>
@@ -17850,7 +17850,7 @@
         </is>
       </c>
       <c r="E481" t="n">
-        <v>14.708</v>
+        <v>13.181</v>
       </c>
       <c r="F481" t="n">
         <v>0.13899999999999998</v>
@@ -17859,7 +17859,7 @@
         <v>762.5699999999999</v>
       </c>
       <c r="H481" t="n">
-        <v>14.708</v>
+        <v>13.181</v>
       </c>
       <c r="I481" t="n">
         <v>0.0</v>
@@ -17887,7 +17887,7 @@
         </is>
       </c>
       <c r="E482" t="n">
-        <v>1180.24</v>
+        <v>1236.88</v>
       </c>
       <c r="F482" t="n">
         <v>0.12000000000000001</v>
@@ -17896,7 +17896,7 @@
         <v>178.56</v>
       </c>
       <c r="H482" t="n">
-        <v>1180.24</v>
+        <v>1236.88</v>
       </c>
       <c r="I482" t="n">
         <v>0.0</v>
@@ -17924,7 +17924,7 @@
         </is>
       </c>
       <c r="E483" t="n">
-        <v>167.96099999999998</v>
+        <v>167.0</v>
       </c>
       <c r="F483" t="n">
         <v>0.0</v>
@@ -17933,7 +17933,7 @@
         <v>708.0</v>
       </c>
       <c r="H483" t="n">
-        <v>167.96099999999998</v>
+        <v>167.0</v>
       </c>
       <c r="I483" t="n">
         <v>0.0</v>
@@ -17961,7 +17961,7 @@
         </is>
       </c>
       <c r="E484" t="n">
-        <v>2282.808</v>
+        <v>2260.885</v>
       </c>
       <c r="F484" t="n">
         <v>0.13899999999999998</v>
@@ -17970,7 +17970,7 @@
         <v>5.55</v>
       </c>
       <c r="H484" t="n">
-        <v>2282.808</v>
+        <v>2260.885</v>
       </c>
       <c r="I484" t="n">
         <v>0.0</v>
@@ -17998,7 +17998,7 @@
         </is>
       </c>
       <c r="E485" t="n">
-        <v>4.88</v>
+        <v>293.23999999999995</v>
       </c>
       <c r="F485" t="n">
         <v>0.0</v>
@@ -18007,10 +18007,10 @@
         <v>62.4</v>
       </c>
       <c r="H485" t="n">
-        <v>4.88</v>
+        <v>2.84</v>
       </c>
       <c r="I485" t="n">
-        <v>0.0</v>
+        <v>290.4</v>
       </c>
     </row>
     <row r="486">
@@ -18035,7 +18035,7 @@
         </is>
       </c>
       <c r="E486" t="n">
-        <v>3483.227</v>
+        <v>3466.761</v>
       </c>
       <c r="F486" t="n">
         <v>0.13899999999999998</v>
@@ -18044,7 +18044,7 @@
         <v>155.955</v>
       </c>
       <c r="H486" t="n">
-        <v>3483.227</v>
+        <v>3466.761</v>
       </c>
       <c r="I486" t="n">
         <v>0.0</v>
@@ -18072,7 +18072,7 @@
         </is>
       </c>
       <c r="E487" t="n">
-        <v>243.76000000000002</v>
+        <v>214.0</v>
       </c>
       <c r="F487" t="n">
         <v>0.0</v>
@@ -18081,7 +18081,7 @@
         <v>110.88000000000001</v>
       </c>
       <c r="H487" t="n">
-        <v>243.76000000000002</v>
+        <v>214.0</v>
       </c>
       <c r="I487" t="n">
         <v>0.0</v>
@@ -18109,7 +18109,7 @@
         </is>
       </c>
       <c r="E488" t="n">
-        <v>1602.933</v>
+        <v>1475.0049999999999</v>
       </c>
       <c r="F488" t="n">
         <v>0.185</v>
@@ -18118,7 +18118,7 @@
         <v>24.42</v>
       </c>
       <c r="H488" t="n">
-        <v>1602.933</v>
+        <v>1475.0049999999999</v>
       </c>
       <c r="I488" t="n">
         <v>0.0</v>
@@ -18220,7 +18220,7 @@
         </is>
       </c>
       <c r="E491" t="n">
-        <v>380.17299999999994</v>
+        <v>375.455</v>
       </c>
       <c r="F491" t="n">
         <v>0.13899999999999998</v>
@@ -18229,7 +18229,7 @@
         <v>533.27</v>
       </c>
       <c r="H491" t="n">
-        <v>380.17299999999994</v>
+        <v>375.455</v>
       </c>
       <c r="I491" t="n">
         <v>0.0</v>
@@ -18294,7 +18294,7 @@
         </is>
       </c>
       <c r="E493" t="n">
-        <v>5876.128</v>
+        <v>8799.6084</v>
       </c>
       <c r="F493" t="n">
         <v>50.336</v>
@@ -18303,10 +18303,10 @@
         <v>2431.122</v>
       </c>
       <c r="H493" t="n">
-        <v>5876.128</v>
+        <v>5838.1269999999995</v>
       </c>
       <c r="I493" t="n">
-        <v>0.0</v>
+        <v>2961.4813999999997</v>
       </c>
     </row>
     <row r="494">
@@ -18331,7 +18331,7 @@
         </is>
       </c>
       <c r="E494" t="n">
-        <v>3239.952</v>
+        <v>2901.63</v>
       </c>
       <c r="F494" t="n">
         <v>19.598999999999997</v>
@@ -18340,7 +18340,7 @@
         <v>3842.3959999999997</v>
       </c>
       <c r="H494" t="n">
-        <v>3239.952</v>
+        <v>2901.63</v>
       </c>
       <c r="I494" t="n">
         <v>0.0</v>
@@ -18368,7 +18368,7 @@
         </is>
       </c>
       <c r="E495" t="n">
-        <v>5717.167</v>
+        <v>5711.034000000001</v>
       </c>
       <c r="F495" t="n">
         <v>24.532999999999998</v>
@@ -18377,7 +18377,7 @@
         <v>49.065999999999995</v>
       </c>
       <c r="H495" t="n">
-        <v>5717.167</v>
+        <v>5711.034000000001</v>
       </c>
       <c r="I495" t="n">
         <v>0.0</v>
@@ -18405,7 +18405,7 @@
         </is>
       </c>
       <c r="E496" t="n">
-        <v>2445.4</v>
+        <v>6653.0</v>
       </c>
       <c r="F496" t="n">
         <v>24.8</v>
@@ -18414,10 +18414,10 @@
         <v>192.8</v>
       </c>
       <c r="H496" t="n">
-        <v>2445.4</v>
+        <v>2355.4</v>
       </c>
       <c r="I496" t="n">
-        <v>0.0</v>
+        <v>4297.6</v>
       </c>
     </row>
     <row r="497">
@@ -19034,7 +19034,7 @@
         </is>
       </c>
       <c r="E513" t="n">
-        <v>1174.836</v>
+        <v>1143.48</v>
       </c>
       <c r="F513" t="n">
         <v>0.0</v>
@@ -19043,7 +19043,7 @@
         <v>1257.789</v>
       </c>
       <c r="H513" t="n">
-        <v>1174.836</v>
+        <v>1143.48</v>
       </c>
       <c r="I513" t="n">
         <v>0.0</v>
@@ -19071,7 +19071,7 @@
         </is>
       </c>
       <c r="E514" t="n">
-        <v>3518.788</v>
+        <v>3518.521</v>
       </c>
       <c r="F514" t="n">
         <v>0.0</v>
@@ -19080,7 +19080,7 @@
         <v>6.793</v>
       </c>
       <c r="H514" t="n">
-        <v>3518.788</v>
+        <v>3518.521</v>
       </c>
       <c r="I514" t="n">
         <v>0.0</v>
@@ -19108,7 +19108,7 @@
         </is>
       </c>
       <c r="E515" t="n">
-        <v>939.374</v>
+        <v>937.772</v>
       </c>
       <c r="F515" t="n">
         <v>0.0</v>
@@ -19117,7 +19117,7 @@
         <v>19.84</v>
       </c>
       <c r="H515" t="n">
-        <v>939.374</v>
+        <v>937.772</v>
       </c>
       <c r="I515" t="n">
         <v>0.0</v>
@@ -19663,7 +19663,7 @@
         </is>
       </c>
       <c r="E530" t="n">
-        <v>1960.32</v>
+        <v>653.44</v>
       </c>
       <c r="F530" t="n">
         <v>104.55</v>
@@ -19672,7 +19672,7 @@
         <v>0.0</v>
       </c>
       <c r="H530" t="n">
-        <v>1960.32</v>
+        <v>653.44</v>
       </c>
       <c r="I530" t="n">
         <v>0.0</v>
@@ -19996,7 +19996,7 @@
         </is>
       </c>
       <c r="E539" t="n">
-        <v>1328.192</v>
+        <v>1314.015</v>
       </c>
       <c r="F539" t="n">
         <v>43.153</v>
@@ -20005,7 +20005,7 @@
         <v>0.313</v>
       </c>
       <c r="H539" t="n">
-        <v>1328.192</v>
+        <v>1314.015</v>
       </c>
       <c r="I539" t="n">
         <v>0.0</v>
@@ -20070,7 +20070,7 @@
         </is>
       </c>
       <c r="E541" t="n">
-        <v>2287.159</v>
+        <v>2207.832</v>
       </c>
       <c r="F541" t="n">
         <v>2663.3019999999997</v>
@@ -20079,7 +20079,7 @@
         <v>2223.507</v>
       </c>
       <c r="H541" t="n">
-        <v>2287.159</v>
+        <v>2207.832</v>
       </c>
       <c r="I541" t="n">
         <v>0.0</v>
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="E551" t="n">
-        <v>5839.4580000000005</v>
+        <v>5619.7791</v>
       </c>
       <c r="F551" t="n">
         <v>22.001</v>
@@ -20449,10 +20449,10 @@
         <v>51.669</v>
       </c>
       <c r="H551" t="n">
-        <v>5839.4580000000005</v>
+        <v>5311.097</v>
       </c>
       <c r="I551" t="n">
-        <v>0.0</v>
+        <v>308.6821</v>
       </c>
     </row>
     <row r="552">
@@ -20477,7 +20477,7 @@
         </is>
       </c>
       <c r="E552" t="n">
-        <v>11507.175</v>
+        <v>10758.058</v>
       </c>
       <c r="F552" t="n">
         <v>24.701</v>
@@ -20486,7 +20486,7 @@
         <v>86.81400000000001</v>
       </c>
       <c r="H552" t="n">
-        <v>11507.175</v>
+        <v>10758.058</v>
       </c>
       <c r="I552" t="n">
         <v>0.0</v>
@@ -20514,7 +20514,7 @@
         </is>
       </c>
       <c r="E553" t="n">
-        <v>1198.905</v>
+        <v>4159.557000000001</v>
       </c>
       <c r="F553" t="n">
         <v>11.613999999999999</v>
@@ -20523,10 +20523,10 @@
         <v>152.568</v>
       </c>
       <c r="H553" t="n">
-        <v>1198.905</v>
+        <v>733.623</v>
       </c>
       <c r="I553" t="n">
-        <v>0.0</v>
+        <v>3425.934</v>
       </c>
     </row>
     <row r="554">
@@ -21328,7 +21328,7 @@
         </is>
       </c>
       <c r="E575" t="n">
-        <v>270.572</v>
+        <v>265.439</v>
       </c>
       <c r="F575" t="n">
         <v>0.0</v>
@@ -21337,7 +21337,7 @@
         <v>0.0</v>
       </c>
       <c r="H575" t="n">
-        <v>270.572</v>
+        <v>265.439</v>
       </c>
       <c r="I575" t="n">
         <v>0.0</v>
@@ -21550,7 +21550,7 @@
         </is>
       </c>
       <c r="E581" t="n">
-        <v>6261.849</v>
+        <v>6257.696</v>
       </c>
       <c r="F581" t="n">
         <v>0.0</v>
@@ -21559,7 +21559,7 @@
         <v>5.539</v>
       </c>
       <c r="H581" t="n">
-        <v>6261.849</v>
+        <v>6257.696</v>
       </c>
       <c r="I581" t="n">
         <v>0.0</v>
@@ -21698,7 +21698,7 @@
         </is>
       </c>
       <c r="E585" t="n">
-        <v>1755.79</v>
+        <v>1751.636</v>
       </c>
       <c r="F585" t="n">
         <v>0.0</v>
@@ -21707,7 +21707,7 @@
         <v>0.0</v>
       </c>
       <c r="H585" t="n">
-        <v>1755.79</v>
+        <v>1751.636</v>
       </c>
       <c r="I585" t="n">
         <v>0.0</v>
@@ -21735,7 +21735,7 @@
         </is>
       </c>
       <c r="E586" t="n">
-        <v>2603.142</v>
+        <v>2171.594</v>
       </c>
       <c r="F586" t="n">
         <v>0.0</v>
@@ -21744,7 +21744,7 @@
         <v>9.231</v>
       </c>
       <c r="H586" t="n">
-        <v>2603.142</v>
+        <v>2171.594</v>
       </c>
       <c r="I586" t="n">
         <v>0.0</v>
@@ -22105,7 +22105,7 @@
         </is>
       </c>
       <c r="E596" t="n">
-        <v>1606.0220000000002</v>
+        <v>3693.5386</v>
       </c>
       <c r="F596" t="n">
         <v>0.0</v>
@@ -22114,10 +22114,10 @@
         <v>1221.269</v>
       </c>
       <c r="H596" t="n">
-        <v>1606.0220000000002</v>
+        <v>2209.555</v>
       </c>
       <c r="I596" t="n">
-        <v>0.0</v>
+        <v>1483.9836</v>
       </c>
     </row>
     <row r="597">
@@ -22142,7 +22142,7 @@
         </is>
       </c>
       <c r="E597" t="n">
-        <v>277.2142</v>
+        <v>3476.0897</v>
       </c>
       <c r="F597" t="n">
         <v>0.0</v>
@@ -22151,10 +22151,10 @@
         <v>386.37899999999996</v>
       </c>
       <c r="H597" t="n">
-        <v>273.664</v>
+        <v>197.48000000000002</v>
       </c>
       <c r="I597" t="n">
-        <v>3.5502</v>
+        <v>3278.6097</v>
       </c>
     </row>
     <row r="598">
@@ -22216,7 +22216,7 @@
         </is>
       </c>
       <c r="E599" t="n">
-        <v>5621.522</v>
+        <v>2862.9500000000003</v>
       </c>
       <c r="F599" t="n">
         <v>0.0</v>
@@ -22225,10 +22225,10 @@
         <v>3.7279999999999998</v>
       </c>
       <c r="H599" t="n">
-        <v>2862.95</v>
+        <v>2862.9500000000003</v>
       </c>
       <c r="I599" t="n">
-        <v>2758.572</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="600">
@@ -22253,7 +22253,7 @@
         </is>
       </c>
       <c r="E600" t="n">
-        <v>6748.781</v>
+        <v>6708.25</v>
       </c>
       <c r="F600" t="n">
         <v>1.7750000000000001</v>
@@ -22262,7 +22262,7 @@
         <v>468.626</v>
       </c>
       <c r="H600" t="n">
-        <v>6748.781</v>
+        <v>6708.25</v>
       </c>
       <c r="I600" t="n">
         <v>0.0</v>
@@ -22327,7 +22327,7 @@
         </is>
       </c>
       <c r="E602" t="n">
-        <v>367.44599999999997</v>
+        <v>364.783</v>
       </c>
       <c r="F602" t="n">
         <v>0.0</v>
@@ -22336,7 +22336,7 @@
         <v>0.888</v>
       </c>
       <c r="H602" t="n">
-        <v>367.44599999999997</v>
+        <v>364.783</v>
       </c>
       <c r="I602" t="n">
         <v>0.0</v>
@@ -22401,7 +22401,7 @@
         </is>
       </c>
       <c r="E604" t="n">
-        <v>6014.2919999999995</v>
+        <v>5983.360000000001</v>
       </c>
       <c r="F604" t="n">
         <v>0.533</v>
@@ -22410,7 +22410,7 @@
         <v>886.345</v>
       </c>
       <c r="H604" t="n">
-        <v>6014.2919999999995</v>
+        <v>5983.360000000001</v>
       </c>
       <c r="I604" t="n">
         <v>0.0</v>
@@ -23363,7 +23363,7 @@
         </is>
       </c>
       <c r="E630" t="n">
-        <v>1276.891</v>
+        <v>1265.69</v>
       </c>
       <c r="F630" t="n">
         <v>0.933</v>
@@ -23372,7 +23372,7 @@
         <v>0.0</v>
       </c>
       <c r="H630" t="n">
-        <v>1276.891</v>
+        <v>1265.69</v>
       </c>
       <c r="I630" t="n">
         <v>0.0</v>
@@ -23437,7 +23437,7 @@
         </is>
       </c>
       <c r="E632" t="n">
-        <v>448.023</v>
+        <v>448.022</v>
       </c>
       <c r="F632" t="n">
         <v>0.0</v>
@@ -23446,7 +23446,7 @@
         <v>0.0</v>
       </c>
       <c r="H632" t="n">
-        <v>448.023</v>
+        <v>448.022</v>
       </c>
       <c r="I632" t="n">
         <v>0.0</v>
@@ -23881,7 +23881,7 @@
         </is>
       </c>
       <c r="E644" t="n">
-        <v>227.101</v>
+        <v>277.694</v>
       </c>
       <c r="F644" t="n">
         <v>0.0</v>
@@ -23890,7 +23890,7 @@
         <v>1.686</v>
       </c>
       <c r="H644" t="n">
-        <v>227.101</v>
+        <v>277.694</v>
       </c>
       <c r="I644" t="n">
         <v>0.0</v>
@@ -23955,7 +23955,7 @@
         </is>
       </c>
       <c r="E646" t="n">
-        <v>1225.578</v>
+        <v>1100.221</v>
       </c>
       <c r="F646" t="n">
         <v>0.0</v>
@@ -23964,7 +23964,7 @@
         <v>0.16699999999999998</v>
       </c>
       <c r="H646" t="n">
-        <v>1225.578</v>
+        <v>1100.221</v>
       </c>
       <c r="I646" t="n">
         <v>0.0</v>
@@ -23992,7 +23992,7 @@
         </is>
       </c>
       <c r="E647" t="n">
-        <v>5527.751</v>
+        <v>5527.752</v>
       </c>
       <c r="F647" t="n">
         <v>0.0</v>
@@ -24001,7 +24001,7 @@
         <v>4099.277</v>
       </c>
       <c r="H647" t="n">
-        <v>5527.751</v>
+        <v>5527.752</v>
       </c>
       <c r="I647" t="n">
         <v>0.0</v>
@@ -24029,7 +24029,7 @@
         </is>
       </c>
       <c r="E648" t="n">
-        <v>1628.165</v>
+        <v>1625.232</v>
       </c>
       <c r="F648" t="n">
         <v>0.6669999999999999</v>
@@ -24038,7 +24038,7 @@
         <v>0.0</v>
       </c>
       <c r="H648" t="n">
-        <v>1628.165</v>
+        <v>1625.232</v>
       </c>
       <c r="I648" t="n">
         <v>0.0</v>
@@ -24177,7 +24177,7 @@
         </is>
       </c>
       <c r="E652" t="n">
-        <v>2985.5</v>
+        <v>2853.5</v>
       </c>
       <c r="F652" t="n">
         <v>0.0</v>
@@ -24186,7 +24186,7 @@
         <v>16.0</v>
       </c>
       <c r="H652" t="n">
-        <v>2985.5</v>
+        <v>2853.5</v>
       </c>
       <c r="I652" t="n">
         <v>0.0</v>
@@ -24214,7 +24214,7 @@
         </is>
       </c>
       <c r="E653" t="n">
-        <v>6394.612</v>
+        <v>6389.608</v>
       </c>
       <c r="F653" t="n">
         <v>0.0</v>
@@ -24223,7 +24223,7 @@
         <v>65.05199999999999</v>
       </c>
       <c r="H653" t="n">
-        <v>6394.612</v>
+        <v>6389.608</v>
       </c>
       <c r="I653" t="n">
         <v>0.0</v>
@@ -24251,7 +24251,7 @@
         </is>
       </c>
       <c r="E654" t="n">
-        <v>1498.42</v>
+        <v>1478.96</v>
       </c>
       <c r="F654" t="n">
         <v>0.0</v>
@@ -24260,7 +24260,7 @@
         <v>0.0</v>
       </c>
       <c r="H654" t="n">
-        <v>1498.42</v>
+        <v>1478.96</v>
       </c>
       <c r="I654" t="n">
         <v>0.0</v>
@@ -24362,7 +24362,7 @@
         </is>
       </c>
       <c r="E657" t="n">
-        <v>1569.27</v>
+        <v>1568.347</v>
       </c>
       <c r="F657" t="n">
         <v>0.462</v>
@@ -24371,7 +24371,7 @@
         <v>11.077</v>
       </c>
       <c r="H657" t="n">
-        <v>1569.27</v>
+        <v>1568.347</v>
       </c>
       <c r="I657" t="n">
         <v>0.0</v>
@@ -24547,7 +24547,7 @@
         </is>
       </c>
       <c r="E662" t="n">
-        <v>1793.442</v>
+        <v>1785.898</v>
       </c>
       <c r="F662" t="n">
         <v>0.7380000000000001</v>
@@ -24556,7 +24556,7 @@
         <v>179.285</v>
       </c>
       <c r="H662" t="n">
-        <v>1793.442</v>
+        <v>1785.898</v>
       </c>
       <c r="I662" t="n">
         <v>0.0</v>
@@ -24584,7 +24584,7 @@
         </is>
       </c>
       <c r="E663" t="n">
-        <v>2319.464</v>
+        <v>2301.713</v>
       </c>
       <c r="F663" t="n">
         <v>0.0</v>
@@ -24593,7 +24593,7 @@
         <v>54.436</v>
       </c>
       <c r="H663" t="n">
-        <v>2319.464</v>
+        <v>2301.713</v>
       </c>
       <c r="I663" t="n">
         <v>0.0</v>
@@ -24769,7 +24769,7 @@
         </is>
       </c>
       <c r="E668" t="n">
-        <v>49.259</v>
+        <v>40.383</v>
       </c>
       <c r="F668" t="n">
         <v>0.888</v>
@@ -24778,7 +24778,7 @@
         <v>142.00799999999998</v>
       </c>
       <c r="H668" t="n">
-        <v>49.259</v>
+        <v>40.383</v>
       </c>
       <c r="I668" t="n">
         <v>0.0</v>
@@ -24806,7 +24806,7 @@
         </is>
       </c>
       <c r="E669" t="n">
-        <v>171.594</v>
+        <v>149.108</v>
       </c>
       <c r="F669" t="n">
         <v>0.0</v>
@@ -24815,7 +24815,7 @@
         <v>36.685</v>
       </c>
       <c r="H669" t="n">
-        <v>171.594</v>
+        <v>149.108</v>
       </c>
       <c r="I669" t="n">
         <v>0.0</v>
@@ -25102,7 +25102,7 @@
         </is>
       </c>
       <c r="E677" t="n">
-        <v>5925.3369999999995</v>
+        <v>3614.101</v>
       </c>
       <c r="F677" t="n">
         <v>0.0</v>
@@ -25114,7 +25114,7 @@
         <v>3614.101</v>
       </c>
       <c r="I677" t="n">
-        <v>2311.236</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="678">
@@ -25139,7 +25139,7 @@
         </is>
       </c>
       <c r="E678" t="n">
-        <v>5199.8592</v>
+        <v>3589.2518</v>
       </c>
       <c r="F678" t="n">
         <v>0.0</v>
@@ -25148,10 +25148,10 @@
         <v>15.088000000000001</v>
       </c>
       <c r="H678" t="n">
-        <v>3101.691</v>
+        <v>3101.6910000000003</v>
       </c>
       <c r="I678" t="n">
-        <v>2098.1682</v>
+        <v>487.5608</v>
       </c>
     </row>
     <row r="679">
@@ -25176,7 +25176,7 @@
         </is>
       </c>
       <c r="E679" t="n">
-        <v>800.57</v>
+        <v>763.883</v>
       </c>
       <c r="F679" t="n">
         <v>13.461</v>
@@ -25185,7 +25185,7 @@
         <v>64.19800000000001</v>
       </c>
       <c r="H679" t="n">
-        <v>800.57</v>
+        <v>763.883</v>
       </c>
       <c r="I679" t="n">
         <v>0.0</v>
@@ -25361,7 +25361,7 @@
         </is>
       </c>
       <c r="E684" t="n">
-        <v>2983.156</v>
+        <v>2981.2889999999998</v>
       </c>
       <c r="F684" t="n">
         <v>0.0</v>
@@ -25370,7 +25370,7 @@
         <v>0.0</v>
       </c>
       <c r="H684" t="n">
-        <v>2983.156</v>
+        <v>2981.2889999999998</v>
       </c>
       <c r="I684" t="n">
         <v>0.0</v>
@@ -25398,7 +25398,7 @@
         </is>
       </c>
       <c r="E685" t="n">
-        <v>3741.7760000000003</v>
+        <v>3740.2200000000003</v>
       </c>
       <c r="F685" t="n">
         <v>3734.0</v>
@@ -25407,7 +25407,7 @@
         <v>0.0</v>
       </c>
       <c r="H685" t="n">
-        <v>3741.7760000000003</v>
+        <v>3740.2200000000003</v>
       </c>
       <c r="I685" t="n">
         <v>0.0</v>
@@ -25805,7 +25805,7 @@
         </is>
       </c>
       <c r="E696" t="n">
-        <v>3590.4993</v>
+        <v>2501.448</v>
       </c>
       <c r="F696" t="n">
         <v>0.0</v>
@@ -25817,7 +25817,7 @@
         <v>2501.448</v>
       </c>
       <c r="I696" t="n">
-        <v>1089.0513</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="697">
@@ -25953,7 +25953,7 @@
         </is>
       </c>
       <c r="E700" t="n">
-        <v>1665.3600000000001</v>
+        <v>1824.0549999999998</v>
       </c>
       <c r="F700" t="n">
         <v>0.624</v>
@@ -25962,7 +25962,7 @@
         <v>0.0</v>
       </c>
       <c r="H700" t="n">
-        <v>1105.26</v>
+        <v>1263.9549999999997</v>
       </c>
       <c r="I700" t="n">
         <v>560.1</v>
@@ -25990,7 +25990,7 @@
         </is>
       </c>
       <c r="E701" t="n">
-        <v>3616.066</v>
+        <v>3552.5879999999997</v>
       </c>
       <c r="F701" t="n">
         <v>26.138</v>
@@ -25999,7 +25999,7 @@
         <v>5.601</v>
       </c>
       <c r="H701" t="n">
-        <v>3616.066</v>
+        <v>3552.5879999999997</v>
       </c>
       <c r="I701" t="n">
         <v>0.0</v>
@@ -26027,7 +26027,7 @@
         </is>
       </c>
       <c r="E702" t="n">
-        <v>8143.5380000000005</v>
+        <v>8093.13</v>
       </c>
       <c r="F702" t="n">
         <v>41.074</v>
@@ -26036,7 +26036,7 @@
         <v>9.334999999999999</v>
       </c>
       <c r="H702" t="n">
-        <v>8143.5380000000005</v>
+        <v>8093.13</v>
       </c>
       <c r="I702" t="n">
         <v>0.0</v>
@@ -26064,7 +26064,7 @@
         </is>
       </c>
       <c r="E703" t="n">
-        <v>2822.489</v>
+        <v>2795.536</v>
       </c>
       <c r="F703" t="n">
         <v>0.0</v>
@@ -26073,7 +26073,7 @@
         <v>3.851</v>
       </c>
       <c r="H703" t="n">
-        <v>2822.489</v>
+        <v>2795.536</v>
       </c>
       <c r="I703" t="n">
         <v>0.0</v>
@@ -26101,7 +26101,7 @@
         </is>
       </c>
       <c r="E704" t="n">
-        <v>1039.662</v>
+        <v>1028.11</v>
       </c>
       <c r="F704" t="n">
         <v>0.0</v>
@@ -26110,7 +26110,7 @@
         <v>0.0</v>
       </c>
       <c r="H704" t="n">
-        <v>1039.662</v>
+        <v>1028.11</v>
       </c>
       <c r="I704" t="n">
         <v>0.0</v>
@@ -26138,7 +26138,7 @@
         </is>
       </c>
       <c r="E705" t="n">
-        <v>215.807</v>
+        <v>213.987</v>
       </c>
       <c r="F705" t="n">
         <v>0.0</v>
@@ -26147,7 +26147,7 @@
         <v>0.0</v>
       </c>
       <c r="H705" t="n">
-        <v>215.807</v>
+        <v>213.987</v>
       </c>
       <c r="I705" t="n">
         <v>0.0</v>
@@ -26397,7 +26397,7 @@
         </is>
       </c>
       <c r="E712" t="n">
-        <v>1448.421</v>
+        <v>1428.429</v>
       </c>
       <c r="F712" t="n">
         <v>0.666</v>
@@ -26406,7 +26406,7 @@
         <v>10.996</v>
       </c>
       <c r="H712" t="n">
-        <v>1448.421</v>
+        <v>1428.429</v>
       </c>
       <c r="I712" t="n">
         <v>0.0</v>
@@ -26471,7 +26471,7 @@
         </is>
       </c>
       <c r="E714" t="n">
-        <v>627.3969999999999</v>
+        <v>623.756</v>
       </c>
       <c r="F714" t="n">
         <v>0.0</v>
@@ -26480,7 +26480,7 @@
         <v>0.0</v>
       </c>
       <c r="H714" t="n">
-        <v>627.3969999999999</v>
+        <v>623.756</v>
       </c>
       <c r="I714" t="n">
         <v>0.0</v>
@@ -26508,7 +26508,7 @@
         </is>
       </c>
       <c r="E715" t="n">
-        <v>357.791</v>
+        <v>354.15</v>
       </c>
       <c r="F715" t="n">
         <v>0.0</v>
@@ -26517,7 +26517,7 @@
         <v>0.0</v>
       </c>
       <c r="H715" t="n">
-        <v>357.791</v>
+        <v>354.15</v>
       </c>
       <c r="I715" t="n">
         <v>0.0</v>
@@ -26545,7 +26545,7 @@
         </is>
       </c>
       <c r="E716" t="n">
-        <v>6255.609</v>
+        <v>6217.211</v>
       </c>
       <c r="F716" t="n">
         <v>0.0</v>
@@ -26554,7 +26554,7 @@
         <v>0.0</v>
       </c>
       <c r="H716" t="n">
-        <v>6255.609</v>
+        <v>6217.211</v>
       </c>
       <c r="I716" t="n">
         <v>0.0</v>
@@ -26582,7 +26582,7 @@
         </is>
       </c>
       <c r="E717" t="n">
-        <v>1672.743</v>
+        <v>1584.731</v>
       </c>
       <c r="F717" t="n">
         <v>0.0</v>
@@ -26591,7 +26591,7 @@
         <v>153.619</v>
       </c>
       <c r="H717" t="n">
-        <v>1672.743</v>
+        <v>1584.731</v>
       </c>
       <c r="I717" t="n">
         <v>0.0</v>
@@ -26619,7 +26619,7 @@
         </is>
       </c>
       <c r="E718" t="n">
-        <v>4607.711</v>
+        <v>4582.113</v>
       </c>
       <c r="F718" t="n">
         <v>0.0</v>
@@ -26628,7 +26628,7 @@
         <v>0.0</v>
       </c>
       <c r="H718" t="n">
-        <v>4607.711</v>
+        <v>4582.113</v>
       </c>
       <c r="I718" t="n">
         <v>0.0</v>
@@ -26656,7 +26656,7 @@
         </is>
       </c>
       <c r="E719" t="n">
-        <v>4353.076</v>
+        <v>4329.072999999999</v>
       </c>
       <c r="F719" t="n">
         <v>0.26699999999999996</v>
@@ -26665,7 +26665,7 @@
         <v>0.0</v>
       </c>
       <c r="H719" t="n">
-        <v>4353.076</v>
+        <v>4329.072999999999</v>
       </c>
       <c r="I719" t="n">
         <v>0.0</v>
@@ -26693,7 +26693,7 @@
         </is>
       </c>
       <c r="E720" t="n">
-        <v>273.05</v>
+        <v>272.516</v>
       </c>
       <c r="F720" t="n">
         <v>6.4</v>
@@ -26702,7 +26702,7 @@
         <v>3.2</v>
       </c>
       <c r="H720" t="n">
-        <v>273.05</v>
+        <v>272.516</v>
       </c>
       <c r="I720" t="n">
         <v>0.0</v>
@@ -26730,7 +26730,7 @@
         </is>
       </c>
       <c r="E721" t="n">
-        <v>41.339</v>
+        <v>33.870999999999995</v>
       </c>
       <c r="F721" t="n">
         <v>0.533</v>
@@ -26739,7 +26739,7 @@
         <v>211.226</v>
       </c>
       <c r="H721" t="n">
-        <v>41.339</v>
+        <v>33.870999999999995</v>
       </c>
       <c r="I721" t="n">
         <v>0.0</v>
@@ -26767,7 +26767,7 @@
         </is>
       </c>
       <c r="E722" t="n">
-        <v>3292.5939999999996</v>
+        <v>3195.533</v>
       </c>
       <c r="F722" t="n">
         <v>0.0</v>
@@ -26776,7 +26776,7 @@
         <v>0.0</v>
       </c>
       <c r="H722" t="n">
-        <v>3292.5939999999996</v>
+        <v>3195.533</v>
       </c>
       <c r="I722" t="n">
         <v>0.0</v>
@@ -26804,7 +26804,7 @@
         </is>
       </c>
       <c r="E723" t="n">
-        <v>26889.76</v>
+        <v>26782.814</v>
       </c>
       <c r="F723" t="n">
         <v>2.4</v>
@@ -26813,7 +26813,7 @@
         <v>288.036</v>
       </c>
       <c r="H723" t="n">
-        <v>26889.76</v>
+        <v>26782.814</v>
       </c>
       <c r="I723" t="n">
         <v>0.0</v>
@@ -26841,7 +26841,7 @@
         </is>
       </c>
       <c r="E724" t="n">
-        <v>4599.7762</v>
+        <v>1713.0149999999999</v>
       </c>
       <c r="F724" t="n">
         <v>2.4</v>
@@ -26850,10 +26850,10 @@
         <v>212.827</v>
       </c>
       <c r="H724" t="n">
-        <v>1853.8329999999999</v>
+        <v>1713.0149999999999</v>
       </c>
       <c r="I724" t="n">
-        <v>2745.9432</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="725">
@@ -26878,7 +26878,7 @@
         </is>
       </c>
       <c r="E725" t="n">
-        <v>2547.219</v>
+        <v>2705.3940000000002</v>
       </c>
       <c r="F725" t="n">
         <v>0.0</v>
@@ -26887,7 +26887,7 @@
         <v>67.155</v>
       </c>
       <c r="H725" t="n">
-        <v>2547.219</v>
+        <v>2705.3940000000002</v>
       </c>
       <c r="I725" t="n">
         <v>0.0</v>
@@ -26915,7 +26915,7 @@
         </is>
       </c>
       <c r="E726" t="n">
-        <v>2038.48</v>
+        <v>2036.08</v>
       </c>
       <c r="F726" t="n">
         <v>0.12000000000000001</v>
@@ -26924,7 +26924,7 @@
         <v>2.8800000000000003</v>
       </c>
       <c r="H726" t="n">
-        <v>2038.48</v>
+        <v>2036.08</v>
       </c>
       <c r="I726" t="n">
         <v>0.0</v>
@@ -26952,7 +26952,7 @@
         </is>
       </c>
       <c r="E727" t="n">
-        <v>3125.5280000000002</v>
+        <v>3115.538</v>
       </c>
       <c r="F727" t="n">
         <v>0.0</v>
@@ -26961,7 +26961,7 @@
         <v>0.555</v>
       </c>
       <c r="H727" t="n">
-        <v>3125.5280000000002</v>
+        <v>3115.538</v>
       </c>
       <c r="I727" t="n">
         <v>0.0</v>
@@ -26989,7 +26989,7 @@
         </is>
       </c>
       <c r="E728" t="n">
-        <v>1788.282</v>
+        <v>1787.922</v>
       </c>
       <c r="F728" t="n">
         <v>0.0</v>
@@ -26998,7 +26998,7 @@
         <v>0.0</v>
       </c>
       <c r="H728" t="n">
-        <v>1788.282</v>
+        <v>1787.922</v>
       </c>
       <c r="I728" t="n">
         <v>0.0</v>
@@ -27100,7 +27100,7 @@
         </is>
       </c>
       <c r="E731" t="n">
-        <v>30.105</v>
+        <v>26.19</v>
       </c>
       <c r="F731" t="n">
         <v>0.675</v>
@@ -27109,7 +27109,7 @@
         <v>0.40499999999999997</v>
       </c>
       <c r="H731" t="n">
-        <v>30.105</v>
+        <v>26.19</v>
       </c>
       <c r="I731" t="n">
         <v>0.0</v>
@@ -27285,7 +27285,7 @@
         </is>
       </c>
       <c r="E736" t="n">
-        <v>1747.802</v>
+        <v>1829.9299999999998</v>
       </c>
       <c r="F736" t="n">
         <v>9.599</v>
@@ -27294,7 +27294,7 @@
         <v>0.0</v>
       </c>
       <c r="H736" t="n">
-        <v>1747.802</v>
+        <v>1829.9299999999998</v>
       </c>
       <c r="I736" t="n">
         <v>0.0</v>
@@ -27581,7 +27581,7 @@
         </is>
       </c>
       <c r="E744" t="n">
-        <v>2830.694</v>
+        <v>2795.191</v>
       </c>
       <c r="F744" t="n">
         <v>0.0</v>
@@ -27590,7 +27590,7 @@
         <v>162.126</v>
       </c>
       <c r="H744" t="n">
-        <v>2830.694</v>
+        <v>2795.191</v>
       </c>
       <c r="I744" t="n">
         <v>0.0</v>
@@ -27618,7 +27618,7 @@
         </is>
       </c>
       <c r="E745" t="n">
-        <v>4026.194</v>
+        <v>3941.949</v>
       </c>
       <c r="F745" t="n">
         <v>5.029999999999999</v>
@@ -27627,7 +27627,7 @@
         <v>2.5149999999999997</v>
       </c>
       <c r="H745" t="n">
-        <v>4026.194</v>
+        <v>3941.949</v>
       </c>
       <c r="I745" t="n">
         <v>0.0</v>
@@ -27655,7 +27655,7 @@
         </is>
       </c>
       <c r="E746" t="n">
-        <v>1164.3505999999998</v>
+        <v>1146.749</v>
       </c>
       <c r="F746" t="n">
         <v>17.604000000000003</v>
@@ -27664,10 +27664,10 @@
         <v>0.0</v>
       </c>
       <c r="H746" t="n">
-        <v>1146.7469999999998</v>
+        <v>1146.749</v>
       </c>
       <c r="I746" t="n">
-        <v>17.6036</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="747">
@@ -27766,7 +27766,7 @@
         </is>
       </c>
       <c r="E749" t="n">
-        <v>807.08</v>
+        <v>777.494</v>
       </c>
       <c r="F749" t="n">
         <v>0.0</v>
@@ -27775,7 +27775,7 @@
         <v>176.327</v>
       </c>
       <c r="H749" t="n">
-        <v>807.08</v>
+        <v>777.494</v>
       </c>
       <c r="I749" t="n">
         <v>0.0</v>
@@ -27840,7 +27840,7 @@
         </is>
       </c>
       <c r="E751" t="n">
-        <v>7.103</v>
+        <v>47.336000000000006</v>
       </c>
       <c r="F751" t="n">
         <v>0.0</v>
@@ -27849,7 +27849,7 @@
         <v>77.217</v>
       </c>
       <c r="H751" t="n">
-        <v>7.103</v>
+        <v>47.336000000000006</v>
       </c>
       <c r="I751" t="n">
         <v>0.0</v>
@@ -27877,7 +27877,7 @@
         </is>
       </c>
       <c r="E752" t="n">
-        <v>2012.29</v>
+        <v>1871.546</v>
       </c>
       <c r="F752" t="n">
         <v>0.0</v>
@@ -27886,7 +27886,7 @@
         <v>2.3080000000000003</v>
       </c>
       <c r="H752" t="n">
-        <v>2012.29</v>
+        <v>1871.546</v>
       </c>
       <c r="I752" t="n">
         <v>0.0</v>
@@ -28025,7 +28025,7 @@
         </is>
       </c>
       <c r="E756" t="n">
-        <v>3514.604</v>
+        <v>3424.627</v>
       </c>
       <c r="F756" t="n">
         <v>0.0</v>
@@ -28034,7 +28034,7 @@
         <v>2.3080000000000003</v>
       </c>
       <c r="H756" t="n">
-        <v>3514.604</v>
+        <v>3424.627</v>
       </c>
       <c r="I756" t="n">
         <v>0.0</v>
@@ -28062,7 +28062,7 @@
         </is>
       </c>
       <c r="E757" t="n">
-        <v>5667.685</v>
+        <v>5515.405</v>
       </c>
       <c r="F757" t="n">
         <v>0.0</v>
@@ -28071,7 +28071,7 @@
         <v>2.3080000000000003</v>
       </c>
       <c r="H757" t="n">
-        <v>5667.685</v>
+        <v>5515.405</v>
       </c>
       <c r="I757" t="n">
         <v>0.0</v>
@@ -28395,7 +28395,7 @@
         </is>
       </c>
       <c r="E766" t="n">
-        <v>936.469</v>
+        <v>927.992</v>
       </c>
       <c r="F766" t="n">
         <v>0.892</v>
@@ -28404,7 +28404,7 @@
         <v>0.0</v>
       </c>
       <c r="H766" t="n">
-        <v>936.469</v>
+        <v>927.992</v>
       </c>
       <c r="I766" t="n">
         <v>0.0</v>
@@ -28506,7 +28506,7 @@
         </is>
       </c>
       <c r="E769" t="n">
-        <v>1447.166</v>
+        <v>1447.167</v>
       </c>
       <c r="F769" t="n">
         <v>0.0</v>
@@ -28515,7 +28515,7 @@
         <v>39.876000000000005</v>
       </c>
       <c r="H769" t="n">
-        <v>1447.166</v>
+        <v>1447.167</v>
       </c>
       <c r="I769" t="n">
         <v>0.0</v>
@@ -28543,7 +28543,7 @@
         </is>
       </c>
       <c r="E770" t="n">
-        <v>19492.6408</v>
+        <v>16529.491</v>
       </c>
       <c r="F770" t="n">
         <v>10.616</v>
@@ -28552,10 +28552,10 @@
         <v>7.385</v>
       </c>
       <c r="H770" t="n">
-        <v>16568.260000000002</v>
+        <v>16529.491</v>
       </c>
       <c r="I770" t="n">
-        <v>2924.3808</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="771">
@@ -28654,7 +28654,7 @@
         </is>
       </c>
       <c r="E773" t="n">
-        <v>585.833</v>
+        <v>585.834</v>
       </c>
       <c r="F773" t="n">
         <v>2.154</v>
@@ -28663,7 +28663,7 @@
         <v>614.048</v>
       </c>
       <c r="H773" t="n">
-        <v>585.833</v>
+        <v>585.834</v>
       </c>
       <c r="I773" t="n">
         <v>0.0</v>
@@ -28691,7 +28691,7 @@
         </is>
       </c>
       <c r="E774" t="n">
-        <v>4689.7934</v>
+        <v>4104.923</v>
       </c>
       <c r="F774" t="n">
         <v>0.6759999999999999</v>
@@ -28703,7 +28703,7 @@
         <v>4104.923</v>
       </c>
       <c r="I774" t="n">
-        <v>584.8704</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="775">
@@ -28802,7 +28802,7 @@
         </is>
       </c>
       <c r="E777" t="n">
-        <v>11887.629</v>
+        <v>11857.845</v>
       </c>
       <c r="F777" t="n">
         <v>0.6759999999999999</v>
@@ -28811,7 +28811,7 @@
         <v>38.585</v>
       </c>
       <c r="H777" t="n">
-        <v>11887.629</v>
+        <v>11857.845</v>
       </c>
       <c r="I777" t="n">
         <v>0.0</v>
@@ -29024,7 +29024,7 @@
         </is>
       </c>
       <c r="E783" t="n">
-        <v>6455.592</v>
+        <v>6453.546</v>
       </c>
       <c r="F783" t="n">
         <v>0.0</v>
@@ -29033,7 +29033,7 @@
         <v>0.0</v>
       </c>
       <c r="H783" t="n">
-        <v>6455.592</v>
+        <v>6453.546</v>
       </c>
       <c r="I783" t="n">
         <v>0.0</v>
@@ -29098,7 +29098,7 @@
         </is>
       </c>
       <c r="E785" t="n">
-        <v>6.72</v>
+        <v>700.8</v>
       </c>
       <c r="F785" t="n">
         <v>0.0</v>
@@ -29107,10 +29107,10 @@
         <v>19.68</v>
       </c>
       <c r="H785" t="n">
-        <v>6.72</v>
+        <v>5.76</v>
       </c>
       <c r="I785" t="n">
-        <v>0.0</v>
+        <v>695.04</v>
       </c>
     </row>
     <row r="786">
@@ -29172,7 +29172,7 @@
         </is>
       </c>
       <c r="E787" t="n">
-        <v>2440.52</v>
+        <v>1684.0549999999998</v>
       </c>
       <c r="F787" t="n">
         <v>0.185</v>
@@ -29181,10 +29181,10 @@
         <v>34.456</v>
       </c>
       <c r="H787" t="n">
-        <v>939.245</v>
+        <v>984.755</v>
       </c>
       <c r="I787" t="n">
-        <v>1501.275</v>
+        <v>699.3</v>
       </c>
     </row>
     <row r="788">
@@ -29209,7 +29209,7 @@
         </is>
       </c>
       <c r="E788" t="n">
-        <v>722.657</v>
+        <v>679.783</v>
       </c>
       <c r="F788" t="n">
         <v>4.995</v>
@@ -29218,7 +29218,7 @@
         <v>79.36500000000001</v>
       </c>
       <c r="H788" t="n">
-        <v>722.657</v>
+        <v>679.783</v>
       </c>
       <c r="I788" t="n">
         <v>0.0</v>
@@ -29246,7 +29246,7 @@
         </is>
       </c>
       <c r="E789" t="n">
-        <v>4866.344999999999</v>
+        <v>3927.6899999999996</v>
       </c>
       <c r="F789" t="n">
         <v>1.485</v>
@@ -29258,7 +29258,7 @@
         <v>345.87</v>
       </c>
       <c r="I789" t="n">
-        <v>4520.474999999999</v>
+        <v>3581.8199999999997</v>
       </c>
     </row>
     <row r="790">
@@ -29283,7 +29283,7 @@
         </is>
       </c>
       <c r="E790" t="n">
-        <v>18.8</v>
+        <v>1419.04</v>
       </c>
       <c r="F790" t="n">
         <v>0.08</v>
@@ -29292,10 +29292,10 @@
         <v>17.32</v>
       </c>
       <c r="H790" t="n">
-        <v>18.8</v>
+        <v>15.52</v>
       </c>
       <c r="I790" t="n">
-        <v>0.0</v>
+        <v>1403.52</v>
       </c>
     </row>
     <row r="791">
@@ -29431,7 +29431,7 @@
         </is>
       </c>
       <c r="E794" t="n">
-        <v>3650.5229999999997</v>
+        <v>3639.607</v>
       </c>
       <c r="F794" t="n">
         <v>1.82</v>
@@ -29440,7 +29440,7 @@
         <v>9.704</v>
       </c>
       <c r="H794" t="n">
-        <v>3650.5229999999997</v>
+        <v>3639.607</v>
       </c>
       <c r="I794" t="n">
         <v>0.0</v>
@@ -29468,7 +29468,7 @@
         </is>
       </c>
       <c r="E795" t="n">
-        <v>1367.6580000000001</v>
+        <v>1356.135</v>
       </c>
       <c r="F795" t="n">
         <v>0.0</v>
@@ -29477,7 +29477,7 @@
         <v>0.0</v>
       </c>
       <c r="H795" t="n">
-        <v>1367.6580000000001</v>
+        <v>1356.135</v>
       </c>
       <c r="I795" t="n">
         <v>0.0</v>
@@ -29616,7 +29616,7 @@
         </is>
       </c>
       <c r="E799" t="n">
-        <v>4532.118</v>
+        <v>4518.241</v>
       </c>
       <c r="F799" t="n">
         <v>0.631</v>
@@ -29625,7 +29625,7 @@
         <v>80.739</v>
       </c>
       <c r="H799" t="n">
-        <v>4532.118</v>
+        <v>4518.241</v>
       </c>
       <c r="I799" t="n">
         <v>0.0</v>
@@ -29653,7 +29653,7 @@
         </is>
       </c>
       <c r="E800" t="n">
-        <v>3232.7219999999998</v>
+        <v>3249.7529999999997</v>
       </c>
       <c r="F800" t="n">
         <v>0.631</v>
@@ -29662,7 +29662,7 @@
         <v>0.631</v>
       </c>
       <c r="H800" t="n">
-        <v>3232.7219999999998</v>
+        <v>3249.7529999999997</v>
       </c>
       <c r="I800" t="n">
         <v>0.0</v>
@@ -29690,7 +29690,7 @@
         </is>
       </c>
       <c r="E801" t="n">
-        <v>4537.397999999999</v>
+        <v>4534.038</v>
       </c>
       <c r="F801" t="n">
         <v>0.0</v>
@@ -29699,7 +29699,7 @@
         <v>0.0</v>
       </c>
       <c r="H801" t="n">
-        <v>4537.397999999999</v>
+        <v>4534.038</v>
       </c>
       <c r="I801" t="n">
         <v>0.0</v>
@@ -29875,7 +29875,7 @@
         </is>
       </c>
       <c r="E806" t="n">
-        <v>506.143</v>
+        <v>499.681</v>
       </c>
       <c r="F806" t="n">
         <v>0.0</v>
@@ -29884,7 +29884,7 @@
         <v>590.1410000000001</v>
       </c>
       <c r="H806" t="n">
-        <v>506.143</v>
+        <v>499.681</v>
       </c>
       <c r="I806" t="n">
         <v>0.0</v>
@@ -30134,7 +30134,7 @@
         </is>
       </c>
       <c r="E813" t="n">
-        <v>1935.8</v>
+        <v>1902.0</v>
       </c>
       <c r="F813" t="n">
         <v>0.4</v>
@@ -30143,7 +30143,7 @@
         <v>0.0</v>
       </c>
       <c r="H813" t="n">
-        <v>1935.8</v>
+        <v>1902.0</v>
       </c>
       <c r="I813" t="n">
         <v>0.0</v>
@@ -30245,7 +30245,7 @@
         </is>
       </c>
       <c r="E816" t="n">
-        <v>17342.916</v>
+        <v>17253.322</v>
       </c>
       <c r="F816" t="n">
         <v>0.533</v>
@@ -30254,7 +30254,7 @@
         <v>0.0</v>
       </c>
       <c r="H816" t="n">
-        <v>17342.916</v>
+        <v>17253.322</v>
       </c>
       <c r="I816" t="n">
         <v>0.0</v>
@@ -30282,7 +30282,7 @@
         </is>
       </c>
       <c r="E817" t="n">
-        <v>1001.725</v>
+        <v>961.721</v>
       </c>
       <c r="F817" t="n">
         <v>0.533</v>
@@ -30291,7 +30291,7 @@
         <v>0.0</v>
       </c>
       <c r="H817" t="n">
-        <v>1001.725</v>
+        <v>961.721</v>
       </c>
       <c r="I817" t="n">
         <v>0.0</v>
@@ -30319,7 +30319,7 @@
         </is>
       </c>
       <c r="E818" t="n">
-        <v>10218.611</v>
+        <v>10109.796</v>
       </c>
       <c r="F818" t="n">
         <v>2.4</v>
@@ -30328,7 +30328,7 @@
         <v>599.008</v>
       </c>
       <c r="H818" t="n">
-        <v>10218.611</v>
+        <v>10109.796</v>
       </c>
       <c r="I818" t="n">
         <v>0.0</v>
@@ -30430,7 +30430,7 @@
         </is>
       </c>
       <c r="E821" t="n">
-        <v>307.18</v>
+        <v>169.59</v>
       </c>
       <c r="F821" t="n">
         <v>3.2</v>
@@ -30439,7 +30439,7 @@
         <v>1.067</v>
       </c>
       <c r="H821" t="n">
-        <v>307.18</v>
+        <v>169.59</v>
       </c>
       <c r="I821" t="n">
         <v>0.0</v>
@@ -30467,7 +30467,7 @@
         </is>
       </c>
       <c r="E822" t="n">
-        <v>1774.622</v>
+        <v>1608.202</v>
       </c>
       <c r="F822" t="n">
         <v>0.0</v>
@@ -30476,7 +30476,7 @@
         <v>192.024</v>
       </c>
       <c r="H822" t="n">
-        <v>1774.622</v>
+        <v>1608.202</v>
       </c>
       <c r="I822" t="n">
         <v>0.0</v>
@@ -30652,7 +30652,7 @@
         </is>
       </c>
       <c r="E827" t="n">
-        <v>1239.659</v>
+        <v>1239.658</v>
       </c>
       <c r="F827" t="n">
         <v>0.0</v>
@@ -30661,7 +30661,7 @@
         <v>0.0</v>
       </c>
       <c r="H827" t="n">
-        <v>1239.659</v>
+        <v>1239.658</v>
       </c>
       <c r="I827" t="n">
         <v>0.0</v>
@@ -30689,7 +30689,7 @@
         </is>
       </c>
       <c r="E828" t="n">
-        <v>1281.024</v>
+        <v>1174.272</v>
       </c>
       <c r="F828" t="n">
         <v>0.0</v>
@@ -30698,7 +30698,7 @@
         <v>1670.6689999999999</v>
       </c>
       <c r="H828" t="n">
-        <v>1281.024</v>
+        <v>1174.272</v>
       </c>
       <c r="I828" t="n">
         <v>0.0</v>
@@ -31281,7 +31281,7 @@
         </is>
       </c>
       <c r="E844" t="n">
-        <v>294.889</v>
+        <v>109.219</v>
       </c>
       <c r="F844" t="n">
         <v>0.0</v>
@@ -31290,7 +31290,7 @@
         <v>0.0</v>
       </c>
       <c r="H844" t="n">
-        <v>294.889</v>
+        <v>109.219</v>
       </c>
       <c r="I844" t="n">
         <v>0.0</v>
@@ -31318,7 +31318,7 @@
         </is>
       </c>
       <c r="E845" t="n">
-        <v>611.621</v>
+        <v>447.794</v>
       </c>
       <c r="F845" t="n">
         <v>77.66499999999999</v>
@@ -31327,7 +31327,7 @@
         <v>0.0</v>
       </c>
       <c r="H845" t="n">
-        <v>611.621</v>
+        <v>447.794</v>
       </c>
       <c r="I845" t="n">
         <v>0.0</v>
@@ -31392,7 +31392,7 @@
         </is>
       </c>
       <c r="E847" t="n">
-        <v>145.625</v>
+        <v>40.047</v>
       </c>
       <c r="F847" t="n">
         <v>0.0</v>
@@ -31401,7 +31401,7 @@
         <v>0.0</v>
       </c>
       <c r="H847" t="n">
-        <v>145.625</v>
+        <v>40.047</v>
       </c>
       <c r="I847" t="n">
         <v>0.0</v>
@@ -31429,7 +31429,7 @@
         </is>
       </c>
       <c r="E848" t="n">
-        <v>2934.813</v>
+        <v>2932.147</v>
       </c>
       <c r="F848" t="n">
         <v>1.333</v>
@@ -31438,7 +31438,7 @@
         <v>0.6669999999999999</v>
       </c>
       <c r="H848" t="n">
-        <v>2934.813</v>
+        <v>2932.147</v>
       </c>
       <c r="I848" t="n">
         <v>0.0</v>
@@ -31466,7 +31466,7 @@
         </is>
       </c>
       <c r="E849" t="n">
-        <v>2617.464</v>
+        <v>2615.464</v>
       </c>
       <c r="F849" t="n">
         <v>2.6670000000000003</v>
@@ -31475,7 +31475,7 @@
         <v>0.0</v>
       </c>
       <c r="H849" t="n">
-        <v>2617.464</v>
+        <v>2615.464</v>
       </c>
       <c r="I849" t="n">
         <v>0.0</v>
@@ -31577,7 +31577,7 @@
         </is>
       </c>
       <c r="E852" t="n">
-        <v>5982.83</v>
+        <v>5962.0289999999995</v>
       </c>
       <c r="F852" t="n">
         <v>0.0</v>
@@ -31586,7 +31586,7 @@
         <v>0.0</v>
       </c>
       <c r="H852" t="n">
-        <v>5982.83</v>
+        <v>5962.0289999999995</v>
       </c>
       <c r="I852" t="n">
         <v>0.0</v>
@@ -31688,7 +31688,7 @@
         </is>
       </c>
       <c r="E855" t="n">
-        <v>10024.252</v>
+        <v>10021.653</v>
       </c>
       <c r="F855" t="n">
         <v>14.734</v>
@@ -31697,7 +31697,7 @@
         <v>0.0</v>
       </c>
       <c r="H855" t="n">
-        <v>10024.252</v>
+        <v>10021.653</v>
       </c>
       <c r="I855" t="n">
         <v>0.0</v>
@@ -31725,7 +31725,7 @@
         </is>
       </c>
       <c r="E856" t="n">
-        <v>706.221</v>
+        <v>684.886</v>
       </c>
       <c r="F856" t="n">
         <v>23.470000000000002</v>
@@ -31734,7 +31734,7 @@
         <v>0.0</v>
       </c>
       <c r="H856" t="n">
-        <v>706.221</v>
+        <v>684.886</v>
       </c>
       <c r="I856" t="n">
         <v>0.0</v>
@@ -31762,7 +31762,7 @@
         </is>
       </c>
       <c r="E857" t="n">
-        <v>2764.863</v>
+        <v>2720.646</v>
       </c>
       <c r="F857" t="n">
         <v>1.734</v>
@@ -31771,7 +31771,7 @@
         <v>0.0</v>
       </c>
       <c r="H857" t="n">
-        <v>2764.863</v>
+        <v>2720.646</v>
       </c>
       <c r="I857" t="n">
         <v>0.0</v>
@@ -31984,7 +31984,7 @@
         </is>
       </c>
       <c r="E863" t="n">
-        <v>1133.643</v>
+        <v>1132.777</v>
       </c>
       <c r="F863" t="n">
         <v>0.867</v>
@@ -31993,7 +31993,7 @@
         <v>0.0</v>
       </c>
       <c r="H863" t="n">
-        <v>1133.643</v>
+        <v>1132.777</v>
       </c>
       <c r="I863" t="n">
         <v>0.0</v>
@@ -32021,7 +32021,7 @@
         </is>
       </c>
       <c r="E864" t="n">
-        <v>11545.443000000001</v>
+        <v>11502.238000000001</v>
       </c>
       <c r="F864" t="n">
         <v>36.005</v>
@@ -32030,7 +32030,7 @@
         <v>0.0</v>
       </c>
       <c r="H864" t="n">
-        <v>11545.443000000001</v>
+        <v>11502.238000000001</v>
       </c>
       <c r="I864" t="n">
         <v>0.0</v>
@@ -32095,7 +32095,7 @@
         </is>
       </c>
       <c r="E866" t="n">
-        <v>2990.24</v>
+        <v>2958.237</v>
       </c>
       <c r="F866" t="n">
         <v>1.067</v>
@@ -32104,7 +32104,7 @@
         <v>0.0</v>
       </c>
       <c r="H866" t="n">
-        <v>2990.24</v>
+        <v>2958.237</v>
       </c>
       <c r="I866" t="n">
         <v>0.0</v>
@@ -32132,7 +32132,7 @@
         </is>
       </c>
       <c r="E867" t="n">
-        <v>1430.578</v>
+        <v>1428.444</v>
       </c>
       <c r="F867" t="n">
         <v>1.067</v>
@@ -32141,7 +32141,7 @@
         <v>25.603</v>
       </c>
       <c r="H867" t="n">
-        <v>1430.578</v>
+        <v>1428.444</v>
       </c>
       <c r="I867" t="n">
         <v>0.0</v>
@@ -32169,7 +32169,7 @@
         </is>
       </c>
       <c r="E868" t="n">
-        <v>1886.2150000000001</v>
+        <v>1844.366</v>
       </c>
       <c r="F868" t="n">
         <v>12.737</v>
@@ -32178,7 +32178,7 @@
         <v>19.408</v>
       </c>
       <c r="H868" t="n">
-        <v>1886.2150000000001</v>
+        <v>1844.366</v>
       </c>
       <c r="I868" t="n">
         <v>0.0</v>
@@ -32206,7 +32206,7 @@
         </is>
       </c>
       <c r="E869" t="n">
-        <v>1581.047</v>
+        <v>1530.136</v>
       </c>
       <c r="F869" t="n">
         <v>0.0</v>
@@ -32215,7 +32215,7 @@
         <v>0.0</v>
       </c>
       <c r="H869" t="n">
-        <v>1581.047</v>
+        <v>1530.136</v>
       </c>
       <c r="I869" t="n">
         <v>0.0</v>
@@ -32243,7 +32243,7 @@
         </is>
       </c>
       <c r="E870" t="n">
-        <v>1449.234</v>
+        <v>1421.543</v>
       </c>
       <c r="F870" t="n">
         <v>0.0</v>
@@ -32252,7 +32252,7 @@
         <v>9.231</v>
       </c>
       <c r="H870" t="n">
-        <v>1449.234</v>
+        <v>1421.543</v>
       </c>
       <c r="I870" t="n">
         <v>0.0</v>
@@ -32280,7 +32280,7 @@
         </is>
       </c>
       <c r="E871" t="n">
-        <v>3183.051</v>
+        <v>3299.911</v>
       </c>
       <c r="F871" t="n">
         <v>4.289000000000001</v>
@@ -32289,7 +32289,7 @@
         <v>346.144</v>
       </c>
       <c r="H871" t="n">
-        <v>3183.051</v>
+        <v>3299.911</v>
       </c>
       <c r="I871" t="n">
         <v>0.0</v>
@@ -32354,7 +32354,7 @@
         </is>
       </c>
       <c r="E873" t="n">
-        <v>4400.668</v>
+        <v>4251.556</v>
       </c>
       <c r="F873" t="n">
         <v>0.0</v>
@@ -32363,7 +32363,7 @@
         <v>0.0</v>
       </c>
       <c r="H873" t="n">
-        <v>4400.668</v>
+        <v>4251.556</v>
       </c>
       <c r="I873" t="n">
         <v>0.0</v>
@@ -32428,7 +32428,7 @@
         </is>
       </c>
       <c r="E875" t="n">
-        <v>2393.083</v>
+        <v>8663.104</v>
       </c>
       <c r="F875" t="n">
         <v>0.0</v>
@@ -32437,10 +32437,10 @@
         <v>6.923</v>
       </c>
       <c r="H875" t="n">
-        <v>2393.083</v>
+        <v>2086.159</v>
       </c>
       <c r="I875" t="n">
-        <v>0.0</v>
+        <v>6576.945</v>
       </c>
     </row>
     <row r="876">
@@ -32465,7 +32465,7 @@
         </is>
       </c>
       <c r="E876" t="n">
-        <v>5305.399</v>
+        <v>5229.248</v>
       </c>
       <c r="F876" t="n">
         <v>0.0</v>
@@ -32474,7 +32474,7 @@
         <v>0.0</v>
       </c>
       <c r="H876" t="n">
-        <v>5305.399</v>
+        <v>5229.248</v>
       </c>
       <c r="I876" t="n">
         <v>0.0</v>
@@ -32576,7 +32576,7 @@
         </is>
       </c>
       <c r="E879" t="n">
-        <v>1455.2819999999997</v>
+        <v>2410.2856</v>
       </c>
       <c r="F879" t="n">
         <v>8.432</v>
@@ -32585,10 +32585,10 @@
         <v>62.128</v>
       </c>
       <c r="H879" t="n">
-        <v>1189.0169999999998</v>
+        <v>1281.3220000000001</v>
       </c>
       <c r="I879" t="n">
-        <v>266.265</v>
+        <v>1128.9636</v>
       </c>
     </row>
     <row r="880">
@@ -32650,7 +32650,7 @@
         </is>
       </c>
       <c r="E881" t="n">
-        <v>731.364</v>
+        <v>596.434</v>
       </c>
       <c r="F881" t="n">
         <v>0.0</v>
@@ -32659,7 +32659,7 @@
         <v>52.07</v>
       </c>
       <c r="H881" t="n">
-        <v>731.364</v>
+        <v>596.434</v>
       </c>
       <c r="I881" t="n">
         <v>0.0</v>
@@ -32687,7 +32687,7 @@
         </is>
       </c>
       <c r="E882" t="n">
-        <v>709.334</v>
+        <v>702.345</v>
       </c>
       <c r="F882" t="n">
         <v>0.399</v>
@@ -32696,7 +32696,7 @@
         <v>299.54999999999995</v>
       </c>
       <c r="H882" t="n">
-        <v>709.334</v>
+        <v>702.345</v>
       </c>
       <c r="I882" t="n">
         <v>0.0</v>
@@ -32724,7 +32724,7 @@
         </is>
       </c>
       <c r="E883" t="n">
-        <v>1703.441</v>
+        <v>1623.561</v>
       </c>
       <c r="F883" t="n">
         <v>0.0</v>
@@ -32733,7 +32733,7 @@
         <v>3.994</v>
       </c>
       <c r="H883" t="n">
-        <v>1703.441</v>
+        <v>1623.561</v>
       </c>
       <c r="I883" t="n">
         <v>0.0</v>
@@ -32761,7 +32761,7 @@
         </is>
       </c>
       <c r="E884" t="n">
-        <v>1181.329</v>
+        <v>1148.638</v>
       </c>
       <c r="F884" t="n">
         <v>1.33</v>
@@ -32770,7 +32770,7 @@
         <v>0.0</v>
       </c>
       <c r="H884" t="n">
-        <v>1181.329</v>
+        <v>1148.638</v>
       </c>
       <c r="I884" t="n">
         <v>0.0</v>
@@ -32798,7 +32798,7 @@
         </is>
       </c>
       <c r="E885" t="n">
-        <v>2464.075</v>
+        <v>2464.076</v>
       </c>
       <c r="F885" t="n">
         <v>0.0</v>
@@ -32807,7 +32807,7 @@
         <v>63.373</v>
       </c>
       <c r="H885" t="n">
-        <v>2464.075</v>
+        <v>2464.076</v>
       </c>
       <c r="I885" t="n">
         <v>0.0</v>
@@ -32835,7 +32835,7 @@
         </is>
       </c>
       <c r="E886" t="n">
-        <v>597.636</v>
+        <v>1100.5628000000002</v>
       </c>
       <c r="F886" t="n">
         <v>0.0</v>
@@ -32844,10 +32844,10 @@
         <v>42.602000000000004</v>
       </c>
       <c r="H886" t="n">
-        <v>597.636</v>
+        <v>358.571</v>
       </c>
       <c r="I886" t="n">
-        <v>0.0</v>
+        <v>741.9918</v>
       </c>
     </row>
     <row r="887">
@@ -33020,7 +33020,7 @@
         </is>
       </c>
       <c r="E891" t="n">
-        <v>2752.201</v>
+        <v>2728.182</v>
       </c>
       <c r="F891" t="n">
         <v>0.0</v>
@@ -33029,7 +33029,7 @@
         <v>240.19199999999998</v>
       </c>
       <c r="H891" t="n">
-        <v>2752.201</v>
+        <v>2728.182</v>
       </c>
       <c r="I891" t="n">
         <v>0.0</v>
@@ -33094,7 +33094,7 @@
         </is>
       </c>
       <c r="E893" t="n">
-        <v>10316.913</v>
+        <v>10307.573</v>
       </c>
       <c r="F893" t="n">
         <v>0.0</v>
@@ -33103,7 +33103,7 @@
         <v>81.621</v>
       </c>
       <c r="H893" t="n">
-        <v>10316.913</v>
+        <v>10307.573</v>
       </c>
       <c r="I893" t="n">
         <v>0.0</v>
@@ -33205,7 +33205,7 @@
         </is>
       </c>
       <c r="E896" t="n">
-        <v>2938.349</v>
+        <v>2906.323</v>
       </c>
       <c r="F896" t="n">
         <v>0.0</v>
@@ -33214,7 +33214,7 @@
         <v>60.047999999999995</v>
       </c>
       <c r="H896" t="n">
-        <v>2938.349</v>
+        <v>2906.323</v>
       </c>
       <c r="I896" t="n">
         <v>0.0</v>
@@ -33242,7 +33242,7 @@
         </is>
       </c>
       <c r="E897" t="n">
-        <v>2091.672</v>
+        <v>2031.624</v>
       </c>
       <c r="F897" t="n">
         <v>0.0</v>
@@ -33251,7 +33251,7 @@
         <v>170.97</v>
       </c>
       <c r="H897" t="n">
-        <v>2091.672</v>
+        <v>2031.624</v>
       </c>
       <c r="I897" t="n">
         <v>0.0</v>
@@ -33316,7 +33316,7 @@
         </is>
       </c>
       <c r="E899" t="n">
-        <v>285.56199999999995</v>
+        <v>274.886</v>
       </c>
       <c r="F899" t="n">
         <v>0.0</v>
@@ -33325,7 +33325,7 @@
         <v>0.0</v>
       </c>
       <c r="H899" t="n">
-        <v>285.56199999999995</v>
+        <v>274.886</v>
       </c>
       <c r="I899" t="n">
         <v>0.0</v>
@@ -33353,7 +33353,7 @@
         </is>
       </c>
       <c r="E900" t="n">
-        <v>105.531</v>
+        <v>2000.237</v>
       </c>
       <c r="F900" t="n">
         <v>1.213</v>
@@ -33365,7 +33365,7 @@
         <v>59.437</v>
       </c>
       <c r="I900" t="n">
-        <v>46.094</v>
+        <v>1940.8000000000002</v>
       </c>
     </row>
     <row r="901">
@@ -33390,7 +33390,7 @@
         </is>
       </c>
       <c r="E901" t="n">
-        <v>1054.097</v>
+        <v>1115.96</v>
       </c>
       <c r="F901" t="n">
         <v>0.607</v>
@@ -33399,7 +33399,7 @@
         <v>0.0</v>
       </c>
       <c r="H901" t="n">
-        <v>1054.097</v>
+        <v>1115.96</v>
       </c>
       <c r="I901" t="n">
         <v>0.0</v>
@@ -33464,7 +33464,7 @@
         </is>
       </c>
       <c r="E903" t="n">
-        <v>3383.306</v>
+        <v>3255.593</v>
       </c>
       <c r="F903" t="n">
         <v>66.098</v>
@@ -33473,7 +33473,7 @@
         <v>0.0</v>
       </c>
       <c r="H903" t="n">
-        <v>3383.306</v>
+        <v>3255.593</v>
       </c>
       <c r="I903" t="n">
         <v>0.0</v>
@@ -33649,7 +33649,7 @@
         </is>
       </c>
       <c r="E908" t="n">
-        <v>1422.983</v>
+        <v>1385.953</v>
       </c>
       <c r="F908" t="n">
         <v>0.0</v>
@@ -33658,7 +33658,7 @@
         <v>0.0</v>
       </c>
       <c r="H908" t="n">
-        <v>1422.983</v>
+        <v>1385.953</v>
       </c>
       <c r="I908" t="n">
         <v>0.0</v>
@@ -33686,7 +33686,7 @@
         </is>
       </c>
       <c r="E909" t="n">
-        <v>2346.835</v>
+        <v>2345.5899999999997</v>
       </c>
       <c r="F909" t="n">
         <v>0.622</v>
@@ -33695,7 +33695,7 @@
         <v>1.245</v>
       </c>
       <c r="H909" t="n">
-        <v>2346.835</v>
+        <v>2345.5899999999997</v>
       </c>
       <c r="I909" t="n">
         <v>0.0</v>
@@ -33723,7 +33723,7 @@
         </is>
       </c>
       <c r="E910" t="n">
-        <v>1415.195</v>
+        <v>1414.573</v>
       </c>
       <c r="F910" t="n">
         <v>0.622</v>
@@ -33732,7 +33732,7 @@
         <v>0.0</v>
       </c>
       <c r="H910" t="n">
-        <v>1415.195</v>
+        <v>1414.573</v>
       </c>
       <c r="I910" t="n">
         <v>0.0</v>
@@ -33797,7 +33797,7 @@
         </is>
       </c>
       <c r="E912" t="n">
-        <v>3528.363</v>
+        <v>3232.128</v>
       </c>
       <c r="F912" t="n">
         <v>0.0</v>
@@ -33806,7 +33806,7 @@
         <v>0.0</v>
       </c>
       <c r="H912" t="n">
-        <v>3528.363</v>
+        <v>3232.128</v>
       </c>
       <c r="I912" t="n">
         <v>0.0</v>
@@ -34093,7 +34093,7 @@
         </is>
       </c>
       <c r="E920" t="n">
-        <v>4725.9</v>
+        <v>4729.054999999999</v>
       </c>
       <c r="F920" t="n">
         <v>0.10500000000000001</v>
@@ -34102,7 +34102,7 @@
         <v>51.757999999999996</v>
       </c>
       <c r="H920" t="n">
-        <v>4725.9</v>
+        <v>4729.054999999999</v>
       </c>
       <c r="I920" t="n">
         <v>0.0</v>
@@ -34130,7 +34130,7 @@
         </is>
       </c>
       <c r="E921" t="n">
-        <v>934.807</v>
+        <v>931.967</v>
       </c>
       <c r="F921" t="n">
         <v>0.0</v>
@@ -34139,7 +34139,7 @@
         <v>0.0</v>
       </c>
       <c r="H921" t="n">
-        <v>934.807</v>
+        <v>931.967</v>
       </c>
       <c r="I921" t="n">
         <v>0.0</v>
@@ -34167,7 +34167,7 @@
         </is>
       </c>
       <c r="E922" t="n">
-        <v>2905.391</v>
+        <v>2875.394</v>
       </c>
       <c r="F922" t="n">
         <v>0.0</v>
@@ -34176,7 +34176,7 @@
         <v>11.539000000000001</v>
       </c>
       <c r="H922" t="n">
-        <v>2905.391</v>
+        <v>2875.394</v>
       </c>
       <c r="I922" t="n">
         <v>0.0</v>
@@ -34278,7 +34278,7 @@
         </is>
       </c>
       <c r="E925" t="n">
-        <v>3696.933</v>
+        <v>3602.32</v>
       </c>
       <c r="F925" t="n">
         <v>0.0</v>
@@ -34287,7 +34287,7 @@
         <v>2.3080000000000003</v>
       </c>
       <c r="H925" t="n">
-        <v>3696.933</v>
+        <v>3602.32</v>
       </c>
       <c r="I925" t="n">
         <v>0.0</v>
@@ -34500,7 +34500,7 @@
         </is>
       </c>
       <c r="E931" t="n">
-        <v>9409.364000000001</v>
+        <v>9381.108</v>
       </c>
       <c r="F931" t="n">
         <v>1.6280000000000001</v>
@@ -34509,7 +34509,7 @@
         <v>128.102</v>
       </c>
       <c r="H931" t="n">
-        <v>9409.364000000001</v>
+        <v>9381.108</v>
       </c>
       <c r="I931" t="n">
         <v>0.0</v>
@@ -34574,7 +34574,7 @@
         </is>
       </c>
       <c r="E933" t="n">
-        <v>4421.548</v>
+        <v>4384.63</v>
       </c>
       <c r="F933" t="n">
         <v>0.0</v>
@@ -34583,7 +34583,7 @@
         <v>2.3080000000000003</v>
       </c>
       <c r="H933" t="n">
-        <v>4421.548</v>
+        <v>4384.63</v>
       </c>
       <c r="I933" t="n">
         <v>0.0</v>
@@ -34648,7 +34648,7 @@
         </is>
       </c>
       <c r="E935" t="n">
-        <v>1324.816</v>
+        <v>1273.338</v>
       </c>
       <c r="F935" t="n">
         <v>0.0</v>
@@ -34657,7 +34657,7 @@
         <v>1.183</v>
       </c>
       <c r="H935" t="n">
-        <v>1324.816</v>
+        <v>1273.338</v>
       </c>
       <c r="I935" t="n">
         <v>0.0</v>
@@ -34722,7 +34722,7 @@
         </is>
       </c>
       <c r="E937" t="n">
-        <v>560.0699999999999</v>
+        <v>549.669</v>
       </c>
       <c r="F937" t="n">
         <v>8.801</v>
@@ -34731,7 +34731,7 @@
         <v>0.0</v>
       </c>
       <c r="H937" t="n">
-        <v>560.0699999999999</v>
+        <v>549.669</v>
       </c>
       <c r="I937" t="n">
         <v>0.0</v>
@@ -34759,7 +34759,7 @@
         </is>
       </c>
       <c r="E938" t="n">
-        <v>25.921</v>
+        <v>25.66</v>
       </c>
       <c r="F938" t="n">
         <v>0.262</v>
@@ -34768,7 +34768,7 @@
         <v>0.0</v>
       </c>
       <c r="H938" t="n">
-        <v>25.921</v>
+        <v>25.66</v>
       </c>
       <c r="I938" t="n">
         <v>0.0</v>
@@ -34796,7 +34796,7 @@
         </is>
       </c>
       <c r="E939" t="n">
-        <v>30.768</v>
+        <v>7.986</v>
       </c>
       <c r="F939" t="n">
         <v>0.525</v>
@@ -34805,7 +34805,7 @@
         <v>0.0</v>
       </c>
       <c r="H939" t="n">
-        <v>30.768</v>
+        <v>7.986</v>
       </c>
       <c r="I939" t="n">
         <v>0.0</v>
@@ -35018,7 +35018,7 @@
         </is>
       </c>
       <c r="E945" t="n">
-        <v>2547.9829999999997</v>
+        <v>2530.433</v>
       </c>
       <c r="F945" t="n">
         <v>57.22</v>
@@ -35027,7 +35027,7 @@
         <v>0.0</v>
       </c>
       <c r="H945" t="n">
-        <v>2547.9829999999997</v>
+        <v>2530.433</v>
       </c>
       <c r="I945" t="n">
         <v>0.0</v>
@@ -35055,7 +35055,7 @@
         </is>
       </c>
       <c r="E946" t="n">
-        <v>1145.662</v>
+        <v>1139.4470000000001</v>
       </c>
       <c r="F946" t="n">
         <v>0.546</v>
@@ -35064,7 +35064,7 @@
         <v>0.0</v>
       </c>
       <c r="H946" t="n">
-        <v>1145.662</v>
+        <v>1139.4470000000001</v>
       </c>
       <c r="I946" t="n">
         <v>0.0</v>
@@ -35092,7 +35092,7 @@
         </is>
       </c>
       <c r="E947" t="n">
-        <v>1794.3029999999999</v>
+        <v>1654.896</v>
       </c>
       <c r="F947" t="n">
         <v>0.0</v>
@@ -35101,7 +35101,7 @@
         <v>0.0</v>
       </c>
       <c r="H947" t="n">
-        <v>1794.3029999999999</v>
+        <v>1654.896</v>
       </c>
       <c r="I947" t="n">
         <v>0.0</v>
@@ -35129,7 +35129,7 @@
         </is>
       </c>
       <c r="E948" t="n">
-        <v>1899.982</v>
+        <v>1765.073</v>
       </c>
       <c r="F948" t="n">
         <v>0.0</v>
@@ -35138,7 +35138,7 @@
         <v>0.0</v>
       </c>
       <c r="H948" t="n">
-        <v>1899.982</v>
+        <v>1765.073</v>
       </c>
       <c r="I948" t="n">
         <v>0.0</v>
@@ -35166,7 +35166,7 @@
         </is>
       </c>
       <c r="E949" t="n">
-        <v>5614.0</v>
+        <v>5576.0</v>
       </c>
       <c r="F949" t="n">
         <v>0.0</v>
@@ -35175,7 +35175,7 @@
         <v>180.0</v>
       </c>
       <c r="H949" t="n">
-        <v>5614.0</v>
+        <v>5576.0</v>
       </c>
       <c r="I949" t="n">
         <v>0.0</v>
@@ -35647,7 +35647,7 @@
         </is>
       </c>
       <c r="E962" t="n">
-        <v>91.985</v>
+        <v>90.483</v>
       </c>
       <c r="F962" t="n">
         <v>0.0</v>
@@ -35656,7 +35656,7 @@
         <v>0.0</v>
       </c>
       <c r="H962" t="n">
-        <v>91.985</v>
+        <v>90.483</v>
       </c>
       <c r="I962" t="n">
         <v>0.0</v>
@@ -36239,7 +36239,7 @@
         </is>
       </c>
       <c r="E978" t="n">
-        <v>311.033</v>
+        <v>1514.333</v>
       </c>
       <c r="F978" t="n">
         <v>14.7</v>
@@ -36248,10 +36248,10 @@
         <v>9.799999999999999</v>
       </c>
       <c r="H978" t="n">
-        <v>311.033</v>
+        <v>312.433</v>
       </c>
       <c r="I978" t="n">
-        <v>0.0</v>
+        <v>1201.9</v>
       </c>
     </row>
     <row r="979">
@@ -36276,7 +36276,7 @@
         </is>
       </c>
       <c r="E979" t="n">
-        <v>2652.967</v>
+        <v>2568.03</v>
       </c>
       <c r="F979" t="n">
         <v>30.335</v>
@@ -36285,7 +36285,7 @@
         <v>0.867</v>
       </c>
       <c r="H979" t="n">
-        <v>2652.967</v>
+        <v>2568.03</v>
       </c>
       <c r="I979" t="n">
         <v>0.0</v>
@@ -36313,7 +36313,7 @@
         </is>
       </c>
       <c r="E980" t="n">
-        <v>4476.788</v>
+        <v>4412.018</v>
       </c>
       <c r="F980" t="n">
         <v>15.467</v>
@@ -36322,7 +36322,7 @@
         <v>8.7</v>
       </c>
       <c r="H980" t="n">
-        <v>4476.788</v>
+        <v>4412.018</v>
       </c>
       <c r="I980" t="n">
         <v>0.0</v>
@@ -37349,7 +37349,7 @@
         </is>
       </c>
       <c r="E1008" t="n">
-        <v>11550.575</v>
+        <v>11550.576</v>
       </c>
       <c r="F1008" t="n">
         <v>0.0</v>
@@ -37358,7 +37358,7 @@
         <v>0.0</v>
       </c>
       <c r="H1008" t="n">
-        <v>11550.575</v>
+        <v>11550.576</v>
       </c>
       <c r="I1008" t="n">
         <v>0.0</v>
@@ -37571,7 +37571,7 @@
         </is>
       </c>
       <c r="E1014" t="n">
-        <v>6071.712</v>
+        <v>6043.91</v>
       </c>
       <c r="F1014" t="n">
         <v>68.241</v>
@@ -37580,7 +37580,7 @@
         <v>25.169</v>
       </c>
       <c r="H1014" t="n">
-        <v>6071.712</v>
+        <v>6043.91</v>
       </c>
       <c r="I1014" t="n">
         <v>0.0</v>
@@ -37867,7 +37867,7 @@
         </is>
       </c>
       <c r="E1022" t="n">
-        <v>5598.05</v>
+        <v>5485.524</v>
       </c>
       <c r="F1022" t="n">
         <v>0.0</v>
@@ -37876,7 +37876,7 @@
         <v>0.0</v>
       </c>
       <c r="H1022" t="n">
-        <v>5598.05</v>
+        <v>5485.524</v>
       </c>
       <c r="I1022" t="n">
         <v>0.0</v>
@@ -37904,7 +37904,7 @@
         </is>
       </c>
       <c r="E1023" t="n">
-        <v>5424.678</v>
+        <v>5342.001</v>
       </c>
       <c r="F1023" t="n">
         <v>0.8</v>
@@ -37913,7 +37913,7 @@
         <v>800.1</v>
       </c>
       <c r="H1023" t="n">
-        <v>5424.678</v>
+        <v>5342.001</v>
       </c>
       <c r="I1023" t="n">
         <v>0.0</v>
@@ -38052,7 +38052,7 @@
         </is>
       </c>
       <c r="E1027" t="n">
-        <v>5438.859</v>
+        <v>5438.86</v>
       </c>
       <c r="F1027" t="n">
         <v>0.0</v>
@@ -38061,7 +38061,7 @@
         <v>0.0</v>
       </c>
       <c r="H1027" t="n">
-        <v>5438.859</v>
+        <v>5438.86</v>
       </c>
       <c r="I1027" t="n">
         <v>0.0</v>
@@ -38089,7 +38089,7 @@
         </is>
       </c>
       <c r="E1028" t="n">
-        <v>3318.3998</v>
+        <v>4067.493</v>
       </c>
       <c r="F1028" t="n">
         <v>9.763000000000002</v>
@@ -38098,10 +38098,10 @@
         <v>10.651000000000002</v>
       </c>
       <c r="H1028" t="n">
-        <v>2647.4120000000003</v>
+        <v>2647.413</v>
       </c>
       <c r="I1028" t="n">
-        <v>670.9878</v>
+        <v>1420.08</v>
       </c>
     </row>
     <row r="1029">
@@ -38126,7 +38126,7 @@
         </is>
       </c>
       <c r="E1029" t="n">
-        <v>7030.579</v>
+        <v>6989.16</v>
       </c>
       <c r="F1029" t="n">
         <v>1.183</v>
@@ -38135,7 +38135,7 @@
         <v>1.479</v>
       </c>
       <c r="H1029" t="n">
-        <v>7030.579</v>
+        <v>6989.16</v>
       </c>
       <c r="I1029" t="n">
         <v>0.0</v>
@@ -38163,7 +38163,7 @@
         </is>
       </c>
       <c r="E1030" t="n">
-        <v>5095.391</v>
+        <v>4950.017</v>
       </c>
       <c r="F1030" t="n">
         <v>0.0</v>
@@ -38172,7 +38172,7 @@
         <v>6.923</v>
       </c>
       <c r="H1030" t="n">
-        <v>5095.391</v>
+        <v>4950.017</v>
       </c>
       <c r="I1030" t="n">
         <v>0.0</v>
@@ -38607,7 +38607,7 @@
         </is>
       </c>
       <c r="E1042" t="n">
-        <v>93.859</v>
+        <v>90.664</v>
       </c>
       <c r="F1042" t="n">
         <v>0.0</v>
@@ -38616,7 +38616,7 @@
         <v>694.956</v>
       </c>
       <c r="H1042" t="n">
-        <v>93.859</v>
+        <v>90.664</v>
       </c>
       <c r="I1042" t="n">
         <v>0.0</v>
@@ -38644,7 +38644,7 @@
         </is>
       </c>
       <c r="E1043" t="n">
-        <v>1093.829</v>
+        <v>1266.9266</v>
       </c>
       <c r="F1043" t="n">
         <v>0.0</v>
@@ -38653,10 +38653,10 @@
         <v>23.077</v>
       </c>
       <c r="H1043" t="n">
-        <v>1093.829</v>
+        <v>810.002</v>
       </c>
       <c r="I1043" t="n">
-        <v>0.0</v>
+        <v>456.9246</v>
       </c>
     </row>
     <row r="1044">
@@ -38903,7 +38903,7 @@
         </is>
       </c>
       <c r="E1050" t="n">
-        <v>929.733</v>
+        <v>904.529</v>
       </c>
       <c r="F1050" t="n">
         <v>2.8</v>
@@ -38912,7 +38912,7 @@
         <v>0.0</v>
       </c>
       <c r="H1050" t="n">
-        <v>929.733</v>
+        <v>904.529</v>
       </c>
       <c r="I1050" t="n">
         <v>0.0</v>
@@ -38977,7 +38977,7 @@
         </is>
       </c>
       <c r="E1052" t="n">
-        <v>2113.18</v>
+        <v>2113.154</v>
       </c>
       <c r="F1052" t="n">
         <v>0.0</v>
@@ -38986,7 +38986,7 @@
         <v>75.97</v>
       </c>
       <c r="H1052" t="n">
-        <v>2113.18</v>
+        <v>2113.154</v>
       </c>
       <c r="I1052" t="n">
         <v>0.0</v>
@@ -39088,7 +39088,7 @@
         </is>
       </c>
       <c r="E1055" t="n">
-        <v>5268.212</v>
+        <v>5260.205</v>
       </c>
       <c r="F1055" t="n">
         <v>0.0</v>
@@ -39097,7 +39097,7 @@
         <v>0.0</v>
       </c>
       <c r="H1055" t="n">
-        <v>5268.212</v>
+        <v>5260.205</v>
       </c>
       <c r="I1055" t="n">
         <v>0.0</v>
@@ -39125,7 +39125,7 @@
         </is>
       </c>
       <c r="E1056" t="n">
-        <v>4493.695</v>
+        <v>4273.676</v>
       </c>
       <c r="F1056" t="n">
         <v>0.0</v>
@@ -39134,7 +39134,7 @@
         <v>0.0</v>
       </c>
       <c r="H1056" t="n">
-        <v>4493.695</v>
+        <v>4273.676</v>
       </c>
       <c r="I1056" t="n">
         <v>0.0</v>
@@ -39162,7 +39162,7 @@
         </is>
       </c>
       <c r="E1057" t="n">
-        <v>4573.009999999999</v>
+        <v>4566.339</v>
       </c>
       <c r="F1057" t="n">
         <v>1.213</v>
@@ -39171,7 +39171,7 @@
         <v>0.0</v>
       </c>
       <c r="H1057" t="n">
-        <v>4573.009999999999</v>
+        <v>4566.339</v>
       </c>
       <c r="I1057" t="n">
         <v>0.0</v>
@@ -39199,7 +39199,7 @@
         </is>
       </c>
       <c r="E1058" t="n">
-        <v>2275.588</v>
+        <v>6171.744000000001</v>
       </c>
       <c r="F1058" t="n">
         <v>2.426</v>
@@ -39211,7 +39211,7 @@
         <v>388.16</v>
       </c>
       <c r="I1058" t="n">
-        <v>1887.428</v>
+        <v>5783.584000000001</v>
       </c>
     </row>
     <row r="1059">
@@ -39236,7 +39236,7 @@
         </is>
       </c>
       <c r="E1059" t="n">
-        <v>1870.911</v>
+        <v>1835.5349999999999</v>
       </c>
       <c r="F1059" t="n">
         <v>547.487</v>
@@ -39245,7 +39245,7 @@
         <v>47.608</v>
       </c>
       <c r="H1059" t="n">
-        <v>1870.911</v>
+        <v>1835.5349999999999</v>
       </c>
       <c r="I1059" t="n">
         <v>0.0</v>
@@ -39273,7 +39273,7 @@
         </is>
       </c>
       <c r="E1060" t="n">
-        <v>6031.2843</v>
+        <v>5273.5289999999995</v>
       </c>
       <c r="F1060" t="n">
         <v>916.7760000000001</v>
@@ -39282,10 +39282,10 @@
         <v>15.869000000000002</v>
       </c>
       <c r="H1060" t="n">
-        <v>5233.857</v>
+        <v>5273.5289999999995</v>
       </c>
       <c r="I1060" t="n">
-        <v>797.4273</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1061">
@@ -39310,7 +39310,7 @@
         </is>
       </c>
       <c r="E1061" t="n">
-        <v>2896.1310000000003</v>
+        <v>3019.119</v>
       </c>
       <c r="F1061" t="n">
         <v>845.035</v>
@@ -39319,7 +39319,7 @@
         <v>0.0</v>
       </c>
       <c r="H1061" t="n">
-        <v>2896.1310000000003</v>
+        <v>3019.119</v>
       </c>
       <c r="I1061" t="n">
         <v>0.0</v>
@@ -39347,7 +39347,7 @@
         </is>
       </c>
       <c r="E1062" t="n">
-        <v>14059.4424</v>
+        <v>10548.384</v>
       </c>
       <c r="F1062" t="n">
         <v>1450.7069999999999</v>
@@ -39356,10 +39356,10 @@
         <v>0.0</v>
       </c>
       <c r="H1062" t="n">
-        <v>10258.769</v>
+        <v>10548.384</v>
       </c>
       <c r="I1062" t="n">
-        <v>3800.6733999999997</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1063">
@@ -39421,7 +39421,7 @@
         </is>
       </c>
       <c r="E1064" t="n">
-        <v>10312.331</v>
+        <v>10181.741</v>
       </c>
       <c r="F1064" t="n">
         <v>2221.688</v>
@@ -39430,7 +39430,7 @@
         <v>0.0</v>
       </c>
       <c r="H1064" t="n">
-        <v>10312.331</v>
+        <v>10181.741</v>
       </c>
       <c r="I1064" t="n">
         <v>0.0</v>
@@ -39495,7 +39495,7 @@
         </is>
       </c>
       <c r="E1066" t="n">
-        <v>6232.3036</v>
+        <v>4554.135</v>
       </c>
       <c r="F1066" t="n">
         <v>929.0070000000001</v>
@@ -39504,10 +39504,10 @@
         <v>0.0</v>
       </c>
       <c r="H1066" t="n">
-        <v>4518.43</v>
+        <v>4554.135</v>
       </c>
       <c r="I1066" t="n">
-        <v>1713.8736</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1067">
@@ -39532,7 +39532,7 @@
         </is>
       </c>
       <c r="E1067" t="n">
-        <v>7285.811</v>
+        <v>15001.0232</v>
       </c>
       <c r="F1067" t="n">
         <v>0.0</v>
@@ -39544,7 +39544,7 @@
         <v>7285.811</v>
       </c>
       <c r="I1067" t="n">
-        <v>0.0</v>
+        <v>7715.2122</v>
       </c>
     </row>
     <row r="1068">
@@ -39606,7 +39606,7 @@
         </is>
       </c>
       <c r="E1069" t="n">
-        <v>25862.5042</v>
+        <v>22331.607</v>
       </c>
       <c r="F1069" t="n">
         <v>3020.766</v>
@@ -39615,10 +39615,10 @@
         <v>3.967</v>
       </c>
       <c r="H1069" t="n">
-        <v>21006.529</v>
+        <v>22331.607</v>
       </c>
       <c r="I1069" t="n">
-        <v>4855.9752</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1070">
@@ -39643,7 +39643,7 @@
         </is>
       </c>
       <c r="E1070" t="n">
-        <v>24238.876500000002</v>
+        <v>21069.005</v>
       </c>
       <c r="F1070" t="n">
         <v>1889.427</v>
@@ -39652,10 +39652,10 @@
         <v>0.0</v>
       </c>
       <c r="H1070" t="n">
-        <v>20886.508</v>
+        <v>21069.005</v>
       </c>
       <c r="I1070" t="n">
-        <v>3352.3685</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1071">
@@ -39754,7 +39754,7 @@
         </is>
       </c>
       <c r="E1073" t="n">
-        <v>5786.8</v>
+        <v>5602.8</v>
       </c>
       <c r="F1073" t="n">
         <v>0.0</v>
@@ -39763,7 +39763,7 @@
         <v>4.83</v>
       </c>
       <c r="H1073" t="n">
-        <v>5786.8</v>
+        <v>5602.8</v>
       </c>
       <c r="I1073" t="n">
         <v>0.0</v>
@@ -39791,7 +39791,7 @@
         </is>
       </c>
       <c r="E1074" t="n">
-        <v>1239.854</v>
+        <v>1093.675</v>
       </c>
       <c r="F1074" t="n">
         <v>0.0</v>
@@ -39800,7 +39800,7 @@
         <v>0.0</v>
       </c>
       <c r="H1074" t="n">
-        <v>1239.854</v>
+        <v>1093.675</v>
       </c>
       <c r="I1074" t="n">
         <v>0.0</v>
@@ -39828,7 +39828,7 @@
         </is>
       </c>
       <c r="E1075" t="n">
-        <v>1680.0</v>
+        <v>1584.0</v>
       </c>
       <c r="F1075" t="n">
         <v>0.0</v>
@@ -39837,7 +39837,7 @@
         <v>0.0</v>
       </c>
       <c r="H1075" t="n">
-        <v>1680.0</v>
+        <v>1584.0</v>
       </c>
       <c r="I1075" t="n">
         <v>0.0</v>
@@ -39865,7 +39865,7 @@
         </is>
       </c>
       <c r="E1076" t="n">
-        <v>5614.641</v>
+        <v>4991.581</v>
       </c>
       <c r="F1076" t="n">
         <v>484.602</v>
@@ -39874,7 +39874,7 @@
         <v>0.0</v>
       </c>
       <c r="H1076" t="n">
-        <v>5614.641</v>
+        <v>4991.581</v>
       </c>
       <c r="I1076" t="n">
         <v>0.0</v>
@@ -40124,7 +40124,7 @@
         </is>
       </c>
       <c r="E1083" t="n">
-        <v>1821.297</v>
+        <v>1819.273</v>
       </c>
       <c r="F1083" t="n">
         <v>0.0</v>
@@ -40133,7 +40133,7 @@
         <v>0.0</v>
       </c>
       <c r="H1083" t="n">
-        <v>1821.297</v>
+        <v>1819.273</v>
       </c>
       <c r="I1083" t="n">
         <v>0.0</v>
@@ -40198,7 +40198,7 @@
         </is>
       </c>
       <c r="E1085" t="n">
-        <v>290.691</v>
+        <v>234.646</v>
       </c>
       <c r="F1085" t="n">
         <v>0.0</v>
@@ -40207,7 +40207,7 @@
         <v>0.0</v>
       </c>
       <c r="H1085" t="n">
-        <v>290.691</v>
+        <v>234.646</v>
       </c>
       <c r="I1085" t="n">
         <v>0.0</v>
@@ -40272,7 +40272,7 @@
         </is>
       </c>
       <c r="E1087" t="n">
-        <v>2145.167</v>
+        <v>2143.142</v>
       </c>
       <c r="F1087" t="n">
         <v>0.0</v>
@@ -40281,7 +40281,7 @@
         <v>0.0</v>
       </c>
       <c r="H1087" t="n">
-        <v>2145.167</v>
+        <v>2143.142</v>
       </c>
       <c r="I1087" t="n">
         <v>0.0</v>
@@ -40309,7 +40309,7 @@
         </is>
       </c>
       <c r="E1088" t="n">
-        <v>2197.122</v>
+        <v>2193.123</v>
       </c>
       <c r="F1088" t="n">
         <v>0.0</v>
@@ -40318,7 +40318,7 @@
         <v>0.0</v>
       </c>
       <c r="H1088" t="n">
-        <v>2197.122</v>
+        <v>2193.123</v>
       </c>
       <c r="I1088" t="n">
         <v>0.0</v>
@@ -40383,7 +40383,7 @@
         </is>
       </c>
       <c r="E1090" t="n">
-        <v>11.915099999999999</v>
+        <v>10.5171</v>
       </c>
       <c r="F1090" t="n">
         <v>0.0</v>
@@ -40392,7 +40392,7 @@
         <v>1.399</v>
       </c>
       <c r="H1090" t="n">
-        <v>5.614</v>
+        <v>4.216</v>
       </c>
       <c r="I1090" t="n">
         <v>6.3011</v>
@@ -40420,7 +40420,7 @@
         </is>
       </c>
       <c r="E1091" t="n">
-        <v>9.8041</v>
+        <v>8.4061</v>
       </c>
       <c r="F1091" t="n">
         <v>0.0</v>
@@ -40429,7 +40429,7 @@
         <v>31.505</v>
       </c>
       <c r="H1091" t="n">
-        <v>3.503</v>
+        <v>2.105</v>
       </c>
       <c r="I1091" t="n">
         <v>6.3011</v>
@@ -40531,7 +40531,7 @@
         </is>
       </c>
       <c r="E1094" t="n">
-        <v>296.856</v>
+        <v>185.535</v>
       </c>
       <c r="F1094" t="n">
         <v>0.0</v>
@@ -40540,7 +40540,7 @@
         <v>0.0</v>
       </c>
       <c r="H1094" t="n">
-        <v>296.856</v>
+        <v>185.535</v>
       </c>
       <c r="I1094" t="n">
         <v>0.0</v>
@@ -40605,7 +40605,7 @@
         </is>
       </c>
       <c r="E1096" t="n">
-        <v>749.562</v>
+        <v>583.816</v>
       </c>
       <c r="F1096" t="n">
         <v>0.0</v>
@@ -40614,7 +40614,7 @@
         <v>2.474</v>
       </c>
       <c r="H1096" t="n">
-        <v>749.562</v>
+        <v>583.816</v>
       </c>
       <c r="I1096" t="n">
         <v>0.0</v>
@@ -40975,7 +40975,7 @@
         </is>
       </c>
       <c r="E1106" t="n">
-        <v>3865.5</v>
+        <v>3541.5</v>
       </c>
       <c r="F1106" t="n">
         <v>0.0</v>
@@ -40984,7 +40984,7 @@
         <v>0.0</v>
       </c>
       <c r="H1106" t="n">
-        <v>3865.5</v>
+        <v>3541.5</v>
       </c>
       <c r="I1106" t="n">
         <v>0.0</v>
@@ -41012,7 +41012,7 @@
         </is>
       </c>
       <c r="E1107" t="n">
-        <v>640.0</v>
+        <v>592.0</v>
       </c>
       <c r="F1107" t="n">
         <v>0.0</v>
@@ -41021,7 +41021,7 @@
         <v>0.0</v>
       </c>
       <c r="H1107" t="n">
-        <v>640.0</v>
+        <v>592.0</v>
       </c>
       <c r="I1107" t="n">
         <v>0.0</v>
@@ -41086,7 +41086,7 @@
         </is>
       </c>
       <c r="E1109" t="n">
-        <v>23535.959</v>
+        <v>23031.977</v>
       </c>
       <c r="F1109" t="n">
         <v>0.0</v>
@@ -41095,7 +41095,7 @@
         <v>0.0</v>
       </c>
       <c r="H1109" t="n">
-        <v>23535.959</v>
+        <v>23031.977</v>
       </c>
       <c r="I1109" t="n">
         <v>0.0</v>
@@ -41160,7 +41160,7 @@
         </is>
       </c>
       <c r="E1111" t="n">
-        <v>2576.932</v>
+        <v>2315.24</v>
       </c>
       <c r="F1111" t="n">
         <v>5.452</v>
@@ -41169,7 +41169,7 @@
         <v>259.87399999999997</v>
       </c>
       <c r="H1111" t="n">
-        <v>2576.932</v>
+        <v>2315.24</v>
       </c>
       <c r="I1111" t="n">
         <v>0.0</v>
@@ -41197,7 +41197,7 @@
         </is>
       </c>
       <c r="E1112" t="n">
-        <v>2130.604</v>
+        <v>2116.585</v>
       </c>
       <c r="F1112" t="n">
         <v>0.0</v>
@@ -41206,7 +41206,7 @@
         <v>0.0</v>
       </c>
       <c r="H1112" t="n">
-        <v>2130.604</v>
+        <v>2116.585</v>
       </c>
       <c r="I1112" t="n">
         <v>0.0</v>
@@ -41234,7 +41234,7 @@
         </is>
       </c>
       <c r="E1113" t="n">
-        <v>2222.268</v>
+        <v>2082.346</v>
       </c>
       <c r="F1113" t="n">
         <v>0.09000000000000001</v>
@@ -41243,10 +41243,10 @@
         <v>0.0</v>
       </c>
       <c r="H1113" t="n">
-        <v>2096.904</v>
+        <v>2082.346</v>
       </c>
       <c r="I1113" t="n">
-        <v>125.364</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1114">
@@ -41308,7 +41308,7 @@
         </is>
       </c>
       <c r="E1115" t="n">
-        <v>1395.1470000000002</v>
+        <v>1388.6930000000002</v>
       </c>
       <c r="F1115" t="n">
         <v>0.0</v>
@@ -41317,7 +41317,7 @@
         <v>0.0</v>
       </c>
       <c r="H1115" t="n">
-        <v>1395.1470000000002</v>
+        <v>1388.6930000000002</v>
       </c>
       <c r="I1115" t="n">
         <v>0.0</v>
@@ -41345,7 +41345,7 @@
         </is>
       </c>
       <c r="E1116" t="n">
-        <v>2895.3142</v>
+        <v>1722.966</v>
       </c>
       <c r="F1116" t="n">
         <v>0.42000000000000004</v>
@@ -41354,10 +41354,10 @@
         <v>0.0</v>
       </c>
       <c r="H1116" t="n">
-        <v>1723.807</v>
+        <v>1722.966</v>
       </c>
       <c r="I1116" t="n">
-        <v>1171.5072</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1117">
@@ -41382,7 +41382,7 @@
         </is>
       </c>
       <c r="E1117" t="n">
-        <v>3543.5562</v>
+        <v>2372.049</v>
       </c>
       <c r="F1117" t="n">
         <v>0.421</v>
@@ -41394,7 +41394,7 @@
         <v>2372.049</v>
       </c>
       <c r="I1117" t="n">
-        <v>1171.5072</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1118">
@@ -41419,7 +41419,7 @@
         </is>
       </c>
       <c r="E1118" t="n">
-        <v>999.571</v>
+        <v>489.48199999999997</v>
       </c>
       <c r="F1118" t="n">
         <v>0.0</v>
@@ -41428,10 +41428,10 @@
         <v>0.0</v>
       </c>
       <c r="H1118" t="n">
-        <v>562.351</v>
+        <v>489.48199999999997</v>
       </c>
       <c r="I1118" t="n">
-        <v>437.22</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1119">
@@ -41493,7 +41493,7 @@
         </is>
       </c>
       <c r="E1120" t="n">
-        <v>7005.436</v>
+        <v>6943.83</v>
       </c>
       <c r="F1120" t="n">
         <v>0.0</v>
@@ -41502,7 +41502,7 @@
         <v>0.0</v>
       </c>
       <c r="H1120" t="n">
-        <v>7005.436</v>
+        <v>6943.83</v>
       </c>
       <c r="I1120" t="n">
         <v>0.0</v>
@@ -41530,7 +41530,7 @@
         </is>
       </c>
       <c r="E1121" t="n">
-        <v>946.468</v>
+        <v>812.059</v>
       </c>
       <c r="F1121" t="n">
         <v>0.0</v>
@@ -41539,7 +41539,7 @@
         <v>0.0</v>
       </c>
       <c r="H1121" t="n">
-        <v>946.468</v>
+        <v>812.059</v>
       </c>
       <c r="I1121" t="n">
         <v>0.0</v>
@@ -41567,7 +41567,7 @@
         </is>
       </c>
       <c r="E1122" t="n">
-        <v>4452.597</v>
+        <v>4382.2</v>
       </c>
       <c r="F1122" t="n">
         <v>0.0</v>
@@ -41576,7 +41576,7 @@
         <v>0.0</v>
       </c>
       <c r="H1122" t="n">
-        <v>4452.597</v>
+        <v>4382.2</v>
       </c>
       <c r="I1122" t="n">
         <v>0.0</v>
@@ -41604,7 +41604,7 @@
         </is>
       </c>
       <c r="E1123" t="n">
-        <v>7894.316</v>
+        <v>7788.708</v>
       </c>
       <c r="F1123" t="n">
         <v>0.0</v>
@@ -41613,7 +41613,7 @@
         <v>0.0</v>
       </c>
       <c r="H1123" t="n">
-        <v>7894.316</v>
+        <v>7788.708</v>
       </c>
       <c r="I1123" t="n">
         <v>0.0</v>
@@ -41641,7 +41641,7 @@
         </is>
       </c>
       <c r="E1124" t="n">
-        <v>11761.599999999999</v>
+        <v>11626.4</v>
       </c>
       <c r="F1124" t="n">
         <v>6.4</v>
@@ -41650,7 +41650,7 @@
         <v>0.0</v>
       </c>
       <c r="H1124" t="n">
-        <v>11761.599999999999</v>
+        <v>11626.4</v>
       </c>
       <c r="I1124" t="n">
         <v>0.0</v>
@@ -41715,7 +41715,7 @@
         </is>
       </c>
       <c r="E1126" t="n">
-        <v>1491.172</v>
+        <v>1489.19</v>
       </c>
       <c r="F1126" t="n">
         <v>0.0</v>
@@ -41724,7 +41724,7 @@
         <v>8.005999999999998</v>
       </c>
       <c r="H1126" t="n">
-        <v>1491.172</v>
+        <v>1489.19</v>
       </c>
       <c r="I1126" t="n">
         <v>0.0</v>
@@ -41752,7 +41752,7 @@
         </is>
       </c>
       <c r="E1127" t="n">
-        <v>1028.807</v>
+        <v>974.779</v>
       </c>
       <c r="F1127" t="n">
         <v>0.0</v>
@@ -41761,7 +41761,7 @@
         <v>0.0</v>
       </c>
       <c r="H1127" t="n">
-        <v>1028.807</v>
+        <v>974.779</v>
       </c>
       <c r="I1127" t="n">
         <v>0.0</v>
@@ -41789,7 +41789,7 @@
         </is>
       </c>
       <c r="E1128" t="n">
-        <v>548.385</v>
+        <v>810.648</v>
       </c>
       <c r="F1128" t="n">
         <v>0.0</v>
@@ -41798,7 +41798,7 @@
         <v>630.5039999999999</v>
       </c>
       <c r="H1128" t="n">
-        <v>548.385</v>
+        <v>810.648</v>
       </c>
       <c r="I1128" t="n">
         <v>0.0</v>
@@ -42122,7 +42122,7 @@
         </is>
       </c>
       <c r="E1137" t="n">
-        <v>608.629</v>
+        <v>608.163</v>
       </c>
       <c r="F1137" t="n">
         <v>0.0</v>
@@ -42131,7 +42131,7 @@
         <v>0.0</v>
       </c>
       <c r="H1137" t="n">
-        <v>608.629</v>
+        <v>608.163</v>
       </c>
       <c r="I1137" t="n">
         <v>0.0</v>
@@ -42159,7 +42159,7 @@
         </is>
       </c>
       <c r="E1138" t="n">
-        <v>1484.234</v>
+        <v>1481.9</v>
       </c>
       <c r="F1138" t="n">
         <v>0.0</v>
@@ -42168,7 +42168,7 @@
         <v>0.0</v>
       </c>
       <c r="H1138" t="n">
-        <v>1484.234</v>
+        <v>1481.9</v>
       </c>
       <c r="I1138" t="n">
         <v>0.0</v>
@@ -42196,7 +42196,7 @@
         </is>
       </c>
       <c r="E1139" t="n">
-        <v>2166.2019999999998</v>
+        <v>2226.1040000000003</v>
       </c>
       <c r="F1139" t="n">
         <v>0.0</v>
@@ -42205,7 +42205,7 @@
         <v>0.0</v>
       </c>
       <c r="H1139" t="n">
-        <v>2166.2019999999998</v>
+        <v>2226.1040000000003</v>
       </c>
       <c r="I1139" t="n">
         <v>0.0</v>
@@ -42233,7 +42233,7 @@
         </is>
       </c>
       <c r="E1140" t="n">
-        <v>3315.8379999999997</v>
+        <v>495.02299999999997</v>
       </c>
       <c r="F1140" t="n">
         <v>0.0</v>
@@ -42242,10 +42242,10 @@
         <v>0.0</v>
       </c>
       <c r="H1140" t="n">
-        <v>509.14199999999994</v>
+        <v>495.02299999999997</v>
       </c>
       <c r="I1140" t="n">
-        <v>2806.696</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1141">
@@ -42270,7 +42270,7 @@
         </is>
       </c>
       <c r="E1141" t="n">
-        <v>3073.082</v>
+        <v>3065.614</v>
       </c>
       <c r="F1141" t="n">
         <v>0.0</v>
@@ -42279,7 +42279,7 @@
         <v>0.0</v>
       </c>
       <c r="H1141" t="n">
-        <v>3073.082</v>
+        <v>3065.614</v>
       </c>
       <c r="I1141" t="n">
         <v>0.0</v>
@@ -42307,7 +42307,7 @@
         </is>
       </c>
       <c r="E1142" t="n">
-        <v>4225.021</v>
+        <v>4219.42</v>
       </c>
       <c r="F1142" t="n">
         <v>0.0</v>
@@ -42316,7 +42316,7 @@
         <v>0.0</v>
       </c>
       <c r="H1142" t="n">
-        <v>4225.021</v>
+        <v>4219.42</v>
       </c>
       <c r="I1142" t="n">
         <v>0.0</v>
@@ -42344,7 +42344,7 @@
         </is>
       </c>
       <c r="E1143" t="n">
-        <v>2366.124</v>
+        <v>2407.1980000000003</v>
       </c>
       <c r="F1143" t="n">
         <v>9.955</v>
@@ -42353,7 +42353,7 @@
         <v>0.0</v>
       </c>
       <c r="H1143" t="n">
-        <v>2366.124</v>
+        <v>2407.1980000000003</v>
       </c>
       <c r="I1143" t="n">
         <v>0.0</v>
@@ -42455,7 +42455,7 @@
         </is>
       </c>
       <c r="E1146" t="n">
-        <v>11034.639</v>
+        <v>10999.175</v>
       </c>
       <c r="F1146" t="n">
         <v>34.29900000000001</v>
@@ -42464,7 +42464,7 @@
         <v>100.563</v>
       </c>
       <c r="H1146" t="n">
-        <v>11034.639</v>
+        <v>10999.175</v>
       </c>
       <c r="I1146" t="n">
         <v>0.0</v>
@@ -42529,7 +42529,7 @@
         </is>
       </c>
       <c r="E1148" t="n">
-        <v>8779.674</v>
+        <v>9026.0252</v>
       </c>
       <c r="F1148" t="n">
         <v>22.488</v>
@@ -42538,10 +42538,10 @@
         <v>7.155</v>
       </c>
       <c r="H1148" t="n">
-        <v>8779.674</v>
+        <v>8764.342</v>
       </c>
       <c r="I1148" t="n">
-        <v>0.0</v>
+        <v>261.6832</v>
       </c>
     </row>
     <row r="1149">
@@ -42566,7 +42566,7 @@
         </is>
       </c>
       <c r="E1149" t="n">
-        <v>13371.835000000001</v>
+        <v>17608.0516</v>
       </c>
       <c r="F1149" t="n">
         <v>17.334</v>
@@ -42575,10 +42575,10 @@
         <v>35.335</v>
       </c>
       <c r="H1149" t="n">
-        <v>13371.835000000001</v>
+        <v>13315.837</v>
       </c>
       <c r="I1149" t="n">
-        <v>0.0</v>
+        <v>4292.2146</v>
       </c>
     </row>
     <row r="1150">
@@ -42603,7 +42603,7 @@
         </is>
       </c>
       <c r="E1150" t="n">
-        <v>21370.8</v>
+        <v>22210.0</v>
       </c>
       <c r="F1150" t="n">
         <v>34.4</v>
@@ -42612,7 +42612,7 @@
         <v>3119.2000000000003</v>
       </c>
       <c r="H1150" t="n">
-        <v>21370.8</v>
+        <v>22210.0</v>
       </c>
       <c r="I1150" t="n">
         <v>0.0</v>
@@ -42677,7 +42677,7 @@
         </is>
       </c>
       <c r="E1152" t="n">
-        <v>5197.008</v>
+        <v>5150.077</v>
       </c>
       <c r="F1152" t="n">
         <v>5.333</v>
@@ -42686,7 +42686,7 @@
         <v>0.0</v>
       </c>
       <c r="H1152" t="n">
-        <v>5197.008</v>
+        <v>5150.077</v>
       </c>
       <c r="I1152" t="n">
         <v>0.0</v>
@@ -42714,7 +42714,7 @@
         </is>
       </c>
       <c r="E1153" t="n">
-        <v>2376.0</v>
+        <v>2342.4</v>
       </c>
       <c r="F1153" t="n">
         <v>0.0</v>
@@ -42723,7 +42723,7 @@
         <v>0.0</v>
       </c>
       <c r="H1153" t="n">
-        <v>2376.0</v>
+        <v>2342.4</v>
       </c>
       <c r="I1153" t="n">
         <v>0.0</v>
@@ -42751,7 +42751,7 @@
         </is>
       </c>
       <c r="E1154" t="n">
-        <v>2145.6</v>
+        <v>1915.2</v>
       </c>
       <c r="F1154" t="n">
         <v>0.4</v>
@@ -42760,7 +42760,7 @@
         <v>0.0</v>
       </c>
       <c r="H1154" t="n">
-        <v>2145.6</v>
+        <v>1915.2</v>
       </c>
       <c r="I1154" t="n">
         <v>0.0</v>
@@ -42788,7 +42788,7 @@
         </is>
       </c>
       <c r="E1155" t="n">
-        <v>2570.583</v>
+        <v>2480.977</v>
       </c>
       <c r="F1155" t="n">
         <v>0.0</v>
@@ -42797,7 +42797,7 @@
         <v>0.0</v>
       </c>
       <c r="H1155" t="n">
-        <v>2570.583</v>
+        <v>2480.977</v>
       </c>
       <c r="I1155" t="n">
         <v>0.0</v>
@@ -42825,7 +42825,7 @@
         </is>
       </c>
       <c r="E1156" t="n">
-        <v>990.9000000000001</v>
+        <v>920.304</v>
       </c>
       <c r="F1156" t="n">
         <v>0.428</v>
@@ -42834,7 +42834,7 @@
         <v>0.0</v>
       </c>
       <c r="H1156" t="n">
-        <v>990.9000000000001</v>
+        <v>920.304</v>
       </c>
       <c r="I1156" t="n">
         <v>0.0</v>
@@ -42973,7 +42973,7 @@
         </is>
       </c>
       <c r="E1160" t="n">
-        <v>6858.400000000001</v>
+        <v>2305.6</v>
       </c>
       <c r="F1160" t="n">
         <v>0.0</v>
@@ -42982,10 +42982,10 @@
         <v>0.8</v>
       </c>
       <c r="H1160" t="n">
-        <v>2320.8</v>
+        <v>2305.6</v>
       </c>
       <c r="I1160" t="n">
-        <v>4537.6</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1161">
@@ -43010,7 +43010,7 @@
         </is>
       </c>
       <c r="E1161" t="n">
-        <v>2974.0425</v>
+        <v>2872.602</v>
       </c>
       <c r="F1161" t="n">
         <v>0.0</v>
@@ -43019,10 +43019,10 @@
         <v>1.1329999999999998</v>
       </c>
       <c r="H1161" t="n">
-        <v>2880.537</v>
+        <v>2872.602</v>
       </c>
       <c r="I1161" t="n">
-        <v>93.5055</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1162">
@@ -43047,7 +43047,7 @@
         </is>
       </c>
       <c r="E1162" t="n">
-        <v>4466.557</v>
+        <v>4423.221</v>
       </c>
       <c r="F1162" t="n">
         <v>0.0</v>
@@ -43056,7 +43056,7 @@
         <v>0.0</v>
       </c>
       <c r="H1162" t="n">
-        <v>4466.557</v>
+        <v>4423.221</v>
       </c>
       <c r="I1162" t="n">
         <v>0.0</v>
@@ -43121,7 +43121,7 @@
         </is>
       </c>
       <c r="E1164" t="n">
-        <v>11088.554</v>
+        <v>10548.527</v>
       </c>
       <c r="F1164" t="n">
         <v>0.0</v>
@@ -43130,7 +43130,7 @@
         <v>0.0</v>
       </c>
       <c r="H1164" t="n">
-        <v>11088.554</v>
+        <v>10548.527</v>
       </c>
       <c r="I1164" t="n">
         <v>0.0</v>
@@ -43232,7 +43232,7 @@
         </is>
       </c>
       <c r="E1167" t="n">
-        <v>8110.4</v>
+        <v>8014.4</v>
       </c>
       <c r="F1167" t="n">
         <v>0.4</v>
@@ -43241,7 +43241,7 @@
         <v>339.2</v>
       </c>
       <c r="H1167" t="n">
-        <v>8110.4</v>
+        <v>8014.4</v>
       </c>
       <c r="I1167" t="n">
         <v>0.0</v>
@@ -43565,7 +43565,7 @@
         </is>
       </c>
       <c r="E1176" t="n">
-        <v>2294.0</v>
+        <v>2174.0</v>
       </c>
       <c r="F1176" t="n">
         <v>0.0</v>
@@ -43574,7 +43574,7 @@
         <v>0.0</v>
       </c>
       <c r="H1176" t="n">
-        <v>2294.0</v>
+        <v>2174.0</v>
       </c>
       <c r="I1176" t="n">
         <v>0.0</v>
@@ -43602,7 +43602,7 @@
         </is>
       </c>
       <c r="E1177" t="n">
-        <v>925.8</v>
+        <v>905.5999999999999</v>
       </c>
       <c r="F1177" t="n">
         <v>0.2</v>
@@ -43611,7 +43611,7 @@
         <v>0.0</v>
       </c>
       <c r="H1177" t="n">
-        <v>925.8</v>
+        <v>905.5999999999999</v>
       </c>
       <c r="I1177" t="n">
         <v>0.0</v>
@@ -43676,7 +43676,7 @@
         </is>
       </c>
       <c r="E1179" t="n">
-        <v>3761.2</v>
+        <v>3677.2</v>
       </c>
       <c r="F1179" t="n">
         <v>6.8</v>
@@ -43685,7 +43685,7 @@
         <v>0.0</v>
       </c>
       <c r="H1179" t="n">
-        <v>3761.2</v>
+        <v>3677.2</v>
       </c>
       <c r="I1179" t="n">
         <v>0.0</v>
@@ -43713,7 +43713,7 @@
         </is>
       </c>
       <c r="E1180" t="n">
-        <v>1380.972</v>
+        <v>1324.9650000000001</v>
       </c>
       <c r="F1180" t="n">
         <v>0.26699999999999996</v>
@@ -43722,7 +43722,7 @@
         <v>0.0</v>
       </c>
       <c r="H1180" t="n">
-        <v>1380.972</v>
+        <v>1324.9650000000001</v>
       </c>
       <c r="I1180" t="n">
         <v>0.0</v>
@@ -43750,7 +43750,7 @@
         </is>
       </c>
       <c r="E1181" t="n">
-        <v>2202.0</v>
+        <v>2179.2000000000003</v>
       </c>
       <c r="F1181" t="n">
         <v>0.0</v>
@@ -43759,7 +43759,7 @@
         <v>0.0</v>
       </c>
       <c r="H1181" t="n">
-        <v>2202.0</v>
+        <v>2179.2000000000003</v>
       </c>
       <c r="I1181" t="n">
         <v>0.0</v>
@@ -43824,7 +43824,7 @@
         </is>
       </c>
       <c r="E1183" t="n">
-        <v>3073.358</v>
+        <v>2971.369</v>
       </c>
       <c r="F1183" t="n">
         <v>0.6669999999999999</v>
@@ -43833,7 +43833,7 @@
         <v>0.0</v>
       </c>
       <c r="H1183" t="n">
-        <v>3073.358</v>
+        <v>2971.369</v>
       </c>
       <c r="I1183" t="n">
         <v>0.0</v>
@@ -43861,7 +43861,7 @@
         </is>
       </c>
       <c r="E1184" t="n">
-        <v>1882.0</v>
+        <v>1876.0</v>
       </c>
       <c r="F1184" t="n">
         <v>2.8</v>
@@ -43870,7 +43870,7 @@
         <v>0.8</v>
       </c>
       <c r="H1184" t="n">
-        <v>1882.0</v>
+        <v>1876.0</v>
       </c>
       <c r="I1184" t="n">
         <v>0.0</v>
@@ -44046,7 +44046,7 @@
         </is>
       </c>
       <c r="E1189" t="n">
-        <v>817.31</v>
+        <v>726.777</v>
       </c>
       <c r="F1189" t="n">
         <v>0.0</v>
@@ -44055,7 +44055,7 @@
         <v>0.0</v>
       </c>
       <c r="H1189" t="n">
-        <v>817.31</v>
+        <v>726.777</v>
       </c>
       <c r="I1189" t="n">
         <v>0.0</v>
@@ -44342,7 +44342,7 @@
         </is>
       </c>
       <c r="E1197" t="n">
-        <v>4567.787</v>
+        <v>4050.965</v>
       </c>
       <c r="F1197" t="n">
         <v>0.0</v>
@@ -44351,10 +44351,10 @@
         <v>0.0</v>
       </c>
       <c r="H1197" t="n">
-        <v>4082.507</v>
+        <v>4050.965</v>
       </c>
       <c r="I1197" t="n">
-        <v>485.28</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1198">
@@ -44379,7 +44379,7 @@
         </is>
       </c>
       <c r="E1198" t="n">
-        <v>1941.322</v>
+        <v>2058.483</v>
       </c>
       <c r="F1198" t="n">
         <v>0.0</v>
@@ -44388,7 +44388,7 @@
         <v>119.291</v>
       </c>
       <c r="H1198" t="n">
-        <v>1941.322</v>
+        <v>2058.483</v>
       </c>
       <c r="I1198" t="n">
         <v>0.0</v>
@@ -44416,7 +44416,7 @@
         </is>
       </c>
       <c r="E1199" t="n">
-        <v>4118.146</v>
+        <v>4074.834</v>
       </c>
       <c r="F1199" t="n">
         <v>0.0</v>
@@ -44425,7 +44425,7 @@
         <v>636.93</v>
       </c>
       <c r="H1199" t="n">
-        <v>4118.146</v>
+        <v>4074.834</v>
       </c>
       <c r="I1199" t="n">
         <v>0.0</v>
@@ -44453,7 +44453,7 @@
         </is>
       </c>
       <c r="E1200" t="n">
-        <v>1924.046</v>
+        <v>1932.567</v>
       </c>
       <c r="F1200" t="n">
         <v>0.0</v>
@@ -44462,7 +44462,7 @@
         <v>4.26</v>
       </c>
       <c r="H1200" t="n">
-        <v>1924.046</v>
+        <v>1932.567</v>
       </c>
       <c r="I1200" t="n">
         <v>0.0</v>
@@ -44638,7 +44638,7 @@
         </is>
       </c>
       <c r="E1205" t="n">
-        <v>4042.7991</v>
+        <v>2889.045</v>
       </c>
       <c r="F1205" t="n">
         <v>0.0</v>
@@ -44650,7 +44650,7 @@
         <v>2889.045</v>
       </c>
       <c r="I1205" t="n">
-        <v>1153.7541</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1206">
@@ -44749,7 +44749,7 @@
         </is>
       </c>
       <c r="E1208" t="n">
-        <v>600.176</v>
+        <v>674.7320000000001</v>
       </c>
       <c r="F1208" t="n">
         <v>0.0</v>
@@ -44761,7 +44761,7 @@
         <v>600.176</v>
       </c>
       <c r="I1208" t="n">
-        <v>0.0</v>
+        <v>74.556</v>
       </c>
     </row>
     <row r="1209">
@@ -44786,7 +44786,7 @@
         </is>
       </c>
       <c r="E1209" t="n">
-        <v>717.6947</v>
+        <v>2330.777</v>
       </c>
       <c r="F1209" t="n">
         <v>0.0</v>
@@ -44798,7 +44798,7 @@
         <v>484.617</v>
       </c>
       <c r="I1209" t="n">
-        <v>233.0777</v>
+        <v>1846.16</v>
       </c>
     </row>
     <row r="1210">
@@ -44860,7 +44860,7 @@
         </is>
       </c>
       <c r="E1211" t="n">
-        <v>1831.902</v>
+        <v>1830.571</v>
       </c>
       <c r="F1211" t="n">
         <v>0.0</v>
@@ -44869,7 +44869,7 @@
         <v>1.7750000000000001</v>
       </c>
       <c r="H1211" t="n">
-        <v>1831.902</v>
+        <v>1830.571</v>
       </c>
       <c r="I1211" t="n">
         <v>0.0</v>
@@ -44897,7 +44897,7 @@
         </is>
       </c>
       <c r="E1212" t="n">
-        <v>2381.537</v>
+        <v>5801.557</v>
       </c>
       <c r="F1212" t="n">
         <v>0.0</v>
@@ -44906,10 +44906,10 @@
         <v>0.0</v>
       </c>
       <c r="H1212" t="n">
-        <v>2381.537</v>
+        <v>2340.007</v>
       </c>
       <c r="I1212" t="n">
-        <v>0.0</v>
+        <v>3461.5499999999997</v>
       </c>
     </row>
     <row r="1213">
@@ -44971,7 +44971,7 @@
         </is>
       </c>
       <c r="E1214" t="n">
-        <v>3249.119</v>
+        <v>4087.859</v>
       </c>
       <c r="F1214" t="n">
         <v>0.0</v>
@@ -44980,10 +44980,10 @@
         <v>3.994</v>
       </c>
       <c r="H1214" t="n">
-        <v>3249.119</v>
+        <v>3009.479</v>
       </c>
       <c r="I1214" t="n">
-        <v>0.0</v>
+        <v>1078.38</v>
       </c>
     </row>
     <row r="1215">
@@ -45045,7 +45045,7 @@
         </is>
       </c>
       <c r="E1216" t="n">
-        <v>1421.264</v>
+        <v>1235.47</v>
       </c>
       <c r="F1216" t="n">
         <v>0.0</v>
@@ -45054,7 +45054,7 @@
         <v>0.0</v>
       </c>
       <c r="H1216" t="n">
-        <v>1421.264</v>
+        <v>1235.47</v>
       </c>
       <c r="I1216" t="n">
         <v>0.0</v>
@@ -45119,7 +45119,7 @@
         </is>
       </c>
       <c r="E1218" t="n">
-        <v>166.859</v>
+        <v>149.108</v>
       </c>
       <c r="F1218" t="n">
         <v>0.0</v>
@@ -45128,7 +45128,7 @@
         <v>0.0</v>
       </c>
       <c r="H1218" t="n">
-        <v>166.859</v>
+        <v>149.108</v>
       </c>
       <c r="I1218" t="n">
         <v>0.0</v>
@@ -45156,7 +45156,7 @@
         </is>
       </c>
       <c r="E1219" t="n">
-        <v>2583.084</v>
+        <v>2550.939</v>
       </c>
       <c r="F1219" t="n">
         <v>2.426</v>
@@ -45165,7 +45165,7 @@
         <v>0.0</v>
       </c>
       <c r="H1219" t="n">
-        <v>2583.084</v>
+        <v>2550.939</v>
       </c>
       <c r="I1219" t="n">
         <v>0.0</v>
@@ -45230,7 +45230,7 @@
         </is>
       </c>
       <c r="E1221" t="n">
-        <v>2396.385</v>
+        <v>2242.544</v>
       </c>
       <c r="F1221" t="n">
         <v>0.0</v>
@@ -45239,7 +45239,7 @@
         <v>0.0</v>
       </c>
       <c r="H1221" t="n">
-        <v>2396.385</v>
+        <v>2242.544</v>
       </c>
       <c r="I1221" t="n">
         <v>0.0</v>
@@ -45378,7 +45378,7 @@
         </is>
       </c>
       <c r="E1225" t="n">
-        <v>1905.274</v>
+        <v>1792.851</v>
       </c>
       <c r="F1225" t="n">
         <v>0.0</v>
@@ -45387,7 +45387,7 @@
         <v>1.183</v>
       </c>
       <c r="H1225" t="n">
-        <v>1905.274</v>
+        <v>1792.851</v>
       </c>
       <c r="I1225" t="n">
         <v>0.0</v>
@@ -45526,7 +45526,7 @@
         </is>
       </c>
       <c r="E1229" t="n">
-        <v>2759.094</v>
+        <v>2751.743</v>
       </c>
       <c r="F1229" t="n">
         <v>0.583</v>
@@ -45535,7 +45535,7 @@
         <v>0.0</v>
       </c>
       <c r="H1229" t="n">
-        <v>2759.094</v>
+        <v>2751.743</v>
       </c>
       <c r="I1229" t="n">
         <v>0.0</v>
@@ -45563,7 +45563,7 @@
         </is>
       </c>
       <c r="E1230" t="n">
-        <v>1565.423</v>
+        <v>1563.79</v>
       </c>
       <c r="F1230" t="n">
         <v>0.35100000000000003</v>
@@ -45572,7 +45572,7 @@
         <v>0.0</v>
       </c>
       <c r="H1230" t="n">
-        <v>1565.423</v>
+        <v>1563.79</v>
       </c>
       <c r="I1230" t="n">
         <v>0.0</v>
@@ -45748,7 +45748,7 @@
         </is>
       </c>
       <c r="E1235" t="n">
-        <v>264.44</v>
+        <v>251.24</v>
       </c>
       <c r="F1235" t="n">
         <v>0.0</v>
@@ -45757,7 +45757,7 @@
         <v>1.5399999999999998</v>
       </c>
       <c r="H1235" t="n">
-        <v>264.44</v>
+        <v>251.24</v>
       </c>
       <c r="I1235" t="n">
         <v>0.0</v>
@@ -45785,7 +45785,7 @@
         </is>
       </c>
       <c r="E1236" t="n">
-        <v>1048.3</v>
+        <v>1040.16</v>
       </c>
       <c r="F1236" t="n">
         <v>0.0</v>
@@ -45794,7 +45794,7 @@
         <v>0.0</v>
       </c>
       <c r="H1236" t="n">
-        <v>1048.3</v>
+        <v>1040.16</v>
       </c>
       <c r="I1236" t="n">
         <v>0.0</v>
@@ -45859,7 +45859,7 @@
         </is>
       </c>
       <c r="E1238" t="n">
-        <v>264.735</v>
+        <v>385.96500000000003</v>
       </c>
       <c r="F1238" t="n">
         <v>0.0</v>
@@ -45868,10 +45868,10 @@
         <v>0.0</v>
       </c>
       <c r="H1238" t="n">
-        <v>264.735</v>
+        <v>258.795</v>
       </c>
       <c r="I1238" t="n">
-        <v>0.0</v>
+        <v>127.17</v>
       </c>
     </row>
     <row r="1239">
@@ -48301,7 +48301,7 @@
         </is>
       </c>
       <c r="E1304" t="n">
-        <v>8444.0</v>
+        <v>8438.0</v>
       </c>
       <c r="F1304" t="n">
         <v>0.0</v>
@@ -48310,7 +48310,7 @@
         <v>18.0</v>
       </c>
       <c r="H1304" t="n">
-        <v>8444.0</v>
+        <v>8438.0</v>
       </c>
       <c r="I1304" t="n">
         <v>0.0</v>
@@ -50151,7 +50151,7 @@
         </is>
       </c>
       <c r="E1354" t="n">
-        <v>2033.626</v>
+        <v>1985.587</v>
       </c>
       <c r="F1354" t="n">
         <v>0.0</v>
@@ -50160,7 +50160,7 @@
         <v>42.701</v>
       </c>
       <c r="H1354" t="n">
-        <v>2033.626</v>
+        <v>1985.587</v>
       </c>
       <c r="I1354" t="n">
         <v>0.0</v>
@@ -50262,7 +50262,7 @@
         </is>
       </c>
       <c r="E1357" t="n">
-        <v>1395.0</v>
+        <v>1183.5</v>
       </c>
       <c r="F1357" t="n">
         <v>0.0</v>
@@ -50271,7 +50271,7 @@
         <v>90.0</v>
       </c>
       <c r="H1357" t="n">
-        <v>1395.0</v>
+        <v>1183.5</v>
       </c>
       <c r="I1357" t="n">
         <v>0.0</v>
@@ -50558,7 +50558,7 @@
         </is>
       </c>
       <c r="E1365" t="n">
-        <v>1493.194</v>
+        <v>1491.193</v>
       </c>
       <c r="F1365" t="n">
         <v>0.0</v>
@@ -50567,7 +50567,7 @@
         <v>14.011</v>
       </c>
       <c r="H1365" t="n">
-        <v>1493.194</v>
+        <v>1491.193</v>
       </c>
       <c r="I1365" t="n">
         <v>0.0</v>
@@ -50632,7 +50632,7 @@
         </is>
       </c>
       <c r="E1367" t="n">
-        <v>619.002</v>
+        <v>617.003</v>
       </c>
       <c r="F1367" t="n">
         <v>0.0</v>
@@ -50641,7 +50641,7 @@
         <v>0.416</v>
       </c>
       <c r="H1367" t="n">
-        <v>619.002</v>
+        <v>617.003</v>
       </c>
       <c r="I1367" t="n">
         <v>0.0</v>
@@ -51298,7 +51298,7 @@
         </is>
       </c>
       <c r="E1385" t="n">
-        <v>60.0</v>
+        <v>59.4</v>
       </c>
       <c r="F1385" t="n">
         <v>0.2</v>
@@ -51307,7 +51307,7 @@
         <v>0.0</v>
       </c>
       <c r="H1385" t="n">
-        <v>60.0</v>
+        <v>59.4</v>
       </c>
       <c r="I1385" t="n">
         <v>0.0</v>
@@ -51446,7 +51446,7 @@
         </is>
       </c>
       <c r="E1389" t="n">
-        <v>1376.573</v>
+        <v>1360.56</v>
       </c>
       <c r="F1389" t="n">
         <v>0.0</v>
@@ -51455,7 +51455,7 @@
         <v>2.669</v>
       </c>
       <c r="H1389" t="n">
-        <v>1376.573</v>
+        <v>1360.56</v>
       </c>
       <c r="I1389" t="n">
         <v>0.0</v>
@@ -52149,7 +52149,7 @@
         </is>
       </c>
       <c r="E1408" t="n">
-        <v>2682.644</v>
+        <v>2682.645</v>
       </c>
       <c r="F1408" t="n">
         <v>0.0</v>
@@ -52158,7 +52158,7 @@
         <v>0.0</v>
       </c>
       <c r="H1408" t="n">
-        <v>2682.644</v>
+        <v>2682.645</v>
       </c>
       <c r="I1408" t="n">
         <v>0.0</v>
@@ -52741,7 +52741,7 @@
         </is>
       </c>
       <c r="E1424" t="n">
-        <v>67.497</v>
+        <v>65.247</v>
       </c>
       <c r="F1424" t="n">
         <v>0.0</v>
@@ -52750,7 +52750,7 @@
         <v>33.75</v>
       </c>
       <c r="H1424" t="n">
-        <v>67.497</v>
+        <v>65.247</v>
       </c>
       <c r="I1424" t="n">
         <v>0.0</v>
@@ -52778,7 +52778,7 @@
         </is>
       </c>
       <c r="E1425" t="n">
-        <v>515.372</v>
+        <v>513.872</v>
       </c>
       <c r="F1425" t="n">
         <v>0.0</v>
@@ -52787,7 +52787,7 @@
         <v>40.5</v>
       </c>
       <c r="H1425" t="n">
-        <v>515.372</v>
+        <v>513.872</v>
       </c>
       <c r="I1425" t="n">
         <v>0.0</v>
@@ -52852,7 +52852,7 @@
         </is>
       </c>
       <c r="E1427" t="n">
-        <v>819.0</v>
+        <v>717.0</v>
       </c>
       <c r="F1427" t="n">
         <v>0.0</v>
@@ -52861,7 +52861,7 @@
         <v>20.625</v>
       </c>
       <c r="H1427" t="n">
-        <v>819.0</v>
+        <v>717.0</v>
       </c>
       <c r="I1427" t="n">
         <v>0.0</v>
@@ -52889,7 +52889,7 @@
         </is>
       </c>
       <c r="E1428" t="n">
-        <v>254.75</v>
+        <v>254.0</v>
       </c>
       <c r="F1428" t="n">
         <v>0.0</v>
@@ -52898,7 +52898,7 @@
         <v>6.75</v>
       </c>
       <c r="H1428" t="n">
-        <v>254.75</v>
+        <v>254.0</v>
       </c>
       <c r="I1428" t="n">
         <v>0.0</v>
@@ -52926,7 +52926,7 @@
         </is>
       </c>
       <c r="E1429" t="n">
-        <v>172.5</v>
+        <v>171.0</v>
       </c>
       <c r="F1429" t="n">
         <v>0.0</v>
@@ -52935,7 +52935,7 @@
         <v>436.5</v>
       </c>
       <c r="H1429" t="n">
-        <v>172.5</v>
+        <v>171.0</v>
       </c>
       <c r="I1429" t="n">
         <v>0.0</v>
@@ -52963,7 +52963,7 @@
         </is>
       </c>
       <c r="E1430" t="n">
-        <v>595.5</v>
+        <v>593.25</v>
       </c>
       <c r="F1430" t="n">
         <v>0.0</v>
@@ -52972,7 +52972,7 @@
         <v>38.25</v>
       </c>
       <c r="H1430" t="n">
-        <v>595.5</v>
+        <v>593.25</v>
       </c>
       <c r="I1430" t="n">
         <v>0.0</v>
@@ -53000,7 +53000,7 @@
         </is>
       </c>
       <c r="E1431" t="n">
-        <v>758.75</v>
+        <v>752.375</v>
       </c>
       <c r="F1431" t="n">
         <v>0.0</v>
@@ -53009,7 +53009,7 @@
         <v>3.75</v>
       </c>
       <c r="H1431" t="n">
-        <v>758.75</v>
+        <v>752.375</v>
       </c>
       <c r="I1431" t="n">
         <v>0.0</v>
@@ -53074,7 +53074,7 @@
         </is>
       </c>
       <c r="E1433" t="n">
-        <v>330.25</v>
+        <v>327.25</v>
       </c>
       <c r="F1433" t="n">
         <v>0.0</v>
@@ -53083,7 +53083,7 @@
         <v>0.0</v>
       </c>
       <c r="H1433" t="n">
-        <v>330.25</v>
+        <v>327.25</v>
       </c>
       <c r="I1433" t="n">
         <v>0.0</v>
@@ -53111,7 +53111,7 @@
         </is>
       </c>
       <c r="E1434" t="n">
-        <v>656.0</v>
+        <v>653.75</v>
       </c>
       <c r="F1434" t="n">
         <v>0.0</v>
@@ -53120,7 +53120,7 @@
         <v>0.75</v>
       </c>
       <c r="H1434" t="n">
-        <v>656.0</v>
+        <v>653.75</v>
       </c>
       <c r="I1434" t="n">
         <v>0.0</v>
@@ -53148,7 +53148,7 @@
         </is>
       </c>
       <c r="E1435" t="n">
-        <v>591.75</v>
+        <v>562.5</v>
       </c>
       <c r="F1435" t="n">
         <v>0.0</v>
@@ -53157,7 +53157,7 @@
         <v>55.5</v>
       </c>
       <c r="H1435" t="n">
-        <v>591.75</v>
+        <v>562.5</v>
       </c>
       <c r="I1435" t="n">
         <v>0.0</v>
@@ -53222,7 +53222,7 @@
         </is>
       </c>
       <c r="E1437" t="n">
-        <v>3490.5</v>
+        <v>3489.0</v>
       </c>
       <c r="F1437" t="n">
         <v>0.0</v>
@@ -53231,7 +53231,7 @@
         <v>37.5</v>
       </c>
       <c r="H1437" t="n">
-        <v>3490.5</v>
+        <v>3489.0</v>
       </c>
       <c r="I1437" t="n">
         <v>0.0</v>
@@ -53259,7 +53259,7 @@
         </is>
       </c>
       <c r="E1438" t="n">
-        <v>420.0</v>
+        <v>414.0</v>
       </c>
       <c r="F1438" t="n">
         <v>0.0</v>
@@ -53268,7 +53268,7 @@
         <v>0.0</v>
       </c>
       <c r="H1438" t="n">
-        <v>420.0</v>
+        <v>414.0</v>
       </c>
       <c r="I1438" t="n">
         <v>0.0</v>
@@ -53296,7 +53296,7 @@
         </is>
       </c>
       <c r="E1439" t="n">
-        <v>240.75</v>
+        <v>240.375</v>
       </c>
       <c r="F1439" t="n">
         <v>0.0</v>
@@ -53305,7 +53305,7 @@
         <v>34.875</v>
       </c>
       <c r="H1439" t="n">
-        <v>240.75</v>
+        <v>240.375</v>
       </c>
       <c r="I1439" t="n">
         <v>0.0</v>
@@ -53370,7 +53370,7 @@
         </is>
       </c>
       <c r="E1441" t="n">
-        <v>2036.182</v>
+        <v>2021.504</v>
       </c>
       <c r="F1441" t="n">
         <v>0.0</v>
@@ -53379,7 +53379,7 @@
         <v>11.342</v>
       </c>
       <c r="H1441" t="n">
-        <v>2036.182</v>
+        <v>2021.504</v>
       </c>
       <c r="I1441" t="n">
         <v>0.0</v>
@@ -53555,7 +53555,7 @@
         </is>
       </c>
       <c r="E1446" t="n">
-        <v>13.62</v>
+        <v>13.32</v>
       </c>
       <c r="F1446" t="n">
         <v>0.0</v>
@@ -53564,7 +53564,7 @@
         <v>0.0</v>
       </c>
       <c r="H1446" t="n">
-        <v>13.62</v>
+        <v>13.32</v>
       </c>
       <c r="I1446" t="n">
         <v>0.0</v>
@@ -53592,7 +53592,7 @@
         </is>
       </c>
       <c r="E1447" t="n">
-        <v>8.057</v>
+        <v>7.725</v>
       </c>
       <c r="F1447" t="n">
         <v>0.0</v>
@@ -53601,7 +53601,7 @@
         <v>0.0</v>
       </c>
       <c r="H1447" t="n">
-        <v>8.057</v>
+        <v>7.725</v>
       </c>
       <c r="I1447" t="n">
         <v>0.0</v>
@@ -53666,7 +53666,7 @@
         </is>
       </c>
       <c r="E1449" t="n">
-        <v>114.954</v>
+        <v>105.957</v>
       </c>
       <c r="F1449" t="n">
         <v>0.0</v>
@@ -53675,7 +53675,7 @@
         <v>0.0</v>
       </c>
       <c r="H1449" t="n">
-        <v>114.954</v>
+        <v>105.957</v>
       </c>
       <c r="I1449" t="n">
         <v>0.0</v>
@@ -54110,7 +54110,7 @@
         </is>
       </c>
       <c r="E1461" t="n">
-        <v>6727.885</v>
+        <v>6631.247</v>
       </c>
       <c r="F1461" t="n">
         <v>0.589</v>
@@ -54119,7 +54119,7 @@
         <v>661.475</v>
       </c>
       <c r="H1461" t="n">
-        <v>6727.885</v>
+        <v>6631.247</v>
       </c>
       <c r="I1461" t="n">
         <v>0.0</v>
@@ -54147,7 +54147,7 @@
         </is>
       </c>
       <c r="E1462" t="n">
-        <v>2615.527</v>
+        <v>2562.234</v>
       </c>
       <c r="F1462" t="n">
         <v>65.467</v>
@@ -54156,7 +54156,7 @@
         <v>121.834</v>
       </c>
       <c r="H1462" t="n">
-        <v>2615.527</v>
+        <v>2562.234</v>
       </c>
       <c r="I1462" t="n">
         <v>0.0</v>
@@ -54406,7 +54406,7 @@
         </is>
       </c>
       <c r="E1469" t="n">
-        <v>53.699999999999996</v>
+        <v>45.6</v>
       </c>
       <c r="F1469" t="n">
         <v>0.0</v>
@@ -54415,7 +54415,7 @@
         <v>0.0</v>
       </c>
       <c r="H1469" t="n">
-        <v>53.699999999999996</v>
+        <v>45.6</v>
       </c>
       <c r="I1469" t="n">
         <v>0.0</v>
@@ -54443,7 +54443,7 @@
         </is>
       </c>
       <c r="E1470" t="n">
-        <v>6768.599999999999</v>
+        <v>6419.400000000001</v>
       </c>
       <c r="F1470" t="n">
         <v>1.2</v>
@@ -54452,7 +54452,7 @@
         <v>0.0</v>
       </c>
       <c r="H1470" t="n">
-        <v>6768.599999999999</v>
+        <v>6419.400000000001</v>
       </c>
       <c r="I1470" t="n">
         <v>0.0</v>
@@ -55139,13 +55139,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CDBB93B-4058-4E84-AF7C-2118F4CD71EA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12EB141A-53B8-498C-A93E-BFEABE2D4D9E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E826A981-FF03-4E30-B3F2-D18CAAA155C5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0BAB3DB-8892-4054-9806-810299FBFEE3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F207A3C-45F3-4ABD-9938-9206EA5EBFBC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0EC19E1-F474-4B44-AC09-FDBB767BF52C}"/>
 </file>
--- a/Inventory_KNIME.xlsx
+++ b/Inventory_KNIME.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>114.5</v>
+        <v>84.5</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -469,7 +469,7 @@
         <v>0.0</v>
       </c>
       <c r="H11" t="n">
-        <v>114.5</v>
+        <v>84.5</v>
       </c>
       <c r="I11" t="n">
         <v>0.0</v>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1010.5</v>
+        <v>884.5</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
@@ -691,7 +691,7 @@
         <v>0.5</v>
       </c>
       <c r="H17" t="n">
-        <v>1010.5</v>
+        <v>884.5</v>
       </c>
       <c r="I17" t="n">
         <v>0.0</v>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1165.0</v>
+        <v>1045.0</v>
       </c>
       <c r="F19" t="n">
         <v>0.0</v>
@@ -765,7 +765,7 @@
         <v>3.0</v>
       </c>
       <c r="H19" t="n">
-        <v>1165.0</v>
+        <v>1045.0</v>
       </c>
       <c r="I19" t="n">
         <v>0.0</v>
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3542.826</v>
+        <v>3535.3430000000003</v>
       </c>
       <c r="F34" t="n">
         <v>37.148</v>
@@ -1320,7 +1320,7 @@
         <v>4.971</v>
       </c>
       <c r="H34" t="n">
-        <v>3542.826</v>
+        <v>3535.3430000000003</v>
       </c>
       <c r="I34" t="n">
         <v>0.0</v>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2119.4260000000004</v>
+        <v>2059.9610000000002</v>
       </c>
       <c r="F35" t="n">
         <v>282.264</v>
@@ -1357,7 +1357,7 @@
         <v>216.545</v>
       </c>
       <c r="H35" t="n">
-        <v>2119.4260000000004</v>
+        <v>2059.9610000000002</v>
       </c>
       <c r="I35" t="n">
         <v>0.0</v>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>916.471</v>
+        <v>916.314</v>
       </c>
       <c r="F40" t="n">
         <v>17.094</v>
@@ -1542,7 +1542,7 @@
         <v>25.329</v>
       </c>
       <c r="H40" t="n">
-        <v>916.471</v>
+        <v>916.314</v>
       </c>
       <c r="I40" t="n">
         <v>0.0</v>
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>10848.75</v>
+        <v>10835.55</v>
       </c>
       <c r="F43" t="n">
         <v>3.3</v>
@@ -1653,7 +1653,7 @@
         <v>409.2</v>
       </c>
       <c r="H43" t="n">
-        <v>10848.75</v>
+        <v>10835.55</v>
       </c>
       <c r="I43" t="n">
         <v>0.0</v>
@@ -2532,7 +2532,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>111.747</v>
+        <v>110.68100000000001</v>
       </c>
       <c r="F67" t="n">
         <v>3.467</v>
@@ -2541,7 +2541,7 @@
         <v>0.0</v>
       </c>
       <c r="H67" t="n">
-        <v>111.747</v>
+        <v>110.68100000000001</v>
       </c>
       <c r="I67" t="n">
         <v>0.0</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3250.2</v>
+        <v>3245.8</v>
       </c>
       <c r="F70" t="n">
         <v>1.2</v>
@@ -2652,7 +2652,7 @@
         <v>0.0</v>
       </c>
       <c r="H70" t="n">
-        <v>3250.2</v>
+        <v>3245.8</v>
       </c>
       <c r="I70" t="n">
         <v>0.0</v>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1379.639</v>
+        <v>1366.838</v>
       </c>
       <c r="F71" t="n">
         <v>4.801</v>
@@ -2689,7 +2689,7 @@
         <v>17.069000000000003</v>
       </c>
       <c r="H71" t="n">
-        <v>1379.639</v>
+        <v>1366.838</v>
       </c>
       <c r="I71" t="n">
         <v>0.0</v>
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>330.17400000000004</v>
+        <v>329.908</v>
       </c>
       <c r="F72" t="n">
         <v>0.0</v>
@@ -2726,7 +2726,7 @@
         <v>4.267</v>
       </c>
       <c r="H72" t="n">
-        <v>330.17400000000004</v>
+        <v>329.908</v>
       </c>
       <c r="I72" t="n">
         <v>0.0</v>
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1809.375</v>
+        <v>1790.7099999999998</v>
       </c>
       <c r="F73" t="n">
         <v>5.777</v>
@@ -2763,7 +2763,7 @@
         <v>0.0</v>
       </c>
       <c r="H73" t="n">
-        <v>1809.375</v>
+        <v>1790.7099999999998</v>
       </c>
       <c r="I73" t="n">
         <v>0.0</v>
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1443.38</v>
+        <v>1443.114</v>
       </c>
       <c r="F74" t="n">
         <v>0.0</v>
@@ -2800,7 +2800,7 @@
         <v>0.0</v>
       </c>
       <c r="H74" t="n">
-        <v>1443.38</v>
+        <v>1443.114</v>
       </c>
       <c r="I74" t="n">
         <v>0.0</v>
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6021.552</v>
+        <v>6020.486</v>
       </c>
       <c r="F75" t="n">
         <v>9.601</v>
@@ -2837,7 +2837,7 @@
         <v>17.069000000000003</v>
       </c>
       <c r="H75" t="n">
-        <v>6021.552</v>
+        <v>6020.486</v>
       </c>
       <c r="I75" t="n">
         <v>0.0</v>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1127.607</v>
+        <v>1127.34</v>
       </c>
       <c r="F77" t="n">
         <v>50.94</v>
@@ -2911,7 +2911,7 @@
         <v>0.0</v>
       </c>
       <c r="H77" t="n">
-        <v>1127.607</v>
+        <v>1127.34</v>
       </c>
       <c r="I77" t="n">
         <v>0.0</v>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>490.391</v>
+        <v>488.389</v>
       </c>
       <c r="F78" t="n">
         <v>0.0</v>
@@ -2948,7 +2948,7 @@
         <v>0.083</v>
       </c>
       <c r="H78" t="n">
-        <v>490.391</v>
+        <v>488.389</v>
       </c>
       <c r="I78" t="n">
         <v>0.0</v>
@@ -3198,7 +3198,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3269.275</v>
+        <v>3319.932</v>
       </c>
       <c r="F85" t="n">
         <v>0.0</v>
@@ -3207,7 +3207,7 @@
         <v>0.0</v>
       </c>
       <c r="H85" t="n">
-        <v>3269.275</v>
+        <v>3319.932</v>
       </c>
       <c r="I85" t="n">
         <v>0.0</v>
@@ -3642,7 +3642,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2552.0</v>
+        <v>2551.0</v>
       </c>
       <c r="F97" t="n">
         <v>0.0</v>
@@ -3651,7 +3651,7 @@
         <v>0.0</v>
       </c>
       <c r="H97" t="n">
-        <v>2552.0</v>
+        <v>2551.0</v>
       </c>
       <c r="I97" t="n">
         <v>0.0</v>
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2410.0</v>
+        <v>2290.0</v>
       </c>
       <c r="F102" t="n">
         <v>0.0</v>
@@ -3836,7 +3836,7 @@
         <v>0.0</v>
       </c>
       <c r="H102" t="n">
-        <v>2410.0</v>
+        <v>2290.0</v>
       </c>
       <c r="I102" t="n">
         <v>0.0</v>
@@ -4012,7 +4012,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>740.7589999999999</v>
+        <v>738.091</v>
       </c>
       <c r="F107" t="n">
         <v>0.0</v>
@@ -4021,7 +4021,7 @@
         <v>18.96</v>
       </c>
       <c r="H107" t="n">
-        <v>740.7589999999999</v>
+        <v>738.091</v>
       </c>
       <c r="I107" t="n">
         <v>0.0</v>
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>896.412</v>
+        <v>893.742</v>
       </c>
       <c r="F109" t="n">
         <v>0.0</v>
@@ -4095,7 +4095,7 @@
         <v>69.38900000000001</v>
       </c>
       <c r="H109" t="n">
-        <v>896.412</v>
+        <v>893.742</v>
       </c>
       <c r="I109" t="n">
         <v>0.0</v>
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>654.301</v>
+        <v>650.298</v>
       </c>
       <c r="F112" t="n">
         <v>0.0</v>
@@ -4206,7 +4206,7 @@
         <v>0.723</v>
       </c>
       <c r="H112" t="n">
-        <v>654.301</v>
+        <v>650.298</v>
       </c>
       <c r="I112" t="n">
         <v>0.0</v>
@@ -4419,7 +4419,7 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>774.1550000000001</v>
+        <v>774.155</v>
       </c>
       <c r="F118" t="n">
         <v>0.0</v>
@@ -4428,7 +4428,7 @@
         <v>0.0</v>
       </c>
       <c r="H118" t="n">
-        <v>774.1550000000001</v>
+        <v>774.155</v>
       </c>
       <c r="I118" t="n">
         <v>0.0</v>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1346.8</v>
+        <v>1281.04</v>
       </c>
       <c r="F122" t="n">
         <v>0.12000000000000001</v>
@@ -4576,7 +4576,7 @@
         <v>25.44</v>
       </c>
       <c r="H122" t="n">
-        <v>1346.8</v>
+        <v>1281.04</v>
       </c>
       <c r="I122" t="n">
         <v>0.0</v>
@@ -4604,7 +4604,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1239.076</v>
+        <v>1235.701</v>
       </c>
       <c r="F123" t="n">
         <v>0.225</v>
@@ -4613,7 +4613,7 @@
         <v>116.775</v>
       </c>
       <c r="H123" t="n">
-        <v>1239.076</v>
+        <v>1235.701</v>
       </c>
       <c r="I123" t="n">
         <v>0.0</v>
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4402.398</v>
+        <v>4328.954</v>
       </c>
       <c r="F124" t="n">
         <v>0.0</v>
@@ -4650,7 +4650,7 @@
         <v>118.215</v>
       </c>
       <c r="H124" t="n">
-        <v>4402.398</v>
+        <v>4328.954</v>
       </c>
       <c r="I124" t="n">
         <v>0.0</v>
@@ -4752,7 +4752,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>498.34400000000005</v>
+        <v>482.62</v>
       </c>
       <c r="F127" t="n">
         <v>0.0</v>
@@ -4761,7 +4761,7 @@
         <v>106.005</v>
       </c>
       <c r="H127" t="n">
-        <v>498.34400000000005</v>
+        <v>482.62</v>
       </c>
       <c r="I127" t="n">
         <v>0.0</v>
@@ -4789,7 +4789,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>265.40000000000003</v>
+        <v>258.08</v>
       </c>
       <c r="F128" t="n">
         <v>0.0</v>
@@ -4798,7 +4798,7 @@
         <v>75.39999999999999</v>
       </c>
       <c r="H128" t="n">
-        <v>265.40000000000003</v>
+        <v>258.08</v>
       </c>
       <c r="I128" t="n">
         <v>0.0</v>
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1900.964</v>
+        <v>1892.624</v>
       </c>
       <c r="F130" t="n">
         <v>0.0</v>
@@ -4872,7 +4872,7 @@
         <v>63.38399999999999</v>
       </c>
       <c r="H130" t="n">
-        <v>1900.964</v>
+        <v>1892.624</v>
       </c>
       <c r="I130" t="n">
         <v>0.0</v>
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>448.358</v>
+        <v>1203.6284</v>
       </c>
       <c r="F131" t="n">
         <v>0.0</v>
@@ -4912,7 +4912,7 @@
         <v>448.358</v>
       </c>
       <c r="I131" t="n">
-        <v>0.0</v>
+        <v>755.2704</v>
       </c>
     </row>
     <row r="132">
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1844.0</v>
+        <v>1820.0</v>
       </c>
       <c r="F141" t="n">
         <v>0.0</v>
@@ -5279,7 +5279,7 @@
         <v>1.0</v>
       </c>
       <c r="H141" t="n">
-        <v>1844.0</v>
+        <v>1820.0</v>
       </c>
       <c r="I141" t="n">
         <v>0.0</v>
@@ -5418,7 +5418,7 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>976.0</v>
+        <v>916.0</v>
       </c>
       <c r="F145" t="n">
         <v>0.0</v>
@@ -5427,7 +5427,7 @@
         <v>0.0</v>
       </c>
       <c r="H145" t="n">
-        <v>976.0</v>
+        <v>916.0</v>
       </c>
       <c r="I145" t="n">
         <v>0.0</v>
@@ -6713,7 +6713,7 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1346.0</v>
+        <v>1176.0</v>
       </c>
       <c r="F180" t="n">
         <v>0.0</v>
@@ -6722,7 +6722,7 @@
         <v>0.0</v>
       </c>
       <c r="H180" t="n">
-        <v>1346.0</v>
+        <v>1176.0</v>
       </c>
       <c r="I180" t="n">
         <v>0.0</v>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1077.221</v>
+        <v>1103.125</v>
       </c>
       <c r="F192" t="n">
         <v>0.0</v>
@@ -7166,7 +7166,7 @@
         <v>1000.443</v>
       </c>
       <c r="H192" t="n">
-        <v>1077.221</v>
+        <v>1103.125</v>
       </c>
       <c r="I192" t="n">
         <v>0.0</v>
@@ -7194,7 +7194,7 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>1423.186</v>
+        <v>1577.9080000000001</v>
       </c>
       <c r="F193" t="n">
         <v>0.23299999999999998</v>
@@ -7203,7 +7203,7 @@
         <v>2296.4449999999997</v>
       </c>
       <c r="H193" t="n">
-        <v>1423.186</v>
+        <v>1577.9080000000001</v>
       </c>
       <c r="I193" t="n">
         <v>0.0</v>
@@ -7231,7 +7231,7 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>186.816</v>
+        <v>173.472</v>
       </c>
       <c r="F194" t="n">
         <v>0.0</v>
@@ -7240,7 +7240,7 @@
         <v>98.746</v>
       </c>
       <c r="H194" t="n">
-        <v>186.816</v>
+        <v>173.472</v>
       </c>
       <c r="I194" t="n">
         <v>0.0</v>
@@ -7453,7 +7453,7 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>103.937</v>
+        <v>102.437</v>
       </c>
       <c r="F200" t="n">
         <v>0.0</v>
@@ -7462,7 +7462,7 @@
         <v>79.125</v>
       </c>
       <c r="H200" t="n">
-        <v>103.937</v>
+        <v>102.437</v>
       </c>
       <c r="I200" t="n">
         <v>0.0</v>
@@ -7490,7 +7490,7 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>408.0</v>
+        <v>400.5</v>
       </c>
       <c r="F201" t="n">
         <v>0.0</v>
@@ -7499,7 +7499,7 @@
         <v>9.0</v>
       </c>
       <c r="H201" t="n">
-        <v>408.0</v>
+        <v>400.5</v>
       </c>
       <c r="I201" t="n">
         <v>0.0</v>
@@ -7601,7 +7601,7 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1184.674</v>
+        <v>1184.1589999999999</v>
       </c>
       <c r="F204" t="n">
         <v>0.0</v>
@@ -7610,7 +7610,7 @@
         <v>0.0</v>
       </c>
       <c r="H204" t="n">
-        <v>1184.674</v>
+        <v>1184.1589999999999</v>
       </c>
       <c r="I204" t="n">
         <v>0.0</v>
@@ -7638,7 +7638,7 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>852.036</v>
+        <v>855.816</v>
       </c>
       <c r="F205" t="n">
         <v>0.0</v>
@@ -7647,7 +7647,7 @@
         <v>0.859</v>
       </c>
       <c r="H205" t="n">
-        <v>852.036</v>
+        <v>855.816</v>
       </c>
       <c r="I205" t="n">
         <v>0.0</v>
@@ -7712,7 +7712,7 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>655.13</v>
+        <v>652.3810000000001</v>
       </c>
       <c r="F207" t="n">
         <v>0.515</v>
@@ -7721,7 +7721,7 @@
         <v>0.34400000000000003</v>
       </c>
       <c r="H207" t="n">
-        <v>655.13</v>
+        <v>652.3810000000001</v>
       </c>
       <c r="I207" t="n">
         <v>0.0</v>
@@ -7786,7 +7786,7 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>542.968</v>
+        <v>538.155</v>
       </c>
       <c r="F209" t="n">
         <v>0.0</v>
@@ -7795,7 +7795,7 @@
         <v>22.681</v>
       </c>
       <c r="H209" t="n">
-        <v>542.968</v>
+        <v>538.155</v>
       </c>
       <c r="I209" t="n">
         <v>0.0</v>
@@ -7823,7 +7823,7 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>442.85</v>
+        <v>441.475</v>
       </c>
       <c r="F210" t="n">
         <v>0.0</v>
@@ -7832,7 +7832,7 @@
         <v>48.111000000000004</v>
       </c>
       <c r="H210" t="n">
-        <v>442.85</v>
+        <v>441.475</v>
       </c>
       <c r="I210" t="n">
         <v>0.0</v>
@@ -7897,7 +7897,7 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>845.485</v>
+        <v>848.12</v>
       </c>
       <c r="F212" t="n">
         <v>0.0</v>
@@ -7906,7 +7906,7 @@
         <v>1.374</v>
       </c>
       <c r="H212" t="n">
-        <v>845.485</v>
+        <v>848.12</v>
       </c>
       <c r="I212" t="n">
         <v>0.0</v>
@@ -7934,7 +7934,7 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>106.23</v>
+        <v>109.895</v>
       </c>
       <c r="F213" t="n">
         <v>0.34400000000000003</v>
@@ -7943,7 +7943,7 @@
         <v>43.981</v>
       </c>
       <c r="H213" t="n">
-        <v>106.23</v>
+        <v>109.895</v>
       </c>
       <c r="I213" t="n">
         <v>0.0</v>
@@ -7971,7 +7971,7 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>84.539</v>
+        <v>84.538</v>
       </c>
       <c r="F214" t="n">
         <v>0.0</v>
@@ -7980,7 +7980,7 @@
         <v>11.684</v>
       </c>
       <c r="H214" t="n">
-        <v>84.539</v>
+        <v>84.538</v>
       </c>
       <c r="I214" t="n">
         <v>0.0</v>
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>1708.0910000000001</v>
+        <v>1688.906</v>
       </c>
       <c r="F215" t="n">
         <v>1.031</v>
@@ -8017,7 +8017,7 @@
         <v>0.34400000000000003</v>
       </c>
       <c r="H215" t="n">
-        <v>1708.0910000000001</v>
+        <v>1688.906</v>
       </c>
       <c r="I215" t="n">
         <v>0.0</v>
@@ -8082,7 +8082,7 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>774.761</v>
+        <v>774.704</v>
       </c>
       <c r="F217" t="n">
         <v>0.34400000000000003</v>
@@ -8091,7 +8091,7 @@
         <v>7.216</v>
       </c>
       <c r="H217" t="n">
-        <v>774.761</v>
+        <v>774.704</v>
       </c>
       <c r="I217" t="n">
         <v>0.0</v>
@@ -8230,7 +8230,7 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>281.435</v>
+        <v>281.436</v>
       </c>
       <c r="F221" t="n">
         <v>0.0</v>
@@ -8239,7 +8239,7 @@
         <v>0.0</v>
       </c>
       <c r="H221" t="n">
-        <v>281.435</v>
+        <v>281.436</v>
       </c>
       <c r="I221" t="n">
         <v>0.0</v>
@@ -8304,7 +8304,7 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>1061.264</v>
+        <v>1053.76</v>
       </c>
       <c r="F223" t="n">
         <v>0.0</v>
@@ -8313,7 +8313,7 @@
         <v>3.436</v>
       </c>
       <c r="H223" t="n">
-        <v>1061.264</v>
+        <v>1053.76</v>
       </c>
       <c r="I223" t="n">
         <v>0.0</v>
@@ -8378,7 +8378,7 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>1224.0</v>
+        <v>1014.0</v>
       </c>
       <c r="F225" t="n">
         <v>0.0</v>
@@ -8387,7 +8387,7 @@
         <v>3.0</v>
       </c>
       <c r="H225" t="n">
-        <v>1224.0</v>
+        <v>1014.0</v>
       </c>
       <c r="I225" t="n">
         <v>0.0</v>
@@ -8859,7 +8859,7 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>70.724</v>
+        <v>66.72</v>
       </c>
       <c r="F238" t="n">
         <v>0.0</v>
@@ -8868,7 +8868,7 @@
         <v>1.056</v>
       </c>
       <c r="H238" t="n">
-        <v>70.724</v>
+        <v>66.72</v>
       </c>
       <c r="I238" t="n">
         <v>0.0</v>
@@ -8896,7 +8896,7 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>79.397</v>
+        <v>78.73</v>
       </c>
       <c r="F239" t="n">
         <v>0.0</v>
@@ -8905,7 +8905,7 @@
         <v>0.0</v>
       </c>
       <c r="H239" t="n">
-        <v>79.397</v>
+        <v>78.73</v>
       </c>
       <c r="I239" t="n">
         <v>0.0</v>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>78.062</v>
+        <v>74.059</v>
       </c>
       <c r="F240" t="n">
         <v>0.0</v>
@@ -8942,7 +8942,7 @@
         <v>0.0</v>
       </c>
       <c r="H240" t="n">
-        <v>78.062</v>
+        <v>74.059</v>
       </c>
       <c r="I240" t="n">
         <v>0.0</v>
@@ -8970,7 +8970,7 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>86.736</v>
+        <v>74.059</v>
       </c>
       <c r="F241" t="n">
         <v>0.0</v>
@@ -8979,7 +8979,7 @@
         <v>5.338</v>
       </c>
       <c r="H241" t="n">
-        <v>86.736</v>
+        <v>74.059</v>
       </c>
       <c r="I241" t="n">
         <v>0.0</v>
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>13.899999999999999</v>
+        <v>10.564</v>
       </c>
       <c r="F242" t="n">
         <v>0.0</v>
@@ -9016,7 +9016,7 @@
         <v>0.0</v>
       </c>
       <c r="H242" t="n">
-        <v>13.899999999999999</v>
+        <v>10.564</v>
       </c>
       <c r="I242" t="n">
         <v>0.0</v>
@@ -9340,7 +9340,7 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>9381.595000000001</v>
+        <v>9412.395</v>
       </c>
       <c r="F251" t="n">
         <v>0.0</v>
@@ -9349,7 +9349,7 @@
         <v>5060.014</v>
       </c>
       <c r="H251" t="n">
-        <v>9381.595000000001</v>
+        <v>9412.395</v>
       </c>
       <c r="I251" t="n">
         <v>0.0</v>
@@ -9377,7 +9377,7 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>9097.172</v>
+        <v>9100.639</v>
       </c>
       <c r="F252" t="n">
         <v>1.7329999999999999</v>
@@ -9386,7 +9386,7 @@
         <v>361.126</v>
       </c>
       <c r="H252" t="n">
-        <v>9097.172</v>
+        <v>9100.639</v>
       </c>
       <c r="I252" t="n">
         <v>0.0</v>
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>4421.0</v>
+        <v>4419.0</v>
       </c>
       <c r="F253" t="n">
         <v>0.0</v>
@@ -9423,7 +9423,7 @@
         <v>11.334</v>
       </c>
       <c r="H253" t="n">
-        <v>4421.0</v>
+        <v>4419.0</v>
       </c>
       <c r="I253" t="n">
         <v>0.0</v>
@@ -9673,7 +9673,7 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>755.6</v>
+        <v>768.4</v>
       </c>
       <c r="F260" t="n">
         <v>5.4</v>
@@ -9682,7 +9682,7 @@
         <v>8.0</v>
       </c>
       <c r="H260" t="n">
-        <v>755.6</v>
+        <v>768.4</v>
       </c>
       <c r="I260" t="n">
         <v>0.0</v>
@@ -9747,7 +9747,7 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>311.467</v>
+        <v>311.32800000000003</v>
       </c>
       <c r="F262" t="n">
         <v>0.0</v>
@@ -9756,7 +9756,7 @@
         <v>604.1959999999999</v>
       </c>
       <c r="H262" t="n">
-        <v>311.467</v>
+        <v>311.32800000000003</v>
       </c>
       <c r="I262" t="n">
         <v>0.0</v>
@@ -9784,7 +9784,7 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>374.4</v>
+        <v>373.79999999999995</v>
       </c>
       <c r="F263" t="n">
         <v>0.6</v>
@@ -9793,7 +9793,7 @@
         <v>8.0</v>
       </c>
       <c r="H263" t="n">
-        <v>374.4</v>
+        <v>373.79999999999995</v>
       </c>
       <c r="I263" t="n">
         <v>0.0</v>
@@ -9821,7 +9821,7 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>6353.017</v>
+        <v>6341.326</v>
       </c>
       <c r="F264" t="n">
         <v>1.59</v>
@@ -9830,7 +9830,7 @@
         <v>62.620999999999995</v>
       </c>
       <c r="H264" t="n">
-        <v>6353.017</v>
+        <v>6341.326</v>
       </c>
       <c r="I264" t="n">
         <v>0.0</v>
@@ -9858,7 +9858,7 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>3489.682</v>
+        <v>3480.047</v>
       </c>
       <c r="F265" t="n">
         <v>3.979</v>
@@ -9867,7 +9867,7 @@
         <v>124.306</v>
       </c>
       <c r="H265" t="n">
-        <v>3489.682</v>
+        <v>3480.047</v>
       </c>
       <c r="I265" t="n">
         <v>0.0</v>
@@ -9895,7 +9895,7 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>3321.742</v>
+        <v>3327.261</v>
       </c>
       <c r="F266" t="n">
         <v>3.367</v>
@@ -9904,7 +9904,7 @@
         <v>145.07</v>
       </c>
       <c r="H266" t="n">
-        <v>3321.742</v>
+        <v>3327.261</v>
       </c>
       <c r="I266" t="n">
         <v>0.0</v>
@@ -10117,7 +10117,7 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>4351.924</v>
+        <v>16.802</v>
       </c>
       <c r="F272" t="n">
         <v>0.0</v>
@@ -10126,7 +10126,7 @@
         <v>138.623</v>
       </c>
       <c r="H272" t="n">
-        <v>4351.924</v>
+        <v>16.802</v>
       </c>
       <c r="I272" t="n">
         <v>0.0</v>
@@ -10302,7 +10302,7 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>326.402</v>
+        <v>325.882</v>
       </c>
       <c r="F277" t="n">
         <v>0.04</v>
@@ -10311,7 +10311,7 @@
         <v>3.8400000000000003</v>
       </c>
       <c r="H277" t="n">
-        <v>326.402</v>
+        <v>325.882</v>
       </c>
       <c r="I277" t="n">
         <v>0.0</v>
@@ -10376,7 +10376,7 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>590.199</v>
+        <v>585.3190000000001</v>
       </c>
       <c r="F279" t="n">
         <v>0.08</v>
@@ -10385,7 +10385,7 @@
         <v>0.0</v>
       </c>
       <c r="H279" t="n">
-        <v>590.199</v>
+        <v>585.3190000000001</v>
       </c>
       <c r="I279" t="n">
         <v>0.0</v>
@@ -10524,7 +10524,7 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>3355.268</v>
+        <v>3108.583</v>
       </c>
       <c r="F283" t="n">
         <v>0.0</v>
@@ -10533,7 +10533,7 @@
         <v>18.752000000000002</v>
       </c>
       <c r="H283" t="n">
-        <v>3355.268</v>
+        <v>3108.583</v>
       </c>
       <c r="I283" t="n">
         <v>0.0</v>
@@ -10561,7 +10561,7 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>2521.2</v>
+        <v>2463.6</v>
       </c>
       <c r="F284" t="n">
         <v>0.0</v>
@@ -10570,7 +10570,7 @@
         <v>194.39999999999998</v>
       </c>
       <c r="H284" t="n">
-        <v>2521.2</v>
+        <v>2463.6</v>
       </c>
       <c r="I284" t="n">
         <v>0.0</v>
@@ -10598,7 +10598,7 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>4649.0</v>
+        <v>4474.8</v>
       </c>
       <c r="F285" t="n">
         <v>0.2</v>
@@ -10607,7 +10607,7 @@
         <v>84.0</v>
       </c>
       <c r="H285" t="n">
-        <v>4649.0</v>
+        <v>4474.8</v>
       </c>
       <c r="I285" t="n">
         <v>0.0</v>
@@ -10635,7 +10635,7 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>1854.036</v>
+        <v>1562.51</v>
       </c>
       <c r="F286" t="n">
         <v>2.222</v>
@@ -10644,7 +10644,7 @@
         <v>18.665000000000003</v>
       </c>
       <c r="H286" t="n">
-        <v>1854.036</v>
+        <v>1562.51</v>
       </c>
       <c r="I286" t="n">
         <v>0.0</v>
@@ -10672,7 +10672,7 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>4922.396</v>
+        <v>4920.84</v>
       </c>
       <c r="F287" t="n">
         <v>0.444</v>
@@ -10681,7 +10681,7 @@
         <v>383.96200000000005</v>
       </c>
       <c r="H287" t="n">
-        <v>4922.396</v>
+        <v>4920.84</v>
       </c>
       <c r="I287" t="n">
         <v>0.0</v>
@@ -10709,7 +10709,7 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>1272.318</v>
+        <v>1208.3239999999998</v>
       </c>
       <c r="F288" t="n">
         <v>0.889</v>
@@ -10718,7 +10718,7 @@
         <v>0.0</v>
       </c>
       <c r="H288" t="n">
-        <v>1272.318</v>
+        <v>1208.3239999999998</v>
       </c>
       <c r="I288" t="n">
         <v>0.0</v>
@@ -10746,7 +10746,7 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>3368.997</v>
+        <v>3294.338</v>
       </c>
       <c r="F289" t="n">
         <v>0.0</v>
@@ -10755,7 +10755,7 @@
         <v>351.965</v>
       </c>
       <c r="H289" t="n">
-        <v>3368.997</v>
+        <v>3294.338</v>
       </c>
       <c r="I289" t="n">
         <v>0.0</v>
@@ -11116,7 +11116,7 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>1626.0</v>
+        <v>1619.0</v>
       </c>
       <c r="F299" t="n">
         <v>0.8</v>
@@ -11125,7 +11125,7 @@
         <v>134.4</v>
       </c>
       <c r="H299" t="n">
-        <v>1626.0</v>
+        <v>1619.0</v>
       </c>
       <c r="I299" t="n">
         <v>0.0</v>
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>4854.0</v>
+        <v>4793.2</v>
       </c>
       <c r="F300" t="n">
         <v>2.4</v>
@@ -11162,7 +11162,7 @@
         <v>333.0</v>
       </c>
       <c r="H300" t="n">
-        <v>4854.0</v>
+        <v>4793.2</v>
       </c>
       <c r="I300" t="n">
         <v>0.0</v>
@@ -11190,7 +11190,7 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>218.8</v>
+        <v>194.2</v>
       </c>
       <c r="F301" t="n">
         <v>1.0</v>
@@ -11199,7 +11199,7 @@
         <v>136.8</v>
       </c>
       <c r="H301" t="n">
-        <v>218.8</v>
+        <v>194.2</v>
       </c>
       <c r="I301" t="n">
         <v>0.0</v>
@@ -11227,7 +11227,7 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>733.8</v>
+        <v>703.8</v>
       </c>
       <c r="F302" t="n">
         <v>0.2</v>
@@ -11236,7 +11236,7 @@
         <v>0.0</v>
       </c>
       <c r="H302" t="n">
-        <v>733.8</v>
+        <v>703.8</v>
       </c>
       <c r="I302" t="n">
         <v>0.0</v>
@@ -11375,7 +11375,7 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>5637.514</v>
+        <v>5636.981</v>
       </c>
       <c r="F306" t="n">
         <v>1.067</v>
@@ -11384,7 +11384,7 @@
         <v>0.0</v>
       </c>
       <c r="H306" t="n">
-        <v>5637.514</v>
+        <v>5636.981</v>
       </c>
       <c r="I306" t="n">
         <v>0.0</v>
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="F314" t="n">
         <v>14.200000000000001</v>
@@ -11680,7 +11680,7 @@
         <v>121.6</v>
       </c>
       <c r="H314" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="I314" t="n">
         <v>0.0</v>
@@ -11708,7 +11708,7 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>5002.0</v>
+        <v>4974.8</v>
       </c>
       <c r="F315" t="n">
         <v>0.0</v>
@@ -11717,7 +11717,7 @@
         <v>166.4</v>
       </c>
       <c r="H315" t="n">
-        <v>5002.0</v>
+        <v>4974.8</v>
       </c>
       <c r="I315" t="n">
         <v>0.0</v>
@@ -11856,7 +11856,7 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>2792.892</v>
+        <v>2792.359</v>
       </c>
       <c r="F319" t="n">
         <v>0.0</v>
@@ -11865,7 +11865,7 @@
         <v>0.0</v>
       </c>
       <c r="H319" t="n">
-        <v>2792.892</v>
+        <v>2792.359</v>
       </c>
       <c r="I319" t="n">
         <v>0.0</v>
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>12542.634</v>
+        <v>12541.833999999999</v>
       </c>
       <c r="F320" t="n">
         <v>0.533</v>
@@ -11902,7 +11902,7 @@
         <v>0.0</v>
       </c>
       <c r="H320" t="n">
-        <v>12542.634</v>
+        <v>12541.833999999999</v>
       </c>
       <c r="I320" t="n">
         <v>0.0</v>
@@ -11967,7 +11967,7 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>1722.3999999999999</v>
+        <v>1491.6000000000001</v>
       </c>
       <c r="F322" t="n">
         <v>0.6</v>
@@ -11976,7 +11976,7 @@
         <v>6.4</v>
       </c>
       <c r="H322" t="n">
-        <v>1722.3999999999999</v>
+        <v>1491.6000000000001</v>
       </c>
       <c r="I322" t="n">
         <v>0.0</v>
@@ -12041,7 +12041,7 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>5311.597</v>
+        <v>5311.064</v>
       </c>
       <c r="F324" t="n">
         <v>0.533</v>
@@ -12050,7 +12050,7 @@
         <v>0.0</v>
       </c>
       <c r="H324" t="n">
-        <v>5311.597</v>
+        <v>5311.064</v>
       </c>
       <c r="I324" t="n">
         <v>0.0</v>
@@ -12078,7 +12078,7 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>2354.6</v>
+        <v>2257.2000000000003</v>
       </c>
       <c r="F325" t="n">
         <v>1.4</v>
@@ -12087,7 +12087,7 @@
         <v>45.6</v>
       </c>
       <c r="H325" t="n">
-        <v>2354.6</v>
+        <v>2257.2000000000003</v>
       </c>
       <c r="I325" t="n">
         <v>0.0</v>
@@ -12300,7 +12300,7 @@
         </is>
       </c>
       <c r="E331" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="F331" t="n">
         <v>6.0</v>
@@ -12309,7 +12309,7 @@
         <v>0.0</v>
       </c>
       <c r="H331" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="I331" t="n">
         <v>0.0</v>
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>3474.96</v>
+        <v>3400.32</v>
       </c>
       <c r="F334" t="n">
         <v>0.0</v>
@@ -12420,7 +12420,7 @@
         <v>77.75999999999999</v>
       </c>
       <c r="H334" t="n">
-        <v>3474.96</v>
+        <v>3400.32</v>
       </c>
       <c r="I334" t="n">
         <v>0.0</v>
@@ -12448,7 +12448,7 @@
         </is>
       </c>
       <c r="E335" t="n">
-        <v>3486.602</v>
+        <v>3455.327</v>
       </c>
       <c r="F335" t="n">
         <v>0.45</v>
@@ -12457,7 +12457,7 @@
         <v>39.375</v>
       </c>
       <c r="H335" t="n">
-        <v>3486.602</v>
+        <v>3455.327</v>
       </c>
       <c r="I335" t="n">
         <v>0.0</v>
@@ -12485,7 +12485,7 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>3080.019</v>
+        <v>3008.4240000000004</v>
       </c>
       <c r="F336" t="n">
         <v>0.0</v>
@@ -12494,7 +12494,7 @@
         <v>88.245</v>
       </c>
       <c r="H336" t="n">
-        <v>3080.019</v>
+        <v>3008.4240000000004</v>
       </c>
       <c r="I336" t="n">
         <v>0.0</v>
@@ -12818,7 +12818,7 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>581.5</v>
+        <v>569.5</v>
       </c>
       <c r="F345" t="n">
         <v>0.0</v>
@@ -12827,7 +12827,7 @@
         <v>0.0</v>
       </c>
       <c r="H345" t="n">
-        <v>581.5</v>
+        <v>569.5</v>
       </c>
       <c r="I345" t="n">
         <v>0.0</v>
@@ -13003,7 +13003,7 @@
         </is>
       </c>
       <c r="E350" t="n">
-        <v>504.0</v>
+        <v>472.0</v>
       </c>
       <c r="F350" t="n">
         <v>0.0</v>
@@ -13012,7 +13012,7 @@
         <v>579.0</v>
       </c>
       <c r="H350" t="n">
-        <v>504.0</v>
+        <v>472.0</v>
       </c>
       <c r="I350" t="n">
         <v>0.0</v>
@@ -13410,7 +13410,7 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>424.853</v>
+        <v>416.852</v>
       </c>
       <c r="F361" t="n">
         <v>19.202</v>
@@ -13419,7 +13419,7 @@
         <v>0.0</v>
       </c>
       <c r="H361" t="n">
-        <v>424.853</v>
+        <v>416.852</v>
       </c>
       <c r="I361" t="n">
         <v>0.0</v>
@@ -13521,7 +13521,7 @@
         </is>
       </c>
       <c r="E364" t="n">
-        <v>1471.842</v>
+        <v>1471.843</v>
       </c>
       <c r="F364" t="n">
         <v>0.0</v>
@@ -13530,7 +13530,7 @@
         <v>0.0</v>
       </c>
       <c r="H364" t="n">
-        <v>1471.842</v>
+        <v>1471.843</v>
       </c>
       <c r="I364" t="n">
         <v>0.0</v>
@@ -13558,7 +13558,7 @@
         </is>
       </c>
       <c r="E365" t="n">
-        <v>23856.011</v>
+        <v>23802.635</v>
       </c>
       <c r="F365" t="n">
         <v>0.111</v>
@@ -13567,7 +13567,7 @@
         <v>37.03</v>
       </c>
       <c r="H365" t="n">
-        <v>23856.011</v>
+        <v>23802.635</v>
       </c>
       <c r="I365" t="n">
         <v>0.0</v>
@@ -13595,7 +13595,7 @@
         </is>
       </c>
       <c r="E366" t="n">
-        <v>3134.353</v>
+        <v>3435.656</v>
       </c>
       <c r="F366" t="n">
         <v>0.0</v>
@@ -13604,7 +13604,7 @@
         <v>8503.482999999998</v>
       </c>
       <c r="H366" t="n">
-        <v>3134.353</v>
+        <v>3435.656</v>
       </c>
       <c r="I366" t="n">
         <v>0.0</v>
@@ -13669,7 +13669,7 @@
         </is>
       </c>
       <c r="E368" t="n">
-        <v>392.314</v>
+        <v>325.594</v>
       </c>
       <c r="F368" t="n">
         <v>0.0</v>
@@ -13678,7 +13678,7 @@
         <v>16.458000000000002</v>
       </c>
       <c r="H368" t="n">
-        <v>392.314</v>
+        <v>325.594</v>
       </c>
       <c r="I368" t="n">
         <v>0.0</v>
@@ -14224,7 +14224,7 @@
         </is>
       </c>
       <c r="E383" t="n">
-        <v>1732.488</v>
+        <v>1721.832</v>
       </c>
       <c r="F383" t="n">
         <v>0.0</v>
@@ -14233,7 +14233,7 @@
         <v>37.296</v>
       </c>
       <c r="H383" t="n">
-        <v>1732.488</v>
+        <v>1721.832</v>
       </c>
       <c r="I383" t="n">
         <v>0.0</v>
@@ -14298,7 +14298,7 @@
         </is>
       </c>
       <c r="E385" t="n">
-        <v>820.1690000000001</v>
+        <v>819.8910000000001</v>
       </c>
       <c r="F385" t="n">
         <v>0.0</v>
@@ -14307,7 +14307,7 @@
         <v>30.12</v>
       </c>
       <c r="H385" t="n">
-        <v>820.1690000000001</v>
+        <v>819.8910000000001</v>
       </c>
       <c r="I385" t="n">
         <v>0.0</v>
@@ -14335,7 +14335,7 @@
         </is>
       </c>
       <c r="E386" t="n">
-        <v>0.222</v>
+        <v>32.224000000000004</v>
       </c>
       <c r="F386" t="n">
         <v>53.336</v>
@@ -14344,7 +14344,7 @@
         <v>545.361</v>
       </c>
       <c r="H386" t="n">
-        <v>0.222</v>
+        <v>32.224000000000004</v>
       </c>
       <c r="I386" t="n">
         <v>0.0</v>
@@ -14409,7 +14409,7 @@
         </is>
       </c>
       <c r="E388" t="n">
-        <v>373.06600000000003</v>
+        <v>363.466</v>
       </c>
       <c r="F388" t="n">
         <v>40.0</v>
@@ -14418,7 +14418,7 @@
         <v>30.4</v>
       </c>
       <c r="H388" t="n">
-        <v>373.06600000000003</v>
+        <v>363.466</v>
       </c>
       <c r="I388" t="n">
         <v>0.0</v>
@@ -14557,7 +14557,7 @@
         </is>
       </c>
       <c r="E392" t="n">
-        <v>27.0</v>
+        <v>36.0</v>
       </c>
       <c r="F392" t="n">
         <v>0.0</v>
@@ -14566,7 +14566,7 @@
         <v>0.0</v>
       </c>
       <c r="H392" t="n">
-        <v>27.0</v>
+        <v>36.0</v>
       </c>
       <c r="I392" t="n">
         <v>0.0</v>
@@ -15223,7 +15223,7 @@
         </is>
       </c>
       <c r="E410" t="n">
-        <v>3205.299</v>
+        <v>3203.5989999999997</v>
       </c>
       <c r="F410" t="n">
         <v>0.2</v>
@@ -15232,7 +15232,7 @@
         <v>74.39999999999999</v>
       </c>
       <c r="H410" t="n">
-        <v>3205.299</v>
+        <v>3203.5989999999997</v>
       </c>
       <c r="I410" t="n">
         <v>0.0</v>
@@ -15260,7 +15260,7 @@
         </is>
       </c>
       <c r="E411" t="n">
-        <v>2588.05</v>
+        <v>2580.5</v>
       </c>
       <c r="F411" t="n">
         <v>0.0</v>
@@ -15269,7 +15269,7 @@
         <v>180.10000000000002</v>
       </c>
       <c r="H411" t="n">
-        <v>2588.05</v>
+        <v>2580.5</v>
       </c>
       <c r="I411" t="n">
         <v>0.0</v>
@@ -15297,7 +15297,7 @@
         </is>
       </c>
       <c r="E412" t="n">
-        <v>1110.7</v>
+        <v>1117.85</v>
       </c>
       <c r="F412" t="n">
         <v>0.15</v>
@@ -15306,7 +15306,7 @@
         <v>101.1</v>
       </c>
       <c r="H412" t="n">
-        <v>1110.7</v>
+        <v>1117.85</v>
       </c>
       <c r="I412" t="n">
         <v>0.0</v>
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="E413" t="n">
-        <v>1800.8500000000001</v>
+        <v>1779.55</v>
       </c>
       <c r="F413" t="n">
         <v>0.0</v>
@@ -15343,7 +15343,7 @@
         <v>163.5</v>
       </c>
       <c r="H413" t="n">
-        <v>1800.8500000000001</v>
+        <v>1779.55</v>
       </c>
       <c r="I413" t="n">
         <v>0.0</v>
@@ -15371,7 +15371,7 @@
         </is>
       </c>
       <c r="E414" t="n">
-        <v>2882.8500000000004</v>
+        <v>2825.7999999999997</v>
       </c>
       <c r="F414" t="n">
         <v>0.15</v>
@@ -15380,7 +15380,7 @@
         <v>31.2</v>
       </c>
       <c r="H414" t="n">
-        <v>2882.8500000000004</v>
+        <v>2825.7999999999997</v>
       </c>
       <c r="I414" t="n">
         <v>0.0</v>
@@ -15408,7 +15408,7 @@
         </is>
       </c>
       <c r="E415" t="n">
-        <v>3293.9500000000003</v>
+        <v>3235.1</v>
       </c>
       <c r="F415" t="n">
         <v>0.1</v>
@@ -15417,7 +15417,7 @@
         <v>0.0</v>
       </c>
       <c r="H415" t="n">
-        <v>3293.9500000000003</v>
+        <v>3235.1</v>
       </c>
       <c r="I415" t="n">
         <v>0.0</v>
@@ -15445,7 +15445,7 @@
         </is>
       </c>
       <c r="E416" t="n">
-        <v>10553.701</v>
+        <v>10570.101</v>
       </c>
       <c r="F416" t="n">
         <v>0.3</v>
@@ -15454,7 +15454,7 @@
         <v>0.0</v>
       </c>
       <c r="H416" t="n">
-        <v>10553.701</v>
+        <v>10570.101</v>
       </c>
       <c r="I416" t="n">
         <v>0.0</v>
@@ -15815,7 +15815,7 @@
         </is>
       </c>
       <c r="E426" t="n">
-        <v>428.4</v>
+        <v>356.4</v>
       </c>
       <c r="F426" t="n">
         <v>0.0</v>
@@ -15824,7 +15824,7 @@
         <v>0.0</v>
       </c>
       <c r="H426" t="n">
-        <v>428.4</v>
+        <v>356.4</v>
       </c>
       <c r="I426" t="n">
         <v>0.0</v>
@@ -16148,7 +16148,7 @@
         </is>
       </c>
       <c r="E435" t="n">
-        <v>1194.402</v>
+        <v>1167.102</v>
       </c>
       <c r="F435" t="n">
         <v>61.196</v>
@@ -16157,7 +16157,7 @@
         <v>4.107</v>
       </c>
       <c r="H435" t="n">
-        <v>1194.402</v>
+        <v>1167.102</v>
       </c>
       <c r="I435" t="n">
         <v>0.0</v>
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="E436" t="n">
-        <v>1962.5720000000001</v>
+        <v>1746.077</v>
       </c>
       <c r="F436" t="n">
         <v>191.516</v>
@@ -16194,7 +16194,7 @@
         <v>2.054</v>
       </c>
       <c r="H436" t="n">
-        <v>1962.5720000000001</v>
+        <v>1746.077</v>
       </c>
       <c r="I436" t="n">
         <v>0.0</v>
@@ -16222,7 +16222,7 @@
         </is>
       </c>
       <c r="E437" t="n">
-        <v>547.501</v>
+        <v>174.117</v>
       </c>
       <c r="F437" t="n">
         <v>0.0</v>
@@ -16231,7 +16231,7 @@
         <v>511.55799999999994</v>
       </c>
       <c r="H437" t="n">
-        <v>547.501</v>
+        <v>174.117</v>
       </c>
       <c r="I437" t="n">
         <v>0.0</v>
@@ -16259,7 +16259,7 @@
         </is>
       </c>
       <c r="E438" t="n">
-        <v>2163.49</v>
+        <v>2167.085</v>
       </c>
       <c r="F438" t="n">
         <v>0.0</v>
@@ -16268,7 +16268,7 @@
         <v>2.054</v>
       </c>
       <c r="H438" t="n">
-        <v>2163.49</v>
+        <v>2167.085</v>
       </c>
       <c r="I438" t="n">
         <v>0.0</v>
@@ -16296,7 +16296,7 @@
         </is>
       </c>
       <c r="E439" t="n">
-        <v>822.876</v>
+        <v>805.605</v>
       </c>
       <c r="F439" t="n">
         <v>0.0</v>
@@ -16305,7 +16305,7 @@
         <v>395.806</v>
       </c>
       <c r="H439" t="n">
-        <v>822.876</v>
+        <v>805.605</v>
       </c>
       <c r="I439" t="n">
         <v>0.0</v>
@@ -16333,7 +16333,7 @@
         </is>
       </c>
       <c r="E440" t="n">
-        <v>8142.402</v>
+        <v>8263.464</v>
       </c>
       <c r="F440" t="n">
         <v>444.002</v>
@@ -16342,7 +16342,7 @@
         <v>30.047</v>
       </c>
       <c r="H440" t="n">
-        <v>8142.402</v>
+        <v>8263.464</v>
       </c>
       <c r="I440" t="n">
         <v>0.0</v>
@@ -16407,7 +16407,7 @@
         </is>
       </c>
       <c r="E442" t="n">
-        <v>2513.908</v>
+        <v>2492.4359999999997</v>
       </c>
       <c r="F442" t="n">
         <v>0.0</v>
@@ -16416,7 +16416,7 @@
         <v>191.83700000000002</v>
       </c>
       <c r="H442" t="n">
-        <v>2513.908</v>
+        <v>2492.4359999999997</v>
       </c>
       <c r="I442" t="n">
         <v>0.0</v>
@@ -16444,7 +16444,7 @@
         </is>
       </c>
       <c r="E443" t="n">
-        <v>10084.601</v>
+        <v>10046.327000000001</v>
       </c>
       <c r="F443" t="n">
         <v>6.069</v>
@@ -16453,7 +16453,7 @@
         <v>148.894</v>
       </c>
       <c r="H443" t="n">
-        <v>10084.601</v>
+        <v>10046.327000000001</v>
       </c>
       <c r="I443" t="n">
         <v>0.0</v>
@@ -16481,7 +16481,7 @@
         </is>
       </c>
       <c r="E444" t="n">
-        <v>17365.898</v>
+        <v>17340.227000000003</v>
       </c>
       <c r="F444" t="n">
         <v>3.733</v>
@@ -16490,7 +16490,7 @@
         <v>50.879</v>
       </c>
       <c r="H444" t="n">
-        <v>17365.898</v>
+        <v>17340.227000000003</v>
       </c>
       <c r="I444" t="n">
         <v>0.0</v>
@@ -16518,7 +16518,7 @@
         </is>
       </c>
       <c r="E445" t="n">
-        <v>3862.038</v>
+        <v>3931.176</v>
       </c>
       <c r="F445" t="n">
         <v>213.82899999999998</v>
@@ -16527,7 +16527,7 @@
         <v>71.762</v>
       </c>
       <c r="H445" t="n">
-        <v>3862.038</v>
+        <v>3931.176</v>
       </c>
       <c r="I445" t="n">
         <v>0.0</v>
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="E446" t="n">
-        <v>2191.0820000000003</v>
+        <v>2184.958</v>
       </c>
       <c r="F446" t="n">
         <v>294.922</v>
@@ -16564,7 +16564,7 @@
         <v>79.056</v>
       </c>
       <c r="H446" t="n">
-        <v>2191.0820000000003</v>
+        <v>2184.958</v>
       </c>
       <c r="I446" t="n">
         <v>0.0</v>
@@ -16666,7 +16666,7 @@
         </is>
       </c>
       <c r="E449" t="n">
-        <v>1100.0600000000002</v>
+        <v>1095.6850000000002</v>
       </c>
       <c r="F449" t="n">
         <v>0.0</v>
@@ -16675,7 +16675,7 @@
         <v>73.80499999999999</v>
       </c>
       <c r="H449" t="n">
-        <v>1100.0600000000002</v>
+        <v>1095.6850000000002</v>
       </c>
       <c r="I449" t="n">
         <v>0.0</v>
@@ -16703,7 +16703,7 @@
         </is>
       </c>
       <c r="E450" t="n">
-        <v>7900.558</v>
+        <v>7851.549</v>
       </c>
       <c r="F450" t="n">
         <v>380.69399999999996</v>
@@ -16712,7 +16712,7 @@
         <v>0.292</v>
       </c>
       <c r="H450" t="n">
-        <v>7900.558</v>
+        <v>7851.549</v>
       </c>
       <c r="I450" t="n">
         <v>0.0</v>
@@ -16740,7 +16740,7 @@
         </is>
       </c>
       <c r="E451" t="n">
-        <v>1627.1750000000002</v>
+        <v>1603.839</v>
       </c>
       <c r="F451" t="n">
         <v>0.0</v>
@@ -16749,7 +16749,7 @@
         <v>19.253</v>
       </c>
       <c r="H451" t="n">
-        <v>1627.1750000000002</v>
+        <v>1603.839</v>
       </c>
       <c r="I451" t="n">
         <v>0.0</v>
@@ -16814,7 +16814,7 @@
         </is>
       </c>
       <c r="E453" t="n">
-        <v>3285.267</v>
+        <v>3345.942</v>
       </c>
       <c r="F453" t="n">
         <v>0.0</v>
@@ -16823,7 +16823,7 @@
         <v>0.0</v>
       </c>
       <c r="H453" t="n">
-        <v>3285.267</v>
+        <v>3345.942</v>
       </c>
       <c r="I453" t="n">
         <v>0.0</v>
@@ -17295,7 +17295,7 @@
         </is>
       </c>
       <c r="E466" t="n">
-        <v>247.351</v>
+        <v>246.41799999999998</v>
       </c>
       <c r="F466" t="n">
         <v>0.0</v>
@@ -17304,7 +17304,7 @@
         <v>0.0</v>
       </c>
       <c r="H466" t="n">
-        <v>247.351</v>
+        <v>246.41799999999998</v>
       </c>
       <c r="I466" t="n">
         <v>0.0</v>
@@ -17480,7 +17480,7 @@
         </is>
       </c>
       <c r="E471" t="n">
-        <v>1710.668</v>
+        <v>1658.672</v>
       </c>
       <c r="F471" t="n">
         <v>135.19</v>
@@ -17489,7 +17489,7 @@
         <v>561.557</v>
       </c>
       <c r="H471" t="n">
-        <v>1710.668</v>
+        <v>1658.672</v>
       </c>
       <c r="I471" t="n">
         <v>0.0</v>
@@ -17517,7 +17517,7 @@
         </is>
       </c>
       <c r="E472" t="n">
-        <v>24.002</v>
+        <v>114.011</v>
       </c>
       <c r="F472" t="n">
         <v>0.0</v>
@@ -17526,7 +17526,7 @@
         <v>78.008</v>
       </c>
       <c r="H472" t="n">
-        <v>24.002</v>
+        <v>114.011</v>
       </c>
       <c r="I472" t="n">
         <v>0.0</v>
@@ -17554,7 +17554,7 @@
         </is>
       </c>
       <c r="E473" t="n">
-        <v>4931.493</v>
+        <v>4871.486</v>
       </c>
       <c r="F473" t="n">
         <v>0.0</v>
@@ -17563,7 +17563,7 @@
         <v>642.064</v>
       </c>
       <c r="H473" t="n">
-        <v>4931.493</v>
+        <v>4871.486</v>
       </c>
       <c r="I473" t="n">
         <v>0.0</v>
@@ -17665,7 +17665,7 @@
         </is>
       </c>
       <c r="E476" t="n">
-        <v>716.0640000000001</v>
+        <v>717.977</v>
       </c>
       <c r="F476" t="n">
         <v>1.125</v>
@@ -17674,7 +17674,7 @@
         <v>85.725</v>
       </c>
       <c r="H476" t="n">
-        <v>716.0640000000001</v>
+        <v>717.977</v>
       </c>
       <c r="I476" t="n">
         <v>0.0</v>
@@ -17702,7 +17702,7 @@
         </is>
       </c>
       <c r="E477" t="n">
-        <v>1848.263</v>
+        <v>1842.863</v>
       </c>
       <c r="F477" t="n">
         <v>0.0</v>
@@ -17711,7 +17711,7 @@
         <v>105.30000000000001</v>
       </c>
       <c r="H477" t="n">
-        <v>1848.263</v>
+        <v>1842.863</v>
       </c>
       <c r="I477" t="n">
         <v>0.0</v>
@@ -17813,7 +17813,7 @@
         </is>
       </c>
       <c r="E480" t="n">
-        <v>155.724</v>
+        <v>145.13299999999998</v>
       </c>
       <c r="F480" t="n">
         <v>0.13899999999999998</v>
@@ -17822,7 +17822,7 @@
         <v>582.75</v>
       </c>
       <c r="H480" t="n">
-        <v>155.724</v>
+        <v>145.13299999999998</v>
       </c>
       <c r="I480" t="n">
         <v>0.0</v>
@@ -17850,7 +17850,7 @@
         </is>
       </c>
       <c r="E481" t="n">
-        <v>1771.4</v>
+        <v>1742.84</v>
       </c>
       <c r="F481" t="n">
         <v>0.12000000000000001</v>
@@ -17859,7 +17859,7 @@
         <v>178.07999999999998</v>
       </c>
       <c r="H481" t="n">
-        <v>1771.4</v>
+        <v>1742.84</v>
       </c>
       <c r="I481" t="n">
         <v>0.0</v>
@@ -17887,7 +17887,7 @@
         </is>
       </c>
       <c r="E482" t="n">
-        <v>144.24</v>
+        <v>84.921</v>
       </c>
       <c r="F482" t="n">
         <v>0.0</v>
@@ -17896,7 +17896,7 @@
         <v>708.0</v>
       </c>
       <c r="H482" t="n">
-        <v>144.24</v>
+        <v>84.921</v>
       </c>
       <c r="I482" t="n">
         <v>0.0</v>
@@ -17924,7 +17924,7 @@
         </is>
       </c>
       <c r="E483" t="n">
-        <v>1969.648</v>
+        <v>1966.0410000000002</v>
       </c>
       <c r="F483" t="n">
         <v>0.13899999999999998</v>
@@ -17933,7 +17933,7 @@
         <v>5.55</v>
       </c>
       <c r="H483" t="n">
-        <v>1969.648</v>
+        <v>1966.0410000000002</v>
       </c>
       <c r="I483" t="n">
         <v>0.0</v>
@@ -17961,7 +17961,7 @@
         </is>
       </c>
       <c r="E484" t="n">
-        <v>222.04</v>
+        <v>219.96</v>
       </c>
       <c r="F484" t="n">
         <v>0.0</v>
@@ -17970,7 +17970,7 @@
         <v>62.4</v>
       </c>
       <c r="H484" t="n">
-        <v>222.04</v>
+        <v>219.96</v>
       </c>
       <c r="I484" t="n">
         <v>0.0</v>
@@ -17998,7 +17998,7 @@
         </is>
       </c>
       <c r="E485" t="n">
-        <v>3094.8179999999998</v>
+        <v>2941.314</v>
       </c>
       <c r="F485" t="n">
         <v>0.231</v>
@@ -18007,7 +18007,7 @@
         <v>155.955</v>
       </c>
       <c r="H485" t="n">
-        <v>3094.8179999999998</v>
+        <v>2941.314</v>
       </c>
       <c r="I485" t="n">
         <v>0.0</v>
@@ -18035,7 +18035,7 @@
         </is>
       </c>
       <c r="E486" t="n">
-        <v>401.6</v>
+        <v>379.84</v>
       </c>
       <c r="F486" t="n">
         <v>0.0</v>
@@ -18044,7 +18044,7 @@
         <v>110.88000000000001</v>
       </c>
       <c r="H486" t="n">
-        <v>401.6</v>
+        <v>379.84</v>
       </c>
       <c r="I486" t="n">
         <v>0.0</v>
@@ -18072,7 +18072,7 @@
         </is>
       </c>
       <c r="E487" t="n">
-        <v>1232.2859999999998</v>
+        <v>1220.77</v>
       </c>
       <c r="F487" t="n">
         <v>0.231</v>
@@ -18081,7 +18081,7 @@
         <v>24.42</v>
       </c>
       <c r="H487" t="n">
-        <v>1232.2859999999998</v>
+        <v>1220.77</v>
       </c>
       <c r="I487" t="n">
         <v>0.0</v>
@@ -18257,7 +18257,7 @@
         </is>
       </c>
       <c r="E492" t="n">
-        <v>11142.723</v>
+        <v>11833.259</v>
       </c>
       <c r="F492" t="n">
         <v>50.336</v>
@@ -18266,7 +18266,7 @@
         <v>5019.250999999999</v>
       </c>
       <c r="H492" t="n">
-        <v>11142.723</v>
+        <v>11833.259</v>
       </c>
       <c r="I492" t="n">
         <v>0.0</v>
@@ -18331,7 +18331,7 @@
         </is>
       </c>
       <c r="E494" t="n">
-        <v>5559.749</v>
+        <v>5508.639</v>
       </c>
       <c r="F494" t="n">
         <v>26.576999999999998</v>
@@ -18340,7 +18340,7 @@
         <v>49.065999999999995</v>
       </c>
       <c r="H494" t="n">
-        <v>5559.749</v>
+        <v>5508.639</v>
       </c>
       <c r="I494" t="n">
         <v>0.0</v>
@@ -18368,7 +18368,7 @@
         </is>
       </c>
       <c r="E495" t="n">
-        <v>4403.6</v>
+        <v>3830.2</v>
       </c>
       <c r="F495" t="n">
         <v>26.8</v>
@@ -18377,7 +18377,7 @@
         <v>340.0</v>
       </c>
       <c r="H495" t="n">
-        <v>4403.6</v>
+        <v>3830.2</v>
       </c>
       <c r="I495" t="n">
         <v>0.0</v>
@@ -18553,7 +18553,7 @@
         </is>
       </c>
       <c r="E500" t="n">
-        <v>1186.8</v>
+        <v>1174.8</v>
       </c>
       <c r="F500" t="n">
         <v>0.0</v>
@@ -18562,7 +18562,7 @@
         <v>0.8</v>
       </c>
       <c r="H500" t="n">
-        <v>1186.8</v>
+        <v>1174.8</v>
       </c>
       <c r="I500" t="n">
         <v>0.0</v>
@@ -19034,7 +19034,7 @@
         </is>
       </c>
       <c r="E513" t="n">
-        <v>3340.3</v>
+        <v>3073.9</v>
       </c>
       <c r="F513" t="n">
         <v>0.0</v>
@@ -19043,7 +19043,7 @@
         <v>6.793</v>
       </c>
       <c r="H513" t="n">
-        <v>3340.3</v>
+        <v>3073.9</v>
       </c>
       <c r="I513" t="n">
         <v>0.0</v>
@@ -19071,7 +19071,7 @@
         </is>
       </c>
       <c r="E514" t="n">
-        <v>898.492</v>
+        <v>892.881</v>
       </c>
       <c r="F514" t="n">
         <v>0.0</v>
@@ -19080,7 +19080,7 @@
         <v>19.855999999999998</v>
       </c>
       <c r="H514" t="n">
-        <v>898.492</v>
+        <v>892.881</v>
       </c>
       <c r="I514" t="n">
         <v>0.0</v>
@@ -19404,7 +19404,7 @@
         </is>
       </c>
       <c r="E523" t="n">
-        <v>900.0</v>
+        <v>840.0</v>
       </c>
       <c r="F523" t="n">
         <v>0.0</v>
@@ -19413,7 +19413,7 @@
         <v>0.0</v>
       </c>
       <c r="H523" t="n">
-        <v>900.0</v>
+        <v>840.0</v>
       </c>
       <c r="I523" t="n">
         <v>0.0</v>
@@ -19959,7 +19959,7 @@
         </is>
       </c>
       <c r="E538" t="n">
-        <v>1080.066</v>
+        <v>1071.257</v>
       </c>
       <c r="F538" t="n">
         <v>43.153</v>
@@ -19968,7 +19968,7 @@
         <v>0.313</v>
       </c>
       <c r="H538" t="n">
-        <v>1080.066</v>
+        <v>1071.257</v>
       </c>
       <c r="I538" t="n">
         <v>0.0</v>
@@ -20033,7 +20033,7 @@
         </is>
       </c>
       <c r="E540" t="n">
-        <v>2139.637</v>
+        <v>2110.0150000000003</v>
       </c>
       <c r="F540" t="n">
         <v>2663.3019999999997</v>
@@ -20042,7 +20042,7 @@
         <v>2297.6549999999997</v>
       </c>
       <c r="H540" t="n">
-        <v>2139.637</v>
+        <v>2110.0150000000003</v>
       </c>
       <c r="I540" t="n">
         <v>0.0</v>
@@ -20403,7 +20403,7 @@
         </is>
       </c>
       <c r="E550" t="n">
-        <v>4811.736999999999</v>
+        <v>4857.409000000001</v>
       </c>
       <c r="F550" t="n">
         <v>25.668</v>
@@ -20412,7 +20412,7 @@
         <v>471.024</v>
       </c>
       <c r="H550" t="n">
-        <v>4811.736999999999</v>
+        <v>4857.409000000001</v>
       </c>
       <c r="I550" t="n">
         <v>0.0</v>
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="E551" t="n">
-        <v>5756.621</v>
+        <v>5437.099</v>
       </c>
       <c r="F551" t="n">
         <v>30.912</v>
@@ -20449,7 +20449,7 @@
         <v>211.041</v>
       </c>
       <c r="H551" t="n">
-        <v>5756.621</v>
+        <v>5437.099</v>
       </c>
       <c r="I551" t="n">
         <v>0.0</v>
@@ -20477,7 +20477,7 @@
         </is>
       </c>
       <c r="E552" t="n">
-        <v>2870.797</v>
+        <v>2801.359</v>
       </c>
       <c r="F552" t="n">
         <v>14.059000000000001</v>
@@ -20486,7 +20486,7 @@
         <v>85.086</v>
       </c>
       <c r="H552" t="n">
-        <v>2870.797</v>
+        <v>2801.359</v>
       </c>
       <c r="I552" t="n">
         <v>0.0</v>
@@ -20810,7 +20810,7 @@
         </is>
       </c>
       <c r="E561" t="n">
-        <v>894.0</v>
+        <v>678.0</v>
       </c>
       <c r="F561" t="n">
         <v>0.0</v>
@@ -20819,7 +20819,7 @@
         <v>0.0</v>
       </c>
       <c r="H561" t="n">
-        <v>894.0</v>
+        <v>678.0</v>
       </c>
       <c r="I561" t="n">
         <v>0.0</v>
@@ -21513,7 +21513,7 @@
         </is>
       </c>
       <c r="E580" t="n">
-        <v>6060.153</v>
+        <v>6093.844999999999</v>
       </c>
       <c r="F580" t="n">
         <v>0.0</v>
@@ -21522,7 +21522,7 @@
         <v>5.539</v>
       </c>
       <c r="H580" t="n">
-        <v>6060.153</v>
+        <v>6093.844999999999</v>
       </c>
       <c r="I580" t="n">
         <v>0.0</v>
@@ -21587,7 +21587,7 @@
         </is>
       </c>
       <c r="E582" t="n">
-        <v>1347.727</v>
+        <v>1344.034</v>
       </c>
       <c r="F582" t="n">
         <v>0.0</v>
@@ -21596,7 +21596,7 @@
         <v>1.846</v>
       </c>
       <c r="H582" t="n">
-        <v>1347.727</v>
+        <v>1344.034</v>
       </c>
       <c r="I582" t="n">
         <v>0.0</v>
@@ -21661,7 +21661,7 @@
         </is>
       </c>
       <c r="E584" t="n">
-        <v>1589.6399999999999</v>
+        <v>1621.2069999999999</v>
       </c>
       <c r="F584" t="n">
         <v>0.0</v>
@@ -21670,7 +21670,7 @@
         <v>0.0</v>
       </c>
       <c r="H584" t="n">
-        <v>1589.6399999999999</v>
+        <v>1621.2069999999999</v>
       </c>
       <c r="I584" t="n">
         <v>0.0</v>
@@ -21698,7 +21698,7 @@
         </is>
       </c>
       <c r="E585" t="n">
-        <v>2012.359</v>
+        <v>2028.05</v>
       </c>
       <c r="F585" t="n">
         <v>0.0</v>
@@ -21707,7 +21707,7 @@
         <v>9.231</v>
       </c>
       <c r="H585" t="n">
-        <v>2012.359</v>
+        <v>2028.05</v>
       </c>
       <c r="I585" t="n">
         <v>0.0</v>
@@ -22068,7 +22068,7 @@
         </is>
       </c>
       <c r="E595" t="n">
-        <v>2650.52</v>
+        <v>2612.061</v>
       </c>
       <c r="F595" t="n">
         <v>0.0</v>
@@ -22077,7 +22077,7 @@
         <v>1050.859</v>
       </c>
       <c r="H595" t="n">
-        <v>2650.52</v>
+        <v>2612.061</v>
       </c>
       <c r="I595" t="n">
         <v>0.0</v>
@@ -22105,7 +22105,7 @@
         </is>
       </c>
       <c r="E596" t="n">
-        <v>862.846</v>
+        <v>484.74899999999997</v>
       </c>
       <c r="F596" t="n">
         <v>0.0</v>
@@ -22114,7 +22114,7 @@
         <v>386.37899999999996</v>
       </c>
       <c r="H596" t="n">
-        <v>862.846</v>
+        <v>484.74899999999997</v>
       </c>
       <c r="I596" t="n">
         <v>0.0</v>
@@ -22216,7 +22216,7 @@
         </is>
       </c>
       <c r="E599" t="n">
-        <v>7432.935</v>
+        <v>7401.28</v>
       </c>
       <c r="F599" t="n">
         <v>2.5149999999999997</v>
@@ -22225,7 +22225,7 @@
         <v>468.626</v>
       </c>
       <c r="H599" t="n">
-        <v>7432.935</v>
+        <v>7401.28</v>
       </c>
       <c r="I599" t="n">
         <v>0.0</v>
@@ -22290,7 +22290,7 @@
         </is>
       </c>
       <c r="E601" t="n">
-        <v>30.62</v>
+        <v>203.692</v>
       </c>
       <c r="F601" t="n">
         <v>0.0</v>
@@ -22299,7 +22299,7 @@
         <v>0.888</v>
       </c>
       <c r="H601" t="n">
-        <v>30.62</v>
+        <v>203.692</v>
       </c>
       <c r="I601" t="n">
         <v>0.0</v>
@@ -22327,7 +22327,7 @@
         </is>
       </c>
       <c r="E602" t="n">
-        <v>737.256</v>
+        <v>633.84</v>
       </c>
       <c r="F602" t="n">
         <v>0.0</v>
@@ -22336,7 +22336,7 @@
         <v>0.5</v>
       </c>
       <c r="H602" t="n">
-        <v>737.256</v>
+        <v>633.84</v>
       </c>
       <c r="I602" t="n">
         <v>0.0</v>
@@ -22364,7 +22364,7 @@
         </is>
       </c>
       <c r="E603" t="n">
-        <v>5755.107999999999</v>
+        <v>5755.64</v>
       </c>
       <c r="F603" t="n">
         <v>1.067</v>
@@ -22373,7 +22373,7 @@
         <v>886.345</v>
       </c>
       <c r="H603" t="n">
-        <v>5755.107999999999</v>
+        <v>5755.64</v>
       </c>
       <c r="I603" t="n">
         <v>0.0</v>
@@ -22845,7 +22845,7 @@
         </is>
       </c>
       <c r="E616" t="n">
-        <v>7250.0</v>
+        <v>7249.0</v>
       </c>
       <c r="F616" t="n">
         <v>0.0</v>
@@ -22854,7 +22854,7 @@
         <v>3.0</v>
       </c>
       <c r="H616" t="n">
-        <v>7250.0</v>
+        <v>7249.0</v>
       </c>
       <c r="I616" t="n">
         <v>0.0</v>
@@ -23511,7 +23511,7 @@
         </is>
       </c>
       <c r="E634" t="n">
-        <v>3827.432</v>
+        <v>3800.76</v>
       </c>
       <c r="F634" t="n">
         <v>0.0</v>
@@ -23520,7 +23520,7 @@
         <v>0.0</v>
       </c>
       <c r="H634" t="n">
-        <v>3827.432</v>
+        <v>3800.76</v>
       </c>
       <c r="I634" t="n">
         <v>0.0</v>
@@ -23955,7 +23955,7 @@
         </is>
       </c>
       <c r="E646" t="n">
-        <v>9639.038</v>
+        <v>10282.2174</v>
       </c>
       <c r="F646" t="n">
         <v>0.0</v>
@@ -23964,10 +23964,10 @@
         <v>25.354000000000003</v>
       </c>
       <c r="H646" t="n">
-        <v>9639.038</v>
+        <v>9627.027</v>
       </c>
       <c r="I646" t="n">
-        <v>0.0</v>
+        <v>655.1904</v>
       </c>
     </row>
     <row r="647">
@@ -23992,7 +23992,7 @@
         </is>
       </c>
       <c r="E647" t="n">
-        <v>1587.2350000000001</v>
+        <v>1582.3020000000001</v>
       </c>
       <c r="F647" t="n">
         <v>0.8</v>
@@ -24001,7 +24001,7 @@
         <v>0.0</v>
       </c>
       <c r="H647" t="n">
-        <v>1587.2350000000001</v>
+        <v>1582.3020000000001</v>
       </c>
       <c r="I647" t="n">
         <v>0.0</v>
@@ -24362,7 +24362,7 @@
         </is>
       </c>
       <c r="E657" t="n">
-        <v>17.077</v>
+        <v>15.693</v>
       </c>
       <c r="F657" t="n">
         <v>0.923</v>
@@ -24371,7 +24371,7 @@
         <v>1524.961</v>
       </c>
       <c r="H657" t="n">
-        <v>17.077</v>
+        <v>15.693</v>
       </c>
       <c r="I657" t="n">
         <v>0.0</v>
@@ -24436,7 +24436,7 @@
         </is>
       </c>
       <c r="E659" t="n">
-        <v>1768.8</v>
+        <v>1557.6</v>
       </c>
       <c r="F659" t="n">
         <v>0.0</v>
@@ -24445,7 +24445,7 @@
         <v>0.0</v>
       </c>
       <c r="H659" t="n">
-        <v>1768.8</v>
+        <v>1557.6</v>
       </c>
       <c r="I659" t="n">
         <v>0.0</v>
@@ -24547,7 +24547,7 @@
         </is>
       </c>
       <c r="E662" t="n">
-        <v>1515.342</v>
+        <v>1569.9270000000001</v>
       </c>
       <c r="F662" t="n">
         <v>1.7730000000000001</v>
@@ -24556,7 +24556,7 @@
         <v>179.285</v>
       </c>
       <c r="H662" t="n">
-        <v>1515.342</v>
+        <v>1569.9270000000001</v>
       </c>
       <c r="I662" t="n">
         <v>0.0</v>
@@ -24584,7 +24584,7 @@
         </is>
       </c>
       <c r="E663" t="n">
-        <v>2246.094</v>
+        <v>2231.892</v>
       </c>
       <c r="F663" t="n">
         <v>0.0</v>
@@ -24593,7 +24593,7 @@
         <v>55.620000000000005</v>
       </c>
       <c r="H663" t="n">
-        <v>2246.094</v>
+        <v>2231.892</v>
       </c>
       <c r="I663" t="n">
         <v>0.0</v>
@@ -25102,7 +25102,7 @@
         </is>
       </c>
       <c r="E677" t="n">
-        <v>12840.406</v>
+        <v>12827.36</v>
       </c>
       <c r="F677" t="n">
         <v>0.0</v>
@@ -25111,7 +25111,7 @@
         <v>3.7279999999999998</v>
       </c>
       <c r="H677" t="n">
-        <v>12840.406</v>
+        <v>12827.36</v>
       </c>
       <c r="I677" t="n">
         <v>0.0</v>
@@ -25176,7 +25176,7 @@
         </is>
       </c>
       <c r="E679" t="n">
-        <v>123.961</v>
+        <v>90.826</v>
       </c>
       <c r="F679" t="n">
         <v>15.383000000000001</v>
@@ -25185,7 +25185,7 @@
         <v>64.19800000000001</v>
       </c>
       <c r="H679" t="n">
-        <v>123.961</v>
+        <v>90.826</v>
       </c>
       <c r="I679" t="n">
         <v>0.0</v>
@@ -25361,7 +25361,7 @@
         </is>
       </c>
       <c r="E684" t="n">
-        <v>2864.2889999999998</v>
+        <v>2880.781</v>
       </c>
       <c r="F684" t="n">
         <v>0.312</v>
@@ -25370,7 +25370,7 @@
         <v>0.0</v>
       </c>
       <c r="H684" t="n">
-        <v>2864.2889999999998</v>
+        <v>2880.781</v>
       </c>
       <c r="I684" t="n">
         <v>0.0</v>
@@ -25398,7 +25398,7 @@
         </is>
       </c>
       <c r="E685" t="n">
-        <v>3664.9170000000004</v>
+        <v>3661.8050000000003</v>
       </c>
       <c r="F685" t="n">
         <v>3734.0</v>
@@ -25407,7 +25407,7 @@
         <v>0.0</v>
       </c>
       <c r="H685" t="n">
-        <v>3664.9170000000004</v>
+        <v>3661.8050000000003</v>
       </c>
       <c r="I685" t="n">
         <v>0.0</v>
@@ -25435,7 +25435,7 @@
         </is>
       </c>
       <c r="E686" t="n">
-        <v>11782.965</v>
+        <v>11656.944</v>
       </c>
       <c r="F686" t="n">
         <v>0.0</v>
@@ -25444,7 +25444,7 @@
         <v>3898.25</v>
       </c>
       <c r="H686" t="n">
-        <v>11782.965</v>
+        <v>11656.944</v>
       </c>
       <c r="I686" t="n">
         <v>0.0</v>
@@ -25953,7 +25953,7 @@
         </is>
       </c>
       <c r="E700" t="n">
-        <v>1282.317</v>
+        <v>1264.581</v>
       </c>
       <c r="F700" t="n">
         <v>0.624</v>
@@ -25962,7 +25962,7 @@
         <v>0.0</v>
       </c>
       <c r="H700" t="n">
-        <v>1282.317</v>
+        <v>1264.581</v>
       </c>
       <c r="I700" t="n">
         <v>0.0</v>
@@ -25990,7 +25990,7 @@
         </is>
       </c>
       <c r="E701" t="n">
-        <v>4436.924</v>
+        <v>4748.713</v>
       </c>
       <c r="F701" t="n">
         <v>26.450000000000003</v>
@@ -25999,7 +25999,7 @@
         <v>5.601</v>
       </c>
       <c r="H701" t="n">
-        <v>4436.924</v>
+        <v>4748.713</v>
       </c>
       <c r="I701" t="n">
         <v>0.0</v>
@@ -26027,7 +26027,7 @@
         </is>
       </c>
       <c r="E702" t="n">
-        <v>7008.403</v>
+        <v>7510.004</v>
       </c>
       <c r="F702" t="n">
         <v>41.385999999999996</v>
@@ -26036,7 +26036,7 @@
         <v>9.334999999999999</v>
       </c>
       <c r="H702" t="n">
-        <v>7008.403</v>
+        <v>7510.004</v>
       </c>
       <c r="I702" t="n">
         <v>0.0</v>
@@ -26064,7 +26064,7 @@
         </is>
       </c>
       <c r="E703" t="n">
-        <v>2599.155</v>
+        <v>2599.154</v>
       </c>
       <c r="F703" t="n">
         <v>0.0</v>
@@ -26073,7 +26073,7 @@
         <v>3.851</v>
       </c>
       <c r="H703" t="n">
-        <v>2599.155</v>
+        <v>2599.154</v>
       </c>
       <c r="I703" t="n">
         <v>0.0</v>
@@ -26212,7 +26212,7 @@
         </is>
       </c>
       <c r="E707" t="n">
-        <v>1867.715</v>
+        <v>1825.895</v>
       </c>
       <c r="F707" t="n">
         <v>0.0</v>
@@ -26221,7 +26221,7 @@
         <v>0.0</v>
       </c>
       <c r="H707" t="n">
-        <v>1867.715</v>
+        <v>1825.895</v>
       </c>
       <c r="I707" t="n">
         <v>0.0</v>
@@ -26249,7 +26249,7 @@
         </is>
       </c>
       <c r="E708" t="n">
-        <v>892.021</v>
+        <v>891.99</v>
       </c>
       <c r="F708" t="n">
         <v>0.0</v>
@@ -26258,7 +26258,7 @@
         <v>2.987</v>
       </c>
       <c r="H708" t="n">
-        <v>892.021</v>
+        <v>891.99</v>
       </c>
       <c r="I708" t="n">
         <v>0.0</v>
@@ -26471,7 +26471,7 @@
         </is>
       </c>
       <c r="E714" t="n">
-        <v>1005.615</v>
+        <v>150.075</v>
       </c>
       <c r="F714" t="n">
         <v>0.0</v>
@@ -26480,7 +26480,7 @@
         <v>0.0</v>
       </c>
       <c r="H714" t="n">
-        <v>1005.615</v>
+        <v>150.075</v>
       </c>
       <c r="I714" t="n">
         <v>0.0</v>
@@ -26582,7 +26582,7 @@
         </is>
       </c>
       <c r="E717" t="n">
-        <v>1308.431</v>
+        <v>1254.0230000000001</v>
       </c>
       <c r="F717" t="n">
         <v>0.0</v>
@@ -26591,7 +26591,7 @@
         <v>153.619</v>
       </c>
       <c r="H717" t="n">
-        <v>1308.431</v>
+        <v>1254.0230000000001</v>
       </c>
       <c r="I717" t="n">
         <v>0.0</v>
@@ -26656,7 +26656,7 @@
         </is>
       </c>
       <c r="E719" t="n">
-        <v>3477.5009999999997</v>
+        <v>2870.491</v>
       </c>
       <c r="F719" t="n">
         <v>0.26699999999999996</v>
@@ -26665,7 +26665,7 @@
         <v>0.0</v>
       </c>
       <c r="H719" t="n">
-        <v>3477.5009999999997</v>
+        <v>2870.491</v>
       </c>
       <c r="I719" t="n">
         <v>0.0</v>
@@ -26693,7 +26693,7 @@
         </is>
       </c>
       <c r="E720" t="n">
-        <v>268.25</v>
+        <v>267.717</v>
       </c>
       <c r="F720" t="n">
         <v>6.4</v>
@@ -26702,7 +26702,7 @@
         <v>3.2</v>
       </c>
       <c r="H720" t="n">
-        <v>268.25</v>
+        <v>267.717</v>
       </c>
       <c r="I720" t="n">
         <v>0.0</v>
@@ -26730,7 +26730,7 @@
         </is>
       </c>
       <c r="E721" t="n">
-        <v>0.533</v>
+        <v>6.401</v>
       </c>
       <c r="F721" t="n">
         <v>0.533</v>
@@ -26739,7 +26739,7 @@
         <v>211.226</v>
       </c>
       <c r="H721" t="n">
-        <v>0.533</v>
+        <v>6.401</v>
       </c>
       <c r="I721" t="n">
         <v>0.0</v>
@@ -26767,7 +26767,7 @@
         </is>
       </c>
       <c r="E722" t="n">
-        <v>2884.619</v>
+        <v>2884.0860000000002</v>
       </c>
       <c r="F722" t="n">
         <v>0.0</v>
@@ -26776,7 +26776,7 @@
         <v>0.0</v>
       </c>
       <c r="H722" t="n">
-        <v>2884.619</v>
+        <v>2884.0860000000002</v>
       </c>
       <c r="I722" t="n">
         <v>0.0</v>
@@ -26804,7 +26804,7 @@
         </is>
       </c>
       <c r="E723" t="n">
-        <v>26193.405</v>
+        <v>26040.32</v>
       </c>
       <c r="F723" t="n">
         <v>2.4</v>
@@ -26813,7 +26813,7 @@
         <v>288.036</v>
       </c>
       <c r="H723" t="n">
-        <v>26193.405</v>
+        <v>26040.32</v>
       </c>
       <c r="I723" t="n">
         <v>0.0</v>
@@ -26841,7 +26841,7 @@
         </is>
       </c>
       <c r="E724" t="n">
-        <v>4159.721</v>
+        <v>4047.174</v>
       </c>
       <c r="F724" t="n">
         <v>2.4</v>
@@ -26850,7 +26850,7 @@
         <v>212.827</v>
       </c>
       <c r="H724" t="n">
-        <v>4159.721</v>
+        <v>4047.174</v>
       </c>
       <c r="I724" t="n">
         <v>0.0</v>
@@ -26878,7 +26878,7 @@
         </is>
       </c>
       <c r="E725" t="n">
-        <v>2693.878</v>
+        <v>2699.382</v>
       </c>
       <c r="F725" t="n">
         <v>0.13899999999999998</v>
@@ -26887,7 +26887,7 @@
         <v>67.155</v>
       </c>
       <c r="H725" t="n">
-        <v>2693.878</v>
+        <v>2699.382</v>
       </c>
       <c r="I725" t="n">
         <v>0.0</v>
@@ -26915,7 +26915,7 @@
         </is>
       </c>
       <c r="E726" t="n">
-        <v>1911.8</v>
+        <v>1891.04</v>
       </c>
       <c r="F726" t="n">
         <v>0.2</v>
@@ -26924,7 +26924,7 @@
         <v>2.8800000000000003</v>
       </c>
       <c r="H726" t="n">
-        <v>1911.8</v>
+        <v>1891.04</v>
       </c>
       <c r="I726" t="n">
         <v>0.0</v>
@@ -26952,7 +26952,7 @@
         </is>
       </c>
       <c r="E727" t="n">
-        <v>3017.025</v>
+        <v>3015.0359999999996</v>
       </c>
       <c r="F727" t="n">
         <v>0.0</v>
@@ -26961,7 +26961,7 @@
         <v>0.555</v>
       </c>
       <c r="H727" t="n">
-        <v>3017.025</v>
+        <v>3015.0359999999996</v>
       </c>
       <c r="I727" t="n">
         <v>0.0</v>
@@ -26989,7 +26989,7 @@
         </is>
       </c>
       <c r="E728" t="n">
-        <v>1720.803</v>
+        <v>1723.683</v>
       </c>
       <c r="F728" t="n">
         <v>0.0</v>
@@ -26998,7 +26998,7 @@
         <v>0.0</v>
       </c>
       <c r="H728" t="n">
-        <v>1720.803</v>
+        <v>1723.683</v>
       </c>
       <c r="I728" t="n">
         <v>0.0</v>
@@ -27285,7 +27285,7 @@
         </is>
       </c>
       <c r="E736" t="n">
-        <v>1148.906</v>
+        <v>930.786</v>
       </c>
       <c r="F736" t="n">
         <v>11.733</v>
@@ -27294,7 +27294,7 @@
         <v>0.0</v>
       </c>
       <c r="H736" t="n">
-        <v>1148.906</v>
+        <v>930.786</v>
       </c>
       <c r="I736" t="n">
         <v>0.0</v>
@@ -27544,7 +27544,7 @@
         </is>
       </c>
       <c r="E743" t="n">
-        <v>2255.559</v>
+        <v>2214.141</v>
       </c>
       <c r="F743" t="n">
         <v>0.0</v>
@@ -27553,7 +27553,7 @@
         <v>162.126</v>
       </c>
       <c r="H743" t="n">
-        <v>2255.559</v>
+        <v>2214.141</v>
       </c>
       <c r="I743" t="n">
         <v>0.0</v>
@@ -27581,7 +27581,7 @@
         </is>
       </c>
       <c r="E744" t="n">
-        <v>907.842</v>
+        <v>994.603</v>
       </c>
       <c r="F744" t="n">
         <v>13.831</v>
@@ -27590,7 +27590,7 @@
         <v>5.029999999999999</v>
       </c>
       <c r="H744" t="n">
-        <v>907.842</v>
+        <v>994.603</v>
       </c>
       <c r="I744" t="n">
         <v>0.0</v>
@@ -27618,7 +27618,7 @@
         </is>
       </c>
       <c r="E745" t="n">
-        <v>916.644</v>
+        <v>894.011</v>
       </c>
       <c r="F745" t="n">
         <v>21.375999999999998</v>
@@ -27627,7 +27627,7 @@
         <v>0.0</v>
       </c>
       <c r="H745" t="n">
-        <v>916.644</v>
+        <v>894.011</v>
       </c>
       <c r="I745" t="n">
         <v>0.0</v>
@@ -27729,7 +27729,7 @@
         </is>
       </c>
       <c r="E748" t="n">
-        <v>1749.064</v>
+        <v>1706.462</v>
       </c>
       <c r="F748" t="n">
         <v>0.0</v>
@@ -27738,7 +27738,7 @@
         <v>177.51</v>
       </c>
       <c r="H748" t="n">
-        <v>1749.064</v>
+        <v>1706.462</v>
       </c>
       <c r="I748" t="n">
         <v>0.0</v>
@@ -27988,7 +27988,7 @@
         </is>
       </c>
       <c r="E755" t="n">
-        <v>2584.623</v>
+        <v>2566.163</v>
       </c>
       <c r="F755" t="n">
         <v>2.3080000000000003</v>
@@ -27997,7 +27997,7 @@
         <v>2.3080000000000003</v>
       </c>
       <c r="H755" t="n">
-        <v>2584.623</v>
+        <v>2566.163</v>
       </c>
       <c r="I755" t="n">
         <v>0.0</v>
@@ -28025,7 +28025,7 @@
         </is>
       </c>
       <c r="E756" t="n">
-        <v>4326.938</v>
+        <v>4271.555</v>
       </c>
       <c r="F756" t="n">
         <v>0.0</v>
@@ -28034,7 +28034,7 @@
         <v>2.3080000000000003</v>
       </c>
       <c r="H756" t="n">
-        <v>4326.938</v>
+        <v>4271.555</v>
       </c>
       <c r="I756" t="n">
         <v>0.0</v>
@@ -28358,7 +28358,7 @@
         </is>
       </c>
       <c r="E765" t="n">
-        <v>839.208</v>
+        <v>792.362</v>
       </c>
       <c r="F765" t="n">
         <v>0.892</v>
@@ -28367,7 +28367,7 @@
         <v>0.0</v>
       </c>
       <c r="H765" t="n">
-        <v>839.208</v>
+        <v>792.362</v>
       </c>
       <c r="I765" t="n">
         <v>0.0</v>
@@ -28506,7 +28506,7 @@
         </is>
       </c>
       <c r="E769" t="n">
-        <v>18489.694</v>
+        <v>18785.086</v>
       </c>
       <c r="F769" t="n">
         <v>15.231</v>
@@ -28515,7 +28515,7 @@
         <v>7.385</v>
       </c>
       <c r="H769" t="n">
-        <v>18489.694</v>
+        <v>18785.086</v>
       </c>
       <c r="I769" t="n">
         <v>0.0</v>
@@ -28654,7 +28654,7 @@
         </is>
       </c>
       <c r="E773" t="n">
-        <v>5240.479</v>
+        <v>5301.742</v>
       </c>
       <c r="F773" t="n">
         <v>2.0309999999999997</v>
@@ -28663,7 +28663,7 @@
         <v>2.0309999999999997</v>
       </c>
       <c r="H773" t="n">
-        <v>5240.479</v>
+        <v>5301.742</v>
       </c>
       <c r="I773" t="n">
         <v>0.0</v>
@@ -28691,7 +28691,7 @@
         </is>
       </c>
       <c r="E774" t="n">
-        <v>1983.075</v>
+        <v>1928.245</v>
       </c>
       <c r="F774" t="n">
         <v>2.0309999999999997</v>
@@ -28700,7 +28700,7 @@
         <v>4.061999999999999</v>
       </c>
       <c r="H774" t="n">
-        <v>1983.075</v>
+        <v>1928.245</v>
       </c>
       <c r="I774" t="n">
         <v>0.0</v>
@@ -28765,7 +28765,7 @@
         </is>
       </c>
       <c r="E776" t="n">
-        <v>11586.395</v>
+        <v>11453.039</v>
       </c>
       <c r="F776" t="n">
         <v>4.736</v>
@@ -28774,7 +28774,7 @@
         <v>38.585</v>
       </c>
       <c r="H776" t="n">
-        <v>11586.395</v>
+        <v>11453.039</v>
       </c>
       <c r="I776" t="n">
         <v>0.0</v>
@@ -28913,7 +28913,7 @@
         </is>
       </c>
       <c r="E780" t="n">
-        <v>3254.02</v>
+        <v>3264.849</v>
       </c>
       <c r="F780" t="n">
         <v>0.0</v>
@@ -28922,7 +28922,7 @@
         <v>0.0</v>
       </c>
       <c r="H780" t="n">
-        <v>3254.02</v>
+        <v>3264.849</v>
       </c>
       <c r="I780" t="n">
         <v>0.0</v>
@@ -28987,7 +28987,7 @@
         </is>
       </c>
       <c r="E782" t="n">
-        <v>16.587</v>
+        <v>13.88</v>
       </c>
       <c r="F782" t="n">
         <v>0.0</v>
@@ -28996,7 +28996,7 @@
         <v>6419.359</v>
       </c>
       <c r="H782" t="n">
-        <v>16.587</v>
+        <v>13.88</v>
       </c>
       <c r="I782" t="n">
         <v>0.0</v>
@@ -29024,7 +29024,7 @@
         </is>
       </c>
       <c r="E783" t="n">
-        <v>904.799</v>
+        <v>904.729</v>
       </c>
       <c r="F783" t="n">
         <v>0.0</v>
@@ -29033,7 +29033,7 @@
         <v>0.8400000000000001</v>
       </c>
       <c r="H783" t="n">
-        <v>904.799</v>
+        <v>904.729</v>
       </c>
       <c r="I783" t="n">
         <v>0.0</v>
@@ -29061,7 +29061,7 @@
         </is>
       </c>
       <c r="E784" t="n">
-        <v>675.601</v>
+        <v>675.001</v>
       </c>
       <c r="F784" t="n">
         <v>0.0</v>
@@ -29070,7 +29070,7 @@
         <v>19.68</v>
       </c>
       <c r="H784" t="n">
-        <v>675.601</v>
+        <v>675.001</v>
       </c>
       <c r="I784" t="n">
         <v>0.0</v>
@@ -29135,7 +29135,7 @@
         </is>
       </c>
       <c r="E786" t="n">
-        <v>4121.662</v>
+        <v>4181.371</v>
       </c>
       <c r="F786" t="n">
         <v>0.185</v>
@@ -29144,7 +29144,7 @@
         <v>34.456</v>
       </c>
       <c r="H786" t="n">
-        <v>4121.662</v>
+        <v>4181.371</v>
       </c>
       <c r="I786" t="n">
         <v>0.0</v>
@@ -29172,7 +29172,7 @@
         </is>
       </c>
       <c r="E787" t="n">
-        <v>556.249</v>
+        <v>552.919</v>
       </c>
       <c r="F787" t="n">
         <v>4.995</v>
@@ -29181,7 +29181,7 @@
         <v>79.36500000000001</v>
       </c>
       <c r="H787" t="n">
-        <v>556.249</v>
+        <v>552.919</v>
       </c>
       <c r="I787" t="n">
         <v>0.0</v>
@@ -29209,7 +29209,7 @@
         </is>
       </c>
       <c r="E788" t="n">
-        <v>2073.735</v>
+        <v>1207.575</v>
       </c>
       <c r="F788" t="n">
         <v>1.485</v>
@@ -29218,7 +29218,7 @@
         <v>8.1</v>
       </c>
       <c r="H788" t="n">
-        <v>2073.735</v>
+        <v>1207.575</v>
       </c>
       <c r="I788" t="n">
         <v>0.0</v>
@@ -29246,7 +29246,7 @@
         </is>
       </c>
       <c r="E789" t="n">
-        <v>1252.04</v>
+        <v>1170.96</v>
       </c>
       <c r="F789" t="n">
         <v>0.32</v>
@@ -29255,7 +29255,7 @@
         <v>17.32</v>
       </c>
       <c r="H789" t="n">
-        <v>1252.04</v>
+        <v>1170.96</v>
       </c>
       <c r="I789" t="n">
         <v>0.0</v>
@@ -29357,7 +29357,7 @@
         </is>
       </c>
       <c r="E792" t="n">
-        <v>4905.978999999999</v>
+        <v>4983.611</v>
       </c>
       <c r="F792" t="n">
         <v>3.033</v>
@@ -29366,7 +29366,7 @@
         <v>12.13</v>
       </c>
       <c r="H792" t="n">
-        <v>4905.978999999999</v>
+        <v>4983.611</v>
       </c>
       <c r="I792" t="n">
         <v>0.0</v>
@@ -29394,7 +29394,7 @@
         </is>
       </c>
       <c r="E793" t="n">
-        <v>3136.212</v>
+        <v>3224.154</v>
       </c>
       <c r="F793" t="n">
         <v>6.065</v>
@@ -29403,7 +29403,7 @@
         <v>9.704</v>
       </c>
       <c r="H793" t="n">
-        <v>3136.212</v>
+        <v>3224.154</v>
       </c>
       <c r="I793" t="n">
         <v>0.0</v>
@@ -29431,7 +29431,7 @@
         </is>
       </c>
       <c r="E794" t="n">
-        <v>809.678</v>
+        <v>443.352</v>
       </c>
       <c r="F794" t="n">
         <v>1.213</v>
@@ -29440,7 +29440,7 @@
         <v>0.0</v>
       </c>
       <c r="H794" t="n">
-        <v>809.678</v>
+        <v>443.352</v>
       </c>
       <c r="I794" t="n">
         <v>0.0</v>
@@ -29579,7 +29579,7 @@
         </is>
       </c>
       <c r="E798" t="n">
-        <v>4016.774</v>
+        <v>4156.806</v>
       </c>
       <c r="F798" t="n">
         <v>1.8920000000000001</v>
@@ -29588,7 +29588,7 @@
         <v>80.739</v>
       </c>
       <c r="H798" t="n">
-        <v>4016.774</v>
+        <v>4156.806</v>
       </c>
       <c r="I798" t="n">
         <v>0.0</v>
@@ -29616,7 +29616,7 @@
         </is>
       </c>
       <c r="E799" t="n">
-        <v>3140.629</v>
+        <v>3165.8599999999997</v>
       </c>
       <c r="F799" t="n">
         <v>3.154</v>
@@ -29625,7 +29625,7 @@
         <v>0.631</v>
       </c>
       <c r="H799" t="n">
-        <v>3140.629</v>
+        <v>3165.8599999999997</v>
       </c>
       <c r="I799" t="n">
         <v>0.0</v>
@@ -30097,7 +30097,7 @@
         </is>
       </c>
       <c r="E812" t="n">
-        <v>1723.3999999999999</v>
+        <v>1684.8000000000002</v>
       </c>
       <c r="F812" t="n">
         <v>0.6</v>
@@ -30106,7 +30106,7 @@
         <v>2.4</v>
       </c>
       <c r="H812" t="n">
-        <v>1723.3999999999999</v>
+        <v>1684.8000000000002</v>
       </c>
       <c r="I812" t="n">
         <v>0.0</v>
@@ -30282,7 +30282,7 @@
         </is>
       </c>
       <c r="E817" t="n">
-        <v>12446.09</v>
+        <v>12409.284</v>
       </c>
       <c r="F817" t="n">
         <v>2.4</v>
@@ -30291,7 +30291,7 @@
         <v>599.008</v>
       </c>
       <c r="H817" t="n">
-        <v>12446.09</v>
+        <v>12409.284</v>
       </c>
       <c r="I817" t="n">
         <v>0.0</v>
@@ -30430,7 +30430,7 @@
         </is>
       </c>
       <c r="E821" t="n">
-        <v>1025.729</v>
+        <v>952.12</v>
       </c>
       <c r="F821" t="n">
         <v>0.0</v>
@@ -30439,7 +30439,7 @@
         <v>192.024</v>
       </c>
       <c r="H821" t="n">
-        <v>1025.729</v>
+        <v>952.12</v>
       </c>
       <c r="I821" t="n">
         <v>0.0</v>
@@ -30652,7 +30652,7 @@
         </is>
       </c>
       <c r="E827" t="n">
-        <v>427.008</v>
+        <v>320.256</v>
       </c>
       <c r="F827" t="n">
         <v>0.0</v>
@@ -30661,7 +30661,7 @@
         <v>1670.6689999999999</v>
       </c>
       <c r="H827" t="n">
-        <v>427.008</v>
+        <v>320.256</v>
       </c>
       <c r="I827" t="n">
         <v>0.0</v>
@@ -30763,7 +30763,7 @@
         </is>
       </c>
       <c r="E830" t="n">
-        <v>5260.553</v>
+        <v>5232.548</v>
       </c>
       <c r="F830" t="n">
         <v>0.0</v>
@@ -30772,7 +30772,7 @@
         <v>1.3339999999999999</v>
       </c>
       <c r="H830" t="n">
-        <v>5260.553</v>
+        <v>5232.548</v>
       </c>
       <c r="I830" t="n">
         <v>0.0</v>
@@ -31429,7 +31429,7 @@
         </is>
       </c>
       <c r="E848" t="n">
-        <v>2611.464</v>
+        <v>2610.1310000000003</v>
       </c>
       <c r="F848" t="n">
         <v>3.333</v>
@@ -31438,7 +31438,7 @@
         <v>0.0</v>
       </c>
       <c r="H848" t="n">
-        <v>2611.464</v>
+        <v>2610.1310000000003</v>
       </c>
       <c r="I848" t="n">
         <v>0.0</v>
@@ -31466,7 +31466,7 @@
         </is>
       </c>
       <c r="E849" t="n">
-        <v>19570.914</v>
+        <v>19563.445</v>
       </c>
       <c r="F849" t="n">
         <v>10.67</v>
@@ -31475,7 +31475,7 @@
         <v>0.0</v>
       </c>
       <c r="H849" t="n">
-        <v>19570.914</v>
+        <v>19563.445</v>
       </c>
       <c r="I849" t="n">
         <v>0.0</v>
@@ -31540,7 +31540,7 @@
         </is>
       </c>
       <c r="E851" t="n">
-        <v>5730.619000000001</v>
+        <v>5709.818</v>
       </c>
       <c r="F851" t="n">
         <v>0.0</v>
@@ -31549,7 +31549,7 @@
         <v>0.0</v>
       </c>
       <c r="H851" t="n">
-        <v>5730.619000000001</v>
+        <v>5709.818</v>
       </c>
       <c r="I851" t="n">
         <v>0.0</v>
@@ -31651,7 +31651,7 @@
         </is>
       </c>
       <c r="E854" t="n">
-        <v>9989.585000000001</v>
+        <v>9983.518</v>
       </c>
       <c r="F854" t="n">
         <v>15.601</v>
@@ -31660,7 +31660,7 @@
         <v>0.0</v>
       </c>
       <c r="H854" t="n">
-        <v>9989.585000000001</v>
+        <v>9983.518</v>
       </c>
       <c r="I854" t="n">
         <v>0.0</v>
@@ -31688,7 +31688,7 @@
         </is>
       </c>
       <c r="E855" t="n">
-        <v>520.598</v>
+        <v>497.12899999999996</v>
       </c>
       <c r="F855" t="n">
         <v>23.470000000000002</v>
@@ -31697,7 +31697,7 @@
         <v>0.0</v>
       </c>
       <c r="H855" t="n">
-        <v>520.598</v>
+        <v>497.12899999999996</v>
       </c>
       <c r="I855" t="n">
         <v>0.0</v>
@@ -31725,7 +31725,7 @@
         </is>
       </c>
       <c r="E856" t="n">
-        <v>2714.5769999999998</v>
+        <v>2713.71</v>
       </c>
       <c r="F856" t="n">
         <v>2.601</v>
@@ -31734,7 +31734,7 @@
         <v>0.0</v>
       </c>
       <c r="H856" t="n">
-        <v>2714.5769999999998</v>
+        <v>2713.71</v>
       </c>
       <c r="I856" t="n">
         <v>0.0</v>
@@ -31836,7 +31836,7 @@
         </is>
       </c>
       <c r="E859" t="n">
-        <v>11994.8</v>
+        <v>11978.801</v>
       </c>
       <c r="F859" t="n">
         <v>15.997999999999998</v>
@@ -31845,7 +31845,7 @@
         <v>0.6669999999999999</v>
       </c>
       <c r="H859" t="n">
-        <v>11994.8</v>
+        <v>11978.801</v>
       </c>
       <c r="I859" t="n">
         <v>0.0</v>
@@ -31910,7 +31910,7 @@
         </is>
       </c>
       <c r="E861" t="n">
-        <v>2302.0</v>
+        <v>2314.7999999999997</v>
       </c>
       <c r="F861" t="n">
         <v>0.0</v>
@@ -31919,7 +31919,7 @@
         <v>0.0</v>
       </c>
       <c r="H861" t="n">
-        <v>2302.0</v>
+        <v>2314.7999999999997</v>
       </c>
       <c r="I861" t="n">
         <v>0.0</v>
@@ -31984,7 +31984,7 @@
         </is>
       </c>
       <c r="E863" t="n">
-        <v>10754.944000000001</v>
+        <v>10994.174</v>
       </c>
       <c r="F863" t="n">
         <v>39.205</v>
@@ -31993,7 +31993,7 @@
         <v>0.0</v>
       </c>
       <c r="H863" t="n">
-        <v>10754.944000000001</v>
+        <v>10994.174</v>
       </c>
       <c r="I863" t="n">
         <v>0.0</v>
@@ -32058,7 +32058,7 @@
         </is>
       </c>
       <c r="E865" t="n">
-        <v>2953.9680000000003</v>
+        <v>2952.902</v>
       </c>
       <c r="F865" t="n">
         <v>2.134</v>
@@ -32067,7 +32067,7 @@
         <v>0.0</v>
       </c>
       <c r="H865" t="n">
-        <v>2953.9680000000003</v>
+        <v>2952.902</v>
       </c>
       <c r="I865" t="n">
         <v>0.0</v>
@@ -32095,7 +32095,7 @@
         </is>
       </c>
       <c r="E866" t="n">
-        <v>1418.8429999999998</v>
+        <v>1393.24</v>
       </c>
       <c r="F866" t="n">
         <v>1.067</v>
@@ -32104,7 +32104,7 @@
         <v>25.603</v>
       </c>
       <c r="H866" t="n">
-        <v>1418.8429999999998</v>
+        <v>1393.24</v>
       </c>
       <c r="I866" t="n">
         <v>0.0</v>
@@ -32132,7 +32132,7 @@
         </is>
       </c>
       <c r="E867" t="n">
-        <v>737.504</v>
+        <v>1055.31</v>
       </c>
       <c r="F867" t="n">
         <v>18.802</v>
@@ -32141,7 +32141,7 @@
         <v>19.408</v>
       </c>
       <c r="H867" t="n">
-        <v>737.504</v>
+        <v>1055.31</v>
       </c>
       <c r="I867" t="n">
         <v>0.0</v>
@@ -32169,7 +32169,7 @@
         </is>
       </c>
       <c r="E868" t="n">
-        <v>1315.943</v>
+        <v>1282.806</v>
       </c>
       <c r="F868" t="n">
         <v>0.0</v>
@@ -32178,7 +32178,7 @@
         <v>0.0</v>
       </c>
       <c r="H868" t="n">
-        <v>1315.943</v>
+        <v>1282.806</v>
       </c>
       <c r="I868" t="n">
         <v>0.0</v>
@@ -32206,7 +32206,7 @@
         </is>
       </c>
       <c r="E869" t="n">
-        <v>1294.621</v>
+        <v>1292.312</v>
       </c>
       <c r="F869" t="n">
         <v>0.0</v>
@@ -32215,7 +32215,7 @@
         <v>9.231</v>
       </c>
       <c r="H869" t="n">
-        <v>1294.621</v>
+        <v>1292.312</v>
       </c>
       <c r="I869" t="n">
         <v>0.0</v>
@@ -32243,7 +32243,7 @@
         </is>
       </c>
       <c r="E870" t="n">
-        <v>1967.847</v>
+        <v>2010.895</v>
       </c>
       <c r="F870" t="n">
         <v>5.916</v>
@@ -32252,7 +32252,7 @@
         <v>346.144</v>
       </c>
       <c r="H870" t="n">
-        <v>1967.847</v>
+        <v>2010.895</v>
       </c>
       <c r="I870" t="n">
         <v>0.0</v>
@@ -32280,7 +32280,7 @@
         </is>
       </c>
       <c r="E871" t="n">
-        <v>4770.284</v>
+        <v>4770.285000000001</v>
       </c>
       <c r="F871" t="n">
         <v>0.593</v>
@@ -32289,7 +32289,7 @@
         <v>226.61999999999998</v>
       </c>
       <c r="H871" t="n">
-        <v>4770.284</v>
+        <v>4770.285000000001</v>
       </c>
       <c r="I871" t="n">
         <v>0.0</v>
@@ -32391,7 +32391,7 @@
         </is>
       </c>
       <c r="E874" t="n">
-        <v>9320.799</v>
+        <v>9313.877</v>
       </c>
       <c r="F874" t="n">
         <v>0.0</v>
@@ -32400,7 +32400,7 @@
         <v>6.923</v>
       </c>
       <c r="H874" t="n">
-        <v>9320.799</v>
+        <v>9313.877</v>
       </c>
       <c r="I874" t="n">
         <v>0.0</v>
@@ -32428,7 +32428,7 @@
         </is>
       </c>
       <c r="E875" t="n">
-        <v>4917.709</v>
+        <v>4896.939</v>
       </c>
       <c r="F875" t="n">
         <v>0.0</v>
@@ -32437,7 +32437,7 @@
         <v>0.0</v>
       </c>
       <c r="H875" t="n">
-        <v>4917.709</v>
+        <v>4896.939</v>
       </c>
       <c r="I875" t="n">
         <v>0.0</v>
@@ -32502,7 +32502,7 @@
         </is>
       </c>
       <c r="E877" t="n">
-        <v>2702.654</v>
+        <v>2689.607</v>
       </c>
       <c r="F877" t="n">
         <v>0.0</v>
@@ -32511,7 +32511,7 @@
         <v>0.9319999999999999</v>
       </c>
       <c r="H877" t="n">
-        <v>2702.654</v>
+        <v>2689.607</v>
       </c>
       <c r="I877" t="n">
         <v>0.0</v>
@@ -32687,7 +32687,7 @@
         </is>
       </c>
       <c r="E882" t="n">
-        <v>1124.311</v>
+        <v>1102.344</v>
       </c>
       <c r="F882" t="n">
         <v>0.0</v>
@@ -32696,7 +32696,7 @@
         <v>3.994</v>
       </c>
       <c r="H882" t="n">
-        <v>1124.311</v>
+        <v>1102.344</v>
       </c>
       <c r="I882" t="n">
         <v>0.0</v>
@@ -32798,7 +32798,7 @@
         </is>
       </c>
       <c r="E885" t="n">
-        <v>2344.315</v>
+        <v>2295.796</v>
       </c>
       <c r="F885" t="n">
         <v>0.0</v>
@@ -32807,7 +32807,7 @@
         <v>42.602000000000004</v>
       </c>
       <c r="H885" t="n">
-        <v>2344.315</v>
+        <v>2295.796</v>
       </c>
       <c r="I885" t="n">
         <v>0.0</v>
@@ -32983,7 +32983,7 @@
         </is>
       </c>
       <c r="E890" t="n">
-        <v>2688.149</v>
+        <v>2648.117</v>
       </c>
       <c r="F890" t="n">
         <v>0.0</v>
@@ -32992,7 +32992,7 @@
         <v>240.19199999999998</v>
       </c>
       <c r="H890" t="n">
-        <v>2688.149</v>
+        <v>2648.117</v>
       </c>
       <c r="I890" t="n">
         <v>0.0</v>
@@ -33057,7 +33057,7 @@
         </is>
       </c>
       <c r="E892" t="n">
-        <v>9113.284</v>
+        <v>9110.615</v>
       </c>
       <c r="F892" t="n">
         <v>0.0</v>
@@ -33066,7 +33066,7 @@
         <v>84.29</v>
       </c>
       <c r="H892" t="n">
-        <v>9113.284</v>
+        <v>9110.615</v>
       </c>
       <c r="I892" t="n">
         <v>0.0</v>
@@ -33094,7 +33094,7 @@
         </is>
       </c>
       <c r="E893" t="n">
-        <v>166.8</v>
+        <v>302.909</v>
       </c>
       <c r="F893" t="n">
         <v>0.0</v>
@@ -33103,7 +33103,7 @@
         <v>0.0</v>
       </c>
       <c r="H893" t="n">
-        <v>166.8</v>
+        <v>302.909</v>
       </c>
       <c r="I893" t="n">
         <v>0.0</v>
@@ -33168,7 +33168,7 @@
         </is>
       </c>
       <c r="E895" t="n">
-        <v>2403.922</v>
+        <v>2443.954</v>
       </c>
       <c r="F895" t="n">
         <v>0.0</v>
@@ -33177,7 +33177,7 @@
         <v>60.047999999999995</v>
       </c>
       <c r="H895" t="n">
-        <v>2403.922</v>
+        <v>2443.954</v>
       </c>
       <c r="I895" t="n">
         <v>0.0</v>
@@ -33205,7 +33205,7 @@
         </is>
       </c>
       <c r="E896" t="n">
-        <v>1843.476</v>
+        <v>1923.538</v>
       </c>
       <c r="F896" t="n">
         <v>20.016</v>
@@ -33214,7 +33214,7 @@
         <v>170.97</v>
       </c>
       <c r="H896" t="n">
-        <v>1843.476</v>
+        <v>1923.538</v>
       </c>
       <c r="I896" t="n">
         <v>0.0</v>
@@ -33242,7 +33242,7 @@
         </is>
       </c>
       <c r="E897" t="n">
-        <v>1810.781</v>
+        <v>1808.112</v>
       </c>
       <c r="F897" t="n">
         <v>0.0</v>
@@ -33251,7 +33251,7 @@
         <v>227.07</v>
       </c>
       <c r="H897" t="n">
-        <v>1810.781</v>
+        <v>1808.112</v>
       </c>
       <c r="I897" t="n">
         <v>0.0</v>
@@ -33279,7 +33279,7 @@
         </is>
       </c>
       <c r="E898" t="n">
-        <v>157.461</v>
+        <v>157.459</v>
       </c>
       <c r="F898" t="n">
         <v>0.0</v>
@@ -33288,7 +33288,7 @@
         <v>0.0</v>
       </c>
       <c r="H898" t="n">
-        <v>157.461</v>
+        <v>157.459</v>
       </c>
       <c r="I898" t="n">
         <v>0.0</v>
@@ -33316,7 +33316,7 @@
         </is>
       </c>
       <c r="E899" t="n">
-        <v>1801.305</v>
+        <v>1849.825</v>
       </c>
       <c r="F899" t="n">
         <v>3.033</v>
@@ -33325,7 +33325,7 @@
         <v>0.0</v>
       </c>
       <c r="H899" t="n">
-        <v>1801.305</v>
+        <v>1849.825</v>
       </c>
       <c r="I899" t="n">
         <v>0.0</v>
@@ -33353,7 +33353,7 @@
         </is>
       </c>
       <c r="E900" t="n">
-        <v>1035.296</v>
+        <v>1025.592</v>
       </c>
       <c r="F900" t="n">
         <v>0.607</v>
@@ -33362,7 +33362,7 @@
         <v>0.0</v>
       </c>
       <c r="H900" t="n">
-        <v>1035.296</v>
+        <v>1025.592</v>
       </c>
       <c r="I900" t="n">
         <v>0.0</v>
@@ -33427,7 +33427,7 @@
         </is>
       </c>
       <c r="E902" t="n">
-        <v>2217.075</v>
+        <v>2469.142</v>
       </c>
       <c r="F902" t="n">
         <v>67.218</v>
@@ -33436,7 +33436,7 @@
         <v>0.0</v>
       </c>
       <c r="H902" t="n">
-        <v>2217.075</v>
+        <v>2469.142</v>
       </c>
       <c r="I902" t="n">
         <v>0.0</v>
@@ -33649,7 +33649,7 @@
         </is>
       </c>
       <c r="E908" t="n">
-        <v>2882.045</v>
+        <v>2906.9379999999996</v>
       </c>
       <c r="F908" t="n">
         <v>0.622</v>
@@ -33658,7 +33658,7 @@
         <v>1.245</v>
       </c>
       <c r="H908" t="n">
-        <v>2882.045</v>
+        <v>2906.9379999999996</v>
       </c>
       <c r="I908" t="n">
         <v>0.0</v>
@@ -34278,7 +34278,7 @@
         </is>
       </c>
       <c r="E925" t="n">
-        <v>2.104</v>
+        <v>0.842</v>
       </c>
       <c r="F925" t="n">
         <v>0.0</v>
@@ -34287,7 +34287,7 @@
         <v>0.0</v>
       </c>
       <c r="H925" t="n">
-        <v>2.104</v>
+        <v>0.842</v>
       </c>
       <c r="I925" t="n">
         <v>0.0</v>
@@ -34315,7 +34315,7 @@
         </is>
       </c>
       <c r="E926" t="n">
-        <v>4596.820000000001</v>
+        <v>4548.323</v>
       </c>
       <c r="F926" t="n">
         <v>0.211</v>
@@ -34324,7 +34324,7 @@
         <v>1.262</v>
       </c>
       <c r="H926" t="n">
-        <v>4596.820000000001</v>
+        <v>4548.323</v>
       </c>
       <c r="I926" t="n">
         <v>0.0</v>
@@ -34352,7 +34352,7 @@
         </is>
       </c>
       <c r="E927" t="n">
-        <v>813.723</v>
+        <v>828.45</v>
       </c>
       <c r="F927" t="n">
         <v>0.0</v>
@@ -34361,7 +34361,7 @@
         <v>0.0</v>
       </c>
       <c r="H927" t="n">
-        <v>813.723</v>
+        <v>828.45</v>
       </c>
       <c r="I927" t="n">
         <v>0.0</v>
@@ -34389,7 +34389,7 @@
         </is>
       </c>
       <c r="E928" t="n">
-        <v>2826.932</v>
+        <v>2820.01</v>
       </c>
       <c r="F928" t="n">
         <v>0.0</v>
@@ -34398,7 +34398,7 @@
         <v>11.539000000000001</v>
       </c>
       <c r="H928" t="n">
-        <v>2826.932</v>
+        <v>2820.01</v>
       </c>
       <c r="I928" t="n">
         <v>0.0</v>
@@ -34500,7 +34500,7 @@
         </is>
       </c>
       <c r="E931" t="n">
-        <v>3505.396</v>
+        <v>3498.472</v>
       </c>
       <c r="F931" t="n">
         <v>0.0</v>
@@ -34509,7 +34509,7 @@
         <v>2.3080000000000003</v>
       </c>
       <c r="H931" t="n">
-        <v>3505.396</v>
+        <v>3498.472</v>
       </c>
       <c r="I931" t="n">
         <v>0.0</v>
@@ -34722,7 +34722,7 @@
         </is>
       </c>
       <c r="E937" t="n">
-        <v>8830.826</v>
+        <v>8908.341</v>
       </c>
       <c r="F937" t="n">
         <v>1.6280000000000001</v>
@@ -34731,7 +34731,7 @@
         <v>128.102</v>
       </c>
       <c r="H937" t="n">
-        <v>8830.826</v>
+        <v>8908.341</v>
       </c>
       <c r="I937" t="n">
         <v>0.0</v>
@@ -34944,7 +34944,7 @@
         </is>
       </c>
       <c r="E943" t="n">
-        <v>242.43099999999998</v>
+        <v>338.443</v>
       </c>
       <c r="F943" t="n">
         <v>9.601</v>
@@ -34953,7 +34953,7 @@
         <v>0.0</v>
       </c>
       <c r="H943" t="n">
-        <v>242.43099999999998</v>
+        <v>338.443</v>
       </c>
       <c r="I943" t="n">
         <v>0.0</v>
@@ -35240,7 +35240,7 @@
         </is>
       </c>
       <c r="E951" t="n">
-        <v>1914.549</v>
+        <v>1964.4560000000001</v>
       </c>
       <c r="F951" t="n">
         <v>57.22</v>
@@ -35249,7 +35249,7 @@
         <v>0.0</v>
       </c>
       <c r="H951" t="n">
-        <v>1914.549</v>
+        <v>1964.4560000000001</v>
       </c>
       <c r="I951" t="n">
         <v>0.0</v>
@@ -35277,7 +35277,7 @@
         </is>
       </c>
       <c r="E952" t="n">
-        <v>857.193</v>
+        <v>924.649</v>
       </c>
       <c r="F952" t="n">
         <v>0.728</v>
@@ -35286,7 +35286,7 @@
         <v>0.0</v>
       </c>
       <c r="H952" t="n">
-        <v>857.193</v>
+        <v>924.649</v>
       </c>
       <c r="I952" t="n">
         <v>0.0</v>
@@ -35388,7 +35388,7 @@
         </is>
       </c>
       <c r="E955" t="n">
-        <v>5458.0</v>
+        <v>5452.0</v>
       </c>
       <c r="F955" t="n">
         <v>0.0</v>
@@ -35397,7 +35397,7 @@
         <v>180.0</v>
       </c>
       <c r="H955" t="n">
-        <v>5458.0</v>
+        <v>5452.0</v>
       </c>
       <c r="I955" t="n">
         <v>0.0</v>
@@ -35832,7 +35832,7 @@
         </is>
       </c>
       <c r="E967" t="n">
-        <v>238.81</v>
+        <v>216.766</v>
       </c>
       <c r="F967" t="n">
         <v>0.0</v>
@@ -35841,7 +35841,7 @@
         <v>0.0</v>
       </c>
       <c r="H967" t="n">
-        <v>238.81</v>
+        <v>216.766</v>
       </c>
       <c r="I967" t="n">
         <v>0.0</v>
@@ -35869,7 +35869,7 @@
         </is>
       </c>
       <c r="E968" t="n">
-        <v>78.958</v>
+        <v>76.954</v>
       </c>
       <c r="F968" t="n">
         <v>0.0</v>
@@ -35878,7 +35878,7 @@
         <v>0.0</v>
       </c>
       <c r="H968" t="n">
-        <v>78.958</v>
+        <v>76.954</v>
       </c>
       <c r="I968" t="n">
         <v>0.0</v>
@@ -36461,7 +36461,7 @@
         </is>
       </c>
       <c r="E984" t="n">
-        <v>958.5329999999999</v>
+        <v>618.3330000000001</v>
       </c>
       <c r="F984" t="n">
         <v>16.1</v>
@@ -36470,7 +36470,7 @@
         <v>12.6</v>
       </c>
       <c r="H984" t="n">
-        <v>958.5329999999999</v>
+        <v>618.3330000000001</v>
       </c>
       <c r="I984" t="n">
         <v>0.0</v>
@@ -36498,7 +36498,7 @@
         </is>
       </c>
       <c r="E985" t="n">
-        <v>3042.985</v>
+        <v>2934.647</v>
       </c>
       <c r="F985" t="n">
         <v>37.268</v>
@@ -36507,7 +36507,7 @@
         <v>0.867</v>
       </c>
       <c r="H985" t="n">
-        <v>3042.985</v>
+        <v>2934.647</v>
       </c>
       <c r="I985" t="n">
         <v>0.0</v>
@@ -36535,7 +36535,7 @@
         </is>
       </c>
       <c r="E986" t="n">
-        <v>3891.933</v>
+        <v>3933.501</v>
       </c>
       <c r="F986" t="n">
         <v>16.434</v>
@@ -36544,7 +36544,7 @@
         <v>8.7</v>
       </c>
       <c r="H986" t="n">
-        <v>3891.933</v>
+        <v>3933.501</v>
       </c>
       <c r="I986" t="n">
         <v>0.0</v>
@@ -37423,7 +37423,7 @@
         </is>
       </c>
       <c r="E1010" t="n">
-        <v>107.586</v>
+        <v>19.516</v>
       </c>
       <c r="F1010" t="n">
         <v>0.0</v>
@@ -37432,7 +37432,7 @@
         <v>0.0</v>
       </c>
       <c r="H1010" t="n">
-        <v>107.586</v>
+        <v>19.516</v>
       </c>
       <c r="I1010" t="n">
         <v>0.0</v>
@@ -37460,7 +37460,7 @@
         </is>
       </c>
       <c r="E1011" t="n">
-        <v>14.201</v>
+        <v>1032.517</v>
       </c>
       <c r="F1011" t="n">
         <v>0.0</v>
@@ -37469,7 +37469,7 @@
         <v>53.253</v>
       </c>
       <c r="H1011" t="n">
-        <v>14.201</v>
+        <v>1032.517</v>
       </c>
       <c r="I1011" t="n">
         <v>0.0</v>
@@ -37534,7 +37534,7 @@
         </is>
       </c>
       <c r="E1013" t="n">
-        <v>10932.839</v>
+        <v>10932.84</v>
       </c>
       <c r="F1013" t="n">
         <v>0.0</v>
@@ -37543,7 +37543,7 @@
         <v>0.0</v>
       </c>
       <c r="H1013" t="n">
-        <v>10932.839</v>
+        <v>10932.84</v>
       </c>
       <c r="I1013" t="n">
         <v>0.0</v>
@@ -37756,7 +37756,7 @@
         </is>
       </c>
       <c r="E1019" t="n">
-        <v>5948.498</v>
+        <v>5948.497</v>
       </c>
       <c r="F1019" t="n">
         <v>68.241</v>
@@ -37765,7 +37765,7 @@
         <v>47.885999999999996</v>
       </c>
       <c r="H1019" t="n">
-        <v>5948.498</v>
+        <v>5948.497</v>
       </c>
       <c r="I1019" t="n">
         <v>0.0</v>
@@ -37830,7 +37830,7 @@
         </is>
       </c>
       <c r="E1021" t="n">
-        <v>1420.977</v>
+        <v>1344.168</v>
       </c>
       <c r="F1021" t="n">
         <v>0.0</v>
@@ -37839,7 +37839,7 @@
         <v>0.0</v>
       </c>
       <c r="H1021" t="n">
-        <v>1420.977</v>
+        <v>1344.168</v>
       </c>
       <c r="I1021" t="n">
         <v>0.0</v>
@@ -38052,7 +38052,7 @@
         </is>
       </c>
       <c r="E1027" t="n">
-        <v>4810.366</v>
+        <v>4745.8369999999995</v>
       </c>
       <c r="F1027" t="n">
         <v>0.0</v>
@@ -38061,7 +38061,7 @@
         <v>0.0</v>
       </c>
       <c r="H1027" t="n">
-        <v>4810.366</v>
+        <v>4745.8369999999995</v>
       </c>
       <c r="I1027" t="n">
         <v>0.0</v>
@@ -38089,7 +38089,7 @@
         </is>
       </c>
       <c r="E1028" t="n">
-        <v>4864.608</v>
+        <v>4816.602</v>
       </c>
       <c r="F1028" t="n">
         <v>0.8</v>
@@ -38098,7 +38098,7 @@
         <v>800.1</v>
       </c>
       <c r="H1028" t="n">
-        <v>4864.608</v>
+        <v>4816.602</v>
       </c>
       <c r="I1028" t="n">
         <v>0.0</v>
@@ -38200,7 +38200,7 @@
         </is>
       </c>
       <c r="E1031" t="n">
-        <v>7593.528</v>
+        <v>7360.54</v>
       </c>
       <c r="F1031" t="n">
         <v>0.0</v>
@@ -38209,7 +38209,7 @@
         <v>3.7279999999999998</v>
       </c>
       <c r="H1031" t="n">
-        <v>7593.528</v>
+        <v>7360.54</v>
       </c>
       <c r="I1031" t="n">
         <v>0.0</v>
@@ -38274,7 +38274,7 @@
         </is>
       </c>
       <c r="E1033" t="n">
-        <v>6725.262</v>
+        <v>6714.612</v>
       </c>
       <c r="F1033" t="n">
         <v>1.183</v>
@@ -38283,7 +38283,7 @@
         <v>3.846</v>
       </c>
       <c r="H1033" t="n">
-        <v>6725.262</v>
+        <v>6714.612</v>
       </c>
       <c r="I1033" t="n">
         <v>0.0</v>
@@ -38755,7 +38755,7 @@
         </is>
       </c>
       <c r="E1046" t="n">
-        <v>32.152</v>
+        <v>27.359</v>
       </c>
       <c r="F1046" t="n">
         <v>0.0</v>
@@ -38764,7 +38764,7 @@
         <v>694.956</v>
       </c>
       <c r="H1046" t="n">
-        <v>32.152</v>
+        <v>27.359</v>
       </c>
       <c r="I1046" t="n">
         <v>0.0</v>
@@ -38792,7 +38792,7 @@
         </is>
       </c>
       <c r="E1047" t="n">
-        <v>597.694</v>
+        <v>576.925</v>
       </c>
       <c r="F1047" t="n">
         <v>0.0</v>
@@ -38801,7 +38801,7 @@
         <v>23.077</v>
       </c>
       <c r="H1047" t="n">
-        <v>597.694</v>
+        <v>576.925</v>
       </c>
       <c r="I1047" t="n">
         <v>0.0</v>
@@ -38829,7 +38829,7 @@
         </is>
       </c>
       <c r="E1048" t="n">
-        <v>19.408</v>
+        <v>65.50200000000001</v>
       </c>
       <c r="F1048" t="n">
         <v>2.426</v>
@@ -38838,7 +38838,7 @@
         <v>2.426</v>
       </c>
       <c r="H1048" t="n">
-        <v>19.408</v>
+        <v>65.50200000000001</v>
       </c>
       <c r="I1048" t="n">
         <v>0.0</v>
@@ -39014,7 +39014,7 @@
         </is>
       </c>
       <c r="E1053" t="n">
-        <v>484.0</v>
+        <v>167.2</v>
       </c>
       <c r="F1053" t="n">
         <v>0.0</v>
@@ -39023,7 +39023,7 @@
         <v>0.0</v>
       </c>
       <c r="H1053" t="n">
-        <v>484.0</v>
+        <v>167.2</v>
       </c>
       <c r="I1053" t="n">
         <v>0.0</v>
@@ -39236,7 +39236,7 @@
         </is>
       </c>
       <c r="E1059" t="n">
-        <v>5222.841</v>
+        <v>5252.198</v>
       </c>
       <c r="F1059" t="n">
         <v>0.0</v>
@@ -39245,7 +39245,7 @@
         <v>0.0</v>
       </c>
       <c r="H1059" t="n">
-        <v>5222.841</v>
+        <v>5252.198</v>
       </c>
       <c r="I1059" t="n">
         <v>0.0</v>
@@ -39347,7 +39347,7 @@
         </is>
       </c>
       <c r="E1062" t="n">
-        <v>4395.911999999999</v>
+        <v>4426.843</v>
       </c>
       <c r="F1062" t="n">
         <v>3.639</v>
@@ -39356,7 +39356,7 @@
         <v>0.0</v>
       </c>
       <c r="H1062" t="n">
-        <v>4395.911999999999</v>
+        <v>4426.843</v>
       </c>
       <c r="I1062" t="n">
         <v>0.0</v>
@@ -39384,7 +39384,7 @@
         </is>
       </c>
       <c r="E1063" t="n">
-        <v>7331.372</v>
+        <v>7020.237999999999</v>
       </c>
       <c r="F1063" t="n">
         <v>4.852</v>
@@ -39393,7 +39393,7 @@
         <v>36.39</v>
       </c>
       <c r="H1063" t="n">
-        <v>7331.372</v>
+        <v>7020.237999999999</v>
       </c>
       <c r="I1063" t="n">
         <v>0.0</v>
@@ -39421,7 +39421,7 @@
         </is>
       </c>
       <c r="E1064" t="n">
-        <v>4004.326</v>
+        <v>3513.045</v>
       </c>
       <c r="F1064" t="n">
         <v>0.0</v>
@@ -39430,7 +39430,7 @@
         <v>47.608</v>
       </c>
       <c r="H1064" t="n">
-        <v>4004.326</v>
+        <v>3513.045</v>
       </c>
       <c r="I1064" t="n">
         <v>0.0</v>
@@ -39458,7 +39458,7 @@
         </is>
       </c>
       <c r="E1065" t="n">
-        <v>8958.822</v>
+        <v>8253.637999999999</v>
       </c>
       <c r="F1065" t="n">
         <v>0.6589999999999999</v>
@@ -39467,7 +39467,7 @@
         <v>15.869000000000002</v>
       </c>
       <c r="H1065" t="n">
-        <v>8958.822</v>
+        <v>8253.637999999999</v>
       </c>
       <c r="I1065" t="n">
         <v>0.0</v>
@@ -39495,7 +39495,7 @@
         </is>
       </c>
       <c r="E1066" t="n">
-        <v>4984.911999999999</v>
+        <v>4197.0740000000005</v>
       </c>
       <c r="F1066" t="n">
         <v>0.0</v>
@@ -39504,7 +39504,7 @@
         <v>0.0</v>
       </c>
       <c r="H1066" t="n">
-        <v>4984.911999999999</v>
+        <v>4197.0740000000005</v>
       </c>
       <c r="I1066" t="n">
         <v>0.0</v>
@@ -39532,7 +39532,7 @@
         </is>
       </c>
       <c r="E1067" t="n">
-        <v>19120.403</v>
+        <v>17899.466</v>
       </c>
       <c r="F1067" t="n">
         <v>3.634</v>
@@ -39541,7 +39541,7 @@
         <v>0.0</v>
       </c>
       <c r="H1067" t="n">
-        <v>19120.403</v>
+        <v>17899.466</v>
       </c>
       <c r="I1067" t="n">
         <v>0.0</v>
@@ -39606,7 +39606,7 @@
         </is>
       </c>
       <c r="E1069" t="n">
-        <v>11311.430999999999</v>
+        <v>9253.723</v>
       </c>
       <c r="F1069" t="n">
         <v>0.32899999999999996</v>
@@ -39615,7 +39615,7 @@
         <v>3.967</v>
       </c>
       <c r="H1069" t="n">
-        <v>11311.430999999999</v>
+        <v>9253.723</v>
       </c>
       <c r="I1069" t="n">
         <v>0.0</v>
@@ -39643,7 +39643,7 @@
         </is>
       </c>
       <c r="E1070" t="n">
-        <v>21217.999</v>
+        <v>28933.211199999998</v>
       </c>
       <c r="F1070" t="n">
         <v>0.0</v>
@@ -39655,7 +39655,7 @@
         <v>21217.999</v>
       </c>
       <c r="I1070" t="n">
-        <v>0.0</v>
+        <v>7715.2122</v>
       </c>
     </row>
     <row r="1071">
@@ -39680,7 +39680,7 @@
         </is>
       </c>
       <c r="E1071" t="n">
-        <v>6894.516</v>
+        <v>5939.39</v>
       </c>
       <c r="F1071" t="n">
         <v>0.6589999999999999</v>
@@ -39689,7 +39689,7 @@
         <v>11.902</v>
       </c>
       <c r="H1071" t="n">
-        <v>6894.516</v>
+        <v>5939.39</v>
       </c>
       <c r="I1071" t="n">
         <v>0.0</v>
@@ -39717,7 +39717,7 @@
         </is>
       </c>
       <c r="E1072" t="n">
-        <v>36480.4004</v>
+        <v>44036.9206</v>
       </c>
       <c r="F1072" t="n">
         <v>0.0</v>
@@ -39726,10 +39726,10 @@
         <v>14.002</v>
       </c>
       <c r="H1072" t="n">
-        <v>21049.976</v>
+        <v>20891.284</v>
       </c>
       <c r="I1072" t="n">
-        <v>15430.4244</v>
+        <v>23145.636599999998</v>
       </c>
     </row>
     <row r="1073">
@@ -39791,7 +39791,7 @@
         </is>
       </c>
       <c r="E1074" t="n">
-        <v>31367.130999999998</v>
+        <v>29447.285</v>
       </c>
       <c r="F1074" t="n">
         <v>2.972</v>
@@ -39800,7 +39800,7 @@
         <v>3.967</v>
       </c>
       <c r="H1074" t="n">
-        <v>31367.130999999998</v>
+        <v>29447.285</v>
       </c>
       <c r="I1074" t="n">
         <v>0.0</v>
@@ -39828,7 +39828,7 @@
         </is>
       </c>
       <c r="E1075" t="n">
-        <v>22611.955</v>
+        <v>20445.809</v>
       </c>
       <c r="F1075" t="n">
         <v>1.984</v>
@@ -39837,7 +39837,7 @@
         <v>0.0</v>
       </c>
       <c r="H1075" t="n">
-        <v>22611.955</v>
+        <v>20445.809</v>
       </c>
       <c r="I1075" t="n">
         <v>0.0</v>
@@ -39976,7 +39976,7 @@
         </is>
       </c>
       <c r="E1079" t="n">
-        <v>424.666</v>
+        <v>587.917</v>
       </c>
       <c r="F1079" t="n">
         <v>1.067</v>
@@ -39985,7 +39985,7 @@
         <v>0.0</v>
       </c>
       <c r="H1079" t="n">
-        <v>424.666</v>
+        <v>587.917</v>
       </c>
       <c r="I1079" t="n">
         <v>0.0</v>
@@ -40346,7 +40346,7 @@
         </is>
       </c>
       <c r="E1089" t="n">
-        <v>568.113</v>
+        <v>1164.232</v>
       </c>
       <c r="F1089" t="n">
         <v>0.0</v>
@@ -40355,10 +40355,10 @@
         <v>0.0</v>
       </c>
       <c r="H1089" t="n">
-        <v>568.113</v>
+        <v>564.112</v>
       </c>
       <c r="I1089" t="n">
-        <v>0.0</v>
+        <v>600.12</v>
       </c>
     </row>
     <row r="1090">
@@ -40494,7 +40494,7 @@
         </is>
       </c>
       <c r="E1093" t="n">
-        <v>4034.387</v>
+        <v>4034.386</v>
       </c>
       <c r="F1093" t="n">
         <v>0.0</v>
@@ -40503,7 +40503,7 @@
         <v>0.0</v>
       </c>
       <c r="H1093" t="n">
-        <v>4034.387</v>
+        <v>4034.386</v>
       </c>
       <c r="I1093" t="n">
         <v>0.0</v>
@@ -40531,7 +40531,7 @@
         </is>
       </c>
       <c r="E1094" t="n">
-        <v>6757.351</v>
+        <v>6753.35</v>
       </c>
       <c r="F1094" t="n">
         <v>0.0</v>
@@ -40540,7 +40540,7 @@
         <v>0.0</v>
       </c>
       <c r="H1094" t="n">
-        <v>6757.351</v>
+        <v>6753.35</v>
       </c>
       <c r="I1094" t="n">
         <v>0.0</v>
@@ -41382,7 +41382,7 @@
         </is>
       </c>
       <c r="E1117" t="n">
-        <v>2026.809</v>
+        <v>2517.2114</v>
       </c>
       <c r="F1117" t="n">
         <v>0.0</v>
@@ -41394,7 +41394,7 @@
         <v>2026.809</v>
       </c>
       <c r="I1117" t="n">
-        <v>0.0</v>
+        <v>490.4024</v>
       </c>
     </row>
     <row r="1118">
@@ -41419,7 +41419,7 @@
         </is>
       </c>
       <c r="E1118" t="n">
-        <v>2110.924</v>
+        <v>2515.324</v>
       </c>
       <c r="F1118" t="n">
         <v>0.09000000000000001</v>
@@ -41431,7 +41431,7 @@
         <v>2110.924</v>
       </c>
       <c r="I1118" t="n">
-        <v>0.0</v>
+        <v>404.4</v>
       </c>
     </row>
     <row r="1119">
@@ -41493,7 +41493,7 @@
         </is>
       </c>
       <c r="E1120" t="n">
-        <v>611.691</v>
+        <v>356.85400000000004</v>
       </c>
       <c r="F1120" t="n">
         <v>0.20900000000000002</v>
@@ -41502,7 +41502,7 @@
         <v>0.0</v>
       </c>
       <c r="H1120" t="n">
-        <v>611.691</v>
+        <v>356.85400000000004</v>
       </c>
       <c r="I1120" t="n">
         <v>0.0</v>
@@ -41530,7 +41530,7 @@
         </is>
       </c>
       <c r="E1121" t="n">
-        <v>2831.248</v>
+        <v>2843.766</v>
       </c>
       <c r="F1121" t="n">
         <v>0.42000000000000004</v>
@@ -41539,7 +41539,7 @@
         <v>0.0</v>
       </c>
       <c r="H1121" t="n">
-        <v>2831.248</v>
+        <v>2843.766</v>
       </c>
       <c r="I1121" t="n">
         <v>0.0</v>
@@ -41604,7 +41604,7 @@
         </is>
       </c>
       <c r="E1123" t="n">
-        <v>737.864</v>
+        <v>665.826</v>
       </c>
       <c r="F1123" t="n">
         <v>0.416</v>
@@ -41613,7 +41613,7 @@
         <v>0.0</v>
       </c>
       <c r="H1123" t="n">
-        <v>737.864</v>
+        <v>665.826</v>
       </c>
       <c r="I1123" t="n">
         <v>0.0</v>
@@ -41641,7 +41641,7 @@
         </is>
       </c>
       <c r="E1124" t="n">
-        <v>2168.448</v>
+        <v>2173.4249999999997</v>
       </c>
       <c r="F1124" t="n">
         <v>0.0</v>
@@ -41650,7 +41650,7 @@
         <v>6274.357</v>
       </c>
       <c r="H1124" t="n">
-        <v>2168.448</v>
+        <v>2173.4249999999997</v>
       </c>
       <c r="I1124" t="n">
         <v>0.0</v>
@@ -41715,7 +41715,7 @@
         </is>
       </c>
       <c r="E1126" t="n">
-        <v>2301.766</v>
+        <v>2116.954</v>
       </c>
       <c r="F1126" t="n">
         <v>0.0</v>
@@ -41724,7 +41724,7 @@
         <v>0.0</v>
       </c>
       <c r="H1126" t="n">
-        <v>2301.766</v>
+        <v>2116.954</v>
       </c>
       <c r="I1126" t="n">
         <v>0.0</v>
@@ -41752,7 +41752,7 @@
         </is>
       </c>
       <c r="E1127" t="n">
-        <v>4197.408</v>
+        <v>4197.409</v>
       </c>
       <c r="F1127" t="n">
         <v>0.0</v>
@@ -41761,7 +41761,7 @@
         <v>0.0</v>
       </c>
       <c r="H1127" t="n">
-        <v>4197.408</v>
+        <v>4197.409</v>
       </c>
       <c r="I1127" t="n">
         <v>0.0</v>
@@ -41826,7 +41826,7 @@
         </is>
       </c>
       <c r="E1129" t="n">
-        <v>22769.600000000002</v>
+        <v>22719.2</v>
       </c>
       <c r="F1129" t="n">
         <v>6.4</v>
@@ -41835,7 +41835,7 @@
         <v>0.0</v>
       </c>
       <c r="H1129" t="n">
-        <v>22769.600000000002</v>
+        <v>22719.2</v>
       </c>
       <c r="I1129" t="n">
         <v>0.0</v>
@@ -41900,7 +41900,7 @@
         </is>
       </c>
       <c r="E1131" t="n">
-        <v>1487.188</v>
+        <v>2137.708</v>
       </c>
       <c r="F1131" t="n">
         <v>0.0</v>
@@ -41912,7 +41912,7 @@
         <v>1487.188</v>
       </c>
       <c r="I1131" t="n">
-        <v>0.0</v>
+        <v>650.52</v>
       </c>
     </row>
     <row r="1132">
@@ -41937,7 +41937,7 @@
         </is>
       </c>
       <c r="E1132" t="n">
-        <v>974.779</v>
+        <v>1519.2142</v>
       </c>
       <c r="F1132" t="n">
         <v>0.0</v>
@@ -41949,7 +41949,7 @@
         <v>974.779</v>
       </c>
       <c r="I1132" t="n">
-        <v>0.0</v>
+        <v>544.4352</v>
       </c>
     </row>
     <row r="1133">
@@ -41974,7 +41974,7 @@
         </is>
       </c>
       <c r="E1133" t="n">
-        <v>1673.337</v>
+        <v>1653.322</v>
       </c>
       <c r="F1133" t="n">
         <v>0.0</v>
@@ -41983,7 +41983,7 @@
         <v>0.0</v>
       </c>
       <c r="H1133" t="n">
-        <v>1673.337</v>
+        <v>1653.322</v>
       </c>
       <c r="I1133" t="n">
         <v>0.0</v>
@@ -42307,7 +42307,7 @@
         </is>
       </c>
       <c r="E1142" t="n">
-        <v>926.946</v>
+        <v>924.146</v>
       </c>
       <c r="F1142" t="n">
         <v>0.0</v>
@@ -42316,7 +42316,7 @@
         <v>0.0</v>
       </c>
       <c r="H1142" t="n">
-        <v>926.946</v>
+        <v>924.146</v>
       </c>
       <c r="I1142" t="n">
         <v>0.0</v>
@@ -42381,7 +42381,7 @@
         </is>
       </c>
       <c r="E1144" t="n">
-        <v>4292.188999999999</v>
+        <v>4218.1720000000005</v>
       </c>
       <c r="F1144" t="n">
         <v>0.428</v>
@@ -42390,7 +42390,7 @@
         <v>0.0</v>
       </c>
       <c r="H1144" t="n">
-        <v>4292.188999999999</v>
+        <v>4218.1720000000005</v>
       </c>
       <c r="I1144" t="n">
         <v>0.0</v>
@@ -42418,7 +42418,7 @@
         </is>
       </c>
       <c r="E1145" t="n">
-        <v>2401.094</v>
+        <v>2103.737</v>
       </c>
       <c r="F1145" t="n">
         <v>0.428</v>
@@ -42427,7 +42427,7 @@
         <v>0.0</v>
       </c>
       <c r="H1145" t="n">
-        <v>2401.094</v>
+        <v>2103.737</v>
       </c>
       <c r="I1145" t="n">
         <v>0.0</v>
@@ -42529,7 +42529,7 @@
         </is>
       </c>
       <c r="E1148" t="n">
-        <v>2752.279</v>
+        <v>2879.8590000000004</v>
       </c>
       <c r="F1148" t="n">
         <v>10.265</v>
@@ -42538,7 +42538,7 @@
         <v>0.0</v>
       </c>
       <c r="H1148" t="n">
-        <v>2752.279</v>
+        <v>2879.8590000000004</v>
       </c>
       <c r="I1148" t="n">
         <v>0.0</v>
@@ -42640,7 +42640,7 @@
         </is>
       </c>
       <c r="E1151" t="n">
-        <v>10359.863000000001</v>
+        <v>9849.349</v>
       </c>
       <c r="F1151" t="n">
         <v>39.898999999999994</v>
@@ -42649,7 +42649,7 @@
         <v>13.766</v>
       </c>
       <c r="H1151" t="n">
-        <v>10359.863000000001</v>
+        <v>9849.349</v>
       </c>
       <c r="I1151" t="n">
         <v>0.0</v>
@@ -42714,7 +42714,7 @@
         </is>
       </c>
       <c r="E1153" t="n">
-        <v>8790.918</v>
+        <v>8595.678</v>
       </c>
       <c r="F1153" t="n">
         <v>27.599</v>
@@ -42723,7 +42723,7 @@
         <v>7.155</v>
       </c>
       <c r="H1153" t="n">
-        <v>8790.918</v>
+        <v>8595.678</v>
       </c>
       <c r="I1153" t="n">
         <v>0.0</v>
@@ -42788,7 +42788,7 @@
         </is>
       </c>
       <c r="E1155" t="n">
-        <v>21431.600000000002</v>
+        <v>20979.600000000002</v>
       </c>
       <c r="F1155" t="n">
         <v>48.0</v>
@@ -42797,7 +42797,7 @@
         <v>16.8</v>
       </c>
       <c r="H1155" t="n">
-        <v>21431.600000000002</v>
+        <v>20979.600000000002</v>
       </c>
       <c r="I1155" t="n">
         <v>0.0</v>
@@ -42862,7 +42862,7 @@
         </is>
       </c>
       <c r="E1157" t="n">
-        <v>4443.455</v>
+        <v>4626.911</v>
       </c>
       <c r="F1157" t="n">
         <v>8.0</v>
@@ -42871,7 +42871,7 @@
         <v>0.0</v>
       </c>
       <c r="H1157" t="n">
-        <v>4443.455</v>
+        <v>4626.911</v>
       </c>
       <c r="I1157" t="n">
         <v>0.0</v>
@@ -42973,7 +42973,7 @@
         </is>
       </c>
       <c r="E1160" t="n">
-        <v>4306.708</v>
+        <v>4362.7119999999995</v>
       </c>
       <c r="F1160" t="n">
         <v>0.0</v>
@@ -42982,7 +42982,7 @@
         <v>0.0</v>
       </c>
       <c r="H1160" t="n">
-        <v>4306.708</v>
+        <v>4362.7119999999995</v>
       </c>
       <c r="I1160" t="n">
         <v>0.0</v>
@@ -43010,7 +43010,7 @@
         </is>
       </c>
       <c r="E1161" t="n">
-        <v>391.053</v>
+        <v>747.882</v>
       </c>
       <c r="F1161" t="n">
         <v>0.428</v>
@@ -43019,7 +43019,7 @@
         <v>0.0</v>
       </c>
       <c r="H1161" t="n">
-        <v>391.053</v>
+        <v>747.882</v>
       </c>
       <c r="I1161" t="n">
         <v>0.0</v>
@@ -43158,7 +43158,7 @@
         </is>
       </c>
       <c r="E1165" t="n">
-        <v>7492.0</v>
+        <v>7044.0</v>
       </c>
       <c r="F1165" t="n">
         <v>0.0</v>
@@ -43167,7 +43167,7 @@
         <v>4.0</v>
       </c>
       <c r="H1165" t="n">
-        <v>7492.0</v>
+        <v>7044.0</v>
       </c>
       <c r="I1165" t="n">
         <v>0.0</v>
@@ -43195,7 +43195,7 @@
         </is>
       </c>
       <c r="E1166" t="n">
-        <v>7690.686</v>
+        <v>7149.487999999999</v>
       </c>
       <c r="F1166" t="n">
         <v>0.0</v>
@@ -43204,7 +43204,7 @@
         <v>5.1000000000000005</v>
       </c>
       <c r="H1166" t="n">
-        <v>7690.686</v>
+        <v>7149.487999999999</v>
       </c>
       <c r="I1166" t="n">
         <v>0.0</v>
@@ -43232,7 +43232,7 @@
         </is>
       </c>
       <c r="E1167" t="n">
-        <v>13771.688</v>
+        <v>12634.296</v>
       </c>
       <c r="F1167" t="n">
         <v>0.0</v>
@@ -43241,7 +43241,7 @@
         <v>20.668</v>
       </c>
       <c r="H1167" t="n">
-        <v>13771.688</v>
+        <v>12634.296</v>
       </c>
       <c r="I1167" t="n">
         <v>0.0</v>
@@ -43417,7 +43417,7 @@
         </is>
       </c>
       <c r="E1172" t="n">
-        <v>7716.8</v>
+        <v>7675.2</v>
       </c>
       <c r="F1172" t="n">
         <v>0.6</v>
@@ -43426,7 +43426,7 @@
         <v>339.2</v>
       </c>
       <c r="H1172" t="n">
-        <v>7716.8</v>
+        <v>7675.2</v>
       </c>
       <c r="I1172" t="n">
         <v>0.0</v>
@@ -43713,7 +43713,7 @@
         </is>
       </c>
       <c r="E1180" t="n">
-        <v>714.0</v>
+        <v>709.2</v>
       </c>
       <c r="F1180" t="n">
         <v>0.0</v>
@@ -43722,7 +43722,7 @@
         <v>0.0</v>
       </c>
       <c r="H1180" t="n">
-        <v>714.0</v>
+        <v>709.2</v>
       </c>
       <c r="I1180" t="n">
         <v>0.0</v>
@@ -43750,7 +43750,7 @@
         </is>
       </c>
       <c r="E1181" t="n">
-        <v>2016.3999999999999</v>
+        <v>2020.8</v>
       </c>
       <c r="F1181" t="n">
         <v>0.0</v>
@@ -43759,7 +43759,7 @@
         <v>4.8</v>
       </c>
       <c r="H1181" t="n">
-        <v>2016.3999999999999</v>
+        <v>2020.8</v>
       </c>
       <c r="I1181" t="n">
         <v>0.0</v>
@@ -43787,7 +43787,7 @@
         </is>
       </c>
       <c r="E1182" t="n">
-        <v>2239.4</v>
+        <v>2238.8</v>
       </c>
       <c r="F1182" t="n">
         <v>0.4</v>
@@ -43796,7 +43796,7 @@
         <v>0.0</v>
       </c>
       <c r="H1182" t="n">
-        <v>2239.4</v>
+        <v>2238.8</v>
       </c>
       <c r="I1182" t="n">
         <v>0.0</v>
@@ -43861,7 +43861,7 @@
         </is>
       </c>
       <c r="E1184" t="n">
-        <v>2880.0</v>
+        <v>2917.2</v>
       </c>
       <c r="F1184" t="n">
         <v>8.4</v>
@@ -43870,7 +43870,7 @@
         <v>0.0</v>
       </c>
       <c r="H1184" t="n">
-        <v>2880.0</v>
+        <v>2917.2</v>
       </c>
       <c r="I1184" t="n">
         <v>0.0</v>
@@ -43898,7 +43898,7 @@
         </is>
       </c>
       <c r="E1185" t="n">
-        <v>2457.906</v>
+        <v>2454.705</v>
       </c>
       <c r="F1185" t="n">
         <v>0.26699999999999996</v>
@@ -43907,7 +43907,7 @@
         <v>3.2</v>
       </c>
       <c r="H1185" t="n">
-        <v>2457.906</v>
+        <v>2454.705</v>
       </c>
       <c r="I1185" t="n">
         <v>0.0</v>
@@ -43935,7 +43935,7 @@
         </is>
       </c>
       <c r="E1186" t="n">
-        <v>2073.6</v>
+        <v>2054.4</v>
       </c>
       <c r="F1186" t="n">
         <v>0.0</v>
@@ -43944,7 +43944,7 @@
         <v>0.0</v>
       </c>
       <c r="H1186" t="n">
-        <v>2073.6</v>
+        <v>2054.4</v>
       </c>
       <c r="I1186" t="n">
         <v>0.0</v>
@@ -44009,7 +44009,7 @@
         </is>
       </c>
       <c r="E1188" t="n">
-        <v>2777.389</v>
+        <v>2777.388</v>
       </c>
       <c r="F1188" t="n">
         <v>0.6669999999999999</v>
@@ -44018,7 +44018,7 @@
         <v>0.0</v>
       </c>
       <c r="H1188" t="n">
-        <v>2777.389</v>
+        <v>2777.388</v>
       </c>
       <c r="I1188" t="n">
         <v>0.0</v>
@@ -44046,7 +44046,7 @@
         </is>
       </c>
       <c r="E1189" t="n">
-        <v>1780.8000000000002</v>
+        <v>1769.6000000000001</v>
       </c>
       <c r="F1189" t="n">
         <v>2.8</v>
@@ -44055,7 +44055,7 @@
         <v>0.8</v>
       </c>
       <c r="H1189" t="n">
-        <v>1780.8000000000002</v>
+        <v>1769.6000000000001</v>
       </c>
       <c r="I1189" t="n">
         <v>0.0</v>
@@ -44120,7 +44120,7 @@
         </is>
       </c>
       <c r="E1191" t="n">
-        <v>1302.13</v>
+        <v>1272.127</v>
       </c>
       <c r="F1191" t="n">
         <v>0.0</v>
@@ -44129,7 +44129,7 @@
         <v>708.071</v>
       </c>
       <c r="H1191" t="n">
-        <v>1302.13</v>
+        <v>1272.127</v>
       </c>
       <c r="I1191" t="n">
         <v>0.0</v>
@@ -44527,7 +44527,7 @@
         </is>
       </c>
       <c r="E1202" t="n">
-        <v>4399.02</v>
+        <v>5134.758400000001</v>
       </c>
       <c r="F1202" t="n">
         <v>0.0</v>
@@ -44539,7 +44539,7 @@
         <v>4399.02</v>
       </c>
       <c r="I1202" t="n">
-        <v>0.0</v>
+        <v>735.7384</v>
       </c>
     </row>
     <row r="1203">
@@ -44934,7 +44934,7 @@
         </is>
       </c>
       <c r="E1213" t="n">
-        <v>2871.745</v>
+        <v>2863.933</v>
       </c>
       <c r="F1213" t="n">
         <v>0.0</v>
@@ -44943,7 +44943,7 @@
         <v>636.93</v>
       </c>
       <c r="H1213" t="n">
-        <v>2871.745</v>
+        <v>2863.933</v>
       </c>
       <c r="I1213" t="n">
         <v>0.0</v>
@@ -44971,7 +44971,7 @@
         </is>
       </c>
       <c r="E1214" t="n">
-        <v>423.20300000000003</v>
+        <v>401.19100000000003</v>
       </c>
       <c r="F1214" t="n">
         <v>0.0</v>
@@ -44980,7 +44980,7 @@
         <v>4.26</v>
       </c>
       <c r="H1214" t="n">
-        <v>423.20300000000003</v>
+        <v>401.19100000000003</v>
       </c>
       <c r="I1214" t="n">
         <v>0.0</v>
@@ -45378,7 +45378,7 @@
         </is>
       </c>
       <c r="E1225" t="n">
-        <v>1295.824</v>
+        <v>1267.421</v>
       </c>
       <c r="F1225" t="n">
         <v>0.0</v>
@@ -45387,7 +45387,7 @@
         <v>0.0</v>
       </c>
       <c r="H1225" t="n">
-        <v>1295.824</v>
+        <v>1267.421</v>
       </c>
       <c r="I1225" t="n">
         <v>0.0</v>
@@ -45415,7 +45415,7 @@
         </is>
       </c>
       <c r="E1226" t="n">
-        <v>2508.3650000000002</v>
+        <v>2341.3590000000004</v>
       </c>
       <c r="F1226" t="n">
         <v>0.0</v>
@@ -45424,7 +45424,7 @@
         <v>1.7750000000000001</v>
       </c>
       <c r="H1226" t="n">
-        <v>2508.3650000000002</v>
+        <v>2341.3590000000004</v>
       </c>
       <c r="I1226" t="n">
         <v>0.0</v>
@@ -45452,7 +45452,7 @@
         </is>
       </c>
       <c r="E1227" t="n">
-        <v>5420.788</v>
+        <v>5418.48</v>
       </c>
       <c r="F1227" t="n">
         <v>0.0</v>
@@ -45461,7 +45461,7 @@
         <v>0.0</v>
       </c>
       <c r="H1227" t="n">
-        <v>5420.788</v>
+        <v>5418.48</v>
       </c>
       <c r="I1227" t="n">
         <v>0.0</v>
@@ -45526,7 +45526,7 @@
         </is>
       </c>
       <c r="E1229" t="n">
-        <v>4087.859</v>
+        <v>3818.264</v>
       </c>
       <c r="F1229" t="n">
         <v>0.0</v>
@@ -45535,7 +45535,7 @@
         <v>5.991</v>
       </c>
       <c r="H1229" t="n">
-        <v>4087.859</v>
+        <v>3818.264</v>
       </c>
       <c r="I1229" t="n">
         <v>0.0</v>
@@ -45600,7 +45600,7 @@
         </is>
       </c>
       <c r="E1231" t="n">
-        <v>3609.371</v>
+        <v>3588.07</v>
       </c>
       <c r="F1231" t="n">
         <v>0.0</v>
@@ -45609,7 +45609,7 @@
         <v>0.0</v>
       </c>
       <c r="H1231" t="n">
-        <v>3609.371</v>
+        <v>3588.07</v>
       </c>
       <c r="I1231" t="n">
         <v>0.0</v>
@@ -45711,7 +45711,7 @@
         </is>
       </c>
       <c r="E1234" t="n">
-        <v>1899.558</v>
+        <v>2037.234</v>
       </c>
       <c r="F1234" t="n">
         <v>3.639</v>
@@ -45720,7 +45720,7 @@
         <v>1567.1960000000001</v>
       </c>
       <c r="H1234" t="n">
-        <v>1899.558</v>
+        <v>2037.234</v>
       </c>
       <c r="I1234" t="n">
         <v>0.0</v>
@@ -45785,7 +45785,7 @@
         </is>
       </c>
       <c r="E1236" t="n">
-        <v>4096.931</v>
+        <v>4036.577</v>
       </c>
       <c r="F1236" t="n">
         <v>0.0</v>
@@ -45794,7 +45794,7 @@
         <v>0.0</v>
       </c>
       <c r="H1236" t="n">
-        <v>4096.931</v>
+        <v>4036.577</v>
       </c>
       <c r="I1236" t="n">
         <v>0.0</v>
@@ -45970,7 +45970,7 @@
         </is>
       </c>
       <c r="E1241" t="n">
-        <v>1556.171</v>
+        <v>1541.97</v>
       </c>
       <c r="F1241" t="n">
         <v>0.0</v>
@@ -45979,7 +45979,7 @@
         <v>1.183</v>
       </c>
       <c r="H1241" t="n">
-        <v>1556.171</v>
+        <v>1541.97</v>
       </c>
       <c r="I1241" t="n">
         <v>0.0</v>
@@ -46155,7 +46155,7 @@
         </is>
       </c>
       <c r="E1246" t="n">
-        <v>2475.321</v>
+        <v>2579.286</v>
       </c>
       <c r="F1246" t="n">
         <v>0.583</v>
@@ -46164,7 +46164,7 @@
         <v>0.0</v>
       </c>
       <c r="H1246" t="n">
-        <v>2475.321</v>
+        <v>2579.286</v>
       </c>
       <c r="I1246" t="n">
         <v>0.0</v>
@@ -46192,7 +46192,7 @@
         </is>
       </c>
       <c r="E1247" t="n">
-        <v>1452.24</v>
+        <v>1495.881</v>
       </c>
       <c r="F1247" t="n">
         <v>0.35100000000000003</v>
@@ -46201,7 +46201,7 @@
         <v>0.0</v>
       </c>
       <c r="H1247" t="n">
-        <v>1452.24</v>
+        <v>1495.881</v>
       </c>
       <c r="I1247" t="n">
         <v>0.0</v>
@@ -46266,7 +46266,7 @@
         </is>
       </c>
       <c r="E1249" t="n">
-        <v>657.585</v>
+        <v>654.615</v>
       </c>
       <c r="F1249" t="n">
         <v>0.0</v>
@@ -46275,7 +46275,7 @@
         <v>0.135</v>
       </c>
       <c r="H1249" t="n">
-        <v>657.585</v>
+        <v>654.615</v>
       </c>
       <c r="I1249" t="n">
         <v>0.0</v>
@@ -46488,7 +46488,7 @@
         </is>
       </c>
       <c r="E1255" t="n">
-        <v>629.1</v>
+        <v>461.97</v>
       </c>
       <c r="F1255" t="n">
         <v>0.0</v>
@@ -46497,7 +46497,7 @@
         <v>0.0</v>
       </c>
       <c r="H1255" t="n">
-        <v>629.1</v>
+        <v>461.97</v>
       </c>
       <c r="I1255" t="n">
         <v>0.0</v>
@@ -47746,7 +47746,7 @@
         </is>
       </c>
       <c r="E1289" t="n">
-        <v>0.0</v>
+        <v>5435.9424</v>
       </c>
       <c r="F1289" t="n">
         <v>0.0</v>
@@ -47758,7 +47758,7 @@
         <v>0.0</v>
       </c>
       <c r="I1289" t="n">
-        <v>0.0</v>
+        <v>5435.9424</v>
       </c>
     </row>
     <row r="1290">
@@ -49004,7 +49004,7 @@
         </is>
       </c>
       <c r="E1323" t="n">
-        <v>9278.0</v>
+        <v>9248.0</v>
       </c>
       <c r="F1323" t="n">
         <v>0.0</v>
@@ -49013,7 +49013,7 @@
         <v>18.0</v>
       </c>
       <c r="H1323" t="n">
-        <v>9278.0</v>
+        <v>9248.0</v>
       </c>
       <c r="I1323" t="n">
         <v>0.0</v>
@@ -49966,7 +49966,7 @@
         </is>
       </c>
       <c r="E1349" t="n">
-        <v>364.1</v>
+        <v>364.7</v>
       </c>
       <c r="F1349" t="n">
         <v>0.0</v>
@@ -49975,7 +49975,7 @@
         <v>9.6</v>
       </c>
       <c r="H1349" t="n">
-        <v>364.1</v>
+        <v>364.7</v>
       </c>
       <c r="I1349" t="n">
         <v>0.0</v>
@@ -50262,7 +50262,7 @@
         </is>
       </c>
       <c r="E1357" t="n">
-        <v>3427.685</v>
+        <v>4263.02</v>
       </c>
       <c r="F1357" t="n">
         <v>0.0</v>
@@ -50271,7 +50271,7 @@
         <v>45.37</v>
       </c>
       <c r="H1357" t="n">
-        <v>3427.685</v>
+        <v>4263.02</v>
       </c>
       <c r="I1357" t="n">
         <v>0.0</v>
@@ -50817,7 +50817,7 @@
         </is>
       </c>
       <c r="E1372" t="n">
-        <v>4913.564</v>
+        <v>5201.796</v>
       </c>
       <c r="F1372" t="n">
         <v>2.669</v>
@@ -50826,7 +50826,7 @@
         <v>0.0</v>
       </c>
       <c r="H1372" t="n">
-        <v>4913.564</v>
+        <v>5201.796</v>
       </c>
       <c r="I1372" t="n">
         <v>0.0</v>
@@ -50854,7 +50854,7 @@
         </is>
       </c>
       <c r="E1373" t="n">
-        <v>1918.867</v>
+        <v>1918.8670000000002</v>
       </c>
       <c r="F1373" t="n">
         <v>0.0</v>
@@ -50863,7 +50863,7 @@
         <v>42.701</v>
       </c>
       <c r="H1373" t="n">
-        <v>1918.867</v>
+        <v>1918.8670000000002</v>
       </c>
       <c r="I1373" t="n">
         <v>0.0</v>
@@ -50965,7 +50965,7 @@
         </is>
       </c>
       <c r="E1376" t="n">
-        <v>1039.5</v>
+        <v>913.5</v>
       </c>
       <c r="F1376" t="n">
         <v>0.0</v>
@@ -50974,7 +50974,7 @@
         <v>90.0</v>
       </c>
       <c r="H1376" t="n">
-        <v>1039.5</v>
+        <v>913.5</v>
       </c>
       <c r="I1376" t="n">
         <v>0.0</v>
@@ -51298,7 +51298,7 @@
         </is>
       </c>
       <c r="E1385" t="n">
-        <v>3345.174</v>
+        <v>3285.126</v>
       </c>
       <c r="F1385" t="n">
         <v>0.0</v>
@@ -51307,7 +51307,7 @@
         <v>236.85600000000002</v>
       </c>
       <c r="H1385" t="n">
-        <v>3345.174</v>
+        <v>3285.126</v>
       </c>
       <c r="I1385" t="n">
         <v>0.0</v>
@@ -51335,7 +51335,7 @@
         </is>
       </c>
       <c r="E1386" t="n">
-        <v>587.016</v>
+        <v>571.021</v>
       </c>
       <c r="F1386" t="n">
         <v>0.0</v>
@@ -51344,7 +51344,7 @@
         <v>0.416</v>
       </c>
       <c r="H1386" t="n">
-        <v>587.016</v>
+        <v>571.021</v>
       </c>
       <c r="I1386" t="n">
         <v>0.0</v>
@@ -51372,7 +51372,7 @@
         </is>
       </c>
       <c r="E1387" t="n">
-        <v>644.181</v>
+        <v>636.174</v>
       </c>
       <c r="F1387" t="n">
         <v>0.0</v>
@@ -51381,7 +51381,7 @@
         <v>0.5559999999999999</v>
       </c>
       <c r="H1387" t="n">
-        <v>644.181</v>
+        <v>636.174</v>
       </c>
       <c r="I1387" t="n">
         <v>0.0</v>
@@ -51483,7 +51483,7 @@
         </is>
       </c>
       <c r="E1390" t="n">
-        <v>1155.404</v>
+        <v>1131.073</v>
       </c>
       <c r="F1390" t="n">
         <v>0.0</v>
@@ -51492,7 +51492,7 @@
         <v>0.0</v>
       </c>
       <c r="H1390" t="n">
-        <v>1155.404</v>
+        <v>1131.073</v>
       </c>
       <c r="I1390" t="n">
         <v>0.0</v>
@@ -52223,7 +52223,7 @@
         </is>
       </c>
       <c r="E1410" t="n">
-        <v>180.48</v>
+        <v>176.16</v>
       </c>
       <c r="F1410" t="n">
         <v>0.0</v>
@@ -52232,7 +52232,7 @@
         <v>0.0</v>
       </c>
       <c r="H1410" t="n">
-        <v>180.48</v>
+        <v>176.16</v>
       </c>
       <c r="I1410" t="n">
         <v>0.0</v>
@@ -52593,7 +52593,7 @@
         </is>
       </c>
       <c r="E1420" t="n">
-        <v>85.401</v>
+        <v>85.402</v>
       </c>
       <c r="F1420" t="n">
         <v>0.0</v>
@@ -52602,7 +52602,7 @@
         <v>141.446</v>
       </c>
       <c r="H1420" t="n">
-        <v>85.401</v>
+        <v>85.402</v>
       </c>
       <c r="I1420" t="n">
         <v>0.0</v>
@@ -52926,7 +52926,7 @@
         </is>
       </c>
       <c r="E1429" t="n">
-        <v>955.875</v>
+        <v>1673.7826</v>
       </c>
       <c r="F1429" t="n">
         <v>0.0</v>
@@ -52935,10 +52935,10 @@
         <v>112.201</v>
       </c>
       <c r="H1429" t="n">
-        <v>955.875</v>
+        <v>947.869</v>
       </c>
       <c r="I1429" t="n">
-        <v>0.0</v>
+        <v>725.9136</v>
       </c>
     </row>
     <row r="1430">
@@ -53444,7 +53444,7 @@
         </is>
       </c>
       <c r="E1443" t="n">
-        <v>26.497</v>
+        <v>27.247</v>
       </c>
       <c r="F1443" t="n">
         <v>0.0</v>
@@ -53453,7 +53453,7 @@
         <v>33.75</v>
       </c>
       <c r="H1443" t="n">
-        <v>26.497</v>
+        <v>27.247</v>
       </c>
       <c r="I1443" t="n">
         <v>0.0</v>
@@ -53481,7 +53481,7 @@
         </is>
       </c>
       <c r="E1444" t="n">
-        <v>455.247</v>
+        <v>451.247</v>
       </c>
       <c r="F1444" t="n">
         <v>0.0</v>
@@ -53490,7 +53490,7 @@
         <v>40.5</v>
       </c>
       <c r="H1444" t="n">
-        <v>455.247</v>
+        <v>451.247</v>
       </c>
       <c r="I1444" t="n">
         <v>0.0</v>
@@ -53518,7 +53518,7 @@
         </is>
       </c>
       <c r="E1445" t="n">
-        <v>1221.878</v>
+        <v>1221.879</v>
       </c>
       <c r="F1445" t="n">
         <v>0.0</v>
@@ -53527,7 +53527,7 @@
         <v>10.666</v>
       </c>
       <c r="H1445" t="n">
-        <v>1221.878</v>
+        <v>1221.879</v>
       </c>
       <c r="I1445" t="n">
         <v>0.0</v>
@@ -53555,7 +53555,7 @@
         </is>
       </c>
       <c r="E1446" t="n">
-        <v>543.0</v>
+        <v>538.125</v>
       </c>
       <c r="F1446" t="n">
         <v>0.0</v>
@@ -53564,7 +53564,7 @@
         <v>20.625</v>
       </c>
       <c r="H1446" t="n">
-        <v>543.0</v>
+        <v>538.125</v>
       </c>
       <c r="I1446" t="n">
         <v>0.0</v>
@@ -53592,7 +53592,7 @@
         </is>
       </c>
       <c r="E1447" t="n">
-        <v>226.625</v>
+        <v>220.625</v>
       </c>
       <c r="F1447" t="n">
         <v>0.0</v>
@@ -53601,7 +53601,7 @@
         <v>6.75</v>
       </c>
       <c r="H1447" t="n">
-        <v>226.625</v>
+        <v>220.625</v>
       </c>
       <c r="I1447" t="n">
         <v>0.0</v>
@@ -53629,7 +53629,7 @@
         </is>
       </c>
       <c r="E1448" t="n">
-        <v>114.0</v>
+        <v>85.5</v>
       </c>
       <c r="F1448" t="n">
         <v>0.0</v>
@@ -53638,7 +53638,7 @@
         <v>436.5</v>
       </c>
       <c r="H1448" t="n">
-        <v>114.0</v>
+        <v>85.5</v>
       </c>
       <c r="I1448" t="n">
         <v>0.0</v>
@@ -53666,7 +53666,7 @@
         </is>
       </c>
       <c r="E1449" t="n">
-        <v>571.875</v>
+        <v>569.625</v>
       </c>
       <c r="F1449" t="n">
         <v>0.0</v>
@@ -53675,7 +53675,7 @@
         <v>38.25</v>
       </c>
       <c r="H1449" t="n">
-        <v>571.875</v>
+        <v>569.625</v>
       </c>
       <c r="I1449" t="n">
         <v>0.0</v>
@@ -53703,7 +53703,7 @@
         </is>
       </c>
       <c r="E1450" t="n">
-        <v>702.5</v>
+        <v>701.375</v>
       </c>
       <c r="F1450" t="n">
         <v>0.375</v>
@@ -53712,7 +53712,7 @@
         <v>3.75</v>
       </c>
       <c r="H1450" t="n">
-        <v>702.5</v>
+        <v>701.375</v>
       </c>
       <c r="I1450" t="n">
         <v>0.0</v>
@@ -53740,7 +53740,7 @@
         </is>
       </c>
       <c r="E1451" t="n">
-        <v>513.0</v>
+        <v>480.0</v>
       </c>
       <c r="F1451" t="n">
         <v>1.5</v>
@@ -53749,7 +53749,7 @@
         <v>0.0</v>
       </c>
       <c r="H1451" t="n">
-        <v>513.0</v>
+        <v>480.0</v>
       </c>
       <c r="I1451" t="n">
         <v>0.0</v>
@@ -53851,7 +53851,7 @@
         </is>
       </c>
       <c r="E1454" t="n">
-        <v>215.25</v>
+        <v>410.25</v>
       </c>
       <c r="F1454" t="n">
         <v>0.0</v>
@@ -53860,7 +53860,7 @@
         <v>55.5</v>
       </c>
       <c r="H1454" t="n">
-        <v>215.25</v>
+        <v>410.25</v>
       </c>
       <c r="I1454" t="n">
         <v>0.0</v>
@@ -53888,7 +53888,7 @@
         </is>
       </c>
       <c r="E1455" t="n">
-        <v>342.0</v>
+        <v>334.5</v>
       </c>
       <c r="F1455" t="n">
         <v>0.0</v>
@@ -53897,7 +53897,7 @@
         <v>297.75</v>
       </c>
       <c r="H1455" t="n">
-        <v>342.0</v>
+        <v>334.5</v>
       </c>
       <c r="I1455" t="n">
         <v>0.0</v>
@@ -53925,7 +53925,7 @@
         </is>
       </c>
       <c r="E1456" t="n">
-        <v>3309.0</v>
+        <v>3305.25</v>
       </c>
       <c r="F1456" t="n">
         <v>0.0</v>
@@ -53934,7 +53934,7 @@
         <v>37.5</v>
       </c>
       <c r="H1456" t="n">
-        <v>3309.0</v>
+        <v>3305.25</v>
       </c>
       <c r="I1456" t="n">
         <v>0.0</v>
@@ -53999,7 +53999,7 @@
         </is>
       </c>
       <c r="E1458" t="n">
-        <v>225.625</v>
+        <v>226.625</v>
       </c>
       <c r="F1458" t="n">
         <v>0.0</v>
@@ -54008,7 +54008,7 @@
         <v>34.875</v>
       </c>
       <c r="H1458" t="n">
-        <v>225.625</v>
+        <v>226.625</v>
       </c>
       <c r="I1458" t="n">
         <v>0.0</v>
@@ -54036,7 +54036,7 @@
         </is>
       </c>
       <c r="E1459" t="n">
-        <v>1088.869</v>
+        <v>1088.87</v>
       </c>
       <c r="F1459" t="n">
         <v>0.0</v>
@@ -54045,7 +54045,7 @@
         <v>0.5</v>
       </c>
       <c r="H1459" t="n">
-        <v>1088.869</v>
+        <v>1088.87</v>
       </c>
       <c r="I1459" t="n">
         <v>0.0</v>
@@ -54517,7 +54517,7 @@
         </is>
       </c>
       <c r="E1472" t="n">
-        <v>122.79</v>
+        <v>1585.2924</v>
       </c>
       <c r="F1472" t="n">
         <v>0.0</v>
@@ -54529,7 +54529,7 @@
         <v>122.79</v>
       </c>
       <c r="I1472" t="n">
-        <v>0.0</v>
+        <v>1462.5024</v>
       </c>
     </row>
     <row r="1473">
@@ -54554,7 +54554,7 @@
         </is>
       </c>
       <c r="E1473" t="n">
-        <v>12.786999999999999</v>
+        <v>3.197</v>
       </c>
       <c r="F1473" t="n">
         <v>0.0</v>
@@ -54563,7 +54563,7 @@
         <v>0.0</v>
       </c>
       <c r="H1473" t="n">
-        <v>12.786999999999999</v>
+        <v>3.197</v>
       </c>
       <c r="I1473" t="n">
         <v>0.0</v>
@@ -54628,7 +54628,7 @@
         </is>
       </c>
       <c r="E1475" t="n">
-        <v>970.777</v>
+        <v>968.107</v>
       </c>
       <c r="F1475" t="n">
         <v>0.0</v>
@@ -54637,7 +54637,7 @@
         <v>0.0</v>
       </c>
       <c r="H1475" t="n">
-        <v>970.777</v>
+        <v>968.107</v>
       </c>
       <c r="I1475" t="n">
         <v>0.0</v>
@@ -54702,7 +54702,7 @@
         </is>
       </c>
       <c r="E1477" t="n">
-        <v>3883.107</v>
+        <v>3869.763</v>
       </c>
       <c r="F1477" t="n">
         <v>0.0</v>
@@ -54711,7 +54711,7 @@
         <v>939.418</v>
       </c>
       <c r="H1477" t="n">
-        <v>3883.107</v>
+        <v>3869.763</v>
       </c>
       <c r="I1477" t="n">
         <v>0.0</v>
@@ -54813,7 +54813,7 @@
         </is>
       </c>
       <c r="E1480" t="n">
-        <v>6132.718</v>
+        <v>6099.263999999999</v>
       </c>
       <c r="F1480" t="n">
         <v>0.589</v>
@@ -54822,7 +54822,7 @@
         <v>661.475</v>
       </c>
       <c r="H1480" t="n">
-        <v>6132.718</v>
+        <v>6099.263999999999</v>
       </c>
       <c r="I1480" t="n">
         <v>0.0</v>
@@ -54850,7 +54850,7 @@
         </is>
       </c>
       <c r="E1481" t="n">
-        <v>2403.479</v>
+        <v>2383.3810000000003</v>
       </c>
       <c r="F1481" t="n">
         <v>65.467</v>
@@ -54859,7 +54859,7 @@
         <v>121.834</v>
       </c>
       <c r="H1481" t="n">
-        <v>2403.479</v>
+        <v>2383.3810000000003</v>
       </c>
       <c r="I1481" t="n">
         <v>0.0</v>
@@ -55146,7 +55146,7 @@
         </is>
       </c>
       <c r="E1489" t="n">
-        <v>5491.2</v>
+        <v>5475.599999999999</v>
       </c>
       <c r="F1489" t="n">
         <v>1.8</v>
@@ -55155,7 +55155,7 @@
         <v>0.0</v>
       </c>
       <c r="H1489" t="n">
-        <v>5491.2</v>
+        <v>5475.599999999999</v>
       </c>
       <c r="I1489" t="n">
         <v>0.0</v>
@@ -55953,13 +55953,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9BC35A3-6796-4FC4-B90C-7F5662AB18F7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDA7D5A4-67FB-4688-8F2F-D40A813C6407}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF11B3F2-6E75-4E28-9120-92D8D2C91D02}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{213BE490-A5FB-485C-8E5C-1877E97CEAFA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DA5A01C-8B78-43FB-9405-2E8A907BBEA7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A5E2721-9368-416A-A07A-817CB84005EE}"/>
 </file>
--- a/Inventory_KNIME.xlsx
+++ b/Inventory_KNIME.xlsx
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>772.7</v>
+        <v>772.1</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -913,7 +913,7 @@
         <v>2.0</v>
       </c>
       <c r="H23" t="n">
-        <v>772.7</v>
+        <v>772.1</v>
       </c>
       <c r="I23" t="n">
         <v>0.0</v>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>161.7</v>
+        <v>158.7</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -950,7 +950,7 @@
         <v>0.4</v>
       </c>
       <c r="H24" t="n">
-        <v>161.7</v>
+        <v>158.7</v>
       </c>
       <c r="I24" t="n">
         <v>0.0</v>
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3535.3430000000003</v>
+        <v>3427.5860000000002</v>
       </c>
       <c r="F34" t="n">
         <v>37.148</v>
@@ -1320,7 +1320,7 @@
         <v>4.971</v>
       </c>
       <c r="H34" t="n">
-        <v>3535.3430000000003</v>
+        <v>3427.5860000000002</v>
       </c>
       <c r="I34" t="n">
         <v>0.0</v>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2059.9610000000002</v>
+        <v>2027.0220000000002</v>
       </c>
       <c r="F35" t="n">
         <v>282.264</v>
@@ -1357,7 +1357,7 @@
         <v>216.545</v>
       </c>
       <c r="H35" t="n">
-        <v>2059.9610000000002</v>
+        <v>2027.0220000000002</v>
       </c>
       <c r="I35" t="n">
         <v>0.0</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1654.652</v>
+        <v>1648.398</v>
       </c>
       <c r="F39" t="n">
         <v>2200.261</v>
@@ -1505,7 +1505,7 @@
         <v>70.722</v>
       </c>
       <c r="H39" t="n">
-        <v>1654.652</v>
+        <v>1648.398</v>
       </c>
       <c r="I39" t="n">
         <v>0.0</v>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1037.7849999999999</v>
+        <v>1036.181</v>
       </c>
       <c r="F42" t="n">
         <v>767.328</v>
@@ -1616,7 +1616,7 @@
         <v>332.94</v>
       </c>
       <c r="H42" t="n">
-        <v>1037.7849999999999</v>
+        <v>1036.181</v>
       </c>
       <c r="I42" t="n">
         <v>0.0</v>
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>10835.55</v>
+        <v>9700.35</v>
       </c>
       <c r="F43" t="n">
         <v>3.3</v>
@@ -1653,7 +1653,7 @@
         <v>409.2</v>
       </c>
       <c r="H43" t="n">
-        <v>10835.55</v>
+        <v>9700.35</v>
       </c>
       <c r="I43" t="n">
         <v>0.0</v>
@@ -2532,7 +2532,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>110.68100000000001</v>
+        <v>109.08</v>
       </c>
       <c r="F67" t="n">
         <v>3.467</v>
@@ -2541,7 +2541,7 @@
         <v>0.0</v>
       </c>
       <c r="H67" t="n">
-        <v>110.68100000000001</v>
+        <v>109.08</v>
       </c>
       <c r="I67" t="n">
         <v>0.0</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3245.8</v>
+        <v>3235.7999999999997</v>
       </c>
       <c r="F70" t="n">
         <v>1.2</v>
@@ -2652,7 +2652,7 @@
         <v>0.0</v>
       </c>
       <c r="H70" t="n">
-        <v>3245.8</v>
+        <v>3235.7999999999997</v>
       </c>
       <c r="I70" t="n">
         <v>0.0</v>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1366.838</v>
+        <v>1366.571</v>
       </c>
       <c r="F71" t="n">
         <v>4.801</v>
@@ -2689,7 +2689,7 @@
         <v>17.069000000000003</v>
       </c>
       <c r="H71" t="n">
-        <v>1366.838</v>
+        <v>1366.571</v>
       </c>
       <c r="I71" t="n">
         <v>0.0</v>
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>329.908</v>
+        <v>329.641</v>
       </c>
       <c r="F72" t="n">
         <v>0.0</v>
@@ -2726,7 +2726,7 @@
         <v>4.267</v>
       </c>
       <c r="H72" t="n">
-        <v>329.908</v>
+        <v>329.641</v>
       </c>
       <c r="I72" t="n">
         <v>0.0</v>
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1790.7099999999998</v>
+        <v>1772.489</v>
       </c>
       <c r="F73" t="n">
         <v>5.777</v>
@@ -2763,7 +2763,7 @@
         <v>0.0</v>
       </c>
       <c r="H73" t="n">
-        <v>1790.7099999999998</v>
+        <v>1772.489</v>
       </c>
       <c r="I73" t="n">
         <v>0.0</v>
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1443.114</v>
+        <v>1441.5130000000001</v>
       </c>
       <c r="F74" t="n">
         <v>0.0</v>
@@ -2800,7 +2800,7 @@
         <v>0.0</v>
       </c>
       <c r="H74" t="n">
-        <v>1443.114</v>
+        <v>1441.5130000000001</v>
       </c>
       <c r="I74" t="n">
         <v>0.0</v>
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6020.486</v>
+        <v>5827.928</v>
       </c>
       <c r="F75" t="n">
         <v>9.601</v>
@@ -2837,7 +2837,7 @@
         <v>17.069000000000003</v>
       </c>
       <c r="H75" t="n">
-        <v>6020.486</v>
+        <v>5827.928</v>
       </c>
       <c r="I75" t="n">
         <v>0.0</v>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1127.34</v>
+        <v>1123.607</v>
       </c>
       <c r="F77" t="n">
         <v>50.94</v>
@@ -2911,7 +2911,7 @@
         <v>0.0</v>
       </c>
       <c r="H77" t="n">
-        <v>1127.34</v>
+        <v>1123.607</v>
       </c>
       <c r="I77" t="n">
         <v>0.0</v>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>488.389</v>
+        <v>486.388</v>
       </c>
       <c r="F78" t="n">
         <v>0.0</v>
@@ -2948,7 +2948,7 @@
         <v>0.083</v>
       </c>
       <c r="H78" t="n">
-        <v>488.389</v>
+        <v>486.388</v>
       </c>
       <c r="I78" t="n">
         <v>0.0</v>
@@ -3198,7 +3198,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3319.932</v>
+        <v>3319.9320000000002</v>
       </c>
       <c r="F85" t="n">
         <v>0.0</v>
@@ -3207,7 +3207,7 @@
         <v>0.0</v>
       </c>
       <c r="H85" t="n">
-        <v>3319.932</v>
+        <v>3319.9320000000002</v>
       </c>
       <c r="I85" t="n">
         <v>0.0</v>
@@ -4012,7 +4012,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>738.091</v>
+        <v>735.422</v>
       </c>
       <c r="F107" t="n">
         <v>0.0</v>
@@ -4021,7 +4021,7 @@
         <v>18.96</v>
       </c>
       <c r="H107" t="n">
-        <v>738.091</v>
+        <v>735.422</v>
       </c>
       <c r="I107" t="n">
         <v>0.0</v>
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>893.742</v>
+        <v>893.743</v>
       </c>
       <c r="F109" t="n">
         <v>0.0</v>
@@ -4095,7 +4095,7 @@
         <v>69.38900000000001</v>
       </c>
       <c r="H109" t="n">
-        <v>893.742</v>
+        <v>893.743</v>
       </c>
       <c r="I109" t="n">
         <v>0.0</v>
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>469.042</v>
+        <v>463.704</v>
       </c>
       <c r="F113" t="n">
         <v>0.0</v>
@@ -4243,7 +4243,7 @@
         <v>8.283999999999999</v>
       </c>
       <c r="H113" t="n">
-        <v>469.042</v>
+        <v>463.704</v>
       </c>
       <c r="I113" t="n">
         <v>0.0</v>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1281.04</v>
+        <v>1171.36</v>
       </c>
       <c r="F122" t="n">
         <v>0.12000000000000001</v>
@@ -4576,7 +4576,7 @@
         <v>25.44</v>
       </c>
       <c r="H122" t="n">
-        <v>1281.04</v>
+        <v>1171.36</v>
       </c>
       <c r="I122" t="n">
         <v>0.0</v>
@@ -4604,7 +4604,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1235.701</v>
+        <v>1204.202</v>
       </c>
       <c r="F123" t="n">
         <v>0.225</v>
@@ -4613,7 +4613,7 @@
         <v>116.775</v>
       </c>
       <c r="H123" t="n">
-        <v>1235.701</v>
+        <v>1204.202</v>
       </c>
       <c r="I123" t="n">
         <v>0.0</v>
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4328.954</v>
+        <v>4244.039000000001</v>
       </c>
       <c r="F124" t="n">
         <v>0.0</v>
@@ -4650,7 +4650,7 @@
         <v>118.215</v>
       </c>
       <c r="H124" t="n">
-        <v>4328.954</v>
+        <v>4244.039000000001</v>
       </c>
       <c r="I124" t="n">
         <v>0.0</v>
@@ -4752,7 +4752,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>482.62</v>
+        <v>356.08</v>
       </c>
       <c r="F127" t="n">
         <v>0.0</v>
@@ -4761,7 +4761,7 @@
         <v>106.005</v>
       </c>
       <c r="H127" t="n">
-        <v>482.62</v>
+        <v>356.08</v>
       </c>
       <c r="I127" t="n">
         <v>0.0</v>
@@ -4789,7 +4789,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>258.08</v>
+        <v>227.79999999999998</v>
       </c>
       <c r="F128" t="n">
         <v>0.0</v>
@@ -4798,7 +4798,7 @@
         <v>75.39999999999999</v>
       </c>
       <c r="H128" t="n">
-        <v>258.08</v>
+        <v>227.79999999999998</v>
       </c>
       <c r="I128" t="n">
         <v>0.0</v>
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1892.624</v>
+        <v>1825.904</v>
       </c>
       <c r="F130" t="n">
         <v>0.0</v>
@@ -4872,7 +4872,7 @@
         <v>63.38399999999999</v>
       </c>
       <c r="H130" t="n">
-        <v>1892.624</v>
+        <v>1825.904</v>
       </c>
       <c r="I130" t="n">
         <v>0.0</v>
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1203.6284</v>
+        <v>448.358</v>
       </c>
       <c r="F131" t="n">
         <v>0.0</v>
@@ -4912,7 +4912,7 @@
         <v>448.358</v>
       </c>
       <c r="I131" t="n">
-        <v>755.2704</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="132">
@@ -7231,7 +7231,7 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>173.472</v>
+        <v>170.803</v>
       </c>
       <c r="F194" t="n">
         <v>0.0</v>
@@ -7240,7 +7240,7 @@
         <v>98.746</v>
       </c>
       <c r="H194" t="n">
-        <v>173.472</v>
+        <v>170.803</v>
       </c>
       <c r="I194" t="n">
         <v>0.0</v>
@@ -7453,7 +7453,7 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>102.437</v>
+        <v>98.312</v>
       </c>
       <c r="F200" t="n">
         <v>0.0</v>
@@ -7462,7 +7462,7 @@
         <v>79.125</v>
       </c>
       <c r="H200" t="n">
-        <v>102.437</v>
+        <v>98.312</v>
       </c>
       <c r="I200" t="n">
         <v>0.0</v>
@@ -7490,7 +7490,7 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>400.5</v>
+        <v>396.75</v>
       </c>
       <c r="F201" t="n">
         <v>0.0</v>
@@ -7499,7 +7499,7 @@
         <v>9.0</v>
       </c>
       <c r="H201" t="n">
-        <v>400.5</v>
+        <v>396.75</v>
       </c>
       <c r="I201" t="n">
         <v>0.0</v>
@@ -7601,7 +7601,7 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1184.1589999999999</v>
+        <v>1182.784</v>
       </c>
       <c r="F204" t="n">
         <v>0.0</v>
@@ -7610,7 +7610,7 @@
         <v>0.0</v>
       </c>
       <c r="H204" t="n">
-        <v>1184.1589999999999</v>
+        <v>1182.784</v>
       </c>
       <c r="I204" t="n">
         <v>0.0</v>
@@ -7638,7 +7638,7 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>855.816</v>
+        <v>855.128</v>
       </c>
       <c r="F205" t="n">
         <v>0.0</v>
@@ -7647,7 +7647,7 @@
         <v>0.859</v>
       </c>
       <c r="H205" t="n">
-        <v>855.816</v>
+        <v>855.128</v>
       </c>
       <c r="I205" t="n">
         <v>0.0</v>
@@ -7712,7 +7712,7 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>652.3810000000001</v>
+        <v>635.028</v>
       </c>
       <c r="F207" t="n">
         <v>0.515</v>
@@ -7721,7 +7721,7 @@
         <v>0.34400000000000003</v>
       </c>
       <c r="H207" t="n">
-        <v>652.3810000000001</v>
+        <v>635.028</v>
       </c>
       <c r="I207" t="n">
         <v>0.0</v>
@@ -7749,7 +7749,7 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>818.574</v>
+        <v>817.2</v>
       </c>
       <c r="F208" t="n">
         <v>0.0</v>
@@ -7758,7 +7758,7 @@
         <v>0.0</v>
       </c>
       <c r="H208" t="n">
-        <v>818.574</v>
+        <v>817.2</v>
       </c>
       <c r="I208" t="n">
         <v>0.0</v>
@@ -7786,7 +7786,7 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>538.155</v>
+        <v>523.037</v>
       </c>
       <c r="F209" t="n">
         <v>0.0</v>
@@ -7795,7 +7795,7 @@
         <v>22.681</v>
       </c>
       <c r="H209" t="n">
-        <v>538.155</v>
+        <v>523.037</v>
       </c>
       <c r="I209" t="n">
         <v>0.0</v>
@@ -7823,7 +7823,7 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>441.475</v>
+        <v>438.038</v>
       </c>
       <c r="F210" t="n">
         <v>0.0</v>
@@ -7832,7 +7832,7 @@
         <v>48.111000000000004</v>
       </c>
       <c r="H210" t="n">
-        <v>441.475</v>
+        <v>438.038</v>
       </c>
       <c r="I210" t="n">
         <v>0.0</v>
@@ -7897,7 +7897,7 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>848.12</v>
+        <v>843.309</v>
       </c>
       <c r="F212" t="n">
         <v>0.0</v>
@@ -7906,7 +7906,7 @@
         <v>1.374</v>
       </c>
       <c r="H212" t="n">
-        <v>848.12</v>
+        <v>843.309</v>
       </c>
       <c r="I212" t="n">
         <v>0.0</v>
@@ -7934,7 +7934,7 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>109.895</v>
+        <v>100.789</v>
       </c>
       <c r="F213" t="n">
         <v>0.34400000000000003</v>
@@ -7943,7 +7943,7 @@
         <v>43.981</v>
       </c>
       <c r="H213" t="n">
-        <v>109.895</v>
+        <v>100.789</v>
       </c>
       <c r="I213" t="n">
         <v>0.0</v>
@@ -7971,7 +7971,7 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>84.538</v>
+        <v>82.476</v>
       </c>
       <c r="F214" t="n">
         <v>0.0</v>
@@ -7980,7 +7980,7 @@
         <v>11.684</v>
       </c>
       <c r="H214" t="n">
-        <v>84.538</v>
+        <v>82.476</v>
       </c>
       <c r="I214" t="n">
         <v>0.0</v>
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>1688.906</v>
+        <v>1672.127</v>
       </c>
       <c r="F215" t="n">
         <v>1.031</v>
@@ -8017,7 +8017,7 @@
         <v>0.34400000000000003</v>
       </c>
       <c r="H215" t="n">
-        <v>1688.906</v>
+        <v>1672.127</v>
       </c>
       <c r="I215" t="n">
         <v>0.0</v>
@@ -8045,7 +8045,7 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>176.636</v>
+        <v>174.574</v>
       </c>
       <c r="F216" t="n">
         <v>0.0</v>
@@ -8054,7 +8054,7 @@
         <v>1019.9530000000001</v>
       </c>
       <c r="H216" t="n">
-        <v>176.636</v>
+        <v>174.574</v>
       </c>
       <c r="I216" t="n">
         <v>0.0</v>
@@ -8082,7 +8082,7 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>774.704</v>
+        <v>770.0649999999999</v>
       </c>
       <c r="F217" t="n">
         <v>0.34400000000000003</v>
@@ -8091,7 +8091,7 @@
         <v>7.216</v>
       </c>
       <c r="H217" t="n">
-        <v>774.704</v>
+        <v>770.0649999999999</v>
       </c>
       <c r="I217" t="n">
         <v>0.0</v>
@@ -8156,7 +8156,7 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>285.559</v>
+        <v>281.435</v>
       </c>
       <c r="F219" t="n">
         <v>0.0</v>
@@ -8165,7 +8165,7 @@
         <v>0.0</v>
       </c>
       <c r="H219" t="n">
-        <v>285.559</v>
+        <v>281.435</v>
       </c>
       <c r="I219" t="n">
         <v>0.0</v>
@@ -8230,7 +8230,7 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>281.436</v>
+        <v>272.157</v>
       </c>
       <c r="F221" t="n">
         <v>0.0</v>
@@ -8239,7 +8239,7 @@
         <v>0.0</v>
       </c>
       <c r="H221" t="n">
-        <v>281.436</v>
+        <v>272.157</v>
       </c>
       <c r="I221" t="n">
         <v>0.0</v>
@@ -8267,7 +8267,7 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>96.90899999999999</v>
+        <v>94.847</v>
       </c>
       <c r="F222" t="n">
         <v>0.0</v>
@@ -8276,7 +8276,7 @@
         <v>685.238</v>
       </c>
       <c r="H222" t="n">
-        <v>96.90899999999999</v>
+        <v>94.847</v>
       </c>
       <c r="I222" t="n">
         <v>0.0</v>
@@ -8304,7 +8304,7 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>1053.76</v>
+        <v>1023.3539999999999</v>
       </c>
       <c r="F223" t="n">
         <v>0.0</v>
@@ -8313,7 +8313,7 @@
         <v>3.436</v>
       </c>
       <c r="H223" t="n">
-        <v>1053.76</v>
+        <v>1023.3539999999999</v>
       </c>
       <c r="I223" t="n">
         <v>0.0</v>
@@ -8859,7 +8859,7 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>66.72</v>
+        <v>66.053</v>
       </c>
       <c r="F238" t="n">
         <v>0.0</v>
@@ -8868,7 +8868,7 @@
         <v>1.056</v>
       </c>
       <c r="H238" t="n">
-        <v>66.72</v>
+        <v>66.053</v>
       </c>
       <c r="I238" t="n">
         <v>0.0</v>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>74.059</v>
+        <v>71.391</v>
       </c>
       <c r="F240" t="n">
         <v>0.0</v>
@@ -8942,7 +8942,7 @@
         <v>0.0</v>
       </c>
       <c r="H240" t="n">
-        <v>74.059</v>
+        <v>71.391</v>
       </c>
       <c r="I240" t="n">
         <v>0.0</v>
@@ -8970,7 +8970,7 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>74.059</v>
+        <v>88.07</v>
       </c>
       <c r="F241" t="n">
         <v>0.0</v>
@@ -8979,7 +8979,7 @@
         <v>5.338</v>
       </c>
       <c r="H241" t="n">
-        <v>74.059</v>
+        <v>88.07</v>
       </c>
       <c r="I241" t="n">
         <v>0.0</v>
@@ -9673,7 +9673,7 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>768.4</v>
+        <v>759.5999999999999</v>
       </c>
       <c r="F260" t="n">
         <v>5.4</v>
@@ -9682,7 +9682,7 @@
         <v>8.0</v>
       </c>
       <c r="H260" t="n">
-        <v>768.4</v>
+        <v>759.5999999999999</v>
       </c>
       <c r="I260" t="n">
         <v>0.0</v>
@@ -9747,7 +9747,7 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>311.32800000000003</v>
+        <v>308.41400000000004</v>
       </c>
       <c r="F262" t="n">
         <v>0.0</v>
@@ -9756,7 +9756,7 @@
         <v>604.1959999999999</v>
       </c>
       <c r="H262" t="n">
-        <v>311.32800000000003</v>
+        <v>308.41400000000004</v>
       </c>
       <c r="I262" t="n">
         <v>0.0</v>
@@ -9784,7 +9784,7 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>373.79999999999995</v>
+        <v>373.0</v>
       </c>
       <c r="F263" t="n">
         <v>0.6</v>
@@ -9793,7 +9793,7 @@
         <v>8.0</v>
       </c>
       <c r="H263" t="n">
-        <v>373.79999999999995</v>
+        <v>373.0</v>
       </c>
       <c r="I263" t="n">
         <v>0.0</v>
@@ -9821,7 +9821,7 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>6341.326</v>
+        <v>6124.845</v>
       </c>
       <c r="F264" t="n">
         <v>1.59</v>
@@ -9830,7 +9830,7 @@
         <v>62.620999999999995</v>
       </c>
       <c r="H264" t="n">
-        <v>6341.326</v>
+        <v>6124.845</v>
       </c>
       <c r="I264" t="n">
         <v>0.0</v>
@@ -9858,7 +9858,7 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>3480.047</v>
+        <v>3475.745</v>
       </c>
       <c r="F265" t="n">
         <v>3.979</v>
@@ -9867,7 +9867,7 @@
         <v>124.306</v>
       </c>
       <c r="H265" t="n">
-        <v>3480.047</v>
+        <v>3475.745</v>
       </c>
       <c r="I265" t="n">
         <v>0.0</v>
@@ -9895,7 +9895,7 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>3327.261</v>
+        <v>3313.978</v>
       </c>
       <c r="F266" t="n">
         <v>3.367</v>
@@ -9904,7 +9904,7 @@
         <v>145.07</v>
       </c>
       <c r="H266" t="n">
-        <v>3327.261</v>
+        <v>3313.978</v>
       </c>
       <c r="I266" t="n">
         <v>0.0</v>
@@ -10302,7 +10302,7 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>325.882</v>
+        <v>325.362</v>
       </c>
       <c r="F277" t="n">
         <v>0.04</v>
@@ -10311,7 +10311,7 @@
         <v>3.8400000000000003</v>
       </c>
       <c r="H277" t="n">
-        <v>325.882</v>
+        <v>325.362</v>
       </c>
       <c r="I277" t="n">
         <v>0.0</v>
@@ -10339,7 +10339,7 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>409.921</v>
+        <v>408.001</v>
       </c>
       <c r="F278" t="n">
         <v>0.0</v>
@@ -10348,7 +10348,7 @@
         <v>0.0</v>
       </c>
       <c r="H278" t="n">
-        <v>409.921</v>
+        <v>408.001</v>
       </c>
       <c r="I278" t="n">
         <v>0.0</v>
@@ -10376,7 +10376,7 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>585.3190000000001</v>
+        <v>585.239</v>
       </c>
       <c r="F279" t="n">
         <v>0.08</v>
@@ -10385,7 +10385,7 @@
         <v>0.0</v>
       </c>
       <c r="H279" t="n">
-        <v>585.3190000000001</v>
+        <v>585.239</v>
       </c>
       <c r="I279" t="n">
         <v>0.0</v>
@@ -10413,7 +10413,7 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>330.24</v>
+        <v>329.28</v>
       </c>
       <c r="F280" t="n">
         <v>0.0</v>
@@ -10422,7 +10422,7 @@
         <v>0.44</v>
       </c>
       <c r="H280" t="n">
-        <v>330.24</v>
+        <v>329.28</v>
       </c>
       <c r="I280" t="n">
         <v>0.0</v>
@@ -10524,7 +10524,7 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>3108.583</v>
+        <v>3008.575</v>
       </c>
       <c r="F283" t="n">
         <v>0.0</v>
@@ -10533,7 +10533,7 @@
         <v>18.752000000000002</v>
       </c>
       <c r="H283" t="n">
-        <v>3108.583</v>
+        <v>3008.575</v>
       </c>
       <c r="I283" t="n">
         <v>0.0</v>
@@ -10561,7 +10561,7 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>2463.6</v>
+        <v>2362.8</v>
       </c>
       <c r="F284" t="n">
         <v>0.0</v>
@@ -10570,7 +10570,7 @@
         <v>194.39999999999998</v>
       </c>
       <c r="H284" t="n">
-        <v>2463.6</v>
+        <v>2362.8</v>
       </c>
       <c r="I284" t="n">
         <v>0.0</v>
@@ -10598,7 +10598,7 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>4474.8</v>
+        <v>4387.400000000001</v>
       </c>
       <c r="F285" t="n">
         <v>0.2</v>
@@ -10607,7 +10607,7 @@
         <v>84.0</v>
       </c>
       <c r="H285" t="n">
-        <v>4474.8</v>
+        <v>4387.400000000001</v>
       </c>
       <c r="I285" t="n">
         <v>0.0</v>
@@ -10635,7 +10635,7 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>1562.51</v>
+        <v>1312.758</v>
       </c>
       <c r="F286" t="n">
         <v>2.222</v>
@@ -10644,7 +10644,7 @@
         <v>18.665000000000003</v>
       </c>
       <c r="H286" t="n">
-        <v>1562.51</v>
+        <v>1312.758</v>
       </c>
       <c r="I286" t="n">
         <v>0.0</v>
@@ -10672,7 +10672,7 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>4920.84</v>
+        <v>4920.618</v>
       </c>
       <c r="F287" t="n">
         <v>0.444</v>
@@ -10681,7 +10681,7 @@
         <v>383.96200000000005</v>
       </c>
       <c r="H287" t="n">
-        <v>4920.84</v>
+        <v>4920.618</v>
       </c>
       <c r="I287" t="n">
         <v>0.0</v>
@@ -10746,7 +10746,7 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>3294.338</v>
+        <v>3283.672</v>
       </c>
       <c r="F289" t="n">
         <v>0.0</v>
@@ -10755,7 +10755,7 @@
         <v>351.965</v>
       </c>
       <c r="H289" t="n">
-        <v>3294.338</v>
+        <v>3283.672</v>
       </c>
       <c r="I289" t="n">
         <v>0.0</v>
@@ -11116,7 +11116,7 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>1619.0</v>
+        <v>1541.0</v>
       </c>
       <c r="F299" t="n">
         <v>0.8</v>
@@ -11125,7 +11125,7 @@
         <v>134.4</v>
       </c>
       <c r="H299" t="n">
-        <v>1619.0</v>
+        <v>1541.0</v>
       </c>
       <c r="I299" t="n">
         <v>0.0</v>
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>4793.2</v>
+        <v>4748.4</v>
       </c>
       <c r="F300" t="n">
         <v>2.4</v>
@@ -11162,7 +11162,7 @@
         <v>333.0</v>
       </c>
       <c r="H300" t="n">
-        <v>4793.2</v>
+        <v>4748.4</v>
       </c>
       <c r="I300" t="n">
         <v>0.0</v>
@@ -11190,7 +11190,7 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>194.2</v>
+        <v>141.2</v>
       </c>
       <c r="F301" t="n">
         <v>1.0</v>
@@ -11199,7 +11199,7 @@
         <v>136.8</v>
       </c>
       <c r="H301" t="n">
-        <v>194.2</v>
+        <v>141.2</v>
       </c>
       <c r="I301" t="n">
         <v>0.0</v>
@@ -11227,7 +11227,7 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>703.8</v>
+        <v>703.6</v>
       </c>
       <c r="F302" t="n">
         <v>0.2</v>
@@ -11236,7 +11236,7 @@
         <v>0.0</v>
       </c>
       <c r="H302" t="n">
-        <v>703.8</v>
+        <v>703.6</v>
       </c>
       <c r="I302" t="n">
         <v>0.0</v>
@@ -11264,7 +11264,7 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>215.454</v>
+        <v>214.92100000000002</v>
       </c>
       <c r="F303" t="n">
         <v>0.533</v>
@@ -11273,7 +11273,7 @@
         <v>0.0</v>
       </c>
       <c r="H303" t="n">
-        <v>215.454</v>
+        <v>214.92100000000002</v>
       </c>
       <c r="I303" t="n">
         <v>0.0</v>
@@ -11301,7 +11301,7 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>963.759</v>
+        <v>937.099</v>
       </c>
       <c r="F304" t="n">
         <v>0.0</v>
@@ -11310,7 +11310,7 @@
         <v>0.0</v>
       </c>
       <c r="H304" t="n">
-        <v>963.759</v>
+        <v>937.099</v>
       </c>
       <c r="I304" t="n">
         <v>0.0</v>
@@ -11375,7 +11375,7 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>5636.981</v>
+        <v>5636.448</v>
       </c>
       <c r="F306" t="n">
         <v>1.067</v>
@@ -11384,7 +11384,7 @@
         <v>0.0</v>
       </c>
       <c r="H306" t="n">
-        <v>5636.981</v>
+        <v>5636.448</v>
       </c>
       <c r="I306" t="n">
         <v>0.0</v>
@@ -11856,7 +11856,7 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>2792.359</v>
+        <v>2791.292</v>
       </c>
       <c r="F319" t="n">
         <v>0.0</v>
@@ -11865,7 +11865,7 @@
         <v>0.0</v>
       </c>
       <c r="H319" t="n">
-        <v>2792.359</v>
+        <v>2791.292</v>
       </c>
       <c r="I319" t="n">
         <v>0.0</v>
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>12541.833999999999</v>
+        <v>12541.3</v>
       </c>
       <c r="F320" t="n">
         <v>0.533</v>
@@ -11902,7 +11902,7 @@
         <v>0.0</v>
       </c>
       <c r="H320" t="n">
-        <v>12541.833999999999</v>
+        <v>12541.3</v>
       </c>
       <c r="I320" t="n">
         <v>0.0</v>
@@ -11967,7 +11967,7 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>1491.6000000000001</v>
+        <v>1417.8</v>
       </c>
       <c r="F322" t="n">
         <v>0.6</v>
@@ -11976,7 +11976,7 @@
         <v>6.4</v>
       </c>
       <c r="H322" t="n">
-        <v>1491.6000000000001</v>
+        <v>1417.8</v>
       </c>
       <c r="I322" t="n">
         <v>0.0</v>
@@ -12004,7 +12004,7 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>25.598</v>
+        <v>25.064999999999998</v>
       </c>
       <c r="F323" t="n">
         <v>0.0</v>
@@ -12013,7 +12013,7 @@
         <v>0.0</v>
       </c>
       <c r="H323" t="n">
-        <v>25.598</v>
+        <v>25.064999999999998</v>
       </c>
       <c r="I323" t="n">
         <v>0.0</v>
@@ -12078,7 +12078,7 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>2257.2000000000003</v>
+        <v>2195.7999999999997</v>
       </c>
       <c r="F325" t="n">
         <v>1.4</v>
@@ -12087,7 +12087,7 @@
         <v>45.6</v>
       </c>
       <c r="H325" t="n">
-        <v>2257.2000000000003</v>
+        <v>2195.7999999999997</v>
       </c>
       <c r="I325" t="n">
         <v>0.0</v>
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>3400.32</v>
+        <v>3269.1600000000003</v>
       </c>
       <c r="F334" t="n">
         <v>0.0</v>
@@ -12420,7 +12420,7 @@
         <v>77.75999999999999</v>
       </c>
       <c r="H334" t="n">
-        <v>3400.32</v>
+        <v>3269.1600000000003</v>
       </c>
       <c r="I334" t="n">
         <v>0.0</v>
@@ -12448,7 +12448,7 @@
         </is>
       </c>
       <c r="E335" t="n">
-        <v>3455.327</v>
+        <v>3401.552</v>
       </c>
       <c r="F335" t="n">
         <v>0.45</v>
@@ -12457,7 +12457,7 @@
         <v>39.375</v>
       </c>
       <c r="H335" t="n">
-        <v>3455.327</v>
+        <v>3401.552</v>
       </c>
       <c r="I335" t="n">
         <v>0.0</v>
@@ -12485,7 +12485,7 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>3008.4240000000004</v>
+        <v>2918.745</v>
       </c>
       <c r="F336" t="n">
         <v>0.0</v>
@@ -12494,7 +12494,7 @@
         <v>88.245</v>
       </c>
       <c r="H336" t="n">
-        <v>3008.4240000000004</v>
+        <v>2918.745</v>
       </c>
       <c r="I336" t="n">
         <v>0.0</v>
@@ -12818,7 +12818,7 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>569.5</v>
+        <v>567.1</v>
       </c>
       <c r="F345" t="n">
         <v>0.0</v>
@@ -12827,7 +12827,7 @@
         <v>0.0</v>
       </c>
       <c r="H345" t="n">
-        <v>569.5</v>
+        <v>567.1</v>
       </c>
       <c r="I345" t="n">
         <v>0.0</v>
@@ -12892,7 +12892,7 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>921.4</v>
+        <v>917.8</v>
       </c>
       <c r="F347" t="n">
         <v>0.0</v>
@@ -12901,7 +12901,7 @@
         <v>3.0</v>
       </c>
       <c r="H347" t="n">
-        <v>921.4</v>
+        <v>917.8</v>
       </c>
       <c r="I347" t="n">
         <v>0.0</v>
@@ -13003,7 +13003,7 @@
         </is>
       </c>
       <c r="E350" t="n">
-        <v>472.0</v>
+        <v>408.0</v>
       </c>
       <c r="F350" t="n">
         <v>0.0</v>
@@ -13012,7 +13012,7 @@
         <v>579.0</v>
       </c>
       <c r="H350" t="n">
-        <v>472.0</v>
+        <v>408.0</v>
       </c>
       <c r="I350" t="n">
         <v>0.0</v>
@@ -13040,7 +13040,7 @@
         </is>
       </c>
       <c r="E351" t="n">
-        <v>1652.0</v>
+        <v>1631.0</v>
       </c>
       <c r="F351" t="n">
         <v>0.0</v>
@@ -13049,7 +13049,7 @@
         <v>577.5</v>
       </c>
       <c r="H351" t="n">
-        <v>1652.0</v>
+        <v>1631.0</v>
       </c>
       <c r="I351" t="n">
         <v>0.0</v>
@@ -13077,7 +13077,7 @@
         </is>
       </c>
       <c r="E352" t="n">
-        <v>252.0</v>
+        <v>189.0</v>
       </c>
       <c r="F352" t="n">
         <v>0.0</v>
@@ -13086,7 +13086,7 @@
         <v>570.5</v>
       </c>
       <c r="H352" t="n">
-        <v>252.0</v>
+        <v>189.0</v>
       </c>
       <c r="I352" t="n">
         <v>0.0</v>
@@ -13410,7 +13410,7 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>416.852</v>
+        <v>413.651</v>
       </c>
       <c r="F361" t="n">
         <v>19.202</v>
@@ -13419,7 +13419,7 @@
         <v>0.0</v>
       </c>
       <c r="H361" t="n">
-        <v>416.852</v>
+        <v>413.651</v>
       </c>
       <c r="I361" t="n">
         <v>0.0</v>
@@ -13521,7 +13521,7 @@
         </is>
       </c>
       <c r="E364" t="n">
-        <v>1471.843</v>
+        <v>1462.502</v>
       </c>
       <c r="F364" t="n">
         <v>0.0</v>
@@ -13530,7 +13530,7 @@
         <v>0.0</v>
       </c>
       <c r="H364" t="n">
-        <v>1471.843</v>
+        <v>1462.502</v>
       </c>
       <c r="I364" t="n">
         <v>0.0</v>
@@ -13558,7 +13558,7 @@
         </is>
       </c>
       <c r="E365" t="n">
-        <v>23802.635</v>
+        <v>23767.942</v>
       </c>
       <c r="F365" t="n">
         <v>0.111</v>
@@ -13567,7 +13567,7 @@
         <v>37.03</v>
       </c>
       <c r="H365" t="n">
-        <v>23802.635</v>
+        <v>23767.942</v>
       </c>
       <c r="I365" t="n">
         <v>0.0</v>
@@ -13669,7 +13669,7 @@
         </is>
       </c>
       <c r="E368" t="n">
-        <v>325.594</v>
+        <v>306.912</v>
       </c>
       <c r="F368" t="n">
         <v>0.0</v>
@@ -13678,7 +13678,7 @@
         <v>16.458000000000002</v>
       </c>
       <c r="H368" t="n">
-        <v>325.594</v>
+        <v>306.912</v>
       </c>
       <c r="I368" t="n">
         <v>0.0</v>
@@ -14039,7 +14039,7 @@
         </is>
       </c>
       <c r="E378" t="n">
-        <v>7489.848</v>
+        <v>8296.383</v>
       </c>
       <c r="F378" t="n">
         <v>0.0</v>
@@ -14048,7 +14048,7 @@
         <v>0.0</v>
       </c>
       <c r="H378" t="n">
-        <v>7489.848</v>
+        <v>8296.383</v>
       </c>
       <c r="I378" t="n">
         <v>0.0</v>
@@ -14224,7 +14224,7 @@
         </is>
       </c>
       <c r="E383" t="n">
-        <v>1721.832</v>
+        <v>1656.12</v>
       </c>
       <c r="F383" t="n">
         <v>0.0</v>
@@ -14233,7 +14233,7 @@
         <v>37.296</v>
       </c>
       <c r="H383" t="n">
-        <v>1721.832</v>
+        <v>1656.12</v>
       </c>
       <c r="I383" t="n">
         <v>0.0</v>
@@ -14409,7 +14409,7 @@
         </is>
       </c>
       <c r="E388" t="n">
-        <v>363.466</v>
+        <v>358.666</v>
       </c>
       <c r="F388" t="n">
         <v>40.0</v>
@@ -14418,7 +14418,7 @@
         <v>30.4</v>
       </c>
       <c r="H388" t="n">
-        <v>363.466</v>
+        <v>358.666</v>
       </c>
       <c r="I388" t="n">
         <v>0.0</v>
@@ -15223,7 +15223,7 @@
         </is>
       </c>
       <c r="E410" t="n">
-        <v>3203.5989999999997</v>
+        <v>3181.249</v>
       </c>
       <c r="F410" t="n">
         <v>0.2</v>
@@ -15232,7 +15232,7 @@
         <v>74.39999999999999</v>
       </c>
       <c r="H410" t="n">
-        <v>3203.5989999999997</v>
+        <v>3181.249</v>
       </c>
       <c r="I410" t="n">
         <v>0.0</v>
@@ -15260,7 +15260,7 @@
         </is>
       </c>
       <c r="E411" t="n">
-        <v>2580.5</v>
+        <v>2567.3</v>
       </c>
       <c r="F411" t="n">
         <v>0.0</v>
@@ -15269,7 +15269,7 @@
         <v>180.10000000000002</v>
       </c>
       <c r="H411" t="n">
-        <v>2580.5</v>
+        <v>2567.3</v>
       </c>
       <c r="I411" t="n">
         <v>0.0</v>
@@ -15297,7 +15297,7 @@
         </is>
       </c>
       <c r="E412" t="n">
-        <v>1117.85</v>
+        <v>1097.65</v>
       </c>
       <c r="F412" t="n">
         <v>0.15</v>
@@ -15306,7 +15306,7 @@
         <v>101.1</v>
       </c>
       <c r="H412" t="n">
-        <v>1117.85</v>
+        <v>1097.65</v>
       </c>
       <c r="I412" t="n">
         <v>0.0</v>
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="E413" t="n">
-        <v>1779.55</v>
+        <v>1756.35</v>
       </c>
       <c r="F413" t="n">
         <v>0.0</v>
@@ -15343,7 +15343,7 @@
         <v>163.5</v>
       </c>
       <c r="H413" t="n">
-        <v>1779.55</v>
+        <v>1756.35</v>
       </c>
       <c r="I413" t="n">
         <v>0.0</v>
@@ -15371,7 +15371,7 @@
         </is>
       </c>
       <c r="E414" t="n">
-        <v>2825.7999999999997</v>
+        <v>2782.2999999999997</v>
       </c>
       <c r="F414" t="n">
         <v>0.15</v>
@@ -15380,7 +15380,7 @@
         <v>31.2</v>
       </c>
       <c r="H414" t="n">
-        <v>2825.7999999999997</v>
+        <v>2782.2999999999997</v>
       </c>
       <c r="I414" t="n">
         <v>0.0</v>
@@ -15408,7 +15408,7 @@
         </is>
       </c>
       <c r="E415" t="n">
-        <v>3235.1</v>
+        <v>3050.9</v>
       </c>
       <c r="F415" t="n">
         <v>0.1</v>
@@ -15417,7 +15417,7 @@
         <v>0.0</v>
       </c>
       <c r="H415" t="n">
-        <v>3235.1</v>
+        <v>3050.9</v>
       </c>
       <c r="I415" t="n">
         <v>0.0</v>
@@ -15445,7 +15445,7 @@
         </is>
       </c>
       <c r="E416" t="n">
-        <v>10570.101</v>
+        <v>10509.101</v>
       </c>
       <c r="F416" t="n">
         <v>0.3</v>
@@ -15454,7 +15454,7 @@
         <v>0.0</v>
       </c>
       <c r="H416" t="n">
-        <v>10570.101</v>
+        <v>10509.101</v>
       </c>
       <c r="I416" t="n">
         <v>0.0</v>
@@ -15815,7 +15815,7 @@
         </is>
       </c>
       <c r="E426" t="n">
-        <v>356.4</v>
+        <v>342.0</v>
       </c>
       <c r="F426" t="n">
         <v>0.0</v>
@@ -15824,7 +15824,7 @@
         <v>0.0</v>
       </c>
       <c r="H426" t="n">
-        <v>356.4</v>
+        <v>342.0</v>
       </c>
       <c r="I426" t="n">
         <v>0.0</v>
@@ -16148,7 +16148,7 @@
         </is>
       </c>
       <c r="E435" t="n">
-        <v>1167.102</v>
+        <v>1108.229</v>
       </c>
       <c r="F435" t="n">
         <v>61.196</v>
@@ -16157,7 +16157,7 @@
         <v>4.107</v>
       </c>
       <c r="H435" t="n">
-        <v>1167.102</v>
+        <v>1108.229</v>
       </c>
       <c r="I435" t="n">
         <v>0.0</v>
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="E436" t="n">
-        <v>1746.077</v>
+        <v>1465.319</v>
       </c>
       <c r="F436" t="n">
         <v>191.516</v>
@@ -16194,7 +16194,7 @@
         <v>2.054</v>
       </c>
       <c r="H436" t="n">
-        <v>1746.077</v>
+        <v>1465.319</v>
       </c>
       <c r="I436" t="n">
         <v>0.0</v>
@@ -16222,7 +16222,7 @@
         </is>
       </c>
       <c r="E437" t="n">
-        <v>174.117</v>
+        <v>173.65</v>
       </c>
       <c r="F437" t="n">
         <v>0.0</v>
@@ -16231,7 +16231,7 @@
         <v>511.55799999999994</v>
       </c>
       <c r="H437" t="n">
-        <v>174.117</v>
+        <v>173.65</v>
       </c>
       <c r="I437" t="n">
         <v>0.0</v>
@@ -16259,7 +16259,7 @@
         </is>
       </c>
       <c r="E438" t="n">
-        <v>2167.085</v>
+        <v>2164.8610000000003</v>
       </c>
       <c r="F438" t="n">
         <v>0.0</v>
@@ -16268,7 +16268,7 @@
         <v>2.054</v>
       </c>
       <c r="H438" t="n">
-        <v>2167.085</v>
+        <v>2164.8610000000003</v>
       </c>
       <c r="I438" t="n">
         <v>0.0</v>
@@ -16296,7 +16296,7 @@
         </is>
       </c>
       <c r="E439" t="n">
-        <v>805.605</v>
+        <v>784.1329999999999</v>
       </c>
       <c r="F439" t="n">
         <v>0.0</v>
@@ -16305,7 +16305,7 @@
         <v>395.806</v>
       </c>
       <c r="H439" t="n">
-        <v>805.605</v>
+        <v>784.1329999999999</v>
       </c>
       <c r="I439" t="n">
         <v>0.0</v>
@@ -16407,7 +16407,7 @@
         </is>
       </c>
       <c r="E442" t="n">
-        <v>2492.4359999999997</v>
+        <v>2489.635</v>
       </c>
       <c r="F442" t="n">
         <v>0.0</v>
@@ -16416,7 +16416,7 @@
         <v>191.83700000000002</v>
       </c>
       <c r="H442" t="n">
-        <v>2492.4359999999997</v>
+        <v>2489.635</v>
       </c>
       <c r="I442" t="n">
         <v>0.0</v>
@@ -16444,7 +16444,7 @@
         </is>
       </c>
       <c r="E443" t="n">
-        <v>10046.327000000001</v>
+        <v>9956.243</v>
       </c>
       <c r="F443" t="n">
         <v>6.069</v>
@@ -16453,7 +16453,7 @@
         <v>148.894</v>
       </c>
       <c r="H443" t="n">
-        <v>10046.327000000001</v>
+        <v>9956.243</v>
       </c>
       <c r="I443" t="n">
         <v>0.0</v>
@@ -16481,7 +16481,7 @@
         </is>
       </c>
       <c r="E444" t="n">
-        <v>17340.227000000003</v>
+        <v>17327.157000000003</v>
       </c>
       <c r="F444" t="n">
         <v>3.733</v>
@@ -16490,7 +16490,7 @@
         <v>50.879</v>
       </c>
       <c r="H444" t="n">
-        <v>17340.227000000003</v>
+        <v>17327.157000000003</v>
       </c>
       <c r="I444" t="n">
         <v>0.0</v>
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="E446" t="n">
-        <v>2184.958</v>
+        <v>2180.875</v>
       </c>
       <c r="F446" t="n">
         <v>294.922</v>
@@ -16564,7 +16564,7 @@
         <v>79.056</v>
       </c>
       <c r="H446" t="n">
-        <v>2184.958</v>
+        <v>2180.875</v>
       </c>
       <c r="I446" t="n">
         <v>0.0</v>
@@ -16666,7 +16666,7 @@
         </is>
       </c>
       <c r="E449" t="n">
-        <v>1095.6850000000002</v>
+        <v>1091.601</v>
       </c>
       <c r="F449" t="n">
         <v>0.0</v>
@@ -16675,7 +16675,7 @@
         <v>73.80499999999999</v>
       </c>
       <c r="H449" t="n">
-        <v>1095.6850000000002</v>
+        <v>1091.601</v>
       </c>
       <c r="I449" t="n">
         <v>0.0</v>
@@ -16703,7 +16703,7 @@
         </is>
       </c>
       <c r="E450" t="n">
-        <v>7851.549</v>
+        <v>7808.9580000000005</v>
       </c>
       <c r="F450" t="n">
         <v>380.69399999999996</v>
@@ -16712,7 +16712,7 @@
         <v>0.292</v>
       </c>
       <c r="H450" t="n">
-        <v>7851.549</v>
+        <v>7808.9580000000005</v>
       </c>
       <c r="I450" t="n">
         <v>0.0</v>
@@ -16740,7 +16740,7 @@
         </is>
       </c>
       <c r="E451" t="n">
-        <v>1603.839</v>
+        <v>1463.816</v>
       </c>
       <c r="F451" t="n">
         <v>0.0</v>
@@ -16749,7 +16749,7 @@
         <v>19.253</v>
       </c>
       <c r="H451" t="n">
-        <v>1603.839</v>
+        <v>1463.816</v>
       </c>
       <c r="I451" t="n">
         <v>0.0</v>
@@ -16814,7 +16814,7 @@
         </is>
       </c>
       <c r="E453" t="n">
-        <v>3345.942</v>
+        <v>3345.65</v>
       </c>
       <c r="F453" t="n">
         <v>0.0</v>
@@ -16823,7 +16823,7 @@
         <v>0.0</v>
       </c>
       <c r="H453" t="n">
-        <v>3345.942</v>
+        <v>3345.65</v>
       </c>
       <c r="I453" t="n">
         <v>0.0</v>
@@ -17258,7 +17258,7 @@
         </is>
       </c>
       <c r="E465" t="n">
-        <v>722.075</v>
+        <v>720.809</v>
       </c>
       <c r="F465" t="n">
         <v>1.267</v>
@@ -17267,7 +17267,7 @@
         <v>0.0</v>
       </c>
       <c r="H465" t="n">
-        <v>722.075</v>
+        <v>720.809</v>
       </c>
       <c r="I465" t="n">
         <v>0.0</v>
@@ -17480,7 +17480,7 @@
         </is>
       </c>
       <c r="E471" t="n">
-        <v>1658.672</v>
+        <v>1190.708</v>
       </c>
       <c r="F471" t="n">
         <v>135.19</v>
@@ -17489,7 +17489,7 @@
         <v>561.557</v>
       </c>
       <c r="H471" t="n">
-        <v>1658.672</v>
+        <v>1190.708</v>
       </c>
       <c r="I471" t="n">
         <v>0.0</v>
@@ -17554,7 +17554,7 @@
         </is>
       </c>
       <c r="E473" t="n">
-        <v>4871.486</v>
+        <v>3989.398</v>
       </c>
       <c r="F473" t="n">
         <v>0.0</v>
@@ -17563,7 +17563,7 @@
         <v>642.064</v>
       </c>
       <c r="H473" t="n">
-        <v>4871.486</v>
+        <v>3989.398</v>
       </c>
       <c r="I473" t="n">
         <v>0.0</v>
@@ -17665,7 +17665,7 @@
         </is>
       </c>
       <c r="E476" t="n">
-        <v>717.977</v>
+        <v>709.4269999999999</v>
       </c>
       <c r="F476" t="n">
         <v>1.125</v>
@@ -17674,7 +17674,7 @@
         <v>85.725</v>
       </c>
       <c r="H476" t="n">
-        <v>717.977</v>
+        <v>709.4269999999999</v>
       </c>
       <c r="I476" t="n">
         <v>0.0</v>
@@ -17702,7 +17702,7 @@
         </is>
       </c>
       <c r="E477" t="n">
-        <v>1842.863</v>
+        <v>1792.0140000000001</v>
       </c>
       <c r="F477" t="n">
         <v>0.0</v>
@@ -17711,7 +17711,7 @@
         <v>105.30000000000001</v>
       </c>
       <c r="H477" t="n">
-        <v>1842.863</v>
+        <v>1792.0140000000001</v>
       </c>
       <c r="I477" t="n">
         <v>0.0</v>
@@ -17813,7 +17813,7 @@
         </is>
       </c>
       <c r="E480" t="n">
-        <v>145.13299999999998</v>
+        <v>140.832</v>
       </c>
       <c r="F480" t="n">
         <v>0.13899999999999998</v>
@@ -17822,7 +17822,7 @@
         <v>582.75</v>
       </c>
       <c r="H480" t="n">
-        <v>145.13299999999998</v>
+        <v>140.832</v>
       </c>
       <c r="I480" t="n">
         <v>0.0</v>
@@ -17850,7 +17850,7 @@
         </is>
       </c>
       <c r="E481" t="n">
-        <v>1742.84</v>
+        <v>1516.28</v>
       </c>
       <c r="F481" t="n">
         <v>0.12000000000000001</v>
@@ -17859,7 +17859,7 @@
         <v>178.07999999999998</v>
       </c>
       <c r="H481" t="n">
-        <v>1742.84</v>
+        <v>1516.28</v>
       </c>
       <c r="I481" t="n">
         <v>0.0</v>
@@ -17887,7 +17887,7 @@
         </is>
       </c>
       <c r="E482" t="n">
-        <v>84.921</v>
+        <v>83.28</v>
       </c>
       <c r="F482" t="n">
         <v>0.0</v>
@@ -17896,7 +17896,7 @@
         <v>708.0</v>
       </c>
       <c r="H482" t="n">
-        <v>84.921</v>
+        <v>83.28</v>
       </c>
       <c r="I482" t="n">
         <v>0.0</v>
@@ -17924,7 +17924,7 @@
         </is>
       </c>
       <c r="E483" t="n">
-        <v>1966.0410000000002</v>
+        <v>1783.076</v>
       </c>
       <c r="F483" t="n">
         <v>0.13899999999999998</v>
@@ -17933,7 +17933,7 @@
         <v>5.55</v>
       </c>
       <c r="H483" t="n">
-        <v>1966.0410000000002</v>
+        <v>1783.076</v>
       </c>
       <c r="I483" t="n">
         <v>0.0</v>
@@ -17961,7 +17961,7 @@
         </is>
       </c>
       <c r="E484" t="n">
-        <v>219.96</v>
+        <v>213.44</v>
       </c>
       <c r="F484" t="n">
         <v>0.0</v>
@@ -17970,7 +17970,7 @@
         <v>62.4</v>
       </c>
       <c r="H484" t="n">
-        <v>219.96</v>
+        <v>213.44</v>
       </c>
       <c r="I484" t="n">
         <v>0.0</v>
@@ -17998,7 +17998,7 @@
         </is>
       </c>
       <c r="E485" t="n">
-        <v>2941.314</v>
+        <v>2877.582</v>
       </c>
       <c r="F485" t="n">
         <v>0.231</v>
@@ -18007,7 +18007,7 @@
         <v>155.955</v>
       </c>
       <c r="H485" t="n">
-        <v>2941.314</v>
+        <v>2877.582</v>
       </c>
       <c r="I485" t="n">
         <v>0.0</v>
@@ -18035,7 +18035,7 @@
         </is>
       </c>
       <c r="E486" t="n">
-        <v>379.84</v>
+        <v>367.48</v>
       </c>
       <c r="F486" t="n">
         <v>0.0</v>
@@ -18044,7 +18044,7 @@
         <v>110.88000000000001</v>
       </c>
       <c r="H486" t="n">
-        <v>379.84</v>
+        <v>367.48</v>
       </c>
       <c r="I486" t="n">
         <v>0.0</v>
@@ -18072,7 +18072,7 @@
         </is>
       </c>
       <c r="E487" t="n">
-        <v>1220.77</v>
+        <v>1196.9969999999998</v>
       </c>
       <c r="F487" t="n">
         <v>0.231</v>
@@ -18081,7 +18081,7 @@
         <v>24.42</v>
       </c>
       <c r="H487" t="n">
-        <v>1220.77</v>
+        <v>1196.9969999999998</v>
       </c>
       <c r="I487" t="n">
         <v>0.0</v>
@@ -18331,7 +18331,7 @@
         </is>
       </c>
       <c r="E494" t="n">
-        <v>5508.639</v>
+        <v>5535.215</v>
       </c>
       <c r="F494" t="n">
         <v>26.576999999999998</v>
@@ -18340,7 +18340,7 @@
         <v>49.065999999999995</v>
       </c>
       <c r="H494" t="n">
-        <v>5508.639</v>
+        <v>5535.215</v>
       </c>
       <c r="I494" t="n">
         <v>0.0</v>
@@ -18368,7 +18368,7 @@
         </is>
       </c>
       <c r="E495" t="n">
-        <v>3830.2</v>
+        <v>3695.6</v>
       </c>
       <c r="F495" t="n">
         <v>26.8</v>
@@ -18377,7 +18377,7 @@
         <v>340.0</v>
       </c>
       <c r="H495" t="n">
-        <v>3830.2</v>
+        <v>3695.6</v>
       </c>
       <c r="I495" t="n">
         <v>0.0</v>
@@ -18997,7 +18997,7 @@
         </is>
       </c>
       <c r="E512" t="n">
-        <v>2292.888</v>
+        <v>2291.718</v>
       </c>
       <c r="F512" t="n">
         <v>0.0</v>
@@ -19006,7 +19006,7 @@
         <v>9.165</v>
       </c>
       <c r="H512" t="n">
-        <v>2292.888</v>
+        <v>2291.718</v>
       </c>
       <c r="I512" t="n">
         <v>0.0</v>
@@ -19071,7 +19071,7 @@
         </is>
       </c>
       <c r="E514" t="n">
-        <v>892.881</v>
+        <v>891.277</v>
       </c>
       <c r="F514" t="n">
         <v>0.0</v>
@@ -19080,7 +19080,7 @@
         <v>19.855999999999998</v>
       </c>
       <c r="H514" t="n">
-        <v>892.881</v>
+        <v>891.277</v>
       </c>
       <c r="I514" t="n">
         <v>0.0</v>
@@ -19626,7 +19626,7 @@
         </is>
       </c>
       <c r="E529" t="n">
-        <v>248.307</v>
+        <v>411.667</v>
       </c>
       <c r="F529" t="n">
         <v>104.55</v>
@@ -19635,7 +19635,7 @@
         <v>0.0</v>
       </c>
       <c r="H529" t="n">
-        <v>248.307</v>
+        <v>411.667</v>
       </c>
       <c r="I529" t="n">
         <v>0.0</v>
@@ -19959,7 +19959,7 @@
         </is>
       </c>
       <c r="E538" t="n">
-        <v>1071.257</v>
+        <v>1064.6909999999998</v>
       </c>
       <c r="F538" t="n">
         <v>43.153</v>
@@ -19968,7 +19968,7 @@
         <v>0.313</v>
       </c>
       <c r="H538" t="n">
-        <v>1071.257</v>
+        <v>1064.6909999999998</v>
       </c>
       <c r="I538" t="n">
         <v>0.0</v>
@@ -20033,7 +20033,7 @@
         </is>
       </c>
       <c r="E540" t="n">
-        <v>2110.0150000000003</v>
+        <v>2004.882</v>
       </c>
       <c r="F540" t="n">
         <v>2663.3019999999997</v>
@@ -20042,7 +20042,7 @@
         <v>2297.6549999999997</v>
       </c>
       <c r="H540" t="n">
-        <v>2110.0150000000003</v>
+        <v>2004.882</v>
       </c>
       <c r="I540" t="n">
         <v>0.0</v>
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="E551" t="n">
-        <v>5437.099</v>
+        <v>5333.096</v>
       </c>
       <c r="F551" t="n">
         <v>30.912</v>
@@ -20449,7 +20449,7 @@
         <v>211.041</v>
       </c>
       <c r="H551" t="n">
-        <v>5437.099</v>
+        <v>5333.096</v>
       </c>
       <c r="I551" t="n">
         <v>0.0</v>
@@ -20477,7 +20477,7 @@
         </is>
       </c>
       <c r="E552" t="n">
-        <v>2801.359</v>
+        <v>2589.3779999999997</v>
       </c>
       <c r="F552" t="n">
         <v>14.059000000000001</v>
@@ -20486,7 +20486,7 @@
         <v>85.086</v>
       </c>
       <c r="H552" t="n">
-        <v>2801.359</v>
+        <v>2589.3779999999997</v>
       </c>
       <c r="I552" t="n">
         <v>0.0</v>
@@ -21513,7 +21513,7 @@
         </is>
       </c>
       <c r="E580" t="n">
-        <v>6093.844999999999</v>
+        <v>6062.920999999999</v>
       </c>
       <c r="F580" t="n">
         <v>0.0</v>
@@ -21522,7 +21522,7 @@
         <v>5.539</v>
       </c>
       <c r="H580" t="n">
-        <v>6093.844999999999</v>
+        <v>6062.920999999999</v>
       </c>
       <c r="I580" t="n">
         <v>0.0</v>
@@ -21661,7 +21661,7 @@
         </is>
       </c>
       <c r="E584" t="n">
-        <v>1621.2069999999999</v>
+        <v>1605.423</v>
       </c>
       <c r="F584" t="n">
         <v>0.0</v>
@@ -21670,7 +21670,7 @@
         <v>0.0</v>
       </c>
       <c r="H584" t="n">
-        <v>1621.2069999999999</v>
+        <v>1605.423</v>
       </c>
       <c r="I584" t="n">
         <v>0.0</v>
@@ -21698,7 +21698,7 @@
         </is>
       </c>
       <c r="E585" t="n">
-        <v>2028.05</v>
+        <v>2010.05</v>
       </c>
       <c r="F585" t="n">
         <v>0.0</v>
@@ -21707,7 +21707,7 @@
         <v>9.231</v>
       </c>
       <c r="H585" t="n">
-        <v>2028.05</v>
+        <v>2010.05</v>
       </c>
       <c r="I585" t="n">
         <v>0.0</v>
@@ -22068,7 +22068,7 @@
         </is>
       </c>
       <c r="E595" t="n">
-        <v>2612.061</v>
+        <v>2327.304</v>
       </c>
       <c r="F595" t="n">
         <v>0.0</v>
@@ -22077,7 +22077,7 @@
         <v>1050.859</v>
       </c>
       <c r="H595" t="n">
-        <v>2612.061</v>
+        <v>2327.304</v>
       </c>
       <c r="I595" t="n">
         <v>0.0</v>
@@ -22105,7 +22105,7 @@
         </is>
       </c>
       <c r="E596" t="n">
-        <v>484.74899999999997</v>
+        <v>135.498</v>
       </c>
       <c r="F596" t="n">
         <v>0.0</v>
@@ -22114,7 +22114,7 @@
         <v>386.37899999999996</v>
       </c>
       <c r="H596" t="n">
-        <v>484.74899999999997</v>
+        <v>135.498</v>
       </c>
       <c r="I596" t="n">
         <v>0.0</v>
@@ -22216,7 +22216,7 @@
         </is>
       </c>
       <c r="E599" t="n">
-        <v>7401.28</v>
+        <v>6933.687</v>
       </c>
       <c r="F599" t="n">
         <v>2.5149999999999997</v>
@@ -22225,7 +22225,7 @@
         <v>468.626</v>
       </c>
       <c r="H599" t="n">
-        <v>7401.28</v>
+        <v>6933.687</v>
       </c>
       <c r="I599" t="n">
         <v>0.0</v>
@@ -22290,7 +22290,7 @@
         </is>
       </c>
       <c r="E601" t="n">
-        <v>203.692</v>
+        <v>59.022999999999996</v>
       </c>
       <c r="F601" t="n">
         <v>0.0</v>
@@ -22299,7 +22299,7 @@
         <v>0.888</v>
       </c>
       <c r="H601" t="n">
-        <v>203.692</v>
+        <v>59.022999999999996</v>
       </c>
       <c r="I601" t="n">
         <v>0.0</v>
@@ -22327,7 +22327,7 @@
         </is>
       </c>
       <c r="E602" t="n">
-        <v>633.84</v>
+        <v>510.408</v>
       </c>
       <c r="F602" t="n">
         <v>0.0</v>
@@ -22336,7 +22336,7 @@
         <v>0.5</v>
       </c>
       <c r="H602" t="n">
-        <v>633.84</v>
+        <v>510.408</v>
       </c>
       <c r="I602" t="n">
         <v>0.0</v>
@@ -22364,7 +22364,7 @@
         </is>
       </c>
       <c r="E603" t="n">
-        <v>5755.64</v>
+        <v>5750.308</v>
       </c>
       <c r="F603" t="n">
         <v>1.067</v>
@@ -22373,7 +22373,7 @@
         <v>886.345</v>
       </c>
       <c r="H603" t="n">
-        <v>5755.64</v>
+        <v>5750.308</v>
       </c>
       <c r="I603" t="n">
         <v>0.0</v>
@@ -23215,7 +23215,7 @@
         </is>
       </c>
       <c r="E626" t="n">
-        <v>66.4</v>
+        <v>66.0</v>
       </c>
       <c r="F626" t="n">
         <v>0.4</v>
@@ -23224,7 +23224,7 @@
         <v>0.0</v>
       </c>
       <c r="H626" t="n">
-        <v>66.4</v>
+        <v>66.0</v>
       </c>
       <c r="I626" t="n">
         <v>0.0</v>
@@ -23511,7 +23511,7 @@
         </is>
       </c>
       <c r="E634" t="n">
-        <v>3800.76</v>
+        <v>3747.416</v>
       </c>
       <c r="F634" t="n">
         <v>0.0</v>
@@ -23520,7 +23520,7 @@
         <v>0.0</v>
       </c>
       <c r="H634" t="n">
-        <v>3800.76</v>
+        <v>3747.416</v>
       </c>
       <c r="I634" t="n">
         <v>0.0</v>
@@ -23955,7 +23955,7 @@
         </is>
       </c>
       <c r="E646" t="n">
-        <v>10282.2174</v>
+        <v>9615.018</v>
       </c>
       <c r="F646" t="n">
         <v>0.0</v>
@@ -23964,10 +23964,10 @@
         <v>25.354000000000003</v>
       </c>
       <c r="H646" t="n">
-        <v>9627.027</v>
+        <v>9615.018</v>
       </c>
       <c r="I646" t="n">
-        <v>655.1904</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="647">
@@ -23992,7 +23992,7 @@
         </is>
       </c>
       <c r="E647" t="n">
-        <v>1582.3020000000001</v>
+        <v>1577.902</v>
       </c>
       <c r="F647" t="n">
         <v>0.8</v>
@@ -24001,7 +24001,7 @@
         <v>0.0</v>
       </c>
       <c r="H647" t="n">
-        <v>1582.3020000000001</v>
+        <v>1577.902</v>
       </c>
       <c r="I647" t="n">
         <v>0.0</v>
@@ -24214,7 +24214,7 @@
         </is>
       </c>
       <c r="E653" t="n">
-        <v>6289.527999999999</v>
+        <v>6249.496</v>
       </c>
       <c r="F653" t="n">
         <v>0.0</v>
@@ -24223,7 +24223,7 @@
         <v>65.05199999999999</v>
       </c>
       <c r="H653" t="n">
-        <v>6289.527999999999</v>
+        <v>6249.496</v>
       </c>
       <c r="I653" t="n">
         <v>0.0</v>
@@ -24362,7 +24362,7 @@
         </is>
       </c>
       <c r="E657" t="n">
-        <v>15.693</v>
+        <v>12.923</v>
       </c>
       <c r="F657" t="n">
         <v>0.923</v>
@@ -24371,7 +24371,7 @@
         <v>1524.961</v>
       </c>
       <c r="H657" t="n">
-        <v>15.693</v>
+        <v>12.923</v>
       </c>
       <c r="I657" t="n">
         <v>0.0</v>
@@ -24547,7 +24547,7 @@
         </is>
       </c>
       <c r="E662" t="n">
-        <v>1569.9270000000001</v>
+        <v>1546.111</v>
       </c>
       <c r="F662" t="n">
         <v>1.7730000000000001</v>
@@ -24556,7 +24556,7 @@
         <v>179.285</v>
       </c>
       <c r="H662" t="n">
-        <v>1569.9270000000001</v>
+        <v>1546.111</v>
       </c>
       <c r="I662" t="n">
         <v>0.0</v>
@@ -24584,7 +24584,7 @@
         </is>
       </c>
       <c r="E663" t="n">
-        <v>2231.892</v>
+        <v>2225.975</v>
       </c>
       <c r="F663" t="n">
         <v>0.0</v>
@@ -24593,7 +24593,7 @@
         <v>55.620000000000005</v>
       </c>
       <c r="H663" t="n">
-        <v>2231.892</v>
+        <v>2225.975</v>
       </c>
       <c r="I663" t="n">
         <v>0.0</v>
@@ -24769,7 +24769,7 @@
         </is>
       </c>
       <c r="E668" t="n">
-        <v>10.207</v>
+        <v>8.431</v>
       </c>
       <c r="F668" t="n">
         <v>1.035</v>
@@ -24778,7 +24778,7 @@
         <v>142.00799999999998</v>
       </c>
       <c r="H668" t="n">
-        <v>10.207</v>
+        <v>8.431</v>
       </c>
       <c r="I668" t="n">
         <v>0.0</v>
@@ -25102,7 +25102,7 @@
         </is>
       </c>
       <c r="E677" t="n">
-        <v>12827.36</v>
+        <v>12814.313</v>
       </c>
       <c r="F677" t="n">
         <v>0.0</v>
@@ -25111,7 +25111,7 @@
         <v>3.7279999999999998</v>
       </c>
       <c r="H677" t="n">
-        <v>12827.36</v>
+        <v>12814.313</v>
       </c>
       <c r="I677" t="n">
         <v>0.0</v>
@@ -25361,7 +25361,7 @@
         </is>
       </c>
       <c r="E684" t="n">
-        <v>2880.781</v>
+        <v>2879.225</v>
       </c>
       <c r="F684" t="n">
         <v>0.312</v>
@@ -25370,7 +25370,7 @@
         <v>0.0</v>
       </c>
       <c r="H684" t="n">
-        <v>2880.781</v>
+        <v>2879.225</v>
       </c>
       <c r="I684" t="n">
         <v>0.0</v>
@@ -25398,7 +25398,7 @@
         </is>
       </c>
       <c r="E685" t="n">
-        <v>3661.8050000000003</v>
+        <v>3661.183</v>
       </c>
       <c r="F685" t="n">
         <v>3734.0</v>
@@ -25407,7 +25407,7 @@
         <v>0.0</v>
       </c>
       <c r="H685" t="n">
-        <v>3661.8050000000003</v>
+        <v>3661.183</v>
       </c>
       <c r="I685" t="n">
         <v>0.0</v>
@@ -25435,7 +25435,7 @@
         </is>
       </c>
       <c r="E686" t="n">
-        <v>11656.944</v>
+        <v>11404.902</v>
       </c>
       <c r="F686" t="n">
         <v>0.0</v>
@@ -25444,7 +25444,7 @@
         <v>3898.25</v>
       </c>
       <c r="H686" t="n">
-        <v>11656.944</v>
+        <v>11404.902</v>
       </c>
       <c r="I686" t="n">
         <v>0.0</v>
@@ -25953,7 +25953,7 @@
         </is>
       </c>
       <c r="E700" t="n">
-        <v>1264.581</v>
+        <v>1243.11</v>
       </c>
       <c r="F700" t="n">
         <v>0.624</v>
@@ -25962,7 +25962,7 @@
         <v>0.0</v>
       </c>
       <c r="H700" t="n">
-        <v>1264.581</v>
+        <v>1243.11</v>
       </c>
       <c r="I700" t="n">
         <v>0.0</v>
@@ -25990,7 +25990,7 @@
         </is>
       </c>
       <c r="E701" t="n">
-        <v>4748.713</v>
+        <v>4664.3859999999995</v>
       </c>
       <c r="F701" t="n">
         <v>26.450000000000003</v>
@@ -25999,7 +25999,7 @@
         <v>5.601</v>
       </c>
       <c r="H701" t="n">
-        <v>4748.713</v>
+        <v>4664.3859999999995</v>
       </c>
       <c r="I701" t="n">
         <v>0.0</v>
@@ -26027,7 +26027,7 @@
         </is>
       </c>
       <c r="E702" t="n">
-        <v>7510.004</v>
+        <v>7424.434</v>
       </c>
       <c r="F702" t="n">
         <v>41.385999999999996</v>
@@ -26036,7 +26036,7 @@
         <v>9.334999999999999</v>
       </c>
       <c r="H702" t="n">
-        <v>7510.004</v>
+        <v>7424.434</v>
       </c>
       <c r="I702" t="n">
         <v>0.0</v>
@@ -26064,7 +26064,7 @@
         </is>
       </c>
       <c r="E703" t="n">
-        <v>2599.154</v>
+        <v>2599.155</v>
       </c>
       <c r="F703" t="n">
         <v>0.0</v>
@@ -26073,7 +26073,7 @@
         <v>3.851</v>
       </c>
       <c r="H703" t="n">
-        <v>2599.154</v>
+        <v>2599.155</v>
       </c>
       <c r="I703" t="n">
         <v>0.0</v>
@@ -26212,7 +26212,7 @@
         </is>
       </c>
       <c r="E707" t="n">
-        <v>1825.895</v>
+        <v>696.732</v>
       </c>
       <c r="F707" t="n">
         <v>0.0</v>
@@ -26221,7 +26221,7 @@
         <v>0.0</v>
       </c>
       <c r="H707" t="n">
-        <v>1825.895</v>
+        <v>696.732</v>
       </c>
       <c r="I707" t="n">
         <v>0.0</v>
@@ -26249,7 +26249,7 @@
         </is>
       </c>
       <c r="E708" t="n">
-        <v>891.99</v>
+        <v>443.91</v>
       </c>
       <c r="F708" t="n">
         <v>0.0</v>
@@ -26258,7 +26258,7 @@
         <v>2.987</v>
       </c>
       <c r="H708" t="n">
-        <v>891.99</v>
+        <v>443.91</v>
       </c>
       <c r="I708" t="n">
         <v>0.0</v>
@@ -26397,7 +26397,7 @@
         </is>
       </c>
       <c r="E712" t="n">
-        <v>1418.434</v>
+        <v>1402.439</v>
       </c>
       <c r="F712" t="n">
         <v>0.666</v>
@@ -26406,7 +26406,7 @@
         <v>10.996</v>
       </c>
       <c r="H712" t="n">
-        <v>1418.434</v>
+        <v>1402.439</v>
       </c>
       <c r="I712" t="n">
         <v>0.0</v>
@@ -26545,7 +26545,7 @@
         </is>
       </c>
       <c r="E716" t="n">
-        <v>6070.02</v>
+        <v>6070.021</v>
       </c>
       <c r="F716" t="n">
         <v>0.0</v>
@@ -26554,7 +26554,7 @@
         <v>0.0</v>
       </c>
       <c r="H716" t="n">
-        <v>6070.02</v>
+        <v>6070.021</v>
       </c>
       <c r="I716" t="n">
         <v>0.0</v>
@@ -26582,7 +26582,7 @@
         </is>
       </c>
       <c r="E717" t="n">
-        <v>1254.0230000000001</v>
+        <v>1252.423</v>
       </c>
       <c r="F717" t="n">
         <v>0.0</v>
@@ -26591,7 +26591,7 @@
         <v>153.619</v>
       </c>
       <c r="H717" t="n">
-        <v>1254.0230000000001</v>
+        <v>1252.423</v>
       </c>
       <c r="I717" t="n">
         <v>0.0</v>
@@ -26619,7 +26619,7 @@
         </is>
       </c>
       <c r="E718" t="n">
-        <v>4473.32</v>
+        <v>4434.922</v>
       </c>
       <c r="F718" t="n">
         <v>0.0</v>
@@ -26628,7 +26628,7 @@
         <v>0.0</v>
       </c>
       <c r="H718" t="n">
-        <v>4473.32</v>
+        <v>4434.922</v>
       </c>
       <c r="I718" t="n">
         <v>0.0</v>
@@ -26656,7 +26656,7 @@
         </is>
       </c>
       <c r="E719" t="n">
-        <v>2870.491</v>
+        <v>2371.229</v>
       </c>
       <c r="F719" t="n">
         <v>0.26699999999999996</v>
@@ -26665,7 +26665,7 @@
         <v>0.0</v>
       </c>
       <c r="H719" t="n">
-        <v>2870.491</v>
+        <v>2371.229</v>
       </c>
       <c r="I719" t="n">
         <v>0.0</v>
@@ -26693,7 +26693,7 @@
         </is>
       </c>
       <c r="E720" t="n">
-        <v>267.717</v>
+        <v>266.117</v>
       </c>
       <c r="F720" t="n">
         <v>6.4</v>
@@ -26702,7 +26702,7 @@
         <v>3.2</v>
       </c>
       <c r="H720" t="n">
-        <v>267.717</v>
+        <v>266.117</v>
       </c>
       <c r="I720" t="n">
         <v>0.0</v>
@@ -26767,7 +26767,7 @@
         </is>
       </c>
       <c r="E722" t="n">
-        <v>2884.0860000000002</v>
+        <v>2844.621</v>
       </c>
       <c r="F722" t="n">
         <v>0.0</v>
@@ -26776,7 +26776,7 @@
         <v>0.0</v>
       </c>
       <c r="H722" t="n">
-        <v>2884.0860000000002</v>
+        <v>2844.621</v>
       </c>
       <c r="I722" t="n">
         <v>0.0</v>
@@ -26804,7 +26804,7 @@
         </is>
       </c>
       <c r="E723" t="n">
-        <v>26040.32</v>
+        <v>25895.236</v>
       </c>
       <c r="F723" t="n">
         <v>2.4</v>
@@ -26813,7 +26813,7 @@
         <v>288.036</v>
       </c>
       <c r="H723" t="n">
-        <v>26040.32</v>
+        <v>25895.236</v>
       </c>
       <c r="I723" t="n">
         <v>0.0</v>
@@ -26841,7 +26841,7 @@
         </is>
       </c>
       <c r="E724" t="n">
-        <v>4047.174</v>
+        <v>3931.425</v>
       </c>
       <c r="F724" t="n">
         <v>2.4</v>
@@ -26850,7 +26850,7 @@
         <v>212.827</v>
       </c>
       <c r="H724" t="n">
-        <v>4047.174</v>
+        <v>3931.425</v>
       </c>
       <c r="I724" t="n">
         <v>0.0</v>
@@ -26878,7 +26878,7 @@
         </is>
       </c>
       <c r="E725" t="n">
-        <v>2699.382</v>
+        <v>2685.924</v>
       </c>
       <c r="F725" t="n">
         <v>0.13899999999999998</v>
@@ -26887,7 +26887,7 @@
         <v>67.155</v>
       </c>
       <c r="H725" t="n">
-        <v>2699.382</v>
+        <v>2685.924</v>
       </c>
       <c r="I725" t="n">
         <v>0.0</v>
@@ -26915,7 +26915,7 @@
         </is>
       </c>
       <c r="E726" t="n">
-        <v>1891.04</v>
+        <v>1879.28</v>
       </c>
       <c r="F726" t="n">
         <v>0.2</v>
@@ -26924,7 +26924,7 @@
         <v>2.8800000000000003</v>
       </c>
       <c r="H726" t="n">
-        <v>1891.04</v>
+        <v>1879.28</v>
       </c>
       <c r="I726" t="n">
         <v>0.0</v>
@@ -26952,7 +26952,7 @@
         </is>
       </c>
       <c r="E727" t="n">
-        <v>3015.0359999999996</v>
+        <v>3005.4170000000004</v>
       </c>
       <c r="F727" t="n">
         <v>0.0</v>
@@ -26961,7 +26961,7 @@
         <v>0.555</v>
       </c>
       <c r="H727" t="n">
-        <v>3015.0359999999996</v>
+        <v>3005.4170000000004</v>
       </c>
       <c r="I727" t="n">
         <v>0.0</v>
@@ -26989,7 +26989,7 @@
         </is>
       </c>
       <c r="E728" t="n">
-        <v>1723.683</v>
+        <v>1722.0030000000002</v>
       </c>
       <c r="F728" t="n">
         <v>0.0</v>
@@ -26998,7 +26998,7 @@
         <v>0.0</v>
       </c>
       <c r="H728" t="n">
-        <v>1723.683</v>
+        <v>1722.0030000000002</v>
       </c>
       <c r="I728" t="n">
         <v>0.0</v>
@@ -27285,7 +27285,7 @@
         </is>
       </c>
       <c r="E736" t="n">
-        <v>930.786</v>
+        <v>770.263</v>
       </c>
       <c r="F736" t="n">
         <v>11.733</v>
@@ -27294,7 +27294,7 @@
         <v>0.0</v>
       </c>
       <c r="H736" t="n">
-        <v>930.786</v>
+        <v>770.263</v>
       </c>
       <c r="I736" t="n">
         <v>0.0</v>
@@ -27544,7 +27544,7 @@
         </is>
       </c>
       <c r="E743" t="n">
-        <v>2214.141</v>
+        <v>2123.019</v>
       </c>
       <c r="F743" t="n">
         <v>0.0</v>
@@ -27553,7 +27553,7 @@
         <v>162.126</v>
       </c>
       <c r="H743" t="n">
-        <v>2214.141</v>
+        <v>2123.019</v>
       </c>
       <c r="I743" t="n">
         <v>0.0</v>
@@ -27581,7 +27581,7 @@
         </is>
       </c>
       <c r="E744" t="n">
-        <v>994.603</v>
+        <v>901.5559999999999</v>
       </c>
       <c r="F744" t="n">
         <v>13.831</v>
@@ -27590,7 +27590,7 @@
         <v>5.029999999999999</v>
       </c>
       <c r="H744" t="n">
-        <v>994.603</v>
+        <v>901.5559999999999</v>
       </c>
       <c r="I744" t="n">
         <v>0.0</v>
@@ -27618,7 +27618,7 @@
         </is>
       </c>
       <c r="E745" t="n">
-        <v>894.011</v>
+        <v>862.576</v>
       </c>
       <c r="F745" t="n">
         <v>21.375999999999998</v>
@@ -27627,7 +27627,7 @@
         <v>0.0</v>
       </c>
       <c r="H745" t="n">
-        <v>894.011</v>
+        <v>862.576</v>
       </c>
       <c r="I745" t="n">
         <v>0.0</v>
@@ -27729,7 +27729,7 @@
         </is>
       </c>
       <c r="E748" t="n">
-        <v>1706.462</v>
+        <v>1590.49</v>
       </c>
       <c r="F748" t="n">
         <v>0.0</v>
@@ -27738,7 +27738,7 @@
         <v>177.51</v>
       </c>
       <c r="H748" t="n">
-        <v>1706.462</v>
+        <v>1590.49</v>
       </c>
       <c r="I748" t="n">
         <v>0.0</v>
@@ -27988,7 +27988,7 @@
         </is>
       </c>
       <c r="E755" t="n">
-        <v>2566.163</v>
+        <v>2510.777</v>
       </c>
       <c r="F755" t="n">
         <v>2.3080000000000003</v>
@@ -27997,7 +27997,7 @@
         <v>2.3080000000000003</v>
       </c>
       <c r="H755" t="n">
-        <v>2566.163</v>
+        <v>2510.777</v>
       </c>
       <c r="I755" t="n">
         <v>0.0</v>
@@ -28025,7 +28025,7 @@
         </is>
       </c>
       <c r="E756" t="n">
-        <v>4271.555</v>
+        <v>4186.169</v>
       </c>
       <c r="F756" t="n">
         <v>0.0</v>
@@ -28034,7 +28034,7 @@
         <v>2.3080000000000003</v>
       </c>
       <c r="H756" t="n">
-        <v>4271.555</v>
+        <v>4186.169</v>
       </c>
       <c r="I756" t="n">
         <v>0.0</v>
@@ -28358,7 +28358,7 @@
         </is>
       </c>
       <c r="E765" t="n">
-        <v>792.362</v>
+        <v>822.6999999999999</v>
       </c>
       <c r="F765" t="n">
         <v>0.892</v>
@@ -28367,7 +28367,7 @@
         <v>0.0</v>
       </c>
       <c r="H765" t="n">
-        <v>792.362</v>
+        <v>822.6999999999999</v>
       </c>
       <c r="I765" t="n">
         <v>0.0</v>
@@ -28506,7 +28506,7 @@
         </is>
       </c>
       <c r="E769" t="n">
-        <v>18785.086</v>
+        <v>18743.547</v>
       </c>
       <c r="F769" t="n">
         <v>15.231</v>
@@ -28515,7 +28515,7 @@
         <v>7.385</v>
       </c>
       <c r="H769" t="n">
-        <v>18785.086</v>
+        <v>18743.547</v>
       </c>
       <c r="I769" t="n">
         <v>0.0</v>
@@ -28654,7 +28654,7 @@
         </is>
       </c>
       <c r="E773" t="n">
-        <v>5301.742</v>
+        <v>5294.974</v>
       </c>
       <c r="F773" t="n">
         <v>2.0309999999999997</v>
@@ -28663,7 +28663,7 @@
         <v>2.0309999999999997</v>
       </c>
       <c r="H773" t="n">
-        <v>5301.742</v>
+        <v>5294.974</v>
       </c>
       <c r="I773" t="n">
         <v>0.0</v>
@@ -28691,7 +28691,7 @@
         </is>
       </c>
       <c r="E774" t="n">
-        <v>1928.245</v>
+        <v>1923.168</v>
       </c>
       <c r="F774" t="n">
         <v>2.0309999999999997</v>
@@ -28700,7 +28700,7 @@
         <v>4.061999999999999</v>
       </c>
       <c r="H774" t="n">
-        <v>1928.245</v>
+        <v>1923.168</v>
       </c>
       <c r="I774" t="n">
         <v>0.0</v>
@@ -28765,7 +28765,7 @@
         </is>
       </c>
       <c r="E776" t="n">
-        <v>11453.039</v>
+        <v>11540.024</v>
       </c>
       <c r="F776" t="n">
         <v>4.736</v>
@@ -28774,7 +28774,7 @@
         <v>38.585</v>
       </c>
       <c r="H776" t="n">
-        <v>11453.039</v>
+        <v>11540.024</v>
       </c>
       <c r="I776" t="n">
         <v>0.0</v>
@@ -28913,7 +28913,7 @@
         </is>
       </c>
       <c r="E780" t="n">
-        <v>3264.849</v>
+        <v>3244.202</v>
       </c>
       <c r="F780" t="n">
         <v>0.0</v>
@@ -28922,7 +28922,7 @@
         <v>0.0</v>
       </c>
       <c r="H780" t="n">
-        <v>3264.849</v>
+        <v>3244.202</v>
       </c>
       <c r="I780" t="n">
         <v>0.0</v>
@@ -28987,7 +28987,7 @@
         </is>
       </c>
       <c r="E782" t="n">
-        <v>13.88</v>
+        <v>11.849</v>
       </c>
       <c r="F782" t="n">
         <v>0.0</v>
@@ -28996,7 +28996,7 @@
         <v>6419.359</v>
       </c>
       <c r="H782" t="n">
-        <v>13.88</v>
+        <v>11.849</v>
       </c>
       <c r="I782" t="n">
         <v>0.0</v>
@@ -29061,7 +29061,7 @@
         </is>
       </c>
       <c r="E784" t="n">
-        <v>675.001</v>
+        <v>666.841</v>
       </c>
       <c r="F784" t="n">
         <v>0.0</v>
@@ -29070,7 +29070,7 @@
         <v>19.68</v>
       </c>
       <c r="H784" t="n">
-        <v>675.001</v>
+        <v>666.841</v>
       </c>
       <c r="I784" t="n">
         <v>0.0</v>
@@ -29135,7 +29135,7 @@
         </is>
       </c>
       <c r="E786" t="n">
-        <v>4181.371</v>
+        <v>4153.389</v>
       </c>
       <c r="F786" t="n">
         <v>0.185</v>
@@ -29144,7 +29144,7 @@
         <v>34.456</v>
       </c>
       <c r="H786" t="n">
-        <v>4181.371</v>
+        <v>4153.389</v>
       </c>
       <c r="I786" t="n">
         <v>0.0</v>
@@ -29172,7 +29172,7 @@
         </is>
       </c>
       <c r="E787" t="n">
-        <v>552.919</v>
+        <v>545.149</v>
       </c>
       <c r="F787" t="n">
         <v>4.995</v>
@@ -29181,7 +29181,7 @@
         <v>79.36500000000001</v>
       </c>
       <c r="H787" t="n">
-        <v>552.919</v>
+        <v>545.149</v>
       </c>
       <c r="I787" t="n">
         <v>0.0</v>
@@ -29209,7 +29209,7 @@
         </is>
       </c>
       <c r="E788" t="n">
-        <v>1207.575</v>
+        <v>1099.575</v>
       </c>
       <c r="F788" t="n">
         <v>1.485</v>
@@ -29218,7 +29218,7 @@
         <v>8.1</v>
       </c>
       <c r="H788" t="n">
-        <v>1207.575</v>
+        <v>1099.575</v>
       </c>
       <c r="I788" t="n">
         <v>0.0</v>
@@ -29246,7 +29246,7 @@
         </is>
       </c>
       <c r="E789" t="n">
-        <v>1170.96</v>
+        <v>1138.68</v>
       </c>
       <c r="F789" t="n">
         <v>0.32</v>
@@ -29255,7 +29255,7 @@
         <v>17.32</v>
       </c>
       <c r="H789" t="n">
-        <v>1170.96</v>
+        <v>1138.68</v>
       </c>
       <c r="I789" t="n">
         <v>0.0</v>
@@ -29357,7 +29357,7 @@
         </is>
       </c>
       <c r="E792" t="n">
-        <v>4983.611</v>
+        <v>4972.6939999999995</v>
       </c>
       <c r="F792" t="n">
         <v>3.033</v>
@@ -29366,7 +29366,7 @@
         <v>12.13</v>
       </c>
       <c r="H792" t="n">
-        <v>4983.611</v>
+        <v>4972.6939999999995</v>
       </c>
       <c r="I792" t="n">
         <v>0.0</v>
@@ -29394,7 +29394,7 @@
         </is>
       </c>
       <c r="E793" t="n">
-        <v>3224.154</v>
+        <v>3199.288</v>
       </c>
       <c r="F793" t="n">
         <v>6.065</v>
@@ -29403,7 +29403,7 @@
         <v>9.704</v>
       </c>
       <c r="H793" t="n">
-        <v>3224.154</v>
+        <v>3199.288</v>
       </c>
       <c r="I793" t="n">
         <v>0.0</v>
@@ -29431,7 +29431,7 @@
         </is>
       </c>
       <c r="E794" t="n">
-        <v>443.352</v>
+        <v>364.507</v>
       </c>
       <c r="F794" t="n">
         <v>1.213</v>
@@ -29440,7 +29440,7 @@
         <v>0.0</v>
       </c>
       <c r="H794" t="n">
-        <v>443.352</v>
+        <v>364.507</v>
       </c>
       <c r="I794" t="n">
         <v>0.0</v>
@@ -29579,7 +29579,7 @@
         </is>
       </c>
       <c r="E798" t="n">
-        <v>4156.806</v>
+        <v>4132.8369999999995</v>
       </c>
       <c r="F798" t="n">
         <v>1.8920000000000001</v>
@@ -29588,7 +29588,7 @@
         <v>80.739</v>
       </c>
       <c r="H798" t="n">
-        <v>4156.806</v>
+        <v>4132.8369999999995</v>
       </c>
       <c r="I798" t="n">
         <v>0.0</v>
@@ -29616,7 +29616,7 @@
         </is>
       </c>
       <c r="E799" t="n">
-        <v>3165.8599999999997</v>
+        <v>3160.183</v>
       </c>
       <c r="F799" t="n">
         <v>3.154</v>
@@ -29625,7 +29625,7 @@
         <v>0.631</v>
       </c>
       <c r="H799" t="n">
-        <v>3165.8599999999997</v>
+        <v>3160.183</v>
       </c>
       <c r="I799" t="n">
         <v>0.0</v>
@@ -30097,7 +30097,7 @@
         </is>
       </c>
       <c r="E812" t="n">
-        <v>1684.8000000000002</v>
+        <v>1631.1999999999998</v>
       </c>
       <c r="F812" t="n">
         <v>0.6</v>
@@ -30106,7 +30106,7 @@
         <v>2.4</v>
       </c>
       <c r="H812" t="n">
-        <v>1684.8000000000002</v>
+        <v>1631.1999999999998</v>
       </c>
       <c r="I812" t="n">
         <v>0.0</v>
@@ -30245,7 +30245,7 @@
         </is>
       </c>
       <c r="E816" t="n">
-        <v>214.427</v>
+        <v>60.274</v>
       </c>
       <c r="F816" t="n">
         <v>0.533</v>
@@ -30254,7 +30254,7 @@
         <v>0.0</v>
       </c>
       <c r="H816" t="n">
-        <v>214.427</v>
+        <v>60.274</v>
       </c>
       <c r="I816" t="n">
         <v>0.0</v>
@@ -30282,7 +30282,7 @@
         </is>
       </c>
       <c r="E817" t="n">
-        <v>12409.284</v>
+        <v>12404.483</v>
       </c>
       <c r="F817" t="n">
         <v>2.4</v>
@@ -30291,7 +30291,7 @@
         <v>599.008</v>
       </c>
       <c r="H817" t="n">
-        <v>12409.284</v>
+        <v>12404.483</v>
       </c>
       <c r="I817" t="n">
         <v>0.0</v>
@@ -30430,7 +30430,7 @@
         </is>
       </c>
       <c r="E821" t="n">
-        <v>952.12</v>
+        <v>752.094</v>
       </c>
       <c r="F821" t="n">
         <v>0.0</v>
@@ -30439,7 +30439,7 @@
         <v>192.024</v>
       </c>
       <c r="H821" t="n">
-        <v>952.12</v>
+        <v>752.094</v>
       </c>
       <c r="I821" t="n">
         <v>0.0</v>
@@ -30652,7 +30652,7 @@
         </is>
       </c>
       <c r="E827" t="n">
-        <v>320.256</v>
+        <v>106.752</v>
       </c>
       <c r="F827" t="n">
         <v>0.0</v>
@@ -30661,7 +30661,7 @@
         <v>1670.6689999999999</v>
       </c>
       <c r="H827" t="n">
-        <v>320.256</v>
+        <v>106.752</v>
       </c>
       <c r="I827" t="n">
         <v>0.0</v>
@@ -31244,7 +31244,7 @@
         </is>
       </c>
       <c r="E843" t="n">
-        <v>589.777</v>
+        <v>567.933</v>
       </c>
       <c r="F843" t="n">
         <v>0.0</v>
@@ -31253,7 +31253,7 @@
         <v>0.0</v>
       </c>
       <c r="H843" t="n">
-        <v>589.777</v>
+        <v>567.933</v>
       </c>
       <c r="I843" t="n">
         <v>0.0</v>
@@ -31318,7 +31318,7 @@
         </is>
       </c>
       <c r="E845" t="n">
-        <v>830.057</v>
+        <v>677.152</v>
       </c>
       <c r="F845" t="n">
         <v>0.0</v>
@@ -31327,7 +31327,7 @@
         <v>0.0</v>
       </c>
       <c r="H845" t="n">
-        <v>830.057</v>
+        <v>677.152</v>
       </c>
       <c r="I845" t="n">
         <v>0.0</v>
@@ -31392,7 +31392,7 @@
         </is>
       </c>
       <c r="E847" t="n">
-        <v>2929.48</v>
+        <v>2928.814</v>
       </c>
       <c r="F847" t="n">
         <v>1.333</v>
@@ -31401,7 +31401,7 @@
         <v>0.6669999999999999</v>
       </c>
       <c r="H847" t="n">
-        <v>2929.48</v>
+        <v>2928.814</v>
       </c>
       <c r="I847" t="n">
         <v>0.0</v>
@@ -31429,7 +31429,7 @@
         </is>
       </c>
       <c r="E848" t="n">
-        <v>2610.1310000000003</v>
+        <v>2609.464</v>
       </c>
       <c r="F848" t="n">
         <v>3.333</v>
@@ -31438,7 +31438,7 @@
         <v>0.0</v>
       </c>
       <c r="H848" t="n">
-        <v>2610.1310000000003</v>
+        <v>2609.464</v>
       </c>
       <c r="I848" t="n">
         <v>0.0</v>
@@ -31466,7 +31466,7 @@
         </is>
       </c>
       <c r="E849" t="n">
-        <v>19563.445</v>
+        <v>19561.311</v>
       </c>
       <c r="F849" t="n">
         <v>10.67</v>
@@ -31475,7 +31475,7 @@
         <v>0.0</v>
       </c>
       <c r="H849" t="n">
-        <v>19563.445</v>
+        <v>19561.311</v>
       </c>
       <c r="I849" t="n">
         <v>0.0</v>
@@ -31540,7 +31540,7 @@
         </is>
       </c>
       <c r="E851" t="n">
-        <v>5709.818</v>
+        <v>5668.217000000001</v>
       </c>
       <c r="F851" t="n">
         <v>0.0</v>
@@ -31549,7 +31549,7 @@
         <v>0.0</v>
       </c>
       <c r="H851" t="n">
-        <v>5709.818</v>
+        <v>5668.217000000001</v>
       </c>
       <c r="I851" t="n">
         <v>0.0</v>
@@ -31651,7 +31651,7 @@
         </is>
       </c>
       <c r="E854" t="n">
-        <v>9983.518</v>
+        <v>9979.184000000001</v>
       </c>
       <c r="F854" t="n">
         <v>15.601</v>
@@ -31660,7 +31660,7 @@
         <v>0.0</v>
       </c>
       <c r="H854" t="n">
-        <v>9983.518</v>
+        <v>9979.184000000001</v>
       </c>
       <c r="I854" t="n">
         <v>0.0</v>
@@ -31688,7 +31688,7 @@
         </is>
       </c>
       <c r="E855" t="n">
-        <v>497.12899999999996</v>
+        <v>477.926</v>
       </c>
       <c r="F855" t="n">
         <v>23.470000000000002</v>
@@ -31697,7 +31697,7 @@
         <v>0.0</v>
       </c>
       <c r="H855" t="n">
-        <v>497.12899999999996</v>
+        <v>477.926</v>
       </c>
       <c r="I855" t="n">
         <v>0.0</v>
@@ -31725,7 +31725,7 @@
         </is>
       </c>
       <c r="E856" t="n">
-        <v>2713.71</v>
+        <v>2712.843</v>
       </c>
       <c r="F856" t="n">
         <v>2.601</v>
@@ -31734,7 +31734,7 @@
         <v>0.0</v>
       </c>
       <c r="H856" t="n">
-        <v>2713.71</v>
+        <v>2712.843</v>
       </c>
       <c r="I856" t="n">
         <v>0.0</v>
@@ -31836,7 +31836,7 @@
         </is>
       </c>
       <c r="E859" t="n">
-        <v>11978.801</v>
+        <v>11954.804</v>
       </c>
       <c r="F859" t="n">
         <v>15.997999999999998</v>
@@ -31845,7 +31845,7 @@
         <v>0.6669999999999999</v>
       </c>
       <c r="H859" t="n">
-        <v>11978.801</v>
+        <v>11954.804</v>
       </c>
       <c r="I859" t="n">
         <v>0.0</v>
@@ -31910,7 +31910,7 @@
         </is>
       </c>
       <c r="E861" t="n">
-        <v>2314.7999999999997</v>
+        <v>2313.7999999999997</v>
       </c>
       <c r="F861" t="n">
         <v>0.0</v>
@@ -31919,7 +31919,7 @@
         <v>0.0</v>
       </c>
       <c r="H861" t="n">
-        <v>2314.7999999999997</v>
+        <v>2313.7999999999997</v>
       </c>
       <c r="I861" t="n">
         <v>0.0</v>
@@ -31947,7 +31947,7 @@
         </is>
       </c>
       <c r="E862" t="n">
-        <v>1130.176</v>
+        <v>1129.31</v>
       </c>
       <c r="F862" t="n">
         <v>0.867</v>
@@ -31956,7 +31956,7 @@
         <v>0.0</v>
       </c>
       <c r="H862" t="n">
-        <v>1130.176</v>
+        <v>1129.31</v>
       </c>
       <c r="I862" t="n">
         <v>0.0</v>
@@ -31984,7 +31984,7 @@
         </is>
       </c>
       <c r="E863" t="n">
-        <v>10994.174</v>
+        <v>10959.769</v>
       </c>
       <c r="F863" t="n">
         <v>39.205</v>
@@ -31993,7 +31993,7 @@
         <v>0.0</v>
       </c>
       <c r="H863" t="n">
-        <v>10994.174</v>
+        <v>10959.769</v>
       </c>
       <c r="I863" t="n">
         <v>0.0</v>
@@ -32058,7 +32058,7 @@
         </is>
       </c>
       <c r="E865" t="n">
-        <v>2952.902</v>
+        <v>2951.835</v>
       </c>
       <c r="F865" t="n">
         <v>2.134</v>
@@ -32067,7 +32067,7 @@
         <v>0.0</v>
       </c>
       <c r="H865" t="n">
-        <v>2952.902</v>
+        <v>2951.835</v>
       </c>
       <c r="I865" t="n">
         <v>0.0</v>
@@ -32132,7 +32132,7 @@
         </is>
       </c>
       <c r="E867" t="n">
-        <v>1055.31</v>
+        <v>999.512</v>
       </c>
       <c r="F867" t="n">
         <v>18.802</v>
@@ -32141,7 +32141,7 @@
         <v>19.408</v>
       </c>
       <c r="H867" t="n">
-        <v>1055.31</v>
+        <v>999.512</v>
       </c>
       <c r="I867" t="n">
         <v>0.0</v>
@@ -32169,7 +32169,7 @@
         </is>
       </c>
       <c r="E868" t="n">
-        <v>1282.806</v>
+        <v>1268.606</v>
       </c>
       <c r="F868" t="n">
         <v>0.0</v>
@@ -32178,7 +32178,7 @@
         <v>0.0</v>
       </c>
       <c r="H868" t="n">
-        <v>1282.806</v>
+        <v>1268.606</v>
       </c>
       <c r="I868" t="n">
         <v>0.0</v>
@@ -32206,7 +32206,7 @@
         </is>
       </c>
       <c r="E869" t="n">
-        <v>1292.312</v>
+        <v>1280.774</v>
       </c>
       <c r="F869" t="n">
         <v>0.0</v>
@@ -32215,7 +32215,7 @@
         <v>9.231</v>
       </c>
       <c r="H869" t="n">
-        <v>1292.312</v>
+        <v>1280.774</v>
       </c>
       <c r="I869" t="n">
         <v>0.0</v>
@@ -32243,7 +32243,7 @@
         </is>
       </c>
       <c r="E870" t="n">
-        <v>2010.895</v>
+        <v>1975.54</v>
       </c>
       <c r="F870" t="n">
         <v>5.916</v>
@@ -32252,7 +32252,7 @@
         <v>346.144</v>
       </c>
       <c r="H870" t="n">
-        <v>2010.895</v>
+        <v>1975.54</v>
       </c>
       <c r="I870" t="n">
         <v>0.0</v>
@@ -32391,7 +32391,7 @@
         </is>
       </c>
       <c r="E874" t="n">
-        <v>9313.877</v>
+        <v>9251.57</v>
       </c>
       <c r="F874" t="n">
         <v>0.0</v>
@@ -32400,7 +32400,7 @@
         <v>6.923</v>
       </c>
       <c r="H874" t="n">
-        <v>9313.877</v>
+        <v>9251.57</v>
       </c>
       <c r="I874" t="n">
         <v>0.0</v>
@@ -32428,7 +32428,7 @@
         </is>
       </c>
       <c r="E875" t="n">
-        <v>4896.939</v>
+        <v>4871.556</v>
       </c>
       <c r="F875" t="n">
         <v>0.0</v>
@@ -32437,7 +32437,7 @@
         <v>0.0</v>
       </c>
       <c r="H875" t="n">
-        <v>4896.939</v>
+        <v>4871.556</v>
       </c>
       <c r="I875" t="n">
         <v>0.0</v>
@@ -32502,7 +32502,7 @@
         </is>
       </c>
       <c r="E877" t="n">
-        <v>2689.607</v>
+        <v>2676.559</v>
       </c>
       <c r="F877" t="n">
         <v>0.0</v>
@@ -32511,7 +32511,7 @@
         <v>0.9319999999999999</v>
       </c>
       <c r="H877" t="n">
-        <v>2689.607</v>
+        <v>2676.559</v>
       </c>
       <c r="I877" t="n">
         <v>0.0</v>
@@ -32687,7 +32687,7 @@
         </is>
       </c>
       <c r="E882" t="n">
-        <v>1102.344</v>
+        <v>822.764</v>
       </c>
       <c r="F882" t="n">
         <v>0.0</v>
@@ -32696,7 +32696,7 @@
         <v>3.994</v>
       </c>
       <c r="H882" t="n">
-        <v>1102.344</v>
+        <v>822.764</v>
       </c>
       <c r="I882" t="n">
         <v>0.0</v>
@@ -32798,7 +32798,7 @@
         </is>
       </c>
       <c r="E885" t="n">
-        <v>2295.796</v>
+        <v>2153.787</v>
       </c>
       <c r="F885" t="n">
         <v>0.0</v>
@@ -32807,7 +32807,7 @@
         <v>42.602000000000004</v>
       </c>
       <c r="H885" t="n">
-        <v>2295.796</v>
+        <v>2153.787</v>
       </c>
       <c r="I885" t="n">
         <v>0.0</v>
@@ -32983,7 +32983,7 @@
         </is>
       </c>
       <c r="E890" t="n">
-        <v>2648.117</v>
+        <v>2628.101</v>
       </c>
       <c r="F890" t="n">
         <v>0.0</v>
@@ -32992,7 +32992,7 @@
         <v>240.19199999999998</v>
       </c>
       <c r="H890" t="n">
-        <v>2648.117</v>
+        <v>2628.101</v>
       </c>
       <c r="I890" t="n">
         <v>0.0</v>
@@ -33057,7 +33057,7 @@
         </is>
       </c>
       <c r="E892" t="n">
-        <v>9110.615</v>
+        <v>9110.616</v>
       </c>
       <c r="F892" t="n">
         <v>0.0</v>
@@ -33066,7 +33066,7 @@
         <v>84.29</v>
       </c>
       <c r="H892" t="n">
-        <v>9110.615</v>
+        <v>9110.616</v>
       </c>
       <c r="I892" t="n">
         <v>0.0</v>
@@ -33131,7 +33131,7 @@
         </is>
       </c>
       <c r="E894" t="n">
-        <v>571.123</v>
+        <v>568.454</v>
       </c>
       <c r="F894" t="n">
         <v>5.338</v>
@@ -33140,7 +33140,7 @@
         <v>0.0</v>
       </c>
       <c r="H894" t="n">
-        <v>571.123</v>
+        <v>568.454</v>
       </c>
       <c r="I894" t="n">
         <v>0.0</v>
@@ -33242,7 +33242,7 @@
         </is>
       </c>
       <c r="E897" t="n">
-        <v>1808.112</v>
+        <v>1802.774</v>
       </c>
       <c r="F897" t="n">
         <v>0.0</v>
@@ -33251,7 +33251,7 @@
         <v>227.07</v>
       </c>
       <c r="H897" t="n">
-        <v>1808.112</v>
+        <v>1802.774</v>
       </c>
       <c r="I897" t="n">
         <v>0.0</v>
@@ -33279,7 +33279,7 @@
         </is>
       </c>
       <c r="E898" t="n">
-        <v>157.459</v>
+        <v>106.751</v>
       </c>
       <c r="F898" t="n">
         <v>0.0</v>
@@ -33288,7 +33288,7 @@
         <v>0.0</v>
       </c>
       <c r="H898" t="n">
-        <v>157.459</v>
+        <v>106.751</v>
       </c>
       <c r="I898" t="n">
         <v>0.0</v>
@@ -33316,7 +33316,7 @@
         </is>
       </c>
       <c r="E899" t="n">
-        <v>1849.825</v>
+        <v>1843.154</v>
       </c>
       <c r="F899" t="n">
         <v>3.033</v>
@@ -33325,7 +33325,7 @@
         <v>0.0</v>
       </c>
       <c r="H899" t="n">
-        <v>1849.825</v>
+        <v>1843.154</v>
       </c>
       <c r="I899" t="n">
         <v>0.0</v>
@@ -33353,7 +33353,7 @@
         </is>
       </c>
       <c r="E900" t="n">
-        <v>1025.592</v>
+        <v>1023.772</v>
       </c>
       <c r="F900" t="n">
         <v>0.607</v>
@@ -33362,7 +33362,7 @@
         <v>0.0</v>
       </c>
       <c r="H900" t="n">
-        <v>1025.592</v>
+        <v>1023.772</v>
       </c>
       <c r="I900" t="n">
         <v>0.0</v>
@@ -33427,7 +33427,7 @@
         </is>
       </c>
       <c r="E902" t="n">
-        <v>2469.142</v>
+        <v>2424.33</v>
       </c>
       <c r="F902" t="n">
         <v>67.218</v>
@@ -33436,7 +33436,7 @@
         <v>0.0</v>
       </c>
       <c r="H902" t="n">
-        <v>2469.142</v>
+        <v>2424.33</v>
       </c>
       <c r="I902" t="n">
         <v>0.0</v>
@@ -34278,7 +34278,7 @@
         </is>
       </c>
       <c r="E925" t="n">
-        <v>0.842</v>
+        <v>0.21</v>
       </c>
       <c r="F925" t="n">
         <v>0.0</v>
@@ -34287,7 +34287,7 @@
         <v>0.0</v>
       </c>
       <c r="H925" t="n">
-        <v>0.842</v>
+        <v>0.21</v>
       </c>
       <c r="I925" t="n">
         <v>0.0</v>
@@ -34315,7 +34315,7 @@
         </is>
       </c>
       <c r="E926" t="n">
-        <v>4548.323</v>
+        <v>4569.678</v>
       </c>
       <c r="F926" t="n">
         <v>0.211</v>
@@ -34324,7 +34324,7 @@
         <v>1.262</v>
       </c>
       <c r="H926" t="n">
-        <v>4548.323</v>
+        <v>4569.678</v>
       </c>
       <c r="I926" t="n">
         <v>0.0</v>
@@ -34352,7 +34352,7 @@
         </is>
       </c>
       <c r="E927" t="n">
-        <v>828.45</v>
+        <v>823.401</v>
       </c>
       <c r="F927" t="n">
         <v>0.0</v>
@@ -34361,7 +34361,7 @@
         <v>0.0</v>
       </c>
       <c r="H927" t="n">
-        <v>828.45</v>
+        <v>823.401</v>
       </c>
       <c r="I927" t="n">
         <v>0.0</v>
@@ -34389,7 +34389,7 @@
         </is>
       </c>
       <c r="E928" t="n">
-        <v>2820.01</v>
+        <v>2820.009</v>
       </c>
       <c r="F928" t="n">
         <v>0.0</v>
@@ -34398,7 +34398,7 @@
         <v>11.539000000000001</v>
       </c>
       <c r="H928" t="n">
-        <v>2820.01</v>
+        <v>2820.009</v>
       </c>
       <c r="I928" t="n">
         <v>0.0</v>
@@ -34500,7 +34500,7 @@
         </is>
       </c>
       <c r="E931" t="n">
-        <v>3498.472</v>
+        <v>3484.625</v>
       </c>
       <c r="F931" t="n">
         <v>0.0</v>
@@ -34509,7 +34509,7 @@
         <v>2.3080000000000003</v>
       </c>
       <c r="H931" t="n">
-        <v>3498.472</v>
+        <v>3484.625</v>
       </c>
       <c r="I931" t="n">
         <v>0.0</v>
@@ -34722,7 +34722,7 @@
         </is>
       </c>
       <c r="E937" t="n">
-        <v>8908.341</v>
+        <v>8881.567</v>
       </c>
       <c r="F937" t="n">
         <v>1.6280000000000001</v>
@@ -34731,7 +34731,7 @@
         <v>128.102</v>
       </c>
       <c r="H937" t="n">
-        <v>8908.341</v>
+        <v>8881.567</v>
       </c>
       <c r="I937" t="n">
         <v>0.0</v>
@@ -34796,7 +34796,7 @@
         </is>
       </c>
       <c r="E939" t="n">
-        <v>4193.091</v>
+        <v>4158.475</v>
       </c>
       <c r="F939" t="n">
         <v>0.0</v>
@@ -34805,7 +34805,7 @@
         <v>2.3080000000000003</v>
       </c>
       <c r="H939" t="n">
-        <v>4193.091</v>
+        <v>4158.475</v>
       </c>
       <c r="I939" t="n">
         <v>0.0</v>
@@ -34944,7 +34944,7 @@
         </is>
       </c>
       <c r="E943" t="n">
-        <v>338.443</v>
+        <v>321.64099999999996</v>
       </c>
       <c r="F943" t="n">
         <v>9.601</v>
@@ -34953,7 +34953,7 @@
         <v>0.0</v>
       </c>
       <c r="H943" t="n">
-        <v>338.443</v>
+        <v>321.64099999999996</v>
       </c>
       <c r="I943" t="n">
         <v>0.0</v>
@@ -35240,7 +35240,7 @@
         </is>
       </c>
       <c r="E951" t="n">
-        <v>1964.4560000000001</v>
+        <v>1758.614</v>
       </c>
       <c r="F951" t="n">
         <v>57.22</v>
@@ -35249,7 +35249,7 @@
         <v>0.0</v>
       </c>
       <c r="H951" t="n">
-        <v>1964.4560000000001</v>
+        <v>1758.614</v>
       </c>
       <c r="I951" t="n">
         <v>0.0</v>
@@ -35277,7 +35277,7 @@
         </is>
       </c>
       <c r="E952" t="n">
-        <v>924.649</v>
+        <v>852.9879999999999</v>
       </c>
       <c r="F952" t="n">
         <v>0.728</v>
@@ -35286,7 +35286,7 @@
         <v>0.0</v>
       </c>
       <c r="H952" t="n">
-        <v>924.649</v>
+        <v>852.9879999999999</v>
       </c>
       <c r="I952" t="n">
         <v>0.0</v>
@@ -35314,7 +35314,7 @@
         </is>
       </c>
       <c r="E953" t="n">
-        <v>1182.711</v>
+        <v>1115.256</v>
       </c>
       <c r="F953" t="n">
         <v>4.497</v>
@@ -35323,7 +35323,7 @@
         <v>0.0</v>
       </c>
       <c r="H953" t="n">
-        <v>1182.711</v>
+        <v>1115.256</v>
       </c>
       <c r="I953" t="n">
         <v>0.0</v>
@@ -35351,7 +35351,7 @@
         </is>
       </c>
       <c r="E954" t="n">
-        <v>2102.3469999999998</v>
+        <v>2034.893</v>
       </c>
       <c r="F954" t="n">
         <v>0.0</v>
@@ -35360,7 +35360,7 @@
         <v>0.0</v>
       </c>
       <c r="H954" t="n">
-        <v>2102.3469999999998</v>
+        <v>2034.893</v>
       </c>
       <c r="I954" t="n">
         <v>0.0</v>
@@ -36461,7 +36461,7 @@
         </is>
       </c>
       <c r="E984" t="n">
-        <v>618.3330000000001</v>
+        <v>3166.3329999999996</v>
       </c>
       <c r="F984" t="n">
         <v>16.1</v>
@@ -36470,10 +36470,10 @@
         <v>12.6</v>
       </c>
       <c r="H984" t="n">
-        <v>618.3330000000001</v>
+        <v>383.133</v>
       </c>
       <c r="I984" t="n">
-        <v>0.0</v>
+        <v>2783.2</v>
       </c>
     </row>
     <row r="985">
@@ -36498,7 +36498,7 @@
         </is>
       </c>
       <c r="E985" t="n">
-        <v>2934.647</v>
+        <v>2334.89</v>
       </c>
       <c r="F985" t="n">
         <v>37.268</v>
@@ -36507,7 +36507,7 @@
         <v>0.867</v>
       </c>
       <c r="H985" t="n">
-        <v>2934.647</v>
+        <v>2334.89</v>
       </c>
       <c r="I985" t="n">
         <v>0.0</v>
@@ -36535,7 +36535,7 @@
         </is>
       </c>
       <c r="E986" t="n">
-        <v>3933.501</v>
+        <v>3748.862</v>
       </c>
       <c r="F986" t="n">
         <v>16.434</v>
@@ -36544,7 +36544,7 @@
         <v>8.7</v>
       </c>
       <c r="H986" t="n">
-        <v>3933.501</v>
+        <v>3748.862</v>
       </c>
       <c r="I986" t="n">
         <v>0.0</v>
@@ -36609,7 +36609,7 @@
         </is>
       </c>
       <c r="E988" t="n">
-        <v>1403.952</v>
+        <v>1370.28</v>
       </c>
       <c r="F988" t="n">
         <v>0.0</v>
@@ -36618,7 +36618,7 @@
         <v>0.0</v>
       </c>
       <c r="H988" t="n">
-        <v>1403.952</v>
+        <v>1370.28</v>
       </c>
       <c r="I988" t="n">
         <v>0.0</v>
@@ -37460,7 +37460,7 @@
         </is>
       </c>
       <c r="E1011" t="n">
-        <v>1032.517</v>
+        <v>13.61</v>
       </c>
       <c r="F1011" t="n">
         <v>0.0</v>
@@ -37469,7 +37469,7 @@
         <v>53.253</v>
       </c>
       <c r="H1011" t="n">
-        <v>1032.517</v>
+        <v>13.61</v>
       </c>
       <c r="I1011" t="n">
         <v>0.0</v>
@@ -37534,7 +37534,7 @@
         </is>
       </c>
       <c r="E1013" t="n">
-        <v>10932.84</v>
+        <v>8509.828</v>
       </c>
       <c r="F1013" t="n">
         <v>0.0</v>
@@ -37543,7 +37543,7 @@
         <v>0.0</v>
       </c>
       <c r="H1013" t="n">
-        <v>10932.84</v>
+        <v>8509.828</v>
       </c>
       <c r="I1013" t="n">
         <v>0.0</v>
@@ -37830,7 +37830,7 @@
         </is>
       </c>
       <c r="E1021" t="n">
-        <v>1344.168</v>
+        <v>1324.966</v>
       </c>
       <c r="F1021" t="n">
         <v>0.0</v>
@@ -37839,7 +37839,7 @@
         <v>0.0</v>
       </c>
       <c r="H1021" t="n">
-        <v>1344.168</v>
+        <v>1324.966</v>
       </c>
       <c r="I1021" t="n">
         <v>0.0</v>
@@ -38052,7 +38052,7 @@
         </is>
       </c>
       <c r="E1027" t="n">
-        <v>4745.8369999999995</v>
+        <v>4681.840999999999</v>
       </c>
       <c r="F1027" t="n">
         <v>0.0</v>
@@ -38061,7 +38061,7 @@
         <v>0.0</v>
       </c>
       <c r="H1027" t="n">
-        <v>4745.8369999999995</v>
+        <v>4681.840999999999</v>
       </c>
       <c r="I1027" t="n">
         <v>0.0</v>
@@ -38089,7 +38089,7 @@
         </is>
       </c>
       <c r="E1028" t="n">
-        <v>4816.602</v>
+        <v>4704.588</v>
       </c>
       <c r="F1028" t="n">
         <v>0.8</v>
@@ -38098,7 +38098,7 @@
         <v>800.1</v>
       </c>
       <c r="H1028" t="n">
-        <v>4816.602</v>
+        <v>4704.588</v>
       </c>
       <c r="I1028" t="n">
         <v>0.0</v>
@@ -38200,7 +38200,7 @@
         </is>
       </c>
       <c r="E1031" t="n">
-        <v>7360.54</v>
+        <v>7127.552</v>
       </c>
       <c r="F1031" t="n">
         <v>0.0</v>
@@ -38209,7 +38209,7 @@
         <v>3.7279999999999998</v>
       </c>
       <c r="H1031" t="n">
-        <v>7360.54</v>
+        <v>7127.552</v>
       </c>
       <c r="I1031" t="n">
         <v>0.0</v>
@@ -38274,7 +38274,7 @@
         </is>
       </c>
       <c r="E1033" t="n">
-        <v>6714.612</v>
+        <v>6666.093</v>
       </c>
       <c r="F1033" t="n">
         <v>1.183</v>
@@ -38283,7 +38283,7 @@
         <v>3.846</v>
       </c>
       <c r="H1033" t="n">
-        <v>6714.612</v>
+        <v>6666.093</v>
       </c>
       <c r="I1033" t="n">
         <v>0.0</v>
@@ -38755,7 +38755,7 @@
         </is>
       </c>
       <c r="E1046" t="n">
-        <v>27.359</v>
+        <v>23.964</v>
       </c>
       <c r="F1046" t="n">
         <v>0.0</v>
@@ -38764,7 +38764,7 @@
         <v>694.956</v>
       </c>
       <c r="H1046" t="n">
-        <v>27.359</v>
+        <v>23.964</v>
       </c>
       <c r="I1046" t="n">
         <v>0.0</v>
@@ -38792,7 +38792,7 @@
         </is>
       </c>
       <c r="E1047" t="n">
-        <v>576.925</v>
+        <v>528.464</v>
       </c>
       <c r="F1047" t="n">
         <v>0.0</v>
@@ -38801,7 +38801,7 @@
         <v>23.077</v>
       </c>
       <c r="H1047" t="n">
-        <v>576.925</v>
+        <v>528.464</v>
       </c>
       <c r="I1047" t="n">
         <v>0.0</v>
@@ -39088,7 +39088,7 @@
         </is>
       </c>
       <c r="E1055" t="n">
-        <v>1302.186</v>
+        <v>1285.384</v>
       </c>
       <c r="F1055" t="n">
         <v>0.0</v>
@@ -39097,7 +39097,7 @@
         <v>0.0</v>
       </c>
       <c r="H1055" t="n">
-        <v>1302.186</v>
+        <v>1285.384</v>
       </c>
       <c r="I1055" t="n">
         <v>0.0</v>
@@ -39125,7 +39125,7 @@
         </is>
       </c>
       <c r="E1056" t="n">
-        <v>2095.161</v>
+        <v>2073.17</v>
       </c>
       <c r="F1056" t="n">
         <v>0.0</v>
@@ -39134,7 +39134,7 @@
         <v>75.97</v>
       </c>
       <c r="H1056" t="n">
-        <v>2095.161</v>
+        <v>2073.17</v>
       </c>
       <c r="I1056" t="n">
         <v>0.0</v>
@@ -39162,7 +39162,7 @@
         </is>
       </c>
       <c r="E1057" t="n">
-        <v>6477.177</v>
+        <v>6338.4</v>
       </c>
       <c r="F1057" t="n">
         <v>0.0</v>
@@ -39171,7 +39171,7 @@
         <v>0.0</v>
       </c>
       <c r="H1057" t="n">
-        <v>6477.177</v>
+        <v>6338.4</v>
       </c>
       <c r="I1057" t="n">
         <v>0.0</v>
@@ -39310,7 +39310,7 @@
         </is>
       </c>
       <c r="E1061" t="n">
-        <v>3633.624</v>
+        <v>3600.288</v>
       </c>
       <c r="F1061" t="n">
         <v>0.0</v>
@@ -39319,7 +39319,7 @@
         <v>0.0</v>
       </c>
       <c r="H1061" t="n">
-        <v>3633.624</v>
+        <v>3600.288</v>
       </c>
       <c r="I1061" t="n">
         <v>0.0</v>
@@ -39347,7 +39347,7 @@
         </is>
       </c>
       <c r="E1062" t="n">
-        <v>4426.843</v>
+        <v>4421.991999999999</v>
       </c>
       <c r="F1062" t="n">
         <v>3.639</v>
@@ -39356,7 +39356,7 @@
         <v>0.0</v>
       </c>
       <c r="H1062" t="n">
-        <v>4426.843</v>
+        <v>4421.991999999999</v>
       </c>
       <c r="I1062" t="n">
         <v>0.0</v>
@@ -39384,7 +39384,7 @@
         </is>
       </c>
       <c r="E1063" t="n">
-        <v>7020.237999999999</v>
+        <v>6990.518999999999</v>
       </c>
       <c r="F1063" t="n">
         <v>4.852</v>
@@ -39393,7 +39393,7 @@
         <v>36.39</v>
       </c>
       <c r="H1063" t="n">
-        <v>7020.237999999999</v>
+        <v>6990.518999999999</v>
       </c>
       <c r="I1063" t="n">
         <v>0.0</v>
@@ -39421,7 +39421,7 @@
         </is>
       </c>
       <c r="E1064" t="n">
-        <v>3513.045</v>
+        <v>3480.316</v>
       </c>
       <c r="F1064" t="n">
         <v>0.0</v>
@@ -39430,7 +39430,7 @@
         <v>47.608</v>
       </c>
       <c r="H1064" t="n">
-        <v>3513.045</v>
+        <v>3480.316</v>
       </c>
       <c r="I1064" t="n">
         <v>0.0</v>
@@ -39458,7 +39458,7 @@
         </is>
       </c>
       <c r="E1065" t="n">
-        <v>8253.637999999999</v>
+        <v>7676.396</v>
       </c>
       <c r="F1065" t="n">
         <v>0.6589999999999999</v>
@@ -39467,7 +39467,7 @@
         <v>15.869000000000002</v>
       </c>
       <c r="H1065" t="n">
-        <v>8253.637999999999</v>
+        <v>7676.396</v>
       </c>
       <c r="I1065" t="n">
         <v>0.0</v>
@@ -39495,7 +39495,7 @@
         </is>
       </c>
       <c r="E1066" t="n">
-        <v>4197.0740000000005</v>
+        <v>4173.27</v>
       </c>
       <c r="F1066" t="n">
         <v>0.0</v>
@@ -39504,7 +39504,7 @@
         <v>0.0</v>
       </c>
       <c r="H1066" t="n">
-        <v>4197.0740000000005</v>
+        <v>4173.27</v>
       </c>
       <c r="I1066" t="n">
         <v>0.0</v>
@@ -39532,7 +39532,7 @@
         </is>
       </c>
       <c r="E1067" t="n">
-        <v>17899.466</v>
+        <v>17742.756</v>
       </c>
       <c r="F1067" t="n">
         <v>3.634</v>
@@ -39541,7 +39541,7 @@
         <v>0.0</v>
       </c>
       <c r="H1067" t="n">
-        <v>17899.466</v>
+        <v>17742.756</v>
       </c>
       <c r="I1067" t="n">
         <v>0.0</v>
@@ -39606,7 +39606,7 @@
         </is>
       </c>
       <c r="E1069" t="n">
-        <v>9253.723</v>
+        <v>9108.92</v>
       </c>
       <c r="F1069" t="n">
         <v>0.32899999999999996</v>
@@ -39615,7 +39615,7 @@
         <v>3.967</v>
       </c>
       <c r="H1069" t="n">
-        <v>9253.723</v>
+        <v>9108.92</v>
       </c>
       <c r="I1069" t="n">
         <v>0.0</v>
@@ -39680,7 +39680,7 @@
         </is>
       </c>
       <c r="E1071" t="n">
-        <v>5939.39</v>
+        <v>5869.961</v>
       </c>
       <c r="F1071" t="n">
         <v>0.6589999999999999</v>
@@ -39689,7 +39689,7 @@
         <v>11.902</v>
       </c>
       <c r="H1071" t="n">
-        <v>5939.39</v>
+        <v>5869.961</v>
       </c>
       <c r="I1071" t="n">
         <v>0.0</v>
@@ -39791,7 +39791,7 @@
         </is>
       </c>
       <c r="E1074" t="n">
-        <v>29447.285</v>
+        <v>28944.1</v>
       </c>
       <c r="F1074" t="n">
         <v>2.972</v>
@@ -39800,7 +39800,7 @@
         <v>3.967</v>
       </c>
       <c r="H1074" t="n">
-        <v>29447.285</v>
+        <v>28944.1</v>
       </c>
       <c r="I1074" t="n">
         <v>0.0</v>
@@ -39828,7 +39828,7 @@
         </is>
       </c>
       <c r="E1075" t="n">
-        <v>20445.809</v>
+        <v>20253.060999999998</v>
       </c>
       <c r="F1075" t="n">
         <v>1.984</v>
@@ -39837,7 +39837,7 @@
         <v>0.0</v>
       </c>
       <c r="H1075" t="n">
-        <v>20445.809</v>
+        <v>20253.060999999998</v>
       </c>
       <c r="I1075" t="n">
         <v>0.0</v>
@@ -39976,7 +39976,7 @@
         </is>
       </c>
       <c r="E1079" t="n">
-        <v>587.917</v>
+        <v>564.443</v>
       </c>
       <c r="F1079" t="n">
         <v>1.067</v>
@@ -39985,7 +39985,7 @@
         <v>0.0</v>
       </c>
       <c r="H1079" t="n">
-        <v>587.917</v>
+        <v>564.443</v>
       </c>
       <c r="I1079" t="n">
         <v>0.0</v>
@@ -40050,7 +40050,7 @@
         </is>
       </c>
       <c r="E1081" t="n">
-        <v>2499.34</v>
+        <v>3260.859</v>
       </c>
       <c r="F1081" t="n">
         <v>484.602</v>
@@ -40059,7 +40059,7 @@
         <v>0.0</v>
       </c>
       <c r="H1081" t="n">
-        <v>2499.34</v>
+        <v>3260.859</v>
       </c>
       <c r="I1081" t="n">
         <v>0.0</v>
@@ -40309,7 +40309,7 @@
         </is>
       </c>
       <c r="E1088" t="n">
-        <v>1817.273</v>
+        <v>3658.5362</v>
       </c>
       <c r="F1088" t="n">
         <v>0.0</v>
@@ -40321,7 +40321,7 @@
         <v>1817.273</v>
       </c>
       <c r="I1088" t="n">
-        <v>0.0</v>
+        <v>1841.2632</v>
       </c>
     </row>
     <row r="1089">
@@ -40346,7 +40346,7 @@
         </is>
       </c>
       <c r="E1089" t="n">
-        <v>1164.232</v>
+        <v>560.111</v>
       </c>
       <c r="F1089" t="n">
         <v>0.0</v>
@@ -40355,10 +40355,10 @@
         <v>0.0</v>
       </c>
       <c r="H1089" t="n">
-        <v>564.112</v>
+        <v>560.111</v>
       </c>
       <c r="I1089" t="n">
-        <v>600.12</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1090">
@@ -40383,7 +40383,7 @@
         </is>
       </c>
       <c r="E1090" t="n">
-        <v>109.322</v>
+        <v>103.989</v>
       </c>
       <c r="F1090" t="n">
         <v>0.0</v>
@@ -40392,7 +40392,7 @@
         <v>0.0</v>
       </c>
       <c r="H1090" t="n">
-        <v>109.322</v>
+        <v>103.989</v>
       </c>
       <c r="I1090" t="n">
         <v>0.0</v>
@@ -40457,7 +40457,7 @@
         </is>
       </c>
       <c r="E1092" t="n">
-        <v>2636.945</v>
+        <v>2634.946</v>
       </c>
       <c r="F1092" t="n">
         <v>0.0</v>
@@ -40466,7 +40466,7 @@
         <v>0.0</v>
       </c>
       <c r="H1092" t="n">
-        <v>2636.945</v>
+        <v>2634.946</v>
       </c>
       <c r="I1092" t="n">
         <v>0.0</v>
@@ -40531,7 +40531,7 @@
         </is>
       </c>
       <c r="E1094" t="n">
-        <v>6753.35</v>
+        <v>9185.8362</v>
       </c>
       <c r="F1094" t="n">
         <v>0.0</v>
@@ -40540,10 +40540,10 @@
         <v>0.0</v>
       </c>
       <c r="H1094" t="n">
-        <v>6753.35</v>
+        <v>6749.349</v>
       </c>
       <c r="I1094" t="n">
-        <v>0.0</v>
+        <v>2436.4872</v>
       </c>
     </row>
     <row r="1095">
@@ -40716,7 +40716,7 @@
         </is>
       </c>
       <c r="E1099" t="n">
-        <v>509.602</v>
+        <v>509.603</v>
       </c>
       <c r="F1099" t="n">
         <v>0.0</v>
@@ -40725,7 +40725,7 @@
         <v>0.0</v>
       </c>
       <c r="H1099" t="n">
-        <v>509.602</v>
+        <v>509.603</v>
       </c>
       <c r="I1099" t="n">
         <v>0.0</v>
@@ -40790,7 +40790,7 @@
         </is>
       </c>
       <c r="E1101" t="n">
-        <v>153.375</v>
+        <v>76.687</v>
       </c>
       <c r="F1101" t="n">
         <v>0.0</v>
@@ -40799,7 +40799,7 @@
         <v>2.474</v>
       </c>
       <c r="H1101" t="n">
-        <v>153.375</v>
+        <v>76.687</v>
       </c>
       <c r="I1101" t="n">
         <v>0.0</v>
@@ -41382,7 +41382,7 @@
         </is>
       </c>
       <c r="E1117" t="n">
-        <v>2517.2114</v>
+        <v>2022.225</v>
       </c>
       <c r="F1117" t="n">
         <v>0.0</v>
@@ -41391,10 +41391,10 @@
         <v>0.0</v>
       </c>
       <c r="H1117" t="n">
-        <v>2026.809</v>
+        <v>2022.225</v>
       </c>
       <c r="I1117" t="n">
-        <v>490.4024</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1118">
@@ -41419,7 +41419,7 @@
         </is>
       </c>
       <c r="E1118" t="n">
-        <v>2515.324</v>
+        <v>2106.34</v>
       </c>
       <c r="F1118" t="n">
         <v>0.09000000000000001</v>
@@ -41428,10 +41428,10 @@
         <v>0.0</v>
       </c>
       <c r="H1118" t="n">
-        <v>2110.924</v>
+        <v>2106.34</v>
       </c>
       <c r="I1118" t="n">
-        <v>404.4</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1119">
@@ -41493,7 +41493,7 @@
         </is>
       </c>
       <c r="E1120" t="n">
-        <v>356.85400000000004</v>
+        <v>128.876</v>
       </c>
       <c r="F1120" t="n">
         <v>0.20900000000000002</v>
@@ -41502,7 +41502,7 @@
         <v>0.0</v>
       </c>
       <c r="H1120" t="n">
-        <v>356.85400000000004</v>
+        <v>128.876</v>
       </c>
       <c r="I1120" t="n">
         <v>0.0</v>
@@ -41530,7 +41530,7 @@
         </is>
       </c>
       <c r="E1121" t="n">
-        <v>2843.766</v>
+        <v>2838.191</v>
       </c>
       <c r="F1121" t="n">
         <v>0.42000000000000004</v>
@@ -41539,7 +41539,7 @@
         <v>0.0</v>
       </c>
       <c r="H1121" t="n">
-        <v>2843.766</v>
+        <v>2838.191</v>
       </c>
       <c r="I1121" t="n">
         <v>0.0</v>
@@ -41604,7 +41604,7 @@
         </is>
       </c>
       <c r="E1123" t="n">
-        <v>665.826</v>
+        <v>603.1590000000001</v>
       </c>
       <c r="F1123" t="n">
         <v>0.416</v>
@@ -41613,7 +41613,7 @@
         <v>0.0</v>
       </c>
       <c r="H1123" t="n">
-        <v>665.826</v>
+        <v>603.1590000000001</v>
       </c>
       <c r="I1123" t="n">
         <v>0.0</v>
@@ -41678,7 +41678,7 @@
         </is>
       </c>
       <c r="E1125" t="n">
-        <v>6556.595</v>
+        <v>6459.785</v>
       </c>
       <c r="F1125" t="n">
         <v>0.0</v>
@@ -41687,7 +41687,7 @@
         <v>0.0</v>
       </c>
       <c r="H1125" t="n">
-        <v>6556.595</v>
+        <v>6459.785</v>
       </c>
       <c r="I1125" t="n">
         <v>0.0</v>
@@ -41715,7 +41715,7 @@
         </is>
       </c>
       <c r="E1126" t="n">
-        <v>2116.954</v>
+        <v>2077.751</v>
       </c>
       <c r="F1126" t="n">
         <v>0.0</v>
@@ -41724,7 +41724,7 @@
         <v>0.0</v>
       </c>
       <c r="H1126" t="n">
-        <v>2116.954</v>
+        <v>2077.751</v>
       </c>
       <c r="I1126" t="n">
         <v>0.0</v>
@@ -41752,7 +41752,7 @@
         </is>
       </c>
       <c r="E1127" t="n">
-        <v>4197.409</v>
+        <v>4188.609</v>
       </c>
       <c r="F1127" t="n">
         <v>0.0</v>
@@ -41761,7 +41761,7 @@
         <v>0.0</v>
       </c>
       <c r="H1127" t="n">
-        <v>4197.409</v>
+        <v>4188.609</v>
       </c>
       <c r="I1127" t="n">
         <v>0.0</v>
@@ -41826,7 +41826,7 @@
         </is>
       </c>
       <c r="E1129" t="n">
-        <v>22719.2</v>
+        <v>22668.0</v>
       </c>
       <c r="F1129" t="n">
         <v>6.4</v>
@@ -41835,7 +41835,7 @@
         <v>0.0</v>
       </c>
       <c r="H1129" t="n">
-        <v>22719.2</v>
+        <v>22668.0</v>
       </c>
       <c r="I1129" t="n">
         <v>0.0</v>
@@ -41863,7 +41863,7 @@
         </is>
       </c>
       <c r="E1130" t="n">
-        <v>1592.728</v>
+        <v>1513.532</v>
       </c>
       <c r="F1130" t="n">
         <v>0.0</v>
@@ -41872,7 +41872,7 @@
         <v>17.599</v>
       </c>
       <c r="H1130" t="n">
-        <v>1592.728</v>
+        <v>1513.532</v>
       </c>
       <c r="I1130" t="n">
         <v>0.0</v>
@@ -41900,7 +41900,7 @@
         </is>
       </c>
       <c r="E1131" t="n">
-        <v>2137.708</v>
+        <v>1485.186</v>
       </c>
       <c r="F1131" t="n">
         <v>0.0</v>
@@ -41909,10 +41909,10 @@
         <v>8.005999999999998</v>
       </c>
       <c r="H1131" t="n">
-        <v>1487.188</v>
+        <v>1485.186</v>
       </c>
       <c r="I1131" t="n">
-        <v>650.52</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1132">
@@ -41937,7 +41937,7 @@
         </is>
       </c>
       <c r="E1132" t="n">
-        <v>1519.2142</v>
+        <v>1363.0892</v>
       </c>
       <c r="F1132" t="n">
         <v>0.0</v>
@@ -41946,10 +41946,10 @@
         <v>0.0</v>
       </c>
       <c r="H1132" t="n">
-        <v>974.779</v>
+        <v>968.774</v>
       </c>
       <c r="I1132" t="n">
-        <v>544.4352</v>
+        <v>394.3152</v>
       </c>
     </row>
     <row r="1133">
@@ -41974,7 +41974,7 @@
         </is>
       </c>
       <c r="E1133" t="n">
-        <v>1653.322</v>
+        <v>1599.279</v>
       </c>
       <c r="F1133" t="n">
         <v>0.0</v>
@@ -41983,7 +41983,7 @@
         <v>0.0</v>
       </c>
       <c r="H1133" t="n">
-        <v>1653.322</v>
+        <v>1599.279</v>
       </c>
       <c r="I1133" t="n">
         <v>0.0</v>
@@ -42344,7 +42344,7 @@
         </is>
       </c>
       <c r="E1143" t="n">
-        <v>1476.299</v>
+        <v>1475.832</v>
       </c>
       <c r="F1143" t="n">
         <v>0.0</v>
@@ -42353,7 +42353,7 @@
         <v>0.0</v>
       </c>
       <c r="H1143" t="n">
-        <v>1476.299</v>
+        <v>1475.832</v>
       </c>
       <c r="I1143" t="n">
         <v>0.0</v>
@@ -42381,7 +42381,7 @@
         </is>
       </c>
       <c r="E1144" t="n">
-        <v>4218.1720000000005</v>
+        <v>4149.715</v>
       </c>
       <c r="F1144" t="n">
         <v>0.428</v>
@@ -42390,7 +42390,7 @@
         <v>0.0</v>
       </c>
       <c r="H1144" t="n">
-        <v>4218.1720000000005</v>
+        <v>4149.715</v>
       </c>
       <c r="I1144" t="n">
         <v>0.0</v>
@@ -42418,7 +42418,7 @@
         </is>
       </c>
       <c r="E1145" t="n">
-        <v>2103.737</v>
+        <v>1791.835</v>
       </c>
       <c r="F1145" t="n">
         <v>0.428</v>
@@ -42427,7 +42427,7 @@
         <v>0.0</v>
       </c>
       <c r="H1145" t="n">
-        <v>2103.737</v>
+        <v>1791.835</v>
       </c>
       <c r="I1145" t="n">
         <v>0.0</v>
@@ -42455,7 +42455,7 @@
         </is>
       </c>
       <c r="E1146" t="n">
-        <v>3056.279</v>
+        <v>3035.7419999999997</v>
       </c>
       <c r="F1146" t="n">
         <v>0.0</v>
@@ -42464,7 +42464,7 @@
         <v>0.0</v>
       </c>
       <c r="H1146" t="n">
-        <v>3056.279</v>
+        <v>3035.7419999999997</v>
       </c>
       <c r="I1146" t="n">
         <v>0.0</v>
@@ -42529,7 +42529,7 @@
         </is>
       </c>
       <c r="E1148" t="n">
-        <v>2879.8590000000004</v>
+        <v>2784.018</v>
       </c>
       <c r="F1148" t="n">
         <v>10.265</v>
@@ -42538,7 +42538,7 @@
         <v>0.0</v>
       </c>
       <c r="H1148" t="n">
-        <v>2879.8590000000004</v>
+        <v>2784.018</v>
       </c>
       <c r="I1148" t="n">
         <v>0.0</v>
@@ -42566,7 +42566,7 @@
         </is>
       </c>
       <c r="E1149" t="n">
-        <v>318.587</v>
+        <v>315.921</v>
       </c>
       <c r="F1149" t="n">
         <v>0.0</v>
@@ -42575,7 +42575,7 @@
         <v>1.333</v>
       </c>
       <c r="H1149" t="n">
-        <v>318.587</v>
+        <v>315.921</v>
       </c>
       <c r="I1149" t="n">
         <v>0.0</v>
@@ -42603,7 +42603,7 @@
         </is>
       </c>
       <c r="E1150" t="n">
-        <v>67.983</v>
+        <v>66.65</v>
       </c>
       <c r="F1150" t="n">
         <v>0.0</v>
@@ -42612,7 +42612,7 @@
         <v>0.0</v>
       </c>
       <c r="H1150" t="n">
-        <v>67.983</v>
+        <v>66.65</v>
       </c>
       <c r="I1150" t="n">
         <v>0.0</v>
@@ -42640,7 +42640,7 @@
         </is>
       </c>
       <c r="E1151" t="n">
-        <v>9849.349</v>
+        <v>9933.347000000002</v>
       </c>
       <c r="F1151" t="n">
         <v>39.898999999999994</v>
@@ -42649,7 +42649,7 @@
         <v>13.766</v>
       </c>
       <c r="H1151" t="n">
-        <v>9849.349</v>
+        <v>9933.347000000002</v>
       </c>
       <c r="I1151" t="n">
         <v>0.0</v>
@@ -42677,7 +42677,7 @@
         </is>
       </c>
       <c r="E1152" t="n">
-        <v>433.225</v>
+        <v>430.559</v>
       </c>
       <c r="F1152" t="n">
         <v>0.0</v>
@@ -42686,7 +42686,7 @@
         <v>1.333</v>
       </c>
       <c r="H1152" t="n">
-        <v>433.225</v>
+        <v>430.559</v>
       </c>
       <c r="I1152" t="n">
         <v>0.0</v>
@@ -42714,7 +42714,7 @@
         </is>
       </c>
       <c r="E1153" t="n">
-        <v>8595.678</v>
+        <v>8662.122</v>
       </c>
       <c r="F1153" t="n">
         <v>27.599</v>
@@ -42723,7 +42723,7 @@
         <v>7.155</v>
       </c>
       <c r="H1153" t="n">
-        <v>8595.678</v>
+        <v>8662.122</v>
       </c>
       <c r="I1153" t="n">
         <v>0.0</v>
@@ -42751,7 +42751,7 @@
         </is>
       </c>
       <c r="E1154" t="n">
-        <v>14540.56</v>
+        <v>13727.863</v>
       </c>
       <c r="F1154" t="n">
         <v>20.001</v>
@@ -42760,7 +42760,7 @@
         <v>2994.8160000000003</v>
       </c>
       <c r="H1154" t="n">
-        <v>14540.56</v>
+        <v>13727.863</v>
       </c>
       <c r="I1154" t="n">
         <v>0.0</v>
@@ -42788,7 +42788,7 @@
         </is>
       </c>
       <c r="E1155" t="n">
-        <v>20979.600000000002</v>
+        <v>18863.6</v>
       </c>
       <c r="F1155" t="n">
         <v>48.0</v>
@@ -42797,7 +42797,7 @@
         <v>16.8</v>
       </c>
       <c r="H1155" t="n">
-        <v>20979.600000000002</v>
+        <v>18863.6</v>
       </c>
       <c r="I1155" t="n">
         <v>0.0</v>
@@ -42862,7 +42862,7 @@
         </is>
       </c>
       <c r="E1157" t="n">
-        <v>4626.911</v>
+        <v>4588.513</v>
       </c>
       <c r="F1157" t="n">
         <v>8.0</v>
@@ -42871,7 +42871,7 @@
         <v>0.0</v>
       </c>
       <c r="H1157" t="n">
-        <v>4626.911</v>
+        <v>4588.513</v>
       </c>
       <c r="I1157" t="n">
         <v>0.0</v>
@@ -42899,7 +42899,7 @@
         </is>
       </c>
       <c r="E1158" t="n">
-        <v>3960.0</v>
+        <v>3955.2</v>
       </c>
       <c r="F1158" t="n">
         <v>0.0</v>
@@ -42908,7 +42908,7 @@
         <v>0.0</v>
       </c>
       <c r="H1158" t="n">
-        <v>3960.0</v>
+        <v>3955.2</v>
       </c>
       <c r="I1158" t="n">
         <v>0.0</v>
@@ -42936,7 +42936,7 @@
         </is>
       </c>
       <c r="E1159" t="n">
-        <v>1416.0</v>
+        <v>1358.4</v>
       </c>
       <c r="F1159" t="n">
         <v>0.4</v>
@@ -42945,7 +42945,7 @@
         <v>0.0</v>
       </c>
       <c r="H1159" t="n">
-        <v>1416.0</v>
+        <v>1358.4</v>
       </c>
       <c r="I1159" t="n">
         <v>0.0</v>
@@ -43158,7 +43158,7 @@
         </is>
       </c>
       <c r="E1165" t="n">
-        <v>7044.0</v>
+        <v>6933.6</v>
       </c>
       <c r="F1165" t="n">
         <v>0.0</v>
@@ -43167,7 +43167,7 @@
         <v>4.0</v>
       </c>
       <c r="H1165" t="n">
-        <v>7044.0</v>
+        <v>6933.6</v>
       </c>
       <c r="I1165" t="n">
         <v>0.0</v>
@@ -43195,7 +43195,7 @@
         </is>
       </c>
       <c r="E1166" t="n">
-        <v>7149.487999999999</v>
+        <v>7334.7970000000005</v>
       </c>
       <c r="F1166" t="n">
         <v>0.0</v>
@@ -43204,7 +43204,7 @@
         <v>5.1000000000000005</v>
       </c>
       <c r="H1166" t="n">
-        <v>7149.487999999999</v>
+        <v>7334.7970000000005</v>
       </c>
       <c r="I1166" t="n">
         <v>0.0</v>
@@ -43232,7 +43232,7 @@
         </is>
       </c>
       <c r="E1167" t="n">
-        <v>12634.296</v>
+        <v>12339.617</v>
       </c>
       <c r="F1167" t="n">
         <v>0.0</v>
@@ -43241,7 +43241,7 @@
         <v>20.668</v>
       </c>
       <c r="H1167" t="n">
-        <v>12634.296</v>
+        <v>12339.617</v>
       </c>
       <c r="I1167" t="n">
         <v>0.0</v>
@@ -43269,7 +43269,7 @@
         </is>
       </c>
       <c r="E1168" t="n">
-        <v>1315.2</v>
+        <v>1123.2</v>
       </c>
       <c r="F1168" t="n">
         <v>0.0</v>
@@ -43278,7 +43278,7 @@
         <v>0.0</v>
       </c>
       <c r="H1168" t="n">
-        <v>1315.2</v>
+        <v>1123.2</v>
       </c>
       <c r="I1168" t="n">
         <v>0.0</v>
@@ -43417,7 +43417,7 @@
         </is>
       </c>
       <c r="E1172" t="n">
-        <v>7675.2</v>
+        <v>7688.0</v>
       </c>
       <c r="F1172" t="n">
         <v>0.6</v>
@@ -43426,7 +43426,7 @@
         <v>339.2</v>
       </c>
       <c r="H1172" t="n">
-        <v>7675.2</v>
+        <v>7688.0</v>
       </c>
       <c r="I1172" t="n">
         <v>0.0</v>
@@ -43750,7 +43750,7 @@
         </is>
       </c>
       <c r="E1181" t="n">
-        <v>2020.8</v>
+        <v>2020.6</v>
       </c>
       <c r="F1181" t="n">
         <v>0.0</v>
@@ -43759,7 +43759,7 @@
         <v>4.8</v>
       </c>
       <c r="H1181" t="n">
-        <v>2020.8</v>
+        <v>2020.6</v>
       </c>
       <c r="I1181" t="n">
         <v>0.0</v>
@@ -43787,7 +43787,7 @@
         </is>
       </c>
       <c r="E1182" t="n">
-        <v>2238.8</v>
+        <v>2233.6</v>
       </c>
       <c r="F1182" t="n">
         <v>0.4</v>
@@ -43796,7 +43796,7 @@
         <v>0.0</v>
       </c>
       <c r="H1182" t="n">
-        <v>2238.8</v>
+        <v>2233.6</v>
       </c>
       <c r="I1182" t="n">
         <v>0.0</v>
@@ -43861,7 +43861,7 @@
         </is>
       </c>
       <c r="E1184" t="n">
-        <v>2917.2</v>
+        <v>2902.3999999999996</v>
       </c>
       <c r="F1184" t="n">
         <v>8.4</v>
@@ -43870,7 +43870,7 @@
         <v>0.0</v>
       </c>
       <c r="H1184" t="n">
-        <v>2917.2</v>
+        <v>2902.3999999999996</v>
       </c>
       <c r="I1184" t="n">
         <v>0.0</v>
@@ -43898,7 +43898,7 @@
         </is>
       </c>
       <c r="E1185" t="n">
-        <v>2454.705</v>
+        <v>2422.702</v>
       </c>
       <c r="F1185" t="n">
         <v>0.26699999999999996</v>
@@ -43907,7 +43907,7 @@
         <v>3.2</v>
       </c>
       <c r="H1185" t="n">
-        <v>2454.705</v>
+        <v>2422.702</v>
       </c>
       <c r="I1185" t="n">
         <v>0.0</v>
@@ -43935,7 +43935,7 @@
         </is>
       </c>
       <c r="E1186" t="n">
-        <v>2054.4</v>
+        <v>2030.4</v>
       </c>
       <c r="F1186" t="n">
         <v>0.0</v>
@@ -43944,7 +43944,7 @@
         <v>0.0</v>
       </c>
       <c r="H1186" t="n">
-        <v>2054.4</v>
+        <v>2030.4</v>
       </c>
       <c r="I1186" t="n">
         <v>0.0</v>
@@ -44046,7 +44046,7 @@
         </is>
       </c>
       <c r="E1189" t="n">
-        <v>1769.6000000000001</v>
+        <v>1763.6000000000001</v>
       </c>
       <c r="F1189" t="n">
         <v>2.8</v>
@@ -44055,7 +44055,7 @@
         <v>0.8</v>
       </c>
       <c r="H1189" t="n">
-        <v>1769.6000000000001</v>
+        <v>1763.6000000000001</v>
       </c>
       <c r="I1189" t="n">
         <v>0.0</v>
@@ -44120,7 +44120,7 @@
         </is>
       </c>
       <c r="E1191" t="n">
-        <v>1272.127</v>
+        <v>876.087</v>
       </c>
       <c r="F1191" t="n">
         <v>0.0</v>
@@ -44129,7 +44129,7 @@
         <v>708.071</v>
       </c>
       <c r="H1191" t="n">
-        <v>1272.127</v>
+        <v>876.087</v>
       </c>
       <c r="I1191" t="n">
         <v>0.0</v>
@@ -44527,7 +44527,7 @@
         </is>
       </c>
       <c r="E1202" t="n">
-        <v>5134.758400000001</v>
+        <v>4378.799</v>
       </c>
       <c r="F1202" t="n">
         <v>0.0</v>
@@ -44536,10 +44536,10 @@
         <v>0.0</v>
       </c>
       <c r="H1202" t="n">
-        <v>4399.02</v>
+        <v>4378.799</v>
       </c>
       <c r="I1202" t="n">
-        <v>735.7384</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1203">
@@ -44934,7 +44934,7 @@
         </is>
       </c>
       <c r="E1213" t="n">
-        <v>2863.933</v>
+        <v>2671.505</v>
       </c>
       <c r="F1213" t="n">
         <v>0.0</v>
@@ -44943,7 +44943,7 @@
         <v>636.93</v>
       </c>
       <c r="H1213" t="n">
-        <v>2863.933</v>
+        <v>2671.505</v>
       </c>
       <c r="I1213" t="n">
         <v>0.0</v>
@@ -44971,7 +44971,7 @@
         </is>
       </c>
       <c r="E1214" t="n">
-        <v>401.19100000000003</v>
+        <v>166.87</v>
       </c>
       <c r="F1214" t="n">
         <v>0.0</v>
@@ -44980,7 +44980,7 @@
         <v>4.26</v>
       </c>
       <c r="H1214" t="n">
-        <v>401.19100000000003</v>
+        <v>166.87</v>
       </c>
       <c r="I1214" t="n">
         <v>0.0</v>
@@ -45378,7 +45378,7 @@
         </is>
       </c>
       <c r="E1225" t="n">
-        <v>1267.421</v>
+        <v>1217.72</v>
       </c>
       <c r="F1225" t="n">
         <v>0.0</v>
@@ -45387,7 +45387,7 @@
         <v>0.0</v>
       </c>
       <c r="H1225" t="n">
-        <v>1267.421</v>
+        <v>1217.72</v>
       </c>
       <c r="I1225" t="n">
         <v>0.0</v>
@@ -45415,7 +45415,7 @@
         </is>
       </c>
       <c r="E1226" t="n">
-        <v>2341.3590000000004</v>
+        <v>2325.3830000000003</v>
       </c>
       <c r="F1226" t="n">
         <v>0.0</v>
@@ -45424,7 +45424,7 @@
         <v>1.7750000000000001</v>
       </c>
       <c r="H1226" t="n">
-        <v>2341.3590000000004</v>
+        <v>2325.3830000000003</v>
       </c>
       <c r="I1226" t="n">
         <v>0.0</v>
@@ -45452,7 +45452,7 @@
         </is>
       </c>
       <c r="E1227" t="n">
-        <v>5418.48</v>
+        <v>5370.018</v>
       </c>
       <c r="F1227" t="n">
         <v>0.0</v>
@@ -45461,7 +45461,7 @@
         <v>0.0</v>
       </c>
       <c r="H1227" t="n">
-        <v>5418.48</v>
+        <v>5370.018</v>
       </c>
       <c r="I1227" t="n">
         <v>0.0</v>
@@ -45526,7 +45526,7 @@
         </is>
       </c>
       <c r="E1229" t="n">
-        <v>3818.264</v>
+        <v>3478.774</v>
       </c>
       <c r="F1229" t="n">
         <v>0.0</v>
@@ -45535,7 +45535,7 @@
         <v>5.991</v>
       </c>
       <c r="H1229" t="n">
-        <v>3818.264</v>
+        <v>3478.774</v>
       </c>
       <c r="I1229" t="n">
         <v>0.0</v>
@@ -45600,7 +45600,7 @@
         </is>
       </c>
       <c r="E1231" t="n">
-        <v>3588.07</v>
+        <v>3562.035</v>
       </c>
       <c r="F1231" t="n">
         <v>0.0</v>
@@ -45609,7 +45609,7 @@
         <v>0.0</v>
       </c>
       <c r="H1231" t="n">
-        <v>3588.07</v>
+        <v>3562.035</v>
       </c>
       <c r="I1231" t="n">
         <v>0.0</v>
@@ -45785,7 +45785,7 @@
         </is>
       </c>
       <c r="E1236" t="n">
-        <v>4036.577</v>
+        <v>3802.264</v>
       </c>
       <c r="F1236" t="n">
         <v>0.0</v>
@@ -45794,7 +45794,7 @@
         <v>0.0</v>
       </c>
       <c r="H1236" t="n">
-        <v>4036.577</v>
+        <v>3802.264</v>
       </c>
       <c r="I1236" t="n">
         <v>0.0</v>
@@ -46155,7 +46155,7 @@
         </is>
       </c>
       <c r="E1246" t="n">
-        <v>2579.286</v>
+        <v>2570.185</v>
       </c>
       <c r="F1246" t="n">
         <v>0.583</v>
@@ -46164,7 +46164,7 @@
         <v>0.0</v>
       </c>
       <c r="H1246" t="n">
-        <v>2579.286</v>
+        <v>2570.185</v>
       </c>
       <c r="I1246" t="n">
         <v>0.0</v>
@@ -46192,7 +46192,7 @@
         </is>
       </c>
       <c r="E1247" t="n">
-        <v>1495.881</v>
+        <v>1491.913</v>
       </c>
       <c r="F1247" t="n">
         <v>0.35100000000000003</v>
@@ -46201,7 +46201,7 @@
         <v>0.0</v>
       </c>
       <c r="H1247" t="n">
-        <v>1495.881</v>
+        <v>1491.913</v>
       </c>
       <c r="I1247" t="n">
         <v>0.0</v>
@@ -46266,7 +46266,7 @@
         </is>
       </c>
       <c r="E1249" t="n">
-        <v>654.615</v>
+        <v>651.645</v>
       </c>
       <c r="F1249" t="n">
         <v>0.0</v>
@@ -46275,7 +46275,7 @@
         <v>0.135</v>
       </c>
       <c r="H1249" t="n">
-        <v>654.615</v>
+        <v>651.645</v>
       </c>
       <c r="I1249" t="n">
         <v>0.0</v>
@@ -46340,7 +46340,7 @@
         </is>
       </c>
       <c r="E1251" t="n">
-        <v>725.355</v>
+        <v>0.27</v>
       </c>
       <c r="F1251" t="n">
         <v>0.0</v>
@@ -46349,7 +46349,7 @@
         <v>0.135</v>
       </c>
       <c r="H1251" t="n">
-        <v>725.355</v>
+        <v>0.27</v>
       </c>
       <c r="I1251" t="n">
         <v>0.0</v>
@@ -46488,7 +46488,7 @@
         </is>
       </c>
       <c r="E1255" t="n">
-        <v>461.97</v>
+        <v>283.77</v>
       </c>
       <c r="F1255" t="n">
         <v>0.0</v>
@@ -46497,7 +46497,7 @@
         <v>0.0</v>
       </c>
       <c r="H1255" t="n">
-        <v>461.97</v>
+        <v>283.77</v>
       </c>
       <c r="I1255" t="n">
         <v>0.0</v>
@@ -47413,7 +47413,7 @@
         </is>
       </c>
       <c r="E1280" t="n">
-        <v>635.174</v>
+        <v>608.486</v>
       </c>
       <c r="F1280" t="n">
         <v>0.0</v>
@@ -47422,7 +47422,7 @@
         <v>0.0</v>
       </c>
       <c r="H1280" t="n">
-        <v>635.174</v>
+        <v>608.486</v>
       </c>
       <c r="I1280" t="n">
         <v>0.0</v>
@@ -47450,7 +47450,7 @@
         </is>
       </c>
       <c r="E1281" t="n">
-        <v>1480.8</v>
+        <v>1414.8</v>
       </c>
       <c r="F1281" t="n">
         <v>0.0</v>
@@ -47459,7 +47459,7 @@
         <v>0.0</v>
       </c>
       <c r="H1281" t="n">
-        <v>1480.8</v>
+        <v>1414.8</v>
       </c>
       <c r="I1281" t="n">
         <v>0.0</v>
@@ -47746,7 +47746,7 @@
         </is>
       </c>
       <c r="E1289" t="n">
-        <v>5435.9424</v>
+        <v>0.0</v>
       </c>
       <c r="F1289" t="n">
         <v>0.0</v>
@@ -47758,7 +47758,7 @@
         <v>0.0</v>
       </c>
       <c r="I1289" t="n">
-        <v>5435.9424</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1290">
@@ -50965,7 +50965,7 @@
         </is>
       </c>
       <c r="E1376" t="n">
-        <v>913.5</v>
+        <v>823.5</v>
       </c>
       <c r="F1376" t="n">
         <v>0.0</v>
@@ -50974,7 +50974,7 @@
         <v>90.0</v>
       </c>
       <c r="H1376" t="n">
-        <v>913.5</v>
+        <v>823.5</v>
       </c>
       <c r="I1376" t="n">
         <v>0.0</v>
@@ -51298,7 +51298,7 @@
         </is>
       </c>
       <c r="E1385" t="n">
-        <v>3285.126</v>
+        <v>3268.446</v>
       </c>
       <c r="F1385" t="n">
         <v>0.0</v>
@@ -51307,7 +51307,7 @@
         <v>236.85600000000002</v>
       </c>
       <c r="H1385" t="n">
-        <v>3285.126</v>
+        <v>3268.446</v>
       </c>
       <c r="I1385" t="n">
         <v>0.0</v>
@@ -51335,7 +51335,7 @@
         </is>
       </c>
       <c r="E1386" t="n">
-        <v>571.021</v>
+        <v>523.041</v>
       </c>
       <c r="F1386" t="n">
         <v>0.0</v>
@@ -51344,7 +51344,7 @@
         <v>0.416</v>
       </c>
       <c r="H1386" t="n">
-        <v>571.021</v>
+        <v>523.041</v>
       </c>
       <c r="I1386" t="n">
         <v>0.0</v>
@@ -51372,7 +51372,7 @@
         </is>
       </c>
       <c r="E1387" t="n">
-        <v>636.174</v>
+        <v>633.505</v>
       </c>
       <c r="F1387" t="n">
         <v>0.0</v>
@@ -51381,7 +51381,7 @@
         <v>0.5559999999999999</v>
       </c>
       <c r="H1387" t="n">
-        <v>636.174</v>
+        <v>633.505</v>
       </c>
       <c r="I1387" t="n">
         <v>0.0</v>
@@ -51483,7 +51483,7 @@
         </is>
       </c>
       <c r="E1390" t="n">
-        <v>1131.073</v>
+        <v>1094.904</v>
       </c>
       <c r="F1390" t="n">
         <v>0.0</v>
@@ -51492,7 +51492,7 @@
         <v>0.0</v>
       </c>
       <c r="H1390" t="n">
-        <v>1131.073</v>
+        <v>1094.904</v>
       </c>
       <c r="I1390" t="n">
         <v>0.0</v>
@@ -52149,7 +52149,7 @@
         </is>
       </c>
       <c r="E1408" t="n">
-        <v>1323.197</v>
+        <v>1317.859</v>
       </c>
       <c r="F1408" t="n">
         <v>0.0</v>
@@ -52158,7 +52158,7 @@
         <v>2.669</v>
       </c>
       <c r="H1408" t="n">
-        <v>1323.197</v>
+        <v>1317.859</v>
       </c>
       <c r="I1408" t="n">
         <v>0.0</v>
@@ -52186,7 +52186,7 @@
         </is>
       </c>
       <c r="E1409" t="n">
-        <v>41.144</v>
+        <v>35.224</v>
       </c>
       <c r="F1409" t="n">
         <v>0.0</v>
@@ -52195,7 +52195,7 @@
         <v>0.0</v>
       </c>
       <c r="H1409" t="n">
-        <v>41.144</v>
+        <v>35.224</v>
       </c>
       <c r="I1409" t="n">
         <v>0.0</v>
@@ -52371,7 +52371,7 @@
         </is>
       </c>
       <c r="E1414" t="n">
-        <v>904.973</v>
+        <v>902.304</v>
       </c>
       <c r="F1414" t="n">
         <v>0.0</v>
@@ -52380,7 +52380,7 @@
         <v>53.543</v>
       </c>
       <c r="H1414" t="n">
-        <v>904.973</v>
+        <v>902.304</v>
       </c>
       <c r="I1414" t="n">
         <v>0.0</v>
@@ -52926,7 +52926,7 @@
         </is>
       </c>
       <c r="E1429" t="n">
-        <v>1673.7826</v>
+        <v>915.398</v>
       </c>
       <c r="F1429" t="n">
         <v>0.0</v>
@@ -52935,10 +52935,10 @@
         <v>112.201</v>
       </c>
       <c r="H1429" t="n">
-        <v>947.869</v>
+        <v>915.398</v>
       </c>
       <c r="I1429" t="n">
-        <v>725.9136</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1430">
@@ -53407,7 +53407,7 @@
         </is>
       </c>
       <c r="E1442" t="n">
-        <v>159.124</v>
+        <v>154.375</v>
       </c>
       <c r="F1442" t="n">
         <v>5.625</v>
@@ -53416,7 +53416,7 @@
         <v>70.5</v>
       </c>
       <c r="H1442" t="n">
-        <v>159.124</v>
+        <v>154.375</v>
       </c>
       <c r="I1442" t="n">
         <v>0.0</v>
@@ -53444,7 +53444,7 @@
         </is>
       </c>
       <c r="E1443" t="n">
-        <v>27.247</v>
+        <v>17.25</v>
       </c>
       <c r="F1443" t="n">
         <v>0.0</v>
@@ -53453,7 +53453,7 @@
         <v>33.75</v>
       </c>
       <c r="H1443" t="n">
-        <v>27.247</v>
+        <v>17.25</v>
       </c>
       <c r="I1443" t="n">
         <v>0.0</v>
@@ -53481,7 +53481,7 @@
         </is>
       </c>
       <c r="E1444" t="n">
-        <v>451.247</v>
+        <v>448.247</v>
       </c>
       <c r="F1444" t="n">
         <v>0.0</v>
@@ -53490,7 +53490,7 @@
         <v>40.5</v>
       </c>
       <c r="H1444" t="n">
-        <v>451.247</v>
+        <v>448.247</v>
       </c>
       <c r="I1444" t="n">
         <v>0.0</v>
@@ -53555,7 +53555,7 @@
         </is>
       </c>
       <c r="E1446" t="n">
-        <v>538.125</v>
+        <v>519.75</v>
       </c>
       <c r="F1446" t="n">
         <v>0.0</v>
@@ -53564,7 +53564,7 @@
         <v>20.625</v>
       </c>
       <c r="H1446" t="n">
-        <v>538.125</v>
+        <v>519.75</v>
       </c>
       <c r="I1446" t="n">
         <v>0.0</v>
@@ -53592,7 +53592,7 @@
         </is>
       </c>
       <c r="E1447" t="n">
-        <v>220.625</v>
+        <v>218.375</v>
       </c>
       <c r="F1447" t="n">
         <v>0.0</v>
@@ -53601,7 +53601,7 @@
         <v>6.75</v>
       </c>
       <c r="H1447" t="n">
-        <v>220.625</v>
+        <v>218.375</v>
       </c>
       <c r="I1447" t="n">
         <v>0.0</v>
@@ -53629,7 +53629,7 @@
         </is>
       </c>
       <c r="E1448" t="n">
-        <v>85.5</v>
+        <v>60.0</v>
       </c>
       <c r="F1448" t="n">
         <v>0.0</v>
@@ -53638,7 +53638,7 @@
         <v>436.5</v>
       </c>
       <c r="H1448" t="n">
-        <v>85.5</v>
+        <v>60.0</v>
       </c>
       <c r="I1448" t="n">
         <v>0.0</v>
@@ -53666,7 +53666,7 @@
         </is>
       </c>
       <c r="E1449" t="n">
-        <v>569.625</v>
+        <v>568.875</v>
       </c>
       <c r="F1449" t="n">
         <v>0.0</v>
@@ -53675,7 +53675,7 @@
         <v>38.25</v>
       </c>
       <c r="H1449" t="n">
-        <v>569.625</v>
+        <v>568.875</v>
       </c>
       <c r="I1449" t="n">
         <v>0.0</v>
@@ -53703,7 +53703,7 @@
         </is>
       </c>
       <c r="E1450" t="n">
-        <v>701.375</v>
+        <v>688.25</v>
       </c>
       <c r="F1450" t="n">
         <v>0.375</v>
@@ -53712,7 +53712,7 @@
         <v>3.75</v>
       </c>
       <c r="H1450" t="n">
-        <v>701.375</v>
+        <v>688.25</v>
       </c>
       <c r="I1450" t="n">
         <v>0.0</v>
@@ -53740,7 +53740,7 @@
         </is>
       </c>
       <c r="E1451" t="n">
-        <v>480.0</v>
+        <v>463.5</v>
       </c>
       <c r="F1451" t="n">
         <v>1.5</v>
@@ -53749,7 +53749,7 @@
         <v>0.0</v>
       </c>
       <c r="H1451" t="n">
-        <v>480.0</v>
+        <v>463.5</v>
       </c>
       <c r="I1451" t="n">
         <v>0.0</v>
@@ -53777,7 +53777,7 @@
         </is>
       </c>
       <c r="E1452" t="n">
-        <v>316.75</v>
+        <v>313.0</v>
       </c>
       <c r="F1452" t="n">
         <v>0.0</v>
@@ -53786,7 +53786,7 @@
         <v>0.0</v>
       </c>
       <c r="H1452" t="n">
-        <v>316.75</v>
+        <v>313.0</v>
       </c>
       <c r="I1452" t="n">
         <v>0.0</v>
@@ -53925,7 +53925,7 @@
         </is>
       </c>
       <c r="E1456" t="n">
-        <v>3305.25</v>
+        <v>3267.75</v>
       </c>
       <c r="F1456" t="n">
         <v>0.0</v>
@@ -53934,7 +53934,7 @@
         <v>37.5</v>
       </c>
       <c r="H1456" t="n">
-        <v>3305.25</v>
+        <v>3267.75</v>
       </c>
       <c r="I1456" t="n">
         <v>0.0</v>
@@ -54517,7 +54517,7 @@
         </is>
       </c>
       <c r="E1472" t="n">
-        <v>1585.2924</v>
+        <v>122.79</v>
       </c>
       <c r="F1472" t="n">
         <v>0.0</v>
@@ -54529,7 +54529,7 @@
         <v>122.79</v>
       </c>
       <c r="I1472" t="n">
-        <v>1462.5024</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1473">
@@ -54554,7 +54554,7 @@
         </is>
       </c>
       <c r="E1473" t="n">
-        <v>3.197</v>
+        <v>12.786999999999999</v>
       </c>
       <c r="F1473" t="n">
         <v>0.0</v>
@@ -54563,7 +54563,7 @@
         <v>0.0</v>
       </c>
       <c r="H1473" t="n">
-        <v>3.197</v>
+        <v>12.786999999999999</v>
       </c>
       <c r="I1473" t="n">
         <v>0.0</v>
@@ -54702,7 +54702,7 @@
         </is>
       </c>
       <c r="E1477" t="n">
-        <v>3869.763</v>
+        <v>3859.087</v>
       </c>
       <c r="F1477" t="n">
         <v>0.0</v>
@@ -54711,7 +54711,7 @@
         <v>939.418</v>
       </c>
       <c r="H1477" t="n">
-        <v>3869.763</v>
+        <v>3859.087</v>
       </c>
       <c r="I1477" t="n">
         <v>0.0</v>
@@ -54739,7 +54739,7 @@
         </is>
       </c>
       <c r="E1478" t="n">
-        <v>2642.112</v>
+        <v>2369.894</v>
       </c>
       <c r="F1478" t="n">
         <v>0.0</v>
@@ -54748,7 +54748,7 @@
         <v>419.002</v>
       </c>
       <c r="H1478" t="n">
-        <v>2642.112</v>
+        <v>2369.894</v>
       </c>
       <c r="I1478" t="n">
         <v>0.0</v>
@@ -54813,7 +54813,7 @@
         </is>
       </c>
       <c r="E1480" t="n">
-        <v>6099.263999999999</v>
+        <v>5905.548</v>
       </c>
       <c r="F1480" t="n">
         <v>0.589</v>
@@ -54822,7 +54822,7 @@
         <v>661.475</v>
       </c>
       <c r="H1480" t="n">
-        <v>6099.263999999999</v>
+        <v>5905.548</v>
       </c>
       <c r="I1480" t="n">
         <v>0.0</v>
@@ -54850,7 +54850,7 @@
         </is>
       </c>
       <c r="E1481" t="n">
-        <v>2383.3810000000003</v>
+        <v>2351.497</v>
       </c>
       <c r="F1481" t="n">
         <v>65.467</v>
@@ -54859,7 +54859,7 @@
         <v>121.834</v>
       </c>
       <c r="H1481" t="n">
-        <v>2383.3810000000003</v>
+        <v>2351.497</v>
       </c>
       <c r="I1481" t="n">
         <v>0.0</v>
@@ -55146,7 +55146,7 @@
         </is>
       </c>
       <c r="E1489" t="n">
-        <v>5475.599999999999</v>
+        <v>5463.0</v>
       </c>
       <c r="F1489" t="n">
         <v>1.8</v>
@@ -55155,7 +55155,7 @@
         <v>0.0</v>
       </c>
       <c r="H1489" t="n">
-        <v>5475.599999999999</v>
+        <v>5463.0</v>
       </c>
       <c r="I1489" t="n">
         <v>0.0</v>
@@ -55953,13 +55953,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDA7D5A4-67FB-4688-8F2F-D40A813C6407}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD466753-0CCC-42D4-8271-7689C615B71B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{213BE490-A5FB-485C-8E5C-1877E97CEAFA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9DCE3A3-7047-47B5-A3DC-D2A416F94EBF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A5E2721-9368-416A-A07A-817CB84005EE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F879ED-7EB1-4F08-A0DF-E8073C33CD3D}"/>
 </file>
--- a/Inventory_KNIME.xlsx
+++ b/Inventory_KNIME.xlsx
@@ -423,7 +423,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>715.0999999999999</v>
+        <v>706.7</v>
       </c>
       <c r="F10" t="n">
         <v>0.0</v>
@@ -432,7 +432,7 @@
         <v>0.2</v>
       </c>
       <c r="H10" t="n">
-        <v>715.0999999999999</v>
+        <v>706.7</v>
       </c>
       <c r="I10" t="n">
         <v>0.0</v>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>884.5</v>
+        <v>878.5</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
@@ -691,7 +691,7 @@
         <v>0.5</v>
       </c>
       <c r="H17" t="n">
-        <v>884.5</v>
+        <v>878.5</v>
       </c>
       <c r="I17" t="n">
         <v>0.0</v>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>11285.5</v>
+        <v>11264.5</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -839,7 +839,7 @@
         <v>0.0</v>
       </c>
       <c r="H21" t="n">
-        <v>11285.5</v>
+        <v>11264.5</v>
       </c>
       <c r="I21" t="n">
         <v>0.0</v>
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4177.5</v>
+        <v>4144.5</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -876,7 +876,7 @@
         <v>3.0</v>
       </c>
       <c r="H22" t="n">
-        <v>4177.5</v>
+        <v>4144.5</v>
       </c>
       <c r="I22" t="n">
         <v>0.0</v>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>772.1</v>
+        <v>760.1</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -913,7 +913,7 @@
         <v>2.0</v>
       </c>
       <c r="H23" t="n">
-        <v>772.1</v>
+        <v>760.1</v>
       </c>
       <c r="I23" t="n">
         <v>0.0</v>
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3427.5860000000002</v>
+        <v>3327.849</v>
       </c>
       <c r="F34" t="n">
         <v>37.148</v>
@@ -1320,7 +1320,7 @@
         <v>4.971</v>
       </c>
       <c r="H34" t="n">
-        <v>3427.5860000000002</v>
+        <v>3327.849</v>
       </c>
       <c r="I34" t="n">
         <v>0.0</v>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2027.0220000000002</v>
+        <v>1953.379</v>
       </c>
       <c r="F35" t="n">
         <v>282.264</v>
@@ -1357,7 +1357,7 @@
         <v>216.545</v>
       </c>
       <c r="H35" t="n">
-        <v>2027.0220000000002</v>
+        <v>1953.379</v>
       </c>
       <c r="I35" t="n">
         <v>0.0</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1648.398</v>
+        <v>1588.36</v>
       </c>
       <c r="F39" t="n">
         <v>2200.261</v>
@@ -1505,7 +1505,7 @@
         <v>70.722</v>
       </c>
       <c r="H39" t="n">
-        <v>1648.398</v>
+        <v>1588.36</v>
       </c>
       <c r="I39" t="n">
         <v>0.0</v>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>916.314</v>
+        <v>914.75</v>
       </c>
       <c r="F40" t="n">
         <v>17.094</v>
@@ -1542,7 +1542,7 @@
         <v>25.329</v>
       </c>
       <c r="H40" t="n">
-        <v>916.314</v>
+        <v>914.75</v>
       </c>
       <c r="I40" t="n">
         <v>0.0</v>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1036.181</v>
+        <v>1027.201</v>
       </c>
       <c r="F42" t="n">
         <v>767.328</v>
@@ -1616,7 +1616,7 @@
         <v>332.94</v>
       </c>
       <c r="H42" t="n">
-        <v>1036.181</v>
+        <v>1027.201</v>
       </c>
       <c r="I42" t="n">
         <v>0.0</v>
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>9700.35</v>
+        <v>9357.15</v>
       </c>
       <c r="F43" t="n">
         <v>3.3</v>
@@ -1653,7 +1653,7 @@
         <v>409.2</v>
       </c>
       <c r="H43" t="n">
-        <v>9700.35</v>
+        <v>9357.15</v>
       </c>
       <c r="I43" t="n">
         <v>0.0</v>
@@ -2532,7 +2532,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>109.08</v>
+        <v>107.747</v>
       </c>
       <c r="F67" t="n">
         <v>3.467</v>
@@ -2541,7 +2541,7 @@
         <v>0.0</v>
       </c>
       <c r="H67" t="n">
-        <v>109.08</v>
+        <v>107.747</v>
       </c>
       <c r="I67" t="n">
         <v>0.0</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3235.7999999999997</v>
+        <v>3113.2</v>
       </c>
       <c r="F70" t="n">
         <v>1.2</v>
@@ -2652,7 +2652,7 @@
         <v>0.0</v>
       </c>
       <c r="H70" t="n">
-        <v>3235.7999999999997</v>
+        <v>3113.2</v>
       </c>
       <c r="I70" t="n">
         <v>0.0</v>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1366.571</v>
+        <v>1268.159</v>
       </c>
       <c r="F71" t="n">
         <v>4.801</v>
@@ -2689,7 +2689,7 @@
         <v>17.069000000000003</v>
       </c>
       <c r="H71" t="n">
-        <v>1366.571</v>
+        <v>1268.159</v>
       </c>
       <c r="I71" t="n">
         <v>0.0</v>
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>329.641</v>
+        <v>304.039</v>
       </c>
       <c r="F72" t="n">
         <v>0.0</v>
@@ -2726,7 +2726,7 @@
         <v>4.267</v>
       </c>
       <c r="H72" t="n">
-        <v>329.641</v>
+        <v>304.039</v>
       </c>
       <c r="I72" t="n">
         <v>0.0</v>
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1772.489</v>
+        <v>1593.6180000000002</v>
       </c>
       <c r="F73" t="n">
         <v>5.777</v>
@@ -2763,7 +2763,7 @@
         <v>0.0</v>
       </c>
       <c r="H73" t="n">
-        <v>1772.489</v>
+        <v>1593.6180000000002</v>
       </c>
       <c r="I73" t="n">
         <v>0.0</v>
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1441.5130000000001</v>
+        <v>1385.773</v>
       </c>
       <c r="F74" t="n">
         <v>0.0</v>
@@ -2800,7 +2800,7 @@
         <v>0.0</v>
       </c>
       <c r="H74" t="n">
-        <v>1441.5130000000001</v>
+        <v>1385.773</v>
       </c>
       <c r="I74" t="n">
         <v>0.0</v>
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5827.928</v>
+        <v>5247.058</v>
       </c>
       <c r="F75" t="n">
         <v>9.601</v>
@@ -2837,7 +2837,7 @@
         <v>17.069000000000003</v>
       </c>
       <c r="H75" t="n">
-        <v>5827.928</v>
+        <v>5247.058</v>
       </c>
       <c r="I75" t="n">
         <v>0.0</v>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>391.249</v>
+        <v>369.913</v>
       </c>
       <c r="F76" t="n">
         <v>1.333</v>
@@ -2874,7 +2874,7 @@
         <v>0.0</v>
       </c>
       <c r="H76" t="n">
-        <v>391.249</v>
+        <v>369.913</v>
       </c>
       <c r="I76" t="n">
         <v>0.0</v>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1123.607</v>
+        <v>1110.805</v>
       </c>
       <c r="F77" t="n">
         <v>50.94</v>
@@ -2911,7 +2911,7 @@
         <v>0.0</v>
       </c>
       <c r="H77" t="n">
-        <v>1123.607</v>
+        <v>1110.805</v>
       </c>
       <c r="I77" t="n">
         <v>0.0</v>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>486.388</v>
+        <v>480.383</v>
       </c>
       <c r="F78" t="n">
         <v>0.0</v>
@@ -2948,7 +2948,7 @@
         <v>0.083</v>
       </c>
       <c r="H78" t="n">
-        <v>486.388</v>
+        <v>480.383</v>
       </c>
       <c r="I78" t="n">
         <v>0.0</v>
@@ -3198,7 +3198,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3319.9320000000002</v>
+        <v>1559.122</v>
       </c>
       <c r="F85" t="n">
         <v>0.0</v>
@@ -3207,7 +3207,7 @@
         <v>0.0</v>
       </c>
       <c r="H85" t="n">
-        <v>3319.9320000000002</v>
+        <v>1559.122</v>
       </c>
       <c r="I85" t="n">
         <v>0.0</v>
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>3650.584</v>
+        <v>3640.576</v>
       </c>
       <c r="F103" t="n">
         <v>0.0</v>
@@ -3873,7 +3873,7 @@
         <v>1.251</v>
       </c>
       <c r="H103" t="n">
-        <v>3650.584</v>
+        <v>3640.576</v>
       </c>
       <c r="I103" t="n">
         <v>0.0</v>
@@ -4049,7 +4049,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>552.885</v>
+        <v>540.876</v>
       </c>
       <c r="F108" t="n">
         <v>0.0</v>
@@ -4058,7 +4058,7 @@
         <v>0.0</v>
       </c>
       <c r="H108" t="n">
-        <v>552.885</v>
+        <v>540.876</v>
       </c>
       <c r="I108" t="n">
         <v>0.0</v>
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>893.743</v>
+        <v>859.049</v>
       </c>
       <c r="F109" t="n">
         <v>0.0</v>
@@ -4095,7 +4095,7 @@
         <v>69.38900000000001</v>
       </c>
       <c r="H109" t="n">
-        <v>893.743</v>
+        <v>859.049</v>
       </c>
       <c r="I109" t="n">
         <v>0.0</v>
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>463.704</v>
+        <v>434.347</v>
       </c>
       <c r="F113" t="n">
         <v>0.0</v>
@@ -4243,7 +4243,7 @@
         <v>8.283999999999999</v>
       </c>
       <c r="H113" t="n">
-        <v>463.704</v>
+        <v>434.347</v>
       </c>
       <c r="I113" t="n">
         <v>0.0</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>905.388</v>
+        <v>908.057</v>
       </c>
       <c r="F114" t="n">
         <v>0.0</v>
@@ -4280,7 +4280,7 @@
         <v>2.669</v>
       </c>
       <c r="H114" t="n">
-        <v>905.388</v>
+        <v>908.057</v>
       </c>
       <c r="I114" t="n">
         <v>0.0</v>
@@ -4419,7 +4419,7 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>774.155</v>
+        <v>774.1550000000001</v>
       </c>
       <c r="F118" t="n">
         <v>0.0</v>
@@ -4428,7 +4428,7 @@
         <v>0.0</v>
       </c>
       <c r="H118" t="n">
-        <v>774.155</v>
+        <v>774.1550000000001</v>
       </c>
       <c r="I118" t="n">
         <v>0.0</v>
@@ -4456,7 +4456,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1043.007</v>
+        <v>1039.896</v>
       </c>
       <c r="F119" t="n">
         <v>0.0</v>
@@ -4465,7 +4465,7 @@
         <v>0.0</v>
       </c>
       <c r="H119" t="n">
-        <v>1043.007</v>
+        <v>1039.896</v>
       </c>
       <c r="I119" t="n">
         <v>0.0</v>
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2323.0</v>
+        <v>2324.0</v>
       </c>
       <c r="F121" t="n">
         <v>0.0</v>
@@ -4539,7 +4539,7 @@
         <v>4.0</v>
       </c>
       <c r="H121" t="n">
-        <v>2323.0</v>
+        <v>2324.0</v>
       </c>
       <c r="I121" t="n">
         <v>0.0</v>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1171.36</v>
+        <v>1144.3600000000001</v>
       </c>
       <c r="F122" t="n">
         <v>0.12000000000000001</v>
@@ -4576,7 +4576,7 @@
         <v>25.44</v>
       </c>
       <c r="H122" t="n">
-        <v>1171.36</v>
+        <v>1144.3600000000001</v>
       </c>
       <c r="I122" t="n">
         <v>0.0</v>
@@ -4604,7 +4604,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1204.202</v>
+        <v>1021.951</v>
       </c>
       <c r="F123" t="n">
         <v>0.225</v>
@@ -4613,7 +4613,7 @@
         <v>116.775</v>
       </c>
       <c r="H123" t="n">
-        <v>1204.202</v>
+        <v>1021.951</v>
       </c>
       <c r="I123" t="n">
         <v>0.0</v>
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4244.039000000001</v>
+        <v>4215.827</v>
       </c>
       <c r="F124" t="n">
         <v>0.0</v>
@@ -4650,7 +4650,7 @@
         <v>118.215</v>
       </c>
       <c r="H124" t="n">
-        <v>4244.039000000001</v>
+        <v>4215.827</v>
       </c>
       <c r="I124" t="n">
         <v>0.0</v>
@@ -4752,7 +4752,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>356.08</v>
+        <v>306.592</v>
       </c>
       <c r="F127" t="n">
         <v>0.0</v>
@@ -4761,7 +4761,7 @@
         <v>106.005</v>
       </c>
       <c r="H127" t="n">
-        <v>356.08</v>
+        <v>306.592</v>
       </c>
       <c r="I127" t="n">
         <v>0.0</v>
@@ -4789,7 +4789,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>227.79999999999998</v>
+        <v>132.16</v>
       </c>
       <c r="F128" t="n">
         <v>0.0</v>
@@ -4798,7 +4798,7 @@
         <v>75.39999999999999</v>
       </c>
       <c r="H128" t="n">
-        <v>227.79999999999998</v>
+        <v>132.16</v>
       </c>
       <c r="I128" t="n">
         <v>0.0</v>
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1825.904</v>
+        <v>1819.232</v>
       </c>
       <c r="F130" t="n">
         <v>0.0</v>
@@ -4872,7 +4872,7 @@
         <v>63.38399999999999</v>
       </c>
       <c r="H130" t="n">
-        <v>1825.904</v>
+        <v>1819.232</v>
       </c>
       <c r="I130" t="n">
         <v>0.0</v>
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>448.358</v>
+        <v>453.69599999999997</v>
       </c>
       <c r="F131" t="n">
         <v>0.0</v>
@@ -4909,7 +4909,7 @@
         <v>0.0</v>
       </c>
       <c r="H131" t="n">
-        <v>448.358</v>
+        <v>453.69599999999997</v>
       </c>
       <c r="I131" t="n">
         <v>0.0</v>
@@ -5233,7 +5233,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4340.8</v>
+        <v>4336.0</v>
       </c>
       <c r="F140" t="n">
         <v>0.0</v>
@@ -5242,7 +5242,7 @@
         <v>1.0</v>
       </c>
       <c r="H140" t="n">
-        <v>4340.8</v>
+        <v>4336.0</v>
       </c>
       <c r="I140" t="n">
         <v>0.0</v>
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1820.0</v>
+        <v>1803.2</v>
       </c>
       <c r="F141" t="n">
         <v>0.0</v>
@@ -5279,7 +5279,7 @@
         <v>1.0</v>
       </c>
       <c r="H141" t="n">
-        <v>1820.0</v>
+        <v>1803.2</v>
       </c>
       <c r="I141" t="n">
         <v>0.0</v>
@@ -5344,7 +5344,7 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1858.5</v>
+        <v>1846.5</v>
       </c>
       <c r="F143" t="n">
         <v>0.0</v>
@@ -5353,7 +5353,7 @@
         <v>0.0</v>
       </c>
       <c r="H143" t="n">
-        <v>1858.5</v>
+        <v>1846.5</v>
       </c>
       <c r="I143" t="n">
         <v>0.0</v>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1410.0</v>
+        <v>1395.0</v>
       </c>
       <c r="F146" t="n">
         <v>0.5</v>
@@ -5464,7 +5464,7 @@
         <v>0.5</v>
       </c>
       <c r="H146" t="n">
-        <v>1410.0</v>
+        <v>1395.0</v>
       </c>
       <c r="I146" t="n">
         <v>0.0</v>
@@ -6010,7 +6010,7 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4348.0</v>
+        <v>4308.0</v>
       </c>
       <c r="F161" t="n">
         <v>0.0</v>
@@ -6019,7 +6019,7 @@
         <v>12.0</v>
       </c>
       <c r="H161" t="n">
-        <v>4348.0</v>
+        <v>4308.0</v>
       </c>
       <c r="I161" t="n">
         <v>0.0</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>4417.8</v>
+        <v>4297.8</v>
       </c>
       <c r="F163" t="n">
         <v>4.8</v>
@@ -6093,7 +6093,7 @@
         <v>136.8</v>
       </c>
       <c r="H163" t="n">
-        <v>4417.8</v>
+        <v>4297.8</v>
       </c>
       <c r="I163" t="n">
         <v>0.0</v>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1103.125</v>
+        <v>1173.135</v>
       </c>
       <c r="F192" t="n">
         <v>0.0</v>
@@ -7169,7 +7169,7 @@
         <v>1103.125</v>
       </c>
       <c r="I192" t="n">
-        <v>0.0</v>
+        <v>70.01</v>
       </c>
     </row>
     <row r="193">
@@ -7453,7 +7453,7 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>98.312</v>
+        <v>67.375</v>
       </c>
       <c r="F200" t="n">
         <v>0.0</v>
@@ -7462,7 +7462,7 @@
         <v>79.125</v>
       </c>
       <c r="H200" t="n">
-        <v>98.312</v>
+        <v>67.375</v>
       </c>
       <c r="I200" t="n">
         <v>0.0</v>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>642.251</v>
+        <v>605.14</v>
       </c>
       <c r="F202" t="n">
         <v>1.031</v>
@@ -7536,7 +7536,7 @@
         <v>0.0</v>
       </c>
       <c r="H202" t="n">
-        <v>642.251</v>
+        <v>605.14</v>
       </c>
       <c r="I202" t="n">
         <v>0.0</v>
@@ -7601,7 +7601,7 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1182.784</v>
+        <v>1183.644</v>
       </c>
       <c r="F204" t="n">
         <v>0.0</v>
@@ -7610,7 +7610,7 @@
         <v>0.0</v>
       </c>
       <c r="H204" t="n">
-        <v>1182.784</v>
+        <v>1183.644</v>
       </c>
       <c r="I204" t="n">
         <v>0.0</v>
@@ -7638,7 +7638,7 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>855.128</v>
+        <v>854.785</v>
       </c>
       <c r="F205" t="n">
         <v>0.0</v>
@@ -7647,7 +7647,7 @@
         <v>0.859</v>
       </c>
       <c r="H205" t="n">
-        <v>855.128</v>
+        <v>854.785</v>
       </c>
       <c r="I205" t="n">
         <v>0.0</v>
@@ -7675,7 +7675,7 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>646.886</v>
+        <v>646.715</v>
       </c>
       <c r="F206" t="n">
         <v>0.0</v>
@@ -7684,7 +7684,7 @@
         <v>128.862</v>
       </c>
       <c r="H206" t="n">
-        <v>646.886</v>
+        <v>646.715</v>
       </c>
       <c r="I206" t="n">
         <v>0.0</v>
@@ -7712,7 +7712,7 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>635.028</v>
+        <v>633.481</v>
       </c>
       <c r="F207" t="n">
         <v>0.515</v>
@@ -7721,7 +7721,7 @@
         <v>0.34400000000000003</v>
       </c>
       <c r="H207" t="n">
-        <v>635.028</v>
+        <v>633.481</v>
       </c>
       <c r="I207" t="n">
         <v>0.0</v>
@@ -7749,7 +7749,7 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>817.2</v>
+        <v>809.64</v>
       </c>
       <c r="F208" t="n">
         <v>0.0</v>
@@ -7758,7 +7758,7 @@
         <v>0.0</v>
       </c>
       <c r="H208" t="n">
-        <v>817.2</v>
+        <v>809.64</v>
       </c>
       <c r="I208" t="n">
         <v>0.0</v>
@@ -7786,7 +7786,7 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>523.037</v>
+        <v>500.355</v>
       </c>
       <c r="F209" t="n">
         <v>0.0</v>
@@ -7795,7 +7795,7 @@
         <v>22.681</v>
       </c>
       <c r="H209" t="n">
-        <v>523.037</v>
+        <v>500.355</v>
       </c>
       <c r="I209" t="n">
         <v>0.0</v>
@@ -7823,7 +7823,7 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>438.038</v>
+        <v>420.168</v>
       </c>
       <c r="F210" t="n">
         <v>0.0</v>
@@ -7832,7 +7832,7 @@
         <v>48.111000000000004</v>
       </c>
       <c r="H210" t="n">
-        <v>438.038</v>
+        <v>420.168</v>
       </c>
       <c r="I210" t="n">
         <v>0.0</v>
@@ -7897,7 +7897,7 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>843.309</v>
+        <v>839.47</v>
       </c>
       <c r="F212" t="n">
         <v>0.0</v>
@@ -7906,7 +7906,7 @@
         <v>1.374</v>
       </c>
       <c r="H212" t="n">
-        <v>843.309</v>
+        <v>839.47</v>
       </c>
       <c r="I212" t="n">
         <v>0.0</v>
@@ -7934,7 +7934,7 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>100.789</v>
+        <v>100.216</v>
       </c>
       <c r="F213" t="n">
         <v>0.34400000000000003</v>
@@ -7943,7 +7943,7 @@
         <v>43.981</v>
       </c>
       <c r="H213" t="n">
-        <v>100.789</v>
+        <v>100.216</v>
       </c>
       <c r="I213" t="n">
         <v>0.0</v>
@@ -7971,7 +7971,7 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>82.476</v>
+        <v>76.291</v>
       </c>
       <c r="F214" t="n">
         <v>0.0</v>
@@ -7980,7 +7980,7 @@
         <v>11.684</v>
       </c>
       <c r="H214" t="n">
-        <v>82.476</v>
+        <v>76.291</v>
       </c>
       <c r="I214" t="n">
         <v>0.0</v>
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>1672.127</v>
+        <v>1664.968</v>
       </c>
       <c r="F215" t="n">
         <v>1.031</v>
@@ -8017,7 +8017,7 @@
         <v>0.34400000000000003</v>
       </c>
       <c r="H215" t="n">
-        <v>1672.127</v>
+        <v>1664.968</v>
       </c>
       <c r="I215" t="n">
         <v>0.0</v>
@@ -8045,7 +8045,7 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>174.574</v>
+        <v>173.199</v>
       </c>
       <c r="F216" t="n">
         <v>0.0</v>
@@ -8054,7 +8054,7 @@
         <v>1019.9530000000001</v>
       </c>
       <c r="H216" t="n">
-        <v>174.574</v>
+        <v>173.199</v>
       </c>
       <c r="I216" t="n">
         <v>0.0</v>
@@ -8082,7 +8082,7 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>770.0649999999999</v>
+        <v>766.629</v>
       </c>
       <c r="F217" t="n">
         <v>0.34400000000000003</v>
@@ -8091,7 +8091,7 @@
         <v>7.216</v>
       </c>
       <c r="H217" t="n">
-        <v>770.0649999999999</v>
+        <v>766.629</v>
       </c>
       <c r="I217" t="n">
         <v>0.0</v>
@@ -8156,7 +8156,7 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>281.435</v>
+        <v>281.436</v>
       </c>
       <c r="F219" t="n">
         <v>0.0</v>
@@ -8165,7 +8165,7 @@
         <v>0.0</v>
       </c>
       <c r="H219" t="n">
-        <v>281.435</v>
+        <v>281.436</v>
       </c>
       <c r="I219" t="n">
         <v>0.0</v>
@@ -8230,7 +8230,7 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>272.157</v>
+        <v>257.724</v>
       </c>
       <c r="F221" t="n">
         <v>0.0</v>
@@ -8239,7 +8239,7 @@
         <v>0.0</v>
       </c>
       <c r="H221" t="n">
-        <v>272.157</v>
+        <v>257.724</v>
       </c>
       <c r="I221" t="n">
         <v>0.0</v>
@@ -8267,7 +8267,7 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>94.847</v>
+        <v>94.16</v>
       </c>
       <c r="F222" t="n">
         <v>0.0</v>
@@ -8276,7 +8276,7 @@
         <v>685.238</v>
       </c>
       <c r="H222" t="n">
-        <v>94.847</v>
+        <v>94.16</v>
       </c>
       <c r="I222" t="n">
         <v>0.0</v>
@@ -8304,7 +8304,7 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>1023.3539999999999</v>
+        <v>1015.737</v>
       </c>
       <c r="F223" t="n">
         <v>0.0</v>
@@ -8313,7 +8313,7 @@
         <v>3.436</v>
       </c>
       <c r="H223" t="n">
-        <v>1023.3539999999999</v>
+        <v>1015.737</v>
       </c>
       <c r="I223" t="n">
         <v>0.0</v>
@@ -8415,7 +8415,7 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>4056.0</v>
+        <v>3933.0</v>
       </c>
       <c r="F226" t="n">
         <v>0.0</v>
@@ -8424,7 +8424,7 @@
         <v>0.0</v>
       </c>
       <c r="H226" t="n">
-        <v>4056.0</v>
+        <v>3933.0</v>
       </c>
       <c r="I226" t="n">
         <v>0.0</v>
@@ -8452,7 +8452,7 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>1915.0</v>
+        <v>1855.0</v>
       </c>
       <c r="F227" t="n">
         <v>0.0</v>
@@ -8461,7 +8461,7 @@
         <v>0.0</v>
       </c>
       <c r="H227" t="n">
-        <v>1915.0</v>
+        <v>1855.0</v>
       </c>
       <c r="I227" t="n">
         <v>0.0</v>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>21.0</v>
+        <v>31.0</v>
       </c>
       <c r="F235" t="n">
         <v>0.0</v>
@@ -8757,7 +8757,7 @@
         <v>0.0</v>
       </c>
       <c r="H235" t="n">
-        <v>21.0</v>
+        <v>31.0</v>
       </c>
       <c r="I235" t="n">
         <v>0.0</v>
@@ -8859,7 +8859,7 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>66.053</v>
+        <v>62.718</v>
       </c>
       <c r="F238" t="n">
         <v>0.0</v>
@@ -8868,7 +8868,7 @@
         <v>1.056</v>
       </c>
       <c r="H238" t="n">
-        <v>66.053</v>
+        <v>62.718</v>
       </c>
       <c r="I238" t="n">
         <v>0.0</v>
@@ -8896,7 +8896,7 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>78.73</v>
+        <v>72.726</v>
       </c>
       <c r="F239" t="n">
         <v>0.0</v>
@@ -8905,7 +8905,7 @@
         <v>0.0</v>
       </c>
       <c r="H239" t="n">
-        <v>78.73</v>
+        <v>72.726</v>
       </c>
       <c r="I239" t="n">
         <v>0.0</v>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>71.391</v>
+        <v>71.39</v>
       </c>
       <c r="F240" t="n">
         <v>0.0</v>
@@ -8942,7 +8942,7 @@
         <v>0.0</v>
       </c>
       <c r="H240" t="n">
-        <v>71.391</v>
+        <v>71.39</v>
       </c>
       <c r="I240" t="n">
         <v>0.0</v>
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>10.564</v>
+        <v>7.228</v>
       </c>
       <c r="F242" t="n">
         <v>0.0</v>
@@ -9016,7 +9016,7 @@
         <v>0.0</v>
       </c>
       <c r="H242" t="n">
-        <v>10.564</v>
+        <v>7.228</v>
       </c>
       <c r="I242" t="n">
         <v>0.0</v>
@@ -9673,7 +9673,7 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>759.5999999999999</v>
+        <v>600.6</v>
       </c>
       <c r="F260" t="n">
         <v>5.4</v>
@@ -9682,7 +9682,7 @@
         <v>8.0</v>
       </c>
       <c r="H260" t="n">
-        <v>759.5999999999999</v>
+        <v>600.6</v>
       </c>
       <c r="I260" t="n">
         <v>0.0</v>
@@ -9747,7 +9747,7 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>308.41400000000004</v>
+        <v>309.94100000000003</v>
       </c>
       <c r="F262" t="n">
         <v>0.0</v>
@@ -9756,7 +9756,7 @@
         <v>604.1959999999999</v>
       </c>
       <c r="H262" t="n">
-        <v>308.41400000000004</v>
+        <v>309.94100000000003</v>
       </c>
       <c r="I262" t="n">
         <v>0.0</v>
@@ -9784,7 +9784,7 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>373.0</v>
+        <v>260.8</v>
       </c>
       <c r="F263" t="n">
         <v>0.6</v>
@@ -9793,7 +9793,7 @@
         <v>8.0</v>
       </c>
       <c r="H263" t="n">
-        <v>373.0</v>
+        <v>260.8</v>
       </c>
       <c r="I263" t="n">
         <v>0.0</v>
@@ -9821,7 +9821,7 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>6124.845</v>
+        <v>5830.915</v>
       </c>
       <c r="F264" t="n">
         <v>1.59</v>
@@ -9830,7 +9830,7 @@
         <v>62.620999999999995</v>
       </c>
       <c r="H264" t="n">
-        <v>6124.845</v>
+        <v>5830.915</v>
       </c>
       <c r="I264" t="n">
         <v>0.0</v>
@@ -9858,7 +9858,7 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>3475.745</v>
+        <v>3444.1240000000003</v>
       </c>
       <c r="F265" t="n">
         <v>3.979</v>
@@ -9867,7 +9867,7 @@
         <v>124.306</v>
       </c>
       <c r="H265" t="n">
-        <v>3475.745</v>
+        <v>3444.1240000000003</v>
       </c>
       <c r="I265" t="n">
         <v>0.0</v>
@@ -9895,7 +9895,7 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>3313.978</v>
+        <v>3302.8959999999997</v>
       </c>
       <c r="F266" t="n">
         <v>3.367</v>
@@ -9904,7 +9904,7 @@
         <v>145.07</v>
       </c>
       <c r="H266" t="n">
-        <v>3313.978</v>
+        <v>3302.8959999999997</v>
       </c>
       <c r="I266" t="n">
         <v>0.0</v>
@@ -10117,7 +10117,7 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>16.802</v>
+        <v>4402.3328</v>
       </c>
       <c r="F272" t="n">
         <v>0.0</v>
@@ -10129,7 +10129,7 @@
         <v>16.802</v>
       </c>
       <c r="I272" t="n">
-        <v>0.0</v>
+        <v>4385.5308</v>
       </c>
     </row>
     <row r="273">
@@ -10302,7 +10302,7 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>325.362</v>
+        <v>321.52200000000005</v>
       </c>
       <c r="F277" t="n">
         <v>0.04</v>
@@ -10311,7 +10311,7 @@
         <v>3.8400000000000003</v>
       </c>
       <c r="H277" t="n">
-        <v>325.362</v>
+        <v>321.52200000000005</v>
       </c>
       <c r="I277" t="n">
         <v>0.0</v>
@@ -10339,7 +10339,7 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>408.001</v>
+        <v>402.241</v>
       </c>
       <c r="F278" t="n">
         <v>0.0</v>
@@ -10348,7 +10348,7 @@
         <v>0.0</v>
       </c>
       <c r="H278" t="n">
-        <v>408.001</v>
+        <v>402.241</v>
       </c>
       <c r="I278" t="n">
         <v>0.0</v>
@@ -10376,7 +10376,7 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>585.239</v>
+        <v>581.399</v>
       </c>
       <c r="F279" t="n">
         <v>0.08</v>
@@ -10385,7 +10385,7 @@
         <v>0.0</v>
       </c>
       <c r="H279" t="n">
-        <v>585.239</v>
+        <v>581.399</v>
       </c>
       <c r="I279" t="n">
         <v>0.0</v>
@@ -10413,7 +10413,7 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>329.28</v>
+        <v>321.6</v>
       </c>
       <c r="F280" t="n">
         <v>0.0</v>
@@ -10422,7 +10422,7 @@
         <v>0.44</v>
       </c>
       <c r="H280" t="n">
-        <v>329.28</v>
+        <v>321.6</v>
       </c>
       <c r="I280" t="n">
         <v>0.0</v>
@@ -10524,7 +10524,7 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>3008.575</v>
+        <v>2435.194</v>
       </c>
       <c r="F283" t="n">
         <v>0.0</v>
@@ -10533,7 +10533,7 @@
         <v>18.752000000000002</v>
       </c>
       <c r="H283" t="n">
-        <v>3008.575</v>
+        <v>2435.194</v>
       </c>
       <c r="I283" t="n">
         <v>0.0</v>
@@ -10561,7 +10561,7 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>2362.8</v>
+        <v>2312.4</v>
       </c>
       <c r="F284" t="n">
         <v>0.0</v>
@@ -10570,7 +10570,7 @@
         <v>194.39999999999998</v>
       </c>
       <c r="H284" t="n">
-        <v>2362.8</v>
+        <v>2312.4</v>
       </c>
       <c r="I284" t="n">
         <v>0.0</v>
@@ -10598,7 +10598,7 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>4387.400000000001</v>
+        <v>4159.0</v>
       </c>
       <c r="F285" t="n">
         <v>0.2</v>
@@ -10607,7 +10607,7 @@
         <v>84.0</v>
       </c>
       <c r="H285" t="n">
-        <v>4387.400000000001</v>
+        <v>4159.0</v>
       </c>
       <c r="I285" t="n">
         <v>0.0</v>
@@ -10635,7 +10635,7 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>1312.758</v>
+        <v>967.91</v>
       </c>
       <c r="F286" t="n">
         <v>2.222</v>
@@ -10644,7 +10644,7 @@
         <v>18.665000000000003</v>
       </c>
       <c r="H286" t="n">
-        <v>1312.758</v>
+        <v>967.91</v>
       </c>
       <c r="I286" t="n">
         <v>0.0</v>
@@ -10672,7 +10672,7 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>4920.618</v>
+        <v>4730.864</v>
       </c>
       <c r="F287" t="n">
         <v>0.444</v>
@@ -10681,7 +10681,7 @@
         <v>383.96200000000005</v>
       </c>
       <c r="H287" t="n">
-        <v>4920.618</v>
+        <v>4730.864</v>
       </c>
       <c r="I287" t="n">
         <v>0.0</v>
@@ -10709,7 +10709,7 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>1208.3239999999998</v>
+        <v>1207.879</v>
       </c>
       <c r="F288" t="n">
         <v>0.889</v>
@@ -10718,7 +10718,7 @@
         <v>0.0</v>
       </c>
       <c r="H288" t="n">
-        <v>1208.3239999999998</v>
+        <v>1207.879</v>
       </c>
       <c r="I288" t="n">
         <v>0.0</v>
@@ -10746,7 +10746,7 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>3283.672</v>
+        <v>3097.023</v>
       </c>
       <c r="F289" t="n">
         <v>0.0</v>
@@ -10755,7 +10755,7 @@
         <v>351.965</v>
       </c>
       <c r="H289" t="n">
-        <v>3283.672</v>
+        <v>3097.023</v>
       </c>
       <c r="I289" t="n">
         <v>0.0</v>
@@ -11116,7 +11116,7 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>1541.0</v>
+        <v>1393.1999999999998</v>
       </c>
       <c r="F299" t="n">
         <v>0.8</v>
@@ -11125,7 +11125,7 @@
         <v>134.4</v>
       </c>
       <c r="H299" t="n">
-        <v>1541.0</v>
+        <v>1393.1999999999998</v>
       </c>
       <c r="I299" t="n">
         <v>0.0</v>
@@ -11190,7 +11190,7 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>141.2</v>
+        <v>66.2</v>
       </c>
       <c r="F301" t="n">
         <v>1.0</v>
@@ -11199,7 +11199,7 @@
         <v>136.8</v>
       </c>
       <c r="H301" t="n">
-        <v>141.2</v>
+        <v>66.2</v>
       </c>
       <c r="I301" t="n">
         <v>0.0</v>
@@ -11227,7 +11227,7 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>703.6</v>
+        <v>703.1999999999999</v>
       </c>
       <c r="F302" t="n">
         <v>0.2</v>
@@ -11236,7 +11236,7 @@
         <v>0.0</v>
       </c>
       <c r="H302" t="n">
-        <v>703.6</v>
+        <v>703.1999999999999</v>
       </c>
       <c r="I302" t="n">
         <v>0.0</v>
@@ -11264,7 +11264,7 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>214.92100000000002</v>
+        <v>213.854</v>
       </c>
       <c r="F303" t="n">
         <v>0.533</v>
@@ -11273,7 +11273,7 @@
         <v>0.0</v>
       </c>
       <c r="H303" t="n">
-        <v>214.92100000000002</v>
+        <v>213.854</v>
       </c>
       <c r="I303" t="n">
         <v>0.0</v>
@@ -11708,7 +11708,7 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>4974.8</v>
+        <v>4925.0</v>
       </c>
       <c r="F315" t="n">
         <v>0.0</v>
@@ -11717,7 +11717,7 @@
         <v>166.4</v>
       </c>
       <c r="H315" t="n">
-        <v>4974.8</v>
+        <v>4925.0</v>
       </c>
       <c r="I315" t="n">
         <v>0.0</v>
@@ -11745,7 +11745,7 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>99.727</v>
+        <v>99.194</v>
       </c>
       <c r="F316" t="n">
         <v>0.533</v>
@@ -11754,7 +11754,7 @@
         <v>0.0</v>
       </c>
       <c r="H316" t="n">
-        <v>99.727</v>
+        <v>99.194</v>
       </c>
       <c r="I316" t="n">
         <v>0.0</v>
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>12541.3</v>
+        <v>12541.034</v>
       </c>
       <c r="F320" t="n">
         <v>0.533</v>
@@ -11902,7 +11902,7 @@
         <v>0.0</v>
       </c>
       <c r="H320" t="n">
-        <v>12541.3</v>
+        <v>12541.034</v>
       </c>
       <c r="I320" t="n">
         <v>0.0</v>
@@ -11967,7 +11967,7 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>1417.8</v>
+        <v>492.8</v>
       </c>
       <c r="F322" t="n">
         <v>0.6</v>
@@ -11976,7 +11976,7 @@
         <v>6.4</v>
       </c>
       <c r="H322" t="n">
-        <v>1417.8</v>
+        <v>492.8</v>
       </c>
       <c r="I322" t="n">
         <v>0.0</v>
@@ -12041,7 +12041,7 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>5311.064</v>
+        <v>5310.797</v>
       </c>
       <c r="F324" t="n">
         <v>0.533</v>
@@ -12050,7 +12050,7 @@
         <v>0.0</v>
       </c>
       <c r="H324" t="n">
-        <v>5311.064</v>
+        <v>5310.797</v>
       </c>
       <c r="I324" t="n">
         <v>0.0</v>
@@ -12078,7 +12078,7 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>2195.7999999999997</v>
+        <v>2173.6000000000004</v>
       </c>
       <c r="F325" t="n">
         <v>1.4</v>
@@ -12087,7 +12087,7 @@
         <v>45.6</v>
       </c>
       <c r="H325" t="n">
-        <v>2195.7999999999997</v>
+        <v>2173.6000000000004</v>
       </c>
       <c r="I325" t="n">
         <v>0.0</v>
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>3269.1600000000003</v>
+        <v>2970.04</v>
       </c>
       <c r="F334" t="n">
         <v>0.0</v>
@@ -12420,7 +12420,7 @@
         <v>77.75999999999999</v>
       </c>
       <c r="H334" t="n">
-        <v>3269.1600000000003</v>
+        <v>2970.04</v>
       </c>
       <c r="I334" t="n">
         <v>0.0</v>
@@ -12448,7 +12448,7 @@
         </is>
       </c>
       <c r="E335" t="n">
-        <v>3401.552</v>
+        <v>3165.751</v>
       </c>
       <c r="F335" t="n">
         <v>0.45</v>
@@ -12457,7 +12457,7 @@
         <v>39.375</v>
       </c>
       <c r="H335" t="n">
-        <v>3401.552</v>
+        <v>3165.751</v>
       </c>
       <c r="I335" t="n">
         <v>0.0</v>
@@ -12485,7 +12485,7 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>2918.745</v>
+        <v>2819.446</v>
       </c>
       <c r="F336" t="n">
         <v>0.0</v>
@@ -12494,7 +12494,7 @@
         <v>88.245</v>
       </c>
       <c r="H336" t="n">
-        <v>2918.745</v>
+        <v>2819.446</v>
       </c>
       <c r="I336" t="n">
         <v>0.0</v>
@@ -12818,7 +12818,7 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>567.1</v>
+        <v>551.5</v>
       </c>
       <c r="F345" t="n">
         <v>0.0</v>
@@ -12827,7 +12827,7 @@
         <v>0.0</v>
       </c>
       <c r="H345" t="n">
-        <v>567.1</v>
+        <v>551.5</v>
       </c>
       <c r="I345" t="n">
         <v>0.0</v>
@@ -12892,7 +12892,7 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>917.8</v>
+        <v>897.4</v>
       </c>
       <c r="F347" t="n">
         <v>0.0</v>
@@ -12901,7 +12901,7 @@
         <v>3.0</v>
       </c>
       <c r="H347" t="n">
-        <v>917.8</v>
+        <v>897.4</v>
       </c>
       <c r="I347" t="n">
         <v>0.0</v>
@@ -12929,7 +12929,7 @@
         </is>
       </c>
       <c r="E348" t="n">
-        <v>367.8</v>
+        <v>361.8</v>
       </c>
       <c r="F348" t="n">
         <v>0.0</v>
@@ -12938,7 +12938,7 @@
         <v>0.1</v>
       </c>
       <c r="H348" t="n">
-        <v>367.8</v>
+        <v>361.8</v>
       </c>
       <c r="I348" t="n">
         <v>0.0</v>
@@ -13410,7 +13410,7 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>413.651</v>
+        <v>403.25</v>
       </c>
       <c r="F361" t="n">
         <v>19.202</v>
@@ -13419,7 +13419,7 @@
         <v>0.0</v>
       </c>
       <c r="H361" t="n">
-        <v>413.651</v>
+        <v>403.25</v>
       </c>
       <c r="I361" t="n">
         <v>0.0</v>
@@ -13558,7 +13558,7 @@
         </is>
       </c>
       <c r="E365" t="n">
-        <v>23767.942</v>
+        <v>23639.838</v>
       </c>
       <c r="F365" t="n">
         <v>0.111</v>
@@ -13567,7 +13567,7 @@
         <v>37.03</v>
       </c>
       <c r="H365" t="n">
-        <v>23767.942</v>
+        <v>23639.838</v>
       </c>
       <c r="I365" t="n">
         <v>0.0</v>
@@ -13632,7 +13632,7 @@
         </is>
       </c>
       <c r="E367" t="n">
-        <v>12540.079</v>
+        <v>12006.986</v>
       </c>
       <c r="F367" t="n">
         <v>0.0</v>
@@ -13641,7 +13641,7 @@
         <v>115.648</v>
       </c>
       <c r="H367" t="n">
-        <v>12540.079</v>
+        <v>12006.986</v>
       </c>
       <c r="I367" t="n">
         <v>0.0</v>
@@ -13669,7 +13669,7 @@
         </is>
       </c>
       <c r="E368" t="n">
-        <v>306.912</v>
+        <v>230.859</v>
       </c>
       <c r="F368" t="n">
         <v>0.0</v>
@@ -13678,7 +13678,7 @@
         <v>16.458000000000002</v>
       </c>
       <c r="H368" t="n">
-        <v>306.912</v>
+        <v>230.859</v>
       </c>
       <c r="I368" t="n">
         <v>0.0</v>
@@ -14039,7 +14039,7 @@
         </is>
       </c>
       <c r="E378" t="n">
-        <v>8296.383</v>
+        <v>8498.016</v>
       </c>
       <c r="F378" t="n">
         <v>0.0</v>
@@ -14048,7 +14048,7 @@
         <v>0.0</v>
       </c>
       <c r="H378" t="n">
-        <v>8296.383</v>
+        <v>8498.016</v>
       </c>
       <c r="I378" t="n">
         <v>0.0</v>
@@ -14224,7 +14224,7 @@
         </is>
       </c>
       <c r="E383" t="n">
-        <v>1656.12</v>
+        <v>1648.128</v>
       </c>
       <c r="F383" t="n">
         <v>0.0</v>
@@ -14233,7 +14233,7 @@
         <v>37.296</v>
       </c>
       <c r="H383" t="n">
-        <v>1656.12</v>
+        <v>1648.128</v>
       </c>
       <c r="I383" t="n">
         <v>0.0</v>
@@ -14409,7 +14409,7 @@
         </is>
       </c>
       <c r="E388" t="n">
-        <v>358.666</v>
+        <v>351.466</v>
       </c>
       <c r="F388" t="n">
         <v>40.0</v>
@@ -14418,7 +14418,7 @@
         <v>30.4</v>
       </c>
       <c r="H388" t="n">
-        <v>358.666</v>
+        <v>351.466</v>
       </c>
       <c r="I388" t="n">
         <v>0.0</v>
@@ -14557,7 +14557,7 @@
         </is>
       </c>
       <c r="E392" t="n">
-        <v>36.0</v>
+        <v>35.0</v>
       </c>
       <c r="F392" t="n">
         <v>0.0</v>
@@ -14566,7 +14566,7 @@
         <v>0.0</v>
       </c>
       <c r="H392" t="n">
-        <v>36.0</v>
+        <v>35.0</v>
       </c>
       <c r="I392" t="n">
         <v>0.0</v>
@@ -15223,7 +15223,7 @@
         </is>
       </c>
       <c r="E410" t="n">
-        <v>3181.249</v>
+        <v>2894.149</v>
       </c>
       <c r="F410" t="n">
         <v>0.2</v>
@@ -15232,7 +15232,7 @@
         <v>74.39999999999999</v>
       </c>
       <c r="H410" t="n">
-        <v>3181.249</v>
+        <v>2894.149</v>
       </c>
       <c r="I410" t="n">
         <v>0.0</v>
@@ -15260,7 +15260,7 @@
         </is>
       </c>
       <c r="E411" t="n">
-        <v>2567.3</v>
+        <v>2456.75</v>
       </c>
       <c r="F411" t="n">
         <v>0.0</v>
@@ -15269,7 +15269,7 @@
         <v>180.10000000000002</v>
       </c>
       <c r="H411" t="n">
-        <v>2567.3</v>
+        <v>2456.75</v>
       </c>
       <c r="I411" t="n">
         <v>0.0</v>
@@ -15297,7 +15297,7 @@
         </is>
       </c>
       <c r="E412" t="n">
-        <v>1097.65</v>
+        <v>984.9</v>
       </c>
       <c r="F412" t="n">
         <v>0.15</v>
@@ -15306,7 +15306,7 @@
         <v>101.1</v>
       </c>
       <c r="H412" t="n">
-        <v>1097.65</v>
+        <v>984.9</v>
       </c>
       <c r="I412" t="n">
         <v>0.0</v>
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="E413" t="n">
-        <v>1756.35</v>
+        <v>1711.8999999999999</v>
       </c>
       <c r="F413" t="n">
         <v>0.0</v>
@@ -15343,7 +15343,7 @@
         <v>163.5</v>
       </c>
       <c r="H413" t="n">
-        <v>1756.35</v>
+        <v>1711.8999999999999</v>
       </c>
       <c r="I413" t="n">
         <v>0.0</v>
@@ -15371,7 +15371,7 @@
         </is>
       </c>
       <c r="E414" t="n">
-        <v>2782.2999999999997</v>
+        <v>2656.2000000000003</v>
       </c>
       <c r="F414" t="n">
         <v>0.15</v>
@@ -15380,7 +15380,7 @@
         <v>31.2</v>
       </c>
       <c r="H414" t="n">
-        <v>2782.2999999999997</v>
+        <v>2656.2000000000003</v>
       </c>
       <c r="I414" t="n">
         <v>0.0</v>
@@ -15408,7 +15408,7 @@
         </is>
       </c>
       <c r="E415" t="n">
-        <v>3050.9</v>
+        <v>2899.4500000000003</v>
       </c>
       <c r="F415" t="n">
         <v>0.1</v>
@@ -15417,7 +15417,7 @@
         <v>0.0</v>
       </c>
       <c r="H415" t="n">
-        <v>3050.9</v>
+        <v>2899.4500000000003</v>
       </c>
       <c r="I415" t="n">
         <v>0.0</v>
@@ -15445,7 +15445,7 @@
         </is>
       </c>
       <c r="E416" t="n">
-        <v>10509.101</v>
+        <v>10316.001</v>
       </c>
       <c r="F416" t="n">
         <v>0.3</v>
@@ -15454,7 +15454,7 @@
         <v>0.0</v>
       </c>
       <c r="H416" t="n">
-        <v>10509.101</v>
+        <v>10316.001</v>
       </c>
       <c r="I416" t="n">
         <v>0.0</v>
@@ -15593,7 +15593,7 @@
         </is>
       </c>
       <c r="E420" t="n">
-        <v>4113.0</v>
+        <v>3834.0</v>
       </c>
       <c r="F420" t="n">
         <v>0.0</v>
@@ -15602,7 +15602,7 @@
         <v>4.75</v>
       </c>
       <c r="H420" t="n">
-        <v>4113.0</v>
+        <v>3834.0</v>
       </c>
       <c r="I420" t="n">
         <v>0.0</v>
@@ -15741,7 +15741,7 @@
         </is>
       </c>
       <c r="E424" t="n">
-        <v>372.5</v>
+        <v>370.1</v>
       </c>
       <c r="F424" t="n">
         <v>0.0</v>
@@ -15750,7 +15750,7 @@
         <v>0.0</v>
       </c>
       <c r="H424" t="n">
-        <v>372.5</v>
+        <v>370.1</v>
       </c>
       <c r="I424" t="n">
         <v>0.0</v>
@@ -15815,7 +15815,7 @@
         </is>
       </c>
       <c r="E426" t="n">
-        <v>342.0</v>
+        <v>162.0</v>
       </c>
       <c r="F426" t="n">
         <v>0.0</v>
@@ -15824,7 +15824,7 @@
         <v>0.0</v>
       </c>
       <c r="H426" t="n">
-        <v>342.0</v>
+        <v>162.0</v>
       </c>
       <c r="I426" t="n">
         <v>0.0</v>
@@ -16148,7 +16148,7 @@
         </is>
       </c>
       <c r="E435" t="n">
-        <v>1108.229</v>
+        <v>1344.1466</v>
       </c>
       <c r="F435" t="n">
         <v>61.196</v>
@@ -16157,10 +16157,10 @@
         <v>4.107</v>
       </c>
       <c r="H435" t="n">
-        <v>1108.229</v>
+        <v>855.366</v>
       </c>
       <c r="I435" t="n">
-        <v>0.0</v>
+        <v>488.7806</v>
       </c>
     </row>
     <row r="436">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="E436" t="n">
-        <v>1465.319</v>
+        <v>7728.7649</v>
       </c>
       <c r="F436" t="n">
         <v>191.516</v>
@@ -16194,10 +16194,10 @@
         <v>2.054</v>
       </c>
       <c r="H436" t="n">
-        <v>1465.319</v>
+        <v>218.38400000000001</v>
       </c>
       <c r="I436" t="n">
-        <v>0.0</v>
+        <v>7510.3809</v>
       </c>
     </row>
     <row r="437">
@@ -16259,7 +16259,7 @@
         </is>
       </c>
       <c r="E438" t="n">
-        <v>2164.8610000000003</v>
+        <v>2144.9230000000002</v>
       </c>
       <c r="F438" t="n">
         <v>0.0</v>
@@ -16268,7 +16268,7 @@
         <v>2.054</v>
       </c>
       <c r="H438" t="n">
-        <v>2164.8610000000003</v>
+        <v>2144.9230000000002</v>
       </c>
       <c r="I438" t="n">
         <v>0.0</v>
@@ -16296,7 +16296,7 @@
         </is>
       </c>
       <c r="E439" t="n">
-        <v>784.1329999999999</v>
+        <v>1171.067</v>
       </c>
       <c r="F439" t="n">
         <v>0.0</v>
@@ -16305,10 +16305,10 @@
         <v>395.806</v>
       </c>
       <c r="H439" t="n">
-        <v>784.1329999999999</v>
+        <v>526.952</v>
       </c>
       <c r="I439" t="n">
-        <v>0.0</v>
+        <v>644.115</v>
       </c>
     </row>
     <row r="440">
@@ -16407,7 +16407,7 @@
         </is>
       </c>
       <c r="E442" t="n">
-        <v>2489.635</v>
+        <v>2347.7419999999997</v>
       </c>
       <c r="F442" t="n">
         <v>0.0</v>
@@ -16416,7 +16416,7 @@
         <v>191.83700000000002</v>
       </c>
       <c r="H442" t="n">
-        <v>2489.635</v>
+        <v>2347.7419999999997</v>
       </c>
       <c r="I442" t="n">
         <v>0.0</v>
@@ -16444,7 +16444,7 @@
         </is>
       </c>
       <c r="E443" t="n">
-        <v>9956.243</v>
+        <v>9190.304</v>
       </c>
       <c r="F443" t="n">
         <v>6.069</v>
@@ -16453,7 +16453,7 @@
         <v>148.894</v>
       </c>
       <c r="H443" t="n">
-        <v>9956.243</v>
+        <v>9190.304</v>
       </c>
       <c r="I443" t="n">
         <v>0.0</v>
@@ -16481,7 +16481,7 @@
         </is>
       </c>
       <c r="E444" t="n">
-        <v>17327.157000000003</v>
+        <v>25128.417499999996</v>
       </c>
       <c r="F444" t="n">
         <v>3.733</v>
@@ -16490,10 +16490,10 @@
         <v>50.879</v>
       </c>
       <c r="H444" t="n">
-        <v>17327.157000000003</v>
+        <v>16679.308999999997</v>
       </c>
       <c r="I444" t="n">
-        <v>0.0</v>
+        <v>8449.1085</v>
       </c>
     </row>
     <row r="445">
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="E446" t="n">
-        <v>2180.875</v>
+        <v>2134.4900000000002</v>
       </c>
       <c r="F446" t="n">
         <v>294.922</v>
@@ -16564,7 +16564,7 @@
         <v>79.056</v>
       </c>
       <c r="H446" t="n">
-        <v>2180.875</v>
+        <v>2134.4900000000002</v>
       </c>
       <c r="I446" t="n">
         <v>0.0</v>
@@ -16592,7 +16592,7 @@
         </is>
       </c>
       <c r="E447" t="n">
-        <v>1428.778</v>
+        <v>2319.337</v>
       </c>
       <c r="F447" t="n">
         <v>1.6800000000000002</v>
@@ -16604,7 +16604,7 @@
         <v>1428.778</v>
       </c>
       <c r="I447" t="n">
-        <v>0.0</v>
+        <v>890.559</v>
       </c>
     </row>
     <row r="448">
@@ -16666,7 +16666,7 @@
         </is>
       </c>
       <c r="E449" t="n">
-        <v>1091.601</v>
+        <v>1064.47</v>
       </c>
       <c r="F449" t="n">
         <v>0.0</v>
@@ -16675,7 +16675,7 @@
         <v>73.80499999999999</v>
       </c>
       <c r="H449" t="n">
-        <v>1091.601</v>
+        <v>1064.47</v>
       </c>
       <c r="I449" t="n">
         <v>0.0</v>
@@ -16703,7 +16703,7 @@
         </is>
       </c>
       <c r="E450" t="n">
-        <v>7808.9580000000005</v>
+        <v>7444.605</v>
       </c>
       <c r="F450" t="n">
         <v>380.69399999999996</v>
@@ -16712,7 +16712,7 @@
         <v>0.292</v>
       </c>
       <c r="H450" t="n">
-        <v>7808.9580000000005</v>
+        <v>7444.605</v>
       </c>
       <c r="I450" t="n">
         <v>0.0</v>
@@ -16740,7 +16740,7 @@
         </is>
       </c>
       <c r="E451" t="n">
-        <v>1463.816</v>
+        <v>1427.3529999999998</v>
       </c>
       <c r="F451" t="n">
         <v>0.0</v>
@@ -16749,7 +16749,7 @@
         <v>19.253</v>
       </c>
       <c r="H451" t="n">
-        <v>1463.816</v>
+        <v>1427.3529999999998</v>
       </c>
       <c r="I451" t="n">
         <v>0.0</v>
@@ -16814,7 +16814,7 @@
         </is>
       </c>
       <c r="E453" t="n">
-        <v>3345.65</v>
+        <v>3100.9030000000002</v>
       </c>
       <c r="F453" t="n">
         <v>0.0</v>
@@ -16823,7 +16823,7 @@
         <v>0.0</v>
       </c>
       <c r="H453" t="n">
-        <v>3345.65</v>
+        <v>3100.9030000000002</v>
       </c>
       <c r="I453" t="n">
         <v>0.0</v>
@@ -17073,7 +17073,7 @@
         </is>
       </c>
       <c r="E460" t="n">
-        <v>374.91</v>
+        <v>333.31</v>
       </c>
       <c r="F460" t="n">
         <v>0.0</v>
@@ -17082,7 +17082,7 @@
         <v>3.2</v>
       </c>
       <c r="H460" t="n">
-        <v>374.91</v>
+        <v>333.31</v>
       </c>
       <c r="I460" t="n">
         <v>0.0</v>
@@ -17258,7 +17258,7 @@
         </is>
       </c>
       <c r="E465" t="n">
-        <v>720.809</v>
+        <v>719.542</v>
       </c>
       <c r="F465" t="n">
         <v>1.267</v>
@@ -17267,7 +17267,7 @@
         <v>0.0</v>
       </c>
       <c r="H465" t="n">
-        <v>720.809</v>
+        <v>719.542</v>
       </c>
       <c r="I465" t="n">
         <v>0.0</v>
@@ -17480,7 +17480,7 @@
         </is>
       </c>
       <c r="E471" t="n">
-        <v>1190.708</v>
+        <v>1138.712</v>
       </c>
       <c r="F471" t="n">
         <v>135.19</v>
@@ -17489,7 +17489,7 @@
         <v>561.557</v>
       </c>
       <c r="H471" t="n">
-        <v>1190.708</v>
+        <v>1138.712</v>
       </c>
       <c r="I471" t="n">
         <v>0.0</v>
@@ -17554,7 +17554,7 @@
         </is>
       </c>
       <c r="E473" t="n">
-        <v>3989.398</v>
+        <v>3869.386</v>
       </c>
       <c r="F473" t="n">
         <v>0.0</v>
@@ -17563,7 +17563,7 @@
         <v>642.064</v>
       </c>
       <c r="H473" t="n">
-        <v>3989.398</v>
+        <v>3869.386</v>
       </c>
       <c r="I473" t="n">
         <v>0.0</v>
@@ -17702,7 +17702,7 @@
         </is>
       </c>
       <c r="E477" t="n">
-        <v>1792.0140000000001</v>
+        <v>1774.464</v>
       </c>
       <c r="F477" t="n">
         <v>0.0</v>
@@ -17711,7 +17711,7 @@
         <v>105.30000000000001</v>
       </c>
       <c r="H477" t="n">
-        <v>1792.0140000000001</v>
+        <v>1774.464</v>
       </c>
       <c r="I477" t="n">
         <v>0.0</v>
@@ -17813,7 +17813,7 @@
         </is>
       </c>
       <c r="E480" t="n">
-        <v>140.832</v>
+        <v>122.42399999999999</v>
       </c>
       <c r="F480" t="n">
         <v>0.13899999999999998</v>
@@ -17822,7 +17822,7 @@
         <v>582.75</v>
       </c>
       <c r="H480" t="n">
-        <v>140.832</v>
+        <v>122.42399999999999</v>
       </c>
       <c r="I480" t="n">
         <v>0.0</v>
@@ -17850,7 +17850,7 @@
         </is>
       </c>
       <c r="E481" t="n">
-        <v>1516.28</v>
+        <v>1399.68</v>
       </c>
       <c r="F481" t="n">
         <v>0.12000000000000001</v>
@@ -17859,7 +17859,7 @@
         <v>178.07999999999998</v>
       </c>
       <c r="H481" t="n">
-        <v>1516.28</v>
+        <v>1399.68</v>
       </c>
       <c r="I481" t="n">
         <v>0.0</v>
@@ -17887,7 +17887,7 @@
         </is>
       </c>
       <c r="E482" t="n">
-        <v>83.28</v>
+        <v>70.881</v>
       </c>
       <c r="F482" t="n">
         <v>0.0</v>
@@ -17896,7 +17896,7 @@
         <v>708.0</v>
       </c>
       <c r="H482" t="n">
-        <v>83.28</v>
+        <v>70.881</v>
       </c>
       <c r="I482" t="n">
         <v>0.0</v>
@@ -17924,7 +17924,7 @@
         </is>
       </c>
       <c r="E483" t="n">
-        <v>1783.076</v>
+        <v>1761.108</v>
       </c>
       <c r="F483" t="n">
         <v>0.13899999999999998</v>
@@ -17933,7 +17933,7 @@
         <v>5.55</v>
       </c>
       <c r="H483" t="n">
-        <v>1783.076</v>
+        <v>1761.108</v>
       </c>
       <c r="I483" t="n">
         <v>0.0</v>
@@ -17961,7 +17961,7 @@
         </is>
       </c>
       <c r="E484" t="n">
-        <v>213.44</v>
+        <v>183.92</v>
       </c>
       <c r="F484" t="n">
         <v>0.0</v>
@@ -17970,7 +17970,7 @@
         <v>62.4</v>
       </c>
       <c r="H484" t="n">
-        <v>213.44</v>
+        <v>183.92</v>
       </c>
       <c r="I484" t="n">
         <v>0.0</v>
@@ -17998,7 +17998,7 @@
         </is>
       </c>
       <c r="E485" t="n">
-        <v>2877.582</v>
+        <v>2697.438</v>
       </c>
       <c r="F485" t="n">
         <v>0.231</v>
@@ -18007,7 +18007,7 @@
         <v>155.955</v>
       </c>
       <c r="H485" t="n">
-        <v>2877.582</v>
+        <v>2697.438</v>
       </c>
       <c r="I485" t="n">
         <v>0.0</v>
@@ -18035,7 +18035,7 @@
         </is>
       </c>
       <c r="E486" t="n">
-        <v>367.48</v>
+        <v>318.4</v>
       </c>
       <c r="F486" t="n">
         <v>0.0</v>
@@ -18044,7 +18044,7 @@
         <v>110.88000000000001</v>
       </c>
       <c r="H486" t="n">
-        <v>367.48</v>
+        <v>318.4</v>
       </c>
       <c r="I486" t="n">
         <v>0.0</v>
@@ -18072,7 +18072,7 @@
         </is>
       </c>
       <c r="E487" t="n">
-        <v>1196.9969999999998</v>
+        <v>1150.5159999999998</v>
       </c>
       <c r="F487" t="n">
         <v>0.231</v>
@@ -18081,7 +18081,7 @@
         <v>24.42</v>
       </c>
       <c r="H487" t="n">
-        <v>1196.9969999999998</v>
+        <v>1150.5159999999998</v>
       </c>
       <c r="I487" t="n">
         <v>0.0</v>
@@ -18257,7 +18257,7 @@
         </is>
       </c>
       <c r="E492" t="n">
-        <v>11833.259</v>
+        <v>11838.5926</v>
       </c>
       <c r="F492" t="n">
         <v>50.336</v>
@@ -18269,7 +18269,7 @@
         <v>11833.259</v>
       </c>
       <c r="I492" t="n">
-        <v>0.0</v>
+        <v>5.3336</v>
       </c>
     </row>
     <row r="493">
@@ -18331,7 +18331,7 @@
         </is>
       </c>
       <c r="E494" t="n">
-        <v>5535.215</v>
+        <v>5523.9710000000005</v>
       </c>
       <c r="F494" t="n">
         <v>26.576999999999998</v>
@@ -18340,7 +18340,7 @@
         <v>49.065999999999995</v>
       </c>
       <c r="H494" t="n">
-        <v>5535.215</v>
+        <v>5523.9710000000005</v>
       </c>
       <c r="I494" t="n">
         <v>0.0</v>
@@ -18368,7 +18368,7 @@
         </is>
       </c>
       <c r="E495" t="n">
-        <v>3695.6</v>
+        <v>11560.0</v>
       </c>
       <c r="F495" t="n">
         <v>26.8</v>
@@ -18377,10 +18377,10 @@
         <v>340.0</v>
       </c>
       <c r="H495" t="n">
-        <v>3695.6</v>
+        <v>3246.3999999999996</v>
       </c>
       <c r="I495" t="n">
-        <v>0.0</v>
+        <v>8313.6</v>
       </c>
     </row>
     <row r="496">
@@ -18553,7 +18553,7 @@
         </is>
       </c>
       <c r="E500" t="n">
-        <v>1174.8</v>
+        <v>1162.8</v>
       </c>
       <c r="F500" t="n">
         <v>0.0</v>
@@ -18562,7 +18562,7 @@
         <v>0.8</v>
       </c>
       <c r="H500" t="n">
-        <v>1174.8</v>
+        <v>1162.8</v>
       </c>
       <c r="I500" t="n">
         <v>0.0</v>
@@ -18997,7 +18997,7 @@
         </is>
       </c>
       <c r="E512" t="n">
-        <v>2291.718</v>
+        <v>2272.062</v>
       </c>
       <c r="F512" t="n">
         <v>0.0</v>
@@ -19006,7 +19006,7 @@
         <v>9.165</v>
       </c>
       <c r="H512" t="n">
-        <v>2291.718</v>
+        <v>2272.062</v>
       </c>
       <c r="I512" t="n">
         <v>0.0</v>
@@ -19034,7 +19034,7 @@
         </is>
       </c>
       <c r="E513" t="n">
-        <v>3073.9</v>
+        <v>2830.944</v>
       </c>
       <c r="F513" t="n">
         <v>0.0</v>
@@ -19043,7 +19043,7 @@
         <v>6.793</v>
       </c>
       <c r="H513" t="n">
-        <v>3073.9</v>
+        <v>2830.944</v>
       </c>
       <c r="I513" t="n">
         <v>0.0</v>
@@ -19071,7 +19071,7 @@
         </is>
       </c>
       <c r="E514" t="n">
-        <v>891.277</v>
+        <v>862.421</v>
       </c>
       <c r="F514" t="n">
         <v>0.0</v>
@@ -19080,7 +19080,7 @@
         <v>19.855999999999998</v>
       </c>
       <c r="H514" t="n">
-        <v>891.277</v>
+        <v>862.421</v>
       </c>
       <c r="I514" t="n">
         <v>0.0</v>
@@ -19404,7 +19404,7 @@
         </is>
       </c>
       <c r="E523" t="n">
-        <v>840.0</v>
+        <v>822.0</v>
       </c>
       <c r="F523" t="n">
         <v>0.0</v>
@@ -19413,7 +19413,7 @@
         <v>0.0</v>
       </c>
       <c r="H523" t="n">
-        <v>840.0</v>
+        <v>822.0</v>
       </c>
       <c r="I523" t="n">
         <v>0.0</v>
@@ -19441,7 +19441,7 @@
         </is>
       </c>
       <c r="E524" t="n">
-        <v>765.0</v>
+        <v>735.0</v>
       </c>
       <c r="F524" t="n">
         <v>0.0</v>
@@ -19450,7 +19450,7 @@
         <v>0.5</v>
       </c>
       <c r="H524" t="n">
-        <v>765.0</v>
+        <v>735.0</v>
       </c>
       <c r="I524" t="n">
         <v>0.0</v>
@@ -19959,7 +19959,7 @@
         </is>
       </c>
       <c r="E538" t="n">
-        <v>1064.6909999999998</v>
+        <v>1045.146</v>
       </c>
       <c r="F538" t="n">
         <v>43.153</v>
@@ -19968,7 +19968,7 @@
         <v>0.313</v>
       </c>
       <c r="H538" t="n">
-        <v>1064.6909999999998</v>
+        <v>1045.146</v>
       </c>
       <c r="I538" t="n">
         <v>0.0</v>
@@ -20033,7 +20033,7 @@
         </is>
       </c>
       <c r="E540" t="n">
-        <v>2004.882</v>
+        <v>1959.8120000000001</v>
       </c>
       <c r="F540" t="n">
         <v>2663.3019999999997</v>
@@ -20042,7 +20042,7 @@
         <v>2297.6549999999997</v>
       </c>
       <c r="H540" t="n">
-        <v>2004.882</v>
+        <v>1959.8120000000001</v>
       </c>
       <c r="I540" t="n">
         <v>0.0</v>
@@ -20218,7 +20218,7 @@
         </is>
       </c>
       <c r="E545" t="n">
-        <v>232.0</v>
+        <v>196.0</v>
       </c>
       <c r="F545" t="n">
         <v>0.0</v>
@@ -20227,7 +20227,7 @@
         <v>1.5</v>
       </c>
       <c r="H545" t="n">
-        <v>232.0</v>
+        <v>196.0</v>
       </c>
       <c r="I545" t="n">
         <v>0.0</v>
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="E551" t="n">
-        <v>5333.096</v>
+        <v>5200.4898</v>
       </c>
       <c r="F551" t="n">
         <v>30.912</v>
@@ -20449,10 +20449,10 @@
         <v>211.041</v>
       </c>
       <c r="H551" t="n">
-        <v>5333.096</v>
+        <v>4986.126</v>
       </c>
       <c r="I551" t="n">
-        <v>0.0</v>
+        <v>214.3638</v>
       </c>
     </row>
     <row r="552">
@@ -20477,7 +20477,7 @@
         </is>
       </c>
       <c r="E552" t="n">
-        <v>2589.3779999999997</v>
+        <v>4647.946</v>
       </c>
       <c r="F552" t="n">
         <v>14.059000000000001</v>
@@ -20486,10 +20486,10 @@
         <v>85.086</v>
       </c>
       <c r="H552" t="n">
-        <v>2589.3779999999997</v>
+        <v>2341.333</v>
       </c>
       <c r="I552" t="n">
-        <v>0.0</v>
+        <v>2306.6130000000003</v>
       </c>
     </row>
     <row r="553">
@@ -20958,7 +20958,7 @@
         </is>
       </c>
       <c r="E565" t="n">
-        <v>993.0</v>
+        <v>977.0</v>
       </c>
       <c r="F565" t="n">
         <v>0.0</v>
@@ -20967,7 +20967,7 @@
         <v>0.0</v>
       </c>
       <c r="H565" t="n">
-        <v>993.0</v>
+        <v>977.0</v>
       </c>
       <c r="I565" t="n">
         <v>0.0</v>
@@ -21254,7 +21254,7 @@
         </is>
       </c>
       <c r="E573" t="n">
-        <v>1944.0</v>
+        <v>1934.0</v>
       </c>
       <c r="F573" t="n">
         <v>0.0</v>
@@ -21263,7 +21263,7 @@
         <v>32.0</v>
       </c>
       <c r="H573" t="n">
-        <v>1944.0</v>
+        <v>1934.0</v>
       </c>
       <c r="I573" t="n">
         <v>0.0</v>
@@ -21476,7 +21476,7 @@
         </is>
       </c>
       <c r="E579" t="n">
-        <v>116.31</v>
+        <v>116.31099999999999</v>
       </c>
       <c r="F579" t="n">
         <v>0.0</v>
@@ -21485,7 +21485,7 @@
         <v>0.0</v>
       </c>
       <c r="H579" t="n">
-        <v>116.31</v>
+        <v>116.31099999999999</v>
       </c>
       <c r="I579" t="n">
         <v>0.0</v>
@@ -21513,7 +21513,7 @@
         </is>
       </c>
       <c r="E580" t="n">
-        <v>6062.920999999999</v>
+        <v>5551.524</v>
       </c>
       <c r="F580" t="n">
         <v>0.0</v>
@@ -21522,7 +21522,7 @@
         <v>5.539</v>
       </c>
       <c r="H580" t="n">
-        <v>6062.920999999999</v>
+        <v>5551.524</v>
       </c>
       <c r="I580" t="n">
         <v>0.0</v>
@@ -21587,7 +21587,7 @@
         </is>
       </c>
       <c r="E582" t="n">
-        <v>1344.034</v>
+        <v>1325.573</v>
       </c>
       <c r="F582" t="n">
         <v>0.0</v>
@@ -21596,7 +21596,7 @@
         <v>1.846</v>
       </c>
       <c r="H582" t="n">
-        <v>1344.034</v>
+        <v>1325.573</v>
       </c>
       <c r="I582" t="n">
         <v>0.0</v>
@@ -21661,7 +21661,7 @@
         </is>
       </c>
       <c r="E584" t="n">
-        <v>1605.423</v>
+        <v>1425.9789999999998</v>
       </c>
       <c r="F584" t="n">
         <v>0.0</v>
@@ -21670,7 +21670,7 @@
         <v>0.0</v>
       </c>
       <c r="H584" t="n">
-        <v>1605.423</v>
+        <v>1425.9789999999998</v>
       </c>
       <c r="I584" t="n">
         <v>0.0</v>
@@ -21698,7 +21698,7 @@
         </is>
       </c>
       <c r="E585" t="n">
-        <v>2010.05</v>
+        <v>1775.1209999999999</v>
       </c>
       <c r="F585" t="n">
         <v>0.0</v>
@@ -21707,7 +21707,7 @@
         <v>9.231</v>
       </c>
       <c r="H585" t="n">
-        <v>2010.05</v>
+        <v>1775.1209999999999</v>
       </c>
       <c r="I585" t="n">
         <v>0.0</v>
@@ -22068,7 +22068,7 @@
         </is>
       </c>
       <c r="E595" t="n">
-        <v>2327.304</v>
+        <v>1711.3449999999998</v>
       </c>
       <c r="F595" t="n">
         <v>0.0</v>
@@ -22077,7 +22077,7 @@
         <v>1050.859</v>
       </c>
       <c r="H595" t="n">
-        <v>2327.304</v>
+        <v>1711.3449999999998</v>
       </c>
       <c r="I595" t="n">
         <v>0.0</v>
@@ -22105,7 +22105,7 @@
         </is>
       </c>
       <c r="E596" t="n">
-        <v>135.498</v>
+        <v>121.742</v>
       </c>
       <c r="F596" t="n">
         <v>0.0</v>
@@ -22114,7 +22114,7 @@
         <v>386.37899999999996</v>
       </c>
       <c r="H596" t="n">
-        <v>135.498</v>
+        <v>121.742</v>
       </c>
       <c r="I596" t="n">
         <v>0.0</v>
@@ -22179,7 +22179,7 @@
         </is>
       </c>
       <c r="E598" t="n">
-        <v>6242.201</v>
+        <v>5888.059</v>
       </c>
       <c r="F598" t="n">
         <v>0.0</v>
@@ -22188,7 +22188,7 @@
         <v>3.7279999999999998</v>
       </c>
       <c r="H598" t="n">
-        <v>6242.201</v>
+        <v>5888.059</v>
       </c>
       <c r="I598" t="n">
         <v>0.0</v>
@@ -22216,7 +22216,7 @@
         </is>
       </c>
       <c r="E599" t="n">
-        <v>6933.687</v>
+        <v>6657.513</v>
       </c>
       <c r="F599" t="n">
         <v>2.5149999999999997</v>
@@ -22225,7 +22225,7 @@
         <v>468.626</v>
       </c>
       <c r="H599" t="n">
-        <v>6933.687</v>
+        <v>6657.513</v>
       </c>
       <c r="I599" t="n">
         <v>0.0</v>
@@ -22290,7 +22290,7 @@
         </is>
       </c>
       <c r="E601" t="n">
-        <v>59.022999999999996</v>
+        <v>40.827</v>
       </c>
       <c r="F601" t="n">
         <v>0.0</v>
@@ -22299,7 +22299,7 @@
         <v>0.888</v>
       </c>
       <c r="H601" t="n">
-        <v>59.022999999999996</v>
+        <v>40.827</v>
       </c>
       <c r="I601" t="n">
         <v>0.0</v>
@@ -22327,7 +22327,7 @@
         </is>
       </c>
       <c r="E602" t="n">
-        <v>510.408</v>
+        <v>366.96</v>
       </c>
       <c r="F602" t="n">
         <v>0.0</v>
@@ -22336,7 +22336,7 @@
         <v>0.5</v>
       </c>
       <c r="H602" t="n">
-        <v>510.408</v>
+        <v>366.96</v>
       </c>
       <c r="I602" t="n">
         <v>0.0</v>
@@ -22364,7 +22364,7 @@
         </is>
       </c>
       <c r="E603" t="n">
-        <v>5750.308</v>
+        <v>5885.765</v>
       </c>
       <c r="F603" t="n">
         <v>1.067</v>
@@ -22373,7 +22373,7 @@
         <v>886.345</v>
       </c>
       <c r="H603" t="n">
-        <v>5750.308</v>
+        <v>5885.765</v>
       </c>
       <c r="I603" t="n">
         <v>0.0</v>
@@ -23215,7 +23215,7 @@
         </is>
       </c>
       <c r="E626" t="n">
-        <v>66.0</v>
+        <v>65.6</v>
       </c>
       <c r="F626" t="n">
         <v>0.4</v>
@@ -23224,7 +23224,7 @@
         <v>0.0</v>
       </c>
       <c r="H626" t="n">
-        <v>66.0</v>
+        <v>65.6</v>
       </c>
       <c r="I626" t="n">
         <v>0.0</v>
@@ -23511,7 +23511,7 @@
         </is>
       </c>
       <c r="E634" t="n">
-        <v>3747.416</v>
+        <v>3597.386</v>
       </c>
       <c r="F634" t="n">
         <v>0.0</v>
@@ -23520,7 +23520,7 @@
         <v>0.0</v>
       </c>
       <c r="H634" t="n">
-        <v>3747.416</v>
+        <v>3597.386</v>
       </c>
       <c r="I634" t="n">
         <v>0.0</v>
@@ -23918,7 +23918,7 @@
         </is>
       </c>
       <c r="E645" t="n">
-        <v>1100.22</v>
+        <v>1065.548</v>
       </c>
       <c r="F645" t="n">
         <v>0.0</v>
@@ -23927,7 +23927,7 @@
         <v>0.16699999999999998</v>
       </c>
       <c r="H645" t="n">
-        <v>1100.22</v>
+        <v>1065.548</v>
       </c>
       <c r="I645" t="n">
         <v>0.0</v>
@@ -23955,7 +23955,7 @@
         </is>
       </c>
       <c r="E646" t="n">
-        <v>9615.018</v>
+        <v>9655.051</v>
       </c>
       <c r="F646" t="n">
         <v>0.0</v>
@@ -23964,7 +23964,7 @@
         <v>25.354000000000003</v>
       </c>
       <c r="H646" t="n">
-        <v>9615.018</v>
+        <v>9655.051</v>
       </c>
       <c r="I646" t="n">
         <v>0.0</v>
@@ -23992,7 +23992,7 @@
         </is>
       </c>
       <c r="E647" t="n">
-        <v>1577.902</v>
+        <v>1574.569</v>
       </c>
       <c r="F647" t="n">
         <v>0.8</v>
@@ -24001,7 +24001,7 @@
         <v>0.0</v>
       </c>
       <c r="H647" t="n">
-        <v>1577.902</v>
+        <v>1574.569</v>
       </c>
       <c r="I647" t="n">
         <v>0.0</v>
@@ -24177,7 +24177,7 @@
         </is>
       </c>
       <c r="E652" t="n">
-        <v>1977.5</v>
+        <v>1968.5</v>
       </c>
       <c r="F652" t="n">
         <v>0.0</v>
@@ -24186,7 +24186,7 @@
         <v>18.0</v>
       </c>
       <c r="H652" t="n">
-        <v>1977.5</v>
+        <v>1968.5</v>
       </c>
       <c r="I652" t="n">
         <v>0.0</v>
@@ -24214,7 +24214,7 @@
         </is>
       </c>
       <c r="E653" t="n">
-        <v>6249.496</v>
+        <v>6149.416</v>
       </c>
       <c r="F653" t="n">
         <v>0.0</v>
@@ -24223,7 +24223,7 @@
         <v>65.05199999999999</v>
       </c>
       <c r="H653" t="n">
-        <v>6249.496</v>
+        <v>6149.416</v>
       </c>
       <c r="I653" t="n">
         <v>0.0</v>
@@ -24251,7 +24251,7 @@
         </is>
       </c>
       <c r="E654" t="n">
-        <v>1328.84</v>
+        <v>1256.56</v>
       </c>
       <c r="F654" t="n">
         <v>0.0</v>
@@ -24260,7 +24260,7 @@
         <v>0.0</v>
       </c>
       <c r="H654" t="n">
-        <v>1328.84</v>
+        <v>1256.56</v>
       </c>
       <c r="I654" t="n">
         <v>0.0</v>
@@ -24362,7 +24362,7 @@
         </is>
       </c>
       <c r="E657" t="n">
-        <v>12.923</v>
+        <v>10.154</v>
       </c>
       <c r="F657" t="n">
         <v>0.923</v>
@@ -24371,7 +24371,7 @@
         <v>1524.961</v>
       </c>
       <c r="H657" t="n">
-        <v>12.923</v>
+        <v>10.154</v>
       </c>
       <c r="I657" t="n">
         <v>0.0</v>
@@ -24547,7 +24547,7 @@
         </is>
       </c>
       <c r="E662" t="n">
-        <v>1546.111</v>
+        <v>1022.0110000000001</v>
       </c>
       <c r="F662" t="n">
         <v>1.7730000000000001</v>
@@ -24556,7 +24556,7 @@
         <v>179.285</v>
       </c>
       <c r="H662" t="n">
-        <v>1546.111</v>
+        <v>1022.0110000000001</v>
       </c>
       <c r="I662" t="n">
         <v>0.0</v>
@@ -24769,7 +24769,7 @@
         </is>
       </c>
       <c r="E668" t="n">
-        <v>8.431</v>
+        <v>8.432</v>
       </c>
       <c r="F668" t="n">
         <v>1.035</v>
@@ -24778,7 +24778,7 @@
         <v>142.00799999999998</v>
       </c>
       <c r="H668" t="n">
-        <v>8.431</v>
+        <v>8.432</v>
       </c>
       <c r="I668" t="n">
         <v>0.0</v>
@@ -24991,7 +24991,7 @@
         </is>
       </c>
       <c r="E674" t="n">
-        <v>1302.866</v>
+        <v>930.086</v>
       </c>
       <c r="F674" t="n">
         <v>0.0</v>
@@ -25000,7 +25000,7 @@
         <v>0.0</v>
       </c>
       <c r="H674" t="n">
-        <v>1302.866</v>
+        <v>930.086</v>
       </c>
       <c r="I674" t="n">
         <v>0.0</v>
@@ -25028,7 +25028,7 @@
         </is>
       </c>
       <c r="E675" t="n">
-        <v>840.619</v>
+        <v>766.063</v>
       </c>
       <c r="F675" t="n">
         <v>0.0</v>
@@ -25037,7 +25037,7 @@
         <v>0.0</v>
       </c>
       <c r="H675" t="n">
-        <v>840.619</v>
+        <v>766.063</v>
       </c>
       <c r="I675" t="n">
         <v>0.0</v>
@@ -25102,7 +25102,7 @@
         </is>
       </c>
       <c r="E677" t="n">
-        <v>12814.313</v>
+        <v>10928.045</v>
       </c>
       <c r="F677" t="n">
         <v>0.0</v>
@@ -25111,7 +25111,7 @@
         <v>3.7279999999999998</v>
       </c>
       <c r="H677" t="n">
-        <v>12814.313</v>
+        <v>10928.045</v>
       </c>
       <c r="I677" t="n">
         <v>0.0</v>
@@ -25361,7 +25361,7 @@
         </is>
       </c>
       <c r="E684" t="n">
-        <v>2879.225</v>
+        <v>2877.0469999999996</v>
       </c>
       <c r="F684" t="n">
         <v>0.312</v>
@@ -25370,7 +25370,7 @@
         <v>0.0</v>
       </c>
       <c r="H684" t="n">
-        <v>2879.225</v>
+        <v>2877.0469999999996</v>
       </c>
       <c r="I684" t="n">
         <v>0.0</v>
@@ -25398,7 +25398,7 @@
         </is>
       </c>
       <c r="E685" t="n">
-        <v>3661.183</v>
+        <v>3649.981</v>
       </c>
       <c r="F685" t="n">
         <v>3734.0</v>
@@ -25407,7 +25407,7 @@
         <v>0.0</v>
       </c>
       <c r="H685" t="n">
-        <v>3661.183</v>
+        <v>3649.981</v>
       </c>
       <c r="I685" t="n">
         <v>0.0</v>
@@ -25435,7 +25435,7 @@
         </is>
       </c>
       <c r="E686" t="n">
-        <v>11404.902</v>
+        <v>12539.09</v>
       </c>
       <c r="F686" t="n">
         <v>0.0</v>
@@ -25444,7 +25444,7 @@
         <v>3898.25</v>
       </c>
       <c r="H686" t="n">
-        <v>11404.902</v>
+        <v>12539.09</v>
       </c>
       <c r="I686" t="n">
         <v>0.0</v>
@@ -25768,7 +25768,7 @@
         </is>
       </c>
       <c r="E695" t="n">
-        <v>5149.6849999999995</v>
+        <v>5094.141</v>
       </c>
       <c r="F695" t="n">
         <v>230.109</v>
@@ -25777,7 +25777,7 @@
         <v>0.0</v>
       </c>
       <c r="H695" t="n">
-        <v>5149.6849999999995</v>
+        <v>5094.141</v>
       </c>
       <c r="I695" t="n">
         <v>0.0</v>
@@ -25953,7 +25953,7 @@
         </is>
       </c>
       <c r="E700" t="n">
-        <v>1243.11</v>
+        <v>436.56600000000003</v>
       </c>
       <c r="F700" t="n">
         <v>0.624</v>
@@ -25962,7 +25962,7 @@
         <v>0.0</v>
       </c>
       <c r="H700" t="n">
-        <v>1243.11</v>
+        <v>436.56600000000003</v>
       </c>
       <c r="I700" t="n">
         <v>0.0</v>
@@ -25990,7 +25990,7 @@
         </is>
       </c>
       <c r="E701" t="n">
-        <v>4664.3859999999995</v>
+        <v>4450.9259999999995</v>
       </c>
       <c r="F701" t="n">
         <v>26.450000000000003</v>
@@ -25999,7 +25999,7 @@
         <v>5.601</v>
       </c>
       <c r="H701" t="n">
-        <v>4664.3859999999995</v>
+        <v>4450.9259999999995</v>
       </c>
       <c r="I701" t="n">
         <v>0.0</v>
@@ -26027,7 +26027,7 @@
         </is>
       </c>
       <c r="E702" t="n">
-        <v>7424.434</v>
+        <v>7165.8550000000005</v>
       </c>
       <c r="F702" t="n">
         <v>41.385999999999996</v>
@@ -26036,7 +26036,7 @@
         <v>9.334999999999999</v>
       </c>
       <c r="H702" t="n">
-        <v>7424.434</v>
+        <v>7165.8550000000005</v>
       </c>
       <c r="I702" t="n">
         <v>0.0</v>
@@ -26064,7 +26064,7 @@
         </is>
       </c>
       <c r="E703" t="n">
-        <v>2599.155</v>
+        <v>2599.154</v>
       </c>
       <c r="F703" t="n">
         <v>0.0</v>
@@ -26073,7 +26073,7 @@
         <v>3.851</v>
       </c>
       <c r="H703" t="n">
-        <v>2599.155</v>
+        <v>2599.154</v>
       </c>
       <c r="I703" t="n">
         <v>0.0</v>
@@ -26138,7 +26138,7 @@
         </is>
       </c>
       <c r="E705" t="n">
-        <v>0.608</v>
+        <v>870.7113999999999</v>
       </c>
       <c r="F705" t="n">
         <v>0.0</v>
@@ -26150,7 +26150,7 @@
         <v>0.608</v>
       </c>
       <c r="I705" t="n">
-        <v>0.0</v>
+        <v>870.1034</v>
       </c>
     </row>
     <row r="706">
@@ -26212,7 +26212,7 @@
         </is>
       </c>
       <c r="E707" t="n">
-        <v>696.732</v>
+        <v>696.733</v>
       </c>
       <c r="F707" t="n">
         <v>0.0</v>
@@ -26221,7 +26221,7 @@
         <v>0.0</v>
       </c>
       <c r="H707" t="n">
-        <v>696.732</v>
+        <v>696.733</v>
       </c>
       <c r="I707" t="n">
         <v>0.0</v>
@@ -26471,7 +26471,7 @@
         </is>
       </c>
       <c r="E714" t="n">
-        <v>150.075</v>
+        <v>142.793</v>
       </c>
       <c r="F714" t="n">
         <v>0.0</v>
@@ -26480,7 +26480,7 @@
         <v>0.0</v>
       </c>
       <c r="H714" t="n">
-        <v>150.075</v>
+        <v>142.793</v>
       </c>
       <c r="I714" t="n">
         <v>0.0</v>
@@ -26508,7 +26508,7 @@
         </is>
       </c>
       <c r="E715" t="n">
-        <v>510.292</v>
+        <v>508.472</v>
       </c>
       <c r="F715" t="n">
         <v>0.0</v>
@@ -26517,7 +26517,7 @@
         <v>0.0</v>
       </c>
       <c r="H715" t="n">
-        <v>510.292</v>
+        <v>508.472</v>
       </c>
       <c r="I715" t="n">
         <v>0.0</v>
@@ -26545,7 +26545,7 @@
         </is>
       </c>
       <c r="E716" t="n">
-        <v>6070.021</v>
+        <v>6054.022</v>
       </c>
       <c r="F716" t="n">
         <v>0.0</v>
@@ -26554,7 +26554,7 @@
         <v>0.0</v>
       </c>
       <c r="H716" t="n">
-        <v>6070.021</v>
+        <v>6054.022</v>
       </c>
       <c r="I716" t="n">
         <v>0.0</v>
@@ -26582,7 +26582,7 @@
         </is>
       </c>
       <c r="E717" t="n">
-        <v>1252.423</v>
+        <v>1033.196</v>
       </c>
       <c r="F717" t="n">
         <v>0.0</v>
@@ -26591,7 +26591,7 @@
         <v>153.619</v>
       </c>
       <c r="H717" t="n">
-        <v>1252.423</v>
+        <v>1033.196</v>
       </c>
       <c r="I717" t="n">
         <v>0.0</v>
@@ -26619,7 +26619,7 @@
         </is>
       </c>
       <c r="E718" t="n">
-        <v>4434.922</v>
+        <v>4425.322</v>
       </c>
       <c r="F718" t="n">
         <v>0.0</v>
@@ -26628,7 +26628,7 @@
         <v>0.0</v>
       </c>
       <c r="H718" t="n">
-        <v>4434.922</v>
+        <v>4425.322</v>
       </c>
       <c r="I718" t="n">
         <v>0.0</v>
@@ -26656,7 +26656,7 @@
         </is>
       </c>
       <c r="E719" t="n">
-        <v>2371.229</v>
+        <v>1890.902</v>
       </c>
       <c r="F719" t="n">
         <v>0.26699999999999996</v>
@@ -26665,7 +26665,7 @@
         <v>0.0</v>
       </c>
       <c r="H719" t="n">
-        <v>2371.229</v>
+        <v>1890.902</v>
       </c>
       <c r="I719" t="n">
         <v>0.0</v>
@@ -26693,7 +26693,7 @@
         </is>
       </c>
       <c r="E720" t="n">
-        <v>266.117</v>
+        <v>265.583</v>
       </c>
       <c r="F720" t="n">
         <v>6.4</v>
@@ -26702,7 +26702,7 @@
         <v>3.2</v>
       </c>
       <c r="H720" t="n">
-        <v>266.117</v>
+        <v>265.583</v>
       </c>
       <c r="I720" t="n">
         <v>0.0</v>
@@ -26767,7 +26767,7 @@
         </is>
       </c>
       <c r="E722" t="n">
-        <v>2844.621</v>
+        <v>2798.756</v>
       </c>
       <c r="F722" t="n">
         <v>0.0</v>
@@ -26776,7 +26776,7 @@
         <v>0.0</v>
       </c>
       <c r="H722" t="n">
-        <v>2844.621</v>
+        <v>2798.756</v>
       </c>
       <c r="I722" t="n">
         <v>0.0</v>
@@ -26804,7 +26804,7 @@
         </is>
       </c>
       <c r="E723" t="n">
-        <v>25895.236</v>
+        <v>24833.77</v>
       </c>
       <c r="F723" t="n">
         <v>2.4</v>
@@ -26813,7 +26813,7 @@
         <v>288.036</v>
       </c>
       <c r="H723" t="n">
-        <v>25895.236</v>
+        <v>24833.77</v>
       </c>
       <c r="I723" t="n">
         <v>0.0</v>
@@ -26841,7 +26841,7 @@
         </is>
       </c>
       <c r="E724" t="n">
-        <v>3931.425</v>
+        <v>3703.6670000000004</v>
       </c>
       <c r="F724" t="n">
         <v>2.4</v>
@@ -26850,7 +26850,7 @@
         <v>212.827</v>
       </c>
       <c r="H724" t="n">
-        <v>3931.425</v>
+        <v>3703.6670000000004</v>
       </c>
       <c r="I724" t="n">
         <v>0.0</v>
@@ -26878,7 +26878,7 @@
         </is>
       </c>
       <c r="E725" t="n">
-        <v>2685.924</v>
+        <v>2605.9100000000003</v>
       </c>
       <c r="F725" t="n">
         <v>0.13899999999999998</v>
@@ -26887,7 +26887,7 @@
         <v>67.155</v>
       </c>
       <c r="H725" t="n">
-        <v>2685.924</v>
+        <v>2605.9100000000003</v>
       </c>
       <c r="I725" t="n">
         <v>0.0</v>
@@ -26915,7 +26915,7 @@
         </is>
       </c>
       <c r="E726" t="n">
-        <v>1879.28</v>
+        <v>1850.0</v>
       </c>
       <c r="F726" t="n">
         <v>0.2</v>
@@ -26924,7 +26924,7 @@
         <v>2.8800000000000003</v>
       </c>
       <c r="H726" t="n">
-        <v>1879.28</v>
+        <v>1850.0</v>
       </c>
       <c r="I726" t="n">
         <v>0.0</v>
@@ -26952,7 +26952,7 @@
         </is>
       </c>
       <c r="E727" t="n">
-        <v>3005.4170000000004</v>
+        <v>2959.861</v>
       </c>
       <c r="F727" t="n">
         <v>0.0</v>
@@ -26961,7 +26961,7 @@
         <v>0.555</v>
       </c>
       <c r="H727" t="n">
-        <v>3005.4170000000004</v>
+        <v>2959.861</v>
       </c>
       <c r="I727" t="n">
         <v>0.0</v>
@@ -26989,7 +26989,7 @@
         </is>
       </c>
       <c r="E728" t="n">
-        <v>1722.0030000000002</v>
+        <v>1720.683</v>
       </c>
       <c r="F728" t="n">
         <v>0.0</v>
@@ -26998,7 +26998,7 @@
         <v>0.0</v>
       </c>
       <c r="H728" t="n">
-        <v>1722.0030000000002</v>
+        <v>1720.683</v>
       </c>
       <c r="I728" t="n">
         <v>0.0</v>
@@ -27285,7 +27285,7 @@
         </is>
       </c>
       <c r="E736" t="n">
-        <v>770.263</v>
+        <v>546.81</v>
       </c>
       <c r="F736" t="n">
         <v>11.733</v>
@@ -27294,7 +27294,7 @@
         <v>0.0</v>
       </c>
       <c r="H736" t="n">
-        <v>770.263</v>
+        <v>546.81</v>
       </c>
       <c r="I736" t="n">
         <v>0.0</v>
@@ -27544,7 +27544,7 @@
         </is>
       </c>
       <c r="E743" t="n">
-        <v>2123.019</v>
+        <v>1435.47</v>
       </c>
       <c r="F743" t="n">
         <v>0.0</v>
@@ -27553,7 +27553,7 @@
         <v>162.126</v>
       </c>
       <c r="H743" t="n">
-        <v>2123.019</v>
+        <v>1435.47</v>
       </c>
       <c r="I743" t="n">
         <v>0.0</v>
@@ -27581,7 +27581,7 @@
         </is>
       </c>
       <c r="E744" t="n">
-        <v>901.5559999999999</v>
+        <v>827.3689999999999</v>
       </c>
       <c r="F744" t="n">
         <v>13.831</v>
@@ -27590,7 +27590,7 @@
         <v>5.029999999999999</v>
       </c>
       <c r="H744" t="n">
-        <v>901.5559999999999</v>
+        <v>827.3689999999999</v>
       </c>
       <c r="I744" t="n">
         <v>0.0</v>
@@ -27618,7 +27618,7 @@
         </is>
       </c>
       <c r="E745" t="n">
-        <v>862.576</v>
+        <v>827.369</v>
       </c>
       <c r="F745" t="n">
         <v>21.375999999999998</v>
@@ -27627,7 +27627,7 @@
         <v>0.0</v>
       </c>
       <c r="H745" t="n">
-        <v>862.576</v>
+        <v>827.369</v>
       </c>
       <c r="I745" t="n">
         <v>0.0</v>
@@ -27729,7 +27729,7 @@
         </is>
       </c>
       <c r="E748" t="n">
-        <v>1590.49</v>
+        <v>704.134</v>
       </c>
       <c r="F748" t="n">
         <v>0.0</v>
@@ -27738,7 +27738,7 @@
         <v>177.51</v>
       </c>
       <c r="H748" t="n">
-        <v>1590.49</v>
+        <v>704.134</v>
       </c>
       <c r="I748" t="n">
         <v>0.0</v>
@@ -27840,7 +27840,7 @@
         </is>
       </c>
       <c r="E751" t="n">
-        <v>3902.3210000000004</v>
+        <v>2833.824</v>
       </c>
       <c r="F751" t="n">
         <v>0.0</v>
@@ -27849,7 +27849,7 @@
         <v>2.3080000000000003</v>
       </c>
       <c r="H751" t="n">
-        <v>3902.3210000000004</v>
+        <v>2833.824</v>
       </c>
       <c r="I751" t="n">
         <v>0.0</v>
@@ -27988,7 +27988,7 @@
         </is>
       </c>
       <c r="E755" t="n">
-        <v>2510.777</v>
+        <v>876.896</v>
       </c>
       <c r="F755" t="n">
         <v>2.3080000000000003</v>
@@ -27997,7 +27997,7 @@
         <v>2.3080000000000003</v>
       </c>
       <c r="H755" t="n">
-        <v>2510.777</v>
+        <v>876.896</v>
       </c>
       <c r="I755" t="n">
         <v>0.0</v>
@@ -28025,7 +28025,7 @@
         </is>
       </c>
       <c r="E756" t="n">
-        <v>4186.169</v>
+        <v>2051.512</v>
       </c>
       <c r="F756" t="n">
         <v>0.0</v>
@@ -28034,7 +28034,7 @@
         <v>2.3080000000000003</v>
       </c>
       <c r="H756" t="n">
-        <v>4186.169</v>
+        <v>2051.512</v>
       </c>
       <c r="I756" t="n">
         <v>0.0</v>
@@ -28210,7 +28210,7 @@
         </is>
       </c>
       <c r="E761" t="n">
-        <v>3133.085</v>
+        <v>3106.683</v>
       </c>
       <c r="F761" t="n">
         <v>0.0</v>
@@ -28219,7 +28219,7 @@
         <v>44.004000000000005</v>
       </c>
       <c r="H761" t="n">
-        <v>3133.085</v>
+        <v>3106.683</v>
       </c>
       <c r="I761" t="n">
         <v>0.0</v>
@@ -28358,7 +28358,7 @@
         </is>
       </c>
       <c r="E765" t="n">
-        <v>822.6999999999999</v>
+        <v>815.116</v>
       </c>
       <c r="F765" t="n">
         <v>0.892</v>
@@ -28367,7 +28367,7 @@
         <v>0.0</v>
       </c>
       <c r="H765" t="n">
-        <v>822.6999999999999</v>
+        <v>815.116</v>
       </c>
       <c r="I765" t="n">
         <v>0.0</v>
@@ -28506,7 +28506,7 @@
         </is>
       </c>
       <c r="E769" t="n">
-        <v>18743.547</v>
+        <v>18694.161</v>
       </c>
       <c r="F769" t="n">
         <v>15.231</v>
@@ -28515,7 +28515,7 @@
         <v>7.385</v>
       </c>
       <c r="H769" t="n">
-        <v>18743.547</v>
+        <v>18694.161</v>
       </c>
       <c r="I769" t="n">
         <v>0.0</v>
@@ -28543,7 +28543,7 @@
         </is>
       </c>
       <c r="E770" t="n">
-        <v>756.173</v>
+        <v>639.991</v>
       </c>
       <c r="F770" t="n">
         <v>0.0</v>
@@ -28552,7 +28552,7 @@
         <v>3.9379999999999997</v>
       </c>
       <c r="H770" t="n">
-        <v>756.173</v>
+        <v>639.991</v>
       </c>
       <c r="I770" t="n">
         <v>0.0</v>
@@ -28617,7 +28617,7 @@
         </is>
       </c>
       <c r="E772" t="n">
-        <v>585.834</v>
+        <v>559.989</v>
       </c>
       <c r="F772" t="n">
         <v>2.154</v>
@@ -28626,7 +28626,7 @@
         <v>614.048</v>
       </c>
       <c r="H772" t="n">
-        <v>585.834</v>
+        <v>559.989</v>
       </c>
       <c r="I772" t="n">
         <v>0.0</v>
@@ -28654,7 +28654,7 @@
         </is>
       </c>
       <c r="E773" t="n">
-        <v>5294.974</v>
+        <v>5231.004</v>
       </c>
       <c r="F773" t="n">
         <v>2.0309999999999997</v>
@@ -28663,7 +28663,7 @@
         <v>2.0309999999999997</v>
       </c>
       <c r="H773" t="n">
-        <v>5294.974</v>
+        <v>5231.004</v>
       </c>
       <c r="I773" t="n">
         <v>0.0</v>
@@ -28691,7 +28691,7 @@
         </is>
       </c>
       <c r="E774" t="n">
-        <v>1923.168</v>
+        <v>1023.5219999999999</v>
       </c>
       <c r="F774" t="n">
         <v>2.0309999999999997</v>
@@ -28700,7 +28700,7 @@
         <v>4.061999999999999</v>
       </c>
       <c r="H774" t="n">
-        <v>1923.168</v>
+        <v>1023.5219999999999</v>
       </c>
       <c r="I774" t="n">
         <v>0.0</v>
@@ -28765,7 +28765,7 @@
         </is>
       </c>
       <c r="E776" t="n">
-        <v>11540.024</v>
+        <v>11519.377</v>
       </c>
       <c r="F776" t="n">
         <v>4.736</v>
@@ -28774,7 +28774,7 @@
         <v>38.585</v>
       </c>
       <c r="H776" t="n">
-        <v>11540.024</v>
+        <v>11519.377</v>
       </c>
       <c r="I776" t="n">
         <v>0.0</v>
@@ -28802,7 +28802,7 @@
         </is>
       </c>
       <c r="E777" t="n">
-        <v>821.156</v>
+        <v>665.59</v>
       </c>
       <c r="F777" t="n">
         <v>0.0</v>
@@ -28811,7 +28811,7 @@
         <v>0.0</v>
       </c>
       <c r="H777" t="n">
-        <v>821.156</v>
+        <v>665.59</v>
       </c>
       <c r="I777" t="n">
         <v>0.0</v>
@@ -28913,7 +28913,7 @@
         </is>
       </c>
       <c r="E780" t="n">
-        <v>3244.202</v>
+        <v>2936.197</v>
       </c>
       <c r="F780" t="n">
         <v>0.0</v>
@@ -28922,7 +28922,7 @@
         <v>0.0</v>
       </c>
       <c r="H780" t="n">
-        <v>3244.202</v>
+        <v>2936.197</v>
       </c>
       <c r="I780" t="n">
         <v>0.0</v>
@@ -28987,7 +28987,7 @@
         </is>
       </c>
       <c r="E782" t="n">
-        <v>11.849</v>
+        <v>9.819</v>
       </c>
       <c r="F782" t="n">
         <v>0.0</v>
@@ -28996,7 +28996,7 @@
         <v>6419.359</v>
       </c>
       <c r="H782" t="n">
-        <v>11.849</v>
+        <v>9.819</v>
       </c>
       <c r="I782" t="n">
         <v>0.0</v>
@@ -29024,7 +29024,7 @@
         </is>
       </c>
       <c r="E783" t="n">
-        <v>904.729</v>
+        <v>904.8000000000001</v>
       </c>
       <c r="F783" t="n">
         <v>0.0</v>
@@ -29033,7 +29033,7 @@
         <v>0.8400000000000001</v>
       </c>
       <c r="H783" t="n">
-        <v>904.729</v>
+        <v>904.8000000000001</v>
       </c>
       <c r="I783" t="n">
         <v>0.0</v>
@@ -29061,7 +29061,7 @@
         </is>
       </c>
       <c r="E784" t="n">
-        <v>666.841</v>
+        <v>668.4</v>
       </c>
       <c r="F784" t="n">
         <v>0.0</v>
@@ -29070,7 +29070,7 @@
         <v>19.68</v>
       </c>
       <c r="H784" t="n">
-        <v>666.841</v>
+        <v>668.4</v>
       </c>
       <c r="I784" t="n">
         <v>0.0</v>
@@ -29135,7 +29135,7 @@
         </is>
       </c>
       <c r="E786" t="n">
-        <v>4153.389</v>
+        <v>4058.854</v>
       </c>
       <c r="F786" t="n">
         <v>0.185</v>
@@ -29144,7 +29144,7 @@
         <v>34.456</v>
       </c>
       <c r="H786" t="n">
-        <v>4153.389</v>
+        <v>4058.854</v>
       </c>
       <c r="I786" t="n">
         <v>0.0</v>
@@ -29172,7 +29172,7 @@
         </is>
       </c>
       <c r="E787" t="n">
-        <v>545.149</v>
+        <v>478.549</v>
       </c>
       <c r="F787" t="n">
         <v>4.995</v>
@@ -29181,7 +29181,7 @@
         <v>79.36500000000001</v>
       </c>
       <c r="H787" t="n">
-        <v>545.149</v>
+        <v>478.549</v>
       </c>
       <c r="I787" t="n">
         <v>0.0</v>
@@ -29209,7 +29209,7 @@
         </is>
       </c>
       <c r="E788" t="n">
-        <v>1099.575</v>
+        <v>1101.735</v>
       </c>
       <c r="F788" t="n">
         <v>1.485</v>
@@ -29218,7 +29218,7 @@
         <v>8.1</v>
       </c>
       <c r="H788" t="n">
-        <v>1099.575</v>
+        <v>1101.735</v>
       </c>
       <c r="I788" t="n">
         <v>0.0</v>
@@ -29246,7 +29246,7 @@
         </is>
       </c>
       <c r="E789" t="n">
-        <v>1138.68</v>
+        <v>790.64</v>
       </c>
       <c r="F789" t="n">
         <v>0.32</v>
@@ -29255,7 +29255,7 @@
         <v>17.32</v>
       </c>
       <c r="H789" t="n">
-        <v>1138.68</v>
+        <v>790.64</v>
       </c>
       <c r="I789" t="n">
         <v>0.0</v>
@@ -29357,7 +29357,7 @@
         </is>
       </c>
       <c r="E792" t="n">
-        <v>4972.6939999999995</v>
+        <v>4957.531</v>
       </c>
       <c r="F792" t="n">
         <v>3.033</v>
@@ -29366,7 +29366,7 @@
         <v>12.13</v>
       </c>
       <c r="H792" t="n">
-        <v>4972.6939999999995</v>
+        <v>4957.531</v>
       </c>
       <c r="I792" t="n">
         <v>0.0</v>
@@ -29394,7 +29394,7 @@
         </is>
       </c>
       <c r="E793" t="n">
-        <v>3199.288</v>
+        <v>3173.815</v>
       </c>
       <c r="F793" t="n">
         <v>6.065</v>
@@ -29403,7 +29403,7 @@
         <v>9.704</v>
       </c>
       <c r="H793" t="n">
-        <v>3199.288</v>
+        <v>3173.815</v>
       </c>
       <c r="I793" t="n">
         <v>0.0</v>
@@ -29431,7 +29431,7 @@
         </is>
       </c>
       <c r="E794" t="n">
-        <v>364.507</v>
+        <v>356.622</v>
       </c>
       <c r="F794" t="n">
         <v>1.213</v>
@@ -29440,7 +29440,7 @@
         <v>0.0</v>
       </c>
       <c r="H794" t="n">
-        <v>364.507</v>
+        <v>356.622</v>
       </c>
       <c r="I794" t="n">
         <v>0.0</v>
@@ -29579,7 +29579,7 @@
         </is>
       </c>
       <c r="E798" t="n">
-        <v>4132.8369999999995</v>
+        <v>3025.828</v>
       </c>
       <c r="F798" t="n">
         <v>1.8920000000000001</v>
@@ -29588,7 +29588,7 @@
         <v>80.739</v>
       </c>
       <c r="H798" t="n">
-        <v>4132.8369999999995</v>
+        <v>3025.828</v>
       </c>
       <c r="I798" t="n">
         <v>0.0</v>
@@ -29616,7 +29616,7 @@
         </is>
       </c>
       <c r="E799" t="n">
-        <v>3160.183</v>
+        <v>3158.2909999999997</v>
       </c>
       <c r="F799" t="n">
         <v>3.154</v>
@@ -29625,7 +29625,7 @@
         <v>0.631</v>
       </c>
       <c r="H799" t="n">
-        <v>3160.183</v>
+        <v>3158.2909999999997</v>
       </c>
       <c r="I799" t="n">
         <v>0.0</v>
@@ -29653,7 +29653,7 @@
         </is>
       </c>
       <c r="E800" t="n">
-        <v>4518.918</v>
+        <v>4515.558</v>
       </c>
       <c r="F800" t="n">
         <v>0.0</v>
@@ -29662,7 +29662,7 @@
         <v>0.0</v>
       </c>
       <c r="H800" t="n">
-        <v>4518.918</v>
+        <v>4515.558</v>
       </c>
       <c r="I800" t="n">
         <v>0.0</v>
@@ -29838,7 +29838,7 @@
         </is>
       </c>
       <c r="E805" t="n">
-        <v>499.682</v>
+        <v>484.604</v>
       </c>
       <c r="F805" t="n">
         <v>0.0</v>
@@ -29847,7 +29847,7 @@
         <v>590.1410000000001</v>
       </c>
       <c r="H805" t="n">
-        <v>499.682</v>
+        <v>484.604</v>
       </c>
       <c r="I805" t="n">
         <v>0.0</v>
@@ -30097,7 +30097,7 @@
         </is>
       </c>
       <c r="E812" t="n">
-        <v>1631.1999999999998</v>
+        <v>1533.2</v>
       </c>
       <c r="F812" t="n">
         <v>0.6</v>
@@ -30106,7 +30106,7 @@
         <v>2.4</v>
       </c>
       <c r="H812" t="n">
-        <v>1631.1999999999998</v>
+        <v>1533.2</v>
       </c>
       <c r="I812" t="n">
         <v>0.0</v>
@@ -30171,7 +30171,7 @@
         </is>
       </c>
       <c r="E814" t="n">
-        <v>1257.521</v>
+        <v>1219.121</v>
       </c>
       <c r="F814" t="n">
         <v>0.0</v>
@@ -30180,7 +30180,7 @@
         <v>0.0</v>
       </c>
       <c r="H814" t="n">
-        <v>1257.521</v>
+        <v>1219.121</v>
       </c>
       <c r="I814" t="n">
         <v>0.0</v>
@@ -30208,7 +30208,7 @@
         </is>
       </c>
       <c r="E815" t="n">
-        <v>16971.74</v>
+        <v>16933.341</v>
       </c>
       <c r="F815" t="n">
         <v>0.533</v>
@@ -30217,7 +30217,7 @@
         <v>0.0</v>
       </c>
       <c r="H815" t="n">
-        <v>16971.74</v>
+        <v>16933.341</v>
       </c>
       <c r="I815" t="n">
         <v>0.0</v>
@@ -30245,7 +30245,7 @@
         </is>
       </c>
       <c r="E816" t="n">
-        <v>60.274</v>
+        <v>35.204</v>
       </c>
       <c r="F816" t="n">
         <v>0.533</v>
@@ -30254,7 +30254,7 @@
         <v>0.0</v>
       </c>
       <c r="H816" t="n">
-        <v>60.274</v>
+        <v>35.204</v>
       </c>
       <c r="I816" t="n">
         <v>0.0</v>
@@ -30282,7 +30282,7 @@
         </is>
       </c>
       <c r="E817" t="n">
-        <v>12404.483</v>
+        <v>12134.052</v>
       </c>
       <c r="F817" t="n">
         <v>2.4</v>
@@ -30291,7 +30291,7 @@
         <v>599.008</v>
       </c>
       <c r="H817" t="n">
-        <v>12404.483</v>
+        <v>12134.052</v>
       </c>
       <c r="I817" t="n">
         <v>0.0</v>
@@ -30430,7 +30430,7 @@
         </is>
       </c>
       <c r="E821" t="n">
-        <v>752.094</v>
+        <v>113.616</v>
       </c>
       <c r="F821" t="n">
         <v>0.0</v>
@@ -30439,7 +30439,7 @@
         <v>192.024</v>
       </c>
       <c r="H821" t="n">
-        <v>752.094</v>
+        <v>113.616</v>
       </c>
       <c r="I821" t="n">
         <v>0.0</v>
@@ -30652,7 +30652,7 @@
         </is>
       </c>
       <c r="E827" t="n">
-        <v>106.752</v>
+        <v>640.512</v>
       </c>
       <c r="F827" t="n">
         <v>0.0</v>
@@ -30661,7 +30661,7 @@
         <v>1670.6689999999999</v>
       </c>
       <c r="H827" t="n">
-        <v>106.752</v>
+        <v>640.512</v>
       </c>
       <c r="I827" t="n">
         <v>0.0</v>
@@ -30763,7 +30763,7 @@
         </is>
       </c>
       <c r="E830" t="n">
-        <v>5232.548</v>
+        <v>5188.537</v>
       </c>
       <c r="F830" t="n">
         <v>0.0</v>
@@ -30772,7 +30772,7 @@
         <v>1.3339999999999999</v>
       </c>
       <c r="H830" t="n">
-        <v>5232.548</v>
+        <v>5188.537</v>
       </c>
       <c r="I830" t="n">
         <v>0.0</v>
@@ -30800,7 +30800,7 @@
         </is>
       </c>
       <c r="E831" t="n">
-        <v>3137.508</v>
+        <v>3129.501</v>
       </c>
       <c r="F831" t="n">
         <v>0.0</v>
@@ -30809,7 +30809,7 @@
         <v>0.5</v>
       </c>
       <c r="H831" t="n">
-        <v>3137.508</v>
+        <v>3129.501</v>
       </c>
       <c r="I831" t="n">
         <v>0.0</v>
@@ -31244,7 +31244,7 @@
         </is>
       </c>
       <c r="E843" t="n">
-        <v>567.933</v>
+        <v>848.26</v>
       </c>
       <c r="F843" t="n">
         <v>0.0</v>
@@ -31253,7 +31253,7 @@
         <v>0.0</v>
       </c>
       <c r="H843" t="n">
-        <v>567.933</v>
+        <v>848.26</v>
       </c>
       <c r="I843" t="n">
         <v>0.0</v>
@@ -31318,7 +31318,7 @@
         </is>
       </c>
       <c r="E845" t="n">
-        <v>677.152</v>
+        <v>476.919</v>
       </c>
       <c r="F845" t="n">
         <v>0.0</v>
@@ -31327,7 +31327,7 @@
         <v>0.0</v>
       </c>
       <c r="H845" t="n">
-        <v>677.152</v>
+        <v>476.919</v>
       </c>
       <c r="I845" t="n">
         <v>0.0</v>
@@ -31355,7 +31355,7 @@
         </is>
       </c>
       <c r="E846" t="n">
-        <v>462.356</v>
+        <v>382.263</v>
       </c>
       <c r="F846" t="n">
         <v>0.0</v>
@@ -31364,7 +31364,7 @@
         <v>0.0</v>
       </c>
       <c r="H846" t="n">
-        <v>462.356</v>
+        <v>382.263</v>
       </c>
       <c r="I846" t="n">
         <v>0.0</v>
@@ -31392,7 +31392,7 @@
         </is>
       </c>
       <c r="E847" t="n">
-        <v>2928.814</v>
+        <v>2928.147</v>
       </c>
       <c r="F847" t="n">
         <v>1.333</v>
@@ -31401,7 +31401,7 @@
         <v>0.6669999999999999</v>
       </c>
       <c r="H847" t="n">
-        <v>2928.814</v>
+        <v>2928.147</v>
       </c>
       <c r="I847" t="n">
         <v>0.0</v>
@@ -31429,7 +31429,7 @@
         </is>
       </c>
       <c r="E848" t="n">
-        <v>2609.464</v>
+        <v>2608.1310000000003</v>
       </c>
       <c r="F848" t="n">
         <v>3.333</v>
@@ -31438,7 +31438,7 @@
         <v>0.0</v>
       </c>
       <c r="H848" t="n">
-        <v>2609.464</v>
+        <v>2608.1310000000003</v>
       </c>
       <c r="I848" t="n">
         <v>0.0</v>
@@ -31466,7 +31466,7 @@
         </is>
       </c>
       <c r="E849" t="n">
-        <v>19561.311</v>
+        <v>19555.976000000002</v>
       </c>
       <c r="F849" t="n">
         <v>10.67</v>
@@ -31475,7 +31475,7 @@
         <v>0.0</v>
       </c>
       <c r="H849" t="n">
-        <v>19561.311</v>
+        <v>19555.976000000002</v>
       </c>
       <c r="I849" t="n">
         <v>0.0</v>
@@ -31540,7 +31540,7 @@
         </is>
       </c>
       <c r="E851" t="n">
-        <v>5668.217000000001</v>
+        <v>5585.014</v>
       </c>
       <c r="F851" t="n">
         <v>0.0</v>
@@ -31549,7 +31549,7 @@
         <v>0.0</v>
       </c>
       <c r="H851" t="n">
-        <v>5668.217000000001</v>
+        <v>5585.014</v>
       </c>
       <c r="I851" t="n">
         <v>0.0</v>
@@ -31651,7 +31651,7 @@
         </is>
       </c>
       <c r="E854" t="n">
-        <v>9979.184000000001</v>
+        <v>9972.251</v>
       </c>
       <c r="F854" t="n">
         <v>15.601</v>
@@ -31660,7 +31660,7 @@
         <v>0.0</v>
       </c>
       <c r="H854" t="n">
-        <v>9979.184000000001</v>
+        <v>9972.251</v>
       </c>
       <c r="I854" t="n">
         <v>0.0</v>
@@ -31688,7 +31688,7 @@
         </is>
       </c>
       <c r="E855" t="n">
-        <v>477.926</v>
+        <v>460.858</v>
       </c>
       <c r="F855" t="n">
         <v>23.470000000000002</v>
@@ -31697,7 +31697,7 @@
         <v>0.0</v>
       </c>
       <c r="H855" t="n">
-        <v>477.926</v>
+        <v>460.858</v>
       </c>
       <c r="I855" t="n">
         <v>0.0</v>
@@ -31725,7 +31725,7 @@
         </is>
       </c>
       <c r="E856" t="n">
-        <v>2712.843</v>
+        <v>2629.611</v>
       </c>
       <c r="F856" t="n">
         <v>2.601</v>
@@ -31734,7 +31734,7 @@
         <v>0.0</v>
       </c>
       <c r="H856" t="n">
-        <v>2712.843</v>
+        <v>2629.611</v>
       </c>
       <c r="I856" t="n">
         <v>0.0</v>
@@ -31910,7 +31910,7 @@
         </is>
       </c>
       <c r="E861" t="n">
-        <v>2313.7999999999997</v>
+        <v>2313.2</v>
       </c>
       <c r="F861" t="n">
         <v>0.0</v>
@@ -31919,7 +31919,7 @@
         <v>0.0</v>
       </c>
       <c r="H861" t="n">
-        <v>2313.7999999999997</v>
+        <v>2313.2</v>
       </c>
       <c r="I861" t="n">
         <v>0.0</v>
@@ -31984,7 +31984,7 @@
         </is>
       </c>
       <c r="E863" t="n">
-        <v>10959.769</v>
+        <v>10922.165</v>
       </c>
       <c r="F863" t="n">
         <v>39.205</v>
@@ -31993,7 +31993,7 @@
         <v>0.0</v>
       </c>
       <c r="H863" t="n">
-        <v>10959.769</v>
+        <v>10922.165</v>
       </c>
       <c r="I863" t="n">
         <v>0.0</v>
@@ -32095,7 +32095,7 @@
         </is>
       </c>
       <c r="E866" t="n">
-        <v>1393.24</v>
+        <v>1316.431</v>
       </c>
       <c r="F866" t="n">
         <v>1.067</v>
@@ -32104,7 +32104,7 @@
         <v>25.603</v>
       </c>
       <c r="H866" t="n">
-        <v>1393.24</v>
+        <v>1316.431</v>
       </c>
       <c r="I866" t="n">
         <v>0.0</v>
@@ -32132,7 +32132,7 @@
         </is>
       </c>
       <c r="E867" t="n">
-        <v>999.512</v>
+        <v>888.523</v>
       </c>
       <c r="F867" t="n">
         <v>18.802</v>
@@ -32141,7 +32141,7 @@
         <v>19.408</v>
       </c>
       <c r="H867" t="n">
-        <v>999.512</v>
+        <v>888.523</v>
       </c>
       <c r="I867" t="n">
         <v>0.0</v>
@@ -32169,7 +32169,7 @@
         </is>
       </c>
       <c r="E868" t="n">
-        <v>1268.606</v>
+        <v>1255.588</v>
       </c>
       <c r="F868" t="n">
         <v>0.0</v>
@@ -32178,7 +32178,7 @@
         <v>0.0</v>
       </c>
       <c r="H868" t="n">
-        <v>1268.606</v>
+        <v>1255.588</v>
       </c>
       <c r="I868" t="n">
         <v>0.0</v>
@@ -32206,7 +32206,7 @@
         </is>
       </c>
       <c r="E869" t="n">
-        <v>1280.774</v>
+        <v>1253.081</v>
       </c>
       <c r="F869" t="n">
         <v>0.0</v>
@@ -32215,7 +32215,7 @@
         <v>9.231</v>
       </c>
       <c r="H869" t="n">
-        <v>1280.774</v>
+        <v>1253.081</v>
       </c>
       <c r="I869" t="n">
         <v>0.0</v>
@@ -32243,7 +32243,7 @@
         </is>
       </c>
       <c r="E870" t="n">
-        <v>1975.54</v>
+        <v>1508.9850000000001</v>
       </c>
       <c r="F870" t="n">
         <v>5.916</v>
@@ -32252,7 +32252,7 @@
         <v>346.144</v>
       </c>
       <c r="H870" t="n">
-        <v>1975.54</v>
+        <v>1508.9850000000001</v>
       </c>
       <c r="I870" t="n">
         <v>0.0</v>
@@ -32280,7 +32280,7 @@
         </is>
       </c>
       <c r="E871" t="n">
-        <v>4770.285000000001</v>
+        <v>4487.452</v>
       </c>
       <c r="F871" t="n">
         <v>0.593</v>
@@ -32289,7 +32289,7 @@
         <v>226.61999999999998</v>
       </c>
       <c r="H871" t="n">
-        <v>4770.285000000001</v>
+        <v>4487.452</v>
       </c>
       <c r="I871" t="n">
         <v>0.0</v>
@@ -32317,7 +32317,7 @@
         </is>
       </c>
       <c r="E872" t="n">
-        <v>4251.556</v>
+        <v>4102.444</v>
       </c>
       <c r="F872" t="n">
         <v>0.0</v>
@@ -32326,7 +32326,7 @@
         <v>0.0</v>
       </c>
       <c r="H872" t="n">
-        <v>4251.556</v>
+        <v>4102.444</v>
       </c>
       <c r="I872" t="n">
         <v>0.0</v>
@@ -32391,7 +32391,7 @@
         </is>
       </c>
       <c r="E874" t="n">
-        <v>9251.57</v>
+        <v>8891.566</v>
       </c>
       <c r="F874" t="n">
         <v>0.0</v>
@@ -32400,7 +32400,7 @@
         <v>6.923</v>
       </c>
       <c r="H874" t="n">
-        <v>9251.57</v>
+        <v>8891.566</v>
       </c>
       <c r="I874" t="n">
         <v>0.0</v>
@@ -32428,7 +32428,7 @@
         </is>
       </c>
       <c r="E875" t="n">
-        <v>4871.556</v>
+        <v>4825.401</v>
       </c>
       <c r="F875" t="n">
         <v>0.0</v>
@@ -32437,7 +32437,7 @@
         <v>0.0</v>
       </c>
       <c r="H875" t="n">
-        <v>4871.556</v>
+        <v>4825.401</v>
       </c>
       <c r="I875" t="n">
         <v>0.0</v>
@@ -32502,7 +32502,7 @@
         </is>
       </c>
       <c r="E877" t="n">
-        <v>2676.559</v>
+        <v>2389.519</v>
       </c>
       <c r="F877" t="n">
         <v>0.0</v>
@@ -32511,7 +32511,7 @@
         <v>0.9319999999999999</v>
       </c>
       <c r="H877" t="n">
-        <v>2676.559</v>
+        <v>2389.519</v>
       </c>
       <c r="I877" t="n">
         <v>0.0</v>
@@ -32687,7 +32687,7 @@
         </is>
       </c>
       <c r="E882" t="n">
-        <v>822.764</v>
+        <v>383.424</v>
       </c>
       <c r="F882" t="n">
         <v>0.0</v>
@@ -32696,7 +32696,7 @@
         <v>3.994</v>
       </c>
       <c r="H882" t="n">
-        <v>822.764</v>
+        <v>383.424</v>
       </c>
       <c r="I882" t="n">
         <v>0.0</v>
@@ -32798,7 +32798,7 @@
         </is>
       </c>
       <c r="E885" t="n">
-        <v>2153.787</v>
+        <v>2003.497</v>
       </c>
       <c r="F885" t="n">
         <v>0.0</v>
@@ -32807,7 +32807,7 @@
         <v>42.602000000000004</v>
       </c>
       <c r="H885" t="n">
-        <v>2153.787</v>
+        <v>2003.497</v>
       </c>
       <c r="I885" t="n">
         <v>0.0</v>
@@ -33057,7 +33057,7 @@
         </is>
       </c>
       <c r="E892" t="n">
-        <v>9110.616</v>
+        <v>7883.972</v>
       </c>
       <c r="F892" t="n">
         <v>0.0</v>
@@ -33066,7 +33066,7 @@
         <v>84.29</v>
       </c>
       <c r="H892" t="n">
-        <v>9110.616</v>
+        <v>7883.972</v>
       </c>
       <c r="I892" t="n">
         <v>0.0</v>
@@ -33131,7 +33131,7 @@
         </is>
       </c>
       <c r="E894" t="n">
-        <v>568.454</v>
+        <v>563.116</v>
       </c>
       <c r="F894" t="n">
         <v>5.338</v>
@@ -33140,7 +33140,7 @@
         <v>0.0</v>
       </c>
       <c r="H894" t="n">
-        <v>568.454</v>
+        <v>563.116</v>
       </c>
       <c r="I894" t="n">
         <v>0.0</v>
@@ -33242,7 +33242,7 @@
         </is>
       </c>
       <c r="E897" t="n">
-        <v>1802.774</v>
+        <v>1730.717</v>
       </c>
       <c r="F897" t="n">
         <v>0.0</v>
@@ -33251,7 +33251,7 @@
         <v>227.07</v>
       </c>
       <c r="H897" t="n">
-        <v>1802.774</v>
+        <v>1730.717</v>
       </c>
       <c r="I897" t="n">
         <v>0.0</v>
@@ -33279,7 +33279,7 @@
         </is>
       </c>
       <c r="E898" t="n">
-        <v>106.751</v>
+        <v>106.752</v>
       </c>
       <c r="F898" t="n">
         <v>0.0</v>
@@ -33288,7 +33288,7 @@
         <v>0.0</v>
       </c>
       <c r="H898" t="n">
-        <v>106.751</v>
+        <v>106.752</v>
       </c>
       <c r="I898" t="n">
         <v>0.0</v>
@@ -33316,7 +33316,7 @@
         </is>
       </c>
       <c r="E899" t="n">
-        <v>1843.154</v>
+        <v>1622.994</v>
       </c>
       <c r="F899" t="n">
         <v>3.033</v>
@@ -33325,7 +33325,7 @@
         <v>0.0</v>
       </c>
       <c r="H899" t="n">
-        <v>1843.154</v>
+        <v>1622.994</v>
       </c>
       <c r="I899" t="n">
         <v>0.0</v>
@@ -33353,7 +33353,7 @@
         </is>
       </c>
       <c r="E900" t="n">
-        <v>1023.772</v>
+        <v>1018.3140000000001</v>
       </c>
       <c r="F900" t="n">
         <v>0.607</v>
@@ -33362,7 +33362,7 @@
         <v>0.0</v>
       </c>
       <c r="H900" t="n">
-        <v>1023.772</v>
+        <v>1018.3140000000001</v>
       </c>
       <c r="I900" t="n">
         <v>0.0</v>
@@ -33427,7 +33427,7 @@
         </is>
       </c>
       <c r="E902" t="n">
-        <v>2424.33</v>
+        <v>2373.916</v>
       </c>
       <c r="F902" t="n">
         <v>67.218</v>
@@ -33436,7 +33436,7 @@
         <v>0.0</v>
       </c>
       <c r="H902" t="n">
-        <v>2424.33</v>
+        <v>2373.916</v>
       </c>
       <c r="I902" t="n">
         <v>0.0</v>
@@ -33501,7 +33501,7 @@
         </is>
       </c>
       <c r="E904" t="n">
-        <v>1560.0</v>
+        <v>1548.0</v>
       </c>
       <c r="F904" t="n">
         <v>8.0</v>
@@ -33510,7 +33510,7 @@
         <v>0.0</v>
       </c>
       <c r="H904" t="n">
-        <v>1560.0</v>
+        <v>1548.0</v>
       </c>
       <c r="I904" t="n">
         <v>0.0</v>
@@ -33612,7 +33612,7 @@
         </is>
       </c>
       <c r="E907" t="n">
-        <v>1354.214</v>
+        <v>1296.025</v>
       </c>
       <c r="F907" t="n">
         <v>0.0</v>
@@ -33621,7 +33621,7 @@
         <v>0.0</v>
       </c>
       <c r="H907" t="n">
-        <v>1354.214</v>
+        <v>1296.025</v>
       </c>
       <c r="I907" t="n">
         <v>0.0</v>
@@ -33760,7 +33760,7 @@
         </is>
       </c>
       <c r="E911" t="n">
-        <v>2676.689</v>
+        <v>2232.337</v>
       </c>
       <c r="F911" t="n">
         <v>0.0</v>
@@ -33769,7 +33769,7 @@
         <v>0.0</v>
       </c>
       <c r="H911" t="n">
-        <v>2676.689</v>
+        <v>2232.337</v>
       </c>
       <c r="I911" t="n">
         <v>0.0</v>
@@ -34315,7 +34315,7 @@
         </is>
       </c>
       <c r="E926" t="n">
-        <v>4569.678</v>
+        <v>4561.786999999999</v>
       </c>
       <c r="F926" t="n">
         <v>0.211</v>
@@ -34324,7 +34324,7 @@
         <v>1.262</v>
       </c>
       <c r="H926" t="n">
-        <v>4569.678</v>
+        <v>4561.786999999999</v>
       </c>
       <c r="I926" t="n">
         <v>0.0</v>
@@ -34352,7 +34352,7 @@
         </is>
       </c>
       <c r="E927" t="n">
-        <v>823.401</v>
+        <v>819.508</v>
       </c>
       <c r="F927" t="n">
         <v>0.0</v>
@@ -34361,7 +34361,7 @@
         <v>0.0</v>
       </c>
       <c r="H927" t="n">
-        <v>823.401</v>
+        <v>819.508</v>
       </c>
       <c r="I927" t="n">
         <v>0.0</v>
@@ -34389,7 +34389,7 @@
         </is>
       </c>
       <c r="E928" t="n">
-        <v>2820.009</v>
+        <v>2610.007</v>
       </c>
       <c r="F928" t="n">
         <v>0.0</v>
@@ -34398,7 +34398,7 @@
         <v>11.539000000000001</v>
       </c>
       <c r="H928" t="n">
-        <v>2820.009</v>
+        <v>2610.007</v>
       </c>
       <c r="I928" t="n">
         <v>0.0</v>
@@ -34500,7 +34500,7 @@
         </is>
       </c>
       <c r="E931" t="n">
-        <v>3484.625</v>
+        <v>3348.471</v>
       </c>
       <c r="F931" t="n">
         <v>0.0</v>
@@ -34509,7 +34509,7 @@
         <v>2.3080000000000003</v>
       </c>
       <c r="H931" t="n">
-        <v>3484.625</v>
+        <v>3348.471</v>
       </c>
       <c r="I931" t="n">
         <v>0.0</v>
@@ -34722,7 +34722,7 @@
         </is>
       </c>
       <c r="E937" t="n">
-        <v>8881.567</v>
+        <v>8775.504</v>
       </c>
       <c r="F937" t="n">
         <v>1.6280000000000001</v>
@@ -34731,7 +34731,7 @@
         <v>128.102</v>
       </c>
       <c r="H937" t="n">
-        <v>8881.567</v>
+        <v>8775.504</v>
       </c>
       <c r="I937" t="n">
         <v>0.0</v>
@@ -34833,7 +34833,7 @@
         </is>
       </c>
       <c r="E940" t="n">
-        <v>4395.076</v>
+        <v>4346.615</v>
       </c>
       <c r="F940" t="n">
         <v>0.0</v>
@@ -34842,7 +34842,7 @@
         <v>0.0</v>
       </c>
       <c r="H940" t="n">
-        <v>4395.076</v>
+        <v>4346.615</v>
       </c>
       <c r="I940" t="n">
         <v>0.0</v>
@@ -34944,7 +34944,7 @@
         </is>
       </c>
       <c r="E943" t="n">
-        <v>321.64099999999996</v>
+        <v>303.238</v>
       </c>
       <c r="F943" t="n">
         <v>9.601</v>
@@ -34953,7 +34953,7 @@
         <v>0.0</v>
       </c>
       <c r="H943" t="n">
-        <v>321.64099999999996</v>
+        <v>303.238</v>
       </c>
       <c r="I943" t="n">
         <v>0.0</v>
@@ -35240,7 +35240,7 @@
         </is>
       </c>
       <c r="E951" t="n">
-        <v>1758.614</v>
+        <v>1714.01</v>
       </c>
       <c r="F951" t="n">
         <v>57.22</v>
@@ -35249,7 +35249,7 @@
         <v>0.0</v>
       </c>
       <c r="H951" t="n">
-        <v>1758.614</v>
+        <v>1714.01</v>
       </c>
       <c r="I951" t="n">
         <v>0.0</v>
@@ -35277,7 +35277,7 @@
         </is>
       </c>
       <c r="E952" t="n">
-        <v>852.9879999999999</v>
+        <v>884.614</v>
       </c>
       <c r="F952" t="n">
         <v>0.728</v>
@@ -35286,7 +35286,7 @@
         <v>0.0</v>
       </c>
       <c r="H952" t="n">
-        <v>852.9879999999999</v>
+        <v>884.614</v>
       </c>
       <c r="I952" t="n">
         <v>0.0</v>
@@ -35388,7 +35388,7 @@
         </is>
       </c>
       <c r="E955" t="n">
-        <v>5452.0</v>
+        <v>5390.0</v>
       </c>
       <c r="F955" t="n">
         <v>0.0</v>
@@ -35397,7 +35397,7 @@
         <v>180.0</v>
       </c>
       <c r="H955" t="n">
-        <v>5452.0</v>
+        <v>5390.0</v>
       </c>
       <c r="I955" t="n">
         <v>0.0</v>
@@ -35869,7 +35869,7 @@
         </is>
       </c>
       <c r="E968" t="n">
-        <v>76.954</v>
+        <v>68.044</v>
       </c>
       <c r="F968" t="n">
         <v>0.0</v>
@@ -35878,7 +35878,7 @@
         <v>0.0</v>
       </c>
       <c r="H968" t="n">
-        <v>76.954</v>
+        <v>68.044</v>
       </c>
       <c r="I968" t="n">
         <v>0.0</v>
@@ -36461,7 +36461,7 @@
         </is>
       </c>
       <c r="E984" t="n">
-        <v>3166.3329999999996</v>
+        <v>297.733</v>
       </c>
       <c r="F984" t="n">
         <v>16.1</v>
@@ -36470,10 +36470,10 @@
         <v>12.6</v>
       </c>
       <c r="H984" t="n">
-        <v>383.133</v>
+        <v>297.733</v>
       </c>
       <c r="I984" t="n">
-        <v>2783.2</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="985">
@@ -36498,7 +36498,7 @@
         </is>
       </c>
       <c r="E985" t="n">
-        <v>2334.89</v>
+        <v>1684.865</v>
       </c>
       <c r="F985" t="n">
         <v>37.268</v>
@@ -36507,7 +36507,7 @@
         <v>0.867</v>
       </c>
       <c r="H985" t="n">
-        <v>2334.89</v>
+        <v>1684.865</v>
       </c>
       <c r="I985" t="n">
         <v>0.0</v>
@@ -36535,7 +36535,7 @@
         </is>
       </c>
       <c r="E986" t="n">
-        <v>3748.862</v>
+        <v>3697.627</v>
       </c>
       <c r="F986" t="n">
         <v>16.434</v>
@@ -36544,7 +36544,7 @@
         <v>8.7</v>
       </c>
       <c r="H986" t="n">
-        <v>3748.862</v>
+        <v>3697.627</v>
       </c>
       <c r="I986" t="n">
         <v>0.0</v>
@@ -37423,7 +37423,7 @@
         </is>
       </c>
       <c r="E1010" t="n">
-        <v>19.516</v>
+        <v>3.503</v>
       </c>
       <c r="F1010" t="n">
         <v>0.0</v>
@@ -37432,7 +37432,7 @@
         <v>0.0</v>
       </c>
       <c r="H1010" t="n">
-        <v>19.516</v>
+        <v>3.503</v>
       </c>
       <c r="I1010" t="n">
         <v>0.0</v>
@@ -37497,7 +37497,7 @@
         </is>
       </c>
       <c r="E1012" t="n">
-        <v>134.908</v>
+        <v>63.904</v>
       </c>
       <c r="F1012" t="n">
         <v>0.0</v>
@@ -37506,7 +37506,7 @@
         <v>0.0</v>
       </c>
       <c r="H1012" t="n">
-        <v>134.908</v>
+        <v>63.904</v>
       </c>
       <c r="I1012" t="n">
         <v>0.0</v>
@@ -37534,7 +37534,7 @@
         </is>
       </c>
       <c r="E1013" t="n">
-        <v>8509.828</v>
+        <v>7125.25</v>
       </c>
       <c r="F1013" t="n">
         <v>0.0</v>
@@ -37543,7 +37543,7 @@
         <v>0.0</v>
       </c>
       <c r="H1013" t="n">
-        <v>8509.828</v>
+        <v>7125.25</v>
       </c>
       <c r="I1013" t="n">
         <v>0.0</v>
@@ -37756,7 +37756,7 @@
         </is>
       </c>
       <c r="E1019" t="n">
-        <v>5948.497</v>
+        <v>5778.402</v>
       </c>
       <c r="F1019" t="n">
         <v>68.241</v>
@@ -37765,7 +37765,7 @@
         <v>47.885999999999996</v>
       </c>
       <c r="H1019" t="n">
-        <v>5948.497</v>
+        <v>5778.402</v>
       </c>
       <c r="I1019" t="n">
         <v>0.0</v>
@@ -37830,7 +37830,7 @@
         </is>
       </c>
       <c r="E1021" t="n">
-        <v>1324.966</v>
+        <v>748.895</v>
       </c>
       <c r="F1021" t="n">
         <v>0.0</v>
@@ -37839,7 +37839,7 @@
         <v>0.0</v>
       </c>
       <c r="H1021" t="n">
-        <v>1324.966</v>
+        <v>748.895</v>
       </c>
       <c r="I1021" t="n">
         <v>0.0</v>
@@ -38052,7 +38052,7 @@
         </is>
       </c>
       <c r="E1027" t="n">
-        <v>4681.840999999999</v>
+        <v>4419.456999999999</v>
       </c>
       <c r="F1027" t="n">
         <v>0.0</v>
@@ -38061,7 +38061,7 @@
         <v>0.0</v>
       </c>
       <c r="H1027" t="n">
-        <v>4681.840999999999</v>
+        <v>4419.456999999999</v>
       </c>
       <c r="I1027" t="n">
         <v>0.0</v>
@@ -38089,7 +38089,7 @@
         </is>
       </c>
       <c r="E1028" t="n">
-        <v>4704.588</v>
+        <v>4488.561</v>
       </c>
       <c r="F1028" t="n">
         <v>0.8</v>
@@ -38098,7 +38098,7 @@
         <v>800.1</v>
       </c>
       <c r="H1028" t="n">
-        <v>4704.588</v>
+        <v>4488.561</v>
       </c>
       <c r="I1028" t="n">
         <v>0.0</v>
@@ -38200,7 +38200,7 @@
         </is>
       </c>
       <c r="E1031" t="n">
-        <v>7127.552</v>
+        <v>6242.198</v>
       </c>
       <c r="F1031" t="n">
         <v>0.0</v>
@@ -38209,7 +38209,7 @@
         <v>3.7279999999999998</v>
       </c>
       <c r="H1031" t="n">
-        <v>7127.552</v>
+        <v>6242.198</v>
       </c>
       <c r="I1031" t="n">
         <v>0.0</v>
@@ -38237,7 +38237,7 @@
         </is>
       </c>
       <c r="E1032" t="n">
-        <v>5714.636</v>
+        <v>4540.41</v>
       </c>
       <c r="F1032" t="n">
         <v>11.094</v>
@@ -38246,7 +38246,7 @@
         <v>12.426</v>
       </c>
       <c r="H1032" t="n">
-        <v>5714.636</v>
+        <v>4540.41</v>
       </c>
       <c r="I1032" t="n">
         <v>0.0</v>
@@ -38274,7 +38274,7 @@
         </is>
       </c>
       <c r="E1033" t="n">
-        <v>6666.093</v>
+        <v>6590.354</v>
       </c>
       <c r="F1033" t="n">
         <v>1.183</v>
@@ -38283,7 +38283,7 @@
         <v>3.846</v>
       </c>
       <c r="H1033" t="n">
-        <v>6666.093</v>
+        <v>6590.354</v>
       </c>
       <c r="I1033" t="n">
         <v>0.0</v>
@@ -38755,7 +38755,7 @@
         </is>
       </c>
       <c r="E1046" t="n">
-        <v>23.964</v>
+        <v>21.568</v>
       </c>
       <c r="F1046" t="n">
         <v>0.0</v>
@@ -38764,7 +38764,7 @@
         <v>694.956</v>
       </c>
       <c r="H1046" t="n">
-        <v>23.964</v>
+        <v>21.568</v>
       </c>
       <c r="I1046" t="n">
         <v>0.0</v>
@@ -38792,7 +38792,7 @@
         </is>
       </c>
       <c r="E1047" t="n">
-        <v>528.464</v>
+        <v>486.925</v>
       </c>
       <c r="F1047" t="n">
         <v>0.0</v>
@@ -38801,7 +38801,7 @@
         <v>23.077</v>
       </c>
       <c r="H1047" t="n">
-        <v>528.464</v>
+        <v>486.925</v>
       </c>
       <c r="I1047" t="n">
         <v>0.0</v>
@@ -39051,7 +39051,7 @@
         </is>
       </c>
       <c r="E1054" t="n">
-        <v>848.521</v>
+        <v>840.12</v>
       </c>
       <c r="F1054" t="n">
         <v>2.8</v>
@@ -39060,7 +39060,7 @@
         <v>0.0</v>
       </c>
       <c r="H1054" t="n">
-        <v>848.521</v>
+        <v>840.12</v>
       </c>
       <c r="I1054" t="n">
         <v>0.0</v>
@@ -39162,7 +39162,7 @@
         </is>
       </c>
       <c r="E1057" t="n">
-        <v>6338.4</v>
+        <v>5951.424</v>
       </c>
       <c r="F1057" t="n">
         <v>0.0</v>
@@ -39171,7 +39171,7 @@
         <v>0.0</v>
       </c>
       <c r="H1057" t="n">
-        <v>6338.4</v>
+        <v>5951.424</v>
       </c>
       <c r="I1057" t="n">
         <v>0.0</v>
@@ -39310,7 +39310,7 @@
         </is>
       </c>
       <c r="E1061" t="n">
-        <v>3600.288</v>
+        <v>3573.62</v>
       </c>
       <c r="F1061" t="n">
         <v>0.0</v>
@@ -39319,7 +39319,7 @@
         <v>0.0</v>
       </c>
       <c r="H1061" t="n">
-        <v>3600.288</v>
+        <v>3573.62</v>
       </c>
       <c r="I1061" t="n">
         <v>0.0</v>
@@ -39347,7 +39347,7 @@
         </is>
       </c>
       <c r="E1062" t="n">
-        <v>4421.991999999999</v>
+        <v>4411.075</v>
       </c>
       <c r="F1062" t="n">
         <v>3.639</v>
@@ -39356,7 +39356,7 @@
         <v>0.0</v>
       </c>
       <c r="H1062" t="n">
-        <v>4421.991999999999</v>
+        <v>4411.075</v>
       </c>
       <c r="I1062" t="n">
         <v>0.0</v>
@@ -39384,7 +39384,7 @@
         </is>
       </c>
       <c r="E1063" t="n">
-        <v>6990.518999999999</v>
+        <v>5305.662</v>
       </c>
       <c r="F1063" t="n">
         <v>4.852</v>
@@ -39393,7 +39393,7 @@
         <v>36.39</v>
       </c>
       <c r="H1063" t="n">
-        <v>6990.518999999999</v>
+        <v>5305.662</v>
       </c>
       <c r="I1063" t="n">
         <v>0.0</v>
@@ -39421,7 +39421,7 @@
         </is>
       </c>
       <c r="E1064" t="n">
-        <v>3480.316</v>
+        <v>3383.779</v>
       </c>
       <c r="F1064" t="n">
         <v>0.0</v>
@@ -39430,7 +39430,7 @@
         <v>47.608</v>
       </c>
       <c r="H1064" t="n">
-        <v>3480.316</v>
+        <v>3383.779</v>
       </c>
       <c r="I1064" t="n">
         <v>0.0</v>
@@ -39458,7 +39458,7 @@
         </is>
       </c>
       <c r="E1065" t="n">
-        <v>7676.396</v>
+        <v>7585.15</v>
       </c>
       <c r="F1065" t="n">
         <v>0.6589999999999999</v>
@@ -39467,7 +39467,7 @@
         <v>15.869000000000002</v>
       </c>
       <c r="H1065" t="n">
-        <v>7676.396</v>
+        <v>7585.15</v>
       </c>
       <c r="I1065" t="n">
         <v>0.0</v>
@@ -39495,7 +39495,7 @@
         </is>
       </c>
       <c r="E1066" t="n">
-        <v>4173.27</v>
+        <v>4145.828</v>
       </c>
       <c r="F1066" t="n">
         <v>0.0</v>
@@ -39504,7 +39504,7 @@
         <v>0.0</v>
       </c>
       <c r="H1066" t="n">
-        <v>4173.27</v>
+        <v>4145.828</v>
       </c>
       <c r="I1066" t="n">
         <v>0.0</v>
@@ -39532,7 +39532,7 @@
         </is>
       </c>
       <c r="E1067" t="n">
-        <v>17742.756</v>
+        <v>16887.14</v>
       </c>
       <c r="F1067" t="n">
         <v>3.634</v>
@@ -39541,7 +39541,7 @@
         <v>0.0</v>
       </c>
       <c r="H1067" t="n">
-        <v>17742.756</v>
+        <v>16887.14</v>
       </c>
       <c r="I1067" t="n">
         <v>0.0</v>
@@ -39569,7 +39569,7 @@
         </is>
       </c>
       <c r="E1068" t="n">
-        <v>19145.675199999998</v>
+        <v>19061.6622</v>
       </c>
       <c r="F1068" t="n">
         <v>4.667</v>
@@ -39578,7 +39578,7 @@
         <v>0.0</v>
       </c>
       <c r="H1068" t="n">
-        <v>11430.463</v>
+        <v>11346.45</v>
       </c>
       <c r="I1068" t="n">
         <v>7715.2122</v>
@@ -39606,7 +39606,7 @@
         </is>
       </c>
       <c r="E1069" t="n">
-        <v>9108.92</v>
+        <v>8887.413</v>
       </c>
       <c r="F1069" t="n">
         <v>0.32899999999999996</v>
@@ -39615,7 +39615,7 @@
         <v>3.967</v>
       </c>
       <c r="H1069" t="n">
-        <v>9108.92</v>
+        <v>8887.413</v>
       </c>
       <c r="I1069" t="n">
         <v>0.0</v>
@@ -39643,7 +39643,7 @@
         </is>
       </c>
       <c r="E1070" t="n">
-        <v>28933.211199999998</v>
+        <v>27673.0132</v>
       </c>
       <c r="F1070" t="n">
         <v>0.0</v>
@@ -39652,7 +39652,7 @@
         <v>18.669999999999998</v>
       </c>
       <c r="H1070" t="n">
-        <v>21217.999</v>
+        <v>19957.801</v>
       </c>
       <c r="I1070" t="n">
         <v>7715.2122</v>
@@ -39680,7 +39680,7 @@
         </is>
       </c>
       <c r="E1071" t="n">
-        <v>5869.961</v>
+        <v>5823.345</v>
       </c>
       <c r="F1071" t="n">
         <v>0.6589999999999999</v>
@@ -39689,7 +39689,7 @@
         <v>11.902</v>
       </c>
       <c r="H1071" t="n">
-        <v>5869.961</v>
+        <v>5823.345</v>
       </c>
       <c r="I1071" t="n">
         <v>0.0</v>
@@ -39717,7 +39717,7 @@
         </is>
       </c>
       <c r="E1072" t="n">
-        <v>44036.9206</v>
+        <v>42188.6286</v>
       </c>
       <c r="F1072" t="n">
         <v>0.0</v>
@@ -39726,7 +39726,7 @@
         <v>14.002</v>
       </c>
       <c r="H1072" t="n">
-        <v>20891.284</v>
+        <v>19042.992</v>
       </c>
       <c r="I1072" t="n">
         <v>23145.636599999998</v>
@@ -39754,7 +39754,7 @@
         </is>
       </c>
       <c r="E1073" t="n">
-        <v>11663.833</v>
+        <v>13997.533</v>
       </c>
       <c r="F1073" t="n">
         <v>0.0</v>
@@ -39766,7 +39766,7 @@
         <v>11663.833</v>
       </c>
       <c r="I1073" t="n">
-        <v>0.0</v>
+        <v>2333.7</v>
       </c>
     </row>
     <row r="1074">
@@ -39791,7 +39791,7 @@
         </is>
       </c>
       <c r="E1074" t="n">
-        <v>28944.1</v>
+        <v>27221.629999999997</v>
       </c>
       <c r="F1074" t="n">
         <v>2.972</v>
@@ -39800,7 +39800,7 @@
         <v>3.967</v>
       </c>
       <c r="H1074" t="n">
-        <v>28944.1</v>
+        <v>27221.629999999997</v>
       </c>
       <c r="I1074" t="n">
         <v>0.0</v>
@@ -39828,7 +39828,7 @@
         </is>
       </c>
       <c r="E1075" t="n">
-        <v>20253.060999999998</v>
+        <v>19503.905</v>
       </c>
       <c r="F1075" t="n">
         <v>1.984</v>
@@ -39837,7 +39837,7 @@
         <v>0.0</v>
       </c>
       <c r="H1075" t="n">
-        <v>20253.060999999998</v>
+        <v>19503.905</v>
       </c>
       <c r="I1075" t="n">
         <v>0.0</v>
@@ -39976,7 +39976,7 @@
         </is>
       </c>
       <c r="E1079" t="n">
-        <v>564.443</v>
+        <v>530.299</v>
       </c>
       <c r="F1079" t="n">
         <v>1.067</v>
@@ -39985,7 +39985,7 @@
         <v>0.0</v>
       </c>
       <c r="H1079" t="n">
-        <v>564.443</v>
+        <v>530.299</v>
       </c>
       <c r="I1079" t="n">
         <v>0.0</v>
@@ -40013,7 +40013,7 @@
         </is>
       </c>
       <c r="E1080" t="n">
-        <v>1584.0</v>
+        <v>1512.0</v>
       </c>
       <c r="F1080" t="n">
         <v>0.0</v>
@@ -40022,7 +40022,7 @@
         <v>0.0</v>
       </c>
       <c r="H1080" t="n">
-        <v>1584.0</v>
+        <v>1512.0</v>
       </c>
       <c r="I1080" t="n">
         <v>0.0</v>
@@ -40309,7 +40309,7 @@
         </is>
       </c>
       <c r="E1088" t="n">
-        <v>3658.5362</v>
+        <v>1817.273</v>
       </c>
       <c r="F1088" t="n">
         <v>0.0</v>
@@ -40321,7 +40321,7 @@
         <v>1817.273</v>
       </c>
       <c r="I1088" t="n">
-        <v>1841.2632</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1089">
@@ -40346,7 +40346,7 @@
         </is>
       </c>
       <c r="E1089" t="n">
-        <v>560.111</v>
+        <v>576.115</v>
       </c>
       <c r="F1089" t="n">
         <v>0.0</v>
@@ -40355,7 +40355,7 @@
         <v>0.0</v>
       </c>
       <c r="H1089" t="n">
-        <v>560.111</v>
+        <v>576.115</v>
       </c>
       <c r="I1089" t="n">
         <v>0.0</v>
@@ -40383,7 +40383,7 @@
         </is>
       </c>
       <c r="E1090" t="n">
-        <v>103.989</v>
+        <v>103.99</v>
       </c>
       <c r="F1090" t="n">
         <v>0.0</v>
@@ -40392,7 +40392,7 @@
         <v>0.0</v>
       </c>
       <c r="H1090" t="n">
-        <v>103.989</v>
+        <v>103.99</v>
       </c>
       <c r="I1090" t="n">
         <v>0.0</v>
@@ -40457,7 +40457,7 @@
         </is>
       </c>
       <c r="E1092" t="n">
-        <v>2634.946</v>
+        <v>2628.949</v>
       </c>
       <c r="F1092" t="n">
         <v>0.0</v>
@@ -40466,7 +40466,7 @@
         <v>0.0</v>
       </c>
       <c r="H1092" t="n">
-        <v>2634.946</v>
+        <v>2628.949</v>
       </c>
       <c r="I1092" t="n">
         <v>0.0</v>
@@ -40494,7 +40494,7 @@
         </is>
       </c>
       <c r="E1093" t="n">
-        <v>4034.386</v>
+        <v>3810.479</v>
       </c>
       <c r="F1093" t="n">
         <v>0.0</v>
@@ -40503,7 +40503,7 @@
         <v>0.0</v>
       </c>
       <c r="H1093" t="n">
-        <v>4034.386</v>
+        <v>3810.479</v>
       </c>
       <c r="I1093" t="n">
         <v>0.0</v>
@@ -40531,7 +40531,7 @@
         </is>
       </c>
       <c r="E1094" t="n">
-        <v>9185.8362</v>
+        <v>6745.349</v>
       </c>
       <c r="F1094" t="n">
         <v>0.0</v>
@@ -40540,10 +40540,10 @@
         <v>0.0</v>
       </c>
       <c r="H1094" t="n">
-        <v>6749.349</v>
+        <v>6745.349</v>
       </c>
       <c r="I1094" t="n">
-        <v>2436.4872</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1095">
@@ -40716,7 +40716,7 @@
         </is>
       </c>
       <c r="E1099" t="n">
-        <v>509.603</v>
+        <v>410.651</v>
       </c>
       <c r="F1099" t="n">
         <v>0.0</v>
@@ -40725,7 +40725,7 @@
         <v>0.0</v>
       </c>
       <c r="H1099" t="n">
-        <v>509.603</v>
+        <v>410.651</v>
       </c>
       <c r="I1099" t="n">
         <v>0.0</v>
@@ -40790,7 +40790,7 @@
         </is>
       </c>
       <c r="E1101" t="n">
-        <v>76.687</v>
+        <v>383.43899999999996</v>
       </c>
       <c r="F1101" t="n">
         <v>0.0</v>
@@ -40799,7 +40799,7 @@
         <v>2.474</v>
       </c>
       <c r="H1101" t="n">
-        <v>76.687</v>
+        <v>383.43899999999996</v>
       </c>
       <c r="I1101" t="n">
         <v>0.0</v>
@@ -41382,7 +41382,7 @@
         </is>
       </c>
       <c r="E1117" t="n">
-        <v>2022.225</v>
+        <v>2060.238</v>
       </c>
       <c r="F1117" t="n">
         <v>0.0</v>
@@ -41391,7 +41391,7 @@
         <v>0.0</v>
       </c>
       <c r="H1117" t="n">
-        <v>2022.225</v>
+        <v>2060.238</v>
       </c>
       <c r="I1117" t="n">
         <v>0.0</v>
@@ -41419,7 +41419,7 @@
         </is>
       </c>
       <c r="E1118" t="n">
-        <v>2106.34</v>
+        <v>2166.191</v>
       </c>
       <c r="F1118" t="n">
         <v>0.09000000000000001</v>
@@ -41428,7 +41428,7 @@
         <v>0.0</v>
       </c>
       <c r="H1118" t="n">
-        <v>2106.34</v>
+        <v>2166.191</v>
       </c>
       <c r="I1118" t="n">
         <v>0.0</v>
@@ -41493,7 +41493,7 @@
         </is>
       </c>
       <c r="E1120" t="n">
-        <v>128.876</v>
+        <v>104.724</v>
       </c>
       <c r="F1120" t="n">
         <v>0.20900000000000002</v>
@@ -41502,7 +41502,7 @@
         <v>0.0</v>
       </c>
       <c r="H1120" t="n">
-        <v>128.876</v>
+        <v>104.724</v>
       </c>
       <c r="I1120" t="n">
         <v>0.0</v>
@@ -41530,7 +41530,7 @@
         </is>
       </c>
       <c r="E1121" t="n">
-        <v>2838.191</v>
+        <v>2834.299</v>
       </c>
       <c r="F1121" t="n">
         <v>0.42000000000000004</v>
@@ -41539,7 +41539,7 @@
         <v>0.0</v>
       </c>
       <c r="H1121" t="n">
-        <v>2838.191</v>
+        <v>2834.299</v>
       </c>
       <c r="I1121" t="n">
         <v>0.0</v>
@@ -41567,7 +41567,7 @@
         </is>
       </c>
       <c r="E1122" t="n">
-        <v>3542.925</v>
+        <v>3540.4</v>
       </c>
       <c r="F1122" t="n">
         <v>0.421</v>
@@ -41576,7 +41576,7 @@
         <v>1.262</v>
       </c>
       <c r="H1122" t="n">
-        <v>3542.925</v>
+        <v>3540.4</v>
       </c>
       <c r="I1122" t="n">
         <v>0.0</v>
@@ -41604,7 +41604,7 @@
         </is>
       </c>
       <c r="E1123" t="n">
-        <v>603.1590000000001</v>
+        <v>290.025</v>
       </c>
       <c r="F1123" t="n">
         <v>0.416</v>
@@ -41613,7 +41613,7 @@
         <v>0.0</v>
       </c>
       <c r="H1123" t="n">
-        <v>603.1590000000001</v>
+        <v>290.025</v>
       </c>
       <c r="I1123" t="n">
         <v>0.0</v>
@@ -41678,7 +41678,7 @@
         </is>
       </c>
       <c r="E1125" t="n">
-        <v>6459.785</v>
+        <v>5764.517</v>
       </c>
       <c r="F1125" t="n">
         <v>0.0</v>
@@ -41687,7 +41687,7 @@
         <v>0.0</v>
       </c>
       <c r="H1125" t="n">
-        <v>6459.785</v>
+        <v>5764.517</v>
       </c>
       <c r="I1125" t="n">
         <v>0.0</v>
@@ -41715,7 +41715,7 @@
         </is>
       </c>
       <c r="E1126" t="n">
-        <v>2077.751</v>
+        <v>1148.092</v>
       </c>
       <c r="F1126" t="n">
         <v>0.0</v>
@@ -41724,7 +41724,7 @@
         <v>0.0</v>
       </c>
       <c r="H1126" t="n">
-        <v>2077.751</v>
+        <v>1148.092</v>
       </c>
       <c r="I1126" t="n">
         <v>0.0</v>
@@ -41789,7 +41789,7 @@
         </is>
       </c>
       <c r="E1128" t="n">
-        <v>7093.445</v>
+        <v>6864.622</v>
       </c>
       <c r="F1128" t="n">
         <v>0.0</v>
@@ -41798,7 +41798,7 @@
         <v>0.0</v>
       </c>
       <c r="H1128" t="n">
-        <v>7093.445</v>
+        <v>6864.622</v>
       </c>
       <c r="I1128" t="n">
         <v>0.0</v>
@@ -41826,7 +41826,7 @@
         </is>
       </c>
       <c r="E1129" t="n">
-        <v>22668.0</v>
+        <v>22624.0</v>
       </c>
       <c r="F1129" t="n">
         <v>6.4</v>
@@ -41835,7 +41835,7 @@
         <v>0.0</v>
       </c>
       <c r="H1129" t="n">
-        <v>22668.0</v>
+        <v>22624.0</v>
       </c>
       <c r="I1129" t="n">
         <v>0.0</v>
@@ -41900,7 +41900,7 @@
         </is>
       </c>
       <c r="E1131" t="n">
-        <v>1485.186</v>
+        <v>1473.177</v>
       </c>
       <c r="F1131" t="n">
         <v>0.0</v>
@@ -41909,7 +41909,7 @@
         <v>8.005999999999998</v>
       </c>
       <c r="H1131" t="n">
-        <v>1485.186</v>
+        <v>1473.177</v>
       </c>
       <c r="I1131" t="n">
         <v>0.0</v>
@@ -41937,7 +41937,7 @@
         </is>
       </c>
       <c r="E1132" t="n">
-        <v>1363.0892</v>
+        <v>974.779</v>
       </c>
       <c r="F1132" t="n">
         <v>0.0</v>
@@ -41946,10 +41946,10 @@
         <v>0.0</v>
       </c>
       <c r="H1132" t="n">
-        <v>968.774</v>
+        <v>974.779</v>
       </c>
       <c r="I1132" t="n">
-        <v>394.3152</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1133">
@@ -41974,7 +41974,7 @@
         </is>
       </c>
       <c r="E1133" t="n">
-        <v>1599.279</v>
+        <v>1517.214</v>
       </c>
       <c r="F1133" t="n">
         <v>0.0</v>
@@ -41983,7 +41983,7 @@
         <v>0.0</v>
       </c>
       <c r="H1133" t="n">
-        <v>1599.279</v>
+        <v>1517.214</v>
       </c>
       <c r="I1133" t="n">
         <v>0.0</v>
@@ -42344,7 +42344,7 @@
         </is>
       </c>
       <c r="E1143" t="n">
-        <v>1475.832</v>
+        <v>1474.8990000000001</v>
       </c>
       <c r="F1143" t="n">
         <v>0.0</v>
@@ -42353,7 +42353,7 @@
         <v>0.0</v>
       </c>
       <c r="H1143" t="n">
-        <v>1475.832</v>
+        <v>1474.8990000000001</v>
       </c>
       <c r="I1143" t="n">
         <v>0.0</v>
@@ -42381,7 +42381,7 @@
         </is>
       </c>
       <c r="E1144" t="n">
-        <v>4149.715</v>
+        <v>4323.4185</v>
       </c>
       <c r="F1144" t="n">
         <v>0.428</v>
@@ -42390,10 +42390,10 @@
         <v>0.0</v>
       </c>
       <c r="H1144" t="n">
-        <v>4149.715</v>
+        <v>3882.7329999999997</v>
       </c>
       <c r="I1144" t="n">
-        <v>0.0</v>
+        <v>440.6855</v>
       </c>
     </row>
     <row r="1145">
@@ -42418,7 +42418,7 @@
         </is>
       </c>
       <c r="E1145" t="n">
-        <v>1791.835</v>
+        <v>995.1750000000001</v>
       </c>
       <c r="F1145" t="n">
         <v>0.428</v>
@@ -42427,7 +42427,7 @@
         <v>0.0</v>
       </c>
       <c r="H1145" t="n">
-        <v>1791.835</v>
+        <v>995.1750000000001</v>
       </c>
       <c r="I1145" t="n">
         <v>0.0</v>
@@ -42455,7 +42455,7 @@
         </is>
       </c>
       <c r="E1146" t="n">
-        <v>3035.7419999999997</v>
+        <v>3033.875</v>
       </c>
       <c r="F1146" t="n">
         <v>0.0</v>
@@ -42464,7 +42464,7 @@
         <v>0.0</v>
       </c>
       <c r="H1146" t="n">
-        <v>3035.7419999999997</v>
+        <v>3033.875</v>
       </c>
       <c r="I1146" t="n">
         <v>0.0</v>
@@ -42529,7 +42529,7 @@
         </is>
       </c>
       <c r="E1148" t="n">
-        <v>2784.018</v>
+        <v>2577.703</v>
       </c>
       <c r="F1148" t="n">
         <v>10.265</v>
@@ -42538,7 +42538,7 @@
         <v>0.0</v>
       </c>
       <c r="H1148" t="n">
-        <v>2784.018</v>
+        <v>2577.703</v>
       </c>
       <c r="I1148" t="n">
         <v>0.0</v>
@@ -42640,7 +42640,7 @@
         </is>
       </c>
       <c r="E1151" t="n">
-        <v>9933.347000000002</v>
+        <v>9242.704</v>
       </c>
       <c r="F1151" t="n">
         <v>39.898999999999994</v>
@@ -42649,7 +42649,7 @@
         <v>13.766</v>
       </c>
       <c r="H1151" t="n">
-        <v>9933.347000000002</v>
+        <v>9242.704</v>
       </c>
       <c r="I1151" t="n">
         <v>0.0</v>
@@ -42714,7 +42714,7 @@
         </is>
       </c>
       <c r="E1153" t="n">
-        <v>8662.122</v>
+        <v>8445.415</v>
       </c>
       <c r="F1153" t="n">
         <v>27.599</v>
@@ -42723,7 +42723,7 @@
         <v>7.155</v>
       </c>
       <c r="H1153" t="n">
-        <v>8662.122</v>
+        <v>8445.415</v>
       </c>
       <c r="I1153" t="n">
         <v>0.0</v>
@@ -42751,7 +42751,7 @@
         </is>
       </c>
       <c r="E1154" t="n">
-        <v>13727.863</v>
+        <v>14149.2148</v>
       </c>
       <c r="F1154" t="n">
         <v>20.001</v>
@@ -42760,10 +42760,10 @@
         <v>2994.8160000000003</v>
       </c>
       <c r="H1154" t="n">
-        <v>13727.863</v>
+        <v>13159.832</v>
       </c>
       <c r="I1154" t="n">
-        <v>0.0</v>
+        <v>989.3828</v>
       </c>
     </row>
     <row r="1155">
@@ -42788,7 +42788,7 @@
         </is>
       </c>
       <c r="E1155" t="n">
-        <v>18863.6</v>
+        <v>15999.6</v>
       </c>
       <c r="F1155" t="n">
         <v>48.0</v>
@@ -42797,7 +42797,7 @@
         <v>16.8</v>
       </c>
       <c r="H1155" t="n">
-        <v>18863.6</v>
+        <v>15999.6</v>
       </c>
       <c r="I1155" t="n">
         <v>0.0</v>
@@ -42862,7 +42862,7 @@
         </is>
       </c>
       <c r="E1157" t="n">
-        <v>4588.513</v>
+        <v>4545.849</v>
       </c>
       <c r="F1157" t="n">
         <v>8.0</v>
@@ -42871,7 +42871,7 @@
         <v>0.0</v>
       </c>
       <c r="H1157" t="n">
-        <v>4588.513</v>
+        <v>4545.849</v>
       </c>
       <c r="I1157" t="n">
         <v>0.0</v>
@@ -42899,7 +42899,7 @@
         </is>
       </c>
       <c r="E1158" t="n">
-        <v>3955.2</v>
+        <v>3662.4</v>
       </c>
       <c r="F1158" t="n">
         <v>0.0</v>
@@ -42908,7 +42908,7 @@
         <v>0.0</v>
       </c>
       <c r="H1158" t="n">
-        <v>3955.2</v>
+        <v>3662.4</v>
       </c>
       <c r="I1158" t="n">
         <v>0.0</v>
@@ -42936,7 +42936,7 @@
         </is>
       </c>
       <c r="E1159" t="n">
-        <v>1358.4</v>
+        <v>1344.0</v>
       </c>
       <c r="F1159" t="n">
         <v>0.4</v>
@@ -42945,7 +42945,7 @@
         <v>0.0</v>
       </c>
       <c r="H1159" t="n">
-        <v>1358.4</v>
+        <v>1344.0</v>
       </c>
       <c r="I1159" t="n">
         <v>0.0</v>
@@ -42973,7 +42973,7 @@
         </is>
       </c>
       <c r="E1160" t="n">
-        <v>4362.7119999999995</v>
+        <v>4357.112</v>
       </c>
       <c r="F1160" t="n">
         <v>0.0</v>
@@ -42982,7 +42982,7 @@
         <v>0.0</v>
       </c>
       <c r="H1160" t="n">
-        <v>4362.7119999999995</v>
+        <v>4357.112</v>
       </c>
       <c r="I1160" t="n">
         <v>0.0</v>
@@ -43010,7 +43010,7 @@
         </is>
       </c>
       <c r="E1161" t="n">
-        <v>747.882</v>
+        <v>581.016</v>
       </c>
       <c r="F1161" t="n">
         <v>0.428</v>
@@ -43019,7 +43019,7 @@
         <v>0.0</v>
       </c>
       <c r="H1161" t="n">
-        <v>747.882</v>
+        <v>581.016</v>
       </c>
       <c r="I1161" t="n">
         <v>0.0</v>
@@ -43158,7 +43158,7 @@
         </is>
       </c>
       <c r="E1165" t="n">
-        <v>6933.6</v>
+        <v>6307.2</v>
       </c>
       <c r="F1165" t="n">
         <v>0.0</v>
@@ -43167,7 +43167,7 @@
         <v>4.0</v>
       </c>
       <c r="H1165" t="n">
-        <v>6933.6</v>
+        <v>6307.2</v>
       </c>
       <c r="I1165" t="n">
         <v>0.0</v>
@@ -43195,7 +43195,7 @@
         </is>
       </c>
       <c r="E1166" t="n">
-        <v>7334.7970000000005</v>
+        <v>7142.685</v>
       </c>
       <c r="F1166" t="n">
         <v>0.0</v>
@@ -43204,7 +43204,7 @@
         <v>5.1000000000000005</v>
       </c>
       <c r="H1166" t="n">
-        <v>7334.7970000000005</v>
+        <v>7142.685</v>
       </c>
       <c r="I1166" t="n">
         <v>0.0</v>
@@ -43232,7 +43232,7 @@
         </is>
       </c>
       <c r="E1167" t="n">
-        <v>12339.617</v>
+        <v>10762.204</v>
       </c>
       <c r="F1167" t="n">
         <v>0.0</v>
@@ -43241,7 +43241,7 @@
         <v>20.668</v>
       </c>
       <c r="H1167" t="n">
-        <v>12339.617</v>
+        <v>10762.204</v>
       </c>
       <c r="I1167" t="n">
         <v>0.0</v>
@@ -43417,7 +43417,7 @@
         </is>
       </c>
       <c r="E1172" t="n">
-        <v>7688.0</v>
+        <v>7302.599999999999</v>
       </c>
       <c r="F1172" t="n">
         <v>0.6</v>
@@ -43426,7 +43426,7 @@
         <v>339.2</v>
       </c>
       <c r="H1172" t="n">
-        <v>7688.0</v>
+        <v>7302.599999999999</v>
       </c>
       <c r="I1172" t="n">
         <v>0.0</v>
@@ -43713,7 +43713,7 @@
         </is>
       </c>
       <c r="E1180" t="n">
-        <v>709.2</v>
+        <v>680.4</v>
       </c>
       <c r="F1180" t="n">
         <v>0.0</v>
@@ -43722,7 +43722,7 @@
         <v>0.0</v>
       </c>
       <c r="H1180" t="n">
-        <v>709.2</v>
+        <v>680.4</v>
       </c>
       <c r="I1180" t="n">
         <v>0.0</v>
@@ -43750,7 +43750,7 @@
         </is>
       </c>
       <c r="E1181" t="n">
-        <v>2020.6</v>
+        <v>1966.3999999999999</v>
       </c>
       <c r="F1181" t="n">
         <v>0.0</v>
@@ -43759,7 +43759,7 @@
         <v>4.8</v>
       </c>
       <c r="H1181" t="n">
-        <v>2020.6</v>
+        <v>1966.3999999999999</v>
       </c>
       <c r="I1181" t="n">
         <v>0.0</v>
@@ -43787,7 +43787,7 @@
         </is>
       </c>
       <c r="E1182" t="n">
-        <v>2233.6</v>
+        <v>2211.8</v>
       </c>
       <c r="F1182" t="n">
         <v>0.4</v>
@@ -43796,7 +43796,7 @@
         <v>0.0</v>
       </c>
       <c r="H1182" t="n">
-        <v>2233.6</v>
+        <v>2211.8</v>
       </c>
       <c r="I1182" t="n">
         <v>0.0</v>
@@ -43861,7 +43861,7 @@
         </is>
       </c>
       <c r="E1184" t="n">
-        <v>2902.3999999999996</v>
+        <v>2351.2</v>
       </c>
       <c r="F1184" t="n">
         <v>8.4</v>
@@ -43870,7 +43870,7 @@
         <v>0.0</v>
       </c>
       <c r="H1184" t="n">
-        <v>2902.3999999999996</v>
+        <v>2351.2</v>
       </c>
       <c r="I1184" t="n">
         <v>0.0</v>
@@ -43898,7 +43898,7 @@
         </is>
       </c>
       <c r="E1185" t="n">
-        <v>2422.702</v>
+        <v>2344.294</v>
       </c>
       <c r="F1185" t="n">
         <v>0.26699999999999996</v>
@@ -43907,7 +43907,7 @@
         <v>3.2</v>
       </c>
       <c r="H1185" t="n">
-        <v>2422.702</v>
+        <v>2344.294</v>
       </c>
       <c r="I1185" t="n">
         <v>0.0</v>
@@ -43935,7 +43935,7 @@
         </is>
       </c>
       <c r="E1186" t="n">
-        <v>2030.4</v>
+        <v>1917.6000000000001</v>
       </c>
       <c r="F1186" t="n">
         <v>0.0</v>
@@ -43944,7 +43944,7 @@
         <v>0.0</v>
       </c>
       <c r="H1186" t="n">
-        <v>2030.4</v>
+        <v>1917.6000000000001</v>
       </c>
       <c r="I1186" t="n">
         <v>0.0</v>
@@ -43972,7 +43972,7 @@
         </is>
       </c>
       <c r="E1187" t="n">
-        <v>686.049</v>
+        <v>649.649</v>
       </c>
       <c r="F1187" t="n">
         <v>0.0</v>
@@ -43981,7 +43981,7 @@
         <v>0.0</v>
       </c>
       <c r="H1187" t="n">
-        <v>686.049</v>
+        <v>649.649</v>
       </c>
       <c r="I1187" t="n">
         <v>0.0</v>
@@ -44009,7 +44009,7 @@
         </is>
       </c>
       <c r="E1188" t="n">
-        <v>2777.388</v>
+        <v>2689.396</v>
       </c>
       <c r="F1188" t="n">
         <v>0.6669999999999999</v>
@@ -44018,7 +44018,7 @@
         <v>0.0</v>
       </c>
       <c r="H1188" t="n">
-        <v>2777.388</v>
+        <v>2689.396</v>
       </c>
       <c r="I1188" t="n">
         <v>0.0</v>
@@ -44046,7 +44046,7 @@
         </is>
       </c>
       <c r="E1189" t="n">
-        <v>1763.6000000000001</v>
+        <v>1745.6</v>
       </c>
       <c r="F1189" t="n">
         <v>2.8</v>
@@ -44055,7 +44055,7 @@
         <v>0.8</v>
       </c>
       <c r="H1189" t="n">
-        <v>1763.6000000000001</v>
+        <v>1745.6</v>
       </c>
       <c r="I1189" t="n">
         <v>0.0</v>
@@ -44083,7 +44083,7 @@
         </is>
       </c>
       <c r="E1190" t="n">
-        <v>1936.8</v>
+        <v>1908.0</v>
       </c>
       <c r="F1190" t="n">
         <v>0.0</v>
@@ -44092,7 +44092,7 @@
         <v>0.0</v>
       </c>
       <c r="H1190" t="n">
-        <v>1936.8</v>
+        <v>1908.0</v>
       </c>
       <c r="I1190" t="n">
         <v>0.0</v>
@@ -44120,7 +44120,7 @@
         </is>
       </c>
       <c r="E1191" t="n">
-        <v>876.087</v>
+        <v>816.082</v>
       </c>
       <c r="F1191" t="n">
         <v>0.0</v>
@@ -44129,7 +44129,7 @@
         <v>708.071</v>
       </c>
       <c r="H1191" t="n">
-        <v>876.087</v>
+        <v>816.082</v>
       </c>
       <c r="I1191" t="n">
         <v>0.0</v>
@@ -44527,7 +44527,7 @@
         </is>
       </c>
       <c r="E1202" t="n">
-        <v>4378.799</v>
+        <v>4466.418</v>
       </c>
       <c r="F1202" t="n">
         <v>0.0</v>
@@ -44536,7 +44536,7 @@
         <v>0.0</v>
       </c>
       <c r="H1202" t="n">
-        <v>4378.799</v>
+        <v>4466.418</v>
       </c>
       <c r="I1202" t="n">
         <v>0.0</v>
@@ -44934,7 +44934,7 @@
         </is>
       </c>
       <c r="E1213" t="n">
-        <v>2671.505</v>
+        <v>2525.23</v>
       </c>
       <c r="F1213" t="n">
         <v>0.0</v>
@@ -44943,7 +44943,7 @@
         <v>636.93</v>
       </c>
       <c r="H1213" t="n">
-        <v>2671.505</v>
+        <v>2525.23</v>
       </c>
       <c r="I1213" t="n">
         <v>0.0</v>
@@ -44971,7 +44971,7 @@
         </is>
       </c>
       <c r="E1214" t="n">
-        <v>166.87</v>
+        <v>140.598</v>
       </c>
       <c r="F1214" t="n">
         <v>0.0</v>
@@ -44980,7 +44980,7 @@
         <v>4.26</v>
       </c>
       <c r="H1214" t="n">
-        <v>166.87</v>
+        <v>140.598</v>
       </c>
       <c r="I1214" t="n">
         <v>0.0</v>
@@ -45378,7 +45378,7 @@
         </is>
       </c>
       <c r="E1225" t="n">
-        <v>1217.72</v>
+        <v>1033.109</v>
       </c>
       <c r="F1225" t="n">
         <v>0.0</v>
@@ -45387,7 +45387,7 @@
         <v>0.0</v>
       </c>
       <c r="H1225" t="n">
-        <v>1217.72</v>
+        <v>1033.109</v>
       </c>
       <c r="I1225" t="n">
         <v>0.0</v>
@@ -45415,7 +45415,7 @@
         </is>
       </c>
       <c r="E1226" t="n">
-        <v>2325.3830000000003</v>
+        <v>1993.4389999999999</v>
       </c>
       <c r="F1226" t="n">
         <v>0.0</v>
@@ -45424,7 +45424,7 @@
         <v>1.7750000000000001</v>
       </c>
       <c r="H1226" t="n">
-        <v>2325.3830000000003</v>
+        <v>1993.4389999999999</v>
       </c>
       <c r="I1226" t="n">
         <v>0.0</v>
@@ -45452,7 +45452,7 @@
         </is>
       </c>
       <c r="E1227" t="n">
-        <v>5370.018</v>
+        <v>5349.249</v>
       </c>
       <c r="F1227" t="n">
         <v>0.0</v>
@@ -45461,7 +45461,7 @@
         <v>0.0</v>
       </c>
       <c r="H1227" t="n">
-        <v>5370.018</v>
+        <v>5349.249</v>
       </c>
       <c r="I1227" t="n">
         <v>0.0</v>
@@ -45526,7 +45526,7 @@
         </is>
       </c>
       <c r="E1229" t="n">
-        <v>3478.774</v>
+        <v>2380.424</v>
       </c>
       <c r="F1229" t="n">
         <v>0.0</v>
@@ -45535,7 +45535,7 @@
         <v>5.991</v>
       </c>
       <c r="H1229" t="n">
-        <v>3478.774</v>
+        <v>2380.424</v>
       </c>
       <c r="I1229" t="n">
         <v>0.0</v>
@@ -45600,7 +45600,7 @@
         </is>
       </c>
       <c r="E1231" t="n">
-        <v>3562.035</v>
+        <v>3299.32</v>
       </c>
       <c r="F1231" t="n">
         <v>0.0</v>
@@ -45609,7 +45609,7 @@
         <v>0.0</v>
       </c>
       <c r="H1231" t="n">
-        <v>3562.035</v>
+        <v>3299.32</v>
       </c>
       <c r="I1231" t="n">
         <v>0.0</v>
@@ -45785,7 +45785,7 @@
         </is>
       </c>
       <c r="E1236" t="n">
-        <v>3802.264</v>
+        <v>3696.94</v>
       </c>
       <c r="F1236" t="n">
         <v>0.0</v>
@@ -45794,7 +45794,7 @@
         <v>0.0</v>
       </c>
       <c r="H1236" t="n">
-        <v>3802.264</v>
+        <v>3696.94</v>
       </c>
       <c r="I1236" t="n">
         <v>0.0</v>
@@ -46118,7 +46118,7 @@
         </is>
       </c>
       <c r="E1245" t="n">
-        <v>0.0</v>
+        <v>410.7312</v>
       </c>
       <c r="F1245" t="n">
         <v>0.0</v>
@@ -46130,7 +46130,7 @@
         <v>0.0</v>
       </c>
       <c r="I1245" t="n">
-        <v>0.0</v>
+        <v>410.7312</v>
       </c>
     </row>
     <row r="1246">
@@ -46155,7 +46155,7 @@
         </is>
       </c>
       <c r="E1246" t="n">
-        <v>2570.185</v>
+        <v>2562.951</v>
       </c>
       <c r="F1246" t="n">
         <v>0.583</v>
@@ -46164,7 +46164,7 @@
         <v>0.0</v>
       </c>
       <c r="H1246" t="n">
-        <v>2570.185</v>
+        <v>2562.951</v>
       </c>
       <c r="I1246" t="n">
         <v>0.0</v>
@@ -46192,7 +46192,7 @@
         </is>
       </c>
       <c r="E1247" t="n">
-        <v>1491.913</v>
+        <v>1488.996</v>
       </c>
       <c r="F1247" t="n">
         <v>0.35100000000000003</v>
@@ -46201,7 +46201,7 @@
         <v>0.0</v>
       </c>
       <c r="H1247" t="n">
-        <v>1491.913</v>
+        <v>1488.996</v>
       </c>
       <c r="I1247" t="n">
         <v>0.0</v>
@@ -46229,7 +46229,7 @@
         </is>
       </c>
       <c r="E1248" t="n">
-        <v>426.73499999999996</v>
+        <v>415.125</v>
       </c>
       <c r="F1248" t="n">
         <v>0.0</v>
@@ -46238,7 +46238,7 @@
         <v>0.0</v>
       </c>
       <c r="H1248" t="n">
-        <v>426.73499999999996</v>
+        <v>415.125</v>
       </c>
       <c r="I1248" t="n">
         <v>0.0</v>
@@ -46266,7 +46266,7 @@
         </is>
       </c>
       <c r="E1249" t="n">
-        <v>651.645</v>
+        <v>449.685</v>
       </c>
       <c r="F1249" t="n">
         <v>0.0</v>
@@ -46275,7 +46275,7 @@
         <v>0.135</v>
       </c>
       <c r="H1249" t="n">
-        <v>651.645</v>
+        <v>449.685</v>
       </c>
       <c r="I1249" t="n">
         <v>0.0</v>
@@ -46340,7 +46340,7 @@
         </is>
       </c>
       <c r="E1251" t="n">
-        <v>0.27</v>
+        <v>725.355</v>
       </c>
       <c r="F1251" t="n">
         <v>0.0</v>
@@ -46349,7 +46349,7 @@
         <v>0.135</v>
       </c>
       <c r="H1251" t="n">
-        <v>0.27</v>
+        <v>725.355</v>
       </c>
       <c r="I1251" t="n">
         <v>0.0</v>
@@ -46377,7 +46377,7 @@
         </is>
       </c>
       <c r="E1252" t="n">
-        <v>1658.14</v>
+        <v>1467.4</v>
       </c>
       <c r="F1252" t="n">
         <v>0.0</v>
@@ -46386,7 +46386,7 @@
         <v>1.5399999999999998</v>
       </c>
       <c r="H1252" t="n">
-        <v>1658.14</v>
+        <v>1467.4</v>
       </c>
       <c r="I1252" t="n">
         <v>0.0</v>
@@ -46488,7 +46488,7 @@
         </is>
       </c>
       <c r="E1255" t="n">
-        <v>283.77</v>
+        <v>922.32</v>
       </c>
       <c r="F1255" t="n">
         <v>0.0</v>
@@ -46497,7 +46497,7 @@
         <v>0.0</v>
       </c>
       <c r="H1255" t="n">
-        <v>283.77</v>
+        <v>922.32</v>
       </c>
       <c r="I1255" t="n">
         <v>0.0</v>
@@ -47413,7 +47413,7 @@
         </is>
       </c>
       <c r="E1280" t="n">
-        <v>608.486</v>
+        <v>605.817</v>
       </c>
       <c r="F1280" t="n">
         <v>0.0</v>
@@ -47422,7 +47422,7 @@
         <v>0.0</v>
       </c>
       <c r="H1280" t="n">
-        <v>608.486</v>
+        <v>605.817</v>
       </c>
       <c r="I1280" t="n">
         <v>0.0</v>
@@ -48708,7 +48708,7 @@
         </is>
       </c>
       <c r="E1315" t="n">
-        <v>245.0</v>
+        <v>213.0</v>
       </c>
       <c r="F1315" t="n">
         <v>0.0</v>
@@ -48717,7 +48717,7 @@
         <v>0.0</v>
       </c>
       <c r="H1315" t="n">
-        <v>245.0</v>
+        <v>213.0</v>
       </c>
       <c r="I1315" t="n">
         <v>0.0</v>
@@ -48967,7 +48967,7 @@
         </is>
       </c>
       <c r="E1322" t="n">
-        <v>3106.0</v>
+        <v>3076.0</v>
       </c>
       <c r="F1322" t="n">
         <v>0.0</v>
@@ -48976,7 +48976,7 @@
         <v>0.0</v>
       </c>
       <c r="H1322" t="n">
-        <v>3106.0</v>
+        <v>3076.0</v>
       </c>
       <c r="I1322" t="n">
         <v>0.0</v>
@@ -49115,7 +49115,7 @@
         </is>
       </c>
       <c r="E1326" t="n">
-        <v>4738.0</v>
+        <v>4528.0</v>
       </c>
       <c r="F1326" t="n">
         <v>0.0</v>
@@ -49124,7 +49124,7 @@
         <v>0.0</v>
       </c>
       <c r="H1326" t="n">
-        <v>4738.0</v>
+        <v>4528.0</v>
       </c>
       <c r="I1326" t="n">
         <v>0.0</v>
@@ -49559,7 +49559,7 @@
         </is>
       </c>
       <c r="E1338" t="n">
-        <v>60.6</v>
+        <v>60.699999999999996</v>
       </c>
       <c r="F1338" t="n">
         <v>0.0</v>
@@ -49568,7 +49568,7 @@
         <v>1.0</v>
       </c>
       <c r="H1338" t="n">
-        <v>60.6</v>
+        <v>60.699999999999996</v>
       </c>
       <c r="I1338" t="n">
         <v>0.0</v>
@@ -49596,7 +49596,7 @@
         </is>
       </c>
       <c r="E1339" t="n">
-        <v>816.0</v>
+        <v>576.0</v>
       </c>
       <c r="F1339" t="n">
         <v>0.0</v>
@@ -49605,7 +49605,7 @@
         <v>0.0</v>
       </c>
       <c r="H1339" t="n">
-        <v>816.0</v>
+        <v>576.0</v>
       </c>
       <c r="I1339" t="n">
         <v>0.0</v>
@@ -49966,7 +49966,7 @@
         </is>
       </c>
       <c r="E1349" t="n">
-        <v>364.7</v>
+        <v>365.0</v>
       </c>
       <c r="F1349" t="n">
         <v>0.0</v>
@@ -49975,7 +49975,7 @@
         <v>9.6</v>
       </c>
       <c r="H1349" t="n">
-        <v>364.7</v>
+        <v>365.0</v>
       </c>
       <c r="I1349" t="n">
         <v>0.0</v>
@@ -51261,7 +51261,7 @@
         </is>
       </c>
       <c r="E1384" t="n">
-        <v>1466.172</v>
+        <v>1462.169</v>
       </c>
       <c r="F1384" t="n">
         <v>0.0</v>
@@ -51270,7 +51270,7 @@
         <v>14.011</v>
       </c>
       <c r="H1384" t="n">
-        <v>1466.172</v>
+        <v>1462.169</v>
       </c>
       <c r="I1384" t="n">
         <v>0.0</v>
@@ -51298,7 +51298,7 @@
         </is>
       </c>
       <c r="E1385" t="n">
-        <v>3268.446</v>
+        <v>3178.374</v>
       </c>
       <c r="F1385" t="n">
         <v>0.0</v>
@@ -51307,7 +51307,7 @@
         <v>236.85600000000002</v>
       </c>
       <c r="H1385" t="n">
-        <v>3268.446</v>
+        <v>3178.374</v>
       </c>
       <c r="I1385" t="n">
         <v>0.0</v>
@@ -51335,7 +51335,7 @@
         </is>
       </c>
       <c r="E1386" t="n">
-        <v>523.041</v>
+        <v>513.045</v>
       </c>
       <c r="F1386" t="n">
         <v>0.0</v>
@@ -51344,7 +51344,7 @@
         <v>0.416</v>
       </c>
       <c r="H1386" t="n">
-        <v>523.041</v>
+        <v>513.045</v>
       </c>
       <c r="I1386" t="n">
         <v>0.0</v>
@@ -51372,7 +51372,7 @@
         </is>
       </c>
       <c r="E1387" t="n">
-        <v>633.505</v>
+        <v>617.492</v>
       </c>
       <c r="F1387" t="n">
         <v>0.0</v>
@@ -51381,7 +51381,7 @@
         <v>0.5559999999999999</v>
       </c>
       <c r="H1387" t="n">
-        <v>633.505</v>
+        <v>617.492</v>
       </c>
       <c r="I1387" t="n">
         <v>0.0</v>
@@ -51483,7 +51483,7 @@
         </is>
       </c>
       <c r="E1390" t="n">
-        <v>1094.904</v>
+        <v>1056.105</v>
       </c>
       <c r="F1390" t="n">
         <v>0.0</v>
@@ -51492,7 +51492,7 @@
         <v>0.0</v>
       </c>
       <c r="H1390" t="n">
-        <v>1094.904</v>
+        <v>1056.105</v>
       </c>
       <c r="I1390" t="n">
         <v>0.0</v>
@@ -52001,7 +52001,7 @@
         </is>
       </c>
       <c r="E1404" t="n">
-        <v>56.6</v>
+        <v>56.4</v>
       </c>
       <c r="F1404" t="n">
         <v>0.4</v>
@@ -52010,7 +52010,7 @@
         <v>0.0</v>
       </c>
       <c r="H1404" t="n">
-        <v>56.6</v>
+        <v>56.4</v>
       </c>
       <c r="I1404" t="n">
         <v>0.0</v>
@@ -52149,7 +52149,7 @@
         </is>
       </c>
       <c r="E1408" t="n">
-        <v>1317.859</v>
+        <v>1299.177</v>
       </c>
       <c r="F1408" t="n">
         <v>0.0</v>
@@ -52158,7 +52158,7 @@
         <v>2.669</v>
       </c>
       <c r="H1408" t="n">
-        <v>1317.859</v>
+        <v>1299.177</v>
       </c>
       <c r="I1408" t="n">
         <v>0.0</v>
@@ -52223,7 +52223,7 @@
         </is>
       </c>
       <c r="E1410" t="n">
-        <v>176.16</v>
+        <v>170.88</v>
       </c>
       <c r="F1410" t="n">
         <v>0.0</v>
@@ -52232,7 +52232,7 @@
         <v>0.0</v>
       </c>
       <c r="H1410" t="n">
-        <v>176.16</v>
+        <v>170.88</v>
       </c>
       <c r="I1410" t="n">
         <v>0.0</v>
@@ -52704,7 +52704,7 @@
         </is>
       </c>
       <c r="E1423" t="n">
-        <v>2733.018</v>
+        <v>2612.922</v>
       </c>
       <c r="F1423" t="n">
         <v>0.0</v>
@@ -52713,7 +52713,7 @@
         <v>0.222</v>
       </c>
       <c r="H1423" t="n">
-        <v>2733.018</v>
+        <v>2612.922</v>
       </c>
       <c r="I1423" t="n">
         <v>0.0</v>
@@ -52741,7 +52741,7 @@
         </is>
       </c>
       <c r="E1424" t="n">
-        <v>257.227</v>
+        <v>255.095</v>
       </c>
       <c r="F1424" t="n">
         <v>0.0</v>
@@ -52750,7 +52750,7 @@
         <v>0.0</v>
       </c>
       <c r="H1424" t="n">
-        <v>257.227</v>
+        <v>255.095</v>
       </c>
       <c r="I1424" t="n">
         <v>0.0</v>
@@ -52926,7 +52926,7 @@
         </is>
       </c>
       <c r="E1429" t="n">
-        <v>915.398</v>
+        <v>1009.2509999999999</v>
       </c>
       <c r="F1429" t="n">
         <v>0.0</v>
@@ -52935,7 +52935,7 @@
         <v>112.201</v>
       </c>
       <c r="H1429" t="n">
-        <v>915.398</v>
+        <v>1009.2509999999999</v>
       </c>
       <c r="I1429" t="n">
         <v>0.0</v>
@@ -52963,7 +52963,7 @@
         </is>
       </c>
       <c r="E1430" t="n">
-        <v>12054.0</v>
+        <v>11754.0</v>
       </c>
       <c r="F1430" t="n">
         <v>18.0</v>
@@ -52972,7 +52972,7 @@
         <v>114.0</v>
       </c>
       <c r="H1430" t="n">
-        <v>12054.0</v>
+        <v>11754.0</v>
       </c>
       <c r="I1430" t="n">
         <v>0.0</v>
@@ -53444,7 +53444,7 @@
         </is>
       </c>
       <c r="E1443" t="n">
-        <v>17.25</v>
+        <v>14.375</v>
       </c>
       <c r="F1443" t="n">
         <v>0.0</v>
@@ -53453,7 +53453,7 @@
         <v>33.75</v>
       </c>
       <c r="H1443" t="n">
-        <v>17.25</v>
+        <v>14.375</v>
       </c>
       <c r="I1443" t="n">
         <v>0.0</v>
@@ -53481,7 +53481,7 @@
         </is>
       </c>
       <c r="E1444" t="n">
-        <v>448.247</v>
+        <v>438.372</v>
       </c>
       <c r="F1444" t="n">
         <v>0.0</v>
@@ -53490,7 +53490,7 @@
         <v>40.5</v>
       </c>
       <c r="H1444" t="n">
-        <v>448.247</v>
+        <v>438.372</v>
       </c>
       <c r="I1444" t="n">
         <v>0.0</v>
@@ -53555,7 +53555,7 @@
         </is>
       </c>
       <c r="E1446" t="n">
-        <v>519.75</v>
+        <v>515.25</v>
       </c>
       <c r="F1446" t="n">
         <v>0.0</v>
@@ -53564,7 +53564,7 @@
         <v>20.625</v>
       </c>
       <c r="H1446" t="n">
-        <v>519.75</v>
+        <v>515.25</v>
       </c>
       <c r="I1446" t="n">
         <v>0.0</v>
@@ -53666,7 +53666,7 @@
         </is>
       </c>
       <c r="E1449" t="n">
-        <v>568.875</v>
+        <v>562.5</v>
       </c>
       <c r="F1449" t="n">
         <v>0.0</v>
@@ -53675,7 +53675,7 @@
         <v>38.25</v>
       </c>
       <c r="H1449" t="n">
-        <v>568.875</v>
+        <v>562.5</v>
       </c>
       <c r="I1449" t="n">
         <v>0.0</v>
@@ -53703,7 +53703,7 @@
         </is>
       </c>
       <c r="E1450" t="n">
-        <v>688.25</v>
+        <v>684.875</v>
       </c>
       <c r="F1450" t="n">
         <v>0.375</v>
@@ -53712,7 +53712,7 @@
         <v>3.75</v>
       </c>
       <c r="H1450" t="n">
-        <v>688.25</v>
+        <v>684.875</v>
       </c>
       <c r="I1450" t="n">
         <v>0.0</v>
@@ -53777,7 +53777,7 @@
         </is>
       </c>
       <c r="E1452" t="n">
-        <v>313.0</v>
+        <v>304.0</v>
       </c>
       <c r="F1452" t="n">
         <v>0.0</v>
@@ -53786,7 +53786,7 @@
         <v>0.0</v>
       </c>
       <c r="H1452" t="n">
-        <v>313.0</v>
+        <v>304.0</v>
       </c>
       <c r="I1452" t="n">
         <v>0.0</v>
@@ -53851,7 +53851,7 @@
         </is>
       </c>
       <c r="E1454" t="n">
-        <v>410.25</v>
+        <v>276.75</v>
       </c>
       <c r="F1454" t="n">
         <v>0.0</v>
@@ -53860,7 +53860,7 @@
         <v>55.5</v>
       </c>
       <c r="H1454" t="n">
-        <v>410.25</v>
+        <v>276.75</v>
       </c>
       <c r="I1454" t="n">
         <v>0.0</v>
@@ -53925,7 +53925,7 @@
         </is>
       </c>
       <c r="E1456" t="n">
-        <v>3267.75</v>
+        <v>3205.5</v>
       </c>
       <c r="F1456" t="n">
         <v>0.0</v>
@@ -53934,7 +53934,7 @@
         <v>37.5</v>
       </c>
       <c r="H1456" t="n">
-        <v>3267.75</v>
+        <v>3205.5</v>
       </c>
       <c r="I1456" t="n">
         <v>0.0</v>
@@ -54036,7 +54036,7 @@
         </is>
       </c>
       <c r="E1459" t="n">
-        <v>1088.87</v>
+        <v>1086.868</v>
       </c>
       <c r="F1459" t="n">
         <v>0.0</v>
@@ -54045,7 +54045,7 @@
         <v>0.5</v>
       </c>
       <c r="H1459" t="n">
-        <v>1088.87</v>
+        <v>1086.868</v>
       </c>
       <c r="I1459" t="n">
         <v>0.0</v>
@@ -54073,7 +54073,7 @@
         </is>
       </c>
       <c r="E1460" t="n">
-        <v>2002.822</v>
+        <v>1984.139</v>
       </c>
       <c r="F1460" t="n">
         <v>0.0</v>
@@ -54082,7 +54082,7 @@
         <v>11.342</v>
       </c>
       <c r="H1460" t="n">
-        <v>2002.822</v>
+        <v>1984.139</v>
       </c>
       <c r="I1460" t="n">
         <v>0.0</v>
@@ -54369,7 +54369,7 @@
         </is>
       </c>
       <c r="E1468" t="n">
-        <v>83.966</v>
+        <v>70.967</v>
       </c>
       <c r="F1468" t="n">
         <v>0.0</v>
@@ -54378,7 +54378,7 @@
         <v>0.0</v>
       </c>
       <c r="H1468" t="n">
-        <v>83.966</v>
+        <v>70.967</v>
       </c>
       <c r="I1468" t="n">
         <v>0.0</v>
@@ -54517,7 +54517,7 @@
         </is>
       </c>
       <c r="E1472" t="n">
-        <v>122.79</v>
+        <v>122.793</v>
       </c>
       <c r="F1472" t="n">
         <v>0.0</v>
@@ -54526,7 +54526,7 @@
         <v>10.481</v>
       </c>
       <c r="H1472" t="n">
-        <v>122.79</v>
+        <v>122.793</v>
       </c>
       <c r="I1472" t="n">
         <v>0.0</v>
@@ -54628,7 +54628,7 @@
         </is>
       </c>
       <c r="E1475" t="n">
-        <v>968.107</v>
+        <v>799.974</v>
       </c>
       <c r="F1475" t="n">
         <v>0.0</v>
@@ -54637,7 +54637,7 @@
         <v>0.0</v>
       </c>
       <c r="H1475" t="n">
-        <v>968.107</v>
+        <v>799.974</v>
       </c>
       <c r="I1475" t="n">
         <v>0.0</v>
@@ -54665,7 +54665,7 @@
         </is>
       </c>
       <c r="E1476" t="n">
-        <v>270.383</v>
+        <v>259.708</v>
       </c>
       <c r="F1476" t="n">
         <v>0.0</v>
@@ -54674,7 +54674,7 @@
         <v>0.0</v>
       </c>
       <c r="H1476" t="n">
-        <v>270.383</v>
+        <v>259.708</v>
       </c>
       <c r="I1476" t="n">
         <v>0.0</v>
@@ -54702,7 +54702,7 @@
         </is>
       </c>
       <c r="E1477" t="n">
-        <v>3859.087</v>
+        <v>3859.088</v>
       </c>
       <c r="F1477" t="n">
         <v>0.0</v>
@@ -54711,7 +54711,7 @@
         <v>939.418</v>
       </c>
       <c r="H1477" t="n">
-        <v>3859.087</v>
+        <v>3859.088</v>
       </c>
       <c r="I1477" t="n">
         <v>0.0</v>
@@ -54813,7 +54813,7 @@
         </is>
       </c>
       <c r="E1480" t="n">
-        <v>5905.548</v>
+        <v>5780.373</v>
       </c>
       <c r="F1480" t="n">
         <v>0.589</v>
@@ -54822,7 +54822,7 @@
         <v>661.475</v>
       </c>
       <c r="H1480" t="n">
-        <v>5905.548</v>
+        <v>5780.373</v>
       </c>
       <c r="I1480" t="n">
         <v>0.0</v>
@@ -54850,7 +54850,7 @@
         </is>
       </c>
       <c r="E1481" t="n">
-        <v>2351.497</v>
+        <v>2285.701</v>
       </c>
       <c r="F1481" t="n">
         <v>65.467</v>
@@ -54859,7 +54859,7 @@
         <v>121.834</v>
       </c>
       <c r="H1481" t="n">
-        <v>2351.497</v>
+        <v>2285.701</v>
       </c>
       <c r="I1481" t="n">
         <v>0.0</v>
@@ -55146,7 +55146,7 @@
         </is>
       </c>
       <c r="E1489" t="n">
-        <v>5463.0</v>
+        <v>5401.2</v>
       </c>
       <c r="F1489" t="n">
         <v>1.8</v>
@@ -55155,7 +55155,7 @@
         <v>0.0</v>
       </c>
       <c r="H1489" t="n">
-        <v>5463.0</v>
+        <v>5401.2</v>
       </c>
       <c r="I1489" t="n">
         <v>0.0</v>
@@ -55953,13 +55953,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD466753-0CCC-42D4-8271-7689C615B71B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5356196F-E527-43D5-9EF8-0930CB96C176}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9DCE3A3-7047-47B5-A3DC-D2A416F94EBF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9066649A-35DA-427E-99C6-2F85CE69878A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F879ED-7EB1-4F08-A0DF-E8073C33CD3D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB50769C-B1B9-497E-98B2-73A992971096}"/>
 </file>
--- a/Inventory_KNIME.xlsx
+++ b/Inventory_KNIME.xlsx
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>878.5</v>
+        <v>875.5</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
@@ -691,7 +691,7 @@
         <v>0.5</v>
       </c>
       <c r="H17" t="n">
-        <v>878.5</v>
+        <v>875.5</v>
       </c>
       <c r="I17" t="n">
         <v>0.0</v>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1045.0</v>
+        <v>1039.0</v>
       </c>
       <c r="F19" t="n">
         <v>0.0</v>
@@ -765,7 +765,7 @@
         <v>3.0</v>
       </c>
       <c r="H19" t="n">
-        <v>1045.0</v>
+        <v>1039.0</v>
       </c>
       <c r="I19" t="n">
         <v>0.0</v>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>11264.5</v>
+        <v>11261.5</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -839,7 +839,7 @@
         <v>0.0</v>
       </c>
       <c r="H21" t="n">
-        <v>11264.5</v>
+        <v>11261.5</v>
       </c>
       <c r="I21" t="n">
         <v>0.0</v>
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4144.5</v>
+        <v>4141.5</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -876,7 +876,7 @@
         <v>3.0</v>
       </c>
       <c r="H22" t="n">
-        <v>4144.5</v>
+        <v>4141.5</v>
       </c>
       <c r="I22" t="n">
         <v>0.0</v>
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3327.849</v>
+        <v>3326.942</v>
       </c>
       <c r="F34" t="n">
         <v>37.148</v>
@@ -1320,7 +1320,7 @@
         <v>4.971</v>
       </c>
       <c r="H34" t="n">
-        <v>3327.849</v>
+        <v>3326.942</v>
       </c>
       <c r="I34" t="n">
         <v>0.0</v>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1953.379</v>
+        <v>1943.323</v>
       </c>
       <c r="F35" t="n">
         <v>282.264</v>
@@ -1357,7 +1357,7 @@
         <v>216.545</v>
       </c>
       <c r="H35" t="n">
-        <v>1953.379</v>
+        <v>1943.323</v>
       </c>
       <c r="I35" t="n">
         <v>0.0</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1588.36</v>
+        <v>1658.404</v>
       </c>
       <c r="F39" t="n">
         <v>2200.261</v>
@@ -1505,7 +1505,7 @@
         <v>70.722</v>
       </c>
       <c r="H39" t="n">
-        <v>1588.36</v>
+        <v>1658.404</v>
       </c>
       <c r="I39" t="n">
         <v>0.0</v>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>914.75</v>
+        <v>913.811</v>
       </c>
       <c r="F40" t="n">
         <v>17.094</v>
@@ -1542,7 +1542,7 @@
         <v>25.329</v>
       </c>
       <c r="H40" t="n">
-        <v>914.75</v>
+        <v>913.811</v>
       </c>
       <c r="I40" t="n">
         <v>0.0</v>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1027.201</v>
+        <v>1020.7879999999999</v>
       </c>
       <c r="F42" t="n">
         <v>767.328</v>
@@ -1616,7 +1616,7 @@
         <v>332.94</v>
       </c>
       <c r="H42" t="n">
-        <v>1027.201</v>
+        <v>1020.7879999999999</v>
       </c>
       <c r="I42" t="n">
         <v>0.0</v>
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>9357.15</v>
+        <v>8961.15</v>
       </c>
       <c r="F43" t="n">
         <v>3.3</v>
@@ -1653,7 +1653,7 @@
         <v>409.2</v>
       </c>
       <c r="H43" t="n">
-        <v>9357.15</v>
+        <v>8961.15</v>
       </c>
       <c r="I43" t="n">
         <v>0.0</v>
@@ -2532,7 +2532,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>107.747</v>
+        <v>86.94399999999999</v>
       </c>
       <c r="F67" t="n">
         <v>3.467</v>
@@ -2541,7 +2541,7 @@
         <v>0.0</v>
       </c>
       <c r="H67" t="n">
-        <v>107.747</v>
+        <v>86.94399999999999</v>
       </c>
       <c r="I67" t="n">
         <v>0.0</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3113.2</v>
+        <v>3105.7999999999997</v>
       </c>
       <c r="F70" t="n">
         <v>1.2</v>
@@ -2652,7 +2652,7 @@
         <v>0.0</v>
       </c>
       <c r="H70" t="n">
-        <v>3113.2</v>
+        <v>3105.7999999999997</v>
       </c>
       <c r="I70" t="n">
         <v>0.0</v>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1268.159</v>
+        <v>1267.625</v>
       </c>
       <c r="F71" t="n">
         <v>4.801</v>
@@ -2689,7 +2689,7 @@
         <v>17.069000000000003</v>
       </c>
       <c r="H71" t="n">
-        <v>1268.159</v>
+        <v>1267.625</v>
       </c>
       <c r="I71" t="n">
         <v>0.0</v>
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>304.039</v>
+        <v>303.505</v>
       </c>
       <c r="F72" t="n">
         <v>0.0</v>
@@ -2726,7 +2726,7 @@
         <v>4.267</v>
       </c>
       <c r="H72" t="n">
-        <v>304.039</v>
+        <v>303.505</v>
       </c>
       <c r="I72" t="n">
         <v>0.0</v>
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1593.6180000000002</v>
+        <v>1592.73</v>
       </c>
       <c r="F73" t="n">
         <v>5.777</v>
@@ -2763,7 +2763,7 @@
         <v>0.0</v>
       </c>
       <c r="H73" t="n">
-        <v>1593.6180000000002</v>
+        <v>1592.73</v>
       </c>
       <c r="I73" t="n">
         <v>0.0</v>
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1385.773</v>
+        <v>1368.704</v>
       </c>
       <c r="F74" t="n">
         <v>0.0</v>
@@ -2800,7 +2800,7 @@
         <v>0.0</v>
       </c>
       <c r="H74" t="n">
-        <v>1385.773</v>
+        <v>1368.704</v>
       </c>
       <c r="I74" t="n">
         <v>0.0</v>
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5247.058</v>
+        <v>5240.389</v>
       </c>
       <c r="F75" t="n">
         <v>9.601</v>
@@ -2837,7 +2837,7 @@
         <v>17.069000000000003</v>
       </c>
       <c r="H75" t="n">
-        <v>5247.058</v>
+        <v>5240.389</v>
       </c>
       <c r="I75" t="n">
         <v>0.0</v>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1110.805</v>
+        <v>1110.271</v>
       </c>
       <c r="F77" t="n">
         <v>50.94</v>
@@ -2911,7 +2911,7 @@
         <v>0.0</v>
       </c>
       <c r="H77" t="n">
-        <v>1110.805</v>
+        <v>1110.271</v>
       </c>
       <c r="I77" t="n">
         <v>0.0</v>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>480.383</v>
+        <v>476.38</v>
       </c>
       <c r="F78" t="n">
         <v>0.0</v>
@@ -2948,7 +2948,7 @@
         <v>0.083</v>
       </c>
       <c r="H78" t="n">
-        <v>480.383</v>
+        <v>476.38</v>
       </c>
       <c r="I78" t="n">
         <v>0.0</v>
@@ -3198,7 +3198,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1559.122</v>
+        <v>3315.245</v>
       </c>
       <c r="F85" t="n">
         <v>0.0</v>
@@ -3207,7 +3207,7 @@
         <v>0.0</v>
       </c>
       <c r="H85" t="n">
-        <v>1559.122</v>
+        <v>3315.245</v>
       </c>
       <c r="I85" t="n">
         <v>0.0</v>
@@ -4049,7 +4049,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>540.876</v>
+        <v>540.875</v>
       </c>
       <c r="F108" t="n">
         <v>0.0</v>
@@ -4058,7 +4058,7 @@
         <v>0.0</v>
       </c>
       <c r="H108" t="n">
-        <v>540.876</v>
+        <v>540.875</v>
       </c>
       <c r="I108" t="n">
         <v>0.0</v>
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>859.049</v>
+        <v>851.042</v>
       </c>
       <c r="F109" t="n">
         <v>0.0</v>
@@ -4095,7 +4095,7 @@
         <v>69.38900000000001</v>
       </c>
       <c r="H109" t="n">
-        <v>859.049</v>
+        <v>851.042</v>
       </c>
       <c r="I109" t="n">
         <v>0.0</v>
@@ -4123,7 +4123,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>231.572</v>
+        <v>207.553</v>
       </c>
       <c r="F110" t="n">
         <v>0.0</v>
@@ -4132,7 +4132,7 @@
         <v>24.686</v>
       </c>
       <c r="H110" t="n">
-        <v>231.572</v>
+        <v>207.553</v>
       </c>
       <c r="I110" t="n">
         <v>0.0</v>
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>434.347</v>
+        <v>434.348</v>
       </c>
       <c r="F113" t="n">
         <v>0.0</v>
@@ -4243,7 +4243,7 @@
         <v>8.283999999999999</v>
       </c>
       <c r="H113" t="n">
-        <v>434.347</v>
+        <v>434.348</v>
       </c>
       <c r="I113" t="n">
         <v>0.0</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>908.057</v>
+        <v>876.032</v>
       </c>
       <c r="F114" t="n">
         <v>0.0</v>
@@ -4280,7 +4280,7 @@
         <v>2.669</v>
       </c>
       <c r="H114" t="n">
-        <v>908.057</v>
+        <v>876.032</v>
       </c>
       <c r="I114" t="n">
         <v>0.0</v>
@@ -4419,7 +4419,7 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>774.1550000000001</v>
+        <v>774.155</v>
       </c>
       <c r="F118" t="n">
         <v>0.0</v>
@@ -4428,7 +4428,7 @@
         <v>0.0</v>
       </c>
       <c r="H118" t="n">
-        <v>774.1550000000001</v>
+        <v>774.155</v>
       </c>
       <c r="I118" t="n">
         <v>0.0</v>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1144.3600000000001</v>
+        <v>1452.2</v>
       </c>
       <c r="F122" t="n">
         <v>0.12000000000000001</v>
@@ -4576,10 +4576,10 @@
         <v>25.44</v>
       </c>
       <c r="H122" t="n">
-        <v>1144.3600000000001</v>
+        <v>912.2</v>
       </c>
       <c r="I122" t="n">
-        <v>0.0</v>
+        <v>540.0</v>
       </c>
     </row>
     <row r="123">
@@ -4604,7 +4604,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1021.951</v>
+        <v>1034.101</v>
       </c>
       <c r="F123" t="n">
         <v>0.225</v>
@@ -4613,7 +4613,7 @@
         <v>116.775</v>
       </c>
       <c r="H123" t="n">
-        <v>1021.951</v>
+        <v>1034.101</v>
       </c>
       <c r="I123" t="n">
         <v>0.0</v>
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4215.827</v>
+        <v>4195.2919999999995</v>
       </c>
       <c r="F124" t="n">
         <v>0.0</v>
@@ -4650,7 +4650,7 @@
         <v>118.215</v>
       </c>
       <c r="H124" t="n">
-        <v>4215.827</v>
+        <v>4195.2919999999995</v>
       </c>
       <c r="I124" t="n">
         <v>0.0</v>
@@ -4752,7 +4752,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>306.592</v>
+        <v>210.392</v>
       </c>
       <c r="F127" t="n">
         <v>0.0</v>
@@ -4761,7 +4761,7 @@
         <v>106.005</v>
       </c>
       <c r="H127" t="n">
-        <v>306.592</v>
+        <v>210.392</v>
       </c>
       <c r="I127" t="n">
         <v>0.0</v>
@@ -4789,7 +4789,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>132.16</v>
+        <v>754.84</v>
       </c>
       <c r="F128" t="n">
         <v>0.0</v>
@@ -4798,10 +4798,10 @@
         <v>75.39999999999999</v>
       </c>
       <c r="H128" t="n">
-        <v>132.16</v>
+        <v>106.84</v>
       </c>
       <c r="I128" t="n">
-        <v>0.0</v>
+        <v>648.0</v>
       </c>
     </row>
     <row r="129">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1819.232</v>
+        <v>1802.552</v>
       </c>
       <c r="F130" t="n">
         <v>0.0</v>
@@ -4872,7 +4872,7 @@
         <v>63.38399999999999</v>
       </c>
       <c r="H130" t="n">
-        <v>1819.232</v>
+        <v>1802.552</v>
       </c>
       <c r="I130" t="n">
         <v>0.0</v>
@@ -5973,7 +5973,7 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>7944.545</v>
+        <v>7692.343</v>
       </c>
       <c r="F160" t="n">
         <v>0.0</v>
@@ -5982,7 +5982,7 @@
         <v>2692.291</v>
       </c>
       <c r="H160" t="n">
-        <v>7944.545</v>
+        <v>7692.343</v>
       </c>
       <c r="I160" t="n">
         <v>0.0</v>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1173.135</v>
+        <v>1103.125</v>
       </c>
       <c r="F192" t="n">
         <v>0.0</v>
@@ -7169,7 +7169,7 @@
         <v>1103.125</v>
       </c>
       <c r="I192" t="n">
-        <v>70.01</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="193">
@@ -7453,7 +7453,7 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>67.375</v>
+        <v>65.687</v>
       </c>
       <c r="F200" t="n">
         <v>0.0</v>
@@ -7462,7 +7462,7 @@
         <v>79.125</v>
       </c>
       <c r="H200" t="n">
-        <v>67.375</v>
+        <v>65.687</v>
       </c>
       <c r="I200" t="n">
         <v>0.0</v>
@@ -7490,7 +7490,7 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>396.75</v>
+        <v>393.75</v>
       </c>
       <c r="F201" t="n">
         <v>0.0</v>
@@ -7499,7 +7499,7 @@
         <v>9.0</v>
       </c>
       <c r="H201" t="n">
-        <v>396.75</v>
+        <v>393.75</v>
       </c>
       <c r="I201" t="n">
         <v>0.0</v>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>605.14</v>
+        <v>605.141</v>
       </c>
       <c r="F202" t="n">
         <v>1.031</v>
@@ -7536,7 +7536,7 @@
         <v>0.0</v>
       </c>
       <c r="H202" t="n">
-        <v>605.14</v>
+        <v>605.141</v>
       </c>
       <c r="I202" t="n">
         <v>0.0</v>
@@ -7601,7 +7601,7 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1183.644</v>
+        <v>1183.3</v>
       </c>
       <c r="F204" t="n">
         <v>0.0</v>
@@ -7610,7 +7610,7 @@
         <v>0.0</v>
       </c>
       <c r="H204" t="n">
-        <v>1183.644</v>
+        <v>1183.3</v>
       </c>
       <c r="I204" t="n">
         <v>0.0</v>
@@ -7638,7 +7638,7 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>854.785</v>
+        <v>852.036</v>
       </c>
       <c r="F205" t="n">
         <v>0.0</v>
@@ -7647,7 +7647,7 @@
         <v>0.859</v>
       </c>
       <c r="H205" t="n">
-        <v>854.785</v>
+        <v>852.036</v>
       </c>
       <c r="I205" t="n">
         <v>0.0</v>
@@ -7675,7 +7675,7 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>646.715</v>
+        <v>646.5419999999999</v>
       </c>
       <c r="F206" t="n">
         <v>0.0</v>
@@ -7684,7 +7684,7 @@
         <v>128.862</v>
       </c>
       <c r="H206" t="n">
-        <v>646.715</v>
+        <v>646.5419999999999</v>
       </c>
       <c r="I206" t="n">
         <v>0.0</v>
@@ -7712,7 +7712,7 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>633.481</v>
+        <v>629.532</v>
       </c>
       <c r="F207" t="n">
         <v>0.515</v>
@@ -7721,7 +7721,7 @@
         <v>0.34400000000000003</v>
       </c>
       <c r="H207" t="n">
-        <v>633.481</v>
+        <v>629.532</v>
       </c>
       <c r="I207" t="n">
         <v>0.0</v>
@@ -7749,7 +7749,7 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>809.64</v>
+        <v>808.265</v>
       </c>
       <c r="F208" t="n">
         <v>0.0</v>
@@ -7758,7 +7758,7 @@
         <v>0.0</v>
       </c>
       <c r="H208" t="n">
-        <v>809.64</v>
+        <v>808.265</v>
       </c>
       <c r="I208" t="n">
         <v>0.0</v>
@@ -7786,7 +7786,7 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>500.355</v>
+        <v>494.169</v>
       </c>
       <c r="F209" t="n">
         <v>0.0</v>
@@ -7795,7 +7795,7 @@
         <v>22.681</v>
       </c>
       <c r="H209" t="n">
-        <v>500.355</v>
+        <v>494.169</v>
       </c>
       <c r="I209" t="n">
         <v>0.0</v>
@@ -7823,7 +7823,7 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>420.168</v>
+        <v>419.481</v>
       </c>
       <c r="F210" t="n">
         <v>0.0</v>
@@ -7832,7 +7832,7 @@
         <v>48.111000000000004</v>
       </c>
       <c r="H210" t="n">
-        <v>420.168</v>
+        <v>419.481</v>
       </c>
       <c r="I210" t="n">
         <v>0.0</v>
@@ -7897,7 +7897,7 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>839.47</v>
+        <v>834.26</v>
       </c>
       <c r="F212" t="n">
         <v>0.0</v>
@@ -7906,7 +7906,7 @@
         <v>1.374</v>
       </c>
       <c r="H212" t="n">
-        <v>839.47</v>
+        <v>834.26</v>
       </c>
       <c r="I212" t="n">
         <v>0.0</v>
@@ -7934,7 +7934,7 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>100.216</v>
+        <v>82.579</v>
       </c>
       <c r="F213" t="n">
         <v>0.34400000000000003</v>
@@ -7943,7 +7943,7 @@
         <v>43.981</v>
       </c>
       <c r="H213" t="n">
-        <v>100.216</v>
+        <v>82.579</v>
       </c>
       <c r="I213" t="n">
         <v>0.0</v>
@@ -7971,7 +7971,7 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>76.291</v>
+        <v>75.603</v>
       </c>
       <c r="F214" t="n">
         <v>0.0</v>
@@ -7980,7 +7980,7 @@
         <v>11.684</v>
       </c>
       <c r="H214" t="n">
-        <v>76.291</v>
+        <v>75.603</v>
       </c>
       <c r="I214" t="n">
         <v>0.0</v>
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>1664.968</v>
+        <v>1618.641</v>
       </c>
       <c r="F215" t="n">
         <v>1.031</v>
@@ -8017,7 +8017,7 @@
         <v>0.34400000000000003</v>
       </c>
       <c r="H215" t="n">
-        <v>1664.968</v>
+        <v>1618.641</v>
       </c>
       <c r="I215" t="n">
         <v>0.0</v>
@@ -8045,7 +8045,7 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>173.199</v>
+        <v>172.513</v>
       </c>
       <c r="F216" t="n">
         <v>0.0</v>
@@ -8054,7 +8054,7 @@
         <v>1019.9530000000001</v>
       </c>
       <c r="H216" t="n">
-        <v>173.199</v>
+        <v>172.513</v>
       </c>
       <c r="I216" t="n">
         <v>0.0</v>
@@ -8082,7 +8082,7 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>766.629</v>
+        <v>763.423</v>
       </c>
       <c r="F217" t="n">
         <v>0.34400000000000003</v>
@@ -8091,7 +8091,7 @@
         <v>7.216</v>
       </c>
       <c r="H217" t="n">
-        <v>766.629</v>
+        <v>763.423</v>
       </c>
       <c r="I217" t="n">
         <v>0.0</v>
@@ -8156,7 +8156,7 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>281.436</v>
+        <v>279.374</v>
       </c>
       <c r="F219" t="n">
         <v>0.0</v>
@@ -8165,7 +8165,7 @@
         <v>0.0</v>
       </c>
       <c r="H219" t="n">
-        <v>281.436</v>
+        <v>279.374</v>
       </c>
       <c r="I219" t="n">
         <v>0.0</v>
@@ -8230,7 +8230,7 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>257.724</v>
+        <v>248.447</v>
       </c>
       <c r="F221" t="n">
         <v>0.0</v>
@@ -8239,7 +8239,7 @@
         <v>0.0</v>
       </c>
       <c r="H221" t="n">
-        <v>257.724</v>
+        <v>248.447</v>
       </c>
       <c r="I221" t="n">
         <v>0.0</v>
@@ -8267,7 +8267,7 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>94.16</v>
+        <v>93.473</v>
       </c>
       <c r="F222" t="n">
         <v>0.0</v>
@@ -8276,7 +8276,7 @@
         <v>685.238</v>
       </c>
       <c r="H222" t="n">
-        <v>94.16</v>
+        <v>93.473</v>
       </c>
       <c r="I222" t="n">
         <v>0.0</v>
@@ -8304,7 +8304,7 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>1015.737</v>
+        <v>1002.7379999999999</v>
       </c>
       <c r="F223" t="n">
         <v>0.0</v>
@@ -8313,7 +8313,7 @@
         <v>3.436</v>
       </c>
       <c r="H223" t="n">
-        <v>1015.737</v>
+        <v>1002.7379999999999</v>
       </c>
       <c r="I223" t="n">
         <v>0.0</v>
@@ -8859,7 +8859,7 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>62.718</v>
+        <v>62.05</v>
       </c>
       <c r="F238" t="n">
         <v>0.0</v>
@@ -8868,7 +8868,7 @@
         <v>1.056</v>
       </c>
       <c r="H238" t="n">
-        <v>62.718</v>
+        <v>62.05</v>
       </c>
       <c r="I238" t="n">
         <v>0.0</v>
@@ -8896,7 +8896,7 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>72.726</v>
+        <v>72.725</v>
       </c>
       <c r="F239" t="n">
         <v>0.0</v>
@@ -8905,7 +8905,7 @@
         <v>0.0</v>
       </c>
       <c r="H239" t="n">
-        <v>72.726</v>
+        <v>72.725</v>
       </c>
       <c r="I239" t="n">
         <v>0.0</v>
@@ -9340,7 +9340,7 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>9412.395</v>
+        <v>10109.7633</v>
       </c>
       <c r="F251" t="n">
         <v>0.0</v>
@@ -9352,7 +9352,7 @@
         <v>9412.395</v>
       </c>
       <c r="I251" t="n">
-        <v>0.0</v>
+        <v>697.3683</v>
       </c>
     </row>
     <row r="252">
@@ -9377,7 +9377,7 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>9100.639</v>
+        <v>9581.6575</v>
       </c>
       <c r="F252" t="n">
         <v>1.7329999999999999</v>
@@ -9389,7 +9389,7 @@
         <v>9100.639</v>
       </c>
       <c r="I252" t="n">
-        <v>0.0</v>
+        <v>481.0185</v>
       </c>
     </row>
     <row r="253">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>4419.0</v>
+        <v>4421.0</v>
       </c>
       <c r="F253" t="n">
         <v>0.0</v>
@@ -9423,10 +9423,10 @@
         <v>11.334</v>
       </c>
       <c r="H253" t="n">
-        <v>4419.0</v>
+        <v>4417.0</v>
       </c>
       <c r="I253" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="254">
@@ -9673,7 +9673,7 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>600.6</v>
+        <v>599.1999999999999</v>
       </c>
       <c r="F260" t="n">
         <v>5.4</v>
@@ -9682,7 +9682,7 @@
         <v>8.0</v>
       </c>
       <c r="H260" t="n">
-        <v>600.6</v>
+        <v>599.1999999999999</v>
       </c>
       <c r="I260" t="n">
         <v>0.0</v>
@@ -9747,7 +9747,7 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>309.94100000000003</v>
+        <v>308.552</v>
       </c>
       <c r="F262" t="n">
         <v>0.0</v>
@@ -9756,7 +9756,7 @@
         <v>604.1959999999999</v>
       </c>
       <c r="H262" t="n">
-        <v>309.94100000000003</v>
+        <v>308.552</v>
       </c>
       <c r="I262" t="n">
         <v>0.0</v>
@@ -9784,7 +9784,7 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>260.8</v>
+        <v>260.2</v>
       </c>
       <c r="F263" t="n">
         <v>0.6</v>
@@ -9793,7 +9793,7 @@
         <v>8.0</v>
       </c>
       <c r="H263" t="n">
-        <v>260.8</v>
+        <v>260.2</v>
       </c>
       <c r="I263" t="n">
         <v>0.0</v>
@@ -9821,7 +9821,7 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>5830.915</v>
+        <v>5678.503</v>
       </c>
       <c r="F264" t="n">
         <v>1.59</v>
@@ -9830,7 +9830,7 @@
         <v>62.620999999999995</v>
       </c>
       <c r="H264" t="n">
-        <v>5830.915</v>
+        <v>5678.503</v>
       </c>
       <c r="I264" t="n">
         <v>0.0</v>
@@ -9858,7 +9858,7 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>3444.1240000000003</v>
+        <v>3499.5960000000005</v>
       </c>
       <c r="F265" t="n">
         <v>3.979</v>
@@ -9867,7 +9867,7 @@
         <v>124.306</v>
       </c>
       <c r="H265" t="n">
-        <v>3444.1240000000003</v>
+        <v>3499.5960000000005</v>
       </c>
       <c r="I265" t="n">
         <v>0.0</v>
@@ -9895,7 +9895,7 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>3302.8959999999997</v>
+        <v>3303.643</v>
       </c>
       <c r="F266" t="n">
         <v>3.367</v>
@@ -9904,7 +9904,7 @@
         <v>145.07</v>
       </c>
       <c r="H266" t="n">
-        <v>3302.8959999999997</v>
+        <v>3303.643</v>
       </c>
       <c r="I266" t="n">
         <v>0.0</v>
@@ -10117,7 +10117,7 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>4402.3328</v>
+        <v>16.802</v>
       </c>
       <c r="F272" t="n">
         <v>0.0</v>
@@ -10129,7 +10129,7 @@
         <v>16.802</v>
       </c>
       <c r="I272" t="n">
-        <v>4385.5308</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="273">
@@ -10302,7 +10302,7 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>321.52200000000005</v>
+        <v>321.44300000000004</v>
       </c>
       <c r="F277" t="n">
         <v>0.04</v>
@@ -10311,7 +10311,7 @@
         <v>3.8400000000000003</v>
       </c>
       <c r="H277" t="n">
-        <v>321.52200000000005</v>
+        <v>321.44300000000004</v>
       </c>
       <c r="I277" t="n">
         <v>0.0</v>
@@ -10339,7 +10339,7 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>402.241</v>
+        <v>401.722</v>
       </c>
       <c r="F278" t="n">
         <v>0.0</v>
@@ -10348,7 +10348,7 @@
         <v>0.0</v>
       </c>
       <c r="H278" t="n">
-        <v>402.241</v>
+        <v>401.722</v>
       </c>
       <c r="I278" t="n">
         <v>0.0</v>
@@ -10376,7 +10376,7 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>581.399</v>
+        <v>581.279</v>
       </c>
       <c r="F279" t="n">
         <v>0.08</v>
@@ -10385,7 +10385,7 @@
         <v>0.0</v>
       </c>
       <c r="H279" t="n">
-        <v>581.399</v>
+        <v>581.279</v>
       </c>
       <c r="I279" t="n">
         <v>0.0</v>
@@ -10413,7 +10413,7 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>321.6</v>
+        <v>320.12</v>
       </c>
       <c r="F280" t="n">
         <v>0.0</v>
@@ -10422,7 +10422,7 @@
         <v>0.44</v>
       </c>
       <c r="H280" t="n">
-        <v>321.6</v>
+        <v>320.12</v>
       </c>
       <c r="I280" t="n">
         <v>0.0</v>
@@ -10524,7 +10524,7 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>2435.194</v>
+        <v>2055.163</v>
       </c>
       <c r="F283" t="n">
         <v>0.0</v>
@@ -10533,7 +10533,7 @@
         <v>18.752000000000002</v>
       </c>
       <c r="H283" t="n">
-        <v>2435.194</v>
+        <v>2055.163</v>
       </c>
       <c r="I283" t="n">
         <v>0.0</v>
@@ -10561,7 +10561,7 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>2312.4</v>
+        <v>2290.8</v>
       </c>
       <c r="F284" t="n">
         <v>0.0</v>
@@ -10570,7 +10570,7 @@
         <v>194.39999999999998</v>
       </c>
       <c r="H284" t="n">
-        <v>2312.4</v>
+        <v>2290.8</v>
       </c>
       <c r="I284" t="n">
         <v>0.0</v>
@@ -10598,7 +10598,7 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>4159.0</v>
+        <v>4070.0</v>
       </c>
       <c r="F285" t="n">
         <v>0.2</v>
@@ -10607,7 +10607,7 @@
         <v>84.0</v>
       </c>
       <c r="H285" t="n">
-        <v>4159.0</v>
+        <v>4070.0</v>
       </c>
       <c r="I285" t="n">
         <v>0.0</v>
@@ -10635,7 +10635,7 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>967.91</v>
+        <v>751.0360000000001</v>
       </c>
       <c r="F286" t="n">
         <v>2.222</v>
@@ -10644,7 +10644,7 @@
         <v>18.665000000000003</v>
       </c>
       <c r="H286" t="n">
-        <v>967.91</v>
+        <v>751.0360000000001</v>
       </c>
       <c r="I286" t="n">
         <v>0.0</v>
@@ -10672,7 +10672,7 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>4730.864</v>
+        <v>4730.415</v>
       </c>
       <c r="F287" t="n">
         <v>0.444</v>
@@ -10681,7 +10681,7 @@
         <v>383.96200000000005</v>
       </c>
       <c r="H287" t="n">
-        <v>4730.864</v>
+        <v>4730.415</v>
       </c>
       <c r="I287" t="n">
         <v>0.0</v>
@@ -10709,7 +10709,7 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>1207.879</v>
+        <v>1207.435</v>
       </c>
       <c r="F288" t="n">
         <v>0.889</v>
@@ -10718,7 +10718,7 @@
         <v>0.0</v>
       </c>
       <c r="H288" t="n">
-        <v>1207.879</v>
+        <v>1207.435</v>
       </c>
       <c r="I288" t="n">
         <v>0.0</v>
@@ -10746,7 +10746,7 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>3097.023</v>
+        <v>3086.358</v>
       </c>
       <c r="F289" t="n">
         <v>0.0</v>
@@ -10755,7 +10755,7 @@
         <v>351.965</v>
       </c>
       <c r="H289" t="n">
-        <v>3097.023</v>
+        <v>3086.358</v>
       </c>
       <c r="I289" t="n">
         <v>0.0</v>
@@ -11116,7 +11116,7 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>1393.1999999999998</v>
+        <v>1386.2</v>
       </c>
       <c r="F299" t="n">
         <v>0.8</v>
@@ -11125,7 +11125,7 @@
         <v>134.4</v>
       </c>
       <c r="H299" t="n">
-        <v>1393.1999999999998</v>
+        <v>1386.2</v>
       </c>
       <c r="I299" t="n">
         <v>0.0</v>
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>4748.4</v>
+        <v>4663.2</v>
       </c>
       <c r="F300" t="n">
         <v>2.4</v>
@@ -11162,7 +11162,7 @@
         <v>333.0</v>
       </c>
       <c r="H300" t="n">
-        <v>4748.4</v>
+        <v>4663.2</v>
       </c>
       <c r="I300" t="n">
         <v>0.0</v>
@@ -11190,7 +11190,7 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>66.2</v>
+        <v>63.199999999999996</v>
       </c>
       <c r="F301" t="n">
         <v>1.0</v>
@@ -11199,7 +11199,7 @@
         <v>136.8</v>
       </c>
       <c r="H301" t="n">
-        <v>66.2</v>
+        <v>63.199999999999996</v>
       </c>
       <c r="I301" t="n">
         <v>0.0</v>
@@ -11227,7 +11227,7 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>703.1999999999999</v>
+        <v>702.6</v>
       </c>
       <c r="F302" t="n">
         <v>0.2</v>
@@ -11236,7 +11236,7 @@
         <v>0.0</v>
       </c>
       <c r="H302" t="n">
-        <v>703.1999999999999</v>
+        <v>702.6</v>
       </c>
       <c r="I302" t="n">
         <v>0.0</v>
@@ -11375,7 +11375,7 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>5636.448</v>
+        <v>5630.581</v>
       </c>
       <c r="F306" t="n">
         <v>1.067</v>
@@ -11384,7 +11384,7 @@
         <v>0.0</v>
       </c>
       <c r="H306" t="n">
-        <v>5636.448</v>
+        <v>5630.581</v>
       </c>
       <c r="I306" t="n">
         <v>0.0</v>
@@ -11708,7 +11708,7 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>4925.0</v>
+        <v>4923.4</v>
       </c>
       <c r="F315" t="n">
         <v>0.0</v>
@@ -11717,7 +11717,7 @@
         <v>166.4</v>
       </c>
       <c r="H315" t="n">
-        <v>4925.0</v>
+        <v>4923.4</v>
       </c>
       <c r="I315" t="n">
         <v>0.0</v>
@@ -11856,7 +11856,7 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>2791.292</v>
+        <v>2790.759</v>
       </c>
       <c r="F319" t="n">
         <v>0.0</v>
@@ -11865,7 +11865,7 @@
         <v>0.0</v>
       </c>
       <c r="H319" t="n">
-        <v>2791.292</v>
+        <v>2790.759</v>
       </c>
       <c r="I319" t="n">
         <v>0.0</v>
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>12541.034</v>
+        <v>12540.234</v>
       </c>
       <c r="F320" t="n">
         <v>0.533</v>
@@ -11902,7 +11902,7 @@
         <v>0.0</v>
       </c>
       <c r="H320" t="n">
-        <v>12541.034</v>
+        <v>12540.234</v>
       </c>
       <c r="I320" t="n">
         <v>0.0</v>
@@ -11967,7 +11967,7 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>492.8</v>
+        <v>378.79999999999995</v>
       </c>
       <c r="F322" t="n">
         <v>0.6</v>
@@ -11976,7 +11976,7 @@
         <v>6.4</v>
       </c>
       <c r="H322" t="n">
-        <v>492.8</v>
+        <v>378.79999999999995</v>
       </c>
       <c r="I322" t="n">
         <v>0.0</v>
@@ -12041,7 +12041,7 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>5310.797</v>
+        <v>5310.531</v>
       </c>
       <c r="F324" t="n">
         <v>0.533</v>
@@ -12050,7 +12050,7 @@
         <v>0.0</v>
       </c>
       <c r="H324" t="n">
-        <v>5310.797</v>
+        <v>5310.531</v>
       </c>
       <c r="I324" t="n">
         <v>0.0</v>
@@ -12078,7 +12078,7 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>2173.6000000000004</v>
+        <v>2148.2</v>
       </c>
       <c r="F325" t="n">
         <v>1.4</v>
@@ -12087,7 +12087,7 @@
         <v>45.6</v>
       </c>
       <c r="H325" t="n">
-        <v>2173.6000000000004</v>
+        <v>2148.2</v>
       </c>
       <c r="I325" t="n">
         <v>0.0</v>
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>2970.04</v>
+        <v>2629.96</v>
       </c>
       <c r="F334" t="n">
         <v>0.0</v>
@@ -12420,7 +12420,7 @@
         <v>77.75999999999999</v>
       </c>
       <c r="H334" t="n">
-        <v>2970.04</v>
+        <v>2629.96</v>
       </c>
       <c r="I334" t="n">
         <v>0.0</v>
@@ -12448,7 +12448,7 @@
         </is>
       </c>
       <c r="E335" t="n">
-        <v>3165.751</v>
+        <v>3140.3269999999998</v>
       </c>
       <c r="F335" t="n">
         <v>0.45</v>
@@ -12457,7 +12457,7 @@
         <v>39.375</v>
       </c>
       <c r="H335" t="n">
-        <v>3165.751</v>
+        <v>3140.3269999999998</v>
       </c>
       <c r="I335" t="n">
         <v>0.0</v>
@@ -12485,7 +12485,7 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>2819.446</v>
+        <v>3005.4170000000004</v>
       </c>
       <c r="F336" t="n">
         <v>0.0</v>
@@ -12494,10 +12494,10 @@
         <v>88.245</v>
       </c>
       <c r="H336" t="n">
-        <v>2819.446</v>
+        <v>2430.992</v>
       </c>
       <c r="I336" t="n">
-        <v>0.0</v>
+        <v>574.425</v>
       </c>
     </row>
     <row r="337">
@@ -12818,7 +12818,7 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>551.5</v>
+        <v>550.9</v>
       </c>
       <c r="F345" t="n">
         <v>0.0</v>
@@ -12827,7 +12827,7 @@
         <v>0.0</v>
       </c>
       <c r="H345" t="n">
-        <v>551.5</v>
+        <v>550.9</v>
       </c>
       <c r="I345" t="n">
         <v>0.0</v>
@@ -12892,7 +12892,7 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>897.4</v>
+        <v>896.2</v>
       </c>
       <c r="F347" t="n">
         <v>0.0</v>
@@ -12901,7 +12901,7 @@
         <v>3.0</v>
       </c>
       <c r="H347" t="n">
-        <v>897.4</v>
+        <v>896.2</v>
       </c>
       <c r="I347" t="n">
         <v>0.0</v>
@@ -12966,7 +12966,7 @@
         </is>
       </c>
       <c r="E349" t="n">
-        <v>1152.0</v>
+        <v>1123.2</v>
       </c>
       <c r="F349" t="n">
         <v>0.0</v>
@@ -12975,7 +12975,7 @@
         <v>0.0</v>
       </c>
       <c r="H349" t="n">
-        <v>1152.0</v>
+        <v>1123.2</v>
       </c>
       <c r="I349" t="n">
         <v>0.0</v>
@@ -13003,7 +13003,7 @@
         </is>
       </c>
       <c r="E350" t="n">
-        <v>408.0</v>
+        <v>376.0</v>
       </c>
       <c r="F350" t="n">
         <v>0.0</v>
@@ -13012,7 +13012,7 @@
         <v>579.0</v>
       </c>
       <c r="H350" t="n">
-        <v>408.0</v>
+        <v>376.0</v>
       </c>
       <c r="I350" t="n">
         <v>0.0</v>
@@ -13410,7 +13410,7 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>403.25</v>
+        <v>391.249</v>
       </c>
       <c r="F361" t="n">
         <v>19.202</v>
@@ -13419,7 +13419,7 @@
         <v>0.0</v>
       </c>
       <c r="H361" t="n">
-        <v>403.25</v>
+        <v>391.249</v>
       </c>
       <c r="I361" t="n">
         <v>0.0</v>
@@ -13521,7 +13521,7 @@
         </is>
       </c>
       <c r="E364" t="n">
-        <v>1462.502</v>
+        <v>1451.827</v>
       </c>
       <c r="F364" t="n">
         <v>0.0</v>
@@ -13530,7 +13530,7 @@
         <v>0.0</v>
       </c>
       <c r="H364" t="n">
-        <v>1462.502</v>
+        <v>1451.827</v>
       </c>
       <c r="I364" t="n">
         <v>0.0</v>
@@ -13558,7 +13558,7 @@
         </is>
       </c>
       <c r="E365" t="n">
-        <v>23639.838</v>
+        <v>23546.429</v>
       </c>
       <c r="F365" t="n">
         <v>0.111</v>
@@ -13567,7 +13567,7 @@
         <v>37.03</v>
       </c>
       <c r="H365" t="n">
-        <v>23639.838</v>
+        <v>23546.429</v>
       </c>
       <c r="I365" t="n">
         <v>0.0</v>
@@ -13632,7 +13632,7 @@
         </is>
       </c>
       <c r="E367" t="n">
-        <v>12006.986</v>
+        <v>11894.896</v>
       </c>
       <c r="F367" t="n">
         <v>0.0</v>
@@ -13641,7 +13641,7 @@
         <v>115.648</v>
       </c>
       <c r="H367" t="n">
-        <v>12006.986</v>
+        <v>11894.896</v>
       </c>
       <c r="I367" t="n">
         <v>0.0</v>
@@ -13669,7 +13669,7 @@
         </is>
       </c>
       <c r="E368" t="n">
-        <v>230.859</v>
+        <v>202.829</v>
       </c>
       <c r="F368" t="n">
         <v>0.0</v>
@@ -13678,7 +13678,7 @@
         <v>16.458000000000002</v>
       </c>
       <c r="H368" t="n">
-        <v>230.859</v>
+        <v>202.829</v>
       </c>
       <c r="I368" t="n">
         <v>0.0</v>
@@ -14039,7 +14039,7 @@
         </is>
       </c>
       <c r="E378" t="n">
-        <v>8498.016</v>
+        <v>8094.747</v>
       </c>
       <c r="F378" t="n">
         <v>0.0</v>
@@ -14048,7 +14048,7 @@
         <v>0.0</v>
       </c>
       <c r="H378" t="n">
-        <v>8498.016</v>
+        <v>8094.747</v>
       </c>
       <c r="I378" t="n">
         <v>0.0</v>
@@ -14224,7 +14224,7 @@
         </is>
       </c>
       <c r="E383" t="n">
-        <v>1648.128</v>
+        <v>1630.368</v>
       </c>
       <c r="F383" t="n">
         <v>0.0</v>
@@ -14233,7 +14233,7 @@
         <v>37.296</v>
       </c>
       <c r="H383" t="n">
-        <v>1648.128</v>
+        <v>1630.368</v>
       </c>
       <c r="I383" t="n">
         <v>0.0</v>
@@ -14298,7 +14298,7 @@
         </is>
       </c>
       <c r="E385" t="n">
-        <v>819.8910000000001</v>
+        <v>818.92</v>
       </c>
       <c r="F385" t="n">
         <v>0.0</v>
@@ -14307,7 +14307,7 @@
         <v>30.12</v>
       </c>
       <c r="H385" t="n">
-        <v>819.8910000000001</v>
+        <v>818.92</v>
       </c>
       <c r="I385" t="n">
         <v>0.0</v>
@@ -14372,7 +14372,7 @@
         </is>
       </c>
       <c r="E387" t="n">
-        <v>872.34</v>
+        <v>982.8465</v>
       </c>
       <c r="F387" t="n">
         <v>17.756</v>
@@ -14384,7 +14384,7 @@
         <v>872.34</v>
       </c>
       <c r="I387" t="n">
-        <v>0.0</v>
+        <v>110.5065</v>
       </c>
     </row>
     <row r="388">
@@ -14409,7 +14409,7 @@
         </is>
       </c>
       <c r="E388" t="n">
-        <v>351.466</v>
+        <v>342.666</v>
       </c>
       <c r="F388" t="n">
         <v>40.0</v>
@@ -14418,7 +14418,7 @@
         <v>30.4</v>
       </c>
       <c r="H388" t="n">
-        <v>351.466</v>
+        <v>342.666</v>
       </c>
       <c r="I388" t="n">
         <v>0.0</v>
@@ -14557,7 +14557,7 @@
         </is>
       </c>
       <c r="E392" t="n">
-        <v>35.0</v>
+        <v>29.0</v>
       </c>
       <c r="F392" t="n">
         <v>0.0</v>
@@ -14566,7 +14566,7 @@
         <v>0.0</v>
       </c>
       <c r="H392" t="n">
-        <v>35.0</v>
+        <v>29.0</v>
       </c>
       <c r="I392" t="n">
         <v>0.0</v>
@@ -15223,7 +15223,7 @@
         </is>
       </c>
       <c r="E410" t="n">
-        <v>2894.149</v>
+        <v>2895.349</v>
       </c>
       <c r="F410" t="n">
         <v>0.2</v>
@@ -15232,7 +15232,7 @@
         <v>74.39999999999999</v>
       </c>
       <c r="H410" t="n">
-        <v>2894.149</v>
+        <v>2895.349</v>
       </c>
       <c r="I410" t="n">
         <v>0.0</v>
@@ -15260,7 +15260,7 @@
         </is>
       </c>
       <c r="E411" t="n">
-        <v>2456.75</v>
+        <v>2452.1</v>
       </c>
       <c r="F411" t="n">
         <v>0.0</v>
@@ -15269,7 +15269,7 @@
         <v>180.10000000000002</v>
       </c>
       <c r="H411" t="n">
-        <v>2456.75</v>
+        <v>2452.1</v>
       </c>
       <c r="I411" t="n">
         <v>0.0</v>
@@ -15297,7 +15297,7 @@
         </is>
       </c>
       <c r="E412" t="n">
-        <v>984.9</v>
+        <v>986.3000000000001</v>
       </c>
       <c r="F412" t="n">
         <v>0.15</v>
@@ -15306,7 +15306,7 @@
         <v>101.1</v>
       </c>
       <c r="H412" t="n">
-        <v>984.9</v>
+        <v>986.3000000000001</v>
       </c>
       <c r="I412" t="n">
         <v>0.0</v>
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="E413" t="n">
-        <v>1711.8999999999999</v>
+        <v>1714.75</v>
       </c>
       <c r="F413" t="n">
         <v>0.0</v>
@@ -15343,7 +15343,7 @@
         <v>163.5</v>
       </c>
       <c r="H413" t="n">
-        <v>1711.8999999999999</v>
+        <v>1714.75</v>
       </c>
       <c r="I413" t="n">
         <v>0.0</v>
@@ -15371,7 +15371,7 @@
         </is>
       </c>
       <c r="E414" t="n">
-        <v>2656.2000000000003</v>
+        <v>2544.2000000000003</v>
       </c>
       <c r="F414" t="n">
         <v>0.15</v>
@@ -15380,7 +15380,7 @@
         <v>31.2</v>
       </c>
       <c r="H414" t="n">
-        <v>2656.2000000000003</v>
+        <v>2544.2000000000003</v>
       </c>
       <c r="I414" t="n">
         <v>0.0</v>
@@ -15408,7 +15408,7 @@
         </is>
       </c>
       <c r="E415" t="n">
-        <v>2899.4500000000003</v>
+        <v>2887.0</v>
       </c>
       <c r="F415" t="n">
         <v>0.1</v>
@@ -15417,7 +15417,7 @@
         <v>0.0</v>
       </c>
       <c r="H415" t="n">
-        <v>2899.4500000000003</v>
+        <v>2887.0</v>
       </c>
       <c r="I415" t="n">
         <v>0.0</v>
@@ -15445,7 +15445,7 @@
         </is>
       </c>
       <c r="E416" t="n">
-        <v>10316.001</v>
+        <v>9714.301</v>
       </c>
       <c r="F416" t="n">
         <v>0.3</v>
@@ -15454,7 +15454,7 @@
         <v>0.0</v>
       </c>
       <c r="H416" t="n">
-        <v>10316.001</v>
+        <v>9714.301</v>
       </c>
       <c r="I416" t="n">
         <v>0.0</v>
@@ -15815,7 +15815,7 @@
         </is>
       </c>
       <c r="E426" t="n">
-        <v>162.0</v>
+        <v>147.6</v>
       </c>
       <c r="F426" t="n">
         <v>0.0</v>
@@ -15824,7 +15824,7 @@
         <v>0.0</v>
       </c>
       <c r="H426" t="n">
-        <v>162.0</v>
+        <v>147.6</v>
       </c>
       <c r="I426" t="n">
         <v>0.0</v>
@@ -16148,7 +16148,7 @@
         </is>
       </c>
       <c r="E435" t="n">
-        <v>1344.1466</v>
+        <v>830.892</v>
       </c>
       <c r="F435" t="n">
         <v>61.196</v>
@@ -16157,10 +16157,10 @@
         <v>4.107</v>
       </c>
       <c r="H435" t="n">
-        <v>855.366</v>
+        <v>830.892</v>
       </c>
       <c r="I435" t="n">
-        <v>488.7806</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="436">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="E436" t="n">
-        <v>7728.7649</v>
+        <v>117.151</v>
       </c>
       <c r="F436" t="n">
         <v>191.516</v>
@@ -16194,10 +16194,10 @@
         <v>2.054</v>
       </c>
       <c r="H436" t="n">
-        <v>218.38400000000001</v>
+        <v>117.151</v>
       </c>
       <c r="I436" t="n">
-        <v>7510.3809</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="437">
@@ -16222,7 +16222,7 @@
         </is>
       </c>
       <c r="E437" t="n">
-        <v>173.65</v>
+        <v>174.584</v>
       </c>
       <c r="F437" t="n">
         <v>0.0</v>
@@ -16231,7 +16231,7 @@
         <v>511.55799999999994</v>
       </c>
       <c r="H437" t="n">
-        <v>173.65</v>
+        <v>174.584</v>
       </c>
       <c r="I437" t="n">
         <v>0.0</v>
@@ -16259,7 +16259,7 @@
         </is>
       </c>
       <c r="E438" t="n">
-        <v>2144.9230000000002</v>
+        <v>2126.0980000000004</v>
       </c>
       <c r="F438" t="n">
         <v>0.0</v>
@@ -16268,7 +16268,7 @@
         <v>2.054</v>
       </c>
       <c r="H438" t="n">
-        <v>2144.9230000000002</v>
+        <v>2126.0980000000004</v>
       </c>
       <c r="I438" t="n">
         <v>0.0</v>
@@ -16296,7 +16296,7 @@
         </is>
       </c>
       <c r="E439" t="n">
-        <v>1171.067</v>
+        <v>511.54999999999995</v>
       </c>
       <c r="F439" t="n">
         <v>0.0</v>
@@ -16305,10 +16305,10 @@
         <v>395.806</v>
       </c>
       <c r="H439" t="n">
-        <v>526.952</v>
+        <v>511.54999999999995</v>
       </c>
       <c r="I439" t="n">
-        <v>644.115</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="440">
@@ -16407,7 +16407,7 @@
         </is>
       </c>
       <c r="E442" t="n">
-        <v>2347.7419999999997</v>
+        <v>2325.339</v>
       </c>
       <c r="F442" t="n">
         <v>0.0</v>
@@ -16416,7 +16416,7 @@
         <v>191.83700000000002</v>
       </c>
       <c r="H442" t="n">
-        <v>2347.7419999999997</v>
+        <v>2325.339</v>
       </c>
       <c r="I442" t="n">
         <v>0.0</v>
@@ -16444,7 +16444,7 @@
         </is>
       </c>
       <c r="E443" t="n">
-        <v>9190.304</v>
+        <v>9203.372</v>
       </c>
       <c r="F443" t="n">
         <v>6.069</v>
@@ -16453,7 +16453,7 @@
         <v>148.894</v>
       </c>
       <c r="H443" t="n">
-        <v>9190.304</v>
+        <v>9203.372</v>
       </c>
       <c r="I443" t="n">
         <v>0.0</v>
@@ -16481,7 +16481,7 @@
         </is>
       </c>
       <c r="E444" t="n">
-        <v>25128.417499999996</v>
+        <v>16585.023</v>
       </c>
       <c r="F444" t="n">
         <v>3.733</v>
@@ -16490,10 +16490,10 @@
         <v>50.879</v>
       </c>
       <c r="H444" t="n">
-        <v>16679.308999999997</v>
+        <v>16585.023</v>
       </c>
       <c r="I444" t="n">
-        <v>8449.1085</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="445">
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="E446" t="n">
-        <v>2134.4900000000002</v>
+        <v>2086.647</v>
       </c>
       <c r="F446" t="n">
         <v>294.922</v>
@@ -16564,7 +16564,7 @@
         <v>79.056</v>
       </c>
       <c r="H446" t="n">
-        <v>2134.4900000000002</v>
+        <v>2086.647</v>
       </c>
       <c r="I446" t="n">
         <v>0.0</v>
@@ -16592,7 +16592,7 @@
         </is>
       </c>
       <c r="E447" t="n">
-        <v>2319.337</v>
+        <v>1428.778</v>
       </c>
       <c r="F447" t="n">
         <v>1.6800000000000002</v>
@@ -16604,7 +16604,7 @@
         <v>1428.778</v>
       </c>
       <c r="I447" t="n">
-        <v>890.559</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="448">
@@ -16666,7 +16666,7 @@
         </is>
       </c>
       <c r="E449" t="n">
-        <v>1064.47</v>
+        <v>1006.71</v>
       </c>
       <c r="F449" t="n">
         <v>0.0</v>
@@ -16675,7 +16675,7 @@
         <v>73.80499999999999</v>
       </c>
       <c r="H449" t="n">
-        <v>1064.47</v>
+        <v>1006.71</v>
       </c>
       <c r="I449" t="n">
         <v>0.0</v>
@@ -16703,7 +16703,7 @@
         </is>
       </c>
       <c r="E450" t="n">
-        <v>7444.605</v>
+        <v>7313.914</v>
       </c>
       <c r="F450" t="n">
         <v>380.69399999999996</v>
@@ -16712,7 +16712,7 @@
         <v>0.292</v>
       </c>
       <c r="H450" t="n">
-        <v>7444.605</v>
+        <v>7313.914</v>
       </c>
       <c r="I450" t="n">
         <v>0.0</v>
@@ -16740,7 +16740,7 @@
         </is>
       </c>
       <c r="E451" t="n">
-        <v>1427.3529999999998</v>
+        <v>1419.4759999999999</v>
       </c>
       <c r="F451" t="n">
         <v>0.0</v>
@@ -16749,7 +16749,7 @@
         <v>19.253</v>
       </c>
       <c r="H451" t="n">
-        <v>1427.3529999999998</v>
+        <v>1419.4759999999999</v>
       </c>
       <c r="I451" t="n">
         <v>0.0</v>
@@ -16814,7 +16814,7 @@
         </is>
       </c>
       <c r="E453" t="n">
-        <v>3100.9030000000002</v>
+        <v>3095.944</v>
       </c>
       <c r="F453" t="n">
         <v>0.0</v>
@@ -16823,7 +16823,7 @@
         <v>0.0</v>
       </c>
       <c r="H453" t="n">
-        <v>3100.9030000000002</v>
+        <v>3095.944</v>
       </c>
       <c r="I453" t="n">
         <v>0.0</v>
@@ -17073,7 +17073,7 @@
         </is>
       </c>
       <c r="E460" t="n">
-        <v>333.31</v>
+        <v>333.312</v>
       </c>
       <c r="F460" t="n">
         <v>0.0</v>
@@ -17082,7 +17082,7 @@
         <v>3.2</v>
       </c>
       <c r="H460" t="n">
-        <v>333.31</v>
+        <v>333.312</v>
       </c>
       <c r="I460" t="n">
         <v>0.0</v>
@@ -17258,7 +17258,7 @@
         </is>
       </c>
       <c r="E465" t="n">
-        <v>719.542</v>
+        <v>714.475</v>
       </c>
       <c r="F465" t="n">
         <v>1.267</v>
@@ -17267,7 +17267,7 @@
         <v>0.0</v>
       </c>
       <c r="H465" t="n">
-        <v>719.542</v>
+        <v>714.475</v>
       </c>
       <c r="I465" t="n">
         <v>0.0</v>
@@ -17295,7 +17295,7 @@
         </is>
       </c>
       <c r="E466" t="n">
-        <v>246.41799999999998</v>
+        <v>244.551</v>
       </c>
       <c r="F466" t="n">
         <v>0.0</v>
@@ -17304,7 +17304,7 @@
         <v>0.0</v>
       </c>
       <c r="H466" t="n">
-        <v>246.41799999999998</v>
+        <v>244.551</v>
       </c>
       <c r="I466" t="n">
         <v>0.0</v>
@@ -17480,7 +17480,7 @@
         </is>
       </c>
       <c r="E471" t="n">
-        <v>1138.712</v>
+        <v>1086.716</v>
       </c>
       <c r="F471" t="n">
         <v>135.19</v>
@@ -17489,7 +17489,7 @@
         <v>561.557</v>
       </c>
       <c r="H471" t="n">
-        <v>1138.712</v>
+        <v>1086.716</v>
       </c>
       <c r="I471" t="n">
         <v>0.0</v>
@@ -17554,7 +17554,7 @@
         </is>
       </c>
       <c r="E473" t="n">
-        <v>3869.386</v>
+        <v>3809.381</v>
       </c>
       <c r="F473" t="n">
         <v>0.0</v>
@@ -17563,7 +17563,7 @@
         <v>642.064</v>
       </c>
       <c r="H473" t="n">
-        <v>3869.386</v>
+        <v>3809.381</v>
       </c>
       <c r="I473" t="n">
         <v>0.0</v>
@@ -17665,7 +17665,7 @@
         </is>
       </c>
       <c r="E476" t="n">
-        <v>709.4269999999999</v>
+        <v>744.302</v>
       </c>
       <c r="F476" t="n">
         <v>1.125</v>
@@ -17674,10 +17674,10 @@
         <v>85.725</v>
       </c>
       <c r="H476" t="n">
-        <v>709.4269999999999</v>
+        <v>706.5020000000001</v>
       </c>
       <c r="I476" t="n">
-        <v>0.0</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="477">
@@ -17702,7 +17702,7 @@
         </is>
       </c>
       <c r="E477" t="n">
-        <v>1774.464</v>
+        <v>1737.339</v>
       </c>
       <c r="F477" t="n">
         <v>0.0</v>
@@ -17711,7 +17711,7 @@
         <v>105.30000000000001</v>
       </c>
       <c r="H477" t="n">
-        <v>1774.464</v>
+        <v>1737.339</v>
       </c>
       <c r="I477" t="n">
         <v>0.0</v>
@@ -17776,7 +17776,7 @@
         </is>
       </c>
       <c r="E479" t="n">
-        <v>29.326</v>
+        <v>91.426</v>
       </c>
       <c r="F479" t="n">
         <v>0.0</v>
@@ -17788,7 +17788,7 @@
         <v>29.326</v>
       </c>
       <c r="I479" t="n">
-        <v>0.0</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="480">
@@ -17813,7 +17813,7 @@
         </is>
       </c>
       <c r="E480" t="n">
-        <v>122.42399999999999</v>
+        <v>116.874</v>
       </c>
       <c r="F480" t="n">
         <v>0.13899999999999998</v>
@@ -17822,7 +17822,7 @@
         <v>582.75</v>
       </c>
       <c r="H480" t="n">
-        <v>122.42399999999999</v>
+        <v>116.874</v>
       </c>
       <c r="I480" t="n">
         <v>0.0</v>
@@ -17850,7 +17850,7 @@
         </is>
       </c>
       <c r="E481" t="n">
-        <v>1399.68</v>
+        <v>1169.48</v>
       </c>
       <c r="F481" t="n">
         <v>0.12000000000000001</v>
@@ -17859,7 +17859,7 @@
         <v>178.07999999999998</v>
       </c>
       <c r="H481" t="n">
-        <v>1399.68</v>
+        <v>1169.48</v>
       </c>
       <c r="I481" t="n">
         <v>0.0</v>
@@ -17887,7 +17887,7 @@
         </is>
       </c>
       <c r="E482" t="n">
-        <v>70.881</v>
+        <v>68.16</v>
       </c>
       <c r="F482" t="n">
         <v>0.0</v>
@@ -17896,7 +17896,7 @@
         <v>708.0</v>
       </c>
       <c r="H482" t="n">
-        <v>70.881</v>
+        <v>68.16</v>
       </c>
       <c r="I482" t="n">
         <v>0.0</v>
@@ -17924,7 +17924,7 @@
         </is>
       </c>
       <c r="E483" t="n">
-        <v>1761.108</v>
+        <v>1750.516</v>
       </c>
       <c r="F483" t="n">
         <v>0.13899999999999998</v>
@@ -17933,7 +17933,7 @@
         <v>5.55</v>
       </c>
       <c r="H483" t="n">
-        <v>1761.108</v>
+        <v>1750.516</v>
       </c>
       <c r="I483" t="n">
         <v>0.0</v>
@@ -17961,7 +17961,7 @@
         </is>
       </c>
       <c r="E484" t="n">
-        <v>183.92</v>
+        <v>457.03999999999996</v>
       </c>
       <c r="F484" t="n">
         <v>0.0</v>
@@ -17970,10 +17970,10 @@
         <v>62.4</v>
       </c>
       <c r="H484" t="n">
-        <v>183.92</v>
+        <v>169.04</v>
       </c>
       <c r="I484" t="n">
-        <v>0.0</v>
+        <v>288.0</v>
       </c>
     </row>
     <row r="485">
@@ -17998,7 +17998,7 @@
         </is>
       </c>
       <c r="E485" t="n">
-        <v>2697.438</v>
+        <v>2623.022</v>
       </c>
       <c r="F485" t="n">
         <v>0.231</v>
@@ -18007,7 +18007,7 @@
         <v>155.955</v>
       </c>
       <c r="H485" t="n">
-        <v>2697.438</v>
+        <v>2623.022</v>
       </c>
       <c r="I485" t="n">
         <v>0.0</v>
@@ -18035,7 +18035,7 @@
         </is>
       </c>
       <c r="E486" t="n">
-        <v>318.4</v>
+        <v>311.08000000000004</v>
       </c>
       <c r="F486" t="n">
         <v>0.0</v>
@@ -18044,7 +18044,7 @@
         <v>110.88000000000001</v>
       </c>
       <c r="H486" t="n">
-        <v>318.4</v>
+        <v>311.08000000000004</v>
       </c>
       <c r="I486" t="n">
         <v>0.0</v>
@@ -18072,7 +18072,7 @@
         </is>
       </c>
       <c r="E487" t="n">
-        <v>1150.5159999999998</v>
+        <v>1102.231</v>
       </c>
       <c r="F487" t="n">
         <v>0.231</v>
@@ -18081,7 +18081,7 @@
         <v>24.42</v>
       </c>
       <c r="H487" t="n">
-        <v>1150.5159999999998</v>
+        <v>1102.231</v>
       </c>
       <c r="I487" t="n">
         <v>0.0</v>
@@ -18257,7 +18257,7 @@
         </is>
       </c>
       <c r="E492" t="n">
-        <v>11838.5926</v>
+        <v>12566.629</v>
       </c>
       <c r="F492" t="n">
         <v>50.336</v>
@@ -18269,7 +18269,7 @@
         <v>11833.259</v>
       </c>
       <c r="I492" t="n">
-        <v>5.3336</v>
+        <v>733.37</v>
       </c>
     </row>
     <row r="493">
@@ -18294,7 +18294,7 @@
         </is>
       </c>
       <c r="E493" t="n">
-        <v>2167.589</v>
+        <v>2327.1833</v>
       </c>
       <c r="F493" t="n">
         <v>20.532999999999998</v>
@@ -18306,7 +18306,7 @@
         <v>2167.589</v>
       </c>
       <c r="I493" t="n">
-        <v>0.0</v>
+        <v>159.5943</v>
       </c>
     </row>
     <row r="494">
@@ -18331,7 +18331,7 @@
         </is>
       </c>
       <c r="E494" t="n">
-        <v>5523.9710000000005</v>
+        <v>5588.3686</v>
       </c>
       <c r="F494" t="n">
         <v>26.576999999999998</v>
@@ -18340,10 +18340,10 @@
         <v>49.065999999999995</v>
       </c>
       <c r="H494" t="n">
-        <v>5523.9710000000005</v>
+        <v>5483.081999999999</v>
       </c>
       <c r="I494" t="n">
-        <v>0.0</v>
+        <v>105.28659999999999</v>
       </c>
     </row>
     <row r="495">
@@ -18368,7 +18368,7 @@
         </is>
       </c>
       <c r="E495" t="n">
-        <v>11560.0</v>
+        <v>5821.8</v>
       </c>
       <c r="F495" t="n">
         <v>26.8</v>
@@ -18377,10 +18377,10 @@
         <v>340.0</v>
       </c>
       <c r="H495" t="n">
-        <v>3246.3999999999996</v>
+        <v>3194.6</v>
       </c>
       <c r="I495" t="n">
-        <v>8313.6</v>
+        <v>2627.2000000000003</v>
       </c>
     </row>
     <row r="496">
@@ -18997,7 +18997,7 @@
         </is>
       </c>
       <c r="E512" t="n">
-        <v>2272.062</v>
+        <v>2271.828</v>
       </c>
       <c r="F512" t="n">
         <v>0.0</v>
@@ -19006,7 +19006,7 @@
         <v>9.165</v>
       </c>
       <c r="H512" t="n">
-        <v>2272.062</v>
+        <v>2271.828</v>
       </c>
       <c r="I512" t="n">
         <v>0.0</v>
@@ -19034,7 +19034,7 @@
         </is>
       </c>
       <c r="E513" t="n">
-        <v>2830.944</v>
+        <v>2830.411</v>
       </c>
       <c r="F513" t="n">
         <v>0.0</v>
@@ -19043,7 +19043,7 @@
         <v>6.793</v>
       </c>
       <c r="H513" t="n">
-        <v>2830.944</v>
+        <v>2830.411</v>
       </c>
       <c r="I513" t="n">
         <v>0.0</v>
@@ -19404,7 +19404,7 @@
         </is>
       </c>
       <c r="E523" t="n">
-        <v>822.0</v>
+        <v>813.0</v>
       </c>
       <c r="F523" t="n">
         <v>0.0</v>
@@ -19413,7 +19413,7 @@
         <v>0.0</v>
       </c>
       <c r="H523" t="n">
-        <v>822.0</v>
+        <v>813.0</v>
       </c>
       <c r="I523" t="n">
         <v>0.0</v>
@@ -19626,7 +19626,7 @@
         </is>
       </c>
       <c r="E529" t="n">
-        <v>411.667</v>
+        <v>150.291</v>
       </c>
       <c r="F529" t="n">
         <v>104.55</v>
@@ -19635,7 +19635,7 @@
         <v>0.0</v>
       </c>
       <c r="H529" t="n">
-        <v>411.667</v>
+        <v>150.291</v>
       </c>
       <c r="I529" t="n">
         <v>0.0</v>
@@ -19959,7 +19959,7 @@
         </is>
       </c>
       <c r="E538" t="n">
-        <v>1045.146</v>
+        <v>1035.2450000000001</v>
       </c>
       <c r="F538" t="n">
         <v>43.153</v>
@@ -19968,7 +19968,7 @@
         <v>0.313</v>
       </c>
       <c r="H538" t="n">
-        <v>1045.146</v>
+        <v>1035.2450000000001</v>
       </c>
       <c r="I538" t="n">
         <v>0.0</v>
@@ -20033,7 +20033,7 @@
         </is>
       </c>
       <c r="E540" t="n">
-        <v>1959.8120000000001</v>
+        <v>2190.6130000000003</v>
       </c>
       <c r="F540" t="n">
         <v>2663.3019999999997</v>
@@ -20042,7 +20042,7 @@
         <v>2297.6549999999997</v>
       </c>
       <c r="H540" t="n">
-        <v>1959.8120000000001</v>
+        <v>2190.6130000000003</v>
       </c>
       <c r="I540" t="n">
         <v>0.0</v>
@@ -20403,7 +20403,7 @@
         </is>
       </c>
       <c r="E550" t="n">
-        <v>4857.409000000001</v>
+        <v>4911.741300000001</v>
       </c>
       <c r="F550" t="n">
         <v>25.668</v>
@@ -20412,10 +20412,10 @@
         <v>471.024</v>
       </c>
       <c r="H550" t="n">
-        <v>4857.409000000001</v>
+        <v>4812.403</v>
       </c>
       <c r="I550" t="n">
-        <v>0.0</v>
+        <v>99.33829999999999</v>
       </c>
     </row>
     <row r="551">
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="E551" t="n">
-        <v>5200.4898</v>
+        <v>5433.4874</v>
       </c>
       <c r="F551" t="n">
         <v>30.912</v>
@@ -20449,10 +20449,10 @@
         <v>211.041</v>
       </c>
       <c r="H551" t="n">
-        <v>4986.126</v>
+        <v>5139.965</v>
       </c>
       <c r="I551" t="n">
-        <v>214.3638</v>
+        <v>293.52239999999995</v>
       </c>
     </row>
     <row r="552">
@@ -20477,7 +20477,7 @@
         </is>
       </c>
       <c r="E552" t="n">
-        <v>4647.946</v>
+        <v>3410.8979999999997</v>
       </c>
       <c r="F552" t="n">
         <v>14.059000000000001</v>
@@ -20486,10 +20486,10 @@
         <v>85.086</v>
       </c>
       <c r="H552" t="n">
-        <v>2341.333</v>
+        <v>2167.8599999999997</v>
       </c>
       <c r="I552" t="n">
-        <v>2306.6130000000003</v>
+        <v>1243.038</v>
       </c>
     </row>
     <row r="553">
@@ -21513,7 +21513,7 @@
         </is>
       </c>
       <c r="E580" t="n">
-        <v>5551.524</v>
+        <v>5667.3732</v>
       </c>
       <c r="F580" t="n">
         <v>0.0</v>
@@ -21522,10 +21522,10 @@
         <v>5.539</v>
       </c>
       <c r="H580" t="n">
-        <v>5551.524</v>
+        <v>5490.138</v>
       </c>
       <c r="I580" t="n">
-        <v>0.0</v>
+        <v>177.2352</v>
       </c>
     </row>
     <row r="581">
@@ -21587,7 +21587,7 @@
         </is>
       </c>
       <c r="E582" t="n">
-        <v>1325.573</v>
+        <v>1323.726</v>
       </c>
       <c r="F582" t="n">
         <v>0.0</v>
@@ -21596,7 +21596,7 @@
         <v>1.846</v>
       </c>
       <c r="H582" t="n">
-        <v>1325.573</v>
+        <v>1323.726</v>
       </c>
       <c r="I582" t="n">
         <v>0.0</v>
@@ -21661,7 +21661,7 @@
         </is>
       </c>
       <c r="E584" t="n">
-        <v>1425.9789999999998</v>
+        <v>1413.5205</v>
       </c>
       <c r="F584" t="n">
         <v>0.0</v>
@@ -21670,10 +21670,10 @@
         <v>0.0</v>
       </c>
       <c r="H584" t="n">
-        <v>1425.9789999999998</v>
+        <v>1375.306</v>
       </c>
       <c r="I584" t="n">
-        <v>0.0</v>
+        <v>38.2145</v>
       </c>
     </row>
     <row r="585">
@@ -21698,7 +21698,7 @@
         </is>
       </c>
       <c r="E585" t="n">
-        <v>1775.1209999999999</v>
+        <v>1732.1979999999999</v>
       </c>
       <c r="F585" t="n">
         <v>0.0</v>
@@ -21707,7 +21707,7 @@
         <v>9.231</v>
       </c>
       <c r="H585" t="n">
-        <v>1775.1209999999999</v>
+        <v>1732.1979999999999</v>
       </c>
       <c r="I585" t="n">
         <v>0.0</v>
@@ -22068,7 +22068,7 @@
         </is>
       </c>
       <c r="E595" t="n">
-        <v>1711.3449999999998</v>
+        <v>4815.847</v>
       </c>
       <c r="F595" t="n">
         <v>0.0</v>
@@ -22077,10 +22077,10 @@
         <v>1050.859</v>
       </c>
       <c r="H595" t="n">
-        <v>1711.3449999999998</v>
+        <v>555.6070000000001</v>
       </c>
       <c r="I595" t="n">
-        <v>0.0</v>
+        <v>4260.24</v>
       </c>
     </row>
     <row r="596">
@@ -22105,7 +22105,7 @@
         </is>
       </c>
       <c r="E596" t="n">
-        <v>121.742</v>
+        <v>104.138</v>
       </c>
       <c r="F596" t="n">
         <v>0.0</v>
@@ -22114,7 +22114,7 @@
         <v>386.37899999999996</v>
       </c>
       <c r="H596" t="n">
-        <v>121.742</v>
+        <v>104.138</v>
       </c>
       <c r="I596" t="n">
         <v>0.0</v>
@@ -22179,7 +22179,7 @@
         </is>
       </c>
       <c r="E598" t="n">
-        <v>5888.059</v>
+        <v>6409.951</v>
       </c>
       <c r="F598" t="n">
         <v>0.0</v>
@@ -22188,10 +22188,10 @@
         <v>3.7279999999999998</v>
       </c>
       <c r="H598" t="n">
-        <v>5888.059</v>
+        <v>5813.503</v>
       </c>
       <c r="I598" t="n">
-        <v>0.0</v>
+        <v>596.448</v>
       </c>
     </row>
     <row r="599">
@@ -22216,7 +22216,7 @@
         </is>
       </c>
       <c r="E599" t="n">
-        <v>6657.513</v>
+        <v>5791.56</v>
       </c>
       <c r="F599" t="n">
         <v>2.5149999999999997</v>
@@ -22225,10 +22225,10 @@
         <v>468.626</v>
       </c>
       <c r="H599" t="n">
-        <v>6657.513</v>
+        <v>5205.777</v>
       </c>
       <c r="I599" t="n">
-        <v>0.0</v>
+        <v>585.783</v>
       </c>
     </row>
     <row r="600">
@@ -22290,7 +22290,7 @@
         </is>
       </c>
       <c r="E601" t="n">
-        <v>40.827</v>
+        <v>2194.9106</v>
       </c>
       <c r="F601" t="n">
         <v>0.0</v>
@@ -22299,10 +22299,10 @@
         <v>0.888</v>
       </c>
       <c r="H601" t="n">
-        <v>40.827</v>
+        <v>36.389</v>
       </c>
       <c r="I601" t="n">
-        <v>0.0</v>
+        <v>2158.5216</v>
       </c>
     </row>
     <row r="602">
@@ -22327,7 +22327,7 @@
         </is>
       </c>
       <c r="E602" t="n">
-        <v>366.96</v>
+        <v>306.912</v>
       </c>
       <c r="F602" t="n">
         <v>0.0</v>
@@ -22336,7 +22336,7 @@
         <v>0.5</v>
       </c>
       <c r="H602" t="n">
-        <v>366.96</v>
+        <v>306.912</v>
       </c>
       <c r="I602" t="n">
         <v>0.0</v>
@@ -23326,7 +23326,7 @@
         </is>
       </c>
       <c r="E629" t="n">
-        <v>1232.088</v>
+        <v>1209.686</v>
       </c>
       <c r="F629" t="n">
         <v>0.933</v>
@@ -23335,7 +23335,7 @@
         <v>0.0</v>
       </c>
       <c r="H629" t="n">
-        <v>1232.088</v>
+        <v>1209.686</v>
       </c>
       <c r="I629" t="n">
         <v>0.0</v>
@@ -23511,7 +23511,7 @@
         </is>
       </c>
       <c r="E634" t="n">
-        <v>3597.386</v>
+        <v>3537.374</v>
       </c>
       <c r="F634" t="n">
         <v>0.0</v>
@@ -23520,7 +23520,7 @@
         <v>0.0</v>
       </c>
       <c r="H634" t="n">
-        <v>3597.386</v>
+        <v>3537.374</v>
       </c>
       <c r="I634" t="n">
         <v>0.0</v>
@@ -23844,7 +23844,7 @@
         </is>
       </c>
       <c r="E643" t="n">
-        <v>32.605000000000004</v>
+        <v>135.4754</v>
       </c>
       <c r="F643" t="n">
         <v>0.0</v>
@@ -23856,7 +23856,7 @@
         <v>32.605000000000004</v>
       </c>
       <c r="I643" t="n">
-        <v>0.0</v>
+        <v>102.8704</v>
       </c>
     </row>
     <row r="644">
@@ -23918,7 +23918,7 @@
         </is>
       </c>
       <c r="E645" t="n">
-        <v>1065.548</v>
+        <v>1065.547</v>
       </c>
       <c r="F645" t="n">
         <v>0.0</v>
@@ -23927,7 +23927,7 @@
         <v>0.16699999999999998</v>
       </c>
       <c r="H645" t="n">
-        <v>1065.548</v>
+        <v>1065.547</v>
       </c>
       <c r="I645" t="n">
         <v>0.0</v>
@@ -23992,7 +23992,7 @@
         </is>
       </c>
       <c r="E647" t="n">
-        <v>1574.569</v>
+        <v>1567.902</v>
       </c>
       <c r="F647" t="n">
         <v>0.8</v>
@@ -24001,7 +24001,7 @@
         <v>0.0</v>
       </c>
       <c r="H647" t="n">
-        <v>1574.569</v>
+        <v>1567.902</v>
       </c>
       <c r="I647" t="n">
         <v>0.0</v>
@@ -24214,7 +24214,7 @@
         </is>
       </c>
       <c r="E653" t="n">
-        <v>6149.416</v>
+        <v>6134.404</v>
       </c>
       <c r="F653" t="n">
         <v>0.0</v>
@@ -24223,7 +24223,7 @@
         <v>65.05199999999999</v>
       </c>
       <c r="H653" t="n">
-        <v>6149.416</v>
+        <v>6134.404</v>
       </c>
       <c r="I653" t="n">
         <v>0.0</v>
@@ -24362,7 +24362,7 @@
         </is>
       </c>
       <c r="E657" t="n">
-        <v>10.154</v>
+        <v>4.615</v>
       </c>
       <c r="F657" t="n">
         <v>0.923</v>
@@ -24371,7 +24371,7 @@
         <v>1524.961</v>
       </c>
       <c r="H657" t="n">
-        <v>10.154</v>
+        <v>4.615</v>
       </c>
       <c r="I657" t="n">
         <v>0.0</v>
@@ -24547,7 +24547,7 @@
         </is>
       </c>
       <c r="E662" t="n">
-        <v>1022.0110000000001</v>
+        <v>1045.533</v>
       </c>
       <c r="F662" t="n">
         <v>1.7730000000000001</v>
@@ -24556,7 +24556,7 @@
         <v>179.285</v>
       </c>
       <c r="H662" t="n">
-        <v>1022.0110000000001</v>
+        <v>1045.533</v>
       </c>
       <c r="I662" t="n">
         <v>0.0</v>
@@ -24584,7 +24584,7 @@
         </is>
       </c>
       <c r="E663" t="n">
-        <v>2225.975</v>
+        <v>2220.058</v>
       </c>
       <c r="F663" t="n">
         <v>0.0</v>
@@ -24593,7 +24593,7 @@
         <v>55.620000000000005</v>
       </c>
       <c r="H663" t="n">
-        <v>2225.975</v>
+        <v>2220.058</v>
       </c>
       <c r="I663" t="n">
         <v>0.0</v>
@@ -24769,7 +24769,7 @@
         </is>
       </c>
       <c r="E668" t="n">
-        <v>8.432</v>
+        <v>8.431</v>
       </c>
       <c r="F668" t="n">
         <v>1.035</v>
@@ -24778,7 +24778,7 @@
         <v>142.00799999999998</v>
       </c>
       <c r="H668" t="n">
-        <v>8.432</v>
+        <v>8.431</v>
       </c>
       <c r="I668" t="n">
         <v>0.0</v>
@@ -24991,7 +24991,7 @@
         </is>
       </c>
       <c r="E674" t="n">
-        <v>930.086</v>
+        <v>557.306</v>
       </c>
       <c r="F674" t="n">
         <v>0.0</v>
@@ -25000,7 +25000,7 @@
         <v>0.0</v>
       </c>
       <c r="H674" t="n">
-        <v>930.086</v>
+        <v>557.306</v>
       </c>
       <c r="I674" t="n">
         <v>0.0</v>
@@ -25102,7 +25102,7 @@
         </is>
       </c>
       <c r="E677" t="n">
-        <v>10928.045</v>
+        <v>10928.046</v>
       </c>
       <c r="F677" t="n">
         <v>0.0</v>
@@ -25111,7 +25111,7 @@
         <v>3.7279999999999998</v>
       </c>
       <c r="H677" t="n">
-        <v>10928.045</v>
+        <v>10928.046</v>
       </c>
       <c r="I677" t="n">
         <v>0.0</v>
@@ -25361,7 +25361,7 @@
         </is>
       </c>
       <c r="E684" t="n">
-        <v>2877.0469999999996</v>
+        <v>2866.1549999999997</v>
       </c>
       <c r="F684" t="n">
         <v>0.312</v>
@@ -25370,7 +25370,7 @@
         <v>0.0</v>
       </c>
       <c r="H684" t="n">
-        <v>2877.0469999999996</v>
+        <v>2866.1549999999997</v>
       </c>
       <c r="I684" t="n">
         <v>0.0</v>
@@ -25398,7 +25398,7 @@
         </is>
       </c>
       <c r="E685" t="n">
-        <v>3649.981</v>
+        <v>3657.137</v>
       </c>
       <c r="F685" t="n">
         <v>3734.0</v>
@@ -25407,7 +25407,7 @@
         <v>0.0</v>
       </c>
       <c r="H685" t="n">
-        <v>3649.981</v>
+        <v>3657.137</v>
       </c>
       <c r="I685" t="n">
         <v>0.0</v>
@@ -25953,7 +25953,7 @@
         </is>
       </c>
       <c r="E700" t="n">
-        <v>436.56600000000003</v>
+        <v>318.323</v>
       </c>
       <c r="F700" t="n">
         <v>0.624</v>
@@ -25962,7 +25962,7 @@
         <v>0.0</v>
       </c>
       <c r="H700" t="n">
-        <v>436.56600000000003</v>
+        <v>318.323</v>
       </c>
       <c r="I700" t="n">
         <v>0.0</v>
@@ -25990,7 +25990,7 @@
         </is>
       </c>
       <c r="E701" t="n">
-        <v>4450.9259999999995</v>
+        <v>4150.0289999999995</v>
       </c>
       <c r="F701" t="n">
         <v>26.450000000000003</v>
@@ -25999,7 +25999,7 @@
         <v>5.601</v>
       </c>
       <c r="H701" t="n">
-        <v>4450.9259999999995</v>
+        <v>4150.0289999999995</v>
       </c>
       <c r="I701" t="n">
         <v>0.0</v>
@@ -26027,7 +26027,7 @@
         </is>
       </c>
       <c r="E702" t="n">
-        <v>7165.8550000000005</v>
+        <v>6779.076</v>
       </c>
       <c r="F702" t="n">
         <v>41.385999999999996</v>
@@ -26036,7 +26036,7 @@
         <v>9.334999999999999</v>
       </c>
       <c r="H702" t="n">
-        <v>7165.8550000000005</v>
+        <v>6779.076</v>
       </c>
       <c r="I702" t="n">
         <v>0.0</v>
@@ -26064,7 +26064,7 @@
         </is>
       </c>
       <c r="E703" t="n">
-        <v>2599.154</v>
+        <v>2599.155</v>
       </c>
       <c r="F703" t="n">
         <v>0.0</v>
@@ -26073,7 +26073,7 @@
         <v>3.851</v>
       </c>
       <c r="H703" t="n">
-        <v>2599.154</v>
+        <v>2599.155</v>
       </c>
       <c r="I703" t="n">
         <v>0.0</v>
@@ -26138,7 +26138,7 @@
         </is>
       </c>
       <c r="E705" t="n">
-        <v>870.7113999999999</v>
+        <v>0.608</v>
       </c>
       <c r="F705" t="n">
         <v>0.0</v>
@@ -26150,7 +26150,7 @@
         <v>0.608</v>
       </c>
       <c r="I705" t="n">
-        <v>870.1034</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="706">
@@ -26397,7 +26397,7 @@
         </is>
       </c>
       <c r="E712" t="n">
-        <v>1402.439</v>
+        <v>1402.44</v>
       </c>
       <c r="F712" t="n">
         <v>0.666</v>
@@ -26406,7 +26406,7 @@
         <v>10.996</v>
       </c>
       <c r="H712" t="n">
-        <v>1402.439</v>
+        <v>1402.44</v>
       </c>
       <c r="I712" t="n">
         <v>0.0</v>
@@ -26545,7 +26545,7 @@
         </is>
       </c>
       <c r="E716" t="n">
-        <v>6054.022</v>
+        <v>6050.822</v>
       </c>
       <c r="F716" t="n">
         <v>0.0</v>
@@ -26554,7 +26554,7 @@
         <v>0.0</v>
       </c>
       <c r="H716" t="n">
-        <v>6054.022</v>
+        <v>6050.822</v>
       </c>
       <c r="I716" t="n">
         <v>0.0</v>
@@ -26582,7 +26582,7 @@
         </is>
       </c>
       <c r="E717" t="n">
-        <v>1033.196</v>
+        <v>1031.329</v>
       </c>
       <c r="F717" t="n">
         <v>0.0</v>
@@ -26591,7 +26591,7 @@
         <v>153.619</v>
       </c>
       <c r="H717" t="n">
-        <v>1033.196</v>
+        <v>1031.329</v>
       </c>
       <c r="I717" t="n">
         <v>0.0</v>
@@ -26619,7 +26619,7 @@
         </is>
       </c>
       <c r="E718" t="n">
-        <v>4425.322</v>
+        <v>4422.124</v>
       </c>
       <c r="F718" t="n">
         <v>0.0</v>
@@ -26628,7 +26628,7 @@
         <v>0.0</v>
       </c>
       <c r="H718" t="n">
-        <v>4425.322</v>
+        <v>4422.124</v>
       </c>
       <c r="I718" t="n">
         <v>0.0</v>
@@ -26656,7 +26656,7 @@
         </is>
       </c>
       <c r="E719" t="n">
-        <v>1890.902</v>
+        <v>1698.6109999999999</v>
       </c>
       <c r="F719" t="n">
         <v>0.26699999999999996</v>
@@ -26665,7 +26665,7 @@
         <v>0.0</v>
       </c>
       <c r="H719" t="n">
-        <v>1890.902</v>
+        <v>1698.6109999999999</v>
       </c>
       <c r="I719" t="n">
         <v>0.0</v>
@@ -26693,7 +26693,7 @@
         </is>
       </c>
       <c r="E720" t="n">
-        <v>265.583</v>
+        <v>265.05</v>
       </c>
       <c r="F720" t="n">
         <v>6.4</v>
@@ -26702,7 +26702,7 @@
         <v>3.2</v>
       </c>
       <c r="H720" t="n">
-        <v>265.583</v>
+        <v>265.05</v>
       </c>
       <c r="I720" t="n">
         <v>0.0</v>
@@ -26767,7 +26767,7 @@
         </is>
       </c>
       <c r="E722" t="n">
-        <v>2798.756</v>
+        <v>2756.094</v>
       </c>
       <c r="F722" t="n">
         <v>0.0</v>
@@ -26776,7 +26776,7 @@
         <v>0.0</v>
       </c>
       <c r="H722" t="n">
-        <v>2798.756</v>
+        <v>2756.094</v>
       </c>
       <c r="I722" t="n">
         <v>0.0</v>
@@ -26804,7 +26804,7 @@
         </is>
       </c>
       <c r="E723" t="n">
-        <v>24833.77</v>
+        <v>24819.899999999998</v>
       </c>
       <c r="F723" t="n">
         <v>2.4</v>
@@ -26813,7 +26813,7 @@
         <v>288.036</v>
       </c>
       <c r="H723" t="n">
-        <v>24833.77</v>
+        <v>24819.899999999998</v>
       </c>
       <c r="I723" t="n">
         <v>0.0</v>
@@ -26841,7 +26841,7 @@
         </is>
       </c>
       <c r="E724" t="n">
-        <v>3703.6670000000004</v>
+        <v>3624.454</v>
       </c>
       <c r="F724" t="n">
         <v>2.4</v>
@@ -26850,7 +26850,7 @@
         <v>212.827</v>
       </c>
       <c r="H724" t="n">
-        <v>3703.6670000000004</v>
+        <v>3624.454</v>
       </c>
       <c r="I724" t="n">
         <v>0.0</v>
@@ -26878,7 +26878,7 @@
         </is>
       </c>
       <c r="E725" t="n">
-        <v>2605.9100000000003</v>
+        <v>2588.936</v>
       </c>
       <c r="F725" t="n">
         <v>0.13899999999999998</v>
@@ -26887,7 +26887,7 @@
         <v>67.155</v>
       </c>
       <c r="H725" t="n">
-        <v>2605.9100000000003</v>
+        <v>2588.936</v>
       </c>
       <c r="I725" t="n">
         <v>0.0</v>
@@ -26915,7 +26915,7 @@
         </is>
       </c>
       <c r="E726" t="n">
-        <v>1850.0</v>
+        <v>1815.32</v>
       </c>
       <c r="F726" t="n">
         <v>0.2</v>
@@ -26924,7 +26924,7 @@
         <v>2.8800000000000003</v>
       </c>
       <c r="H726" t="n">
-        <v>1850.0</v>
+        <v>1815.32</v>
       </c>
       <c r="I726" t="n">
         <v>0.0</v>
@@ -26952,7 +26952,7 @@
         </is>
       </c>
       <c r="E727" t="n">
-        <v>2959.861</v>
+        <v>2952.044</v>
       </c>
       <c r="F727" t="n">
         <v>0.0</v>
@@ -26961,7 +26961,7 @@
         <v>0.555</v>
       </c>
       <c r="H727" t="n">
-        <v>2959.861</v>
+        <v>2952.044</v>
       </c>
       <c r="I727" t="n">
         <v>0.0</v>
@@ -26989,7 +26989,7 @@
         </is>
       </c>
       <c r="E728" t="n">
-        <v>1720.683</v>
+        <v>1715.6429999999998</v>
       </c>
       <c r="F728" t="n">
         <v>0.0</v>
@@ -26998,7 +26998,7 @@
         <v>0.0</v>
       </c>
       <c r="H728" t="n">
-        <v>1720.683</v>
+        <v>1715.6429999999998</v>
       </c>
       <c r="I728" t="n">
         <v>0.0</v>
@@ -27285,7 +27285,7 @@
         </is>
       </c>
       <c r="E736" t="n">
-        <v>546.81</v>
+        <v>449.75</v>
       </c>
       <c r="F736" t="n">
         <v>11.733</v>
@@ -27294,7 +27294,7 @@
         <v>0.0</v>
       </c>
       <c r="H736" t="n">
-        <v>546.81</v>
+        <v>449.75</v>
       </c>
       <c r="I736" t="n">
         <v>0.0</v>
@@ -27544,7 +27544,7 @@
         </is>
       </c>
       <c r="E743" t="n">
-        <v>1435.47</v>
+        <v>1334.875</v>
       </c>
       <c r="F743" t="n">
         <v>0.0</v>
@@ -27553,7 +27553,7 @@
         <v>162.126</v>
       </c>
       <c r="H743" t="n">
-        <v>1435.47</v>
+        <v>1334.875</v>
       </c>
       <c r="I743" t="n">
         <v>0.0</v>
@@ -27581,7 +27581,7 @@
         </is>
       </c>
       <c r="E744" t="n">
-        <v>827.3689999999999</v>
+        <v>3125.8968</v>
       </c>
       <c r="F744" t="n">
         <v>13.831</v>
@@ -27590,10 +27590,10 @@
         <v>5.029999999999999</v>
       </c>
       <c r="H744" t="n">
-        <v>827.3689999999999</v>
+        <v>696.5999999999999</v>
       </c>
       <c r="I744" t="n">
-        <v>0.0</v>
+        <v>2429.2968</v>
       </c>
     </row>
     <row r="745">
@@ -27618,7 +27618,7 @@
         </is>
       </c>
       <c r="E745" t="n">
-        <v>827.369</v>
+        <v>798.4490000000001</v>
       </c>
       <c r="F745" t="n">
         <v>21.375999999999998</v>
@@ -27627,7 +27627,7 @@
         <v>0.0</v>
       </c>
       <c r="H745" t="n">
-        <v>827.369</v>
+        <v>798.4490000000001</v>
       </c>
       <c r="I745" t="n">
         <v>0.0</v>
@@ -27729,7 +27729,7 @@
         </is>
       </c>
       <c r="E748" t="n">
-        <v>704.134</v>
+        <v>622.468</v>
       </c>
       <c r="F748" t="n">
         <v>0.0</v>
@@ -27738,7 +27738,7 @@
         <v>177.51</v>
       </c>
       <c r="H748" t="n">
-        <v>704.134</v>
+        <v>622.468</v>
       </c>
       <c r="I748" t="n">
         <v>0.0</v>
@@ -27803,7 +27803,7 @@
         </is>
       </c>
       <c r="E750" t="n">
-        <v>0.0</v>
+        <v>2496.974</v>
       </c>
       <c r="F750" t="n">
         <v>0.0</v>
@@ -27815,7 +27815,7 @@
         <v>0.0</v>
       </c>
       <c r="I750" t="n">
-        <v>0.0</v>
+        <v>2496.974</v>
       </c>
     </row>
     <row r="751">
@@ -27840,7 +27840,7 @@
         </is>
       </c>
       <c r="E751" t="n">
-        <v>2833.824</v>
+        <v>2785.394</v>
       </c>
       <c r="F751" t="n">
         <v>0.0</v>
@@ -27849,7 +27849,7 @@
         <v>2.3080000000000003</v>
       </c>
       <c r="H751" t="n">
-        <v>2833.824</v>
+        <v>2785.394</v>
       </c>
       <c r="I751" t="n">
         <v>0.0</v>
@@ -27988,7 +27988,7 @@
         </is>
       </c>
       <c r="E755" t="n">
-        <v>876.896</v>
+        <v>826.157</v>
       </c>
       <c r="F755" t="n">
         <v>2.3080000000000003</v>
@@ -27997,7 +27997,7 @@
         <v>2.3080000000000003</v>
       </c>
       <c r="H755" t="n">
-        <v>876.896</v>
+        <v>826.157</v>
       </c>
       <c r="I755" t="n">
         <v>0.0</v>
@@ -28025,7 +28025,7 @@
         </is>
       </c>
       <c r="E756" t="n">
-        <v>2051.512</v>
+        <v>1975.392</v>
       </c>
       <c r="F756" t="n">
         <v>0.0</v>
@@ -28034,7 +28034,7 @@
         <v>2.3080000000000003</v>
       </c>
       <c r="H756" t="n">
-        <v>2051.512</v>
+        <v>1975.392</v>
       </c>
       <c r="I756" t="n">
         <v>0.0</v>
@@ -28358,7 +28358,7 @@
         </is>
       </c>
       <c r="E765" t="n">
-        <v>815.116</v>
+        <v>778.978</v>
       </c>
       <c r="F765" t="n">
         <v>0.892</v>
@@ -28367,7 +28367,7 @@
         <v>0.0</v>
       </c>
       <c r="H765" t="n">
-        <v>815.116</v>
+        <v>778.978</v>
       </c>
       <c r="I765" t="n">
         <v>0.0</v>
@@ -28506,7 +28506,7 @@
         </is>
       </c>
       <c r="E769" t="n">
-        <v>18694.161</v>
+        <v>19065.247</v>
       </c>
       <c r="F769" t="n">
         <v>15.231</v>
@@ -28515,10 +28515,10 @@
         <v>7.385</v>
       </c>
       <c r="H769" t="n">
-        <v>18694.161</v>
+        <v>18446.77</v>
       </c>
       <c r="I769" t="n">
-        <v>0.0</v>
+        <v>618.477</v>
       </c>
     </row>
     <row r="770">
@@ -28654,7 +28654,7 @@
         </is>
       </c>
       <c r="E773" t="n">
-        <v>5231.004</v>
+        <v>5180.2339999999995</v>
       </c>
       <c r="F773" t="n">
         <v>2.0309999999999997</v>
@@ -28663,7 +28663,7 @@
         <v>2.0309999999999997</v>
       </c>
       <c r="H773" t="n">
-        <v>5231.004</v>
+        <v>5180.2339999999995</v>
       </c>
       <c r="I773" t="n">
         <v>0.0</v>
@@ -28691,7 +28691,7 @@
         </is>
       </c>
       <c r="E774" t="n">
-        <v>1023.5219999999999</v>
+        <v>2230.154</v>
       </c>
       <c r="F774" t="n">
         <v>2.0309999999999997</v>
@@ -28700,10 +28700,10 @@
         <v>4.061999999999999</v>
       </c>
       <c r="H774" t="n">
-        <v>1023.5219999999999</v>
+        <v>991.366</v>
       </c>
       <c r="I774" t="n">
-        <v>0.0</v>
+        <v>1238.788</v>
       </c>
     </row>
     <row r="775">
@@ -28765,7 +28765,7 @@
         </is>
       </c>
       <c r="E776" t="n">
-        <v>11519.377</v>
+        <v>11485.869</v>
       </c>
       <c r="F776" t="n">
         <v>4.736</v>
@@ -28774,10 +28774,10 @@
         <v>38.585</v>
       </c>
       <c r="H776" t="n">
-        <v>11519.377</v>
+        <v>11414.791000000001</v>
       </c>
       <c r="I776" t="n">
-        <v>0.0</v>
+        <v>71.078</v>
       </c>
     </row>
     <row r="777">
@@ -28913,7 +28913,7 @@
         </is>
       </c>
       <c r="E780" t="n">
-        <v>2936.197</v>
+        <v>5158.5684</v>
       </c>
       <c r="F780" t="n">
         <v>0.0</v>
@@ -28922,10 +28922,10 @@
         <v>0.0</v>
       </c>
       <c r="H780" t="n">
-        <v>2936.197</v>
+        <v>2949.058</v>
       </c>
       <c r="I780" t="n">
-        <v>0.0</v>
+        <v>2209.5104</v>
       </c>
     </row>
     <row r="781">
@@ -28987,7 +28987,7 @@
         </is>
       </c>
       <c r="E782" t="n">
-        <v>9.819</v>
+        <v>7.109</v>
       </c>
       <c r="F782" t="n">
         <v>0.0</v>
@@ -28996,7 +28996,7 @@
         <v>6419.359</v>
       </c>
       <c r="H782" t="n">
-        <v>9.819</v>
+        <v>7.109</v>
       </c>
       <c r="I782" t="n">
         <v>0.0</v>
@@ -29061,7 +29061,7 @@
         </is>
       </c>
       <c r="E784" t="n">
-        <v>668.4</v>
+        <v>666.24</v>
       </c>
       <c r="F784" t="n">
         <v>0.0</v>
@@ -29070,7 +29070,7 @@
         <v>19.68</v>
       </c>
       <c r="H784" t="n">
-        <v>668.4</v>
+        <v>666.24</v>
       </c>
       <c r="I784" t="n">
         <v>0.0</v>
@@ -29135,7 +29135,7 @@
         </is>
       </c>
       <c r="E786" t="n">
-        <v>4058.854</v>
+        <v>3963.163</v>
       </c>
       <c r="F786" t="n">
         <v>0.185</v>
@@ -29144,7 +29144,7 @@
         <v>34.456</v>
       </c>
       <c r="H786" t="n">
-        <v>4058.854</v>
+        <v>3963.163</v>
       </c>
       <c r="I786" t="n">
         <v>0.0</v>
@@ -29172,7 +29172,7 @@
         </is>
       </c>
       <c r="E787" t="n">
-        <v>478.549</v>
+        <v>481.87899999999996</v>
       </c>
       <c r="F787" t="n">
         <v>4.995</v>
@@ -29181,7 +29181,7 @@
         <v>79.36500000000001</v>
       </c>
       <c r="H787" t="n">
-        <v>478.549</v>
+        <v>481.87899999999996</v>
       </c>
       <c r="I787" t="n">
         <v>0.0</v>
@@ -29209,7 +29209,7 @@
         </is>
       </c>
       <c r="E788" t="n">
-        <v>1101.735</v>
+        <v>1101.6</v>
       </c>
       <c r="F788" t="n">
         <v>1.485</v>
@@ -29218,7 +29218,7 @@
         <v>8.1</v>
       </c>
       <c r="H788" t="n">
-        <v>1101.735</v>
+        <v>1101.6</v>
       </c>
       <c r="I788" t="n">
         <v>0.0</v>
@@ -29246,7 +29246,7 @@
         </is>
       </c>
       <c r="E789" t="n">
-        <v>790.64</v>
+        <v>781.88</v>
       </c>
       <c r="F789" t="n">
         <v>0.32</v>
@@ -29255,7 +29255,7 @@
         <v>17.32</v>
       </c>
       <c r="H789" t="n">
-        <v>790.64</v>
+        <v>781.88</v>
       </c>
       <c r="I789" t="n">
         <v>0.0</v>
@@ -29357,7 +29357,7 @@
         </is>
       </c>
       <c r="E792" t="n">
-        <v>4957.531</v>
+        <v>4880.506</v>
       </c>
       <c r="F792" t="n">
         <v>3.033</v>
@@ -29366,7 +29366,7 @@
         <v>12.13</v>
       </c>
       <c r="H792" t="n">
-        <v>4957.531</v>
+        <v>4880.506</v>
       </c>
       <c r="I792" t="n">
         <v>0.0</v>
@@ -29394,7 +29394,7 @@
         </is>
       </c>
       <c r="E793" t="n">
-        <v>3173.815</v>
+        <v>3025.222</v>
       </c>
       <c r="F793" t="n">
         <v>6.065</v>
@@ -29403,7 +29403,7 @@
         <v>9.704</v>
       </c>
       <c r="H793" t="n">
-        <v>3173.815</v>
+        <v>3025.222</v>
       </c>
       <c r="I793" t="n">
         <v>0.0</v>
@@ -29431,7 +29431,7 @@
         </is>
       </c>
       <c r="E794" t="n">
-        <v>356.622</v>
+        <v>337.214</v>
       </c>
       <c r="F794" t="n">
         <v>1.213</v>
@@ -29440,7 +29440,7 @@
         <v>0.0</v>
       </c>
       <c r="H794" t="n">
-        <v>356.622</v>
+        <v>337.214</v>
       </c>
       <c r="I794" t="n">
         <v>0.0</v>
@@ -29579,7 +29579,7 @@
         </is>
       </c>
       <c r="E798" t="n">
-        <v>3025.828</v>
+        <v>6130.5025000000005</v>
       </c>
       <c r="F798" t="n">
         <v>1.8920000000000001</v>
@@ -29588,10 +29588,10 @@
         <v>80.739</v>
       </c>
       <c r="H798" t="n">
-        <v>3025.828</v>
+        <v>2964.012</v>
       </c>
       <c r="I798" t="n">
-        <v>0.0</v>
+        <v>3166.4905</v>
       </c>
     </row>
     <row r="799">
@@ -29616,7 +29616,7 @@
         </is>
       </c>
       <c r="E799" t="n">
-        <v>3158.2909999999997</v>
+        <v>3151.352</v>
       </c>
       <c r="F799" t="n">
         <v>3.154</v>
@@ -29625,7 +29625,7 @@
         <v>0.631</v>
       </c>
       <c r="H799" t="n">
-        <v>3158.2909999999997</v>
+        <v>3151.352</v>
       </c>
       <c r="I799" t="n">
         <v>0.0</v>
@@ -29653,7 +29653,7 @@
         </is>
       </c>
       <c r="E800" t="n">
-        <v>4515.558</v>
+        <v>4513.878</v>
       </c>
       <c r="F800" t="n">
         <v>0.0</v>
@@ -29662,7 +29662,7 @@
         <v>0.0</v>
       </c>
       <c r="H800" t="n">
-        <v>4515.558</v>
+        <v>4513.878</v>
       </c>
       <c r="I800" t="n">
         <v>0.0</v>
@@ -29838,7 +29838,7 @@
         </is>
       </c>
       <c r="E805" t="n">
-        <v>484.604</v>
+        <v>478.143</v>
       </c>
       <c r="F805" t="n">
         <v>0.0</v>
@@ -29847,7 +29847,7 @@
         <v>590.1410000000001</v>
       </c>
       <c r="H805" t="n">
-        <v>484.604</v>
+        <v>478.143</v>
       </c>
       <c r="I805" t="n">
         <v>0.0</v>
@@ -30097,7 +30097,7 @@
         </is>
       </c>
       <c r="E812" t="n">
-        <v>1533.2</v>
+        <v>1526.0</v>
       </c>
       <c r="F812" t="n">
         <v>0.6</v>
@@ -30106,7 +30106,7 @@
         <v>2.4</v>
       </c>
       <c r="H812" t="n">
-        <v>1533.2</v>
+        <v>1526.0</v>
       </c>
       <c r="I812" t="n">
         <v>0.0</v>
@@ -30171,7 +30171,7 @@
         </is>
       </c>
       <c r="E814" t="n">
-        <v>1219.121</v>
+        <v>1215.924</v>
       </c>
       <c r="F814" t="n">
         <v>0.0</v>
@@ -30180,7 +30180,7 @@
         <v>0.0</v>
       </c>
       <c r="H814" t="n">
-        <v>1219.121</v>
+        <v>1215.924</v>
       </c>
       <c r="I814" t="n">
         <v>0.0</v>
@@ -30208,7 +30208,7 @@
         </is>
       </c>
       <c r="E815" t="n">
-        <v>16933.341</v>
+        <v>16933.342</v>
       </c>
       <c r="F815" t="n">
         <v>0.533</v>
@@ -30217,7 +30217,7 @@
         <v>0.0</v>
       </c>
       <c r="H815" t="n">
-        <v>16933.341</v>
+        <v>16933.342</v>
       </c>
       <c r="I815" t="n">
         <v>0.0</v>
@@ -30245,7 +30245,7 @@
         </is>
       </c>
       <c r="E816" t="n">
-        <v>35.204</v>
+        <v>32.537</v>
       </c>
       <c r="F816" t="n">
         <v>0.533</v>
@@ -30254,7 +30254,7 @@
         <v>0.0</v>
       </c>
       <c r="H816" t="n">
-        <v>35.204</v>
+        <v>32.537</v>
       </c>
       <c r="I816" t="n">
         <v>0.0</v>
@@ -30282,7 +30282,7 @@
         </is>
       </c>
       <c r="E817" t="n">
-        <v>12134.052</v>
+        <v>12127.648</v>
       </c>
       <c r="F817" t="n">
         <v>2.4</v>
@@ -30291,7 +30291,7 @@
         <v>599.008</v>
       </c>
       <c r="H817" t="n">
-        <v>12134.052</v>
+        <v>12127.648</v>
       </c>
       <c r="I817" t="n">
         <v>0.0</v>
@@ -30430,7 +30430,7 @@
         </is>
       </c>
       <c r="E821" t="n">
-        <v>113.616</v>
+        <v>30.404</v>
       </c>
       <c r="F821" t="n">
         <v>0.0</v>
@@ -30439,7 +30439,7 @@
         <v>192.024</v>
       </c>
       <c r="H821" t="n">
-        <v>113.616</v>
+        <v>30.404</v>
       </c>
       <c r="I821" t="n">
         <v>0.0</v>
@@ -30763,7 +30763,7 @@
         </is>
       </c>
       <c r="E830" t="n">
-        <v>5188.537</v>
+        <v>5188.538</v>
       </c>
       <c r="F830" t="n">
         <v>0.0</v>
@@ -30772,7 +30772,7 @@
         <v>1.3339999999999999</v>
       </c>
       <c r="H830" t="n">
-        <v>5188.537</v>
+        <v>5188.538</v>
       </c>
       <c r="I830" t="n">
         <v>0.0</v>
@@ -30800,7 +30800,7 @@
         </is>
       </c>
       <c r="E831" t="n">
-        <v>3129.501</v>
+        <v>3129.502</v>
       </c>
       <c r="F831" t="n">
         <v>0.0</v>
@@ -30809,7 +30809,7 @@
         <v>0.5</v>
       </c>
       <c r="H831" t="n">
-        <v>3129.501</v>
+        <v>3129.502</v>
       </c>
       <c r="I831" t="n">
         <v>0.0</v>
@@ -31392,7 +31392,7 @@
         </is>
       </c>
       <c r="E847" t="n">
-        <v>2928.147</v>
+        <v>2927.48</v>
       </c>
       <c r="F847" t="n">
         <v>1.333</v>
@@ -31401,7 +31401,7 @@
         <v>0.6669999999999999</v>
       </c>
       <c r="H847" t="n">
-        <v>2928.147</v>
+        <v>2927.48</v>
       </c>
       <c r="I847" t="n">
         <v>0.0</v>
@@ -31429,7 +31429,7 @@
         </is>
       </c>
       <c r="E848" t="n">
-        <v>2608.1310000000003</v>
+        <v>2607.464</v>
       </c>
       <c r="F848" t="n">
         <v>3.333</v>
@@ -31438,7 +31438,7 @@
         <v>0.0</v>
       </c>
       <c r="H848" t="n">
-        <v>2608.1310000000003</v>
+        <v>2607.464</v>
       </c>
       <c r="I848" t="n">
         <v>0.0</v>
@@ -31466,7 +31466,7 @@
         </is>
       </c>
       <c r="E849" t="n">
-        <v>19555.976000000002</v>
+        <v>19550.641</v>
       </c>
       <c r="F849" t="n">
         <v>10.67</v>
@@ -31475,7 +31475,7 @@
         <v>0.0</v>
       </c>
       <c r="H849" t="n">
-        <v>19555.976000000002</v>
+        <v>19550.641</v>
       </c>
       <c r="I849" t="n">
         <v>0.0</v>
@@ -31651,7 +31651,7 @@
         </is>
       </c>
       <c r="E854" t="n">
-        <v>9972.251</v>
+        <v>9965.317000000001</v>
       </c>
       <c r="F854" t="n">
         <v>15.601</v>
@@ -31660,7 +31660,7 @@
         <v>0.0</v>
       </c>
       <c r="H854" t="n">
-        <v>9972.251</v>
+        <v>9965.317000000001</v>
       </c>
       <c r="I854" t="n">
         <v>0.0</v>
@@ -31688,7 +31688,7 @@
         </is>
       </c>
       <c r="E855" t="n">
-        <v>460.858</v>
+        <v>435.25399999999996</v>
       </c>
       <c r="F855" t="n">
         <v>23.470000000000002</v>
@@ -31697,7 +31697,7 @@
         <v>0.0</v>
       </c>
       <c r="H855" t="n">
-        <v>460.858</v>
+        <v>435.25399999999996</v>
       </c>
       <c r="I855" t="n">
         <v>0.0</v>
@@ -31836,7 +31836,7 @@
         </is>
       </c>
       <c r="E859" t="n">
-        <v>11954.804</v>
+        <v>11954.803</v>
       </c>
       <c r="F859" t="n">
         <v>15.997999999999998</v>
@@ -31845,7 +31845,7 @@
         <v>0.6669999999999999</v>
       </c>
       <c r="H859" t="n">
-        <v>11954.804</v>
+        <v>11954.803</v>
       </c>
       <c r="I859" t="n">
         <v>0.0</v>
@@ -31910,7 +31910,7 @@
         </is>
       </c>
       <c r="E861" t="n">
-        <v>2313.2</v>
+        <v>2311.3999999999996</v>
       </c>
       <c r="F861" t="n">
         <v>0.0</v>
@@ -31919,7 +31919,7 @@
         <v>0.0</v>
       </c>
       <c r="H861" t="n">
-        <v>2313.2</v>
+        <v>2311.3999999999996</v>
       </c>
       <c r="I861" t="n">
         <v>0.0</v>
@@ -31984,7 +31984,7 @@
         </is>
       </c>
       <c r="E863" t="n">
-        <v>10922.165</v>
+        <v>10733.341</v>
       </c>
       <c r="F863" t="n">
         <v>39.205</v>
@@ -31993,7 +31993,7 @@
         <v>0.0</v>
       </c>
       <c r="H863" t="n">
-        <v>10922.165</v>
+        <v>10733.341</v>
       </c>
       <c r="I863" t="n">
         <v>0.0</v>
@@ -32058,7 +32058,7 @@
         </is>
       </c>
       <c r="E865" t="n">
-        <v>2951.835</v>
+        <v>2950.768</v>
       </c>
       <c r="F865" t="n">
         <v>2.134</v>
@@ -32067,7 +32067,7 @@
         <v>0.0</v>
       </c>
       <c r="H865" t="n">
-        <v>2951.835</v>
+        <v>2950.768</v>
       </c>
       <c r="I865" t="n">
         <v>0.0</v>
@@ -32095,7 +32095,7 @@
         </is>
       </c>
       <c r="E866" t="n">
-        <v>1316.431</v>
+        <v>1314.298</v>
       </c>
       <c r="F866" t="n">
         <v>1.067</v>
@@ -32104,7 +32104,7 @@
         <v>25.603</v>
       </c>
       <c r="H866" t="n">
-        <v>1316.431</v>
+        <v>1314.298</v>
       </c>
       <c r="I866" t="n">
         <v>0.0</v>
@@ -32132,7 +32132,7 @@
         </is>
       </c>
       <c r="E867" t="n">
-        <v>888.523</v>
+        <v>620.45</v>
       </c>
       <c r="F867" t="n">
         <v>18.802</v>
@@ -32141,7 +32141,7 @@
         <v>19.408</v>
       </c>
       <c r="H867" t="n">
-        <v>888.523</v>
+        <v>620.45</v>
       </c>
       <c r="I867" t="n">
         <v>0.0</v>
@@ -32169,7 +32169,7 @@
         </is>
       </c>
       <c r="E868" t="n">
-        <v>1255.588</v>
+        <v>1244.937</v>
       </c>
       <c r="F868" t="n">
         <v>0.0</v>
@@ -32178,7 +32178,7 @@
         <v>0.0</v>
       </c>
       <c r="H868" t="n">
-        <v>1255.588</v>
+        <v>1244.937</v>
       </c>
       <c r="I868" t="n">
         <v>0.0</v>
@@ -32206,7 +32206,7 @@
         </is>
       </c>
       <c r="E869" t="n">
-        <v>1253.081</v>
+        <v>1239.235</v>
       </c>
       <c r="F869" t="n">
         <v>0.0</v>
@@ -32215,7 +32215,7 @@
         <v>9.231</v>
       </c>
       <c r="H869" t="n">
-        <v>1253.081</v>
+        <v>1239.235</v>
       </c>
       <c r="I869" t="n">
         <v>0.0</v>
@@ -32243,7 +32243,7 @@
         </is>
       </c>
       <c r="E870" t="n">
-        <v>1508.9850000000001</v>
+        <v>1260.62</v>
       </c>
       <c r="F870" t="n">
         <v>5.916</v>
@@ -32252,7 +32252,7 @@
         <v>346.144</v>
       </c>
       <c r="H870" t="n">
-        <v>1508.9850000000001</v>
+        <v>1260.62</v>
       </c>
       <c r="I870" t="n">
         <v>0.0</v>
@@ -32317,7 +32317,7 @@
         </is>
       </c>
       <c r="E872" t="n">
-        <v>4102.444</v>
+        <v>3953.332</v>
       </c>
       <c r="F872" t="n">
         <v>0.0</v>
@@ -32326,7 +32326,7 @@
         <v>0.0</v>
       </c>
       <c r="H872" t="n">
-        <v>4102.444</v>
+        <v>3953.332</v>
       </c>
       <c r="I872" t="n">
         <v>0.0</v>
@@ -32391,7 +32391,7 @@
         </is>
       </c>
       <c r="E874" t="n">
-        <v>8891.566</v>
+        <v>11810.8095</v>
       </c>
       <c r="F874" t="n">
         <v>0.0</v>
@@ -32400,10 +32400,10 @@
         <v>6.923</v>
       </c>
       <c r="H874" t="n">
-        <v>8891.566</v>
+        <v>8822.338</v>
       </c>
       <c r="I874" t="n">
-        <v>0.0</v>
+        <v>2988.4715</v>
       </c>
     </row>
     <row r="875">
@@ -32428,7 +32428,7 @@
         </is>
       </c>
       <c r="E875" t="n">
-        <v>4825.401</v>
+        <v>4788.478</v>
       </c>
       <c r="F875" t="n">
         <v>0.0</v>
@@ -32437,7 +32437,7 @@
         <v>0.0</v>
       </c>
       <c r="H875" t="n">
-        <v>4825.401</v>
+        <v>4788.478</v>
       </c>
       <c r="I875" t="n">
         <v>0.0</v>
@@ -32502,7 +32502,7 @@
         </is>
       </c>
       <c r="E877" t="n">
-        <v>2389.519</v>
+        <v>2046.563</v>
       </c>
       <c r="F877" t="n">
         <v>0.0</v>
@@ -32511,7 +32511,7 @@
         <v>0.9319999999999999</v>
       </c>
       <c r="H877" t="n">
-        <v>2389.519</v>
+        <v>2046.563</v>
       </c>
       <c r="I877" t="n">
         <v>0.0</v>
@@ -32539,7 +32539,7 @@
         </is>
       </c>
       <c r="E878" t="n">
-        <v>1832.051</v>
+        <v>2453.336</v>
       </c>
       <c r="F878" t="n">
         <v>13.168</v>
@@ -32551,7 +32551,7 @@
         <v>1832.051</v>
       </c>
       <c r="I878" t="n">
-        <v>0.0</v>
+        <v>621.285</v>
       </c>
     </row>
     <row r="879">
@@ -32576,7 +32576,7 @@
         </is>
       </c>
       <c r="E879" t="n">
-        <v>1677.138</v>
+        <v>1161.643</v>
       </c>
       <c r="F879" t="n">
         <v>0.0</v>
@@ -32585,7 +32585,7 @@
         <v>2.84</v>
       </c>
       <c r="H879" t="n">
-        <v>1677.138</v>
+        <v>1161.643</v>
       </c>
       <c r="I879" t="n">
         <v>0.0</v>
@@ -32650,7 +32650,7 @@
         </is>
       </c>
       <c r="E881" t="n">
-        <v>95.25699999999999</v>
+        <v>1293.457</v>
       </c>
       <c r="F881" t="n">
         <v>0.9990000000000001</v>
@@ -32662,7 +32662,7 @@
         <v>95.25699999999999</v>
       </c>
       <c r="I881" t="n">
-        <v>0.0</v>
+        <v>1198.2</v>
       </c>
     </row>
     <row r="882">
@@ -32687,7 +32687,7 @@
         </is>
       </c>
       <c r="E882" t="n">
-        <v>383.424</v>
+        <v>69.895</v>
       </c>
       <c r="F882" t="n">
         <v>0.0</v>
@@ -32696,7 +32696,7 @@
         <v>3.994</v>
       </c>
       <c r="H882" t="n">
-        <v>383.424</v>
+        <v>69.895</v>
       </c>
       <c r="I882" t="n">
         <v>0.0</v>
@@ -32798,7 +32798,7 @@
         </is>
       </c>
       <c r="E885" t="n">
-        <v>2003.497</v>
+        <v>2827.1422000000002</v>
       </c>
       <c r="F885" t="n">
         <v>0.0</v>
@@ -32807,10 +32807,10 @@
         <v>42.602000000000004</v>
       </c>
       <c r="H885" t="n">
-        <v>2003.497</v>
+        <v>1941.959</v>
       </c>
       <c r="I885" t="n">
-        <v>0.0</v>
+        <v>885.1832</v>
       </c>
     </row>
     <row r="886">
@@ -32983,7 +32983,7 @@
         </is>
       </c>
       <c r="E890" t="n">
-        <v>2628.101</v>
+        <v>2620.095</v>
       </c>
       <c r="F890" t="n">
         <v>0.0</v>
@@ -32992,7 +32992,7 @@
         <v>240.19199999999998</v>
       </c>
       <c r="H890" t="n">
-        <v>2628.101</v>
+        <v>2620.095</v>
       </c>
       <c r="I890" t="n">
         <v>0.0</v>
@@ -33057,7 +33057,7 @@
         </is>
       </c>
       <c r="E892" t="n">
-        <v>7883.972</v>
+        <v>7877.297</v>
       </c>
       <c r="F892" t="n">
         <v>0.0</v>
@@ -33066,7 +33066,7 @@
         <v>84.29</v>
       </c>
       <c r="H892" t="n">
-        <v>7883.972</v>
+        <v>7877.297</v>
       </c>
       <c r="I892" t="n">
         <v>0.0</v>
@@ -33242,7 +33242,7 @@
         </is>
       </c>
       <c r="E897" t="n">
-        <v>1730.717</v>
+        <v>1810.781</v>
       </c>
       <c r="F897" t="n">
         <v>0.0</v>
@@ -33251,7 +33251,7 @@
         <v>227.07</v>
       </c>
       <c r="H897" t="n">
-        <v>1730.717</v>
+        <v>1810.781</v>
       </c>
       <c r="I897" t="n">
         <v>0.0</v>
@@ -33279,7 +33279,7 @@
         </is>
       </c>
       <c r="E898" t="n">
-        <v>106.752</v>
+        <v>30.691</v>
       </c>
       <c r="F898" t="n">
         <v>0.0</v>
@@ -33288,7 +33288,7 @@
         <v>0.0</v>
       </c>
       <c r="H898" t="n">
-        <v>106.752</v>
+        <v>30.691</v>
       </c>
       <c r="I898" t="n">
         <v>0.0</v>
@@ -33316,7 +33316,7 @@
         </is>
       </c>
       <c r="E899" t="n">
-        <v>1622.994</v>
+        <v>1296.6970000000001</v>
       </c>
       <c r="F899" t="n">
         <v>3.033</v>
@@ -33325,7 +33325,7 @@
         <v>0.0</v>
       </c>
       <c r="H899" t="n">
-        <v>1622.994</v>
+        <v>1296.6970000000001</v>
       </c>
       <c r="I899" t="n">
         <v>0.0</v>
@@ -33353,7 +33353,7 @@
         </is>
       </c>
       <c r="E900" t="n">
-        <v>1018.3140000000001</v>
+        <v>2945.164</v>
       </c>
       <c r="F900" t="n">
         <v>0.607</v>
@@ -33362,10 +33362,10 @@
         <v>0.0</v>
       </c>
       <c r="H900" t="n">
-        <v>1018.3140000000001</v>
+        <v>984.956</v>
       </c>
       <c r="I900" t="n">
-        <v>0.0</v>
+        <v>1960.208</v>
       </c>
     </row>
     <row r="901">
@@ -33427,7 +33427,7 @@
         </is>
       </c>
       <c r="E902" t="n">
-        <v>2373.916</v>
+        <v>2087.12</v>
       </c>
       <c r="F902" t="n">
         <v>67.218</v>
@@ -33436,7 +33436,7 @@
         <v>0.0</v>
       </c>
       <c r="H902" t="n">
-        <v>2373.916</v>
+        <v>2087.12</v>
       </c>
       <c r="I902" t="n">
         <v>0.0</v>
@@ -34315,7 +34315,7 @@
         </is>
       </c>
       <c r="E926" t="n">
-        <v>4561.786999999999</v>
+        <v>4514.659</v>
       </c>
       <c r="F926" t="n">
         <v>0.211</v>
@@ -34324,7 +34324,7 @@
         <v>1.262</v>
       </c>
       <c r="H926" t="n">
-        <v>4561.786999999999</v>
+        <v>4514.659</v>
       </c>
       <c r="I926" t="n">
         <v>0.0</v>
@@ -34352,7 +34352,7 @@
         </is>
       </c>
       <c r="E927" t="n">
-        <v>819.508</v>
+        <v>792.366</v>
       </c>
       <c r="F927" t="n">
         <v>0.0</v>
@@ -34361,7 +34361,7 @@
         <v>0.0</v>
       </c>
       <c r="H927" t="n">
-        <v>819.508</v>
+        <v>792.366</v>
       </c>
       <c r="I927" t="n">
         <v>0.0</v>
@@ -34389,7 +34389,7 @@
         </is>
       </c>
       <c r="E928" t="n">
-        <v>2610.007</v>
+        <v>2610.008</v>
       </c>
       <c r="F928" t="n">
         <v>0.0</v>
@@ -34398,7 +34398,7 @@
         <v>11.539000000000001</v>
       </c>
       <c r="H928" t="n">
-        <v>2610.007</v>
+        <v>2610.008</v>
       </c>
       <c r="I928" t="n">
         <v>0.0</v>
@@ -34500,7 +34500,7 @@
         </is>
       </c>
       <c r="E931" t="n">
-        <v>3348.471</v>
+        <v>3334.626</v>
       </c>
       <c r="F931" t="n">
         <v>0.0</v>
@@ -34509,7 +34509,7 @@
         <v>2.3080000000000003</v>
       </c>
       <c r="H931" t="n">
-        <v>3348.471</v>
+        <v>3334.626</v>
       </c>
       <c r="I931" t="n">
         <v>0.0</v>
@@ -34722,7 +34722,7 @@
         </is>
       </c>
       <c r="E937" t="n">
-        <v>8775.504</v>
+        <v>8819.882000000001</v>
       </c>
       <c r="F937" t="n">
         <v>1.6280000000000001</v>
@@ -34731,7 +34731,7 @@
         <v>128.102</v>
       </c>
       <c r="H937" t="n">
-        <v>8775.504</v>
+        <v>8819.882000000001</v>
       </c>
       <c r="I937" t="n">
         <v>0.0</v>
@@ -34796,7 +34796,7 @@
         </is>
       </c>
       <c r="E939" t="n">
-        <v>4158.475</v>
+        <v>4149.245</v>
       </c>
       <c r="F939" t="n">
         <v>0.0</v>
@@ -34805,7 +34805,7 @@
         <v>2.3080000000000003</v>
       </c>
       <c r="H939" t="n">
-        <v>4158.475</v>
+        <v>4149.245</v>
       </c>
       <c r="I939" t="n">
         <v>0.0</v>
@@ -34944,7 +34944,7 @@
         </is>
       </c>
       <c r="E943" t="n">
-        <v>303.238</v>
+        <v>209.627</v>
       </c>
       <c r="F943" t="n">
         <v>9.601</v>
@@ -34953,7 +34953,7 @@
         <v>0.0</v>
       </c>
       <c r="H943" t="n">
-        <v>303.238</v>
+        <v>209.627</v>
       </c>
       <c r="I943" t="n">
         <v>0.0</v>
@@ -35240,7 +35240,7 @@
         </is>
       </c>
       <c r="E951" t="n">
-        <v>1714.01</v>
+        <v>1484.404</v>
       </c>
       <c r="F951" t="n">
         <v>57.22</v>
@@ -35249,7 +35249,7 @@
         <v>0.0</v>
       </c>
       <c r="H951" t="n">
-        <v>1714.01</v>
+        <v>1484.404</v>
       </c>
       <c r="I951" t="n">
         <v>0.0</v>
@@ -35277,7 +35277,7 @@
         </is>
       </c>
       <c r="E952" t="n">
-        <v>884.614</v>
+        <v>827.214</v>
       </c>
       <c r="F952" t="n">
         <v>0.728</v>
@@ -35286,7 +35286,7 @@
         <v>0.0</v>
       </c>
       <c r="H952" t="n">
-        <v>884.614</v>
+        <v>827.214</v>
       </c>
       <c r="I952" t="n">
         <v>0.0</v>
@@ -35388,7 +35388,7 @@
         </is>
       </c>
       <c r="E955" t="n">
-        <v>5390.0</v>
+        <v>5388.0</v>
       </c>
       <c r="F955" t="n">
         <v>0.0</v>
@@ -35397,7 +35397,7 @@
         <v>180.0</v>
       </c>
       <c r="H955" t="n">
-        <v>5390.0</v>
+        <v>5388.0</v>
       </c>
       <c r="I955" t="n">
         <v>0.0</v>
@@ -35869,7 +35869,7 @@
         </is>
       </c>
       <c r="E968" t="n">
-        <v>68.044</v>
+        <v>68.035</v>
       </c>
       <c r="F968" t="n">
         <v>0.0</v>
@@ -35878,7 +35878,7 @@
         <v>0.0</v>
       </c>
       <c r="H968" t="n">
-        <v>68.044</v>
+        <v>68.035</v>
       </c>
       <c r="I968" t="n">
         <v>0.0</v>
@@ -36461,7 +36461,7 @@
         </is>
       </c>
       <c r="E984" t="n">
-        <v>297.733</v>
+        <v>259.233</v>
       </c>
       <c r="F984" t="n">
         <v>16.1</v>
@@ -36470,7 +36470,7 @@
         <v>12.6</v>
       </c>
       <c r="H984" t="n">
-        <v>297.733</v>
+        <v>259.233</v>
       </c>
       <c r="I984" t="n">
         <v>0.0</v>
@@ -36498,7 +36498,7 @@
         </is>
       </c>
       <c r="E985" t="n">
-        <v>1684.865</v>
+        <v>1768.935</v>
       </c>
       <c r="F985" t="n">
         <v>37.268</v>
@@ -36507,7 +36507,7 @@
         <v>0.867</v>
       </c>
       <c r="H985" t="n">
-        <v>1684.865</v>
+        <v>1768.935</v>
       </c>
       <c r="I985" t="n">
         <v>0.0</v>
@@ -36535,7 +36535,7 @@
         </is>
       </c>
       <c r="E986" t="n">
-        <v>3697.627</v>
+        <v>3602.8900000000003</v>
       </c>
       <c r="F986" t="n">
         <v>16.434</v>
@@ -36544,7 +36544,7 @@
         <v>8.7</v>
       </c>
       <c r="H986" t="n">
-        <v>3697.627</v>
+        <v>3602.8900000000003</v>
       </c>
       <c r="I986" t="n">
         <v>0.0</v>
@@ -37423,7 +37423,7 @@
         </is>
       </c>
       <c r="E1010" t="n">
-        <v>3.503</v>
+        <v>123.599</v>
       </c>
       <c r="F1010" t="n">
         <v>0.0</v>
@@ -37432,7 +37432,7 @@
         <v>0.0</v>
       </c>
       <c r="H1010" t="n">
-        <v>3.503</v>
+        <v>123.599</v>
       </c>
       <c r="I1010" t="n">
         <v>0.0</v>
@@ -37497,7 +37497,7 @@
         </is>
       </c>
       <c r="E1012" t="n">
-        <v>63.904</v>
+        <v>276.916</v>
       </c>
       <c r="F1012" t="n">
         <v>0.0</v>
@@ -37506,7 +37506,7 @@
         <v>0.0</v>
       </c>
       <c r="H1012" t="n">
-        <v>63.904</v>
+        <v>276.916</v>
       </c>
       <c r="I1012" t="n">
         <v>0.0</v>
@@ -37534,7 +37534,7 @@
         </is>
       </c>
       <c r="E1013" t="n">
-        <v>7125.25</v>
+        <v>6571.419</v>
       </c>
       <c r="F1013" t="n">
         <v>0.0</v>
@@ -37543,7 +37543,7 @@
         <v>0.0</v>
       </c>
       <c r="H1013" t="n">
-        <v>7125.25</v>
+        <v>6571.419</v>
       </c>
       <c r="I1013" t="n">
         <v>0.0</v>
@@ -37756,7 +37756,7 @@
         </is>
       </c>
       <c r="E1019" t="n">
-        <v>5778.402</v>
+        <v>5778.396</v>
       </c>
       <c r="F1019" t="n">
         <v>68.241</v>
@@ -37765,7 +37765,7 @@
         <v>47.885999999999996</v>
       </c>
       <c r="H1019" t="n">
-        <v>5778.402</v>
+        <v>5778.396</v>
       </c>
       <c r="I1019" t="n">
         <v>0.0</v>
@@ -37830,7 +37830,7 @@
         </is>
       </c>
       <c r="E1021" t="n">
-        <v>748.895</v>
+        <v>710.489</v>
       </c>
       <c r="F1021" t="n">
         <v>0.0</v>
@@ -37839,7 +37839,7 @@
         <v>0.0</v>
       </c>
       <c r="H1021" t="n">
-        <v>748.895</v>
+        <v>710.489</v>
       </c>
       <c r="I1021" t="n">
         <v>0.0</v>
@@ -38052,7 +38052,7 @@
         </is>
       </c>
       <c r="E1027" t="n">
-        <v>4419.456999999999</v>
+        <v>4157.607</v>
       </c>
       <c r="F1027" t="n">
         <v>0.0</v>
@@ -38061,7 +38061,7 @@
         <v>0.0</v>
       </c>
       <c r="H1027" t="n">
-        <v>4419.456999999999</v>
+        <v>4157.607</v>
       </c>
       <c r="I1027" t="n">
         <v>0.0</v>
@@ -38200,7 +38200,7 @@
         </is>
       </c>
       <c r="E1031" t="n">
-        <v>6242.198</v>
+        <v>5869.419</v>
       </c>
       <c r="F1031" t="n">
         <v>0.0</v>
@@ -38209,7 +38209,7 @@
         <v>3.7279999999999998</v>
       </c>
       <c r="H1031" t="n">
-        <v>6242.198</v>
+        <v>5869.419</v>
       </c>
       <c r="I1031" t="n">
         <v>0.0</v>
@@ -38237,7 +38237,7 @@
         </is>
       </c>
       <c r="E1032" t="n">
-        <v>4540.41</v>
+        <v>4158.763</v>
       </c>
       <c r="F1032" t="n">
         <v>11.094</v>
@@ -38246,7 +38246,7 @@
         <v>12.426</v>
       </c>
       <c r="H1032" t="n">
-        <v>4540.41</v>
+        <v>4158.763</v>
       </c>
       <c r="I1032" t="n">
         <v>0.0</v>
@@ -38274,7 +38274,7 @@
         </is>
       </c>
       <c r="E1033" t="n">
-        <v>6590.354</v>
+        <v>6560.77</v>
       </c>
       <c r="F1033" t="n">
         <v>1.183</v>
@@ -38283,7 +38283,7 @@
         <v>3.846</v>
       </c>
       <c r="H1033" t="n">
-        <v>6590.354</v>
+        <v>6560.77</v>
       </c>
       <c r="I1033" t="n">
         <v>0.0</v>
@@ -38755,7 +38755,7 @@
         </is>
       </c>
       <c r="E1046" t="n">
-        <v>21.568</v>
+        <v>10.185</v>
       </c>
       <c r="F1046" t="n">
         <v>0.0</v>
@@ -38764,7 +38764,7 @@
         <v>694.956</v>
       </c>
       <c r="H1046" t="n">
-        <v>21.568</v>
+        <v>10.185</v>
       </c>
       <c r="I1046" t="n">
         <v>0.0</v>
@@ -38792,7 +38792,7 @@
         </is>
       </c>
       <c r="E1047" t="n">
-        <v>486.925</v>
+        <v>443.079</v>
       </c>
       <c r="F1047" t="n">
         <v>0.0</v>
@@ -38801,7 +38801,7 @@
         <v>23.077</v>
       </c>
       <c r="H1047" t="n">
-        <v>486.925</v>
+        <v>443.079</v>
       </c>
       <c r="I1047" t="n">
         <v>0.0</v>
@@ -39088,7 +39088,7 @@
         </is>
       </c>
       <c r="E1055" t="n">
-        <v>1285.384</v>
+        <v>1285.383</v>
       </c>
       <c r="F1055" t="n">
         <v>0.0</v>
@@ -39097,7 +39097,7 @@
         <v>0.0</v>
       </c>
       <c r="H1055" t="n">
-        <v>1285.384</v>
+        <v>1285.383</v>
       </c>
       <c r="I1055" t="n">
         <v>0.0</v>
@@ -39125,7 +39125,7 @@
         </is>
       </c>
       <c r="E1056" t="n">
-        <v>2073.17</v>
+        <v>1979.208</v>
       </c>
       <c r="F1056" t="n">
         <v>0.0</v>
@@ -39134,7 +39134,7 @@
         <v>75.97</v>
       </c>
       <c r="H1056" t="n">
-        <v>2073.17</v>
+        <v>1979.208</v>
       </c>
       <c r="I1056" t="n">
         <v>0.0</v>
@@ -39162,7 +39162,7 @@
         </is>
       </c>
       <c r="E1057" t="n">
-        <v>5951.424</v>
+        <v>5684.543</v>
       </c>
       <c r="F1057" t="n">
         <v>0.0</v>
@@ -39171,7 +39171,7 @@
         <v>0.0</v>
       </c>
       <c r="H1057" t="n">
-        <v>5951.424</v>
+        <v>5684.543</v>
       </c>
       <c r="I1057" t="n">
         <v>0.0</v>
@@ -39310,7 +39310,7 @@
         </is>
       </c>
       <c r="E1061" t="n">
-        <v>3573.62</v>
+        <v>3573.619</v>
       </c>
       <c r="F1061" t="n">
         <v>0.0</v>
@@ -39319,7 +39319,7 @@
         <v>0.0</v>
       </c>
       <c r="H1061" t="n">
-        <v>3573.62</v>
+        <v>3573.619</v>
       </c>
       <c r="I1061" t="n">
         <v>0.0</v>
@@ -39347,7 +39347,7 @@
         </is>
       </c>
       <c r="E1062" t="n">
-        <v>4411.075</v>
+        <v>4353.456999999999</v>
       </c>
       <c r="F1062" t="n">
         <v>3.639</v>
@@ -39356,7 +39356,7 @@
         <v>0.0</v>
       </c>
       <c r="H1062" t="n">
-        <v>4411.075</v>
+        <v>4353.456999999999</v>
       </c>
       <c r="I1062" t="n">
         <v>0.0</v>
@@ -39384,7 +39384,7 @@
         </is>
       </c>
       <c r="E1063" t="n">
-        <v>5305.662</v>
+        <v>6764.295</v>
       </c>
       <c r="F1063" t="n">
         <v>4.852</v>
@@ -39393,10 +39393,10 @@
         <v>36.39</v>
       </c>
       <c r="H1063" t="n">
-        <v>5305.662</v>
+        <v>5134.023</v>
       </c>
       <c r="I1063" t="n">
-        <v>0.0</v>
+        <v>1630.272</v>
       </c>
     </row>
     <row r="1064">
@@ -39421,7 +39421,7 @@
         </is>
       </c>
       <c r="E1064" t="n">
-        <v>3383.779</v>
+        <v>3728.273</v>
       </c>
       <c r="F1064" t="n">
         <v>0.0</v>
@@ -39430,7 +39430,7 @@
         <v>47.608</v>
       </c>
       <c r="H1064" t="n">
-        <v>3383.779</v>
+        <v>3728.273</v>
       </c>
       <c r="I1064" t="n">
         <v>0.0</v>
@@ -39458,7 +39458,7 @@
         </is>
       </c>
       <c r="E1065" t="n">
-        <v>7585.15</v>
+        <v>7094.528</v>
       </c>
       <c r="F1065" t="n">
         <v>0.6589999999999999</v>
@@ -39467,7 +39467,7 @@
         <v>15.869000000000002</v>
       </c>
       <c r="H1065" t="n">
-        <v>7585.15</v>
+        <v>7094.528</v>
       </c>
       <c r="I1065" t="n">
         <v>0.0</v>
@@ -39495,7 +39495,7 @@
         </is>
       </c>
       <c r="E1066" t="n">
-        <v>4145.828</v>
+        <v>3979.864</v>
       </c>
       <c r="F1066" t="n">
         <v>0.0</v>
@@ -39504,7 +39504,7 @@
         <v>0.0</v>
       </c>
       <c r="H1066" t="n">
-        <v>4145.828</v>
+        <v>3979.864</v>
       </c>
       <c r="I1066" t="n">
         <v>0.0</v>
@@ -39532,7 +39532,7 @@
         </is>
       </c>
       <c r="E1067" t="n">
-        <v>16887.14</v>
+        <v>16637.532</v>
       </c>
       <c r="F1067" t="n">
         <v>3.634</v>
@@ -39541,7 +39541,7 @@
         <v>0.0</v>
       </c>
       <c r="H1067" t="n">
-        <v>16887.14</v>
+        <v>16637.532</v>
       </c>
       <c r="I1067" t="n">
         <v>0.0</v>
@@ -39569,7 +39569,7 @@
         </is>
       </c>
       <c r="E1068" t="n">
-        <v>19061.6622</v>
+        <v>19061.6632</v>
       </c>
       <c r="F1068" t="n">
         <v>4.667</v>
@@ -39578,7 +39578,7 @@
         <v>0.0</v>
       </c>
       <c r="H1068" t="n">
-        <v>11346.45</v>
+        <v>11346.451</v>
       </c>
       <c r="I1068" t="n">
         <v>7715.2122</v>
@@ -39606,7 +39606,7 @@
         </is>
       </c>
       <c r="E1069" t="n">
-        <v>8887.413</v>
+        <v>8867.247</v>
       </c>
       <c r="F1069" t="n">
         <v>0.32899999999999996</v>
@@ -39615,7 +39615,7 @@
         <v>3.967</v>
       </c>
       <c r="H1069" t="n">
-        <v>8887.413</v>
+        <v>8867.247</v>
       </c>
       <c r="I1069" t="n">
         <v>0.0</v>
@@ -39680,7 +39680,7 @@
         </is>
       </c>
       <c r="E1071" t="n">
-        <v>5823.345</v>
+        <v>5496.0419999999995</v>
       </c>
       <c r="F1071" t="n">
         <v>0.6589999999999999</v>
@@ -39689,7 +39689,7 @@
         <v>11.902</v>
       </c>
       <c r="H1071" t="n">
-        <v>5823.345</v>
+        <v>5496.0419999999995</v>
       </c>
       <c r="I1071" t="n">
         <v>0.0</v>
@@ -39717,7 +39717,7 @@
         </is>
       </c>
       <c r="E1072" t="n">
-        <v>42188.6286</v>
+        <v>34473.4174</v>
       </c>
       <c r="F1072" t="n">
         <v>0.0</v>
@@ -39726,10 +39726,10 @@
         <v>14.002</v>
       </c>
       <c r="H1072" t="n">
-        <v>19042.992</v>
+        <v>19042.993</v>
       </c>
       <c r="I1072" t="n">
-        <v>23145.636599999998</v>
+        <v>15430.4244</v>
       </c>
     </row>
     <row r="1073">
@@ -39754,7 +39754,7 @@
         </is>
       </c>
       <c r="E1073" t="n">
-        <v>13997.533</v>
+        <v>11663.833</v>
       </c>
       <c r="F1073" t="n">
         <v>0.0</v>
@@ -39766,7 +39766,7 @@
         <v>11663.833</v>
       </c>
       <c r="I1073" t="n">
-        <v>2333.7</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1074">
@@ -39791,7 +39791,7 @@
         </is>
       </c>
       <c r="E1074" t="n">
-        <v>27221.629999999997</v>
+        <v>26170.958</v>
       </c>
       <c r="F1074" t="n">
         <v>2.972</v>
@@ -39800,7 +39800,7 @@
         <v>3.967</v>
       </c>
       <c r="H1074" t="n">
-        <v>27221.629999999997</v>
+        <v>26170.958</v>
       </c>
       <c r="I1074" t="n">
         <v>0.0</v>
@@ -39828,7 +39828,7 @@
         </is>
       </c>
       <c r="E1075" t="n">
-        <v>19503.905</v>
+        <v>19082.707</v>
       </c>
       <c r="F1075" t="n">
         <v>1.984</v>
@@ -39837,7 +39837,7 @@
         <v>0.0</v>
       </c>
       <c r="H1075" t="n">
-        <v>19503.905</v>
+        <v>19082.707</v>
       </c>
       <c r="I1075" t="n">
         <v>0.0</v>
@@ -39976,7 +39976,7 @@
         </is>
       </c>
       <c r="E1079" t="n">
-        <v>530.299</v>
+        <v>482.284</v>
       </c>
       <c r="F1079" t="n">
         <v>1.067</v>
@@ -39985,7 +39985,7 @@
         <v>0.0</v>
       </c>
       <c r="H1079" t="n">
-        <v>530.299</v>
+        <v>482.284</v>
       </c>
       <c r="I1079" t="n">
         <v>0.0</v>
@@ -40013,7 +40013,7 @@
         </is>
       </c>
       <c r="E1080" t="n">
-        <v>1512.0</v>
+        <v>1488.0</v>
       </c>
       <c r="F1080" t="n">
         <v>0.0</v>
@@ -40022,7 +40022,7 @@
         <v>0.0</v>
       </c>
       <c r="H1080" t="n">
-        <v>1512.0</v>
+        <v>1488.0</v>
       </c>
       <c r="I1080" t="n">
         <v>0.0</v>
@@ -40457,7 +40457,7 @@
         </is>
       </c>
       <c r="E1092" t="n">
-        <v>2628.949</v>
+        <v>2628.948</v>
       </c>
       <c r="F1092" t="n">
         <v>0.0</v>
@@ -40466,7 +40466,7 @@
         <v>0.0</v>
       </c>
       <c r="H1092" t="n">
-        <v>2628.949</v>
+        <v>2628.948</v>
       </c>
       <c r="I1092" t="n">
         <v>0.0</v>
@@ -40494,7 +40494,7 @@
         </is>
       </c>
       <c r="E1093" t="n">
-        <v>3810.479</v>
+        <v>3810.476</v>
       </c>
       <c r="F1093" t="n">
         <v>0.0</v>
@@ -40503,7 +40503,7 @@
         <v>0.0</v>
       </c>
       <c r="H1093" t="n">
-        <v>3810.479</v>
+        <v>3810.476</v>
       </c>
       <c r="I1093" t="n">
         <v>0.0</v>
@@ -40531,7 +40531,7 @@
         </is>
       </c>
       <c r="E1094" t="n">
-        <v>6745.349</v>
+        <v>6729.345</v>
       </c>
       <c r="F1094" t="n">
         <v>0.0</v>
@@ -40540,7 +40540,7 @@
         <v>0.0</v>
       </c>
       <c r="H1094" t="n">
-        <v>6745.349</v>
+        <v>6729.345</v>
       </c>
       <c r="I1094" t="n">
         <v>0.0</v>
@@ -40827,7 +40827,7 @@
         </is>
       </c>
       <c r="E1102" t="n">
-        <v>6597.978</v>
+        <v>6508.362</v>
       </c>
       <c r="F1102" t="n">
         <v>0.0</v>
@@ -40836,7 +40836,7 @@
         <v>0.0</v>
       </c>
       <c r="H1102" t="n">
-        <v>6597.978</v>
+        <v>6508.362</v>
       </c>
       <c r="I1102" t="n">
         <v>0.0</v>
@@ -41493,7 +41493,7 @@
         </is>
       </c>
       <c r="E1120" t="n">
-        <v>104.724</v>
+        <v>92.44</v>
       </c>
       <c r="F1120" t="n">
         <v>0.20900000000000002</v>
@@ -41502,7 +41502,7 @@
         <v>0.0</v>
       </c>
       <c r="H1120" t="n">
-        <v>104.724</v>
+        <v>92.44</v>
       </c>
       <c r="I1120" t="n">
         <v>0.0</v>
@@ -41530,7 +41530,7 @@
         </is>
       </c>
       <c r="E1121" t="n">
-        <v>2834.299</v>
+        <v>2814.205</v>
       </c>
       <c r="F1121" t="n">
         <v>0.42000000000000004</v>
@@ -41539,7 +41539,7 @@
         <v>0.0</v>
       </c>
       <c r="H1121" t="n">
-        <v>2834.299</v>
+        <v>2814.205</v>
       </c>
       <c r="I1121" t="n">
         <v>0.0</v>
@@ -41604,7 +41604,7 @@
         </is>
       </c>
       <c r="E1123" t="n">
-        <v>290.025</v>
+        <v>271.913</v>
       </c>
       <c r="F1123" t="n">
         <v>0.416</v>
@@ -41613,7 +41613,7 @@
         <v>0.0</v>
       </c>
       <c r="H1123" t="n">
-        <v>290.025</v>
+        <v>271.913</v>
       </c>
       <c r="I1123" t="n">
         <v>0.0</v>
@@ -41678,7 +41678,7 @@
         </is>
       </c>
       <c r="E1125" t="n">
-        <v>5764.517</v>
+        <v>5720.519</v>
       </c>
       <c r="F1125" t="n">
         <v>0.0</v>
@@ -41687,7 +41687,7 @@
         <v>0.0</v>
       </c>
       <c r="H1125" t="n">
-        <v>5764.517</v>
+        <v>5720.519</v>
       </c>
       <c r="I1125" t="n">
         <v>0.0</v>
@@ -41715,7 +41715,7 @@
         </is>
       </c>
       <c r="E1126" t="n">
-        <v>1148.092</v>
+        <v>817.658</v>
       </c>
       <c r="F1126" t="n">
         <v>0.0</v>
@@ -41724,7 +41724,7 @@
         <v>0.0</v>
       </c>
       <c r="H1126" t="n">
-        <v>1148.092</v>
+        <v>817.658</v>
       </c>
       <c r="I1126" t="n">
         <v>0.0</v>
@@ -41752,7 +41752,7 @@
         </is>
       </c>
       <c r="E1127" t="n">
-        <v>4188.609</v>
+        <v>4179.81</v>
       </c>
       <c r="F1127" t="n">
         <v>0.0</v>
@@ -41761,7 +41761,7 @@
         <v>0.0</v>
       </c>
       <c r="H1127" t="n">
-        <v>4188.609</v>
+        <v>4179.81</v>
       </c>
       <c r="I1127" t="n">
         <v>0.0</v>
@@ -41789,7 +41789,7 @@
         </is>
       </c>
       <c r="E1128" t="n">
-        <v>6864.622</v>
+        <v>6864.624</v>
       </c>
       <c r="F1128" t="n">
         <v>0.0</v>
@@ -41798,7 +41798,7 @@
         <v>0.0</v>
       </c>
       <c r="H1128" t="n">
-        <v>6864.622</v>
+        <v>6864.624</v>
       </c>
       <c r="I1128" t="n">
         <v>0.0</v>
@@ -41826,7 +41826,7 @@
         </is>
       </c>
       <c r="E1129" t="n">
-        <v>22624.0</v>
+        <v>22504.0</v>
       </c>
       <c r="F1129" t="n">
         <v>6.4</v>
@@ -41835,7 +41835,7 @@
         <v>0.0</v>
       </c>
       <c r="H1129" t="n">
-        <v>22624.0</v>
+        <v>22504.0</v>
       </c>
       <c r="I1129" t="n">
         <v>0.0</v>
@@ -41863,7 +41863,7 @@
         </is>
       </c>
       <c r="E1130" t="n">
-        <v>1513.532</v>
+        <v>1451.935</v>
       </c>
       <c r="F1130" t="n">
         <v>0.0</v>
@@ -41872,7 +41872,7 @@
         <v>17.599</v>
       </c>
       <c r="H1130" t="n">
-        <v>1513.532</v>
+        <v>1451.935</v>
       </c>
       <c r="I1130" t="n">
         <v>0.0</v>
@@ -41900,7 +41900,7 @@
         </is>
       </c>
       <c r="E1131" t="n">
-        <v>1473.177</v>
+        <v>1463.169</v>
       </c>
       <c r="F1131" t="n">
         <v>0.0</v>
@@ -41909,7 +41909,7 @@
         <v>8.005999999999998</v>
       </c>
       <c r="H1131" t="n">
-        <v>1473.177</v>
+        <v>1463.169</v>
       </c>
       <c r="I1131" t="n">
         <v>0.0</v>
@@ -41974,7 +41974,7 @@
         </is>
       </c>
       <c r="E1133" t="n">
-        <v>1517.214</v>
+        <v>1481.185</v>
       </c>
       <c r="F1133" t="n">
         <v>0.0</v>
@@ -41983,7 +41983,7 @@
         <v>0.0</v>
       </c>
       <c r="H1133" t="n">
-        <v>1517.214</v>
+        <v>1481.185</v>
       </c>
       <c r="I1133" t="n">
         <v>0.0</v>
@@ -42307,7 +42307,7 @@
         </is>
       </c>
       <c r="E1142" t="n">
-        <v>924.146</v>
+        <v>922.279</v>
       </c>
       <c r="F1142" t="n">
         <v>0.0</v>
@@ -42316,7 +42316,7 @@
         <v>0.0</v>
       </c>
       <c r="H1142" t="n">
-        <v>924.146</v>
+        <v>922.279</v>
       </c>
       <c r="I1142" t="n">
         <v>0.0</v>
@@ -42344,7 +42344,7 @@
         </is>
       </c>
       <c r="E1143" t="n">
-        <v>1474.8990000000001</v>
+        <v>1473.9650000000001</v>
       </c>
       <c r="F1143" t="n">
         <v>0.0</v>
@@ -42353,7 +42353,7 @@
         <v>0.0</v>
       </c>
       <c r="H1143" t="n">
-        <v>1474.8990000000001</v>
+        <v>1473.9650000000001</v>
       </c>
       <c r="I1143" t="n">
         <v>0.0</v>
@@ -42381,7 +42381,7 @@
         </is>
       </c>
       <c r="E1144" t="n">
-        <v>4323.4185</v>
+        <v>3869.474</v>
       </c>
       <c r="F1144" t="n">
         <v>0.428</v>
@@ -42390,10 +42390,10 @@
         <v>0.0</v>
       </c>
       <c r="H1144" t="n">
-        <v>3882.7329999999997</v>
+        <v>3869.474</v>
       </c>
       <c r="I1144" t="n">
-        <v>440.6855</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1145">
@@ -42418,7 +42418,7 @@
         </is>
       </c>
       <c r="E1145" t="n">
-        <v>995.1750000000001</v>
+        <v>981.058</v>
       </c>
       <c r="F1145" t="n">
         <v>0.428</v>
@@ -42427,7 +42427,7 @@
         <v>0.0</v>
       </c>
       <c r="H1145" t="n">
-        <v>995.1750000000001</v>
+        <v>981.058</v>
       </c>
       <c r="I1145" t="n">
         <v>0.0</v>
@@ -42529,7 +42529,7 @@
         </is>
       </c>
       <c r="E1148" t="n">
-        <v>2577.703</v>
+        <v>2631.846</v>
       </c>
       <c r="F1148" t="n">
         <v>10.265</v>
@@ -42538,7 +42538,7 @@
         <v>0.0</v>
       </c>
       <c r="H1148" t="n">
-        <v>2577.703</v>
+        <v>2631.846</v>
       </c>
       <c r="I1148" t="n">
         <v>0.0</v>
@@ -42640,7 +42640,7 @@
         </is>
       </c>
       <c r="E1151" t="n">
-        <v>9242.704</v>
+        <v>8585.6615</v>
       </c>
       <c r="F1151" t="n">
         <v>39.898999999999994</v>
@@ -42649,10 +42649,10 @@
         <v>13.766</v>
       </c>
       <c r="H1151" t="n">
-        <v>9242.704</v>
+        <v>8506.331</v>
       </c>
       <c r="I1151" t="n">
-        <v>0.0</v>
+        <v>79.3305</v>
       </c>
     </row>
     <row r="1152">
@@ -42677,7 +42677,7 @@
         </is>
       </c>
       <c r="E1152" t="n">
-        <v>430.559</v>
+        <v>515.871</v>
       </c>
       <c r="F1152" t="n">
         <v>0.0</v>
@@ -42689,7 +42689,7 @@
         <v>430.559</v>
       </c>
       <c r="I1152" t="n">
-        <v>0.0</v>
+        <v>85.312</v>
       </c>
     </row>
     <row r="1153">
@@ -42714,7 +42714,7 @@
         </is>
       </c>
       <c r="E1153" t="n">
-        <v>8445.415</v>
+        <v>8227.686</v>
       </c>
       <c r="F1153" t="n">
         <v>27.599</v>
@@ -42723,7 +42723,7 @@
         <v>7.155</v>
       </c>
       <c r="H1153" t="n">
-        <v>8445.415</v>
+        <v>8227.686</v>
       </c>
       <c r="I1153" t="n">
         <v>0.0</v>
@@ -42751,7 +42751,7 @@
         </is>
       </c>
       <c r="E1154" t="n">
-        <v>14149.2148</v>
+        <v>14749.9084</v>
       </c>
       <c r="F1154" t="n">
         <v>20.001</v>
@@ -42760,10 +42760,10 @@
         <v>2994.8160000000003</v>
       </c>
       <c r="H1154" t="n">
-        <v>13159.832</v>
+        <v>11695.089</v>
       </c>
       <c r="I1154" t="n">
-        <v>989.3828</v>
+        <v>3054.8194000000003</v>
       </c>
     </row>
     <row r="1155">
@@ -42788,7 +42788,7 @@
         </is>
       </c>
       <c r="E1155" t="n">
-        <v>15999.6</v>
+        <v>14258.8</v>
       </c>
       <c r="F1155" t="n">
         <v>48.0</v>
@@ -42797,10 +42797,10 @@
         <v>16.8</v>
       </c>
       <c r="H1155" t="n">
-        <v>15999.6</v>
+        <v>13746.0</v>
       </c>
       <c r="I1155" t="n">
-        <v>0.0</v>
+        <v>512.8</v>
       </c>
     </row>
     <row r="1156">
@@ -42862,7 +42862,7 @@
         </is>
       </c>
       <c r="E1157" t="n">
-        <v>4545.849</v>
+        <v>4333.063</v>
       </c>
       <c r="F1157" t="n">
         <v>8.0</v>
@@ -42871,7 +42871,7 @@
         <v>0.0</v>
       </c>
       <c r="H1157" t="n">
-        <v>4545.849</v>
+        <v>4333.063</v>
       </c>
       <c r="I1157" t="n">
         <v>0.0</v>
@@ -42899,7 +42899,7 @@
         </is>
       </c>
       <c r="E1158" t="n">
-        <v>3662.4</v>
+        <v>3657.6</v>
       </c>
       <c r="F1158" t="n">
         <v>0.0</v>
@@ -42908,7 +42908,7 @@
         <v>0.0</v>
       </c>
       <c r="H1158" t="n">
-        <v>3662.4</v>
+        <v>3657.6</v>
       </c>
       <c r="I1158" t="n">
         <v>0.0</v>
@@ -42936,7 +42936,7 @@
         </is>
       </c>
       <c r="E1159" t="n">
-        <v>1344.0</v>
+        <v>1320.0</v>
       </c>
       <c r="F1159" t="n">
         <v>0.4</v>
@@ -42945,7 +42945,7 @@
         <v>0.0</v>
       </c>
       <c r="H1159" t="n">
-        <v>1344.0</v>
+        <v>1320.0</v>
       </c>
       <c r="I1159" t="n">
         <v>0.0</v>
@@ -42973,7 +42973,7 @@
         </is>
       </c>
       <c r="E1160" t="n">
-        <v>4357.112</v>
+        <v>4351.5109999999995</v>
       </c>
       <c r="F1160" t="n">
         <v>0.0</v>
@@ -42982,7 +42982,7 @@
         <v>0.0</v>
       </c>
       <c r="H1160" t="n">
-        <v>4357.112</v>
+        <v>4351.5109999999995</v>
       </c>
       <c r="I1160" t="n">
         <v>0.0</v>
@@ -43010,7 +43010,7 @@
         </is>
       </c>
       <c r="E1161" t="n">
-        <v>581.016</v>
+        <v>459.506</v>
       </c>
       <c r="F1161" t="n">
         <v>0.428</v>
@@ -43019,7 +43019,7 @@
         <v>0.0</v>
       </c>
       <c r="H1161" t="n">
-        <v>581.016</v>
+        <v>459.506</v>
       </c>
       <c r="I1161" t="n">
         <v>0.0</v>
@@ -43158,7 +43158,7 @@
         </is>
       </c>
       <c r="E1165" t="n">
-        <v>6307.2</v>
+        <v>5763.200000000001</v>
       </c>
       <c r="F1165" t="n">
         <v>0.0</v>
@@ -43167,7 +43167,7 @@
         <v>4.0</v>
       </c>
       <c r="H1165" t="n">
-        <v>6307.2</v>
+        <v>5763.200000000001</v>
       </c>
       <c r="I1165" t="n">
         <v>0.0</v>
@@ -43195,7 +43195,7 @@
         </is>
       </c>
       <c r="E1166" t="n">
-        <v>7142.685</v>
+        <v>6547.651000000001</v>
       </c>
       <c r="F1166" t="n">
         <v>0.0</v>
@@ -43204,7 +43204,7 @@
         <v>5.1000000000000005</v>
       </c>
       <c r="H1166" t="n">
-        <v>7142.685</v>
+        <v>6547.651000000001</v>
       </c>
       <c r="I1166" t="n">
         <v>0.0</v>
@@ -43232,7 +43232,7 @@
         </is>
       </c>
       <c r="E1167" t="n">
-        <v>10762.204</v>
+        <v>9318.132</v>
       </c>
       <c r="F1167" t="n">
         <v>0.0</v>
@@ -43241,7 +43241,7 @@
         <v>20.668</v>
       </c>
       <c r="H1167" t="n">
-        <v>10762.204</v>
+        <v>9318.132</v>
       </c>
       <c r="I1167" t="n">
         <v>0.0</v>
@@ -43417,7 +43417,7 @@
         </is>
       </c>
       <c r="E1172" t="n">
-        <v>7302.599999999999</v>
+        <v>7301.799999999999</v>
       </c>
       <c r="F1172" t="n">
         <v>0.6</v>
@@ -43426,7 +43426,7 @@
         <v>339.2</v>
       </c>
       <c r="H1172" t="n">
-        <v>7302.599999999999</v>
+        <v>7301.799999999999</v>
       </c>
       <c r="I1172" t="n">
         <v>0.0</v>
@@ -43713,7 +43713,7 @@
         </is>
       </c>
       <c r="E1180" t="n">
-        <v>680.4</v>
+        <v>666.0</v>
       </c>
       <c r="F1180" t="n">
         <v>0.0</v>
@@ -43722,7 +43722,7 @@
         <v>0.0</v>
       </c>
       <c r="H1180" t="n">
-        <v>680.4</v>
+        <v>666.0</v>
       </c>
       <c r="I1180" t="n">
         <v>0.0</v>
@@ -43750,7 +43750,7 @@
         </is>
       </c>
       <c r="E1181" t="n">
-        <v>1966.3999999999999</v>
+        <v>1966.1999999999998</v>
       </c>
       <c r="F1181" t="n">
         <v>0.0</v>
@@ -43759,7 +43759,7 @@
         <v>4.8</v>
       </c>
       <c r="H1181" t="n">
-        <v>1966.3999999999999</v>
+        <v>1966.1999999999998</v>
       </c>
       <c r="I1181" t="n">
         <v>0.0</v>
@@ -43787,7 +43787,7 @@
         </is>
       </c>
       <c r="E1182" t="n">
-        <v>2211.8</v>
+        <v>2210.8</v>
       </c>
       <c r="F1182" t="n">
         <v>0.4</v>
@@ -43796,7 +43796,7 @@
         <v>0.0</v>
       </c>
       <c r="H1182" t="n">
-        <v>2211.8</v>
+        <v>2210.8</v>
       </c>
       <c r="I1182" t="n">
         <v>0.0</v>
@@ -43861,7 +43861,7 @@
         </is>
       </c>
       <c r="E1184" t="n">
-        <v>2351.2</v>
+        <v>2257.2000000000003</v>
       </c>
       <c r="F1184" t="n">
         <v>8.4</v>
@@ -43870,7 +43870,7 @@
         <v>0.0</v>
       </c>
       <c r="H1184" t="n">
-        <v>2351.2</v>
+        <v>2257.2000000000003</v>
       </c>
       <c r="I1184" t="n">
         <v>0.0</v>
@@ -43898,7 +43898,7 @@
         </is>
       </c>
       <c r="E1185" t="n">
-        <v>2344.294</v>
+        <v>2344.293</v>
       </c>
       <c r="F1185" t="n">
         <v>0.26699999999999996</v>
@@ -43907,7 +43907,7 @@
         <v>3.2</v>
       </c>
       <c r="H1185" t="n">
-        <v>2344.294</v>
+        <v>2344.293</v>
       </c>
       <c r="I1185" t="n">
         <v>0.0</v>
@@ -43935,7 +43935,7 @@
         </is>
       </c>
       <c r="E1186" t="n">
-        <v>1917.6000000000001</v>
+        <v>1888.8000000000002</v>
       </c>
       <c r="F1186" t="n">
         <v>0.0</v>
@@ -43944,7 +43944,7 @@
         <v>0.0</v>
       </c>
       <c r="H1186" t="n">
-        <v>1917.6000000000001</v>
+        <v>1888.8000000000002</v>
       </c>
       <c r="I1186" t="n">
         <v>0.0</v>
@@ -43972,7 +43972,7 @@
         </is>
       </c>
       <c r="E1187" t="n">
-        <v>649.649</v>
+        <v>649.646</v>
       </c>
       <c r="F1187" t="n">
         <v>0.0</v>
@@ -43981,7 +43981,7 @@
         <v>0.0</v>
       </c>
       <c r="H1187" t="n">
-        <v>649.649</v>
+        <v>649.646</v>
       </c>
       <c r="I1187" t="n">
         <v>0.0</v>
@@ -44009,7 +44009,7 @@
         </is>
       </c>
       <c r="E1188" t="n">
-        <v>2689.396</v>
+        <v>2689.398</v>
       </c>
       <c r="F1188" t="n">
         <v>0.6669999999999999</v>
@@ -44018,7 +44018,7 @@
         <v>0.0</v>
       </c>
       <c r="H1188" t="n">
-        <v>2689.396</v>
+        <v>2689.398</v>
       </c>
       <c r="I1188" t="n">
         <v>0.0</v>
@@ -44046,7 +44046,7 @@
         </is>
       </c>
       <c r="E1189" t="n">
-        <v>1745.6</v>
+        <v>1729.6</v>
       </c>
       <c r="F1189" t="n">
         <v>2.8</v>
@@ -44055,7 +44055,7 @@
         <v>0.8</v>
       </c>
       <c r="H1189" t="n">
-        <v>1745.6</v>
+        <v>1729.6</v>
       </c>
       <c r="I1189" t="n">
         <v>0.0</v>
@@ -44083,7 +44083,7 @@
         </is>
       </c>
       <c r="E1190" t="n">
-        <v>1908.0</v>
+        <v>1888.8</v>
       </c>
       <c r="F1190" t="n">
         <v>0.0</v>
@@ -44092,7 +44092,7 @@
         <v>0.0</v>
       </c>
       <c r="H1190" t="n">
-        <v>1908.0</v>
+        <v>1888.8</v>
       </c>
       <c r="I1190" t="n">
         <v>0.0</v>
@@ -44120,7 +44120,7 @@
         </is>
       </c>
       <c r="E1191" t="n">
-        <v>816.082</v>
+        <v>492.05</v>
       </c>
       <c r="F1191" t="n">
         <v>0.0</v>
@@ -44129,7 +44129,7 @@
         <v>708.071</v>
       </c>
       <c r="H1191" t="n">
-        <v>816.082</v>
+        <v>492.05</v>
       </c>
       <c r="I1191" t="n">
         <v>0.0</v>
@@ -44157,7 +44157,7 @@
         </is>
       </c>
       <c r="E1192" t="n">
-        <v>0.0</v>
+        <v>2500.8</v>
       </c>
       <c r="F1192" t="n">
         <v>0.0</v>
@@ -44169,7 +44169,7 @@
         <v>0.0</v>
       </c>
       <c r="I1192" t="n">
-        <v>0.0</v>
+        <v>2500.8</v>
       </c>
     </row>
     <row r="1193">
@@ -44897,7 +44897,7 @@
         </is>
       </c>
       <c r="E1212" t="n">
-        <v>1848.302</v>
+        <v>1871.7341999999999</v>
       </c>
       <c r="F1212" t="n">
         <v>0.0</v>
@@ -44909,7 +44909,7 @@
         <v>1848.302</v>
       </c>
       <c r="I1212" t="n">
-        <v>0.0</v>
+        <v>23.4322</v>
       </c>
     </row>
     <row r="1213">
@@ -44934,7 +44934,7 @@
         </is>
       </c>
       <c r="E1213" t="n">
-        <v>2525.23</v>
+        <v>2507.9500000000003</v>
       </c>
       <c r="F1213" t="n">
         <v>0.0</v>
@@ -44943,7 +44943,7 @@
         <v>636.93</v>
       </c>
       <c r="H1213" t="n">
-        <v>2525.23</v>
+        <v>2507.9500000000003</v>
       </c>
       <c r="I1213" t="n">
         <v>0.0</v>
@@ -44971,7 +44971,7 @@
         </is>
       </c>
       <c r="E1214" t="n">
-        <v>140.598</v>
+        <v>2581.334</v>
       </c>
       <c r="F1214" t="n">
         <v>0.0</v>
@@ -44980,10 +44980,10 @@
         <v>4.26</v>
       </c>
       <c r="H1214" t="n">
-        <v>140.598</v>
+        <v>25.094</v>
       </c>
       <c r="I1214" t="n">
-        <v>0.0</v>
+        <v>2556.24</v>
       </c>
     </row>
     <row r="1215">
@@ -45156,7 +45156,7 @@
         </is>
       </c>
       <c r="E1219" t="n">
-        <v>3670.019</v>
+        <v>3371.795</v>
       </c>
       <c r="F1219" t="n">
         <v>0.0</v>
@@ -45165,7 +45165,7 @@
         <v>0.0</v>
       </c>
       <c r="H1219" t="n">
-        <v>3670.019</v>
+        <v>3371.795</v>
       </c>
       <c r="I1219" t="n">
         <v>0.0</v>
@@ -45378,7 +45378,7 @@
         </is>
       </c>
       <c r="E1225" t="n">
-        <v>1033.109</v>
+        <v>1002.339</v>
       </c>
       <c r="F1225" t="n">
         <v>0.0</v>
@@ -45387,7 +45387,7 @@
         <v>0.0</v>
       </c>
       <c r="H1225" t="n">
-        <v>1033.109</v>
+        <v>1002.339</v>
       </c>
       <c r="I1225" t="n">
         <v>0.0</v>
@@ -45415,7 +45415,7 @@
         </is>
       </c>
       <c r="E1226" t="n">
-        <v>1993.4389999999999</v>
+        <v>1999.8010000000002</v>
       </c>
       <c r="F1226" t="n">
         <v>0.0</v>
@@ -45424,7 +45424,7 @@
         <v>1.7750000000000001</v>
       </c>
       <c r="H1226" t="n">
-        <v>1993.4389999999999</v>
+        <v>1999.8010000000002</v>
       </c>
       <c r="I1226" t="n">
         <v>0.0</v>
@@ -45452,7 +45452,7 @@
         </is>
       </c>
       <c r="E1227" t="n">
-        <v>5349.249</v>
+        <v>5441.5572999999995</v>
       </c>
       <c r="F1227" t="n">
         <v>0.0</v>
@@ -45461,10 +45461,10 @@
         <v>0.0</v>
       </c>
       <c r="H1227" t="n">
-        <v>5349.249</v>
+        <v>5328.48</v>
       </c>
       <c r="I1227" t="n">
-        <v>0.0</v>
+        <v>113.0773</v>
       </c>
     </row>
     <row r="1228">
@@ -45526,7 +45526,7 @@
         </is>
       </c>
       <c r="E1229" t="n">
-        <v>2380.424</v>
+        <v>2174.7329999999997</v>
       </c>
       <c r="F1229" t="n">
         <v>0.0</v>
@@ -45535,10 +45535,10 @@
         <v>5.991</v>
       </c>
       <c r="H1229" t="n">
-        <v>2380.424</v>
+        <v>2120.814</v>
       </c>
       <c r="I1229" t="n">
-        <v>0.0</v>
+        <v>53.919</v>
       </c>
     </row>
     <row r="1230">
@@ -45563,7 +45563,7 @@
         </is>
       </c>
       <c r="E1230" t="n">
-        <v>3017.67</v>
+        <v>3342.2177</v>
       </c>
       <c r="F1230" t="n">
         <v>1.7750000000000001</v>
@@ -45572,10 +45572,10 @@
         <v>3.5500000000000003</v>
       </c>
       <c r="H1230" t="n">
-        <v>3017.67</v>
+        <v>2459.993</v>
       </c>
       <c r="I1230" t="n">
-        <v>0.0</v>
+        <v>882.2247</v>
       </c>
     </row>
     <row r="1231">
@@ -45600,7 +45600,7 @@
         </is>
       </c>
       <c r="E1231" t="n">
-        <v>3299.32</v>
+        <v>3272.101</v>
       </c>
       <c r="F1231" t="n">
         <v>0.0</v>
@@ -45609,7 +45609,7 @@
         <v>0.0</v>
       </c>
       <c r="H1231" t="n">
-        <v>3299.32</v>
+        <v>3272.101</v>
       </c>
       <c r="I1231" t="n">
         <v>0.0</v>
@@ -45711,7 +45711,7 @@
         </is>
       </c>
       <c r="E1234" t="n">
-        <v>2037.234</v>
+        <v>4254.598</v>
       </c>
       <c r="F1234" t="n">
         <v>3.639</v>
@@ -45723,7 +45723,7 @@
         <v>2037.234</v>
       </c>
       <c r="I1234" t="n">
-        <v>0.0</v>
+        <v>2217.364</v>
       </c>
     </row>
     <row r="1235">
@@ -45748,7 +45748,7 @@
         </is>
       </c>
       <c r="E1235" t="n">
-        <v>1077.4859999999999</v>
+        <v>1075.711</v>
       </c>
       <c r="F1235" t="n">
         <v>1.479</v>
@@ -45757,7 +45757,7 @@
         <v>3.5500000000000003</v>
       </c>
       <c r="H1235" t="n">
-        <v>1077.4859999999999</v>
+        <v>1075.711</v>
       </c>
       <c r="I1235" t="n">
         <v>0.0</v>
@@ -45785,7 +45785,7 @@
         </is>
       </c>
       <c r="E1236" t="n">
-        <v>3696.94</v>
+        <v>3557.3</v>
       </c>
       <c r="F1236" t="n">
         <v>0.0</v>
@@ -45794,7 +45794,7 @@
         <v>0.0</v>
       </c>
       <c r="H1236" t="n">
-        <v>3696.94</v>
+        <v>3557.3</v>
       </c>
       <c r="I1236" t="n">
         <v>0.0</v>
@@ -45933,7 +45933,7 @@
         </is>
       </c>
       <c r="E1240" t="n">
-        <v>8044.642</v>
+        <v>9198.492</v>
       </c>
       <c r="F1240" t="n">
         <v>0.0</v>
@@ -45945,7 +45945,7 @@
         <v>8044.642</v>
       </c>
       <c r="I1240" t="n">
-        <v>0.0</v>
+        <v>1153.85</v>
       </c>
     </row>
     <row r="1241">
@@ -45970,7 +45970,7 @@
         </is>
       </c>
       <c r="E1241" t="n">
-        <v>1541.97</v>
+        <v>1540.787</v>
       </c>
       <c r="F1241" t="n">
         <v>0.0</v>
@@ -45979,7 +45979,7 @@
         <v>1.183</v>
       </c>
       <c r="H1241" t="n">
-        <v>1541.97</v>
+        <v>1540.787</v>
       </c>
       <c r="I1241" t="n">
         <v>0.0</v>
@@ -46118,7 +46118,7 @@
         </is>
       </c>
       <c r="E1245" t="n">
-        <v>410.7312</v>
+        <v>0.0</v>
       </c>
       <c r="F1245" t="n">
         <v>0.0</v>
@@ -46130,7 +46130,7 @@
         <v>0.0</v>
       </c>
       <c r="I1245" t="n">
-        <v>410.7312</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1246">
@@ -46155,7 +46155,7 @@
         </is>
       </c>
       <c r="E1246" t="n">
-        <v>2562.951</v>
+        <v>2517.5609999999997</v>
       </c>
       <c r="F1246" t="n">
         <v>0.583</v>
@@ -46164,7 +46164,7 @@
         <v>0.0</v>
       </c>
       <c r="H1246" t="n">
-        <v>2562.951</v>
+        <v>2517.5609999999997</v>
       </c>
       <c r="I1246" t="n">
         <v>0.0</v>
@@ -46192,7 +46192,7 @@
         </is>
       </c>
       <c r="E1247" t="n">
-        <v>1488.996</v>
+        <v>1471.376</v>
       </c>
       <c r="F1247" t="n">
         <v>0.35100000000000003</v>
@@ -46201,7 +46201,7 @@
         <v>0.0</v>
       </c>
       <c r="H1247" t="n">
-        <v>1488.996</v>
+        <v>1471.376</v>
       </c>
       <c r="I1247" t="n">
         <v>0.0</v>
@@ -46266,7 +46266,7 @@
         </is>
       </c>
       <c r="E1249" t="n">
-        <v>449.685</v>
+        <v>448.605</v>
       </c>
       <c r="F1249" t="n">
         <v>0.0</v>
@@ -46275,7 +46275,7 @@
         <v>0.135</v>
       </c>
       <c r="H1249" t="n">
-        <v>449.685</v>
+        <v>448.605</v>
       </c>
       <c r="I1249" t="n">
         <v>0.0</v>
@@ -46303,7 +46303,7 @@
         </is>
       </c>
       <c r="E1250" t="n">
-        <v>0.0</v>
+        <v>724.95</v>
       </c>
       <c r="F1250" t="n">
         <v>0.0</v>
@@ -46315,7 +46315,7 @@
         <v>0.0</v>
       </c>
       <c r="I1250" t="n">
-        <v>0.0</v>
+        <v>724.95</v>
       </c>
     </row>
     <row r="1251">
@@ -46414,7 +46414,7 @@
         </is>
       </c>
       <c r="E1253" t="n">
-        <v>1283.92</v>
+        <v>1276.88</v>
       </c>
       <c r="F1253" t="n">
         <v>0.0</v>
@@ -46423,7 +46423,7 @@
         <v>0.0</v>
       </c>
       <c r="H1253" t="n">
-        <v>1283.92</v>
+        <v>1276.88</v>
       </c>
       <c r="I1253" t="n">
         <v>0.0</v>
@@ -47413,7 +47413,7 @@
         </is>
       </c>
       <c r="E1280" t="n">
-        <v>605.817</v>
+        <v>579.13</v>
       </c>
       <c r="F1280" t="n">
         <v>0.0</v>
@@ -47422,7 +47422,7 @@
         <v>0.0</v>
       </c>
       <c r="H1280" t="n">
-        <v>605.817</v>
+        <v>579.13</v>
       </c>
       <c r="I1280" t="n">
         <v>0.0</v>
@@ -51298,7 +51298,7 @@
         </is>
       </c>
       <c r="E1385" t="n">
-        <v>3178.374</v>
+        <v>3171.702</v>
       </c>
       <c r="F1385" t="n">
         <v>0.0</v>
@@ -51307,7 +51307,7 @@
         <v>236.85600000000002</v>
       </c>
       <c r="H1385" t="n">
-        <v>3178.374</v>
+        <v>3171.702</v>
       </c>
       <c r="I1385" t="n">
         <v>0.0</v>
@@ -51335,7 +51335,7 @@
         </is>
       </c>
       <c r="E1386" t="n">
-        <v>513.045</v>
+        <v>505.047</v>
       </c>
       <c r="F1386" t="n">
         <v>0.0</v>
@@ -51344,7 +51344,7 @@
         <v>0.416</v>
       </c>
       <c r="H1386" t="n">
-        <v>513.045</v>
+        <v>505.047</v>
       </c>
       <c r="I1386" t="n">
         <v>0.0</v>
@@ -51372,7 +51372,7 @@
         </is>
       </c>
       <c r="E1387" t="n">
-        <v>617.492</v>
+        <v>617.493</v>
       </c>
       <c r="F1387" t="n">
         <v>0.0</v>
@@ -51381,7 +51381,7 @@
         <v>0.5559999999999999</v>
       </c>
       <c r="H1387" t="n">
-        <v>617.492</v>
+        <v>617.493</v>
       </c>
       <c r="I1387" t="n">
         <v>0.0</v>
@@ -51483,7 +51483,7 @@
         </is>
       </c>
       <c r="E1390" t="n">
-        <v>1056.105</v>
+        <v>1019.938</v>
       </c>
       <c r="F1390" t="n">
         <v>0.0</v>
@@ -51492,7 +51492,7 @@
         <v>0.0</v>
       </c>
       <c r="H1390" t="n">
-        <v>1056.105</v>
+        <v>1019.938</v>
       </c>
       <c r="I1390" t="n">
         <v>0.0</v>
@@ -52001,7 +52001,7 @@
         </is>
       </c>
       <c r="E1404" t="n">
-        <v>56.4</v>
+        <v>56.2</v>
       </c>
       <c r="F1404" t="n">
         <v>0.4</v>
@@ -52010,7 +52010,7 @@
         <v>0.0</v>
       </c>
       <c r="H1404" t="n">
-        <v>56.4</v>
+        <v>56.2</v>
       </c>
       <c r="I1404" t="n">
         <v>0.0</v>
@@ -52186,7 +52186,7 @@
         </is>
       </c>
       <c r="E1409" t="n">
-        <v>35.224</v>
+        <v>31.08</v>
       </c>
       <c r="F1409" t="n">
         <v>0.0</v>
@@ -52195,7 +52195,7 @@
         <v>0.0</v>
       </c>
       <c r="H1409" t="n">
-        <v>35.224</v>
+        <v>31.08</v>
       </c>
       <c r="I1409" t="n">
         <v>0.0</v>
@@ -52223,7 +52223,7 @@
         </is>
       </c>
       <c r="E1410" t="n">
-        <v>170.88</v>
+        <v>161.28</v>
       </c>
       <c r="F1410" t="n">
         <v>0.0</v>
@@ -52232,7 +52232,7 @@
         <v>0.0</v>
       </c>
       <c r="H1410" t="n">
-        <v>170.88</v>
+        <v>161.28</v>
       </c>
       <c r="I1410" t="n">
         <v>0.0</v>
@@ -52741,7 +52741,7 @@
         </is>
       </c>
       <c r="E1424" t="n">
-        <v>255.095</v>
+        <v>255.096</v>
       </c>
       <c r="F1424" t="n">
         <v>0.0</v>
@@ -52750,7 +52750,7 @@
         <v>0.0</v>
       </c>
       <c r="H1424" t="n">
-        <v>255.095</v>
+        <v>255.096</v>
       </c>
       <c r="I1424" t="n">
         <v>0.0</v>
@@ -53407,7 +53407,7 @@
         </is>
       </c>
       <c r="E1442" t="n">
-        <v>154.375</v>
+        <v>148.375</v>
       </c>
       <c r="F1442" t="n">
         <v>5.625</v>
@@ -53416,7 +53416,7 @@
         <v>70.5</v>
       </c>
       <c r="H1442" t="n">
-        <v>154.375</v>
+        <v>148.375</v>
       </c>
       <c r="I1442" t="n">
         <v>0.0</v>
@@ -53444,7 +53444,7 @@
         </is>
       </c>
       <c r="E1443" t="n">
-        <v>14.375</v>
+        <v>14.126</v>
       </c>
       <c r="F1443" t="n">
         <v>0.0</v>
@@ -53453,7 +53453,7 @@
         <v>33.75</v>
       </c>
       <c r="H1443" t="n">
-        <v>14.375</v>
+        <v>14.126</v>
       </c>
       <c r="I1443" t="n">
         <v>0.0</v>
@@ -53481,7 +53481,7 @@
         </is>
       </c>
       <c r="E1444" t="n">
-        <v>438.372</v>
+        <v>433.872</v>
       </c>
       <c r="F1444" t="n">
         <v>0.0</v>
@@ -53490,7 +53490,7 @@
         <v>40.5</v>
       </c>
       <c r="H1444" t="n">
-        <v>438.372</v>
+        <v>433.872</v>
       </c>
       <c r="I1444" t="n">
         <v>0.0</v>
@@ -53518,7 +53518,7 @@
         </is>
       </c>
       <c r="E1445" t="n">
-        <v>1221.879</v>
+        <v>1216.546</v>
       </c>
       <c r="F1445" t="n">
         <v>0.0</v>
@@ -53527,7 +53527,7 @@
         <v>10.666</v>
       </c>
       <c r="H1445" t="n">
-        <v>1221.879</v>
+        <v>1216.546</v>
       </c>
       <c r="I1445" t="n">
         <v>0.0</v>
@@ -53555,7 +53555,7 @@
         </is>
       </c>
       <c r="E1446" t="n">
-        <v>515.25</v>
+        <v>512.625</v>
       </c>
       <c r="F1446" t="n">
         <v>0.0</v>
@@ -53564,7 +53564,7 @@
         <v>20.625</v>
       </c>
       <c r="H1446" t="n">
-        <v>515.25</v>
+        <v>512.625</v>
       </c>
       <c r="I1446" t="n">
         <v>0.0</v>
@@ -53592,7 +53592,7 @@
         </is>
       </c>
       <c r="E1447" t="n">
-        <v>218.375</v>
+        <v>216.5</v>
       </c>
       <c r="F1447" t="n">
         <v>0.0</v>
@@ -53601,7 +53601,7 @@
         <v>6.75</v>
       </c>
       <c r="H1447" t="n">
-        <v>218.375</v>
+        <v>216.5</v>
       </c>
       <c r="I1447" t="n">
         <v>0.0</v>
@@ -53666,7 +53666,7 @@
         </is>
       </c>
       <c r="E1449" t="n">
-        <v>562.5</v>
+        <v>561.375</v>
       </c>
       <c r="F1449" t="n">
         <v>0.0</v>
@@ -53675,7 +53675,7 @@
         <v>38.25</v>
       </c>
       <c r="H1449" t="n">
-        <v>562.5</v>
+        <v>561.375</v>
       </c>
       <c r="I1449" t="n">
         <v>0.0</v>
@@ -53703,7 +53703,7 @@
         </is>
       </c>
       <c r="E1450" t="n">
-        <v>684.875</v>
+        <v>668.0</v>
       </c>
       <c r="F1450" t="n">
         <v>0.375</v>
@@ -53712,7 +53712,7 @@
         <v>3.75</v>
       </c>
       <c r="H1450" t="n">
-        <v>684.875</v>
+        <v>668.0</v>
       </c>
       <c r="I1450" t="n">
         <v>0.0</v>
@@ -53851,7 +53851,7 @@
         </is>
       </c>
       <c r="E1454" t="n">
-        <v>276.75</v>
+        <v>232.5</v>
       </c>
       <c r="F1454" t="n">
         <v>0.0</v>
@@ -53860,7 +53860,7 @@
         <v>55.5</v>
       </c>
       <c r="H1454" t="n">
-        <v>276.75</v>
+        <v>232.5</v>
       </c>
       <c r="I1454" t="n">
         <v>0.0</v>
@@ -53925,7 +53925,7 @@
         </is>
       </c>
       <c r="E1456" t="n">
-        <v>3205.5</v>
+        <v>3201.75</v>
       </c>
       <c r="F1456" t="n">
         <v>0.0</v>
@@ -53934,7 +53934,7 @@
         <v>37.5</v>
       </c>
       <c r="H1456" t="n">
-        <v>3205.5</v>
+        <v>3201.75</v>
       </c>
       <c r="I1456" t="n">
         <v>0.0</v>
@@ -54036,7 +54036,7 @@
         </is>
       </c>
       <c r="E1459" t="n">
-        <v>1086.868</v>
+        <v>1084.866</v>
       </c>
       <c r="F1459" t="n">
         <v>0.0</v>
@@ -54045,7 +54045,7 @@
         <v>0.5</v>
       </c>
       <c r="H1459" t="n">
-        <v>1086.868</v>
+        <v>1084.866</v>
       </c>
       <c r="I1459" t="n">
         <v>0.0</v>
@@ -54073,7 +54073,7 @@
         </is>
       </c>
       <c r="E1460" t="n">
-        <v>1984.139</v>
+        <v>1984.14</v>
       </c>
       <c r="F1460" t="n">
         <v>0.0</v>
@@ -54082,7 +54082,7 @@
         <v>11.342</v>
       </c>
       <c r="H1460" t="n">
-        <v>1984.139</v>
+        <v>1984.14</v>
       </c>
       <c r="I1460" t="n">
         <v>0.0</v>
@@ -54369,7 +54369,7 @@
         </is>
       </c>
       <c r="E1468" t="n">
-        <v>70.967</v>
+        <v>70.972</v>
       </c>
       <c r="F1468" t="n">
         <v>0.0</v>
@@ -54378,7 +54378,7 @@
         <v>0.0</v>
       </c>
       <c r="H1468" t="n">
-        <v>70.967</v>
+        <v>70.972</v>
       </c>
       <c r="I1468" t="n">
         <v>0.0</v>
@@ -54628,7 +54628,7 @@
         </is>
       </c>
       <c r="E1475" t="n">
-        <v>799.974</v>
+        <v>649.187</v>
       </c>
       <c r="F1475" t="n">
         <v>0.0</v>
@@ -54637,7 +54637,7 @@
         <v>0.0</v>
       </c>
       <c r="H1475" t="n">
-        <v>799.974</v>
+        <v>649.187</v>
       </c>
       <c r="I1475" t="n">
         <v>0.0</v>
@@ -54665,7 +54665,7 @@
         </is>
       </c>
       <c r="E1476" t="n">
-        <v>259.708</v>
+        <v>259.709</v>
       </c>
       <c r="F1476" t="n">
         <v>0.0</v>
@@ -54674,7 +54674,7 @@
         <v>0.0</v>
       </c>
       <c r="H1476" t="n">
-        <v>259.708</v>
+        <v>259.709</v>
       </c>
       <c r="I1476" t="n">
         <v>0.0</v>
@@ -54702,7 +54702,7 @@
         </is>
       </c>
       <c r="E1477" t="n">
-        <v>3859.088</v>
+        <v>3888.442</v>
       </c>
       <c r="F1477" t="n">
         <v>0.0</v>
@@ -54711,7 +54711,7 @@
         <v>939.418</v>
       </c>
       <c r="H1477" t="n">
-        <v>3859.088</v>
+        <v>3888.442</v>
       </c>
       <c r="I1477" t="n">
         <v>0.0</v>
@@ -54813,7 +54813,7 @@
         </is>
       </c>
       <c r="E1480" t="n">
-        <v>5780.373</v>
+        <v>5648.132</v>
       </c>
       <c r="F1480" t="n">
         <v>0.589</v>
@@ -54822,7 +54822,7 @@
         <v>661.475</v>
       </c>
       <c r="H1480" t="n">
-        <v>5780.373</v>
+        <v>5648.132</v>
       </c>
       <c r="I1480" t="n">
         <v>0.0</v>
@@ -54850,7 +54850,7 @@
         </is>
       </c>
       <c r="E1481" t="n">
-        <v>2285.701</v>
+        <v>2284.72</v>
       </c>
       <c r="F1481" t="n">
         <v>65.467</v>
@@ -54859,7 +54859,7 @@
         <v>121.834</v>
       </c>
       <c r="H1481" t="n">
-        <v>2285.701</v>
+        <v>2284.72</v>
       </c>
       <c r="I1481" t="n">
         <v>0.0</v>
@@ -55146,7 +55146,7 @@
         </is>
       </c>
       <c r="E1489" t="n">
-        <v>5401.2</v>
+        <v>5309.4</v>
       </c>
       <c r="F1489" t="n">
         <v>1.8</v>
@@ -55155,7 +55155,7 @@
         <v>0.0</v>
       </c>
       <c r="H1489" t="n">
-        <v>5401.2</v>
+        <v>5309.4</v>
       </c>
       <c r="I1489" t="n">
         <v>0.0</v>
@@ -55368,7 +55368,7 @@
         </is>
       </c>
       <c r="E1495" t="n">
-        <v>797.971</v>
+        <v>1331.731</v>
       </c>
       <c r="F1495" t="n">
         <v>0.0</v>
@@ -55377,7 +55377,7 @@
         <v>0.0</v>
       </c>
       <c r="H1495" t="n">
-        <v>797.971</v>
+        <v>1331.731</v>
       </c>
       <c r="I1495" t="n">
         <v>0.0</v>
@@ -55686,8 +55686,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100200F1D6FEFF3D544A41ED546B108247B" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9c48becc4e219a1276de5fa0fe58c65b">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="57147975-5687-4135-8263-39f5df548c17" xmlns:ns3="96d24a6b-8465-4498-bb54-acea15c87a74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="606254f618d9a057eb2f31c00a1c51f7" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100200F1D6FEFF3D544A41ED546B108247B" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="40a43f087754221fa183e12f61eae985">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="57147975-5687-4135-8263-39f5df548c17" xmlns:ns3="96d24a6b-8465-4498-bb54-acea15c87a74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="025949cc6f7c326f5f6f4d123f9252f7" ns2:_="" ns3:_="">
     <xsd:import namespace="57147975-5687-4135-8263-39f5df548c17"/>
     <xsd:import namespace="96d24a6b-8465-4498-bb54-acea15c87a74"/>
     <xsd:element name="properties">
@@ -55953,13 +55953,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5356196F-E527-43D5-9EF8-0930CB96C176}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E95F307-2FD2-4BF4-8CC5-6D7883B16A96}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9066649A-35DA-427E-99C6-2F85CE69878A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{694CC462-5F7B-4B6D-A720-A0944DBB8D4B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB50769C-B1B9-497E-98B2-73A992971096}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BDD87EE-622A-469B-9743-241E4BC1AB8C}"/>
 </file>
--- a/Inventory_KNIME.xlsx
+++ b/Inventory_KNIME.xlsx
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>869.5</v>
+        <v>863.5</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
@@ -691,7 +691,7 @@
         <v>0.5</v>
       </c>
       <c r="H17" t="n">
-        <v>869.5</v>
+        <v>863.5</v>
       </c>
       <c r="I17" t="n">
         <v>0.0</v>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1027.0</v>
+        <v>1024.0</v>
       </c>
       <c r="F19" t="n">
         <v>0.0</v>
@@ -765,7 +765,7 @@
         <v>3.0</v>
       </c>
       <c r="H19" t="n">
-        <v>1027.0</v>
+        <v>1024.0</v>
       </c>
       <c r="I19" t="n">
         <v>0.0</v>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>158.1</v>
+        <v>998.1</v>
       </c>
       <c r="F24" t="n">
         <v>0.1</v>
@@ -950,7 +950,7 @@
         <v>0.3</v>
       </c>
       <c r="H24" t="n">
-        <v>158.1</v>
+        <v>998.1</v>
       </c>
       <c r="I24" t="n">
         <v>0.0</v>
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3316.573</v>
+        <v>3280.653</v>
       </c>
       <c r="F34" t="n">
         <v>37.148</v>
@@ -1320,7 +1320,7 @@
         <v>5.292</v>
       </c>
       <c r="H34" t="n">
-        <v>3316.573</v>
+        <v>3280.653</v>
       </c>
       <c r="I34" t="n">
         <v>0.0</v>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1927.741</v>
+        <v>1869.838</v>
       </c>
       <c r="F35" t="n">
         <v>282.264</v>
@@ -1357,7 +1357,7 @@
         <v>216.545</v>
       </c>
       <c r="H35" t="n">
-        <v>1927.741</v>
+        <v>1869.838</v>
       </c>
       <c r="I35" t="n">
         <v>0.0</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1657.779</v>
+        <v>1635.89</v>
       </c>
       <c r="F39" t="n">
         <v>2118.334</v>
@@ -1505,7 +1505,7 @@
         <v>70.722</v>
       </c>
       <c r="H39" t="n">
-        <v>1657.779</v>
+        <v>1635.89</v>
       </c>
       <c r="I39" t="n">
         <v>0.0</v>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>905.4730000000001</v>
+        <v>906.881</v>
       </c>
       <c r="F40" t="n">
         <v>17.094</v>
@@ -1542,7 +1542,7 @@
         <v>25.329</v>
       </c>
       <c r="H40" t="n">
-        <v>905.4730000000001</v>
+        <v>906.881</v>
       </c>
       <c r="I40" t="n">
         <v>0.0</v>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1014.374</v>
+        <v>1007.96</v>
       </c>
       <c r="F42" t="n">
         <v>767.328</v>
@@ -1616,7 +1616,7 @@
         <v>337.75100000000003</v>
       </c>
       <c r="H42" t="n">
-        <v>1014.374</v>
+        <v>1007.96</v>
       </c>
       <c r="I42" t="n">
         <v>0.0</v>
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>8947.95</v>
+        <v>9739.95</v>
       </c>
       <c r="F43" t="n">
         <v>3.3</v>
@@ -1653,10 +1653,10 @@
         <v>409.2</v>
       </c>
       <c r="H43" t="n">
-        <v>8947.95</v>
+        <v>8815.95</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0</v>
+        <v>924.0</v>
       </c>
     </row>
     <row r="44">
@@ -2347,7 +2347,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>97.612</v>
+        <v>96.54599999999999</v>
       </c>
       <c r="F62" t="n">
         <v>3.734</v>
@@ -2356,7 +2356,7 @@
         <v>0.0</v>
       </c>
       <c r="H62" t="n">
-        <v>97.612</v>
+        <v>96.54599999999999</v>
       </c>
       <c r="I62" t="n">
         <v>0.0</v>
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3037.2</v>
+        <v>3023.7999999999997</v>
       </c>
       <c r="F65" t="n">
         <v>1.2</v>
@@ -2467,7 +2467,7 @@
         <v>0.0</v>
       </c>
       <c r="H65" t="n">
-        <v>3037.2</v>
+        <v>3023.7999999999997</v>
       </c>
       <c r="I65" t="n">
         <v>0.0</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1189.2160000000001</v>
+        <v>1167.612</v>
       </c>
       <c r="F66" t="n">
         <v>4.801</v>
@@ -2504,7 +2504,7 @@
         <v>17.069000000000003</v>
       </c>
       <c r="H66" t="n">
-        <v>1189.2160000000001</v>
+        <v>1167.612</v>
       </c>
       <c r="I66" t="n">
         <v>0.0</v>
@@ -2532,7 +2532,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>303.238</v>
+        <v>281.635</v>
       </c>
       <c r="F67" t="n">
         <v>0.0</v>
@@ -2541,7 +2541,7 @@
         <v>4.267</v>
       </c>
       <c r="H67" t="n">
-        <v>303.238</v>
+        <v>281.635</v>
       </c>
       <c r="I67" t="n">
         <v>0.0</v>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1510.9599999999998</v>
+        <v>1416.747</v>
       </c>
       <c r="F68" t="n">
         <v>5.777</v>
@@ -2578,7 +2578,7 @@
         <v>0.0</v>
       </c>
       <c r="H68" t="n">
-        <v>1510.9599999999998</v>
+        <v>1416.747</v>
       </c>
       <c r="I68" t="n">
         <v>0.0</v>
@@ -2606,7 +2606,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1261.758</v>
+        <v>1146.5439999999999</v>
       </c>
       <c r="F69" t="n">
         <v>0.0</v>
@@ -2615,7 +2615,7 @@
         <v>0.0</v>
       </c>
       <c r="H69" t="n">
-        <v>1261.758</v>
+        <v>1146.5439999999999</v>
       </c>
       <c r="I69" t="n">
         <v>0.0</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4773.129000000001</v>
+        <v>4761.661</v>
       </c>
       <c r="F70" t="n">
         <v>9.601</v>
@@ -2652,7 +2652,7 @@
         <v>17.069000000000003</v>
       </c>
       <c r="H70" t="n">
-        <v>4773.129000000001</v>
+        <v>4761.661</v>
       </c>
       <c r="I70" t="n">
         <v>0.0</v>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>326.44100000000003</v>
+        <v>326.17400000000004</v>
       </c>
       <c r="F71" t="n">
         <v>1.333</v>
@@ -2689,7 +2689,7 @@
         <v>0.0</v>
       </c>
       <c r="H71" t="n">
-        <v>326.44100000000003</v>
+        <v>326.17400000000004</v>
       </c>
       <c r="I71" t="n">
         <v>0.0</v>
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1090.538</v>
+        <v>1090.271</v>
       </c>
       <c r="F72" t="n">
         <v>50.94</v>
@@ -2726,7 +2726,7 @@
         <v>0.0</v>
       </c>
       <c r="H72" t="n">
-        <v>1090.538</v>
+        <v>1090.271</v>
       </c>
       <c r="I72" t="n">
         <v>0.0</v>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1244.0</v>
+        <v>554.0</v>
       </c>
       <c r="F96" t="n">
         <v>0.0</v>
@@ -3614,7 +3614,7 @@
         <v>0.0</v>
       </c>
       <c r="H96" t="n">
-        <v>1244.0</v>
+        <v>554.0</v>
       </c>
       <c r="I96" t="n">
         <v>0.0</v>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3638.574</v>
+        <v>3632.569</v>
       </c>
       <c r="F98" t="n">
         <v>1.251</v>
@@ -3688,7 +3688,7 @@
         <v>0.0</v>
       </c>
       <c r="H98" t="n">
-        <v>3638.574</v>
+        <v>3632.569</v>
       </c>
       <c r="I98" t="n">
         <v>0.0</v>
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>493.672</v>
+        <v>573.736</v>
       </c>
       <c r="F100" t="n">
         <v>0.0</v>
@@ -3762,7 +3762,7 @@
         <v>4.002999999999999</v>
       </c>
       <c r="H100" t="n">
-        <v>493.672</v>
+        <v>573.736</v>
       </c>
       <c r="I100" t="n">
         <v>0.0</v>
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>685.576</v>
+        <v>685.5759999999999</v>
       </c>
       <c r="F104" t="n">
         <v>0.0</v>
@@ -3910,7 +3910,7 @@
         <v>69.38900000000001</v>
       </c>
       <c r="H104" t="n">
-        <v>685.576</v>
+        <v>685.5759999999999</v>
       </c>
       <c r="I104" t="n">
         <v>0.0</v>
@@ -4049,7 +4049,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>429.01</v>
+        <v>621.163</v>
       </c>
       <c r="F108" t="n">
         <v>0.16699999999999998</v>
@@ -4058,7 +4058,7 @@
         <v>8.118</v>
       </c>
       <c r="H108" t="n">
-        <v>429.01</v>
+        <v>621.163</v>
       </c>
       <c r="I108" t="n">
         <v>0.0</v>
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>876.032</v>
+        <v>872.029</v>
       </c>
       <c r="F109" t="n">
         <v>0.0</v>
@@ -4095,7 +4095,7 @@
         <v>0.0</v>
       </c>
       <c r="H109" t="n">
-        <v>876.032</v>
+        <v>872.029</v>
       </c>
       <c r="I109" t="n">
         <v>0.0</v>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1158.08</v>
+        <v>1380.5600000000002</v>
       </c>
       <c r="F117" t="n">
         <v>0.36000000000000004</v>
@@ -4391,10 +4391,10 @@
         <v>25.44</v>
       </c>
       <c r="H117" t="n">
-        <v>1158.08</v>
+        <v>1360.4</v>
       </c>
       <c r="I117" t="n">
-        <v>0.0</v>
+        <v>20.16</v>
       </c>
     </row>
     <row r="118">
@@ -4419,7 +4419,7 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>990.452</v>
+        <v>957.377</v>
       </c>
       <c r="F118" t="n">
         <v>0.9</v>
@@ -4428,7 +4428,7 @@
         <v>56.025</v>
       </c>
       <c r="H118" t="n">
-        <v>990.452</v>
+        <v>957.377</v>
       </c>
       <c r="I118" t="n">
         <v>0.0</v>
@@ -4456,7 +4456,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4057.097</v>
+        <v>4046.552</v>
       </c>
       <c r="F119" t="n">
         <v>0.0</v>
@@ -4465,7 +4465,7 @@
         <v>74.92500000000001</v>
       </c>
       <c r="H119" t="n">
-        <v>4057.097</v>
+        <v>4046.552</v>
       </c>
       <c r="I119" t="n">
         <v>0.0</v>
@@ -4567,16 +4567,16 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>111.417</v>
+        <v>160.81199999999998</v>
       </c>
       <c r="F122" t="n">
         <v>0.0</v>
       </c>
       <c r="G122" t="n">
-        <v>106.005</v>
+        <v>52.725</v>
       </c>
       <c r="H122" t="n">
-        <v>111.417</v>
+        <v>160.81199999999998</v>
       </c>
       <c r="I122" t="n">
         <v>0.0</v>
@@ -4604,16 +4604,16 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>697.12</v>
+        <v>748.4399999999999</v>
       </c>
       <c r="F123" t="n">
         <v>0.0</v>
       </c>
       <c r="G123" t="n">
-        <v>75.39999999999999</v>
+        <v>26.919999999999998</v>
       </c>
       <c r="H123" t="n">
-        <v>697.12</v>
+        <v>748.4399999999999</v>
       </c>
       <c r="I123" t="n">
         <v>0.0</v>
@@ -4715,16 +4715,16 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1190.284</v>
+        <v>1187.615</v>
       </c>
       <c r="F126" t="n">
         <v>0.0</v>
       </c>
       <c r="G126" t="n">
-        <v>0.0</v>
+        <v>18.682000000000002</v>
       </c>
       <c r="H126" t="n">
-        <v>1190.284</v>
+        <v>1187.615</v>
       </c>
       <c r="I126" t="n">
         <v>0.0</v>
@@ -5683,7 +5683,7 @@
         <v>0.0</v>
       </c>
       <c r="G152" t="n">
-        <v>2692.291</v>
+        <v>4756.608</v>
       </c>
       <c r="H152" t="n">
         <v>7692.343</v>
@@ -5831,7 +5831,7 @@
         <v>0.0</v>
       </c>
       <c r="G156" t="n">
-        <v>21.6</v>
+        <v>24.8</v>
       </c>
       <c r="H156" t="n">
         <v>6827.2</v>
@@ -6861,7 +6861,7 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>2052.692</v>
+        <v>2038.69</v>
       </c>
       <c r="F184" t="n">
         <v>0.0</v>
@@ -6870,7 +6870,7 @@
         <v>4.201</v>
       </c>
       <c r="H184" t="n">
-        <v>2052.692</v>
+        <v>2038.69</v>
       </c>
       <c r="I184" t="n">
         <v>0.0</v>
@@ -7120,7 +7120,7 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>59.812</v>
+        <v>59.25</v>
       </c>
       <c r="F191" t="n">
         <v>0.0</v>
@@ -7129,7 +7129,7 @@
         <v>79.125</v>
       </c>
       <c r="H191" t="n">
-        <v>59.812</v>
+        <v>59.25</v>
       </c>
       <c r="I191" t="n">
         <v>0.0</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>851.864</v>
+        <v>851.52</v>
       </c>
       <c r="F196" t="n">
         <v>0.0</v>
@@ -7314,7 +7314,7 @@
         <v>0.859</v>
       </c>
       <c r="H196" t="n">
-        <v>851.864</v>
+        <v>851.52</v>
       </c>
       <c r="I196" t="n">
         <v>0.0</v>
@@ -7379,7 +7379,7 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>625.637</v>
+        <v>624.091</v>
       </c>
       <c r="F198" t="n">
         <v>0.515</v>
@@ -7388,7 +7388,7 @@
         <v>0.34400000000000003</v>
       </c>
       <c r="H198" t="n">
-        <v>625.637</v>
+        <v>624.091</v>
       </c>
       <c r="I198" t="n">
         <v>0.0</v>
@@ -7453,7 +7453,7 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>473.551</v>
+        <v>465.303</v>
       </c>
       <c r="F200" t="n">
         <v>0.0</v>
@@ -7462,7 +7462,7 @@
         <v>22.681</v>
       </c>
       <c r="H200" t="n">
-        <v>473.551</v>
+        <v>465.303</v>
       </c>
       <c r="I200" t="n">
         <v>0.0</v>
@@ -7490,16 +7490,16 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>416.733</v>
+        <v>402.986</v>
       </c>
       <c r="F201" t="n">
-        <v>0.0</v>
+        <v>0.687</v>
       </c>
       <c r="G201" t="n">
-        <v>48.798</v>
+        <v>48.111000000000004</v>
       </c>
       <c r="H201" t="n">
-        <v>416.733</v>
+        <v>402.986</v>
       </c>
       <c r="I201" t="n">
         <v>0.0</v>
@@ -7601,7 +7601,7 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>82.121</v>
+        <v>54.289</v>
       </c>
       <c r="F204" t="n">
         <v>0.34400000000000003</v>
@@ -7610,7 +7610,7 @@
         <v>43.981</v>
       </c>
       <c r="H204" t="n">
-        <v>82.121</v>
+        <v>54.289</v>
       </c>
       <c r="I204" t="n">
         <v>0.0</v>
@@ -7638,7 +7638,7 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>74.916</v>
+        <v>70.105</v>
       </c>
       <c r="F205" t="n">
         <v>0.0</v>
@@ -7647,7 +7647,7 @@
         <v>11.684</v>
       </c>
       <c r="H205" t="n">
-        <v>74.916</v>
+        <v>70.105</v>
       </c>
       <c r="I205" t="n">
         <v>0.0</v>
@@ -7675,7 +7675,7 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>1615.8349999999998</v>
+        <v>1588.804</v>
       </c>
       <c r="F206" t="n">
         <v>1.031</v>
@@ -7684,7 +7684,7 @@
         <v>0.34400000000000003</v>
       </c>
       <c r="H206" t="n">
-        <v>1615.8349999999998</v>
+        <v>1588.804</v>
       </c>
       <c r="I206" t="n">
         <v>0.0</v>
@@ -7712,7 +7712,7 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>172.512</v>
+        <v>165.64</v>
       </c>
       <c r="F207" t="n">
         <v>0.0</v>
@@ -7721,7 +7721,7 @@
         <v>1019.9530000000001</v>
       </c>
       <c r="H207" t="n">
-        <v>172.512</v>
+        <v>165.64</v>
       </c>
       <c r="I207" t="n">
         <v>0.0</v>
@@ -7971,7 +7971,7 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>984.126</v>
+        <v>975.021</v>
       </c>
       <c r="F214" t="n">
         <v>0.0</v>
@@ -7980,7 +7980,7 @@
         <v>3.436</v>
       </c>
       <c r="H214" t="n">
-        <v>984.126</v>
+        <v>975.021</v>
       </c>
       <c r="I214" t="n">
         <v>0.0</v>
@@ -8193,7 +8193,7 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>1069.0</v>
+        <v>1055.0</v>
       </c>
       <c r="F220" t="n">
         <v>0.0</v>
@@ -8202,7 +8202,7 @@
         <v>0.0</v>
       </c>
       <c r="H220" t="n">
-        <v>1069.0</v>
+        <v>1055.0</v>
       </c>
       <c r="I220" t="n">
         <v>0.0</v>
@@ -8415,7 +8415,7 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>0.0</v>
+        <v>32.0</v>
       </c>
       <c r="F226" t="n">
         <v>0.0</v>
@@ -8424,7 +8424,7 @@
         <v>0.0</v>
       </c>
       <c r="H226" t="n">
-        <v>0.0</v>
+        <v>32.0</v>
       </c>
       <c r="I226" t="n">
         <v>0.0</v>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>62.05</v>
+        <v>82.733</v>
       </c>
       <c r="F229" t="n">
         <v>0.0</v>
@@ -8535,7 +8535,7 @@
         <v>1.279</v>
       </c>
       <c r="H229" t="n">
-        <v>62.05</v>
+        <v>82.733</v>
       </c>
       <c r="I229" t="n">
         <v>0.0</v>
@@ -8637,7 +8637,7 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>108.086</v>
+        <v>138.778</v>
       </c>
       <c r="F232" t="n">
         <v>0.0</v>
@@ -8646,7 +8646,7 @@
         <v>4.002999999999999</v>
       </c>
       <c r="H232" t="n">
-        <v>108.086</v>
+        <v>138.778</v>
       </c>
       <c r="I232" t="n">
         <v>0.0</v>
@@ -9007,16 +9007,16 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>13850.326</v>
+        <v>13750.594000000001</v>
       </c>
       <c r="F242" t="n">
         <v>0.733</v>
       </c>
       <c r="G242" t="n">
-        <v>762.876</v>
+        <v>316.29600000000005</v>
       </c>
       <c r="H242" t="n">
-        <v>13850.326</v>
+        <v>13750.594000000001</v>
       </c>
       <c r="I242" t="n">
         <v>0.0</v>
@@ -9044,16 +9044,16 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>9197.709</v>
+        <v>9494.988</v>
       </c>
       <c r="F243" t="n">
         <v>1.7329999999999999</v>
       </c>
       <c r="G243" t="n">
-        <v>703.4730000000001</v>
+        <v>812.677</v>
       </c>
       <c r="H243" t="n">
-        <v>9197.709</v>
+        <v>9494.988</v>
       </c>
       <c r="I243" t="n">
         <v>0.0</v>
@@ -9087,7 +9087,7 @@
         <v>0.0</v>
       </c>
       <c r="G244" t="n">
-        <v>15.334</v>
+        <v>11.334</v>
       </c>
       <c r="H244" t="n">
         <v>4417.0</v>
@@ -9303,7 +9303,7 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>95.742</v>
+        <v>5.004</v>
       </c>
       <c r="F250" t="n">
         <v>0.0</v>
@@ -9312,7 +9312,7 @@
         <v>0.0</v>
       </c>
       <c r="H250" t="n">
-        <v>95.742</v>
+        <v>5.004</v>
       </c>
       <c r="I250" t="n">
         <v>0.0</v>
@@ -9340,7 +9340,7 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>493.40000000000003</v>
+        <v>462.6</v>
       </c>
       <c r="F251" t="n">
         <v>5.4</v>
@@ -9349,7 +9349,7 @@
         <v>4.4</v>
       </c>
       <c r="H251" t="n">
-        <v>493.40000000000003</v>
+        <v>462.6</v>
       </c>
       <c r="I251" t="n">
         <v>0.0</v>
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>309.246</v>
+        <v>308.83</v>
       </c>
       <c r="F253" t="n">
         <v>0.0</v>
@@ -9423,7 +9423,7 @@
         <v>604.1959999999999</v>
       </c>
       <c r="H253" t="n">
-        <v>309.246</v>
+        <v>308.83</v>
       </c>
       <c r="I253" t="n">
         <v>0.0</v>
@@ -9451,7 +9451,7 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>258.2</v>
+        <v>257.8</v>
       </c>
       <c r="F254" t="n">
         <v>0.6</v>
@@ -9460,7 +9460,7 @@
         <v>10.0</v>
       </c>
       <c r="H254" t="n">
-        <v>258.2</v>
+        <v>257.8</v>
       </c>
       <c r="I254" t="n">
         <v>0.0</v>
@@ -9488,16 +9488,16 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>5576.926</v>
+        <v>5419.8369999999995</v>
       </c>
       <c r="F255" t="n">
         <v>1.777</v>
       </c>
       <c r="G255" t="n">
-        <v>62.620999999999995</v>
+        <v>17.725</v>
       </c>
       <c r="H255" t="n">
-        <v>5576.926</v>
+        <v>5419.8369999999995</v>
       </c>
       <c r="I255" t="n">
         <v>0.0</v>
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>3521.39</v>
+        <v>3513.907</v>
       </c>
       <c r="F256" t="n">
         <v>4.446000000000001</v>
@@ -9534,7 +9534,7 @@
         <v>35.356</v>
       </c>
       <c r="H256" t="n">
-        <v>3521.39</v>
+        <v>3513.907</v>
       </c>
       <c r="I256" t="n">
         <v>0.0</v>
@@ -9562,7 +9562,7 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>3285.216</v>
+        <v>3276.191</v>
       </c>
       <c r="F257" t="n">
         <v>3.367</v>
@@ -9571,7 +9571,7 @@
         <v>145.07</v>
       </c>
       <c r="H257" t="n">
-        <v>3285.216</v>
+        <v>3276.191</v>
       </c>
       <c r="I257" t="n">
         <v>0.0</v>
@@ -9784,7 +9784,7 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>16.802</v>
+        <v>4414.934899999999</v>
       </c>
       <c r="F263" t="n">
         <v>0.0</v>
@@ -9796,7 +9796,7 @@
         <v>16.802</v>
       </c>
       <c r="I263" t="n">
-        <v>0.0</v>
+        <v>4398.1329</v>
       </c>
     </row>
     <row r="264">
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>305.963</v>
+        <v>301.163</v>
       </c>
       <c r="F268" t="n">
         <v>0.04</v>
@@ -9978,7 +9978,7 @@
         <v>3.8400000000000003</v>
       </c>
       <c r="H268" t="n">
-        <v>305.963</v>
+        <v>301.163</v>
       </c>
       <c r="I268" t="n">
         <v>0.0</v>
@@ -10006,7 +10006,7 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>400.561</v>
+        <v>400.481</v>
       </c>
       <c r="F269" t="n">
         <v>0.0</v>
@@ -10015,7 +10015,7 @@
         <v>0.0</v>
       </c>
       <c r="H269" t="n">
-        <v>400.561</v>
+        <v>400.481</v>
       </c>
       <c r="I269" t="n">
         <v>0.0</v>
@@ -10043,7 +10043,7 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>572.9190000000001</v>
+        <v>572.399</v>
       </c>
       <c r="F270" t="n">
         <v>0.08</v>
@@ -10052,7 +10052,7 @@
         <v>0.0</v>
       </c>
       <c r="H270" t="n">
-        <v>572.9190000000001</v>
+        <v>572.399</v>
       </c>
       <c r="I270" t="n">
         <v>0.0</v>
@@ -10080,7 +10080,7 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>319.28</v>
+        <v>314.4</v>
       </c>
       <c r="F271" t="n">
         <v>0.0</v>
@@ -10089,7 +10089,7 @@
         <v>0.44</v>
       </c>
       <c r="H271" t="n">
-        <v>319.28</v>
+        <v>314.4</v>
       </c>
       <c r="I271" t="n">
         <v>0.0</v>
@@ -10154,16 +10154,16 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>160.008</v>
+        <v>166.67499999999998</v>
       </c>
       <c r="F273" t="n">
         <v>87.338</v>
       </c>
       <c r="G273" t="n">
-        <v>6.667</v>
+        <v>0.0</v>
       </c>
       <c r="H273" t="n">
-        <v>160.008</v>
+        <v>166.67499999999998</v>
       </c>
       <c r="I273" t="n">
         <v>0.0</v>
@@ -10228,7 +10228,7 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>2149.2</v>
+        <v>2077.2</v>
       </c>
       <c r="F275" t="n">
         <v>0.0</v>
@@ -10237,7 +10237,7 @@
         <v>194.39999999999998</v>
       </c>
       <c r="H275" t="n">
-        <v>2149.2</v>
+        <v>2077.2</v>
       </c>
       <c r="I275" t="n">
         <v>0.0</v>
@@ -10265,7 +10265,7 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>3976.7999999999997</v>
+        <v>3976.4</v>
       </c>
       <c r="F276" t="n">
         <v>0.2</v>
@@ -10274,7 +10274,7 @@
         <v>84.0</v>
       </c>
       <c r="H276" t="n">
-        <v>3976.7999999999997</v>
+        <v>3976.4</v>
       </c>
       <c r="I276" t="n">
         <v>0.0</v>
@@ -10302,7 +10302,7 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>702.152</v>
+        <v>587.497</v>
       </c>
       <c r="F277" t="n">
         <v>2.222</v>
@@ -10311,7 +10311,7 @@
         <v>18.665000000000003</v>
       </c>
       <c r="H277" t="n">
-        <v>702.152</v>
+        <v>587.497</v>
       </c>
       <c r="I277" t="n">
         <v>0.0</v>
@@ -10339,7 +10339,7 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>4635.9800000000005</v>
+        <v>7377.039200000001</v>
       </c>
       <c r="F278" t="n">
         <v>0.444</v>
@@ -10351,7 +10351,7 @@
         <v>4635.9800000000005</v>
       </c>
       <c r="I278" t="n">
-        <v>0.0</v>
+        <v>2741.0592</v>
       </c>
     </row>
     <row r="279">
@@ -10376,7 +10376,7 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>1207.435</v>
+        <v>1206.1019999999999</v>
       </c>
       <c r="F279" t="n">
         <v>0.889</v>
@@ -10385,7 +10385,7 @@
         <v>0.0</v>
       </c>
       <c r="H279" t="n">
-        <v>1207.435</v>
+        <v>1206.1019999999999</v>
       </c>
       <c r="I279" t="n">
         <v>0.0</v>
@@ -10413,7 +10413,7 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>3010.367</v>
+        <v>2893.044</v>
       </c>
       <c r="F280" t="n">
         <v>0.0</v>
@@ -10422,7 +10422,7 @@
         <v>351.965</v>
       </c>
       <c r="H280" t="n">
-        <v>3010.367</v>
+        <v>2893.044</v>
       </c>
       <c r="I280" t="n">
         <v>0.0</v>
@@ -10783,7 +10783,7 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>1135.0</v>
+        <v>1096.6000000000001</v>
       </c>
       <c r="F290" t="n">
         <v>1.0</v>
@@ -10792,7 +10792,7 @@
         <v>132.8</v>
       </c>
       <c r="H290" t="n">
-        <v>1135.0</v>
+        <v>1096.6000000000001</v>
       </c>
       <c r="I290" t="n">
         <v>0.0</v>
@@ -10820,7 +10820,7 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>4581.6</v>
+        <v>4581.0</v>
       </c>
       <c r="F291" t="n">
         <v>2.4</v>
@@ -10829,7 +10829,7 @@
         <v>333.0</v>
       </c>
       <c r="H291" t="n">
-        <v>4581.6</v>
+        <v>4581.0</v>
       </c>
       <c r="I291" t="n">
         <v>0.0</v>
@@ -10857,7 +10857,7 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>36.6</v>
+        <v>21.799999999999997</v>
       </c>
       <c r="F292" t="n">
         <v>1.2</v>
@@ -10866,7 +10866,7 @@
         <v>136.8</v>
       </c>
       <c r="H292" t="n">
-        <v>36.6</v>
+        <v>21.799999999999997</v>
       </c>
       <c r="I292" t="n">
         <v>0.0</v>
@@ -10894,7 +10894,7 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>698.6</v>
+        <v>623.0</v>
       </c>
       <c r="F293" t="n">
         <v>0.4</v>
@@ -10903,7 +10903,7 @@
         <v>0.0</v>
       </c>
       <c r="H293" t="n">
-        <v>698.6</v>
+        <v>623.0</v>
       </c>
       <c r="I293" t="n">
         <v>0.0</v>
@@ -11042,7 +11042,7 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>5633.2480000000005</v>
+        <v>5631.115000000001</v>
       </c>
       <c r="F297" t="n">
         <v>1.067</v>
@@ -11051,7 +11051,7 @@
         <v>0.0</v>
       </c>
       <c r="H297" t="n">
-        <v>5633.2480000000005</v>
+        <v>5631.115000000001</v>
       </c>
       <c r="I297" t="n">
         <v>0.0</v>
@@ -11560,7 +11560,7 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>12540.234</v>
+        <v>12523.965</v>
       </c>
       <c r="F311" t="n">
         <v>0.533</v>
@@ -11569,7 +11569,7 @@
         <v>0.0</v>
       </c>
       <c r="H311" t="n">
-        <v>12540.234</v>
+        <v>12523.965</v>
       </c>
       <c r="I311" t="n">
         <v>0.0</v>
@@ -11634,7 +11634,7 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>306.0</v>
+        <v>305.59999999999997</v>
       </c>
       <c r="F313" t="n">
         <v>0.6</v>
@@ -11643,7 +11643,7 @@
         <v>6.4</v>
       </c>
       <c r="H313" t="n">
-        <v>306.0</v>
+        <v>305.59999999999997</v>
       </c>
       <c r="I313" t="n">
         <v>0.0</v>
@@ -11745,7 +11745,7 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>2025.6000000000001</v>
+        <v>2025.6</v>
       </c>
       <c r="F316" t="n">
         <v>1.4</v>
@@ -11754,7 +11754,7 @@
         <v>43.2</v>
       </c>
       <c r="H316" t="n">
-        <v>2025.6000000000001</v>
+        <v>2025.6</v>
       </c>
       <c r="I316" t="n">
         <v>0.0</v>
@@ -12004,16 +12004,16 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>14.4</v>
+        <v>62.4</v>
       </c>
       <c r="F323" t="n">
         <v>0.0</v>
       </c>
       <c r="G323" t="n">
-        <v>48.0</v>
+        <v>0.0</v>
       </c>
       <c r="H323" t="n">
-        <v>14.4</v>
+        <v>62.4</v>
       </c>
       <c r="I323" t="n">
         <v>0.0</v>
@@ -12078,7 +12078,7 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>2455.32</v>
+        <v>3098.2799999999997</v>
       </c>
       <c r="F325" t="n">
         <v>0.04</v>
@@ -12087,10 +12087,10 @@
         <v>77.75999999999999</v>
       </c>
       <c r="H325" t="n">
-        <v>2455.32</v>
+        <v>2376.3599999999997</v>
       </c>
       <c r="I325" t="n">
-        <v>0.0</v>
+        <v>721.92</v>
       </c>
     </row>
     <row r="326">
@@ -12115,16 +12115,16 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>3055.952</v>
+        <v>3090.152</v>
       </c>
       <c r="F326" t="n">
         <v>1.013</v>
       </c>
       <c r="G326" t="n">
-        <v>39.375</v>
+        <v>2.25</v>
       </c>
       <c r="H326" t="n">
-        <v>3055.952</v>
+        <v>3090.152</v>
       </c>
       <c r="I326" t="n">
         <v>0.0</v>
@@ -12152,7 +12152,7 @@
         </is>
       </c>
       <c r="E327" t="n">
-        <v>2375.955</v>
+        <v>3168.6340000000005</v>
       </c>
       <c r="F327" t="n">
         <v>0.0</v>
@@ -12161,10 +12161,10 @@
         <v>88.245</v>
       </c>
       <c r="H327" t="n">
-        <v>2375.955</v>
+        <v>2703.5440000000003</v>
       </c>
       <c r="I327" t="n">
-        <v>0.0</v>
+        <v>465.09</v>
       </c>
     </row>
     <row r="328">
@@ -12226,16 +12226,16 @@
         </is>
       </c>
       <c r="E329" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F329" t="n">
         <v>271.75</v>
-      </c>
-      <c r="F329" t="n">
-        <v>0.0</v>
       </c>
       <c r="G329" t="n">
         <v>1240.596</v>
       </c>
       <c r="H329" t="n">
-        <v>271.75</v>
+        <v>0.0</v>
       </c>
       <c r="I329" t="n">
         <v>0.0</v>
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>2091.2</v>
+        <v>2079.2</v>
       </c>
       <c r="F334" t="n">
         <v>0.0</v>
@@ -12420,7 +12420,7 @@
         <v>0.0</v>
       </c>
       <c r="H334" t="n">
-        <v>2091.2</v>
+        <v>2079.2</v>
       </c>
       <c r="I334" t="n">
         <v>0.0</v>
@@ -12559,7 +12559,7 @@
         </is>
       </c>
       <c r="E338" t="n">
-        <v>896.2</v>
+        <v>884.2</v>
       </c>
       <c r="F338" t="n">
         <v>0.6</v>
@@ -12568,7 +12568,7 @@
         <v>2.4</v>
       </c>
       <c r="H338" t="n">
-        <v>896.2</v>
+        <v>884.2</v>
       </c>
       <c r="I338" t="n">
         <v>0.0</v>
@@ -13077,7 +13077,7 @@
         </is>
       </c>
       <c r="E352" t="n">
-        <v>357.644</v>
+        <v>348.843</v>
       </c>
       <c r="F352" t="n">
         <v>19.202</v>
@@ -13086,7 +13086,7 @@
         <v>0.0</v>
       </c>
       <c r="H352" t="n">
-        <v>357.644</v>
+        <v>348.843</v>
       </c>
       <c r="I352" t="n">
         <v>0.0</v>
@@ -13225,7 +13225,7 @@
         </is>
       </c>
       <c r="E356" t="n">
-        <v>23092.733</v>
+        <v>22916.593</v>
       </c>
       <c r="F356" t="n">
         <v>0.111</v>
@@ -13234,7 +13234,7 @@
         <v>37.03</v>
       </c>
       <c r="H356" t="n">
-        <v>23092.733</v>
+        <v>22916.593</v>
       </c>
       <c r="I356" t="n">
         <v>0.0</v>
@@ -13262,7 +13262,7 @@
         </is>
       </c>
       <c r="E357" t="n">
-        <v>8915.108</v>
+        <v>8397.826</v>
       </c>
       <c r="F357" t="n">
         <v>0.333</v>
@@ -13271,7 +13271,7 @@
         <v>2.666</v>
       </c>
       <c r="H357" t="n">
-        <v>8915.108</v>
+        <v>8397.826</v>
       </c>
       <c r="I357" t="n">
         <v>0.0</v>
@@ -13299,16 +13299,16 @@
         </is>
       </c>
       <c r="E358" t="n">
-        <v>10544.483</v>
+        <v>10344.323</v>
       </c>
       <c r="F358" t="n">
         <v>0.222</v>
       </c>
       <c r="G358" t="n">
-        <v>120.09599999999999</v>
+        <v>122.765</v>
       </c>
       <c r="H358" t="n">
-        <v>10544.483</v>
+        <v>10344.323</v>
       </c>
       <c r="I358" t="n">
         <v>0.0</v>
@@ -13706,7 +13706,7 @@
         </is>
       </c>
       <c r="E369" t="n">
-        <v>6179.229</v>
+        <v>6179.23</v>
       </c>
       <c r="F369" t="n">
         <v>0.0</v>
@@ -13715,7 +13715,7 @@
         <v>0.0</v>
       </c>
       <c r="H369" t="n">
-        <v>6179.229</v>
+        <v>6179.23</v>
       </c>
       <c r="I369" t="n">
         <v>0.0</v>
@@ -14008,7 +14008,7 @@
         <v>53.336</v>
       </c>
       <c r="G377" t="n">
-        <v>33.334999999999994</v>
+        <v>54.003</v>
       </c>
       <c r="H377" t="n">
         <v>0.222</v>
@@ -14039,16 +14039,16 @@
         </is>
       </c>
       <c r="E378" t="n">
-        <v>1108.653</v>
+        <v>1083.719</v>
       </c>
       <c r="F378" t="n">
         <v>25.124</v>
       </c>
       <c r="G378" t="n">
-        <v>137.14100000000002</v>
+        <v>27.202</v>
       </c>
       <c r="H378" t="n">
-        <v>1108.653</v>
+        <v>1083.719</v>
       </c>
       <c r="I378" t="n">
         <v>0.0</v>
@@ -14076,7 +14076,7 @@
         </is>
       </c>
       <c r="E379" t="n">
-        <v>307.466</v>
+        <v>293.06600000000003</v>
       </c>
       <c r="F379" t="n">
         <v>53.6</v>
@@ -14085,7 +14085,7 @@
         <v>30.4</v>
       </c>
       <c r="H379" t="n">
-        <v>307.466</v>
+        <v>293.06600000000003</v>
       </c>
       <c r="I379" t="n">
         <v>0.0</v>
@@ -14224,7 +14224,7 @@
         </is>
       </c>
       <c r="E383" t="n">
-        <v>34.0</v>
+        <v>33.0</v>
       </c>
       <c r="F383" t="n">
         <v>0.0</v>
@@ -14233,7 +14233,7 @@
         <v>0.0</v>
       </c>
       <c r="H383" t="n">
-        <v>34.0</v>
+        <v>33.0</v>
       </c>
       <c r="I383" t="n">
         <v>0.0</v>
@@ -14853,7 +14853,7 @@
         </is>
       </c>
       <c r="E400" t="n">
-        <v>2722.0989999999997</v>
+        <v>2709.049</v>
       </c>
       <c r="F400" t="n">
         <v>0.2</v>
@@ -14862,7 +14862,7 @@
         <v>74.39999999999999</v>
       </c>
       <c r="H400" t="n">
-        <v>2722.0989999999997</v>
+        <v>2709.049</v>
       </c>
       <c r="I400" t="n">
         <v>0.0</v>
@@ -14890,16 +14890,16 @@
         </is>
       </c>
       <c r="E401" t="n">
-        <v>2365.6</v>
+        <v>2404.5</v>
       </c>
       <c r="F401" t="n">
         <v>0.0</v>
       </c>
       <c r="G401" t="n">
-        <v>180.10000000000002</v>
+        <v>79.3</v>
       </c>
       <c r="H401" t="n">
-        <v>2365.6</v>
+        <v>2404.5</v>
       </c>
       <c r="I401" t="n">
         <v>0.0</v>
@@ -14927,7 +14927,7 @@
         </is>
       </c>
       <c r="E402" t="n">
-        <v>871.65</v>
+        <v>869.6999999999999</v>
       </c>
       <c r="F402" t="n">
         <v>0.15</v>
@@ -14936,7 +14936,7 @@
         <v>101.1</v>
       </c>
       <c r="H402" t="n">
-        <v>871.65</v>
+        <v>869.6999999999999</v>
       </c>
       <c r="I402" t="n">
         <v>0.0</v>
@@ -14964,16 +14964,16 @@
         </is>
       </c>
       <c r="E403" t="n">
-        <v>1686.15</v>
+        <v>1755.3</v>
       </c>
       <c r="F403" t="n">
         <v>0.0</v>
       </c>
       <c r="G403" t="n">
-        <v>163.5</v>
+        <v>62.7</v>
       </c>
       <c r="H403" t="n">
-        <v>1686.15</v>
+        <v>1755.3</v>
       </c>
       <c r="I403" t="n">
         <v>0.0</v>
@@ -15001,7 +15001,7 @@
         </is>
       </c>
       <c r="E404" t="n">
-        <v>2436.5</v>
+        <v>2429.3</v>
       </c>
       <c r="F404" t="n">
         <v>0.15</v>
@@ -15010,7 +15010,7 @@
         <v>31.2</v>
       </c>
       <c r="H404" t="n">
-        <v>2436.5</v>
+        <v>2429.3</v>
       </c>
       <c r="I404" t="n">
         <v>0.0</v>
@@ -15038,7 +15038,7 @@
         </is>
       </c>
       <c r="E405" t="n">
-        <v>2714.25</v>
+        <v>2666.5</v>
       </c>
       <c r="F405" t="n">
         <v>0.1</v>
@@ -15047,7 +15047,7 @@
         <v>0.0</v>
       </c>
       <c r="H405" t="n">
-        <v>2714.25</v>
+        <v>2666.5</v>
       </c>
       <c r="I405" t="n">
         <v>0.0</v>
@@ -15075,7 +15075,7 @@
         </is>
       </c>
       <c r="E406" t="n">
-        <v>9467.850999999999</v>
+        <v>9427.951</v>
       </c>
       <c r="F406" t="n">
         <v>0.9</v>
@@ -15084,7 +15084,7 @@
         <v>0.0</v>
       </c>
       <c r="H406" t="n">
-        <v>9467.850999999999</v>
+        <v>9427.951</v>
       </c>
       <c r="I406" t="n">
         <v>0.0</v>
@@ -15445,7 +15445,7 @@
         </is>
       </c>
       <c r="E416" t="n">
-        <v>82.8</v>
+        <v>61.2</v>
       </c>
       <c r="F416" t="n">
         <v>0.0</v>
@@ -15454,7 +15454,7 @@
         <v>0.0</v>
       </c>
       <c r="H416" t="n">
-        <v>82.8</v>
+        <v>61.2</v>
       </c>
       <c r="I416" t="n">
         <v>0.0</v>
@@ -15778,7 +15778,7 @@
         </is>
       </c>
       <c r="E425" t="n">
-        <v>1234.614</v>
+        <v>1221.778</v>
       </c>
       <c r="F425" t="n">
         <v>61.196</v>
@@ -15787,7 +15787,7 @@
         <v>4.107</v>
       </c>
       <c r="H425" t="n">
-        <v>1234.614</v>
+        <v>1221.778</v>
       </c>
       <c r="I425" t="n">
         <v>0.0</v>
@@ -15815,7 +15815,7 @@
         </is>
       </c>
       <c r="E426" t="n">
-        <v>7319.818</v>
+        <v>7075.086</v>
       </c>
       <c r="F426" t="n">
         <v>193.912</v>
@@ -15824,7 +15824,7 @@
         <v>8.215</v>
       </c>
       <c r="H426" t="n">
-        <v>7319.818</v>
+        <v>7075.086</v>
       </c>
       <c r="I426" t="n">
         <v>0.0</v>
@@ -15889,7 +15889,7 @@
         </is>
       </c>
       <c r="E428" t="n">
-        <v>2102.7360000000003</v>
+        <v>2101.025</v>
       </c>
       <c r="F428" t="n">
         <v>0.0</v>
@@ -15898,7 +15898,7 @@
         <v>2.054</v>
       </c>
       <c r="H428" t="n">
-        <v>2102.7360000000003</v>
+        <v>2101.025</v>
       </c>
       <c r="I428" t="n">
         <v>0.0</v>
@@ -15926,16 +15926,16 @@
         </is>
       </c>
       <c r="E429" t="n">
-        <v>785.0690000000001</v>
+        <v>1063.2510000000002</v>
       </c>
       <c r="F429" t="n">
         <v>0.0</v>
       </c>
       <c r="G429" t="n">
-        <v>395.806</v>
+        <v>115.756</v>
       </c>
       <c r="H429" t="n">
-        <v>785.0690000000001</v>
+        <v>1063.2510000000002</v>
       </c>
       <c r="I429" t="n">
         <v>0.0</v>
@@ -15963,7 +15963,7 @@
         </is>
       </c>
       <c r="E430" t="n">
-        <v>8623.437</v>
+        <v>8426.527</v>
       </c>
       <c r="F430" t="n">
         <v>444.002</v>
@@ -15972,7 +15972,7 @@
         <v>30.047</v>
       </c>
       <c r="H430" t="n">
-        <v>8623.437</v>
+        <v>8426.527</v>
       </c>
       <c r="I430" t="n">
         <v>0.0</v>
@@ -16037,7 +16037,7 @@
         </is>
       </c>
       <c r="E432" t="n">
-        <v>2052.758</v>
+        <v>1937.939</v>
       </c>
       <c r="F432" t="n">
         <v>0.0</v>
@@ -16046,7 +16046,7 @@
         <v>191.83700000000002</v>
       </c>
       <c r="H432" t="n">
-        <v>2052.758</v>
+        <v>1937.939</v>
       </c>
       <c r="I432" t="n">
         <v>0.0</v>
@@ -16074,7 +16074,7 @@
         </is>
       </c>
       <c r="E433" t="n">
-        <v>6473.817</v>
+        <v>6465.884</v>
       </c>
       <c r="F433" t="n">
         <v>6.069</v>
@@ -16083,7 +16083,7 @@
         <v>148.894</v>
       </c>
       <c r="H433" t="n">
-        <v>6473.817</v>
+        <v>6465.884</v>
       </c>
       <c r="I433" t="n">
         <v>0.0</v>
@@ -16111,7 +16111,7 @@
         </is>
       </c>
       <c r="E434" t="n">
-        <v>23070.514</v>
+        <v>23024.307</v>
       </c>
       <c r="F434" t="n">
         <v>3.733</v>
@@ -16120,7 +16120,7 @@
         <v>50.879</v>
       </c>
       <c r="H434" t="n">
-        <v>23070.514</v>
+        <v>23024.307</v>
       </c>
       <c r="I434" t="n">
         <v>0.0</v>
@@ -16148,7 +16148,7 @@
         </is>
       </c>
       <c r="E435" t="n">
-        <v>4354.165</v>
+        <v>4248.565</v>
       </c>
       <c r="F435" t="n">
         <v>217.32999999999998</v>
@@ -16157,7 +16157,7 @@
         <v>71.762</v>
       </c>
       <c r="H435" t="n">
-        <v>4354.165</v>
+        <v>4248.565</v>
       </c>
       <c r="I435" t="n">
         <v>0.0</v>
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="E436" t="n">
-        <v>2051.642</v>
+        <v>1850.9399999999998</v>
       </c>
       <c r="F436" t="n">
         <v>294.922</v>
@@ -16194,7 +16194,7 @@
         <v>79.056</v>
       </c>
       <c r="H436" t="n">
-        <v>2051.642</v>
+        <v>1850.9399999999998</v>
       </c>
       <c r="I436" t="n">
         <v>0.0</v>
@@ -16296,7 +16296,7 @@
         </is>
       </c>
       <c r="E439" t="n">
-        <v>967.3290000000001</v>
+        <v>924.74</v>
       </c>
       <c r="F439" t="n">
         <v>0.0</v>
@@ -16305,7 +16305,7 @@
         <v>73.80499999999999</v>
       </c>
       <c r="H439" t="n">
-        <v>967.3290000000001</v>
+        <v>924.74</v>
       </c>
       <c r="I439" t="n">
         <v>0.0</v>
@@ -16333,7 +16333,7 @@
         </is>
       </c>
       <c r="E440" t="n">
-        <v>7230.193</v>
+        <v>7072.374</v>
       </c>
       <c r="F440" t="n">
         <v>382.444</v>
@@ -16342,7 +16342,7 @@
         <v>0.292</v>
       </c>
       <c r="H440" t="n">
-        <v>7230.193</v>
+        <v>7072.374</v>
       </c>
       <c r="I440" t="n">
         <v>0.0</v>
@@ -16370,7 +16370,7 @@
         </is>
       </c>
       <c r="E441" t="n">
-        <v>1410.433</v>
+        <v>1410.14</v>
       </c>
       <c r="F441" t="n">
         <v>0.0</v>
@@ -16379,7 +16379,7 @@
         <v>19.253</v>
       </c>
       <c r="H441" t="n">
-        <v>1410.433</v>
+        <v>1410.14</v>
       </c>
       <c r="I441" t="n">
         <v>0.0</v>
@@ -16444,7 +16444,7 @@
         </is>
       </c>
       <c r="E443" t="n">
-        <v>2928.7920000000004</v>
+        <v>2961.174</v>
       </c>
       <c r="F443" t="n">
         <v>0.0</v>
@@ -16453,7 +16453,7 @@
         <v>0.0</v>
       </c>
       <c r="H443" t="n">
-        <v>2928.7920000000004</v>
+        <v>2961.174</v>
       </c>
       <c r="I443" t="n">
         <v>0.0</v>
@@ -16851,7 +16851,7 @@
         </is>
       </c>
       <c r="E454" t="n">
-        <v>217.627</v>
+        <v>204.825</v>
       </c>
       <c r="F454" t="n">
         <v>0.0</v>
@@ -16860,7 +16860,7 @@
         <v>0.0</v>
       </c>
       <c r="H454" t="n">
-        <v>217.627</v>
+        <v>204.825</v>
       </c>
       <c r="I454" t="n">
         <v>0.0</v>
@@ -16888,7 +16888,7 @@
         </is>
       </c>
       <c r="E455" t="n">
-        <v>708.141</v>
+        <v>706.874</v>
       </c>
       <c r="F455" t="n">
         <v>1.267</v>
@@ -16897,7 +16897,7 @@
         <v>0.0</v>
       </c>
       <c r="H455" t="n">
-        <v>708.141</v>
+        <v>706.874</v>
       </c>
       <c r="I455" t="n">
         <v>0.0</v>
@@ -16925,7 +16925,7 @@
         </is>
       </c>
       <c r="E456" t="n">
-        <v>242.684</v>
+        <v>239.884</v>
       </c>
       <c r="F456" t="n">
         <v>0.0</v>
@@ -16934,7 +16934,7 @@
         <v>0.0</v>
       </c>
       <c r="H456" t="n">
-        <v>242.684</v>
+        <v>239.884</v>
       </c>
       <c r="I456" t="n">
         <v>0.0</v>
@@ -17110,7 +17110,7 @@
         </is>
       </c>
       <c r="E461" t="n">
-        <v>1008.722</v>
+        <v>956.726</v>
       </c>
       <c r="F461" t="n">
         <v>135.19</v>
@@ -17119,7 +17119,7 @@
         <v>561.557</v>
       </c>
       <c r="H461" t="n">
-        <v>1008.722</v>
+        <v>956.726</v>
       </c>
       <c r="I461" t="n">
         <v>0.0</v>
@@ -17295,7 +17295,7 @@
         </is>
       </c>
       <c r="E466" t="n">
-        <v>736.877</v>
+        <v>735.7520000000001</v>
       </c>
       <c r="F466" t="n">
         <v>1.575</v>
@@ -17304,7 +17304,7 @@
         <v>85.725</v>
       </c>
       <c r="H466" t="n">
-        <v>736.877</v>
+        <v>735.7520000000001</v>
       </c>
       <c r="I466" t="n">
         <v>0.0</v>
@@ -17332,16 +17332,16 @@
         </is>
       </c>
       <c r="E467" t="n">
-        <v>1701.789</v>
+        <v>1737.114</v>
       </c>
       <c r="F467" t="n">
         <v>0.0</v>
       </c>
       <c r="G467" t="n">
-        <v>105.30000000000001</v>
+        <v>60.75</v>
       </c>
       <c r="H467" t="n">
-        <v>1701.789</v>
+        <v>1737.114</v>
       </c>
       <c r="I467" t="n">
         <v>0.0</v>
@@ -17443,7 +17443,7 @@
         </is>
       </c>
       <c r="E470" t="n">
-        <v>117.198</v>
+        <v>116.828</v>
       </c>
       <c r="F470" t="n">
         <v>0.13899999999999998</v>
@@ -17452,7 +17452,7 @@
         <v>582.75</v>
       </c>
       <c r="H470" t="n">
-        <v>117.198</v>
+        <v>116.828</v>
       </c>
       <c r="I470" t="n">
         <v>0.0</v>
@@ -17480,7 +17480,7 @@
         </is>
       </c>
       <c r="E471" t="n">
-        <v>1119.6399999999999</v>
+        <v>1099.2399999999998</v>
       </c>
       <c r="F471" t="n">
         <v>1.08</v>
@@ -17489,7 +17489,7 @@
         <v>178.07999999999998</v>
       </c>
       <c r="H471" t="n">
-        <v>1119.6399999999999</v>
+        <v>1099.2399999999998</v>
       </c>
       <c r="I471" t="n">
         <v>0.0</v>
@@ -17517,7 +17517,7 @@
         </is>
       </c>
       <c r="E472" t="n">
-        <v>64.761</v>
+        <v>59.601</v>
       </c>
       <c r="F472" t="n">
         <v>58.56</v>
@@ -17526,7 +17526,7 @@
         <v>101.76</v>
       </c>
       <c r="H472" t="n">
-        <v>64.761</v>
+        <v>59.601</v>
       </c>
       <c r="I472" t="n">
         <v>0.0</v>
@@ -17554,7 +17554,7 @@
         </is>
       </c>
       <c r="E473" t="n">
-        <v>1628.3700000000001</v>
+        <v>1623.375</v>
       </c>
       <c r="F473" t="n">
         <v>0.13899999999999998</v>
@@ -17563,7 +17563,7 @@
         <v>5.55</v>
       </c>
       <c r="H473" t="n">
-        <v>1628.3700000000001</v>
+        <v>1623.375</v>
       </c>
       <c r="I473" t="n">
         <v>0.0</v>
@@ -17591,7 +17591,7 @@
         </is>
       </c>
       <c r="E474" t="n">
-        <v>438.64</v>
+        <v>436.72</v>
       </c>
       <c r="F474" t="n">
         <v>0.04</v>
@@ -17600,7 +17600,7 @@
         <v>62.4</v>
       </c>
       <c r="H474" t="n">
-        <v>438.64</v>
+        <v>436.72</v>
       </c>
       <c r="I474" t="n">
         <v>0.0</v>
@@ -17628,7 +17628,7 @@
         </is>
       </c>
       <c r="E475" t="n">
-        <v>2519.005</v>
+        <v>2492.227</v>
       </c>
       <c r="F475" t="n">
         <v>0.786</v>
@@ -17637,7 +17637,7 @@
         <v>155.955</v>
       </c>
       <c r="H475" t="n">
-        <v>2519.005</v>
+        <v>2492.227</v>
       </c>
       <c r="I475" t="n">
         <v>0.0</v>
@@ -17665,7 +17665,7 @@
         </is>
       </c>
       <c r="E476" t="n">
-        <v>291.08</v>
+        <v>290.12</v>
       </c>
       <c r="F476" t="n">
         <v>0.0</v>
@@ -17674,7 +17674,7 @@
         <v>110.88000000000001</v>
       </c>
       <c r="H476" t="n">
-        <v>291.08</v>
+        <v>290.12</v>
       </c>
       <c r="I476" t="n">
         <v>0.0</v>
@@ -17702,7 +17702,7 @@
         </is>
       </c>
       <c r="E477" t="n">
-        <v>1076.516</v>
+        <v>1068.422</v>
       </c>
       <c r="F477" t="n">
         <v>0.231</v>
@@ -17711,7 +17711,7 @@
         <v>24.42</v>
       </c>
       <c r="H477" t="n">
-        <v>1076.516</v>
+        <v>1068.422</v>
       </c>
       <c r="I477" t="n">
         <v>0.0</v>
@@ -17739,7 +17739,7 @@
         </is>
       </c>
       <c r="E478" t="n">
-        <v>462.61999999999995</v>
+        <v>462.342</v>
       </c>
       <c r="F478" t="n">
         <v>0.0</v>
@@ -17748,7 +17748,7 @@
         <v>0.0</v>
       </c>
       <c r="H478" t="n">
-        <v>462.61999999999995</v>
+        <v>462.342</v>
       </c>
       <c r="I478" t="n">
         <v>0.0</v>
@@ -17813,7 +17813,7 @@
         </is>
       </c>
       <c r="E480" t="n">
-        <v>374.76</v>
+        <v>374.06800000000004</v>
       </c>
       <c r="F480" t="n">
         <v>0.13899999999999998</v>
@@ -17822,7 +17822,7 @@
         <v>533.27</v>
       </c>
       <c r="H480" t="n">
-        <v>374.76</v>
+        <v>374.06800000000004</v>
       </c>
       <c r="I480" t="n">
         <v>0.0</v>
@@ -17887,16 +17887,16 @@
         </is>
       </c>
       <c r="E482" t="n">
-        <v>11838.09</v>
+        <v>12353.116999999998</v>
       </c>
       <c r="F482" t="n">
         <v>56.336</v>
       </c>
       <c r="G482" t="n">
-        <v>915.046</v>
+        <v>976.382</v>
       </c>
       <c r="H482" t="n">
-        <v>11838.09</v>
+        <v>12353.116999999998</v>
       </c>
       <c r="I482" t="n">
         <v>0.0</v>
@@ -17924,16 +17924,16 @@
         </is>
       </c>
       <c r="E483" t="n">
-        <v>3136.588</v>
+        <v>3002.192</v>
       </c>
       <c r="F483" t="n">
         <v>20.532999999999998</v>
       </c>
       <c r="G483" t="n">
-        <v>190.393</v>
+        <v>30.799</v>
       </c>
       <c r="H483" t="n">
-        <v>3136.588</v>
+        <v>3002.192</v>
       </c>
       <c r="I483" t="n">
         <v>0.0</v>
@@ -17961,16 +17961,16 @@
         </is>
       </c>
       <c r="E484" t="n">
-        <v>5445.26</v>
+        <v>5439.127</v>
       </c>
       <c r="F484" t="n">
         <v>26.576999999999998</v>
       </c>
       <c r="G484" t="n">
-        <v>154.35199999999998</v>
+        <v>49.065999999999995</v>
       </c>
       <c r="H484" t="n">
-        <v>5445.26</v>
+        <v>5439.127</v>
       </c>
       <c r="I484" t="n">
         <v>0.0</v>
@@ -17998,16 +17998,16 @@
         </is>
       </c>
       <c r="E485" t="n">
-        <v>232.2</v>
+        <v>10916.4</v>
       </c>
       <c r="F485" t="n">
         <v>30.8</v>
       </c>
       <c r="G485" t="n">
-        <v>11047.2</v>
+        <v>831.2</v>
       </c>
       <c r="H485" t="n">
-        <v>232.2</v>
+        <v>10916.4</v>
       </c>
       <c r="I485" t="n">
         <v>0.0</v>
@@ -18183,7 +18183,7 @@
         </is>
       </c>
       <c r="E490" t="n">
-        <v>1162.8</v>
+        <v>1117.2</v>
       </c>
       <c r="F490" t="n">
         <v>0.8</v>
@@ -18192,7 +18192,7 @@
         <v>0.0</v>
       </c>
       <c r="H490" t="n">
-        <v>1162.8</v>
+        <v>1117.2</v>
       </c>
       <c r="I490" t="n">
         <v>0.0</v>
@@ -18627,7 +18627,7 @@
         </is>
       </c>
       <c r="E502" t="n">
-        <v>2258.49</v>
+        <v>2252.874</v>
       </c>
       <c r="F502" t="n">
         <v>0.0</v>
@@ -18636,7 +18636,7 @@
         <v>9.165</v>
       </c>
       <c r="H502" t="n">
-        <v>2258.49</v>
+        <v>2252.874</v>
       </c>
       <c r="I502" t="n">
         <v>0.0</v>
@@ -18664,7 +18664,7 @@
         </is>
       </c>
       <c r="E503" t="n">
-        <v>2713.195</v>
+        <v>2632.209</v>
       </c>
       <c r="F503" t="n">
         <v>0.0</v>
@@ -18673,7 +18673,7 @@
         <v>6.793</v>
       </c>
       <c r="H503" t="n">
-        <v>2713.195</v>
+        <v>2632.209</v>
       </c>
       <c r="I503" t="n">
         <v>0.0</v>
@@ -18701,7 +18701,7 @@
         </is>
       </c>
       <c r="E504" t="n">
-        <v>861.619</v>
+        <v>860.017</v>
       </c>
       <c r="F504" t="n">
         <v>0.367</v>
@@ -18710,7 +18710,7 @@
         <v>19.489</v>
       </c>
       <c r="H504" t="n">
-        <v>861.619</v>
+        <v>860.017</v>
       </c>
       <c r="I504" t="n">
         <v>0.0</v>
@@ -19034,7 +19034,7 @@
         </is>
       </c>
       <c r="E513" t="n">
-        <v>735.0</v>
+        <v>717.0</v>
       </c>
       <c r="F513" t="n">
         <v>0.0</v>
@@ -19043,7 +19043,7 @@
         <v>0.5</v>
       </c>
       <c r="H513" t="n">
-        <v>735.0</v>
+        <v>717.0</v>
       </c>
       <c r="I513" t="n">
         <v>0.0</v>
@@ -19515,7 +19515,7 @@
         </is>
       </c>
       <c r="E526" t="n">
-        <v>992.6129999999999</v>
+        <v>976.0409999999999</v>
       </c>
       <c r="F526" t="n">
         <v>43.466</v>
@@ -19524,7 +19524,7 @@
         <v>0.313</v>
       </c>
       <c r="H526" t="n">
-        <v>992.6129999999999</v>
+        <v>976.0409999999999</v>
       </c>
       <c r="I526" t="n">
         <v>0.0</v>
@@ -19589,7 +19589,7 @@
         </is>
       </c>
       <c r="E528" t="n">
-        <v>3639.074</v>
+        <v>3619.447</v>
       </c>
       <c r="F528" t="n">
         <v>949.602</v>
@@ -19598,7 +19598,7 @@
         <v>2297.6549999999997</v>
       </c>
       <c r="H528" t="n">
-        <v>3639.074</v>
+        <v>3619.447</v>
       </c>
       <c r="I528" t="n">
         <v>0.0</v>
@@ -19959,16 +19959,16 @@
         </is>
       </c>
       <c r="E538" t="n">
-        <v>4644.896</v>
+        <v>4576.391</v>
       </c>
       <c r="F538" t="n">
         <v>27.501</v>
       </c>
       <c r="G538" t="n">
-        <v>151.674</v>
+        <v>57.003</v>
       </c>
       <c r="H538" t="n">
-        <v>4644.896</v>
+        <v>4576.391</v>
       </c>
       <c r="I538" t="n">
         <v>0.0</v>
@@ -19996,16 +19996,16 @@
         </is>
       </c>
       <c r="E539" t="n">
-        <v>4621.823</v>
+        <v>4521.719</v>
       </c>
       <c r="F539" t="n">
         <v>35.535</v>
       </c>
       <c r="G539" t="n">
-        <v>594.701</v>
+        <v>87.392</v>
       </c>
       <c r="H539" t="n">
-        <v>4621.823</v>
+        <v>4521.719</v>
       </c>
       <c r="I539" t="n">
         <v>0.0</v>
@@ -20033,16 +20033,16 @@
         </is>
       </c>
       <c r="E540" t="n">
-        <v>2142.798</v>
+        <v>4343.054</v>
       </c>
       <c r="F540" t="n">
         <v>16.747999999999998</v>
       </c>
       <c r="G540" t="n">
-        <v>3634.737</v>
+        <v>301.713</v>
       </c>
       <c r="H540" t="n">
-        <v>2142.798</v>
+        <v>4343.054</v>
       </c>
       <c r="I540" t="n">
         <v>0.0</v>
@@ -20181,16 +20181,16 @@
         </is>
       </c>
       <c r="E544" t="n">
-        <v>2039.0</v>
+        <v>2053.4</v>
       </c>
       <c r="F544" t="n">
         <v>6.2</v>
       </c>
       <c r="G544" t="n">
-        <v>28.8</v>
+        <v>14.4</v>
       </c>
       <c r="H544" t="n">
-        <v>2039.0</v>
+        <v>2053.4</v>
       </c>
       <c r="I544" t="n">
         <v>0.0</v>
@@ -20218,16 +20218,16 @@
         </is>
       </c>
       <c r="E545" t="n">
-        <v>0.6</v>
+        <v>5.4</v>
       </c>
       <c r="F545" t="n">
         <v>1.0</v>
       </c>
       <c r="G545" t="n">
-        <v>9.799999999999999</v>
+        <v>5.0</v>
       </c>
       <c r="H545" t="n">
-        <v>0.6</v>
+        <v>5.4</v>
       </c>
       <c r="I545" t="n">
         <v>0.0</v>
@@ -20403,7 +20403,7 @@
         </is>
       </c>
       <c r="E550" t="n">
-        <v>4551.0</v>
+        <v>5547.0</v>
       </c>
       <c r="F550" t="n">
         <v>0.0</v>
@@ -20412,7 +20412,7 @@
         <v>0.0</v>
       </c>
       <c r="H550" t="n">
-        <v>4551.0</v>
+        <v>5547.0</v>
       </c>
       <c r="I550" t="n">
         <v>0.0</v>
@@ -20551,7 +20551,7 @@
         </is>
       </c>
       <c r="E554" t="n">
-        <v>1923.001</v>
+        <v>3197.001</v>
       </c>
       <c r="F554" t="n">
         <v>0.0</v>
@@ -20560,7 +20560,7 @@
         <v>4.0</v>
       </c>
       <c r="H554" t="n">
-        <v>1923.001</v>
+        <v>3197.001</v>
       </c>
       <c r="I554" t="n">
         <v>0.0</v>
@@ -21069,7 +21069,7 @@
         </is>
       </c>
       <c r="E568" t="n">
-        <v>5479.523</v>
+        <v>5659.5271999999995</v>
       </c>
       <c r="F568" t="n">
         <v>0.0</v>
@@ -21078,10 +21078,10 @@
         <v>5.539</v>
       </c>
       <c r="H568" t="n">
-        <v>5479.523</v>
+        <v>5583.833</v>
       </c>
       <c r="I568" t="n">
-        <v>0.0</v>
+        <v>75.6942</v>
       </c>
     </row>
     <row r="569">
@@ -21143,7 +21143,7 @@
         </is>
       </c>
       <c r="E570" t="n">
-        <v>1320.033</v>
+        <v>1299.725</v>
       </c>
       <c r="F570" t="n">
         <v>0.0</v>
@@ -21152,7 +21152,7 @@
         <v>1.846</v>
       </c>
       <c r="H570" t="n">
-        <v>1320.033</v>
+        <v>1299.725</v>
       </c>
       <c r="I570" t="n">
         <v>0.0</v>
@@ -21217,7 +21217,7 @@
         </is>
       </c>
       <c r="E572" t="n">
-        <v>1403.552</v>
+        <v>2114.258</v>
       </c>
       <c r="F572" t="n">
         <v>0.0</v>
@@ -21226,10 +21226,10 @@
         <v>0.0</v>
       </c>
       <c r="H572" t="n">
-        <v>1403.552</v>
+        <v>1396.49</v>
       </c>
       <c r="I572" t="n">
-        <v>0.0</v>
+        <v>717.768</v>
       </c>
     </row>
     <row r="573">
@@ -21254,7 +21254,7 @@
         </is>
       </c>
       <c r="E573" t="n">
-        <v>1739.12</v>
+        <v>3679.0152</v>
       </c>
       <c r="F573" t="n">
         <v>0.0</v>
@@ -21263,10 +21263,10 @@
         <v>9.231</v>
       </c>
       <c r="H573" t="n">
-        <v>1739.12</v>
+        <v>1729.4279999999999</v>
       </c>
       <c r="I573" t="n">
-        <v>0.0</v>
+        <v>1949.5872</v>
       </c>
     </row>
     <row r="574">
@@ -21291,16 +21291,16 @@
         </is>
       </c>
       <c r="E574" t="n">
-        <v>0.0</v>
+        <v>189.41</v>
       </c>
       <c r="F574" t="n">
         <v>0.0</v>
       </c>
       <c r="G574" t="n">
-        <v>648.906</v>
+        <v>459.49600000000004</v>
       </c>
       <c r="H574" t="n">
-        <v>0.0</v>
+        <v>189.41</v>
       </c>
       <c r="I574" t="n">
         <v>0.0</v>
@@ -21624,16 +21624,16 @@
         </is>
       </c>
       <c r="E583" t="n">
-        <v>4748.245</v>
+        <v>4651.058</v>
       </c>
       <c r="F583" t="n">
         <v>0.0</v>
       </c>
       <c r="G583" t="n">
-        <v>1050.859</v>
+        <v>695.8389999999999</v>
       </c>
       <c r="H583" t="n">
-        <v>4748.245</v>
+        <v>4651.058</v>
       </c>
       <c r="I583" t="n">
         <v>0.0</v>
@@ -21661,7 +21661,7 @@
         </is>
       </c>
       <c r="E584" t="n">
-        <v>80.321</v>
+        <v>4147.8158</v>
       </c>
       <c r="F584" t="n">
         <v>2.219</v>
@@ -21670,10 +21670,10 @@
         <v>386.37899999999996</v>
       </c>
       <c r="H584" t="n">
-        <v>80.321</v>
+        <v>68.636</v>
       </c>
       <c r="I584" t="n">
-        <v>0.0</v>
+        <v>4079.1798</v>
       </c>
     </row>
     <row r="585">
@@ -21735,7 +21735,7 @@
         </is>
       </c>
       <c r="E586" t="n">
-        <v>6335.396</v>
+        <v>7140.6008</v>
       </c>
       <c r="F586" t="n">
         <v>0.0</v>
@@ -21747,7 +21747,7 @@
         <v>6335.396</v>
       </c>
       <c r="I586" t="n">
-        <v>0.0</v>
+        <v>805.2048</v>
       </c>
     </row>
     <row r="587">
@@ -21772,7 +21772,7 @@
         </is>
       </c>
       <c r="E587" t="n">
-        <v>5421.599</v>
+        <v>5279.888</v>
       </c>
       <c r="F587" t="n">
         <v>2.5149999999999997</v>
@@ -21781,7 +21781,7 @@
         <v>326.618</v>
       </c>
       <c r="H587" t="n">
-        <v>5421.599</v>
+        <v>5279.888</v>
       </c>
       <c r="I587" t="n">
         <v>0.0</v>
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="E589" t="n">
-        <v>1513.7169999999999</v>
+        <v>1720.5149999999999</v>
       </c>
       <c r="F589" t="n">
         <v>0.888</v>
@@ -21855,10 +21855,10 @@
         <v>0.888</v>
       </c>
       <c r="H589" t="n">
-        <v>1513.7169999999999</v>
+        <v>1454.25</v>
       </c>
       <c r="I589" t="n">
-        <v>0.0</v>
+        <v>266.265</v>
       </c>
     </row>
     <row r="590">
@@ -21883,7 +21883,7 @@
         </is>
       </c>
       <c r="E590" t="n">
-        <v>440.352</v>
+        <v>773.952</v>
       </c>
       <c r="F590" t="n">
         <v>0.0</v>
@@ -21892,7 +21892,7 @@
         <v>0.5</v>
       </c>
       <c r="H590" t="n">
-        <v>440.352</v>
+        <v>773.952</v>
       </c>
       <c r="I590" t="n">
         <v>0.0</v>
@@ -21920,7 +21920,7 @@
         </is>
       </c>
       <c r="E591" t="n">
-        <v>6098.819</v>
+        <v>6098.286</v>
       </c>
       <c r="F591" t="n">
         <v>1.067</v>
@@ -21929,7 +21929,7 @@
         <v>392.24199999999996</v>
       </c>
       <c r="H591" t="n">
-        <v>6098.819</v>
+        <v>6098.286</v>
       </c>
       <c r="I591" t="n">
         <v>0.0</v>
@@ -22401,7 +22401,7 @@
         </is>
       </c>
       <c r="E604" t="n">
-        <v>7239.0</v>
+        <v>7236.0</v>
       </c>
       <c r="F604" t="n">
         <v>0.0</v>
@@ -22410,7 +22410,7 @@
         <v>3.0</v>
       </c>
       <c r="H604" t="n">
-        <v>7239.0</v>
+        <v>7236.0</v>
       </c>
       <c r="I604" t="n">
         <v>0.0</v>
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="E619" t="n">
-        <v>448.022</v>
+        <v>277.347</v>
       </c>
       <c r="F619" t="n">
         <v>0.0</v>
@@ -22965,7 +22965,7 @@
         <v>0.0</v>
       </c>
       <c r="H619" t="n">
-        <v>448.022</v>
+        <v>277.347</v>
       </c>
       <c r="I619" t="n">
         <v>0.0</v>
@@ -23067,7 +23067,7 @@
         </is>
       </c>
       <c r="E622" t="n">
-        <v>3017.27</v>
+        <v>2980.596</v>
       </c>
       <c r="F622" t="n">
         <v>0.0</v>
@@ -23076,7 +23076,7 @@
         <v>0.0</v>
       </c>
       <c r="H622" t="n">
-        <v>3017.27</v>
+        <v>2980.596</v>
       </c>
       <c r="I622" t="n">
         <v>0.0</v>
@@ -23363,7 +23363,7 @@
         </is>
       </c>
       <c r="E630" t="n">
-        <v>2.809</v>
+        <v>1739.801</v>
       </c>
       <c r="F630" t="n">
         <v>1.125</v>
@@ -23375,7 +23375,7 @@
         <v>2.809</v>
       </c>
       <c r="I630" t="n">
-        <v>0.0</v>
+        <v>1736.992</v>
       </c>
     </row>
     <row r="631">
@@ -23400,7 +23400,7 @@
         </is>
       </c>
       <c r="E631" t="n">
-        <v>135.47500000000002</v>
+        <v>1998.9470000000001</v>
       </c>
       <c r="F631" t="n">
         <v>0.0</v>
@@ -23412,7 +23412,7 @@
         <v>135.47500000000002</v>
       </c>
       <c r="I631" t="n">
-        <v>0.0</v>
+        <v>1863.4720000000002</v>
       </c>
     </row>
     <row r="632">
@@ -23437,7 +23437,7 @@
         </is>
       </c>
       <c r="E632" t="n">
-        <v>0.013</v>
+        <v>9.696</v>
       </c>
       <c r="F632" t="n">
         <v>0.0</v>
@@ -23446,7 +23446,7 @@
         <v>0.0</v>
       </c>
       <c r="H632" t="n">
-        <v>0.013</v>
+        <v>9.696</v>
       </c>
       <c r="I632" t="n">
         <v>0.0</v>
@@ -23511,16 +23511,16 @@
         </is>
       </c>
       <c r="E634" t="n">
-        <v>9916.592</v>
+        <v>9889.904</v>
       </c>
       <c r="F634" t="n">
         <v>0.0</v>
       </c>
       <c r="G634" t="n">
-        <v>25.354000000000003</v>
+        <v>4590.335999999999</v>
       </c>
       <c r="H634" t="n">
-        <v>9916.592</v>
+        <v>9889.904</v>
       </c>
       <c r="I634" t="n">
         <v>0.0</v>
@@ -23548,7 +23548,7 @@
         </is>
       </c>
       <c r="E635" t="n">
-        <v>1561.903</v>
+        <v>1558.97</v>
       </c>
       <c r="F635" t="n">
         <v>0.933</v>
@@ -23557,7 +23557,7 @@
         <v>0.0</v>
       </c>
       <c r="H635" t="n">
-        <v>1561.903</v>
+        <v>1558.97</v>
       </c>
       <c r="I635" t="n">
         <v>0.0</v>
@@ -24103,16 +24103,16 @@
         </is>
       </c>
       <c r="E650" t="n">
-        <v>862.55</v>
+        <v>1071.8629999999998</v>
       </c>
       <c r="F650" t="n">
         <v>1.7730000000000001</v>
       </c>
       <c r="G650" t="n">
-        <v>179.285</v>
+        <v>47.928</v>
       </c>
       <c r="H650" t="n">
-        <v>862.55</v>
+        <v>1071.8629999999998</v>
       </c>
       <c r="I650" t="n">
         <v>0.0</v>
@@ -24140,7 +24140,7 @@
         </is>
       </c>
       <c r="E651" t="n">
-        <v>2220.058</v>
+        <v>2139.587</v>
       </c>
       <c r="F651" t="n">
         <v>0.0</v>
@@ -24149,7 +24149,7 @@
         <v>55.620000000000005</v>
       </c>
       <c r="H651" t="n">
-        <v>2220.058</v>
+        <v>2139.587</v>
       </c>
       <c r="I651" t="n">
         <v>0.0</v>
@@ -24399,7 +24399,7 @@
         </is>
       </c>
       <c r="E658" t="n">
-        <v>850.639</v>
+        <v>843.538</v>
       </c>
       <c r="F658" t="n">
         <v>0.0</v>
@@ -24408,7 +24408,7 @@
         <v>1.42</v>
       </c>
       <c r="H658" t="n">
-        <v>850.639</v>
+        <v>843.538</v>
       </c>
       <c r="I658" t="n">
         <v>0.0</v>
@@ -24658,7 +24658,7 @@
         </is>
       </c>
       <c r="E665" t="n">
-        <v>10914.999</v>
+        <v>10914.998</v>
       </c>
       <c r="F665" t="n">
         <v>1.8639999999999999</v>
@@ -24667,7 +24667,7 @@
         <v>3.7279999999999998</v>
       </c>
       <c r="H665" t="n">
-        <v>10914.999</v>
+        <v>10914.998</v>
       </c>
       <c r="I665" t="n">
         <v>0.0</v>
@@ -24732,16 +24732,16 @@
         </is>
       </c>
       <c r="E667" t="n">
-        <v>90.826</v>
+        <v>140.529</v>
       </c>
       <c r="F667" t="n">
         <v>16.271</v>
       </c>
       <c r="G667" t="n">
-        <v>64.19800000000001</v>
+        <v>14.495</v>
       </c>
       <c r="H667" t="n">
-        <v>90.826</v>
+        <v>140.529</v>
       </c>
       <c r="I667" t="n">
         <v>0.0</v>
@@ -24917,7 +24917,7 @@
         </is>
       </c>
       <c r="E672" t="n">
-        <v>2866.776</v>
+        <v>2863.6639999999998</v>
       </c>
       <c r="F672" t="n">
         <v>0.312</v>
@@ -24926,7 +24926,7 @@
         <v>0.0</v>
       </c>
       <c r="H672" t="n">
-        <v>2866.776</v>
+        <v>2863.6639999999998</v>
       </c>
       <c r="I672" t="n">
         <v>0.0</v>
@@ -24954,7 +24954,7 @@
         </is>
       </c>
       <c r="E673" t="n">
-        <v>3652.779</v>
+        <v>3651.224</v>
       </c>
       <c r="F673" t="n">
         <v>3734.0</v>
@@ -24963,7 +24963,7 @@
         <v>0.0</v>
       </c>
       <c r="H673" t="n">
-        <v>3652.779</v>
+        <v>3651.224</v>
       </c>
       <c r="I673" t="n">
         <v>0.0</v>
@@ -24991,7 +24991,7 @@
         </is>
       </c>
       <c r="E674" t="n">
-        <v>14421.004</v>
+        <v>14294.983</v>
       </c>
       <c r="F674" t="n">
         <v>0.0</v>
@@ -25000,7 +25000,7 @@
         <v>0.0</v>
       </c>
       <c r="H674" t="n">
-        <v>14421.004</v>
+        <v>14294.983</v>
       </c>
       <c r="I674" t="n">
         <v>0.0</v>
@@ -25509,7 +25509,7 @@
         </is>
       </c>
       <c r="E688" t="n">
-        <v>203.815</v>
+        <v>194.791</v>
       </c>
       <c r="F688" t="n">
         <v>2.491</v>
@@ -25518,7 +25518,7 @@
         <v>0.0</v>
       </c>
       <c r="H688" t="n">
-        <v>203.815</v>
+        <v>194.791</v>
       </c>
       <c r="I688" t="n">
         <v>0.0</v>
@@ -25546,7 +25546,7 @@
         </is>
       </c>
       <c r="E689" t="n">
-        <v>3998.49</v>
+        <v>3967.371</v>
       </c>
       <c r="F689" t="n">
         <v>29.564</v>
@@ -25555,7 +25555,7 @@
         <v>5.601</v>
       </c>
       <c r="H689" t="n">
-        <v>3998.49</v>
+        <v>3967.371</v>
       </c>
       <c r="I689" t="n">
         <v>0.0</v>
@@ -25583,7 +25583,7 @@
         </is>
       </c>
       <c r="E690" t="n">
-        <v>6834.151</v>
+        <v>6783.120999999999</v>
       </c>
       <c r="F690" t="n">
         <v>43.566</v>
@@ -25592,7 +25592,7 @@
         <v>14.936</v>
       </c>
       <c r="H690" t="n">
-        <v>6834.151</v>
+        <v>6783.120999999999</v>
       </c>
       <c r="I690" t="n">
         <v>0.0</v>
@@ -25620,7 +25620,7 @@
         </is>
       </c>
       <c r="E691" t="n">
-        <v>2599.154</v>
+        <v>2522.142</v>
       </c>
       <c r="F691" t="n">
         <v>0.0</v>
@@ -25629,7 +25629,7 @@
         <v>3.851</v>
       </c>
       <c r="H691" t="n">
-        <v>2599.154</v>
+        <v>2522.142</v>
       </c>
       <c r="I691" t="n">
         <v>0.0</v>
@@ -25657,7 +25657,7 @@
         </is>
       </c>
       <c r="E692" t="n">
-        <v>910.665</v>
+        <v>775.894</v>
       </c>
       <c r="F692" t="n">
         <v>0.0</v>
@@ -25666,7 +25666,7 @@
         <v>0.0</v>
       </c>
       <c r="H692" t="n">
-        <v>910.665</v>
+        <v>775.894</v>
       </c>
       <c r="I692" t="n">
         <v>0.0</v>
@@ -25953,7 +25953,7 @@
         </is>
       </c>
       <c r="E700" t="n">
-        <v>1356.458</v>
+        <v>1356.457</v>
       </c>
       <c r="F700" t="n">
         <v>0.666</v>
@@ -25962,7 +25962,7 @@
         <v>10.996</v>
       </c>
       <c r="H700" t="n">
-        <v>1356.458</v>
+        <v>1356.457</v>
       </c>
       <c r="I700" t="n">
         <v>0.0</v>
@@ -25990,7 +25990,7 @@
         </is>
       </c>
       <c r="E701" t="n">
-        <v>500.8</v>
+        <v>496.802</v>
       </c>
       <c r="F701" t="n">
         <v>0.0</v>
@@ -25999,7 +25999,7 @@
         <v>12.995</v>
       </c>
       <c r="H701" t="n">
-        <v>500.8</v>
+        <v>496.802</v>
       </c>
       <c r="I701" t="n">
         <v>0.0</v>
@@ -26070,7 +26070,7 @@
         <v>0.0</v>
       </c>
       <c r="G703" t="n">
-        <v>0.0</v>
+        <v>1.82</v>
       </c>
       <c r="H703" t="n">
         <v>0.608</v>
@@ -26138,7 +26138,7 @@
         </is>
       </c>
       <c r="E705" t="n">
-        <v>992.39</v>
+        <v>992.391</v>
       </c>
       <c r="F705" t="n">
         <v>0.0</v>
@@ -26147,7 +26147,7 @@
         <v>153.619</v>
       </c>
       <c r="H705" t="n">
-        <v>992.39</v>
+        <v>992.391</v>
       </c>
       <c r="I705" t="n">
         <v>0.0</v>
@@ -26212,7 +26212,7 @@
         </is>
       </c>
       <c r="E707" t="n">
-        <v>1352.168</v>
+        <v>891.043</v>
       </c>
       <c r="F707" t="n">
         <v>0.26699999999999996</v>
@@ -26221,7 +26221,7 @@
         <v>0.0</v>
       </c>
       <c r="H707" t="n">
-        <v>1352.168</v>
+        <v>891.043</v>
       </c>
       <c r="I707" t="n">
         <v>0.0</v>
@@ -26323,7 +26323,7 @@
         </is>
       </c>
       <c r="E710" t="n">
-        <v>2715.563</v>
+        <v>2382.251</v>
       </c>
       <c r="F710" t="n">
         <v>0.0</v>
@@ -26332,7 +26332,7 @@
         <v>0.0</v>
       </c>
       <c r="H710" t="n">
-        <v>2715.563</v>
+        <v>2382.251</v>
       </c>
       <c r="I710" t="n">
         <v>0.0</v>
@@ -26360,7 +26360,7 @@
         </is>
       </c>
       <c r="E711" t="n">
-        <v>24137.950999999997</v>
+        <v>24118.747000000003</v>
       </c>
       <c r="F711" t="n">
         <v>2.4</v>
@@ -26369,7 +26369,7 @@
         <v>284.83599999999996</v>
       </c>
       <c r="H711" t="n">
-        <v>24137.950999999997</v>
+        <v>24118.747000000003</v>
       </c>
       <c r="I711" t="n">
         <v>0.0</v>
@@ -26397,7 +26397,7 @@
         </is>
       </c>
       <c r="E712" t="n">
-        <v>3335.884</v>
+        <v>3311.614</v>
       </c>
       <c r="F712" t="n">
         <v>2.4</v>
@@ -26406,7 +26406,7 @@
         <v>214.427</v>
       </c>
       <c r="H712" t="n">
-        <v>3335.884</v>
+        <v>3311.614</v>
       </c>
       <c r="I712" t="n">
         <v>0.0</v>
@@ -26434,19 +26434,19 @@
         </is>
       </c>
       <c r="E713" t="n">
-        <v>2575.986</v>
+        <v>2818.753</v>
       </c>
       <c r="F713" t="n">
         <v>0.13899999999999998</v>
       </c>
       <c r="G713" t="n">
-        <v>67.155</v>
+        <v>20.535</v>
       </c>
       <c r="H713" t="n">
-        <v>2575.986</v>
+        <v>2618.953</v>
       </c>
       <c r="I713" t="n">
-        <v>0.0</v>
+        <v>199.8</v>
       </c>
     </row>
     <row r="714">
@@ -26471,7 +26471,7 @@
         </is>
       </c>
       <c r="E714" t="n">
-        <v>1757.68</v>
+        <v>1748.56</v>
       </c>
       <c r="F714" t="n">
         <v>0.32</v>
@@ -26480,7 +26480,7 @@
         <v>2.8800000000000003</v>
       </c>
       <c r="H714" t="n">
-        <v>1757.68</v>
+        <v>1748.56</v>
       </c>
       <c r="I714" t="n">
         <v>0.0</v>
@@ -26508,7 +26508,7 @@
         </is>
       </c>
       <c r="E715" t="n">
-        <v>2951.72</v>
+        <v>2947.603</v>
       </c>
       <c r="F715" t="n">
         <v>0.0</v>
@@ -26517,7 +26517,7 @@
         <v>0.555</v>
       </c>
       <c r="H715" t="n">
-        <v>2951.72</v>
+        <v>2947.603</v>
       </c>
       <c r="I715" t="n">
         <v>0.0</v>
@@ -26545,7 +26545,7 @@
         </is>
       </c>
       <c r="E716" t="n">
-        <v>1717.4029999999998</v>
+        <v>1716.3229999999999</v>
       </c>
       <c r="F716" t="n">
         <v>0.0</v>
@@ -26554,7 +26554,7 @@
         <v>0.0</v>
       </c>
       <c r="H716" t="n">
-        <v>1717.4029999999998</v>
+        <v>1716.3229999999999</v>
       </c>
       <c r="I716" t="n">
         <v>0.0</v>
@@ -26656,7 +26656,7 @@
         </is>
       </c>
       <c r="E719" t="n">
-        <v>7006.77</v>
+        <v>6966.945</v>
       </c>
       <c r="F719" t="n">
         <v>1.08</v>
@@ -26665,7 +26665,7 @@
         <v>0.40499999999999997</v>
       </c>
       <c r="H719" t="n">
-        <v>7006.77</v>
+        <v>6966.945</v>
       </c>
       <c r="I719" t="n">
         <v>0.0</v>
@@ -26841,7 +26841,7 @@
         </is>
       </c>
       <c r="E724" t="n">
-        <v>194.298</v>
+        <v>178.833</v>
       </c>
       <c r="F724" t="n">
         <v>13.866</v>
@@ -26850,7 +26850,7 @@
         <v>0.0</v>
       </c>
       <c r="H724" t="n">
-        <v>194.298</v>
+        <v>178.833</v>
       </c>
       <c r="I724" t="n">
         <v>0.0</v>
@@ -27100,7 +27100,7 @@
         </is>
       </c>
       <c r="E731" t="n">
-        <v>1160.915</v>
+        <v>3349.0204</v>
       </c>
       <c r="F731" t="n">
         <v>0.0</v>
@@ -27109,10 +27109,10 @@
         <v>162.126</v>
       </c>
       <c r="H731" t="n">
-        <v>1160.915</v>
+        <v>1128.962</v>
       </c>
       <c r="I731" t="n">
-        <v>0.0</v>
+        <v>2220.0584</v>
       </c>
     </row>
     <row r="732">
@@ -27137,7 +27137,7 @@
         </is>
       </c>
       <c r="E732" t="n">
-        <v>2953.632</v>
+        <v>2416.723</v>
       </c>
       <c r="F732" t="n">
         <v>30.178</v>
@@ -27146,10 +27146,10 @@
         <v>5.029999999999999</v>
       </c>
       <c r="H732" t="n">
-        <v>2953.632</v>
+        <v>1813.1709999999998</v>
       </c>
       <c r="I732" t="n">
-        <v>0.0</v>
+        <v>603.552</v>
       </c>
     </row>
     <row r="733">
@@ -27174,7 +27174,7 @@
         </is>
       </c>
       <c r="E733" t="n">
-        <v>729.2919999999999</v>
+        <v>711.688</v>
       </c>
       <c r="F733" t="n">
         <v>21.375999999999998</v>
@@ -27183,7 +27183,7 @@
         <v>0.0</v>
       </c>
       <c r="H733" t="n">
-        <v>729.2919999999999</v>
+        <v>711.688</v>
       </c>
       <c r="I733" t="n">
         <v>0.0</v>
@@ -27285,7 +27285,7 @@
         </is>
       </c>
       <c r="E736" t="n">
-        <v>481.644</v>
+        <v>1253.2214</v>
       </c>
       <c r="F736" t="n">
         <v>0.0</v>
@@ -27294,10 +27294,10 @@
         <v>177.51</v>
       </c>
       <c r="H736" t="n">
-        <v>481.644</v>
+        <v>287.567</v>
       </c>
       <c r="I736" t="n">
-        <v>0.0</v>
+        <v>965.6544</v>
       </c>
     </row>
     <row r="737">
@@ -27359,7 +27359,7 @@
         </is>
       </c>
       <c r="E738" t="n">
-        <v>3002.287</v>
+        <v>2874.479</v>
       </c>
       <c r="F738" t="n">
         <v>0.0</v>
@@ -27368,7 +27368,7 @@
         <v>79.584</v>
       </c>
       <c r="H738" t="n">
-        <v>3002.287</v>
+        <v>2874.479</v>
       </c>
       <c r="I738" t="n">
         <v>0.0</v>
@@ -27396,7 +27396,7 @@
         </is>
       </c>
       <c r="E739" t="n">
-        <v>2739.24</v>
+        <v>2723.085</v>
       </c>
       <c r="F739" t="n">
         <v>0.0</v>
@@ -27405,7 +27405,7 @@
         <v>2.3080000000000003</v>
       </c>
       <c r="H739" t="n">
-        <v>2739.24</v>
+        <v>2723.085</v>
       </c>
       <c r="I739" t="n">
         <v>0.0</v>
@@ -27544,7 +27544,7 @@
         </is>
       </c>
       <c r="E743" t="n">
-        <v>759.234</v>
+        <v>750.002</v>
       </c>
       <c r="F743" t="n">
         <v>2.3080000000000003</v>
@@ -27553,7 +27553,7 @@
         <v>2.3080000000000003</v>
       </c>
       <c r="H743" t="n">
-        <v>759.234</v>
+        <v>750.002</v>
       </c>
       <c r="I743" t="n">
         <v>0.0</v>
@@ -27581,7 +27581,7 @@
         </is>
       </c>
       <c r="E744" t="n">
-        <v>1910.776</v>
+        <v>2810.78</v>
       </c>
       <c r="F744" t="n">
         <v>0.0</v>
@@ -27590,10 +27590,10 @@
         <v>2.3080000000000003</v>
       </c>
       <c r="H744" t="n">
-        <v>1910.776</v>
+        <v>1887.7</v>
       </c>
       <c r="I744" t="n">
-        <v>0.0</v>
+        <v>923.08</v>
       </c>
     </row>
     <row r="745">
@@ -27914,7 +27914,7 @@
         </is>
       </c>
       <c r="E753" t="n">
-        <v>783.439</v>
+        <v>781.655</v>
       </c>
       <c r="F753" t="n">
         <v>0.892</v>
@@ -27923,7 +27923,7 @@
         <v>0.0</v>
       </c>
       <c r="H753" t="n">
-        <v>783.439</v>
+        <v>781.655</v>
       </c>
       <c r="I753" t="n">
         <v>0.0</v>
@@ -27988,16 +27988,16 @@
         </is>
       </c>
       <c r="E755" t="n">
-        <v>0.0</v>
+        <v>252.547</v>
       </c>
       <c r="F755" t="n">
         <v>0.0</v>
       </c>
       <c r="G755" t="n">
-        <v>515.617</v>
+        <v>263.07000000000005</v>
       </c>
       <c r="H755" t="n">
-        <v>0.0</v>
+        <v>252.547</v>
       </c>
       <c r="I755" t="n">
         <v>0.0</v>
@@ -28062,7 +28062,7 @@
         </is>
       </c>
       <c r="E757" t="n">
-        <v>18494.308999999997</v>
+        <v>20740.2102</v>
       </c>
       <c r="F757" t="n">
         <v>19.847</v>
@@ -28071,10 +28071,10 @@
         <v>7.385</v>
       </c>
       <c r="H757" t="n">
-        <v>18494.308999999997</v>
+        <v>19104.477000000003</v>
       </c>
       <c r="I757" t="n">
-        <v>0.0</v>
+        <v>1635.7332</v>
       </c>
     </row>
     <row r="758">
@@ -28173,16 +28173,16 @@
         </is>
       </c>
       <c r="E760" t="n">
-        <v>534.142</v>
+        <v>620.294</v>
       </c>
       <c r="F760" t="n">
         <v>2.154</v>
       </c>
       <c r="G760" t="n">
-        <v>614.048</v>
+        <v>527.8960000000001</v>
       </c>
       <c r="H760" t="n">
-        <v>534.142</v>
+        <v>620.294</v>
       </c>
       <c r="I760" t="n">
         <v>0.0</v>
@@ -28210,7 +28210,7 @@
         </is>
       </c>
       <c r="E761" t="n">
-        <v>5161.2789999999995</v>
+        <v>5154.509</v>
       </c>
       <c r="F761" t="n">
         <v>3.385</v>
@@ -28219,7 +28219,7 @@
         <v>2.0309999999999997</v>
       </c>
       <c r="H761" t="n">
-        <v>5161.2789999999995</v>
+        <v>5154.509</v>
       </c>
       <c r="I761" t="n">
         <v>0.0</v>
@@ -28247,7 +28247,7 @@
         </is>
       </c>
       <c r="E762" t="n">
-        <v>1980.706</v>
+        <v>2627.8558</v>
       </c>
       <c r="F762" t="n">
         <v>2.7070000000000003</v>
@@ -28256,10 +28256,10 @@
         <v>4.061999999999999</v>
       </c>
       <c r="H762" t="n">
-        <v>1980.706</v>
+        <v>1945.5069999999998</v>
       </c>
       <c r="I762" t="n">
-        <v>0.0</v>
+        <v>682.3488</v>
       </c>
     </row>
     <row r="763">
@@ -28321,7 +28321,7 @@
         </is>
       </c>
       <c r="E764" t="n">
-        <v>11505.5</v>
+        <v>11488.914</v>
       </c>
       <c r="F764" t="n">
         <v>6.088</v>
@@ -28330,7 +28330,7 @@
         <v>38.585</v>
       </c>
       <c r="H764" t="n">
-        <v>11505.5</v>
+        <v>11488.914</v>
       </c>
       <c r="I764" t="n">
         <v>0.0</v>
@@ -28469,7 +28469,7 @@
         </is>
       </c>
       <c r="E768" t="n">
-        <v>5097.308</v>
+        <v>5100.3534</v>
       </c>
       <c r="F768" t="n">
         <v>0.0</v>
@@ -28478,10 +28478,10 @@
         <v>0.0</v>
       </c>
       <c r="H768" t="n">
-        <v>5097.308</v>
+        <v>5094.2609999999995</v>
       </c>
       <c r="I768" t="n">
-        <v>0.0</v>
+        <v>6.0924</v>
       </c>
     </row>
     <row r="769">
@@ -28543,7 +28543,7 @@
         </is>
       </c>
       <c r="E770" t="n">
-        <v>3.048</v>
+        <v>2.372</v>
       </c>
       <c r="F770" t="n">
         <v>18.277</v>
@@ -28552,7 +28552,7 @@
         <v>6401.081999999999</v>
       </c>
       <c r="H770" t="n">
-        <v>3.048</v>
+        <v>2.372</v>
       </c>
       <c r="I770" t="n">
         <v>0.0</v>
@@ -28691,7 +28691,7 @@
         </is>
       </c>
       <c r="E774" t="n">
-        <v>3989.526</v>
+        <v>3932.916</v>
       </c>
       <c r="F774" t="n">
         <v>0.27799999999999997</v>
@@ -28700,7 +28700,7 @@
         <v>34.456</v>
       </c>
       <c r="H774" t="n">
-        <v>3989.526</v>
+        <v>3932.916</v>
       </c>
       <c r="I774" t="n">
         <v>0.0</v>
@@ -28728,7 +28728,7 @@
         </is>
       </c>
       <c r="E775" t="n">
-        <v>442.93600000000004</v>
+        <v>441.271</v>
       </c>
       <c r="F775" t="n">
         <v>4.995</v>
@@ -28737,7 +28737,7 @@
         <v>79.36500000000001</v>
       </c>
       <c r="H775" t="n">
-        <v>442.93600000000004</v>
+        <v>441.271</v>
       </c>
       <c r="I775" t="n">
         <v>0.0</v>
@@ -28802,7 +28802,7 @@
         </is>
       </c>
       <c r="E777" t="n">
-        <v>604.5999999999999</v>
+        <v>620.4</v>
       </c>
       <c r="F777" t="n">
         <v>0.5599999999999999</v>
@@ -28811,7 +28811,7 @@
         <v>17.32</v>
       </c>
       <c r="H777" t="n">
-        <v>604.5999999999999</v>
+        <v>620.4</v>
       </c>
       <c r="I777" t="n">
         <v>0.0</v>
@@ -28913,7 +28913,7 @@
         </is>
       </c>
       <c r="E780" t="n">
-        <v>4890.209999999999</v>
+        <v>4877.473</v>
       </c>
       <c r="F780" t="n">
         <v>4.244999999999999</v>
@@ -28922,7 +28922,7 @@
         <v>12.13</v>
       </c>
       <c r="H780" t="n">
-        <v>4890.209999999999</v>
+        <v>4877.473</v>
       </c>
       <c r="I780" t="n">
         <v>0.0</v>
@@ -28950,7 +28950,7 @@
         </is>
       </c>
       <c r="E781" t="n">
-        <v>3068.8900000000003</v>
+        <v>3053.728</v>
       </c>
       <c r="F781" t="n">
         <v>9.704</v>
@@ -28959,7 +28959,7 @@
         <v>9.704</v>
       </c>
       <c r="H781" t="n">
-        <v>3068.8900000000003</v>
+        <v>3053.728</v>
       </c>
       <c r="I781" t="n">
         <v>0.0</v>
@@ -28987,7 +28987,7 @@
         </is>
       </c>
       <c r="E782" t="n">
-        <v>288.694</v>
+        <v>277.171</v>
       </c>
       <c r="F782" t="n">
         <v>1.82</v>
@@ -28996,7 +28996,7 @@
         <v>0.0</v>
       </c>
       <c r="H782" t="n">
-        <v>288.694</v>
+        <v>277.171</v>
       </c>
       <c r="I782" t="n">
         <v>0.0</v>
@@ -29246,7 +29246,7 @@
         </is>
       </c>
       <c r="E789" t="n">
-        <v>5714.19</v>
+        <v>5278.325000000001</v>
       </c>
       <c r="F789" t="n">
         <v>1.8920000000000001</v>
@@ -29255,7 +29255,7 @@
         <v>80.739</v>
       </c>
       <c r="H789" t="n">
-        <v>5714.19</v>
+        <v>5278.325000000001</v>
       </c>
       <c r="I789" t="n">
         <v>0.0</v>
@@ -29283,7 +29283,7 @@
         </is>
       </c>
       <c r="E790" t="n">
-        <v>3137.475</v>
+        <v>4826.6902</v>
       </c>
       <c r="F790" t="n">
         <v>3.154</v>
@@ -29292,10 +29292,10 @@
         <v>0.631</v>
       </c>
       <c r="H790" t="n">
-        <v>3137.475</v>
+        <v>3131.167</v>
       </c>
       <c r="I790" t="n">
-        <v>0.0</v>
+        <v>1695.5232</v>
       </c>
     </row>
     <row r="791">
@@ -29505,16 +29505,16 @@
         </is>
       </c>
       <c r="E796" t="n">
-        <v>475.99</v>
+        <v>549.219</v>
       </c>
       <c r="F796" t="n">
         <v>0.0</v>
       </c>
       <c r="G796" t="n">
-        <v>590.1410000000001</v>
+        <v>516.912</v>
       </c>
       <c r="H796" t="n">
-        <v>475.99</v>
+        <v>549.219</v>
       </c>
       <c r="I796" t="n">
         <v>0.0</v>
@@ -29542,16 +29542,16 @@
         </is>
       </c>
       <c r="E797" t="n">
-        <v>0.0</v>
+        <v>51.691</v>
       </c>
       <c r="F797" t="n">
         <v>0.0</v>
       </c>
       <c r="G797" t="n">
-        <v>605.2180000000001</v>
+        <v>553.527</v>
       </c>
       <c r="H797" t="n">
-        <v>0.0</v>
+        <v>51.691</v>
       </c>
       <c r="I797" t="n">
         <v>0.0</v>
@@ -29764,7 +29764,7 @@
         </is>
       </c>
       <c r="E803" t="n">
-        <v>1392.3999999999999</v>
+        <v>1389.3999999999999</v>
       </c>
       <c r="F803" t="n">
         <v>0.6</v>
@@ -29773,7 +29773,7 @@
         <v>2.4</v>
       </c>
       <c r="H803" t="n">
-        <v>1392.3999999999999</v>
+        <v>1389.3999999999999</v>
       </c>
       <c r="I803" t="n">
         <v>0.0</v>
@@ -29801,7 +29801,7 @@
         </is>
       </c>
       <c r="E804" t="n">
-        <v>1267.1209999999999</v>
+        <v>1958.2777999999998</v>
       </c>
       <c r="F804" t="n">
         <v>0.0</v>
@@ -29813,7 +29813,7 @@
         <v>1267.1209999999999</v>
       </c>
       <c r="I804" t="n">
-        <v>0.0</v>
+        <v>691.1568</v>
       </c>
     </row>
     <row r="805">
@@ -29875,7 +29875,7 @@
         </is>
       </c>
       <c r="E806" t="n">
-        <v>16741.354</v>
+        <v>16677.358</v>
       </c>
       <c r="F806" t="n">
         <v>0.533</v>
@@ -29884,7 +29884,7 @@
         <v>0.0</v>
       </c>
       <c r="H806" t="n">
-        <v>16741.354</v>
+        <v>16677.358</v>
       </c>
       <c r="I806" t="n">
         <v>0.0</v>
@@ -29912,7 +29912,7 @@
         </is>
       </c>
       <c r="E807" t="n">
-        <v>27.203</v>
+        <v>26.137</v>
       </c>
       <c r="F807" t="n">
         <v>1.067</v>
@@ -29921,7 +29921,7 @@
         <v>0.0</v>
       </c>
       <c r="H807" t="n">
-        <v>27.203</v>
+        <v>26.137</v>
       </c>
       <c r="I807" t="n">
         <v>0.0</v>
@@ -29949,7 +29949,7 @@
         </is>
       </c>
       <c r="E808" t="n">
-        <v>12007.633</v>
+        <v>11999.632</v>
       </c>
       <c r="F808" t="n">
         <v>2.4</v>
@@ -29958,7 +29958,7 @@
         <v>594.208</v>
       </c>
       <c r="H808" t="n">
-        <v>12007.633</v>
+        <v>11999.632</v>
       </c>
       <c r="I808" t="n">
         <v>0.0</v>
@@ -30023,7 +30023,7 @@
         </is>
       </c>
       <c r="E810" t="n">
-        <v>1463.634</v>
+        <v>2359.41</v>
       </c>
       <c r="F810" t="n">
         <v>0.0</v>
@@ -30035,7 +30035,7 @@
         <v>1463.634</v>
       </c>
       <c r="I810" t="n">
-        <v>0.0</v>
+        <v>895.776</v>
       </c>
     </row>
     <row r="811">
@@ -30060,7 +30060,7 @@
         </is>
       </c>
       <c r="E811" t="n">
-        <v>0.0</v>
+        <v>5782.0383999999995</v>
       </c>
       <c r="F811" t="n">
         <v>3.2</v>
@@ -30069,10 +30069,10 @@
         <v>1.067</v>
       </c>
       <c r="H811" t="n">
-        <v>0.0</v>
+        <v>1596.7</v>
       </c>
       <c r="I811" t="n">
-        <v>0.0</v>
+        <v>4185.3384</v>
       </c>
     </row>
     <row r="812">
@@ -30097,7 +30097,7 @@
         </is>
       </c>
       <c r="E812" t="n">
-        <v>0.0</v>
+        <v>2669.1336</v>
       </c>
       <c r="F812" t="n">
         <v>0.0</v>
@@ -30109,7 +30109,7 @@
         <v>0.0</v>
       </c>
       <c r="I812" t="n">
-        <v>0.0</v>
+        <v>2669.1336</v>
       </c>
     </row>
     <row r="813">
@@ -30911,7 +30911,7 @@
         </is>
       </c>
       <c r="E834" t="n">
-        <v>1201.398</v>
+        <v>1175.914</v>
       </c>
       <c r="F834" t="n">
         <v>0.0</v>
@@ -30920,7 +30920,7 @@
         <v>0.0</v>
       </c>
       <c r="H834" t="n">
-        <v>1201.398</v>
+        <v>1175.914</v>
       </c>
       <c r="I834" t="n">
         <v>0.0</v>
@@ -30948,7 +30948,7 @@
         </is>
       </c>
       <c r="E835" t="n">
-        <v>2169.798</v>
+        <v>3036.26</v>
       </c>
       <c r="F835" t="n">
         <v>77.66499999999999</v>
@@ -30957,7 +30957,7 @@
         <v>0.0</v>
       </c>
       <c r="H835" t="n">
-        <v>2169.798</v>
+        <v>3036.26</v>
       </c>
       <c r="I835" t="n">
         <v>0.0</v>
@@ -30985,7 +30985,7 @@
         </is>
       </c>
       <c r="E836" t="n">
-        <v>902.869</v>
+        <v>902.868</v>
       </c>
       <c r="F836" t="n">
         <v>0.0</v>
@@ -30994,7 +30994,7 @@
         <v>0.0</v>
       </c>
       <c r="H836" t="n">
-        <v>902.869</v>
+        <v>902.868</v>
       </c>
       <c r="I836" t="n">
         <v>0.0</v>
@@ -31022,7 +31022,7 @@
         </is>
       </c>
       <c r="E837" t="n">
-        <v>800.932</v>
+        <v>666.23</v>
       </c>
       <c r="F837" t="n">
         <v>0.0</v>
@@ -31031,7 +31031,7 @@
         <v>0.0</v>
       </c>
       <c r="H837" t="n">
-        <v>800.932</v>
+        <v>666.23</v>
       </c>
       <c r="I837" t="n">
         <v>0.0</v>
@@ -31133,7 +31133,7 @@
         </is>
       </c>
       <c r="E840" t="n">
-        <v>19529.301</v>
+        <v>19523.966</v>
       </c>
       <c r="F840" t="n">
         <v>11.736999999999998</v>
@@ -31142,7 +31142,7 @@
         <v>0.0</v>
       </c>
       <c r="H840" t="n">
-        <v>19529.301</v>
+        <v>19523.966</v>
       </c>
       <c r="I840" t="n">
         <v>0.0</v>
@@ -31207,7 +31207,7 @@
         </is>
       </c>
       <c r="E842" t="n">
-        <v>5498.345</v>
+        <v>5082.329</v>
       </c>
       <c r="F842" t="n">
         <v>0.0</v>
@@ -31216,7 +31216,7 @@
         <v>0.0</v>
       </c>
       <c r="H842" t="n">
-        <v>5498.345</v>
+        <v>5082.329</v>
       </c>
       <c r="I842" t="n">
         <v>0.0</v>
@@ -31318,7 +31318,7 @@
         </is>
       </c>
       <c r="E845" t="n">
-        <v>9951.449</v>
+        <v>9950.582</v>
       </c>
       <c r="F845" t="n">
         <v>15.601</v>
@@ -31327,7 +31327,7 @@
         <v>0.0</v>
       </c>
       <c r="H845" t="n">
-        <v>9951.449</v>
+        <v>9950.582</v>
       </c>
       <c r="I845" t="n">
         <v>0.0</v>
@@ -31355,7 +31355,7 @@
         </is>
       </c>
       <c r="E846" t="n">
-        <v>371.246</v>
+        <v>358.445</v>
       </c>
       <c r="F846" t="n">
         <v>23.470000000000002</v>
@@ -31364,7 +31364,7 @@
         <v>0.0</v>
       </c>
       <c r="H846" t="n">
-        <v>371.246</v>
+        <v>358.445</v>
       </c>
       <c r="I846" t="n">
         <v>0.0</v>
@@ -31392,7 +31392,7 @@
         </is>
       </c>
       <c r="E847" t="n">
-        <v>2607.069</v>
+        <v>2189.175</v>
       </c>
       <c r="F847" t="n">
         <v>2.601</v>
@@ -31401,7 +31401,7 @@
         <v>0.0</v>
       </c>
       <c r="H847" t="n">
-        <v>2607.069</v>
+        <v>2189.175</v>
       </c>
       <c r="I847" t="n">
         <v>0.0</v>
@@ -31503,7 +31503,7 @@
         </is>
       </c>
       <c r="E850" t="n">
-        <v>11930.806</v>
+        <v>11714.828</v>
       </c>
       <c r="F850" t="n">
         <v>15.997999999999998</v>
@@ -31512,7 +31512,7 @@
         <v>0.6669999999999999</v>
       </c>
       <c r="H850" t="n">
-        <v>11930.806</v>
+        <v>11714.828</v>
       </c>
       <c r="I850" t="n">
         <v>0.0</v>
@@ -31577,7 +31577,7 @@
         </is>
       </c>
       <c r="E852" t="n">
-        <v>2309.7999999999997</v>
+        <v>2309.6</v>
       </c>
       <c r="F852" t="n">
         <v>0.0</v>
@@ -31586,7 +31586,7 @@
         <v>0.0</v>
       </c>
       <c r="H852" t="n">
-        <v>2309.7999999999997</v>
+        <v>2309.6</v>
       </c>
       <c r="I852" t="n">
         <v>0.0</v>
@@ -31651,7 +31651,7 @@
         </is>
       </c>
       <c r="E854" t="n">
-        <v>10747.744</v>
+        <v>10709.339</v>
       </c>
       <c r="F854" t="n">
         <v>41.605000000000004</v>
@@ -31660,7 +31660,7 @@
         <v>0.0</v>
       </c>
       <c r="H854" t="n">
-        <v>10747.744</v>
+        <v>10709.339</v>
       </c>
       <c r="I854" t="n">
         <v>0.0</v>
@@ -31725,7 +31725,7 @@
         </is>
       </c>
       <c r="E856" t="n">
-        <v>2942.234</v>
+        <v>2940.1</v>
       </c>
       <c r="F856" t="n">
         <v>2.134</v>
@@ -31734,7 +31734,7 @@
         <v>0.0</v>
       </c>
       <c r="H856" t="n">
-        <v>2942.234</v>
+        <v>2940.1</v>
       </c>
       <c r="I856" t="n">
         <v>0.0</v>
@@ -31762,7 +31762,7 @@
         </is>
       </c>
       <c r="E857" t="n">
-        <v>1311.096</v>
+        <v>1307.8960000000002</v>
       </c>
       <c r="F857" t="n">
         <v>2.134</v>
@@ -31771,7 +31771,7 @@
         <v>25.603</v>
       </c>
       <c r="H857" t="n">
-        <v>1311.096</v>
+        <v>1307.8960000000002</v>
       </c>
       <c r="I857" t="n">
         <v>0.0</v>
@@ -31799,7 +31799,7 @@
         </is>
       </c>
       <c r="E858" t="n">
-        <v>603.468</v>
+        <v>2000.844</v>
       </c>
       <c r="F858" t="n">
         <v>28.506</v>
@@ -31811,7 +31811,7 @@
         <v>603.468</v>
       </c>
       <c r="I858" t="n">
-        <v>0.0</v>
+        <v>1397.376</v>
       </c>
     </row>
     <row r="859">
@@ -31836,7 +31836,7 @@
         </is>
       </c>
       <c r="E859" t="n">
-        <v>1233.103</v>
+        <v>1230.737</v>
       </c>
       <c r="F859" t="n">
         <v>0.0</v>
@@ -31845,7 +31845,7 @@
         <v>0.0</v>
       </c>
       <c r="H859" t="n">
-        <v>1233.103</v>
+        <v>1230.737</v>
       </c>
       <c r="I859" t="n">
         <v>0.0</v>
@@ -31910,16 +31910,16 @@
         </is>
       </c>
       <c r="E861" t="n">
-        <v>1140.947</v>
+        <v>958.8509999999999</v>
       </c>
       <c r="F861" t="n">
         <v>6.951</v>
       </c>
       <c r="G861" t="n">
-        <v>346.144</v>
+        <v>204.13600000000002</v>
       </c>
       <c r="H861" t="n">
-        <v>1140.947</v>
+        <v>958.8509999999999</v>
       </c>
       <c r="I861" t="n">
         <v>0.0</v>
@@ -32058,7 +32058,7 @@
         </is>
       </c>
       <c r="E865" t="n">
-        <v>10225.419</v>
+        <v>11720.81</v>
       </c>
       <c r="F865" t="n">
         <v>0.0</v>
@@ -32067,7 +32067,7 @@
         <v>6.923</v>
       </c>
       <c r="H865" t="n">
-        <v>10225.419</v>
+        <v>11720.81</v>
       </c>
       <c r="I865" t="n">
         <v>0.0</v>
@@ -32095,7 +32095,7 @@
         </is>
       </c>
       <c r="E866" t="n">
-        <v>4763.093</v>
+        <v>4758.478</v>
       </c>
       <c r="F866" t="n">
         <v>0.0</v>
@@ -32104,7 +32104,7 @@
         <v>0.0</v>
       </c>
       <c r="H866" t="n">
-        <v>4763.093</v>
+        <v>4758.478</v>
       </c>
       <c r="I866" t="n">
         <v>0.0</v>
@@ -32206,7 +32206,7 @@
         </is>
       </c>
       <c r="E869" t="n">
-        <v>1839.297</v>
+        <v>3932.5840000000003</v>
       </c>
       <c r="F869" t="n">
         <v>15.09</v>
@@ -32215,10 +32215,10 @@
         <v>72.779</v>
       </c>
       <c r="H869" t="n">
-        <v>1839.297</v>
+        <v>1216.681</v>
       </c>
       <c r="I869" t="n">
-        <v>0.0</v>
+        <v>2715.9030000000002</v>
       </c>
     </row>
     <row r="870">
@@ -32243,7 +32243,7 @@
         </is>
       </c>
       <c r="E870" t="n">
-        <v>443.07099999999997</v>
+        <v>431.711</v>
       </c>
       <c r="F870" t="n">
         <v>399.048</v>
@@ -32252,7 +32252,7 @@
         <v>2.84</v>
       </c>
       <c r="H870" t="n">
-        <v>443.07099999999997</v>
+        <v>431.711</v>
       </c>
       <c r="I870" t="n">
         <v>0.0</v>
@@ -32280,7 +32280,7 @@
         </is>
       </c>
       <c r="E871" t="n">
-        <v>1513.569</v>
+        <v>1512.386</v>
       </c>
       <c r="F871" t="n">
         <v>0.0</v>
@@ -32289,7 +32289,7 @@
         <v>56.803</v>
       </c>
       <c r="H871" t="n">
-        <v>1513.569</v>
+        <v>1512.386</v>
       </c>
       <c r="I871" t="n">
         <v>0.0</v>
@@ -32317,16 +32317,16 @@
         </is>
       </c>
       <c r="E872" t="n">
-        <v>1896.152</v>
+        <v>1590.411</v>
       </c>
       <c r="F872" t="n">
         <v>0.9990000000000001</v>
       </c>
       <c r="G872" t="n">
-        <v>299.54999999999995</v>
+        <v>219.67000000000002</v>
       </c>
       <c r="H872" t="n">
-        <v>1896.152</v>
+        <v>1590.411</v>
       </c>
       <c r="I872" t="n">
         <v>0.0</v>
@@ -32363,10 +32363,10 @@
         <v>3.994</v>
       </c>
       <c r="H873" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I873" t="n">
         <v>69.895</v>
-      </c>
-      <c r="I873" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="874">
@@ -32391,7 +32391,7 @@
         </is>
       </c>
       <c r="E874" t="n">
-        <v>1921.546</v>
+        <v>1830.719</v>
       </c>
       <c r="F874" t="n">
         <v>3.992</v>
@@ -32400,7 +32400,7 @@
         <v>0.0</v>
       </c>
       <c r="H874" t="n">
-        <v>1921.546</v>
+        <v>1830.719</v>
       </c>
       <c r="I874" t="n">
         <v>0.0</v>
@@ -32428,7 +32428,7 @@
         </is>
       </c>
       <c r="E875" t="n">
-        <v>5669.984</v>
+        <v>10903.815200000001</v>
       </c>
       <c r="F875" t="n">
         <v>0.0</v>
@@ -32440,7 +32440,7 @@
         <v>5669.984</v>
       </c>
       <c r="I875" t="n">
-        <v>0.0</v>
+        <v>5233.8312000000005</v>
       </c>
     </row>
     <row r="876">
@@ -32465,7 +32465,7 @@
         </is>
       </c>
       <c r="E876" t="n">
-        <v>2778.624</v>
+        <v>3695.7588</v>
       </c>
       <c r="F876" t="n">
         <v>1.183</v>
@@ -32474,10 +32474,10 @@
         <v>46.153</v>
       </c>
       <c r="H876" t="n">
-        <v>2778.624</v>
+        <v>2770.34</v>
       </c>
       <c r="I876" t="n">
-        <v>0.0</v>
+        <v>925.4188</v>
       </c>
     </row>
     <row r="877">
@@ -32650,16 +32650,16 @@
         </is>
       </c>
       <c r="E881" t="n">
-        <v>2582.065</v>
+        <v>2606.083</v>
       </c>
       <c r="F881" t="n">
         <v>0.0</v>
       </c>
       <c r="G881" t="n">
-        <v>238.19000000000003</v>
+        <v>198.158</v>
       </c>
       <c r="H881" t="n">
-        <v>2582.065</v>
+        <v>2606.083</v>
       </c>
       <c r="I881" t="n">
         <v>0.0</v>
@@ -32687,7 +32687,7 @@
         </is>
       </c>
       <c r="E882" t="n">
-        <v>1622.63</v>
+        <v>1086.202</v>
       </c>
       <c r="F882" t="n">
         <v>0.0</v>
@@ -32696,7 +32696,7 @@
         <v>0.0</v>
       </c>
       <c r="H882" t="n">
-        <v>1622.63</v>
+        <v>1086.202</v>
       </c>
       <c r="I882" t="n">
         <v>0.0</v>
@@ -32835,7 +32835,7 @@
         </is>
       </c>
       <c r="E886" t="n">
-        <v>3620.894</v>
+        <v>3616.891</v>
       </c>
       <c r="F886" t="n">
         <v>0.0</v>
@@ -32844,7 +32844,7 @@
         <v>60.047999999999995</v>
       </c>
       <c r="H886" t="n">
-        <v>3620.894</v>
+        <v>3616.891</v>
       </c>
       <c r="I886" t="n">
         <v>0.0</v>
@@ -32872,7 +32872,7 @@
         </is>
       </c>
       <c r="E887" t="n">
-        <v>2796.235</v>
+        <v>2676.14</v>
       </c>
       <c r="F887" t="n">
         <v>20.016</v>
@@ -32881,7 +32881,7 @@
         <v>26.855</v>
       </c>
       <c r="H887" t="n">
-        <v>2796.235</v>
+        <v>2676.14</v>
       </c>
       <c r="I887" t="n">
         <v>0.0</v>
@@ -32909,7 +32909,7 @@
         </is>
       </c>
       <c r="E888" t="n">
-        <v>1858.82</v>
+        <v>1834.801</v>
       </c>
       <c r="F888" t="n">
         <v>0.222</v>
@@ -32918,7 +32918,7 @@
         <v>94.742</v>
       </c>
       <c r="H888" t="n">
-        <v>1858.82</v>
+        <v>1834.801</v>
       </c>
       <c r="I888" t="n">
         <v>0.0</v>
@@ -32983,7 +32983,7 @@
         </is>
       </c>
       <c r="E890" t="n">
-        <v>816.3489999999999</v>
+        <v>867.2950000000001</v>
       </c>
       <c r="F890" t="n">
         <v>3.033</v>
@@ -32992,10 +32992,10 @@
         <v>0.0</v>
       </c>
       <c r="H890" t="n">
-        <v>816.3489999999999</v>
+        <v>707.1790000000001</v>
       </c>
       <c r="I890" t="n">
-        <v>0.0</v>
+        <v>160.116</v>
       </c>
     </row>
     <row r="891">
@@ -33094,7 +33094,7 @@
         </is>
       </c>
       <c r="E893" t="n">
-        <v>2074.7960000000003</v>
+        <v>2018.781</v>
       </c>
       <c r="F893" t="n">
         <v>73.94000000000001</v>
@@ -33103,7 +33103,7 @@
         <v>0.0</v>
       </c>
       <c r="H893" t="n">
-        <v>2074.7960000000003</v>
+        <v>2018.781</v>
       </c>
       <c r="I893" t="n">
         <v>0.0</v>
@@ -33316,7 +33316,7 @@
         </is>
       </c>
       <c r="E899" t="n">
-        <v>331.971</v>
+        <v>0.0</v>
       </c>
       <c r="F899" t="n">
         <v>0.0</v>
@@ -33325,7 +33325,7 @@
         <v>0.0</v>
       </c>
       <c r="H899" t="n">
-        <v>331.971</v>
+        <v>0.0</v>
       </c>
       <c r="I899" t="n">
         <v>0.0</v>
@@ -33353,7 +33353,7 @@
         </is>
       </c>
       <c r="E900" t="n">
-        <v>1296.025</v>
+        <v>1264.285</v>
       </c>
       <c r="F900" t="n">
         <v>0.0</v>
@@ -33362,7 +33362,7 @@
         <v>0.0</v>
       </c>
       <c r="H900" t="n">
-        <v>1296.025</v>
+        <v>1264.285</v>
       </c>
       <c r="I900" t="n">
         <v>0.0</v>
@@ -33390,7 +33390,7 @@
         </is>
       </c>
       <c r="E901" t="n">
-        <v>3097.996</v>
+        <v>3094.2619999999997</v>
       </c>
       <c r="F901" t="n">
         <v>0.622</v>
@@ -33399,7 +33399,7 @@
         <v>1.245</v>
       </c>
       <c r="H901" t="n">
-        <v>3097.996</v>
+        <v>3094.2619999999997</v>
       </c>
       <c r="I901" t="n">
         <v>0.0</v>
@@ -33427,7 +33427,7 @@
         </is>
       </c>
       <c r="E902" t="n">
-        <v>1871.991</v>
+        <v>1867.013</v>
       </c>
       <c r="F902" t="n">
         <v>1.245</v>
@@ -33436,7 +33436,7 @@
         <v>0.0</v>
       </c>
       <c r="H902" t="n">
-        <v>1871.991</v>
+        <v>1867.013</v>
       </c>
       <c r="I902" t="n">
         <v>0.0</v>
@@ -34056,7 +34056,7 @@
         </is>
       </c>
       <c r="E919" t="n">
-        <v>4499.299</v>
+        <v>4461.428</v>
       </c>
       <c r="F919" t="n">
         <v>0.211</v>
@@ -34065,7 +34065,7 @@
         <v>1.262</v>
       </c>
       <c r="H919" t="n">
-        <v>4499.299</v>
+        <v>4461.428</v>
       </c>
       <c r="I919" t="n">
         <v>0.0</v>
@@ -34093,7 +34093,7 @@
         </is>
       </c>
       <c r="E920" t="n">
-        <v>790.263</v>
+        <v>765.12</v>
       </c>
       <c r="F920" t="n">
         <v>0.0</v>
@@ -34102,7 +34102,7 @@
         <v>0.0</v>
       </c>
       <c r="H920" t="n">
-        <v>790.263</v>
+        <v>765.12</v>
       </c>
       <c r="I920" t="n">
         <v>0.0</v>
@@ -34130,7 +34130,7 @@
         </is>
       </c>
       <c r="E921" t="n">
-        <v>2390.776</v>
+        <v>2284.623</v>
       </c>
       <c r="F921" t="n">
         <v>0.0</v>
@@ -34139,7 +34139,7 @@
         <v>11.539000000000001</v>
       </c>
       <c r="H921" t="n">
-        <v>2390.776</v>
+        <v>2284.623</v>
       </c>
       <c r="I921" t="n">
         <v>0.0</v>
@@ -34241,7 +34241,7 @@
         </is>
       </c>
       <c r="E924" t="n">
-        <v>3283.857</v>
+        <v>3272.318</v>
       </c>
       <c r="F924" t="n">
         <v>0.0</v>
@@ -34250,7 +34250,7 @@
         <v>2.3080000000000003</v>
       </c>
       <c r="H924" t="n">
-        <v>3283.857</v>
+        <v>3272.318</v>
       </c>
       <c r="I924" t="n">
         <v>0.0</v>
@@ -34463,16 +34463,16 @@
         </is>
       </c>
       <c r="E930" t="n">
-        <v>8528.472</v>
+        <v>8636.605</v>
       </c>
       <c r="F930" t="n">
         <v>2.663</v>
       </c>
       <c r="G930" t="n">
-        <v>128.102</v>
+        <v>57.098000000000006</v>
       </c>
       <c r="H930" t="n">
-        <v>8528.472</v>
+        <v>8636.605</v>
       </c>
       <c r="I930" t="n">
         <v>0.0</v>
@@ -34611,7 +34611,7 @@
         </is>
       </c>
       <c r="E934" t="n">
-        <v>1828.946</v>
+        <v>1828.945</v>
       </c>
       <c r="F934" t="n">
         <v>0.0</v>
@@ -34620,7 +34620,7 @@
         <v>1.183</v>
       </c>
       <c r="H934" t="n">
-        <v>1828.946</v>
+        <v>1828.945</v>
       </c>
       <c r="I934" t="n">
         <v>0.0</v>
@@ -34685,7 +34685,7 @@
         </is>
       </c>
       <c r="E936" t="n">
-        <v>169.621</v>
+        <v>212.827</v>
       </c>
       <c r="F936" t="n">
         <v>10.401</v>
@@ -34694,7 +34694,7 @@
         <v>0.0</v>
       </c>
       <c r="H936" t="n">
-        <v>169.621</v>
+        <v>212.827</v>
       </c>
       <c r="I936" t="n">
         <v>0.0</v>
@@ -35055,7 +35055,7 @@
         </is>
       </c>
       <c r="E946" t="n">
-        <v>1413.107</v>
+        <v>1387.879</v>
       </c>
       <c r="F946" t="n">
         <v>58.132999999999996</v>
@@ -35064,7 +35064,7 @@
         <v>0.0</v>
       </c>
       <c r="H946" t="n">
-        <v>1413.107</v>
+        <v>1387.879</v>
       </c>
       <c r="I946" t="n">
         <v>0.0</v>
@@ -35092,7 +35092,7 @@
         </is>
       </c>
       <c r="E947" t="n">
-        <v>731.788</v>
+        <v>810.395</v>
       </c>
       <c r="F947" t="n">
         <v>2.007</v>
@@ -35101,7 +35101,7 @@
         <v>0.0</v>
       </c>
       <c r="H947" t="n">
-        <v>731.788</v>
+        <v>810.395</v>
       </c>
       <c r="I947" t="n">
         <v>0.0</v>
@@ -35166,7 +35166,7 @@
         </is>
       </c>
       <c r="E949" t="n">
-        <v>1899.983</v>
+        <v>1899.982</v>
       </c>
       <c r="F949" t="n">
         <v>0.0</v>
@@ -35175,7 +35175,7 @@
         <v>0.0</v>
       </c>
       <c r="H949" t="n">
-        <v>1899.983</v>
+        <v>1899.982</v>
       </c>
       <c r="I949" t="n">
         <v>0.0</v>
@@ -35203,7 +35203,7 @@
         </is>
       </c>
       <c r="E950" t="n">
-        <v>5360.0</v>
+        <v>5200.0</v>
       </c>
       <c r="F950" t="n">
         <v>0.0</v>
@@ -35212,7 +35212,7 @@
         <v>180.0</v>
       </c>
       <c r="H950" t="n">
-        <v>5360.0</v>
+        <v>5200.0</v>
       </c>
       <c r="I950" t="n">
         <v>0.0</v>
@@ -35610,16 +35610,16 @@
         </is>
       </c>
       <c r="E961" t="n">
-        <v>0.0</v>
+        <v>79.88</v>
       </c>
       <c r="F961" t="n">
         <v>0.599</v>
       </c>
       <c r="G961" t="n">
-        <v>423.36400000000003</v>
+        <v>343.48400000000004</v>
       </c>
       <c r="H961" t="n">
-        <v>0.0</v>
+        <v>79.88</v>
       </c>
       <c r="I961" t="n">
         <v>0.0</v>
@@ -36276,7 +36276,7 @@
         </is>
       </c>
       <c r="E979" t="n">
-        <v>2736.533</v>
+        <v>2879.333</v>
       </c>
       <c r="F979" t="n">
         <v>21.7</v>
@@ -36285,7 +36285,7 @@
         <v>12.6</v>
       </c>
       <c r="H979" t="n">
-        <v>2736.533</v>
+        <v>2879.333</v>
       </c>
       <c r="I979" t="n">
         <v>0.0</v>
@@ -36313,7 +36313,7 @@
         </is>
       </c>
       <c r="E980" t="n">
-        <v>1469.924</v>
+        <v>1364.186</v>
       </c>
       <c r="F980" t="n">
         <v>42.467999999999996</v>
@@ -36322,7 +36322,7 @@
         <v>0.867</v>
       </c>
       <c r="H980" t="n">
-        <v>1469.924</v>
+        <v>1364.186</v>
       </c>
       <c r="I980" t="n">
         <v>0.0</v>
@@ -36350,7 +36350,7 @@
         </is>
       </c>
       <c r="E981" t="n">
-        <v>3613.524</v>
+        <v>3599.991</v>
       </c>
       <c r="F981" t="n">
         <v>20.301</v>
@@ -36359,7 +36359,7 @@
         <v>8.7</v>
       </c>
       <c r="H981" t="n">
-        <v>3613.524</v>
+        <v>3599.991</v>
       </c>
       <c r="I981" t="n">
         <v>0.0</v>
@@ -36430,7 +36430,7 @@
         <v>0.0</v>
       </c>
       <c r="G983" t="n">
-        <v>0.0</v>
+        <v>1010.16</v>
       </c>
       <c r="H983" t="n">
         <v>1370.28</v>
@@ -36572,7 +36572,7 @@
         </is>
       </c>
       <c r="E987" t="n">
-        <v>0.0</v>
+        <v>618.5699999999999</v>
       </c>
       <c r="F987" t="n">
         <v>0.0</v>
@@ -36581,7 +36581,7 @@
         <v>0.0</v>
       </c>
       <c r="H987" t="n">
-        <v>0.0</v>
+        <v>618.5699999999999</v>
       </c>
       <c r="I987" t="n">
         <v>0.0</v>
@@ -36646,7 +36646,7 @@
         </is>
       </c>
       <c r="E989" t="n">
-        <v>824.76</v>
+        <v>927.855</v>
       </c>
       <c r="F989" t="n">
         <v>0.0</v>
@@ -36655,7 +36655,7 @@
         <v>0.0</v>
       </c>
       <c r="H989" t="n">
-        <v>824.76</v>
+        <v>927.855</v>
       </c>
       <c r="I989" t="n">
         <v>0.0</v>
@@ -36831,7 +36831,7 @@
         </is>
       </c>
       <c r="E994" t="n">
-        <v>0.0</v>
+        <v>927.855</v>
       </c>
       <c r="F994" t="n">
         <v>0.0</v>
@@ -36840,7 +36840,7 @@
         <v>0.0</v>
       </c>
       <c r="H994" t="n">
-        <v>0.0</v>
+        <v>927.855</v>
       </c>
       <c r="I994" t="n">
         <v>0.0</v>
@@ -36979,7 +36979,7 @@
         </is>
       </c>
       <c r="E998" t="n">
-        <v>98.965</v>
+        <v>75.256</v>
       </c>
       <c r="F998" t="n">
         <v>0.0</v>
@@ -36988,7 +36988,7 @@
         <v>0.0</v>
       </c>
       <c r="H998" t="n">
-        <v>98.965</v>
+        <v>75.256</v>
       </c>
       <c r="I998" t="n">
         <v>0.0</v>
@@ -37016,7 +37016,7 @@
         </is>
       </c>
       <c r="E999" t="n">
-        <v>0.0</v>
+        <v>587.613</v>
       </c>
       <c r="F999" t="n">
         <v>0.0</v>
@@ -37025,7 +37025,7 @@
         <v>0.0</v>
       </c>
       <c r="H999" t="n">
-        <v>0.0</v>
+        <v>587.613</v>
       </c>
       <c r="I999" t="n">
         <v>0.0</v>
@@ -37127,7 +37127,7 @@
         </is>
       </c>
       <c r="E1002" t="n">
-        <v>0.0</v>
+        <v>927.855</v>
       </c>
       <c r="F1002" t="n">
         <v>0.0</v>
@@ -37136,7 +37136,7 @@
         <v>0.0</v>
       </c>
       <c r="H1002" t="n">
-        <v>0.0</v>
+        <v>927.855</v>
       </c>
       <c r="I1002" t="n">
         <v>0.0</v>
@@ -37238,7 +37238,7 @@
         </is>
       </c>
       <c r="E1005" t="n">
-        <v>0.0</v>
+        <v>881.419</v>
       </c>
       <c r="F1005" t="n">
         <v>0.0</v>
@@ -37247,7 +37247,7 @@
         <v>0.0</v>
       </c>
       <c r="H1005" t="n">
-        <v>0.0</v>
+        <v>881.419</v>
       </c>
       <c r="I1005" t="n">
         <v>0.0</v>
@@ -37571,7 +37571,7 @@
         </is>
       </c>
       <c r="E1014" t="n">
-        <v>2306.0584</v>
+        <v>1.498</v>
       </c>
       <c r="F1014" t="n">
         <v>1451.595</v>
@@ -37583,7 +37583,7 @@
         <v>1.498</v>
       </c>
       <c r="I1014" t="n">
-        <v>2304.5604</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1015">
@@ -37608,7 +37608,7 @@
         </is>
       </c>
       <c r="E1015" t="n">
-        <v>5694.979</v>
+        <v>5573.399</v>
       </c>
       <c r="F1015" t="n">
         <v>68.241</v>
@@ -37617,7 +37617,7 @@
         <v>47.885999999999996</v>
       </c>
       <c r="H1015" t="n">
-        <v>5694.979</v>
+        <v>5573.399</v>
       </c>
       <c r="I1015" t="n">
         <v>0.0</v>
@@ -37645,7 +37645,7 @@
         </is>
       </c>
       <c r="E1016" t="n">
-        <v>2289.6</v>
+        <v>2181.6</v>
       </c>
       <c r="F1016" t="n">
         <v>0.0</v>
@@ -37654,7 +37654,7 @@
         <v>0.0</v>
       </c>
       <c r="H1016" t="n">
-        <v>2289.6</v>
+        <v>2181.6</v>
       </c>
       <c r="I1016" t="n">
         <v>0.0</v>
@@ -37682,7 +37682,7 @@
         </is>
       </c>
       <c r="E1017" t="n">
-        <v>518.465</v>
+        <v>518.464</v>
       </c>
       <c r="F1017" t="n">
         <v>0.0</v>
@@ -37691,7 +37691,7 @@
         <v>0.0</v>
       </c>
       <c r="H1017" t="n">
-        <v>518.465</v>
+        <v>518.464</v>
       </c>
       <c r="I1017" t="n">
         <v>0.0</v>
@@ -37904,7 +37904,7 @@
         </is>
       </c>
       <c r="E1023" t="n">
-        <v>3261.13</v>
+        <v>5563.919</v>
       </c>
       <c r="F1023" t="n">
         <v>0.0</v>
@@ -37913,10 +37913,10 @@
         <v>0.0</v>
       </c>
       <c r="H1023" t="n">
-        <v>3261.13</v>
+        <v>3004.079</v>
       </c>
       <c r="I1023" t="n">
-        <v>0.0</v>
+        <v>2559.84</v>
       </c>
     </row>
     <row r="1024">
@@ -37941,7 +37941,7 @@
         </is>
       </c>
       <c r="E1024" t="n">
-        <v>4296.537</v>
+        <v>7299.579</v>
       </c>
       <c r="F1024" t="n">
         <v>0.8</v>
@@ -37950,10 +37950,10 @@
         <v>800.1</v>
       </c>
       <c r="H1024" t="n">
-        <v>4296.537</v>
+        <v>4163.187</v>
       </c>
       <c r="I1024" t="n">
-        <v>0.0</v>
+        <v>3136.392</v>
       </c>
     </row>
     <row r="1025">
@@ -38052,7 +38052,7 @@
         </is>
       </c>
       <c r="E1027" t="n">
-        <v>1905.772</v>
+        <v>1905.773</v>
       </c>
       <c r="F1027" t="n">
         <v>0.0</v>
@@ -38061,7 +38061,7 @@
         <v>8.521</v>
       </c>
       <c r="H1027" t="n">
-        <v>1905.772</v>
+        <v>1905.773</v>
       </c>
       <c r="I1027" t="n">
         <v>0.0</v>
@@ -38126,7 +38126,7 @@
         </is>
       </c>
       <c r="E1029" t="n">
-        <v>3480.08</v>
+        <v>3592.6528</v>
       </c>
       <c r="F1029" t="n">
         <v>14.497</v>
@@ -38135,10 +38135,10 @@
         <v>12.426</v>
       </c>
       <c r="H1029" t="n">
-        <v>3480.08</v>
+        <v>3471.946</v>
       </c>
       <c r="I1029" t="n">
-        <v>0.0</v>
+        <v>120.7068</v>
       </c>
     </row>
     <row r="1030">
@@ -38163,7 +38163,7 @@
         </is>
       </c>
       <c r="E1030" t="n">
-        <v>6526.451</v>
+        <v>6509.883</v>
       </c>
       <c r="F1030" t="n">
         <v>1.183</v>
@@ -38172,7 +38172,7 @@
         <v>1.479</v>
       </c>
       <c r="H1030" t="n">
-        <v>6526.451</v>
+        <v>6509.883</v>
       </c>
       <c r="I1030" t="n">
         <v>0.0</v>
@@ -38644,16 +38644,16 @@
         </is>
       </c>
       <c r="E1043" t="n">
-        <v>0.2</v>
+        <v>479.48</v>
       </c>
       <c r="F1043" t="n">
         <v>0.0</v>
       </c>
       <c r="G1043" t="n">
-        <v>694.956</v>
+        <v>215.67600000000002</v>
       </c>
       <c r="H1043" t="n">
-        <v>0.2</v>
+        <v>479.48</v>
       </c>
       <c r="I1043" t="n">
         <v>0.0</v>
@@ -38681,7 +38681,7 @@
         </is>
       </c>
       <c r="E1044" t="n">
-        <v>323.079</v>
+        <v>295.384</v>
       </c>
       <c r="F1044" t="n">
         <v>0.0</v>
@@ -38690,7 +38690,7 @@
         <v>20.769</v>
       </c>
       <c r="H1044" t="n">
-        <v>323.079</v>
+        <v>295.384</v>
       </c>
       <c r="I1044" t="n">
         <v>0.0</v>
@@ -38903,7 +38903,7 @@
         </is>
       </c>
       <c r="E1050" t="n">
-        <v>163.89999999999998</v>
+        <v>705.0999999999999</v>
       </c>
       <c r="F1050" t="n">
         <v>0.0</v>
@@ -38912,7 +38912,7 @@
         <v>0.0</v>
       </c>
       <c r="H1050" t="n">
-        <v>163.89999999999998</v>
+        <v>705.0999999999999</v>
       </c>
       <c r="I1050" t="n">
         <v>0.0</v>
@@ -38940,7 +38940,7 @@
         </is>
       </c>
       <c r="E1051" t="n">
-        <v>823.318</v>
+        <v>806.516</v>
       </c>
       <c r="F1051" t="n">
         <v>2.8</v>
@@ -38949,7 +38949,7 @@
         <v>0.0</v>
       </c>
       <c r="H1051" t="n">
-        <v>823.318</v>
+        <v>806.516</v>
       </c>
       <c r="I1051" t="n">
         <v>0.0</v>
@@ -39051,7 +39051,7 @@
         </is>
       </c>
       <c r="E1054" t="n">
-        <v>5374.962</v>
+        <v>5220.172</v>
       </c>
       <c r="F1054" t="n">
         <v>0.0</v>
@@ -39060,7 +39060,7 @@
         <v>0.0</v>
       </c>
       <c r="H1054" t="n">
-        <v>5374.962</v>
+        <v>5220.172</v>
       </c>
       <c r="I1054" t="n">
         <v>0.0</v>
@@ -39125,7 +39125,7 @@
         </is>
       </c>
       <c r="E1056" t="n">
-        <v>5294.899</v>
+        <v>7606.08</v>
       </c>
       <c r="F1056" t="n">
         <v>0.0</v>
@@ -39134,10 +39134,10 @@
         <v>0.0</v>
       </c>
       <c r="H1056" t="n">
-        <v>5294.899</v>
+        <v>5257.536</v>
       </c>
       <c r="I1056" t="n">
-        <v>0.0</v>
+        <v>2348.544</v>
       </c>
     </row>
     <row r="1057">
@@ -39310,7 +39310,7 @@
         </is>
       </c>
       <c r="E1061" t="n">
-        <v>3519.991</v>
+        <v>3477.343</v>
       </c>
       <c r="F1061" t="n">
         <v>155.054</v>
@@ -39319,7 +39319,7 @@
         <v>47.608</v>
       </c>
       <c r="H1061" t="n">
-        <v>3519.991</v>
+        <v>3477.343</v>
       </c>
       <c r="I1061" t="n">
         <v>0.0</v>
@@ -39347,7 +39347,7 @@
         </is>
       </c>
       <c r="E1062" t="n">
-        <v>7023.45</v>
+        <v>6689.534</v>
       </c>
       <c r="F1062" t="n">
         <v>919.747</v>
@@ -39356,7 +39356,7 @@
         <v>15.54</v>
       </c>
       <c r="H1062" t="n">
-        <v>7023.45</v>
+        <v>6689.534</v>
       </c>
       <c r="I1062" t="n">
         <v>0.0</v>
@@ -39384,7 +39384,7 @@
         </is>
       </c>
       <c r="E1063" t="n">
-        <v>3949.779</v>
+        <v>3905.146</v>
       </c>
       <c r="F1063" t="n">
         <v>845.364</v>
@@ -39393,7 +39393,7 @@
         <v>0.0</v>
       </c>
       <c r="H1063" t="n">
-        <v>3949.779</v>
+        <v>3905.146</v>
       </c>
       <c r="I1063" t="n">
         <v>0.0</v>
@@ -39421,7 +39421,7 @@
         </is>
       </c>
       <c r="E1064" t="n">
-        <v>16436.519</v>
+        <v>16379.324</v>
       </c>
       <c r="F1064" t="n">
         <v>1451.699</v>
@@ -39430,7 +39430,7 @@
         <v>0.0</v>
       </c>
       <c r="H1064" t="n">
-        <v>16436.519</v>
+        <v>16379.324</v>
       </c>
       <c r="I1064" t="n">
         <v>0.0</v>
@@ -39495,7 +39495,7 @@
         </is>
       </c>
       <c r="E1066" t="n">
-        <v>8182.231000000001</v>
+        <v>8076.105</v>
       </c>
       <c r="F1066" t="n">
         <v>1986.951</v>
@@ -39504,7 +39504,7 @@
         <v>3.967</v>
       </c>
       <c r="H1066" t="n">
-        <v>8182.231000000001</v>
+        <v>8076.105</v>
       </c>
       <c r="I1066" t="n">
         <v>0.0</v>
@@ -39569,7 +39569,7 @@
         </is>
       </c>
       <c r="E1068" t="n">
-        <v>5473.232</v>
+        <v>5407.771</v>
       </c>
       <c r="F1068" t="n">
         <v>929.0070000000001</v>
@@ -39578,7 +39578,7 @@
         <v>11.902</v>
       </c>
       <c r="H1068" t="n">
-        <v>5473.232</v>
+        <v>5407.771</v>
       </c>
       <c r="I1068" t="n">
         <v>0.0</v>
@@ -39606,7 +39606,7 @@
         </is>
       </c>
       <c r="E1069" t="n">
-        <v>34300.7244</v>
+        <v>40078.965599999996</v>
       </c>
       <c r="F1069" t="n">
         <v>0.0</v>
@@ -39618,7 +39618,7 @@
         <v>18870.3</v>
       </c>
       <c r="I1069" t="n">
-        <v>15430.4244</v>
+        <v>21208.6656</v>
       </c>
     </row>
     <row r="1070">
@@ -39643,7 +39643,7 @@
         </is>
       </c>
       <c r="E1070" t="n">
-        <v>16881.987</v>
+        <v>17190.0344</v>
       </c>
       <c r="F1070" t="n">
         <v>0.0</v>
@@ -39652,10 +39652,10 @@
         <v>51.341</v>
       </c>
       <c r="H1070" t="n">
-        <v>16881.987</v>
+        <v>16881.986</v>
       </c>
       <c r="I1070" t="n">
-        <v>0.0</v>
+        <v>308.0484</v>
       </c>
     </row>
     <row r="1071">
@@ -39680,7 +39680,7 @@
         </is>
       </c>
       <c r="E1071" t="n">
-        <v>25053.828999999998</v>
+        <v>25565.612</v>
       </c>
       <c r="F1071" t="n">
         <v>2795.292</v>
@@ -39689,7 +39689,7 @@
         <v>3.967</v>
       </c>
       <c r="H1071" t="n">
-        <v>25053.828999999998</v>
+        <v>25565.612</v>
       </c>
       <c r="I1071" t="n">
         <v>0.0</v>
@@ -39717,7 +39717,7 @@
         </is>
       </c>
       <c r="E1072" t="n">
-        <v>18255.527</v>
+        <v>17601.25</v>
       </c>
       <c r="F1072" t="n">
         <v>1890.418</v>
@@ -39726,7 +39726,7 @@
         <v>0.0</v>
       </c>
       <c r="H1072" t="n">
-        <v>18255.527</v>
+        <v>17601.25</v>
       </c>
       <c r="I1072" t="n">
         <v>0.0</v>
@@ -39865,7 +39865,7 @@
         </is>
       </c>
       <c r="E1076" t="n">
-        <v>250.745</v>
+        <v>189.926</v>
       </c>
       <c r="F1076" t="n">
         <v>3.201</v>
@@ -39874,7 +39874,7 @@
         <v>0.0</v>
       </c>
       <c r="H1076" t="n">
-        <v>250.745</v>
+        <v>189.926</v>
       </c>
       <c r="I1076" t="n">
         <v>0.0</v>
@@ -39902,7 +39902,7 @@
         </is>
       </c>
       <c r="E1077" t="n">
-        <v>1320.0</v>
+        <v>936.0</v>
       </c>
       <c r="F1077" t="n">
         <v>0.0</v>
@@ -39911,7 +39911,7 @@
         <v>0.0</v>
       </c>
       <c r="H1077" t="n">
-        <v>1320.0</v>
+        <v>936.0</v>
       </c>
       <c r="I1077" t="n">
         <v>0.0</v>
@@ -40161,7 +40161,7 @@
         </is>
       </c>
       <c r="E1084" t="n">
-        <v>786.0</v>
+        <v>831.0</v>
       </c>
       <c r="F1084" t="n">
         <v>0.0</v>
@@ -40170,7 +40170,7 @@
         <v>0.0</v>
       </c>
       <c r="H1084" t="n">
-        <v>786.0</v>
+        <v>831.0</v>
       </c>
       <c r="I1084" t="n">
         <v>0.0</v>
@@ -40198,7 +40198,7 @@
         </is>
       </c>
       <c r="E1085" t="n">
-        <v>3658.5359999999996</v>
+        <v>3654.539</v>
       </c>
       <c r="F1085" t="n">
         <v>0.0</v>
@@ -40207,7 +40207,7 @@
         <v>0.0</v>
       </c>
       <c r="H1085" t="n">
-        <v>3658.5359999999996</v>
+        <v>3654.539</v>
       </c>
       <c r="I1085" t="n">
         <v>0.0</v>
@@ -40241,7 +40241,7 @@
         <v>0.0</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.0</v>
+        <v>152.03</v>
       </c>
       <c r="H1086" t="n">
         <v>1156.231</v>
@@ -40272,7 +40272,7 @@
         </is>
       </c>
       <c r="E1087" t="n">
-        <v>103.99</v>
+        <v>77.326</v>
       </c>
       <c r="F1087" t="n">
         <v>0.0</v>
@@ -40281,7 +40281,7 @@
         <v>0.0</v>
       </c>
       <c r="H1087" t="n">
-        <v>103.99</v>
+        <v>77.326</v>
       </c>
       <c r="I1087" t="n">
         <v>0.0</v>
@@ -40346,7 +40346,7 @@
         </is>
       </c>
       <c r="E1089" t="n">
-        <v>2606.959</v>
+        <v>3102.76</v>
       </c>
       <c r="F1089" t="n">
         <v>0.0</v>
@@ -40355,7 +40355,7 @@
         <v>0.0</v>
       </c>
       <c r="H1089" t="n">
-        <v>2606.959</v>
+        <v>3102.76</v>
       </c>
       <c r="I1089" t="n">
         <v>0.0</v>
@@ -40383,7 +40383,7 @@
         </is>
       </c>
       <c r="E1090" t="n">
-        <v>3808.477</v>
+        <v>3788.485</v>
       </c>
       <c r="F1090" t="n">
         <v>0.0</v>
@@ -40392,7 +40392,7 @@
         <v>0.0</v>
       </c>
       <c r="H1090" t="n">
-        <v>3808.477</v>
+        <v>3788.485</v>
       </c>
       <c r="I1090" t="n">
         <v>0.0</v>
@@ -40426,7 +40426,7 @@
         <v>0.0</v>
       </c>
       <c r="G1091" t="n">
-        <v>0.0</v>
+        <v>740.148</v>
       </c>
       <c r="H1091" t="n">
         <v>9165.832</v>
@@ -40457,7 +40457,7 @@
         </is>
       </c>
       <c r="E1092" t="n">
-        <v>8695.517000000002</v>
+        <v>13044.675100000002</v>
       </c>
       <c r="F1092" t="n">
         <v>0.0</v>
@@ -40466,10 +40466,10 @@
         <v>4355.459</v>
       </c>
       <c r="H1092" t="n">
-        <v>8695.517000000002</v>
+        <v>8690.615000000002</v>
       </c>
       <c r="I1092" t="n">
-        <v>0.0</v>
+        <v>4354.060100000001</v>
       </c>
     </row>
     <row r="1093">
@@ -40605,7 +40605,7 @@
         </is>
       </c>
       <c r="E1096" t="n">
-        <v>133.585</v>
+        <v>455.179</v>
       </c>
       <c r="F1096" t="n">
         <v>0.0</v>
@@ -40614,7 +40614,7 @@
         <v>0.0</v>
       </c>
       <c r="H1096" t="n">
-        <v>133.585</v>
+        <v>455.179</v>
       </c>
       <c r="I1096" t="n">
         <v>0.0</v>
@@ -41271,7 +41271,7 @@
         </is>
       </c>
       <c r="E1114" t="n">
-        <v>2468.952</v>
+        <v>2457.09</v>
       </c>
       <c r="F1114" t="n">
         <v>0.0</v>
@@ -41280,7 +41280,7 @@
         <v>0.0</v>
       </c>
       <c r="H1114" t="n">
-        <v>2468.952</v>
+        <v>2457.09</v>
       </c>
       <c r="I1114" t="n">
         <v>0.0</v>
@@ -41308,7 +41308,7 @@
         </is>
       </c>
       <c r="E1115" t="n">
-        <v>2460.866</v>
+        <v>2458.707</v>
       </c>
       <c r="F1115" t="n">
         <v>0.09000000000000001</v>
@@ -41317,7 +41317,7 @@
         <v>0.0</v>
       </c>
       <c r="H1115" t="n">
-        <v>2460.866</v>
+        <v>2458.707</v>
       </c>
       <c r="I1115" t="n">
         <v>0.0</v>
@@ -41382,7 +41382,7 @@
         </is>
       </c>
       <c r="E1117" t="n">
-        <v>70.161</v>
+        <v>66.414</v>
       </c>
       <c r="F1117" t="n">
         <v>0.20900000000000002</v>
@@ -41391,7 +41391,7 @@
         <v>0.0</v>
       </c>
       <c r="H1117" t="n">
-        <v>70.161</v>
+        <v>66.414</v>
       </c>
       <c r="I1117" t="n">
         <v>0.0</v>
@@ -41419,7 +41419,7 @@
         </is>
       </c>
       <c r="E1118" t="n">
-        <v>2814.415</v>
+        <v>2811.4700000000003</v>
       </c>
       <c r="F1118" t="n">
         <v>0.526</v>
@@ -41428,7 +41428,7 @@
         <v>0.0</v>
       </c>
       <c r="H1118" t="n">
-        <v>2814.415</v>
+        <v>2811.4700000000003</v>
       </c>
       <c r="I1118" t="n">
         <v>0.0</v>
@@ -41493,7 +41493,7 @@
         </is>
       </c>
       <c r="E1120" t="n">
-        <v>200.083</v>
+        <v>198.00099999999998</v>
       </c>
       <c r="F1120" t="n">
         <v>0.625</v>
@@ -41502,7 +41502,7 @@
         <v>0.0</v>
       </c>
       <c r="H1120" t="n">
-        <v>200.083</v>
+        <v>198.00099999999998</v>
       </c>
       <c r="I1120" t="n">
         <v>0.0</v>
@@ -41604,7 +41604,7 @@
         </is>
       </c>
       <c r="E1123" t="n">
-        <v>487.235</v>
+        <v>487.236</v>
       </c>
       <c r="F1123" t="n">
         <v>0.0</v>
@@ -41613,7 +41613,7 @@
         <v>0.0</v>
       </c>
       <c r="H1123" t="n">
-        <v>487.235</v>
+        <v>487.236</v>
       </c>
       <c r="I1123" t="n">
         <v>0.0</v>
@@ -41715,7 +41715,7 @@
         </is>
       </c>
       <c r="E1126" t="n">
-        <v>22460.8</v>
+        <v>22152.0</v>
       </c>
       <c r="F1126" t="n">
         <v>7.2</v>
@@ -41724,7 +41724,7 @@
         <v>0.0</v>
       </c>
       <c r="H1126" t="n">
-        <v>22460.8</v>
+        <v>22152.0</v>
       </c>
       <c r="I1126" t="n">
         <v>0.0</v>
@@ -41795,7 +41795,7 @@
         <v>0.0</v>
       </c>
       <c r="G1128" t="n">
-        <v>658.526</v>
+        <v>678.542</v>
       </c>
       <c r="H1128" t="n">
         <v>1459.166</v>
@@ -41832,7 +41832,7 @@
         <v>0.0</v>
       </c>
       <c r="G1129" t="n">
-        <v>0.0</v>
+        <v>100.08</v>
       </c>
       <c r="H1129" t="n">
         <v>1883.505</v>
@@ -41863,7 +41863,7 @@
         </is>
       </c>
       <c r="E1130" t="n">
-        <v>1445.156</v>
+        <v>1345.076</v>
       </c>
       <c r="F1130" t="n">
         <v>0.0</v>
@@ -41872,7 +41872,7 @@
         <v>0.0</v>
       </c>
       <c r="H1130" t="n">
-        <v>1445.156</v>
+        <v>1345.076</v>
       </c>
       <c r="I1130" t="n">
         <v>0.0</v>
@@ -42196,7 +42196,7 @@
         </is>
       </c>
       <c r="E1139" t="n">
-        <v>911.0780000000001</v>
+        <v>908.277</v>
       </c>
       <c r="F1139" t="n">
         <v>0.0</v>
@@ -42205,7 +42205,7 @@
         <v>0.0</v>
       </c>
       <c r="H1139" t="n">
-        <v>911.0780000000001</v>
+        <v>908.277</v>
       </c>
       <c r="I1139" t="n">
         <v>0.0</v>
@@ -42233,7 +42233,7 @@
         </is>
       </c>
       <c r="E1140" t="n">
-        <v>1463.231</v>
+        <v>1406.755</v>
       </c>
       <c r="F1140" t="n">
         <v>0.0</v>
@@ -42242,7 +42242,7 @@
         <v>0.0</v>
       </c>
       <c r="H1140" t="n">
-        <v>1463.231</v>
+        <v>1406.755</v>
       </c>
       <c r="I1140" t="n">
         <v>0.0</v>
@@ -42270,7 +42270,7 @@
         </is>
       </c>
       <c r="E1141" t="n">
-        <v>4247.2660000000005</v>
+        <v>4238.709</v>
       </c>
       <c r="F1141" t="n">
         <v>0.428</v>
@@ -42279,7 +42279,7 @@
         <v>0.0</v>
       </c>
       <c r="H1141" t="n">
-        <v>4247.2660000000005</v>
+        <v>4238.709</v>
       </c>
       <c r="I1141" t="n">
         <v>0.0</v>
@@ -42307,7 +42307,7 @@
         </is>
       </c>
       <c r="E1142" t="n">
-        <v>346.129</v>
+        <v>340.994</v>
       </c>
       <c r="F1142" t="n">
         <v>0.856</v>
@@ -42316,7 +42316,7 @@
         <v>0.0</v>
       </c>
       <c r="H1142" t="n">
-        <v>346.129</v>
+        <v>340.994</v>
       </c>
       <c r="I1142" t="n">
         <v>0.0</v>
@@ -42418,7 +42418,7 @@
         </is>
       </c>
       <c r="E1145" t="n">
-        <v>2547.5209999999997</v>
+        <v>2516.716</v>
       </c>
       <c r="F1145" t="n">
         <v>10.265</v>
@@ -42427,7 +42427,7 @@
         <v>0.0</v>
       </c>
       <c r="H1145" t="n">
-        <v>2547.5209999999997</v>
+        <v>2516.716</v>
       </c>
       <c r="I1145" t="n">
         <v>0.0</v>
@@ -42529,16 +42529,16 @@
         </is>
       </c>
       <c r="E1148" t="n">
-        <v>8452.199</v>
+        <v>8220.741</v>
       </c>
       <c r="F1148" t="n">
         <v>51.098</v>
       </c>
       <c r="G1148" t="n">
-        <v>93.097</v>
+        <v>287.223</v>
       </c>
       <c r="H1148" t="n">
-        <v>8452.199</v>
+        <v>8220.741</v>
       </c>
       <c r="I1148" t="n">
         <v>0.0</v>
@@ -42566,16 +42566,16 @@
         </is>
       </c>
       <c r="E1149" t="n">
-        <v>207.948</v>
+        <v>293.26</v>
       </c>
       <c r="F1149" t="n">
         <v>0.0</v>
       </c>
       <c r="G1149" t="n">
-        <v>86.645</v>
+        <v>34.658</v>
       </c>
       <c r="H1149" t="n">
-        <v>207.948</v>
+        <v>293.26</v>
       </c>
       <c r="I1149" t="n">
         <v>0.0</v>
@@ -42603,16 +42603,16 @@
         </is>
       </c>
       <c r="E1150" t="n">
-        <v>8212.351999999999</v>
+        <v>8129.553000000001</v>
       </c>
       <c r="F1150" t="n">
         <v>37.821</v>
       </c>
       <c r="G1150" t="n">
-        <v>7.155</v>
+        <v>9.2</v>
       </c>
       <c r="H1150" t="n">
-        <v>8212.351999999999</v>
+        <v>8129.553000000001</v>
       </c>
       <c r="I1150" t="n">
         <v>0.0</v>
@@ -42640,16 +42640,16 @@
         </is>
       </c>
       <c r="E1151" t="n">
-        <v>10973.056</v>
+        <v>14368.557999999999</v>
       </c>
       <c r="F1151" t="n">
         <v>31.335</v>
       </c>
       <c r="G1151" t="n">
-        <v>4052.869</v>
+        <v>1688.0839999999998</v>
       </c>
       <c r="H1151" t="n">
-        <v>10973.056</v>
+        <v>14368.557999999999</v>
       </c>
       <c r="I1151" t="n">
         <v>0.0</v>
@@ -42677,16 +42677,16 @@
         </is>
       </c>
       <c r="E1152" t="n">
-        <v>12329.2</v>
+        <v>12046.0</v>
       </c>
       <c r="F1152" t="n">
         <v>66.4</v>
       </c>
       <c r="G1152" t="n">
-        <v>529.5999999999999</v>
+        <v>1240.0</v>
       </c>
       <c r="H1152" t="n">
-        <v>12329.2</v>
+        <v>12046.0</v>
       </c>
       <c r="I1152" t="n">
         <v>0.0</v>
@@ -42751,7 +42751,7 @@
         </is>
       </c>
       <c r="E1154" t="n">
-        <v>4354.394</v>
+        <v>7195.8152</v>
       </c>
       <c r="F1154" t="n">
         <v>10.666</v>
@@ -42760,10 +42760,10 @@
         <v>0.0</v>
       </c>
       <c r="H1154" t="n">
-        <v>4354.394</v>
+        <v>4303.196</v>
       </c>
       <c r="I1154" t="n">
-        <v>0.0</v>
+        <v>2892.6192</v>
       </c>
     </row>
     <row r="1155">
@@ -42862,7 +42862,7 @@
         </is>
       </c>
       <c r="E1157" t="n">
-        <v>4097.625</v>
+        <v>4078.492</v>
       </c>
       <c r="F1157" t="n">
         <v>0.0</v>
@@ -42871,7 +42871,7 @@
         <v>0.0</v>
       </c>
       <c r="H1157" t="n">
-        <v>4097.625</v>
+        <v>4078.492</v>
       </c>
       <c r="I1157" t="n">
         <v>0.0</v>
@@ -42899,7 +42899,7 @@
         </is>
       </c>
       <c r="E1158" t="n">
-        <v>343.135</v>
+        <v>339.713</v>
       </c>
       <c r="F1158" t="n">
         <v>0.856</v>
@@ -42908,7 +42908,7 @@
         <v>0.0</v>
       </c>
       <c r="H1158" t="n">
-        <v>343.135</v>
+        <v>339.713</v>
       </c>
       <c r="I1158" t="n">
         <v>0.0</v>
@@ -42936,7 +42936,7 @@
         </is>
       </c>
       <c r="E1159" t="n">
-        <v>598.652</v>
+        <v>427.99</v>
       </c>
       <c r="F1159" t="n">
         <v>0.0</v>
@@ -42945,7 +42945,7 @@
         <v>0.0</v>
       </c>
       <c r="H1159" t="n">
-        <v>598.652</v>
+        <v>427.99</v>
       </c>
       <c r="I1159" t="n">
         <v>0.0</v>
@@ -42973,7 +42973,7 @@
         </is>
       </c>
       <c r="E1160" t="n">
-        <v>449.322</v>
+        <v>413.323</v>
       </c>
       <c r="F1160" t="n">
         <v>0.0</v>
@@ -42982,7 +42982,7 @@
         <v>0.0</v>
       </c>
       <c r="H1160" t="n">
-        <v>449.322</v>
+        <v>413.323</v>
       </c>
       <c r="I1160" t="n">
         <v>0.0</v>
@@ -43010,7 +43010,7 @@
         </is>
       </c>
       <c r="E1161" t="n">
-        <v>733.315</v>
+        <v>675.983</v>
       </c>
       <c r="F1161" t="n">
         <v>0.0</v>
@@ -43019,7 +43019,7 @@
         <v>0.0</v>
       </c>
       <c r="H1161" t="n">
-        <v>733.315</v>
+        <v>675.983</v>
       </c>
       <c r="I1161" t="n">
         <v>0.0</v>
@@ -43047,7 +43047,7 @@
         </is>
       </c>
       <c r="E1162" t="n">
-        <v>5392.8</v>
+        <v>5341.6</v>
       </c>
       <c r="F1162" t="n">
         <v>3.2</v>
@@ -43056,7 +43056,7 @@
         <v>4.0</v>
       </c>
       <c r="H1162" t="n">
-        <v>5392.8</v>
+        <v>5341.6</v>
       </c>
       <c r="I1162" t="n">
         <v>0.0</v>
@@ -43084,7 +43084,7 @@
         </is>
       </c>
       <c r="E1163" t="n">
-        <v>5662.465</v>
+        <v>5575.193</v>
       </c>
       <c r="F1163" t="n">
         <v>0.5670000000000001</v>
@@ -43093,7 +43093,7 @@
         <v>5.1000000000000005</v>
       </c>
       <c r="H1163" t="n">
-        <v>5662.465</v>
+        <v>5575.193</v>
       </c>
       <c r="I1163" t="n">
         <v>0.0</v>
@@ -43121,7 +43121,7 @@
         </is>
       </c>
       <c r="E1164" t="n">
-        <v>8879.444</v>
+        <v>8739.437</v>
       </c>
       <c r="F1164" t="n">
         <v>7.3340000000000005</v>
@@ -43130,7 +43130,7 @@
         <v>20.668</v>
       </c>
       <c r="H1164" t="n">
-        <v>8879.444</v>
+        <v>8739.437</v>
       </c>
       <c r="I1164" t="n">
         <v>0.0</v>
@@ -43306,7 +43306,7 @@
         </is>
       </c>
       <c r="E1169" t="n">
-        <v>6957.0</v>
+        <v>6900.4</v>
       </c>
       <c r="F1169" t="n">
         <v>0.6</v>
@@ -43315,7 +43315,7 @@
         <v>339.2</v>
       </c>
       <c r="H1169" t="n">
-        <v>6957.0</v>
+        <v>6900.4</v>
       </c>
       <c r="I1169" t="n">
         <v>0.0</v>
@@ -43343,7 +43343,7 @@
         </is>
       </c>
       <c r="E1170" t="n">
-        <v>7136.0</v>
+        <v>7315.2</v>
       </c>
       <c r="F1170" t="n">
         <v>0.0</v>
@@ -43355,7 +43355,7 @@
         <v>7136.0</v>
       </c>
       <c r="I1170" t="n">
-        <v>0.0</v>
+        <v>179.2</v>
       </c>
     </row>
     <row r="1171">
@@ -43639,7 +43639,7 @@
         </is>
       </c>
       <c r="E1178" t="n">
-        <v>1922.0</v>
+        <v>1881.1999999999998</v>
       </c>
       <c r="F1178" t="n">
         <v>0.0</v>
@@ -43648,7 +43648,7 @@
         <v>0.0</v>
       </c>
       <c r="H1178" t="n">
-        <v>1922.0</v>
+        <v>1881.1999999999998</v>
       </c>
       <c r="I1178" t="n">
         <v>0.0</v>
@@ -43676,7 +43676,7 @@
         </is>
       </c>
       <c r="E1179" t="n">
-        <v>2189.4</v>
+        <v>2164.7999999999997</v>
       </c>
       <c r="F1179" t="n">
         <v>0.4</v>
@@ -43685,7 +43685,7 @@
         <v>0.0</v>
       </c>
       <c r="H1179" t="n">
-        <v>2189.4</v>
+        <v>2164.7999999999997</v>
       </c>
       <c r="I1179" t="n">
         <v>0.0</v>
@@ -43750,7 +43750,7 @@
         </is>
       </c>
       <c r="E1181" t="n">
-        <v>2202.0</v>
+        <v>2181.6</v>
       </c>
       <c r="F1181" t="n">
         <v>10.0</v>
@@ -43759,7 +43759,7 @@
         <v>0.0</v>
       </c>
       <c r="H1181" t="n">
-        <v>2202.0</v>
+        <v>2181.6</v>
       </c>
       <c r="I1181" t="n">
         <v>0.0</v>
@@ -43787,16 +43787,16 @@
         </is>
       </c>
       <c r="E1182" t="n">
-        <v>2158.67</v>
+        <v>2241.88</v>
       </c>
       <c r="F1182" t="n">
         <v>0.26699999999999996</v>
       </c>
       <c r="G1182" t="n">
-        <v>83.21000000000001</v>
+        <v>0.0</v>
       </c>
       <c r="H1182" t="n">
-        <v>2158.67</v>
+        <v>2241.88</v>
       </c>
       <c r="I1182" t="n">
         <v>0.0</v>
@@ -43824,7 +43824,7 @@
         </is>
       </c>
       <c r="E1183" t="n">
-        <v>1783.2</v>
+        <v>1777.2</v>
       </c>
       <c r="F1183" t="n">
         <v>0.0</v>
@@ -43833,7 +43833,7 @@
         <v>0.0</v>
       </c>
       <c r="H1183" t="n">
-        <v>1783.2</v>
+        <v>1777.2</v>
       </c>
       <c r="I1183" t="n">
         <v>0.0</v>
@@ -43898,7 +43898,7 @@
         </is>
       </c>
       <c r="E1185" t="n">
-        <v>2553.411</v>
+        <v>2553.41</v>
       </c>
       <c r="F1185" t="n">
         <v>0.6669999999999999</v>
@@ -43907,7 +43907,7 @@
         <v>0.0</v>
       </c>
       <c r="H1185" t="n">
-        <v>2553.411</v>
+        <v>2553.41</v>
       </c>
       <c r="I1185" t="n">
         <v>0.0</v>
@@ -43935,7 +43935,7 @@
         </is>
       </c>
       <c r="E1186" t="n">
-        <v>1698.0</v>
+        <v>1624.8</v>
       </c>
       <c r="F1186" t="n">
         <v>3.2</v>
@@ -43944,7 +43944,7 @@
         <v>0.8</v>
       </c>
       <c r="H1186" t="n">
-        <v>1698.0</v>
+        <v>1624.8</v>
       </c>
       <c r="I1186" t="n">
         <v>0.0</v>
@@ -43972,7 +43972,7 @@
         </is>
       </c>
       <c r="E1187" t="n">
-        <v>1888.8</v>
+        <v>1831.2</v>
       </c>
       <c r="F1187" t="n">
         <v>0.0</v>
@@ -43981,7 +43981,7 @@
         <v>0.0</v>
       </c>
       <c r="H1187" t="n">
-        <v>1888.8</v>
+        <v>1831.2</v>
       </c>
       <c r="I1187" t="n">
         <v>0.0</v>
@@ -44052,7 +44052,7 @@
         <v>0.0</v>
       </c>
       <c r="G1189" t="n">
-        <v>2500.592</v>
+        <v>2500.7999999999997</v>
       </c>
       <c r="H1189" t="n">
         <v>0.0</v>
@@ -44120,7 +44120,7 @@
         </is>
       </c>
       <c r="E1191" t="n">
-        <v>3611.252</v>
+        <v>3520.719</v>
       </c>
       <c r="F1191" t="n">
         <v>0.0</v>
@@ -44129,7 +44129,7 @@
         <v>0.0</v>
       </c>
       <c r="H1191" t="n">
-        <v>3611.252</v>
+        <v>3520.719</v>
       </c>
       <c r="I1191" t="n">
         <v>0.0</v>
@@ -44157,7 +44157,7 @@
         </is>
       </c>
       <c r="E1192" t="n">
-        <v>856.8</v>
+        <v>830.4</v>
       </c>
       <c r="F1192" t="n">
         <v>0.4</v>
@@ -44166,7 +44166,7 @@
         <v>0.0</v>
       </c>
       <c r="H1192" t="n">
-        <v>856.8</v>
+        <v>830.4</v>
       </c>
       <c r="I1192" t="n">
         <v>0.0</v>
@@ -44416,7 +44416,7 @@
         </is>
       </c>
       <c r="E1199" t="n">
-        <v>5035.005</v>
+        <v>5032.848</v>
       </c>
       <c r="F1199" t="n">
         <v>0.0</v>
@@ -44425,7 +44425,7 @@
         <v>0.0</v>
       </c>
       <c r="H1199" t="n">
-        <v>5035.005</v>
+        <v>5032.848</v>
       </c>
       <c r="I1199" t="n">
         <v>0.0</v>
@@ -44527,7 +44527,7 @@
         </is>
       </c>
       <c r="E1202" t="n">
-        <v>15.693999999999999</v>
+        <v>0.0</v>
       </c>
       <c r="F1202" t="n">
         <v>0.0</v>
@@ -44536,7 +44536,7 @@
         <v>0.0</v>
       </c>
       <c r="H1202" t="n">
-        <v>15.693999999999999</v>
+        <v>0.0</v>
       </c>
       <c r="I1202" t="n">
         <v>0.0</v>
@@ -44786,7 +44786,7 @@
         </is>
       </c>
       <c r="E1209" t="n">
-        <v>3533.526</v>
+        <v>3532.106</v>
       </c>
       <c r="F1209" t="n">
         <v>0.0</v>
@@ -44795,7 +44795,7 @@
         <v>119.291</v>
       </c>
       <c r="H1209" t="n">
-        <v>3533.526</v>
+        <v>3532.106</v>
       </c>
       <c r="I1209" t="n">
         <v>0.0</v>
@@ -44823,7 +44823,7 @@
         </is>
       </c>
       <c r="E1210" t="n">
-        <v>2489.4880000000003</v>
+        <v>2131.142</v>
       </c>
       <c r="F1210" t="n">
         <v>2.13</v>
@@ -44832,7 +44832,7 @@
         <v>530.42</v>
       </c>
       <c r="H1210" t="n">
-        <v>2489.4880000000003</v>
+        <v>2131.142</v>
       </c>
       <c r="I1210" t="n">
         <v>0.0</v>
@@ -45267,7 +45267,7 @@
         </is>
       </c>
       <c r="E1222" t="n">
-        <v>982.223</v>
+        <v>976.306</v>
       </c>
       <c r="F1222" t="n">
         <v>0.0</v>
@@ -45276,7 +45276,7 @@
         <v>0.0</v>
       </c>
       <c r="H1222" t="n">
-        <v>982.223</v>
+        <v>976.306</v>
       </c>
       <c r="I1222" t="n">
         <v>0.0</v>
@@ -45304,7 +45304,7 @@
         </is>
       </c>
       <c r="E1223" t="n">
-        <v>1828.06</v>
+        <v>1756.9080000000001</v>
       </c>
       <c r="F1223" t="n">
         <v>0.5910000000000001</v>
@@ -45313,7 +45313,7 @@
         <v>1.7750000000000001</v>
       </c>
       <c r="H1223" t="n">
-        <v>1828.06</v>
+        <v>1756.9080000000001</v>
       </c>
       <c r="I1223" t="n">
         <v>0.0</v>
@@ -45341,7 +45341,7 @@
         </is>
       </c>
       <c r="E1224" t="n">
-        <v>5397.71</v>
+        <v>5381.557</v>
       </c>
       <c r="F1224" t="n">
         <v>0.0</v>
@@ -45350,7 +45350,7 @@
         <v>0.0</v>
       </c>
       <c r="H1224" t="n">
-        <v>5397.71</v>
+        <v>5381.557</v>
       </c>
       <c r="I1224" t="n">
         <v>0.0</v>
@@ -45415,7 +45415,7 @@
         </is>
       </c>
       <c r="E1226" t="n">
-        <v>2014.973</v>
+        <v>1535.693</v>
       </c>
       <c r="F1226" t="n">
         <v>0.0</v>
@@ -45424,7 +45424,7 @@
         <v>5.991</v>
       </c>
       <c r="H1226" t="n">
-        <v>2014.973</v>
+        <v>1535.693</v>
       </c>
       <c r="I1226" t="n">
         <v>0.0</v>
@@ -45452,7 +45452,7 @@
         </is>
       </c>
       <c r="E1227" t="n">
-        <v>2584.402</v>
+        <v>1911.3408000000002</v>
       </c>
       <c r="F1227" t="n">
         <v>1.7750000000000001</v>
@@ -45461,10 +45461,10 @@
         <v>12.426</v>
       </c>
       <c r="H1227" t="n">
-        <v>2584.402</v>
+        <v>1737.381</v>
       </c>
       <c r="I1227" t="n">
-        <v>0.0</v>
+        <v>173.9598</v>
       </c>
     </row>
     <row r="1228">
@@ -45489,7 +45489,7 @@
         </is>
       </c>
       <c r="E1228" t="n">
-        <v>3236.6</v>
+        <v>3230.683</v>
       </c>
       <c r="F1228" t="n">
         <v>0.0</v>
@@ -45498,7 +45498,7 @@
         <v>0.0</v>
       </c>
       <c r="H1228" t="n">
-        <v>3236.6</v>
+        <v>3230.683</v>
       </c>
       <c r="I1228" t="n">
         <v>0.0</v>
@@ -45563,7 +45563,7 @@
         </is>
       </c>
       <c r="E1230" t="n">
-        <v>659.154</v>
+        <v>654.864</v>
       </c>
       <c r="F1230" t="n">
         <v>0.444</v>
@@ -45572,7 +45572,7 @@
         <v>0.0</v>
       </c>
       <c r="H1230" t="n">
-        <v>659.154</v>
+        <v>654.864</v>
       </c>
       <c r="I1230" t="n">
         <v>0.0</v>
@@ -45600,7 +45600,7 @@
         </is>
       </c>
       <c r="E1231" t="n">
-        <v>3296.934</v>
+        <v>2503.632</v>
       </c>
       <c r="F1231" t="n">
         <v>473.677</v>
@@ -45609,10 +45609,10 @@
         <v>0.0</v>
       </c>
       <c r="H1231" t="n">
-        <v>3296.934</v>
+        <v>2467.242</v>
       </c>
       <c r="I1231" t="n">
-        <v>0.0</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="1232">
@@ -45711,7 +45711,7 @@
         </is>
       </c>
       <c r="E1234" t="n">
-        <v>3450.795</v>
+        <v>3430.676</v>
       </c>
       <c r="F1234" t="n">
         <v>0.0</v>
@@ -45720,7 +45720,7 @@
         <v>0.0</v>
       </c>
       <c r="H1234" t="n">
-        <v>3450.795</v>
+        <v>3430.676</v>
       </c>
       <c r="I1234" t="n">
         <v>0.0</v>
@@ -46081,7 +46081,7 @@
         </is>
       </c>
       <c r="E1244" t="n">
-        <v>0.0</v>
+        <v>135.856</v>
       </c>
       <c r="F1244" t="n">
         <v>0.0</v>
@@ -46093,7 +46093,7 @@
         <v>0.0</v>
       </c>
       <c r="I1244" t="n">
-        <v>0.0</v>
+        <v>135.856</v>
       </c>
     </row>
     <row r="1245">
@@ -46118,7 +46118,7 @@
         </is>
       </c>
       <c r="E1245" t="n">
-        <v>410.731</v>
+        <v>6702.3866</v>
       </c>
       <c r="F1245" t="n">
         <v>0.0</v>
@@ -46127,10 +46127,10 @@
         <v>0.0</v>
       </c>
       <c r="H1245" t="n">
-        <v>410.731</v>
+        <v>406.06399999999996</v>
       </c>
       <c r="I1245" t="n">
-        <v>0.0</v>
+        <v>6296.3225999999995</v>
       </c>
     </row>
     <row r="1246">
@@ -46155,7 +46155,7 @@
         </is>
       </c>
       <c r="E1246" t="n">
-        <v>2533.896</v>
+        <v>2523.862</v>
       </c>
       <c r="F1246" t="n">
         <v>0.8170000000000001</v>
@@ -46164,7 +46164,7 @@
         <v>0.0</v>
       </c>
       <c r="H1246" t="n">
-        <v>2533.896</v>
+        <v>2523.862</v>
       </c>
       <c r="I1246" t="n">
         <v>0.0</v>
@@ -46192,7 +46192,7 @@
         </is>
       </c>
       <c r="E1247" t="n">
-        <v>1475.81</v>
+        <v>1472.076</v>
       </c>
       <c r="F1247" t="n">
         <v>0.35100000000000003</v>
@@ -46201,7 +46201,7 @@
         <v>0.0</v>
       </c>
       <c r="H1247" t="n">
-        <v>1475.81</v>
+        <v>1472.076</v>
       </c>
       <c r="I1247" t="n">
         <v>0.0</v>
@@ -46303,7 +46303,7 @@
         </is>
       </c>
       <c r="E1250" t="n">
-        <v>676.215</v>
+        <v>642.06</v>
       </c>
       <c r="F1250" t="n">
         <v>0.0</v>
@@ -46312,7 +46312,7 @@
         <v>1.35</v>
       </c>
       <c r="H1250" t="n">
-        <v>676.215</v>
+        <v>642.06</v>
       </c>
       <c r="I1250" t="n">
         <v>0.0</v>
@@ -46414,7 +46414,7 @@
         </is>
       </c>
       <c r="E1253" t="n">
-        <v>1192.6200000000001</v>
+        <v>1189.1000000000001</v>
       </c>
       <c r="F1253" t="n">
         <v>0.22</v>
@@ -46423,7 +46423,7 @@
         <v>0.22</v>
       </c>
       <c r="H1253" t="n">
-        <v>1192.6200000000001</v>
+        <v>1189.1000000000001</v>
       </c>
       <c r="I1253" t="n">
         <v>0.0</v>
@@ -47006,7 +47006,7 @@
         </is>
       </c>
       <c r="E1269" t="n">
-        <v>0.0</v>
+        <v>2562.24</v>
       </c>
       <c r="F1269" t="n">
         <v>0.0</v>
@@ -47018,7 +47018,7 @@
         <v>0.0</v>
       </c>
       <c r="I1269" t="n">
-        <v>0.0</v>
+        <v>2562.24</v>
       </c>
     </row>
     <row r="1270">
@@ -48301,19 +48301,19 @@
         </is>
       </c>
       <c r="E1304" t="n">
-        <v>7220.1884</v>
+        <v>9938.1596</v>
       </c>
       <c r="F1304" t="n">
         <v>8.956000000000001</v>
       </c>
       <c r="G1304" t="n">
-        <v>4.622</v>
+        <v>2722.594</v>
       </c>
       <c r="H1304" t="n">
         <v>6314.198</v>
       </c>
       <c r="I1304" t="n">
-        <v>905.9904</v>
+        <v>3623.9616</v>
       </c>
     </row>
     <row r="1305">
@@ -48338,7 +48338,7 @@
         </is>
       </c>
       <c r="E1305" t="n">
-        <v>970.7152</v>
+        <v>0.0</v>
       </c>
       <c r="F1305" t="n">
         <v>0.0</v>
@@ -48350,7 +48350,7 @@
         <v>0.0</v>
       </c>
       <c r="I1305" t="n">
-        <v>970.7152</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1306">
@@ -48375,7 +48375,7 @@
         </is>
       </c>
       <c r="E1306" t="n">
-        <v>6502.157999999999</v>
+        <v>2795.306</v>
       </c>
       <c r="F1306" t="n">
         <v>0.0</v>
@@ -48387,7 +48387,7 @@
         <v>2795.306</v>
       </c>
       <c r="I1306" t="n">
-        <v>3706.852</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1307">
@@ -48412,7 +48412,7 @@
         </is>
       </c>
       <c r="E1307" t="n">
-        <v>5968.8</v>
+        <v>3978.4</v>
       </c>
       <c r="F1307" t="n">
         <v>0.0</v>
@@ -48424,7 +48424,7 @@
         <v>3978.4</v>
       </c>
       <c r="I1307" t="n">
-        <v>1990.4</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="1308">
@@ -49337,7 +49337,7 @@
         </is>
       </c>
       <c r="E1332" t="n">
-        <v>213.0</v>
+        <v>245.0</v>
       </c>
       <c r="F1332" t="n">
         <v>0.0</v>
@@ -49346,7 +49346,7 @@
         <v>0.0</v>
       </c>
       <c r="H1332" t="n">
-        <v>213.0</v>
+        <v>245.0</v>
       </c>
       <c r="I1332" t="n">
         <v>0.0</v>
@@ -49596,7 +49596,7 @@
         </is>
       </c>
       <c r="E1339" t="n">
-        <v>3034.0</v>
+        <v>2956.0</v>
       </c>
       <c r="F1339" t="n">
         <v>0.0</v>
@@ -49605,7 +49605,7 @@
         <v>0.0</v>
       </c>
       <c r="H1339" t="n">
-        <v>3034.0</v>
+        <v>2956.0</v>
       </c>
       <c r="I1339" t="n">
         <v>0.0</v>
@@ -49744,7 +49744,7 @@
         </is>
       </c>
       <c r="E1343" t="n">
-        <v>4528.0</v>
+        <v>3592.0</v>
       </c>
       <c r="F1343" t="n">
         <v>0.0</v>
@@ -49753,7 +49753,7 @@
         <v>0.0</v>
       </c>
       <c r="H1343" t="n">
-        <v>4528.0</v>
+        <v>3592.0</v>
       </c>
       <c r="I1343" t="n">
         <v>0.0</v>
@@ -50225,7 +50225,7 @@
         </is>
       </c>
       <c r="E1356" t="n">
-        <v>516.0</v>
+        <v>420.0</v>
       </c>
       <c r="F1356" t="n">
         <v>0.0</v>
@@ -50234,7 +50234,7 @@
         <v>0.0</v>
       </c>
       <c r="H1356" t="n">
-        <v>516.0</v>
+        <v>420.0</v>
       </c>
       <c r="I1356" t="n">
         <v>0.0</v>
@@ -51187,7 +51187,7 @@
         </is>
       </c>
       <c r="E1382" t="n">
-        <v>0.012</v>
+        <v>125.84</v>
       </c>
       <c r="F1382" t="n">
         <v>0.0</v>
@@ -51196,7 +51196,7 @@
         <v>0.0</v>
       </c>
       <c r="H1382" t="n">
-        <v>0.012</v>
+        <v>125.84</v>
       </c>
       <c r="I1382" t="n">
         <v>0.0</v>
@@ -51557,7 +51557,7 @@
         </is>
       </c>
       <c r="E1392" t="n">
-        <v>823.5</v>
+        <v>643.5</v>
       </c>
       <c r="F1392" t="n">
         <v>0.0</v>
@@ -51566,7 +51566,7 @@
         <v>90.0</v>
       </c>
       <c r="H1392" t="n">
-        <v>823.5</v>
+        <v>643.5</v>
       </c>
       <c r="I1392" t="n">
         <v>0.0</v>
@@ -51890,7 +51890,7 @@
         </is>
       </c>
       <c r="E1401" t="n">
-        <v>3121.662</v>
+        <v>3081.63</v>
       </c>
       <c r="F1401" t="n">
         <v>0.0</v>
@@ -51899,7 +51899,7 @@
         <v>236.85600000000002</v>
       </c>
       <c r="H1401" t="n">
-        <v>3121.662</v>
+        <v>3081.63</v>
       </c>
       <c r="I1401" t="n">
         <v>0.0</v>
@@ -51927,7 +51927,7 @@
         </is>
       </c>
       <c r="E1402" t="n">
-        <v>477.059</v>
+        <v>471.061</v>
       </c>
       <c r="F1402" t="n">
         <v>0.416</v>
@@ -51936,7 +51936,7 @@
         <v>0.0</v>
       </c>
       <c r="H1402" t="n">
-        <v>477.059</v>
+        <v>471.061</v>
       </c>
       <c r="I1402" t="n">
         <v>0.0</v>
@@ -51964,7 +51964,7 @@
         </is>
       </c>
       <c r="E1403" t="n">
-        <v>609.486</v>
+        <v>598.811</v>
       </c>
       <c r="F1403" t="n">
         <v>0.5559999999999999</v>
@@ -51973,7 +51973,7 @@
         <v>0.0</v>
       </c>
       <c r="H1403" t="n">
-        <v>609.486</v>
+        <v>598.811</v>
       </c>
       <c r="I1403" t="n">
         <v>0.0</v>
@@ -52556,7 +52556,7 @@
         </is>
       </c>
       <c r="E1419" t="n">
-        <v>56.2</v>
+        <v>55.599999999999994</v>
       </c>
       <c r="F1419" t="n">
         <v>0.4</v>
@@ -52565,7 +52565,7 @@
         <v>0.0</v>
       </c>
       <c r="H1419" t="n">
-        <v>56.2</v>
+        <v>55.599999999999994</v>
       </c>
       <c r="I1419" t="n">
         <v>0.0</v>
@@ -52704,7 +52704,7 @@
         </is>
       </c>
       <c r="E1423" t="n">
-        <v>1272.489</v>
+        <v>1269.82</v>
       </c>
       <c r="F1423" t="n">
         <v>0.0</v>
@@ -52713,7 +52713,7 @@
         <v>2.669</v>
       </c>
       <c r="H1423" t="n">
-        <v>1272.489</v>
+        <v>1269.82</v>
       </c>
       <c r="I1423" t="n">
         <v>0.0</v>
@@ -52741,7 +52741,7 @@
         </is>
       </c>
       <c r="E1424" t="n">
-        <v>29.304</v>
+        <v>51.8</v>
       </c>
       <c r="F1424" t="n">
         <v>0.0</v>
@@ -52750,7 +52750,7 @@
         <v>0.0</v>
       </c>
       <c r="H1424" t="n">
-        <v>29.304</v>
+        <v>51.8</v>
       </c>
       <c r="I1424" t="n">
         <v>0.0</v>
@@ -52778,7 +52778,7 @@
         </is>
       </c>
       <c r="E1425" t="n">
-        <v>160.8</v>
+        <v>159.84</v>
       </c>
       <c r="F1425" t="n">
         <v>0.0</v>
@@ -52787,7 +52787,7 @@
         <v>0.0</v>
       </c>
       <c r="H1425" t="n">
-        <v>160.8</v>
+        <v>159.84</v>
       </c>
       <c r="I1425" t="n">
         <v>0.0</v>
@@ -53148,16 +53148,16 @@
         </is>
       </c>
       <c r="E1435" t="n">
-        <v>0.0</v>
+        <v>192.154</v>
       </c>
       <c r="F1435" t="n">
         <v>0.0</v>
       </c>
       <c r="G1435" t="n">
-        <v>205.498</v>
+        <v>13.344</v>
       </c>
       <c r="H1435" t="n">
-        <v>0.0</v>
+        <v>192.154</v>
       </c>
       <c r="I1435" t="n">
         <v>0.0</v>
@@ -53222,7 +53222,7 @@
         </is>
       </c>
       <c r="E1437" t="n">
-        <v>2508.839</v>
+        <v>2476.813</v>
       </c>
       <c r="F1437" t="n">
         <v>0.0</v>
@@ -53231,7 +53231,7 @@
         <v>0.222</v>
       </c>
       <c r="H1437" t="n">
-        <v>2508.839</v>
+        <v>2476.813</v>
       </c>
       <c r="I1437" t="n">
         <v>0.0</v>
@@ -53259,7 +53259,7 @@
         </is>
       </c>
       <c r="E1438" t="n">
-        <v>255.096</v>
+        <v>208.21</v>
       </c>
       <c r="F1438" t="n">
         <v>0.0</v>
@@ -53268,7 +53268,7 @@
         <v>0.0</v>
       </c>
       <c r="H1438" t="n">
-        <v>255.096</v>
+        <v>208.21</v>
       </c>
       <c r="I1438" t="n">
         <v>0.0</v>
@@ -53376,7 +53376,7 @@
         <v>0.0</v>
       </c>
       <c r="G1441" t="n">
-        <v>0.0</v>
+        <v>480.38399999999996</v>
       </c>
       <c r="H1441" t="n">
         <v>3464.603</v>
@@ -53444,7 +53444,7 @@
         </is>
       </c>
       <c r="E1443" t="n">
-        <v>1575.928</v>
+        <v>1562.582</v>
       </c>
       <c r="F1443" t="n">
         <v>0.44499999999999995</v>
@@ -53453,7 +53453,7 @@
         <v>110.866</v>
       </c>
       <c r="H1443" t="n">
-        <v>1575.928</v>
+        <v>1562.582</v>
       </c>
       <c r="I1443" t="n">
         <v>0.0</v>
@@ -53925,7 +53925,7 @@
         </is>
       </c>
       <c r="E1456" t="n">
-        <v>146.875</v>
+        <v>145.375</v>
       </c>
       <c r="F1456" t="n">
         <v>5.625</v>
@@ -53934,7 +53934,7 @@
         <v>70.5</v>
       </c>
       <c r="H1456" t="n">
-        <v>146.875</v>
+        <v>145.375</v>
       </c>
       <c r="I1456" t="n">
         <v>0.0</v>
@@ -53962,7 +53962,7 @@
         </is>
       </c>
       <c r="E1457" t="n">
-        <v>9.5</v>
+        <v>3.375</v>
       </c>
       <c r="F1457" t="n">
         <v>0.0</v>
@@ -53971,7 +53971,7 @@
         <v>33.75</v>
       </c>
       <c r="H1457" t="n">
-        <v>9.5</v>
+        <v>3.375</v>
       </c>
       <c r="I1457" t="n">
         <v>0.0</v>
@@ -53999,7 +53999,7 @@
         </is>
       </c>
       <c r="E1458" t="n">
-        <v>432.372</v>
+        <v>423.372</v>
       </c>
       <c r="F1458" t="n">
         <v>0.0</v>
@@ -54008,7 +54008,7 @@
         <v>40.5</v>
       </c>
       <c r="H1458" t="n">
-        <v>432.372</v>
+        <v>423.372</v>
       </c>
       <c r="I1458" t="n">
         <v>0.0</v>
@@ -54036,7 +54036,7 @@
         </is>
       </c>
       <c r="E1459" t="n">
-        <v>1211.213</v>
+        <v>1211.212</v>
       </c>
       <c r="F1459" t="n">
         <v>0.0</v>
@@ -54045,7 +54045,7 @@
         <v>10.666</v>
       </c>
       <c r="H1459" t="n">
-        <v>1211.213</v>
+        <v>1211.212</v>
       </c>
       <c r="I1459" t="n">
         <v>0.0</v>
@@ -54073,7 +54073,7 @@
         </is>
       </c>
       <c r="E1460" t="n">
-        <v>503.25</v>
+        <v>502.5</v>
       </c>
       <c r="F1460" t="n">
         <v>0.0</v>
@@ -54082,7 +54082,7 @@
         <v>20.625</v>
       </c>
       <c r="H1460" t="n">
-        <v>503.25</v>
+        <v>502.5</v>
       </c>
       <c r="I1460" t="n">
         <v>0.0</v>
@@ -54110,7 +54110,7 @@
         </is>
       </c>
       <c r="E1461" t="n">
-        <v>215.0</v>
+        <v>210.875</v>
       </c>
       <c r="F1461" t="n">
         <v>0.0</v>
@@ -54119,7 +54119,7 @@
         <v>6.75</v>
       </c>
       <c r="H1461" t="n">
-        <v>215.0</v>
+        <v>210.875</v>
       </c>
       <c r="I1461" t="n">
         <v>0.0</v>
@@ -54221,7 +54221,7 @@
         </is>
       </c>
       <c r="E1464" t="n">
-        <v>670.625</v>
+        <v>667.625</v>
       </c>
       <c r="F1464" t="n">
         <v>0.375</v>
@@ -54230,7 +54230,7 @@
         <v>3.75</v>
       </c>
       <c r="H1464" t="n">
-        <v>670.625</v>
+        <v>667.625</v>
       </c>
       <c r="I1464" t="n">
         <v>0.0</v>
@@ -54295,7 +54295,7 @@
         </is>
       </c>
       <c r="E1466" t="n">
-        <v>301.0</v>
+        <v>295.0</v>
       </c>
       <c r="F1466" t="n">
         <v>0.0</v>
@@ -54304,7 +54304,7 @@
         <v>0.0</v>
       </c>
       <c r="H1466" t="n">
-        <v>301.0</v>
+        <v>295.0</v>
       </c>
       <c r="I1466" t="n">
         <v>0.0</v>
@@ -54332,7 +54332,7 @@
         </is>
       </c>
       <c r="E1467" t="n">
-        <v>884.75</v>
+        <v>881.75</v>
       </c>
       <c r="F1467" t="n">
         <v>0.0</v>
@@ -54341,7 +54341,7 @@
         <v>0.75</v>
       </c>
       <c r="H1467" t="n">
-        <v>884.75</v>
+        <v>881.75</v>
       </c>
       <c r="I1467" t="n">
         <v>0.0</v>
@@ -54369,7 +54369,7 @@
         </is>
       </c>
       <c r="E1468" t="n">
-        <v>164.25</v>
+        <v>163.5</v>
       </c>
       <c r="F1468" t="n">
         <v>0.0</v>
@@ -54378,7 +54378,7 @@
         <v>55.5</v>
       </c>
       <c r="H1468" t="n">
-        <v>164.25</v>
+        <v>163.5</v>
       </c>
       <c r="I1468" t="n">
         <v>0.0</v>
@@ -54443,7 +54443,7 @@
         </is>
       </c>
       <c r="E1470" t="n">
-        <v>3195.0</v>
+        <v>3194.25</v>
       </c>
       <c r="F1470" t="n">
         <v>0.0</v>
@@ -54452,7 +54452,7 @@
         <v>38.25</v>
       </c>
       <c r="H1470" t="n">
-        <v>3195.0</v>
+        <v>3194.25</v>
       </c>
       <c r="I1470" t="n">
         <v>0.0</v>
@@ -54480,7 +54480,7 @@
         </is>
       </c>
       <c r="E1471" t="n">
-        <v>592.5</v>
+        <v>591.0</v>
       </c>
       <c r="F1471" t="n">
         <v>0.0</v>
@@ -54489,7 +54489,7 @@
         <v>0.0</v>
       </c>
       <c r="H1471" t="n">
-        <v>592.5</v>
+        <v>591.0</v>
       </c>
       <c r="I1471" t="n">
         <v>0.0</v>
@@ -54554,7 +54554,7 @@
         </is>
       </c>
       <c r="E1473" t="n">
-        <v>1078.861</v>
+        <v>1078.862</v>
       </c>
       <c r="F1473" t="n">
         <v>0.5</v>
@@ -54563,7 +54563,7 @@
         <v>0.0</v>
       </c>
       <c r="H1473" t="n">
-        <v>1078.861</v>
+        <v>1078.862</v>
       </c>
       <c r="I1473" t="n">
         <v>0.0</v>
@@ -54591,7 +54591,7 @@
         </is>
       </c>
       <c r="E1474" t="n">
-        <v>1978.803</v>
+        <v>1976.134</v>
       </c>
       <c r="F1474" t="n">
         <v>1.1119999999999999</v>
@@ -54600,7 +54600,7 @@
         <v>10.229999999999999</v>
       </c>
       <c r="H1474" t="n">
-        <v>1978.803</v>
+        <v>1976.134</v>
       </c>
       <c r="I1474" t="n">
         <v>0.0</v>
@@ -54665,7 +54665,7 @@
         </is>
       </c>
       <c r="E1476" t="n">
-        <v>0.0</v>
+        <v>14.095</v>
       </c>
       <c r="F1476" t="n">
         <v>0.0</v>
@@ -54674,7 +54674,7 @@
         <v>0.0</v>
       </c>
       <c r="H1476" t="n">
-        <v>0.0</v>
+        <v>14.095</v>
       </c>
       <c r="I1476" t="n">
         <v>0.0</v>
@@ -55146,7 +55146,7 @@
         </is>
       </c>
       <c r="E1489" t="n">
-        <v>637.177</v>
+        <v>637.1759999999999</v>
       </c>
       <c r="F1489" t="n">
         <v>0.0</v>
@@ -55155,7 +55155,7 @@
         <v>0.0</v>
       </c>
       <c r="H1489" t="n">
-        <v>637.177</v>
+        <v>637.1759999999999</v>
       </c>
       <c r="I1489" t="n">
         <v>0.0</v>
@@ -55183,7 +55183,7 @@
         </is>
       </c>
       <c r="E1490" t="n">
-        <v>251.702</v>
+        <v>239.693</v>
       </c>
       <c r="F1490" t="n">
         <v>0.0</v>
@@ -55192,7 +55192,7 @@
         <v>0.0</v>
       </c>
       <c r="H1490" t="n">
-        <v>251.702</v>
+        <v>239.693</v>
       </c>
       <c r="I1490" t="n">
         <v>0.0</v>
@@ -55220,7 +55220,7 @@
         </is>
       </c>
       <c r="E1491" t="n">
-        <v>4037.898</v>
+        <v>4037.894</v>
       </c>
       <c r="F1491" t="n">
         <v>0.0</v>
@@ -55229,7 +55229,7 @@
         <v>747.264</v>
       </c>
       <c r="H1491" t="n">
-        <v>4037.898</v>
+        <v>4037.894</v>
       </c>
       <c r="I1491" t="n">
         <v>0.0</v>
@@ -55331,7 +55331,7 @@
         </is>
       </c>
       <c r="E1494" t="n">
-        <v>5502.472</v>
+        <v>5276.349999999999</v>
       </c>
       <c r="F1494" t="n">
         <v>0.9169999999999999</v>
@@ -55340,7 +55340,7 @@
         <v>661.475</v>
       </c>
       <c r="H1494" t="n">
-        <v>5502.472</v>
+        <v>5276.349999999999</v>
       </c>
       <c r="I1494" t="n">
         <v>0.0</v>
@@ -55368,7 +55368,7 @@
         </is>
       </c>
       <c r="E1495" t="n">
-        <v>2251.399</v>
+        <v>2249.566</v>
       </c>
       <c r="F1495" t="n">
         <v>65.467</v>
@@ -55377,7 +55377,7 @@
         <v>125.76200000000001</v>
       </c>
       <c r="H1495" t="n">
-        <v>2251.399</v>
+        <v>2249.566</v>
       </c>
       <c r="I1495" t="n">
         <v>0.0</v>
@@ -55664,7 +55664,7 @@
         </is>
       </c>
       <c r="E1503" t="n">
-        <v>5294.400000000001</v>
+        <v>5277.6</v>
       </c>
       <c r="F1503" t="n">
         <v>2.4</v>
@@ -55673,7 +55673,7 @@
         <v>0.0</v>
       </c>
       <c r="H1503" t="n">
-        <v>5294.400000000001</v>
+        <v>5277.6</v>
       </c>
       <c r="I1503" t="n">
         <v>0.0</v>
@@ -55771,7 +55771,7 @@
       </c>
       <c r="D1506" t="inlineStr">
         <is>
-          <t>4987176392039</t>
+          <t>4987176365262</t>
         </is>
       </c>
       <c r="E1506" t="n">
@@ -55941,22 +55941,22 @@
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>Oral Care</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="B1511" t="inlineStr">
         <is>
-          <t>83907567</t>
+          <t>83907339</t>
         </is>
       </c>
       <c r="C1511" t="inlineStr">
         <is>
-          <t>OB GLIDE comfort floss 40m 8P Costco</t>
+          <t>PTN ROT (400MLX3)X14 SDC ATTN COSTCO STK</t>
         </is>
       </c>
       <c r="D1511" t="inlineStr">
         <is>
-          <t>4987176353382</t>
+          <t>4987176266279</t>
         </is>
       </c>
       <c r="E1511" t="n">
@@ -55983,17 +55983,17 @@
       </c>
       <c r="B1512" t="inlineStr">
         <is>
-          <t>83907925</t>
+          <t>83907567</t>
         </is>
       </c>
       <c r="C1512" t="inlineStr">
         <is>
-          <t>ORALB MOC Expert9000 7ct KR EME2</t>
+          <t>OB GLIDE comfort floss 40m 8P Costco</t>
         </is>
       </c>
       <c r="D1512" t="inlineStr">
         <is>
-          <t>4987176384782</t>
+          <t>4987176353382</t>
         </is>
       </c>
       <c r="E1512" t="n">
@@ -56015,22 +56015,22 @@
     <row r="1513">
       <c r="A1513" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Oral Care</t>
         </is>
       </c>
       <c r="B1513" t="inlineStr">
         <is>
-          <t>83908048</t>
+          <t>83907925</t>
         </is>
       </c>
       <c r="C1513" t="inlineStr">
         <is>
-          <t>LENOR LFE 4LX3 BTL Musk KR ship (CM) D2</t>
+          <t>ORALB MOC Expert9000 7ct KR EME2</t>
         </is>
       </c>
       <c r="D1513" t="inlineStr">
         <is>
-          <t>4987176333230</t>
+          <t>4987176384782</t>
         </is>
       </c>
       <c r="E1513" t="n">
@@ -56052,22 +56052,22 @@
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>Appliances</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B1514" t="inlineStr">
         <is>
-          <t>83908964</t>
+          <t>83908048</t>
         </is>
       </c>
       <c r="C1514" t="inlineStr">
         <is>
-          <t>BRAUN MALHRREMKP CCR8 Costco</t>
+          <t>LENOR LFE 4LX3 BTL Musk KR ship (CM) D2</t>
         </is>
       </c>
       <c r="D1514" t="inlineStr">
         <is>
-          <t>4987176177155</t>
+          <t>4987176333230</t>
         </is>
       </c>
       <c r="E1514" t="n">
@@ -56094,17 +56094,17 @@
       </c>
       <c r="B1515" t="inlineStr">
         <is>
-          <t>83908965</t>
+          <t>83908964</t>
         </is>
       </c>
       <c r="C1515" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER 9665cc+ PC Bundle</t>
+          <t>BRAUN MALHRREMKP CCR8 Costco</t>
         </is>
       </c>
       <c r="D1515" t="inlineStr">
         <is>
-          <t>4987176340788</t>
+          <t>4987176177155</t>
         </is>
       </c>
       <c r="E1515" t="n">
@@ -56131,17 +56131,17 @@
       </c>
       <c r="B1516" t="inlineStr">
         <is>
-          <t>83908966</t>
+          <t>83908965</t>
         </is>
       </c>
       <c r="C1516" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER 9667cc+ PC bundle</t>
+          <t>BRAUN SHAVER 9665cc+ PC Bundle</t>
         </is>
       </c>
       <c r="D1516" t="inlineStr">
         <is>
-          <t>4987176340771</t>
+          <t>4987176340788</t>
         </is>
       </c>
       <c r="E1516" t="n">
@@ -56168,17 +56168,17 @@
       </c>
       <c r="B1517" t="inlineStr">
         <is>
-          <t>83908967</t>
+          <t>83908966</t>
         </is>
       </c>
       <c r="C1517" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER 9660cc+ PC bundle</t>
+          <t>BRAUN SHAVER 9667cc+ PC bundle</t>
         </is>
       </c>
       <c r="D1517" t="inlineStr">
         <is>
-          <t>4987176340764</t>
+          <t>4987176340771</t>
         </is>
       </c>
       <c r="E1517" t="n">
@@ -56205,17 +56205,17 @@
       </c>
       <c r="B1518" t="inlineStr">
         <is>
-          <t>83908968</t>
+          <t>83908967</t>
         </is>
       </c>
       <c r="C1518" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER 8663cc BLK X4 KR COSTCO</t>
+          <t>BRAUN SHAVER 9660cc+ PC bundle</t>
         </is>
       </c>
       <c r="D1518" t="inlineStr">
         <is>
-          <t>4987176269683</t>
+          <t>4987176340764</t>
         </is>
       </c>
       <c r="E1518" t="n">
@@ -56237,22 +56237,22 @@
     <row r="1519">
       <c r="A1519" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="B1519" t="inlineStr">
         <is>
-          <t>83909758</t>
+          <t>83908968</t>
         </is>
       </c>
       <c r="C1519" t="inlineStr">
         <is>
-          <t>Gil PS Pwr 4UP+PG Gel 170G 1x6 OY</t>
+          <t>BRAUN SHAVER 8663cc BLK X4 KR COSTCO</t>
         </is>
       </c>
       <c r="D1519" t="inlineStr">
         <is>
-          <t>4987176273413</t>
+          <t>4987176269683</t>
         </is>
       </c>
       <c r="E1519" t="n">
@@ -56274,22 +56274,22 @@
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="B1520" t="inlineStr">
         <is>
-          <t>83912510</t>
+          <t>83909499</t>
         </is>
       </c>
       <c r="C1520" t="inlineStr">
         <is>
-          <t>699 Labs 2up+Gel+T/B(OY)</t>
+          <t>BRAUN SHAVER 8667cc SILV X4 KR COSTCO</t>
         </is>
       </c>
       <c r="D1520" t="inlineStr">
         <is>
-          <t>4987176399106</t>
+          <t>4987176269690</t>
         </is>
       </c>
       <c r="E1520" t="n">
@@ -56316,32 +56316,106 @@
       </c>
       <c r="B1521" t="inlineStr">
         <is>
+          <t>83909758</t>
+        </is>
+      </c>
+      <c r="C1521" t="inlineStr">
+        <is>
+          <t>Gil PS Pwr 4UP+PG Gel 170G 1x6 OY</t>
+        </is>
+      </c>
+      <c r="D1521" t="inlineStr">
+        <is>
+          <t>4987176273413</t>
+        </is>
+      </c>
+      <c r="E1521" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F1521" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G1521" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H1521" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I1521" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="inlineStr">
+        <is>
+          <t>Shave Care</t>
+        </is>
+      </c>
+      <c r="B1522" t="inlineStr">
+        <is>
+          <t>83912510</t>
+        </is>
+      </c>
+      <c r="C1522" t="inlineStr">
+        <is>
+          <t>699 Labs 2up+Gel+T/B(OY)</t>
+        </is>
+      </c>
+      <c r="D1522" t="inlineStr">
+        <is>
+          <t>4987176399106</t>
+        </is>
+      </c>
+      <c r="E1522" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F1522" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G1522" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H1522" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I1522" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="inlineStr">
+        <is>
+          <t>Shave Care</t>
+        </is>
+      </c>
+      <c r="B1523" t="inlineStr">
+        <is>
           <t>83913156</t>
         </is>
       </c>
-      <c r="C1521" t="inlineStr">
+      <c r="C1523" t="inlineStr">
         <is>
           <t>Gil PSY Mnl 16CT+PG Gel 170G 1x12 CP</t>
         </is>
       </c>
-      <c r="D1521" t="inlineStr">
+      <c r="D1523" t="inlineStr">
         <is>
           <t>4987176259110</t>
         </is>
       </c>
-      <c r="E1521" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F1521" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G1521" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H1521" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I1521" t="n">
+      <c r="E1523" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F1523" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G1523" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H1523" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I1523" t="n">
         <v>0.0</v>
       </c>
     </row>
@@ -56619,13 +56693,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20E4BC83-F086-4A73-9200-1A7006B13F6E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79DB5E03-2F62-42F3-B38E-6028B5A0D6C4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6FBAC6D-0AD6-4686-91EB-D06E7082B730}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58A5018D-408E-4D03-BD7D-75A8269BD250}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E675CD6A-708A-4EEF-8BF0-E6B3E3535CBC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A52914F7-B6B5-417D-B7D3-C348570B39F9}"/>
 </file>